--- a/Deliverables/SM_Top Board/_BOM/eSpark BOM (20 Boards).xlsx
+++ b/Deliverables/SM_Top Board/_BOM/eSpark BOM (20 Boards).xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Faizan\GitHub\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="12555"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15480" windowHeight="7872"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="473">
   <si>
     <t>Component list</t>
   </si>
@@ -202,9 +202,6 @@
     <t>R10, R11, R12, R13</t>
   </si>
   <si>
-    <t>R14, R15, R16, R17, R18, R19, R20, R26</t>
-  </si>
-  <si>
     <t>R21</t>
   </si>
   <si>
@@ -229,18 +226,9 @@
     <t>R29</t>
   </si>
   <si>
-    <t>R30</t>
-  </si>
-  <si>
-    <t>R31</t>
-  </si>
-  <si>
     <t>R33, R46</t>
   </si>
   <si>
-    <t>R34</t>
-  </si>
-  <si>
     <t>R35, R39</t>
   </si>
   <si>
@@ -487,15 +475,9 @@
     <t>Res Thick Film 0603 100K Ohm 5% 1/10W 100ppm/C Molded SMD SMD Paper T/R</t>
   </si>
   <si>
-    <t>RES SMD 100K OHM 0.1% 1/10W 0603</t>
-  </si>
-  <si>
     <t>RES SMD 51R 100mW 0603</t>
   </si>
   <si>
-    <t>RES SMD 150 OHM 5% 1/20W 0201</t>
-  </si>
-  <si>
     <t>RES SMD 2K OHM 1% 1/10W 0603</t>
   </si>
   <si>
@@ -811,15 +793,9 @@
     <t>RC0603JR-07100KL</t>
   </si>
   <si>
-    <t>RT0603BRD07100KL</t>
-  </si>
-  <si>
     <t>RC0603FR-0751RL</t>
   </si>
   <si>
-    <t>CRCW0201150RJNED</t>
-  </si>
-  <si>
     <t>RC0603FR-072KL</t>
   </si>
   <si>
@@ -934,9 +910,6 @@
     <t>Panasonic</t>
   </si>
   <si>
-    <t>Vishay Dale</t>
-  </si>
-  <si>
     <t>UNI-ROYAL</t>
   </si>
   <si>
@@ -1364,16 +1337,163 @@
   </si>
   <si>
     <t>Mouser</t>
+  </si>
+  <si>
+    <t>C144395</t>
+  </si>
+  <si>
+    <t>C93225</t>
+  </si>
+  <si>
+    <t>C281265</t>
+  </si>
+  <si>
+    <t>Chipmall</t>
+  </si>
+  <si>
+    <t>NACSemi</t>
+  </si>
+  <si>
+    <t>Available for Lower cost in China</t>
+  </si>
+  <si>
+    <t>DO NOT MOUNT</t>
+  </si>
+  <si>
+    <t>AO4882-MS</t>
+  </si>
+  <si>
+    <t>C2847038</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Quantity changed from 8/board to 4/board because alternate part is MOSFET 2N Array. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Design change required</t>
+    </r>
+  </si>
+  <si>
+    <t>C14677</t>
+  </si>
+  <si>
+    <t>C114616</t>
+  </si>
+  <si>
+    <t>C322001</t>
+  </si>
+  <si>
+    <t>C100044</t>
+  </si>
+  <si>
+    <t>C114623</t>
+  </si>
+  <si>
+    <t>LR2512-22R033F4</t>
+  </si>
+  <si>
+    <t>C2681032</t>
+  </si>
+  <si>
+    <t>C114608</t>
+  </si>
+  <si>
+    <t>C137801</t>
+  </si>
+  <si>
+    <t>C137798</t>
+  </si>
+  <si>
+    <t>C227561</t>
+  </si>
+  <si>
+    <t>C141685</t>
+  </si>
+  <si>
+    <t>ARG03FTC1273</t>
+  </si>
+  <si>
+    <t>C217715</t>
+  </si>
+  <si>
+    <t>C100048</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">R30, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R31</t>
+    </r>
+  </si>
+  <si>
+    <t>C114628</t>
+  </si>
+  <si>
+    <t>Two different part numbers for 100K merged into single part number. Changes highlighted</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">R14, R15, R16, R17, R18, R19, R20, R26, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R34</t>
+    </r>
+  </si>
+  <si>
+    <t>Two different part numbers for 150R merged into single part number. Changes highlighted</t>
+  </si>
+  <si>
+    <t>C105576</t>
+  </si>
+  <si>
+    <t>TME</t>
+  </si>
+  <si>
+    <t>C295786</t>
+  </si>
+  <si>
+    <t>C22765</t>
+  </si>
+  <si>
+    <t>C103893</t>
+  </si>
+  <si>
+    <t>C22548</t>
+  </si>
+  <si>
+    <t>C98220</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1518,8 +1638,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1553,6 +1688,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1809,7 +1950,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1975,15 +2116,6 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2031,6 +2163,42 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2077,7 +2245,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2375,27 +2543,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R95"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:R93"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.109375" style="25" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" style="25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="30.140625" customWidth="1"/>
-    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="22.140625" customWidth="1"/>
-    <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="16.7109375" customWidth="1"/>
-    <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="29.42578125" customWidth="1"/>
+    <col min="6" max="6" width="30.109375" customWidth="1"/>
+    <col min="7" max="7" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="22.109375" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="16.6640625" customWidth="1"/>
+    <col min="16" max="16" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -2406,16 +2574,16 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-    </row>
-    <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
+      <c r="O1" s="79"/>
+      <c r="P1" s="79"/>
+      <c r="Q1" s="79"/>
+      <c r="R1" s="79"/>
+    </row>
+    <row r="2" spans="1:18" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
       <c r="C2" s="46"/>
@@ -2424,7 +2592,7 @@
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="54" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
@@ -2439,7 +2607,7 @@
       <c r="Q2" s="3"/>
       <c r="R2" s="43"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
       <c r="C3" s="47"/>
@@ -2448,7 +2616,7 @@
       </c>
       <c r="E3" s="12"/>
       <c r="F3" s="55" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="4"/>
@@ -2461,9 +2629,9 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="63"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R3" s="80"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
       <c r="C4" s="47"/>
@@ -2472,7 +2640,7 @@
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="56" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="6"/>
@@ -2480,14 +2648,14 @@
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
-      <c r="M4" s="65"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="64"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="M4" s="62"/>
+      <c r="N4" s="62"/>
+      <c r="O4" s="62"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="81"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
       <c r="C5" s="47"/>
@@ -2502,14 +2670,14 @@
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="65"/>
-      <c r="Q5" s="65"/>
-      <c r="R5" s="64"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="M5" s="62"/>
+      <c r="N5" s="62"/>
+      <c r="O5" s="62"/>
+      <c r="P5" s="62"/>
+      <c r="Q5" s="62"/>
+      <c r="R5" s="81"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
       <c r="C6" s="48"/>
@@ -2522,14 +2690,14 @@
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
-      <c r="M6" s="65"/>
-      <c r="N6" s="65"/>
-      <c r="O6" s="65"/>
-      <c r="P6" s="65"/>
-      <c r="Q6" s="65"/>
-      <c r="R6" s="64"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="M6" s="62"/>
+      <c r="N6" s="62"/>
+      <c r="O6" s="62"/>
+      <c r="P6" s="62"/>
+      <c r="Q6" s="62"/>
+      <c r="R6" s="81"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
       <c r="C7" s="49"/>
@@ -2547,9 +2715,9 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="64"/>
-    </row>
-    <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R7" s="81"/>
+    </row>
+    <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="B8" s="26"/>
       <c r="C8" s="50"/>
@@ -2567,94 +2735,94 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="64"/>
-    </row>
-    <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R8" s="81"/>
+    </row>
+    <row r="9" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
       <c r="B9" s="29" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="D9" s="29" t="s">
         <v>7</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="I9" s="29" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="J9" s="29" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="L9" s="29" t="s">
+        <v>354</v>
+      </c>
+      <c r="M9" s="31" t="s">
+        <v>385</v>
+      </c>
+      <c r="N9" s="31" t="s">
+        <v>386</v>
+      </c>
+      <c r="O9" s="31" t="s">
+        <v>387</v>
+      </c>
+      <c r="P9" s="31" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q9" s="31" t="s">
+        <v>389</v>
+      </c>
+      <c r="R9" s="31" t="s">
         <v>363</v>
       </c>
-      <c r="M9" s="31" t="s">
-        <v>394</v>
-      </c>
-      <c r="N9" s="31" t="s">
-        <v>395</v>
-      </c>
-      <c r="O9" s="31" t="s">
-        <v>396</v>
-      </c>
-      <c r="P9" s="31" t="s">
-        <v>397</v>
-      </c>
-      <c r="Q9" s="31" t="s">
-        <v>398</v>
-      </c>
-      <c r="R9" s="31" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1"/>
       <c r="B10" s="53">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D10" s="37" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="38" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="G10" s="38" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="K10" s="38" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="L10" s="37">
         <v>1</v>
@@ -2666,8 +2834,8 @@
       <c r="N10" s="41">
         <v>22</v>
       </c>
-      <c r="O10" s="67" t="s">
-        <v>400</v>
+      <c r="O10" s="64" t="s">
+        <v>391</v>
       </c>
       <c r="P10" s="41">
         <v>0.25869999999999999</v>
@@ -2678,38 +2846,38 @@
       </c>
       <c r="R10" s="41"/>
     </row>
-    <row r="11" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
       <c r="B11" s="53">
-        <f t="shared" ref="B11:B92" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B90" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="60" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D11" s="39" t="s">
         <v>9</v>
       </c>
       <c r="E11" s="40" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F11" s="39" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G11" s="40" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="H11" s="39" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="I11" s="39" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="J11" s="39" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="K11" s="40" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="L11" s="39">
         <v>9</v>
@@ -2721,8 +2889,8 @@
       <c r="N11" s="42">
         <v>198</v>
       </c>
-      <c r="O11" s="68" t="s">
-        <v>400</v>
+      <c r="O11" s="65" t="s">
+        <v>391</v>
       </c>
       <c r="P11" s="42">
         <v>1.4E-3</v>
@@ -2733,51 +2901,51 @@
       </c>
       <c r="R11" s="42"/>
     </row>
-    <row r="12" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
       <c r="B12" s="53">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
       <c r="C12" s="61" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D12" s="37" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="K12" s="38" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="L12" s="37">
         <v>1</v>
       </c>
       <c r="M12" s="41">
-        <f t="shared" ref="M12:M74" si="1">L12*20</f>
+        <f t="shared" ref="M12:M72" si="1">L12*20</f>
         <v>20</v>
       </c>
       <c r="N12" s="41">
         <v>100</v>
       </c>
-      <c r="O12" s="67" t="s">
-        <v>400</v>
+      <c r="O12" s="64" t="s">
+        <v>391</v>
       </c>
       <c r="P12" s="41">
         <v>1.2999999999999999E-3</v>
@@ -2788,38 +2956,38 @@
       </c>
       <c r="R12" s="41"/>
     </row>
-    <row r="13" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
       <c r="B13" s="53">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C13" s="60" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D13" s="39" t="s">
         <v>11</v>
       </c>
       <c r="E13" s="40" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="G13" s="40" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="I13" s="39" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="J13" s="39" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="K13" s="40" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="L13" s="39">
         <v>2</v>
@@ -2831,8 +2999,8 @@
       <c r="N13" s="42">
         <v>60</v>
       </c>
-      <c r="O13" s="68" t="s">
-        <v>400</v>
+      <c r="O13" s="65" t="s">
+        <v>391</v>
       </c>
       <c r="P13" s="42">
         <v>3.5900000000000001E-2</v>
@@ -2843,38 +3011,38 @@
       </c>
       <c r="R13" s="42"/>
     </row>
-    <row r="14" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1"/>
       <c r="B14" s="53">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
       <c r="C14" s="61" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D14" s="37" t="s">
         <v>12</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="J14" s="37" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="K14" s="38" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="L14" s="37">
         <v>9</v>
@@ -2886,8 +3054,8 @@
       <c r="N14" s="41">
         <v>200</v>
       </c>
-      <c r="O14" s="67" t="s">
-        <v>400</v>
+      <c r="O14" s="64" t="s">
+        <v>391</v>
       </c>
       <c r="P14" s="41">
         <v>4.0899999999999999E-2</v>
@@ -2898,38 +3066,38 @@
       </c>
       <c r="R14" s="41"/>
     </row>
-    <row r="15" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
       <c r="B15" s="53">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C15" s="60" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D15" s="39" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="40" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G15" s="40" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="H15" s="39" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="I15" s="39" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="J15" s="39" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="K15" s="40" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="L15" s="39">
         <v>1</v>
@@ -2941,8 +3109,8 @@
       <c r="N15" s="42">
         <v>50</v>
       </c>
-      <c r="O15" s="68" t="s">
-        <v>400</v>
+      <c r="O15" s="65" t="s">
+        <v>391</v>
       </c>
       <c r="P15" s="42">
         <v>5.8999999999999999E-3</v>
@@ -2953,38 +3121,38 @@
       </c>
       <c r="R15" s="42"/>
     </row>
-    <row r="16" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
       <c r="B16" s="53">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
       <c r="C16" s="61" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D16" s="37" t="s">
         <v>14</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G16" s="38" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="K16" s="38" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="L16" s="37">
         <v>4</v>
@@ -2996,8 +3164,8 @@
       <c r="N16" s="41">
         <v>100</v>
       </c>
-      <c r="O16" s="67" t="s">
-        <v>400</v>
+      <c r="O16" s="64" t="s">
+        <v>391</v>
       </c>
       <c r="P16" s="41">
         <v>1.44E-2</v>
@@ -3008,38 +3176,38 @@
       </c>
       <c r="R16" s="41"/>
     </row>
-    <row r="17" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
       <c r="B17" s="53">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C17" s="60" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D17" s="39" t="s">
         <v>15</v>
       </c>
       <c r="E17" s="40" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G17" s="40" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="H17" s="39" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="I17" s="39" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="J17" s="39" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="K17" s="40" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="L17" s="39">
         <v>1</v>
@@ -3051,8 +3219,8 @@
       <c r="N17" s="42">
         <v>50</v>
       </c>
-      <c r="O17" s="68" t="s">
-        <v>400</v>
+      <c r="O17" s="65" t="s">
+        <v>391</v>
       </c>
       <c r="P17" s="42">
         <v>9.9000000000000008E-3</v>
@@ -3063,38 +3231,38 @@
       </c>
       <c r="R17" s="42"/>
     </row>
-    <row r="18" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" s="53">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
       <c r="C18" s="61" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D18" s="37" t="s">
         <v>16</v>
       </c>
       <c r="E18" s="38" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G18" s="38" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="I18" s="37" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="J18" s="37" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="K18" s="38" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="L18" s="37">
         <v>3</v>
@@ -3106,8 +3274,8 @@
       <c r="N18" s="41">
         <v>100</v>
       </c>
-      <c r="O18" s="67" t="s">
-        <v>400</v>
+      <c r="O18" s="64" t="s">
+        <v>391</v>
       </c>
       <c r="P18" s="41">
         <v>8.0999999999999996E-3</v>
@@ -3118,38 +3286,38 @@
       </c>
       <c r="R18" s="41"/>
     </row>
-    <row r="19" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="53">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="C19" s="60" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="E19" s="40" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F19" s="39" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="G19" s="40" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="H19" s="39" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="I19" s="39" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="J19" s="39" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="K19" s="40" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="L19" s="39">
         <v>8</v>
@@ -3161,8 +3329,8 @@
       <c r="N19" s="42">
         <v>180</v>
       </c>
-      <c r="O19" s="68" t="s">
-        <v>400</v>
+      <c r="O19" s="65" t="s">
+        <v>391</v>
       </c>
       <c r="P19" s="42">
         <v>3.09E-2</v>
@@ -3173,38 +3341,38 @@
       </c>
       <c r="R19" s="42"/>
     </row>
-    <row r="20" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1"/>
       <c r="B20" s="53">
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
       <c r="C20" s="61" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D20" s="37" t="s">
         <v>17</v>
       </c>
       <c r="E20" s="38" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G20" s="38" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="I20" s="37" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="J20" s="37" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="K20" s="38" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="L20" s="37">
         <v>1</v>
@@ -3216,8 +3384,8 @@
       <c r="N20" s="41">
         <v>50</v>
       </c>
-      <c r="O20" s="67" t="s">
-        <v>400</v>
+      <c r="O20" s="64" t="s">
+        <v>391</v>
       </c>
       <c r="P20" s="41">
         <v>5.3E-3</v>
@@ -3228,38 +3396,38 @@
       </c>
       <c r="R20" s="41"/>
     </row>
-    <row r="21" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
       <c r="B21" s="53">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="C21" s="60" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D21" s="39" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="40" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F21" s="39" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="G21" s="39" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="H21" s="39" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="I21" s="39" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="J21" s="39" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="K21" s="40" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="L21" s="39">
         <v>1</v>
@@ -3271,8 +3439,8 @@
       <c r="N21" s="42">
         <v>22</v>
       </c>
-      <c r="O21" s="68" t="s">
-        <v>400</v>
+      <c r="O21" s="65" t="s">
+        <v>391</v>
       </c>
       <c r="P21" s="42">
         <v>0.22189999999999999</v>
@@ -3283,38 +3451,38 @@
       </c>
       <c r="R21" s="42"/>
     </row>
-    <row r="22" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1"/>
       <c r="B22" s="53">
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
       <c r="C22" s="61" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D22" s="37" t="s">
         <v>19</v>
       </c>
       <c r="E22" s="38" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="J22" s="37" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="K22" s="38" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="L22" s="37">
         <v>2</v>
@@ -3326,8 +3494,8 @@
       <c r="N22" s="41">
         <v>50</v>
       </c>
-      <c r="O22" s="67" t="s">
-        <v>400</v>
+      <c r="O22" s="64" t="s">
+        <v>391</v>
       </c>
       <c r="P22" s="41">
         <v>7.7000000000000002E-3</v>
@@ -3338,38 +3506,38 @@
       </c>
       <c r="R22" s="41"/>
     </row>
-    <row r="23" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
       <c r="B23" s="53">
         <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
       </c>
       <c r="C23" s="61" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D23" s="37" t="s">
         <v>20</v>
       </c>
       <c r="E23" s="38" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F23" s="37" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G23" s="38" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="H23" s="37" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="I23" s="37" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="J23" s="37" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="K23" s="38" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="L23" s="37">
         <v>1</v>
@@ -3381,8 +3549,8 @@
       <c r="N23" s="41">
         <v>40</v>
       </c>
-      <c r="O23" s="67" t="s">
-        <v>400</v>
+      <c r="O23" s="64" t="s">
+        <v>391</v>
       </c>
       <c r="P23" s="41">
         <v>3.49E-2</v>
@@ -3393,38 +3561,38 @@
       </c>
       <c r="R23" s="41"/>
     </row>
-    <row r="24" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
       <c r="B24" s="53">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="C24" s="60" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D24" s="39" t="s">
         <v>21</v>
       </c>
       <c r="E24" s="40" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F24" s="39" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G24" s="40" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="H24" s="39" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="I24" s="39" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="J24" s="39" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="K24" s="40" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="L24" s="39">
         <v>3</v>
@@ -3436,8 +3604,8 @@
       <c r="N24" s="42">
         <v>80</v>
       </c>
-      <c r="O24" s="68" t="s">
-        <v>400</v>
+      <c r="O24" s="65" t="s">
+        <v>391</v>
       </c>
       <c r="P24" s="42">
         <v>1.9199999999999998E-2</v>
@@ -3448,38 +3616,38 @@
       </c>
       <c r="R24" s="42"/>
     </row>
-    <row r="25" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
       <c r="B25" s="53">
         <f>ROW(B25) - ROW($B$9)</f>
         <v>16</v>
       </c>
       <c r="C25" s="61" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D25" s="37" t="s">
         <v>22</v>
       </c>
       <c r="E25" s="38" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F25" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="G25" s="69">
+        <v>173</v>
+      </c>
+      <c r="G25" s="66">
         <v>885012205080</v>
       </c>
       <c r="H25" s="37" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="I25" s="37" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="J25" s="37" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="K25" s="38" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="L25" s="37">
         <v>1</v>
@@ -3491,8 +3659,8 @@
       <c r="N25" s="41">
         <v>50</v>
       </c>
-      <c r="O25" s="67" t="s">
-        <v>400</v>
+      <c r="O25" s="64" t="s">
+        <v>391</v>
       </c>
       <c r="P25" s="41">
         <v>5.1999999999999998E-3</v>
@@ -3503,38 +3671,38 @@
       </c>
       <c r="R25" s="41"/>
     </row>
-    <row r="26" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
       <c r="B26" s="53">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="C26" s="60" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D26" s="39" t="s">
         <v>23</v>
       </c>
       <c r="E26" s="40" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F26" s="39" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G26" s="40" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="H26" s="39" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="I26" s="39" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="J26" s="39" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="K26" s="40" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="L26" s="39">
         <v>1</v>
@@ -3546,8 +3714,8 @@
       <c r="N26" s="42">
         <v>100</v>
       </c>
-      <c r="O26" s="68" t="s">
-        <v>400</v>
+      <c r="O26" s="65" t="s">
+        <v>391</v>
       </c>
       <c r="P26" s="42">
         <v>3.2000000000000002E-3</v>
@@ -3558,38 +3726,38 @@
       </c>
       <c r="R26" s="42"/>
     </row>
-    <row r="27" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
       <c r="B27" s="53">
         <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
       <c r="C27" s="61" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D27" s="37" t="s">
         <v>24</v>
       </c>
       <c r="E27" s="38" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F27" s="37" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="G27" s="38" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="H27" s="37" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="I27" s="37" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="J27" s="37" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="K27" s="38" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="L27" s="37">
         <v>1</v>
@@ -3601,8 +3769,8 @@
       <c r="N27" s="41">
         <v>22</v>
       </c>
-      <c r="O27" s="67" t="s">
-        <v>400</v>
+      <c r="O27" s="64" t="s">
+        <v>391</v>
       </c>
       <c r="P27" s="41">
         <v>0.1653</v>
@@ -3613,38 +3781,38 @@
       </c>
       <c r="R27" s="41"/>
     </row>
-    <row r="28" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
       <c r="B28" s="53">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="C28" s="60" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D28" s="39" t="s">
         <v>25</v>
       </c>
       <c r="E28" s="40" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F28" s="39" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G28" s="40" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="H28" s="39" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="I28" s="39" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="J28" s="39" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="K28" s="40" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="L28" s="39">
         <v>1</v>
@@ -3656,8 +3824,8 @@
       <c r="N28" s="42">
         <v>100</v>
       </c>
-      <c r="O28" s="68" t="s">
-        <v>400</v>
+      <c r="O28" s="65" t="s">
+        <v>391</v>
       </c>
       <c r="P28" s="42">
         <v>3.3999999999999998E-3</v>
@@ -3668,38 +3836,38 @@
       </c>
       <c r="R28" s="42"/>
     </row>
-    <row r="29" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
       <c r="B29" s="53">
         <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
       <c r="C29" s="61" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D29" s="37" t="s">
         <v>26</v>
       </c>
       <c r="E29" s="38" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F29" s="37" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="G29" s="38" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="H29" s="37" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="I29" s="37" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="J29" s="37" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="K29" s="38" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="L29" s="37">
         <v>3</v>
@@ -3711,8 +3879,8 @@
       <c r="N29" s="41">
         <v>70</v>
       </c>
-      <c r="O29" s="67" t="s">
-        <v>400</v>
+      <c r="O29" s="64" t="s">
+        <v>391</v>
       </c>
       <c r="P29" s="41">
         <v>0.2525</v>
@@ -3723,38 +3891,38 @@
       </c>
       <c r="R29" s="41"/>
     </row>
-    <row r="30" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
       <c r="B30" s="53">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="C30" s="60" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D30" s="39" t="s">
         <v>27</v>
       </c>
       <c r="E30" s="40" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F30" s="39" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G30" s="40" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="H30" s="39" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="I30" s="39" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="J30" s="39" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="K30" s="40" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="L30" s="39">
         <v>1</v>
@@ -3766,8 +3934,8 @@
       <c r="N30" s="42">
         <v>50</v>
       </c>
-      <c r="O30" s="68" t="s">
-        <v>400</v>
+      <c r="O30" s="65" t="s">
+        <v>391</v>
       </c>
       <c r="P30" s="42">
         <v>4.1999999999999997E-3</v>
@@ -3778,38 +3946,38 @@
       </c>
       <c r="R30" s="42"/>
     </row>
-    <row r="31" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1"/>
       <c r="B31" s="53">
         <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
       <c r="C31" s="61" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D31" s="37" t="s">
         <v>28</v>
       </c>
       <c r="E31" s="38" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F31" s="37" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="G31" s="38" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H31" s="37" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="I31" s="37" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="J31" s="37" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="K31" s="38" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="L31" s="37">
         <v>1</v>
@@ -3821,8 +3989,8 @@
       <c r="N31" s="41">
         <v>22</v>
       </c>
-      <c r="O31" s="67" t="s">
-        <v>400</v>
+      <c r="O31" s="64" t="s">
+        <v>391</v>
       </c>
       <c r="P31" s="41">
         <v>0.89629999999999999</v>
@@ -3833,38 +4001,38 @@
       </c>
       <c r="R31" s="41"/>
     </row>
-    <row r="32" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1"/>
       <c r="B32" s="53">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="C32" s="60" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D32" s="39" t="s">
         <v>29</v>
       </c>
       <c r="E32" s="40" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F32" s="39" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="G32" s="39" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="H32" s="39" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I32" s="39" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="J32" s="39" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="K32" s="40" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="L32" s="39">
         <v>1</v>
@@ -3876,8 +4044,8 @@
       <c r="N32" s="42">
         <v>21</v>
       </c>
-      <c r="O32" s="68" t="s">
-        <v>400</v>
+      <c r="O32" s="65" t="s">
+        <v>391</v>
       </c>
       <c r="P32" s="42">
         <v>0.47249999999999998</v>
@@ -3888,38 +4056,38 @@
       </c>
       <c r="R32" s="42"/>
     </row>
-    <row r="33" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1"/>
       <c r="B33" s="53">
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
       <c r="C33" s="61" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D33" s="37" t="s">
         <v>30</v>
       </c>
       <c r="E33" s="38" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G33" s="38" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="H33" s="37" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="J33" s="37" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="K33" s="38" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="L33" s="37">
         <v>1</v>
@@ -3931,8 +4099,8 @@
       <c r="N33" s="41">
         <v>100</v>
       </c>
-      <c r="O33" s="67" t="s">
-        <v>400</v>
+      <c r="O33" s="64" t="s">
+        <v>391</v>
       </c>
       <c r="P33" s="41">
         <v>3.0999999999999999E-3</v>
@@ -3943,38 +4111,38 @@
       </c>
       <c r="R33" s="41"/>
     </row>
-    <row r="34" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
       <c r="B34" s="53">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="C34" s="60" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D34" s="39" t="s">
         <v>31</v>
       </c>
       <c r="E34" s="40" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F34" s="39" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="G34" s="40" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="H34" s="39" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="I34" s="39" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="J34" s="39" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="K34" s="40" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="L34" s="39">
         <v>1</v>
@@ -3986,8 +4154,8 @@
       <c r="N34" s="42">
         <v>25</v>
       </c>
-      <c r="O34" s="68" t="s">
-        <v>400</v>
+      <c r="O34" s="65" t="s">
+        <v>391</v>
       </c>
       <c r="P34" s="42">
         <v>9.1899999999999996E-2</v>
@@ -3998,38 +4166,38 @@
       </c>
       <c r="R34" s="42"/>
     </row>
-    <row r="35" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1"/>
       <c r="B35" s="53">
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
       <c r="C35" s="61" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D35" s="37" t="s">
         <v>32</v>
       </c>
       <c r="E35" s="38" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F35" s="37" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G35" s="38" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="H35" s="37" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="I35" s="37" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="J35" s="37" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="K35" s="38" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="L35" s="37">
         <v>4</v>
@@ -4041,8 +4209,8 @@
       <c r="N35" s="41">
         <v>100</v>
       </c>
-      <c r="O35" s="67" t="s">
-        <v>400</v>
+      <c r="O35" s="64" t="s">
+        <v>391</v>
       </c>
       <c r="P35" s="41">
         <v>5.4999999999999997E-3</v>
@@ -4053,38 +4221,38 @@
       </c>
       <c r="R35" s="41"/>
     </row>
-    <row r="36" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1"/>
       <c r="B36" s="53">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="C36" s="60" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="D36" s="39" t="s">
         <v>33</v>
       </c>
       <c r="E36" s="40" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F36" s="39" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="G36" s="40" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="H36" s="39" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="I36" s="39" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="J36" s="39" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="K36" s="40" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="L36" s="39">
         <v>1</v>
@@ -4096,8 +4264,8 @@
       <c r="N36" s="42">
         <v>30</v>
       </c>
-      <c r="O36" s="68" t="s">
-        <v>400</v>
+      <c r="O36" s="65" t="s">
+        <v>391</v>
       </c>
       <c r="P36" s="42">
         <v>4.87E-2</v>
@@ -4108,38 +4276,38 @@
       </c>
       <c r="R36" s="42"/>
     </row>
-    <row r="37" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1"/>
       <c r="B37" s="53">
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
       <c r="C37" s="61" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="D37" s="37" t="s">
         <v>34</v>
       </c>
       <c r="E37" s="38" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F37" s="37" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G37" s="38" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="H37" s="37" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="I37" s="37" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="J37" s="37" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="K37" s="38" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="L37" s="37">
         <v>1</v>
@@ -4151,8 +4319,8 @@
       <c r="N37" s="41">
         <v>30</v>
       </c>
-      <c r="O37" s="67" t="s">
-        <v>400</v>
+      <c r="O37" s="64" t="s">
+        <v>391</v>
       </c>
       <c r="P37" s="41">
         <v>7.4300000000000005E-2</v>
@@ -4163,38 +4331,38 @@
       </c>
       <c r="R37" s="41"/>
     </row>
-    <row r="38" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1"/>
       <c r="B38" s="53">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="C38" s="60" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="D38" s="39" t="s">
         <v>35</v>
       </c>
       <c r="E38" s="40" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F38" s="39" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G38" s="40" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="H38" s="39" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="I38" s="39" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="J38" s="39" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="K38" s="40" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="L38" s="39">
         <v>1</v>
@@ -4206,8 +4374,8 @@
       <c r="N38" s="42">
         <v>40</v>
       </c>
-      <c r="O38" s="68" t="s">
-        <v>400</v>
+      <c r="O38" s="65" t="s">
+        <v>391</v>
       </c>
       <c r="P38" s="42">
         <v>2.8899999999999999E-2</v>
@@ -4218,95 +4386,95 @@
       </c>
       <c r="R38" s="42"/>
     </row>
-    <row r="39" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1"/>
-      <c r="B39" s="70">
+      <c r="B39" s="67">
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="71" t="s">
-        <v>374</v>
-      </c>
-      <c r="D39" s="72" t="s">
+      <c r="C39" s="68" t="s">
+        <v>365</v>
+      </c>
+      <c r="D39" s="69" t="s">
         <v>36</v>
       </c>
-      <c r="E39" s="73" t="s">
-        <v>121</v>
-      </c>
-      <c r="F39" s="72" t="s">
-        <v>188</v>
-      </c>
-      <c r="G39" s="73" t="s">
-        <v>242</v>
-      </c>
-      <c r="H39" s="72" t="s">
-        <v>287</v>
-      </c>
-      <c r="I39" s="72" t="s">
-        <v>435</v>
-      </c>
-      <c r="J39" s="72" t="s">
-        <v>436</v>
-      </c>
-      <c r="K39" s="73" t="s">
-        <v>370</v>
-      </c>
-      <c r="L39" s="72">
+      <c r="E39" s="70" t="s">
+        <v>117</v>
+      </c>
+      <c r="F39" s="69" t="s">
+        <v>182</v>
+      </c>
+      <c r="G39" s="70" t="s">
+        <v>236</v>
+      </c>
+      <c r="H39" s="69" t="s">
+        <v>279</v>
+      </c>
+      <c r="I39" s="69" t="s">
+        <v>426</v>
+      </c>
+      <c r="J39" s="69" t="s">
+        <v>427</v>
+      </c>
+      <c r="K39" s="70" t="s">
+        <v>361</v>
+      </c>
+      <c r="L39" s="69">
         <v>8</v>
       </c>
-      <c r="M39" s="74">
+      <c r="M39" s="71">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="N39" s="74">
+      <c r="N39" s="71">
         <v>170</v>
       </c>
-      <c r="O39" s="75" t="s">
-        <v>400</v>
-      </c>
-      <c r="P39" s="74">
+      <c r="O39" s="72" t="s">
+        <v>391</v>
+      </c>
+      <c r="P39" s="71">
         <v>0.12590000000000001</v>
       </c>
-      <c r="Q39" s="74">
+      <c r="Q39" s="71">
         <f t="shared" ref="Q39" si="29">P39*N39</f>
         <v>21.403000000000002</v>
       </c>
-      <c r="R39" s="76" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R39" s="73" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1"/>
       <c r="B40" s="53">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="C40" s="60" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="D40" s="39" t="s">
         <v>37</v>
       </c>
       <c r="E40" s="40" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F40" s="39" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="G40" s="40" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="H40" s="39" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="I40" s="39" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="J40" s="39" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="K40" s="40" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="L40" s="39">
         <v>1</v>
@@ -4318,8 +4486,8 @@
       <c r="N40" s="42">
         <v>30</v>
       </c>
-      <c r="O40" s="68" t="s">
-        <v>400</v>
+      <c r="O40" s="65" t="s">
+        <v>391</v>
       </c>
       <c r="P40" s="42">
         <v>5.6000000000000001E-2</v>
@@ -4330,38 +4498,38 @@
       </c>
       <c r="R40" s="42"/>
     </row>
-    <row r="41" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1"/>
       <c r="B41" s="53">
         <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
       <c r="C41" s="61" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="D41" s="37" t="s">
         <v>38</v>
       </c>
       <c r="E41" s="38" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F41" s="37" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="G41" s="38" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H41" s="37" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="I41" s="37" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="J41" s="37" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="K41" s="38" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="L41" s="37">
         <v>4</v>
@@ -4373,8 +4541,8 @@
       <c r="N41" s="41">
         <v>100</v>
       </c>
-      <c r="O41" s="67" t="s">
-        <v>400</v>
+      <c r="O41" s="64" t="s">
+        <v>391</v>
       </c>
       <c r="P41" s="41">
         <v>2.9499999999999998E-2</v>
@@ -4385,152 +4553,152 @@
       </c>
       <c r="R41" s="41"/>
     </row>
-    <row r="42" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1"/>
-      <c r="B42" s="70">
+      <c r="B42" s="67">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="77" t="s">
-        <v>377</v>
-      </c>
-      <c r="D42" s="78" t="s">
+      <c r="C42" s="74" t="s">
+        <v>368</v>
+      </c>
+      <c r="D42" s="75" t="s">
         <v>39</v>
       </c>
-      <c r="E42" s="79" t="s">
-        <v>124</v>
-      </c>
-      <c r="F42" s="78" t="s">
-        <v>364</v>
-      </c>
-      <c r="G42" s="79" t="s">
-        <v>191</v>
-      </c>
-      <c r="H42" s="78" t="s">
-        <v>289</v>
-      </c>
-      <c r="I42" s="78" t="s">
-        <v>440</v>
-      </c>
-      <c r="J42" s="78" t="s">
-        <v>441</v>
-      </c>
-      <c r="K42" s="79" t="s">
-        <v>370</v>
-      </c>
-      <c r="L42" s="78">
+      <c r="E42" s="76" t="s">
+        <v>120</v>
+      </c>
+      <c r="F42" s="75" t="s">
+        <v>355</v>
+      </c>
+      <c r="G42" s="76" t="s">
+        <v>185</v>
+      </c>
+      <c r="H42" s="75" t="s">
+        <v>281</v>
+      </c>
+      <c r="I42" s="75" t="s">
+        <v>431</v>
+      </c>
+      <c r="J42" s="75" t="s">
+        <v>432</v>
+      </c>
+      <c r="K42" s="76" t="s">
+        <v>361</v>
+      </c>
+      <c r="L42" s="75">
         <v>1</v>
       </c>
-      <c r="M42" s="80">
+      <c r="M42" s="77">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N42" s="80">
+      <c r="N42" s="77">
         <v>21</v>
       </c>
-      <c r="O42" s="81" t="s">
-        <v>400</v>
-      </c>
-      <c r="P42" s="80">
+      <c r="O42" s="78" t="s">
+        <v>391</v>
+      </c>
+      <c r="P42" s="77">
         <v>0.53559999999999997</v>
       </c>
-      <c r="Q42" s="80">
+      <c r="Q42" s="77">
         <f t="shared" ref="Q42" si="32">N42*P42</f>
         <v>11.247599999999998</v>
       </c>
-      <c r="R42" s="76" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R42" s="73" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
-      <c r="B43" s="70">
+      <c r="B43" s="67">
         <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
       </c>
-      <c r="C43" s="71" t="s">
-        <v>377</v>
-      </c>
-      <c r="D43" s="72" t="s">
+      <c r="C43" s="68" t="s">
+        <v>368</v>
+      </c>
+      <c r="D43" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="E43" s="73" t="s">
-        <v>125</v>
-      </c>
-      <c r="F43" s="72" t="s">
-        <v>364</v>
-      </c>
-      <c r="G43" s="73" t="s">
-        <v>192</v>
-      </c>
-      <c r="H43" s="72" t="s">
-        <v>290</v>
-      </c>
-      <c r="I43" s="72" t="s">
-        <v>442</v>
-      </c>
-      <c r="J43" s="72" t="s">
-        <v>443</v>
-      </c>
-      <c r="K43" s="73" t="s">
-        <v>370</v>
-      </c>
-      <c r="L43" s="72">
+      <c r="E43" s="70" t="s">
+        <v>121</v>
+      </c>
+      <c r="F43" s="69" t="s">
+        <v>355</v>
+      </c>
+      <c r="G43" s="70" t="s">
+        <v>186</v>
+      </c>
+      <c r="H43" s="69" t="s">
+        <v>282</v>
+      </c>
+      <c r="I43" s="69" t="s">
+        <v>433</v>
+      </c>
+      <c r="J43" s="69" t="s">
+        <v>434</v>
+      </c>
+      <c r="K43" s="70" t="s">
+        <v>361</v>
+      </c>
+      <c r="L43" s="69">
         <v>2</v>
       </c>
-      <c r="M43" s="74">
+      <c r="M43" s="71">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N43" s="74">
+      <c r="N43" s="71">
         <v>42</v>
       </c>
-      <c r="O43" s="75" t="s">
-        <v>400</v>
-      </c>
-      <c r="P43" s="74">
+      <c r="O43" s="72" t="s">
+        <v>391</v>
+      </c>
+      <c r="P43" s="71">
         <v>0.65639999999999998</v>
       </c>
-      <c r="Q43" s="74">
+      <c r="Q43" s="71">
         <f t="shared" ref="Q43" si="33">P43*N43</f>
         <v>27.5688</v>
       </c>
-      <c r="R43" s="76" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R43" s="73" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
       <c r="B44" s="53">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="C44" s="60" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="D44" s="39" t="s">
         <v>41</v>
       </c>
       <c r="E44" s="40" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F44" s="39" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="G44" s="40" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="H44" s="39" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="I44" s="39" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="J44" s="39" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="K44" s="40" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="L44" s="39">
         <v>1</v>
@@ -4542,8 +4710,8 @@
       <c r="N44" s="42">
         <v>21</v>
       </c>
-      <c r="O44" s="68" t="s">
-        <v>444</v>
+      <c r="O44" s="65" t="s">
+        <v>435</v>
       </c>
       <c r="P44" s="42">
         <v>1.2</v>
@@ -4554,34 +4722,38 @@
       </c>
       <c r="R44" s="42"/>
     </row>
-    <row r="45" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
       <c r="B45" s="53">
         <f>ROW(B45) - ROW($B$9)</f>
         <v>36</v>
       </c>
       <c r="C45" s="61" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="D45" s="37" t="s">
         <v>42</v>
       </c>
       <c r="E45" s="38" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F45" s="37" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="G45" s="38" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="H45" s="37" t="s">
-        <v>292</v>
-      </c>
-      <c r="I45" s="37"/>
-      <c r="J45" s="37"/>
+        <v>284</v>
+      </c>
+      <c r="I45" s="37" t="s">
+        <v>361</v>
+      </c>
+      <c r="J45" s="37" t="s">
+        <v>436</v>
+      </c>
       <c r="K45" s="38" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="L45" s="37">
         <v>1</v>
@@ -4591,45 +4763,52 @@
         <v>20</v>
       </c>
       <c r="N45" s="41">
-        <f t="shared" ref="N23:N74" si="35">M45+(M45*0.1)</f>
-        <v>22</v>
-      </c>
-      <c r="O45" s="41"/>
-      <c r="P45" s="41"/>
+        <v>25</v>
+      </c>
+      <c r="O45" s="64" t="s">
+        <v>391</v>
+      </c>
+      <c r="P45" s="41">
+        <v>9.2200000000000004E-2</v>
+      </c>
       <c r="Q45" s="41">
-        <f t="shared" ref="Q45" si="36">P45*N45</f>
-        <v>0</v>
+        <f t="shared" ref="Q45" si="35">P45*N45</f>
+        <v>2.3050000000000002</v>
       </c>
       <c r="R45" s="41"/>
     </row>
-    <row r="46" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1"/>
       <c r="B46" s="53">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="C46" s="60" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="D46" s="39" t="s">
         <v>43</v>
       </c>
       <c r="E46" s="40" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F46" s="39" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="G46" s="40" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="H46" s="39" t="s">
-        <v>281</v>
-      </c>
-      <c r="I46" s="39"/>
-      <c r="J46" s="39"/>
+        <v>273</v>
+      </c>
+      <c r="I46" s="39" t="s">
+        <v>361</v>
+      </c>
+      <c r="J46" s="39" t="s">
+        <v>437</v>
+      </c>
       <c r="K46" s="40" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="L46" s="39">
         <v>1</v>
@@ -4639,45 +4818,52 @@
         <v>20</v>
       </c>
       <c r="N46" s="42">
-        <f t="shared" si="35"/>
-        <v>22</v>
-      </c>
-      <c r="O46" s="42"/>
-      <c r="P46" s="42"/>
+        <v>21</v>
+      </c>
+      <c r="O46" s="65" t="s">
+        <v>391</v>
+      </c>
+      <c r="P46" s="42">
+        <v>0.45629999999999998</v>
+      </c>
       <c r="Q46" s="42">
-        <f t="shared" ref="Q46" si="37">N46*P46</f>
-        <v>0</v>
+        <f t="shared" ref="Q46" si="36">N46*P46</f>
+        <v>9.5823</v>
       </c>
       <c r="R46" s="42"/>
     </row>
-    <row r="47" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
       <c r="B47" s="53">
         <f>ROW(B47) - ROW($B$9)</f>
         <v>38</v>
       </c>
       <c r="C47" s="61" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="D47" s="37" t="s">
         <v>44</v>
       </c>
       <c r="E47" s="38" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F47" s="37" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="G47" s="38" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H47" s="37" t="s">
-        <v>293</v>
-      </c>
-      <c r="I47" s="37"/>
-      <c r="J47" s="37"/>
+        <v>285</v>
+      </c>
+      <c r="I47" s="37" t="s">
+        <v>361</v>
+      </c>
+      <c r="J47" s="37" t="s">
+        <v>438</v>
+      </c>
       <c r="K47" s="38" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="L47" s="37">
         <v>1</v>
@@ -4687,45 +4873,52 @@
         <v>20</v>
       </c>
       <c r="N47" s="41">
-        <f t="shared" si="35"/>
-        <v>22</v>
-      </c>
-      <c r="O47" s="41"/>
-      <c r="P47" s="41"/>
+        <v>30</v>
+      </c>
+      <c r="O47" s="64" t="s">
+        <v>391</v>
+      </c>
+      <c r="P47" s="41">
+        <v>9.5500000000000002E-2</v>
+      </c>
       <c r="Q47" s="41">
-        <f t="shared" ref="Q47" si="38">P47*N47</f>
-        <v>0</v>
+        <f t="shared" ref="Q47" si="37">P47*N47</f>
+        <v>2.8650000000000002</v>
       </c>
       <c r="R47" s="41"/>
     </row>
-    <row r="48" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1"/>
       <c r="B48" s="53">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="C48" s="60" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="D48" s="39" t="s">
         <v>45</v>
       </c>
       <c r="E48" s="40" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F48" s="39" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="G48" s="40" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="H48" s="39" t="s">
-        <v>294</v>
-      </c>
-      <c r="I48" s="39"/>
-      <c r="J48" s="39"/>
+        <v>286</v>
+      </c>
+      <c r="I48" s="39" t="s">
+        <v>361</v>
+      </c>
+      <c r="J48" s="39" t="s">
+        <v>361</v>
+      </c>
       <c r="K48" s="40" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="L48" s="39">
         <v>1</v>
@@ -4735,45 +4928,52 @@
         <v>20</v>
       </c>
       <c r="N48" s="42">
-        <f t="shared" si="35"/>
-        <v>22</v>
-      </c>
-      <c r="O48" s="42"/>
-      <c r="P48" s="42"/>
+        <v>30</v>
+      </c>
+      <c r="O48" s="65" t="s">
+        <v>439</v>
+      </c>
+      <c r="P48" s="42">
+        <v>0.156</v>
+      </c>
       <c r="Q48" s="42">
-        <f t="shared" ref="Q48" si="39">N48*P48</f>
-        <v>0</v>
+        <f t="shared" ref="Q48" si="38">N48*P48</f>
+        <v>4.68</v>
       </c>
       <c r="R48" s="42"/>
     </row>
-    <row r="49" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1"/>
       <c r="B49" s="53">
         <f>ROW(B49) - ROW($B$9)</f>
         <v>40</v>
       </c>
       <c r="C49" s="61" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="D49" s="37" t="s">
         <v>46</v>
       </c>
       <c r="E49" s="38" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F49" s="37" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="G49" s="38" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="H49" s="37" t="s">
-        <v>295</v>
-      </c>
-      <c r="I49" s="37"/>
-      <c r="J49" s="37"/>
+        <v>287</v>
+      </c>
+      <c r="I49" s="37" t="s">
+        <v>361</v>
+      </c>
+      <c r="J49" s="37" t="s">
+        <v>361</v>
+      </c>
       <c r="K49" s="38" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="L49" s="37">
         <v>1</v>
@@ -4783,45 +4983,52 @@
         <v>20</v>
       </c>
       <c r="N49" s="41">
-        <f t="shared" si="35"/>
-        <v>22</v>
-      </c>
-      <c r="O49" s="41"/>
-      <c r="P49" s="41"/>
+        <v>30</v>
+      </c>
+      <c r="O49" s="64" t="s">
+        <v>440</v>
+      </c>
+      <c r="P49" s="41">
+        <v>0.08</v>
+      </c>
       <c r="Q49" s="41">
-        <f t="shared" ref="Q49" si="40">P49*N49</f>
-        <v>0</v>
+        <f t="shared" ref="Q49" si="39">P49*N49</f>
+        <v>2.4</v>
       </c>
       <c r="R49" s="41"/>
     </row>
-    <row r="50" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1"/>
       <c r="B50" s="53">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="C50" s="60" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="D50" s="39" t="s">
         <v>47</v>
       </c>
       <c r="E50" s="40" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F50" s="39" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="G50" s="40" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H50" s="39" t="s">
-        <v>296</v>
-      </c>
-      <c r="I50" s="39"/>
-      <c r="J50" s="39"/>
+        <v>288</v>
+      </c>
+      <c r="I50" s="39" t="s">
+        <v>361</v>
+      </c>
+      <c r="J50" s="39" t="s">
+        <v>361</v>
+      </c>
       <c r="K50" s="40" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="L50" s="39">
         <v>2</v>
@@ -4831,93 +5038,104 @@
         <v>40</v>
       </c>
       <c r="N50" s="42">
-        <f t="shared" si="35"/>
-        <v>44</v>
-      </c>
-      <c r="O50" s="42"/>
-      <c r="P50" s="42"/>
+        <v>50</v>
+      </c>
+      <c r="O50" s="65" t="s">
+        <v>435</v>
+      </c>
+      <c r="P50" s="42">
+        <v>1.5</v>
+      </c>
       <c r="Q50" s="42">
-        <f t="shared" ref="Q50" si="41">N50*P50</f>
-        <v>0</v>
-      </c>
-      <c r="R50" s="42"/>
-    </row>
-    <row r="51" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" ref="Q50" si="40">N50*P50</f>
+        <v>75</v>
+      </c>
+      <c r="R50" s="42" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1"/>
-      <c r="B51" s="53">
+      <c r="B51" s="82">
         <f>ROW(B51) - ROW($B$9)</f>
         <v>42</v>
       </c>
-      <c r="C51" s="61" t="s">
-        <v>337</v>
-      </c>
-      <c r="D51" s="37" t="s">
+      <c r="C51" s="83" t="s">
+        <v>328</v>
+      </c>
+      <c r="D51" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="E51" s="38" t="s">
-        <v>133</v>
-      </c>
-      <c r="F51" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="G51" s="38" t="s">
-        <v>370</v>
-      </c>
-      <c r="H51" s="37" t="s">
-        <v>370</v>
-      </c>
-      <c r="I51" s="37"/>
-      <c r="J51" s="37"/>
-      <c r="K51" s="38" t="s">
-        <v>370</v>
-      </c>
-      <c r="L51" s="37">
+      <c r="E51" s="85" t="s">
+        <v>129</v>
+      </c>
+      <c r="F51" s="84" t="s">
+        <v>194</v>
+      </c>
+      <c r="G51" s="85" t="s">
+        <v>361</v>
+      </c>
+      <c r="H51" s="84" t="s">
+        <v>361</v>
+      </c>
+      <c r="I51" s="84"/>
+      <c r="J51" s="84"/>
+      <c r="K51" s="85" t="s">
+        <v>361</v>
+      </c>
+      <c r="L51" s="84">
         <v>4</v>
       </c>
-      <c r="M51" s="41">
+      <c r="M51" s="86">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N51" s="41">
-        <f t="shared" si="35"/>
+      <c r="N51" s="86">
+        <f t="shared" ref="N51:N72" si="41">M51+(M51*0.1)</f>
         <v>88</v>
       </c>
-      <c r="O51" s="41"/>
-      <c r="P51" s="41"/>
-      <c r="Q51" s="41">
+      <c r="O51" s="86"/>
+      <c r="P51" s="86"/>
+      <c r="Q51" s="86">
         <f t="shared" ref="Q51" si="42">P51*N51</f>
         <v>0</v>
       </c>
-      <c r="R51" s="41"/>
-    </row>
-    <row r="52" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R51" s="90" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1"/>
       <c r="B52" s="53">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="C52" s="60" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="D52" s="39" t="s">
         <v>49</v>
       </c>
       <c r="E52" s="40" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F52" s="39" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G52" s="40">
         <v>61300211121</v>
       </c>
       <c r="H52" s="39" t="s">
-        <v>283</v>
-      </c>
-      <c r="I52" s="39"/>
-      <c r="J52" s="39"/>
+        <v>275</v>
+      </c>
+      <c r="I52" s="39" t="s">
+        <v>361</v>
+      </c>
+      <c r="J52" s="39" t="s">
+        <v>361</v>
+      </c>
       <c r="K52" s="40" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="L52" s="39">
         <v>4</v>
@@ -4927,93 +5145,111 @@
         <v>80</v>
       </c>
       <c r="N52" s="42">
-        <f t="shared" si="35"/>
-        <v>88</v>
-      </c>
-      <c r="O52" s="42"/>
-      <c r="P52" s="42"/>
+        <v>90</v>
+      </c>
+      <c r="O52" s="65" t="s">
+        <v>435</v>
+      </c>
+      <c r="P52" s="42">
+        <v>0.13</v>
+      </c>
       <c r="Q52" s="42">
         <f t="shared" ref="Q52" si="43">N52*P52</f>
-        <v>0</v>
-      </c>
-      <c r="R52" s="42"/>
-    </row>
-    <row r="53" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>11.700000000000001</v>
+      </c>
+      <c r="R52" s="42" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1"/>
-      <c r="B53" s="53">
+      <c r="B53" s="67">
         <f>ROW(B53) - ROW($B$9)</f>
         <v>44</v>
       </c>
-      <c r="C53" s="61" t="s">
-        <v>380</v>
-      </c>
-      <c r="D53" s="37" t="s">
+      <c r="C53" s="68" t="s">
+        <v>371</v>
+      </c>
+      <c r="D53" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="E53" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="F53" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="G53" s="38" t="s">
-        <v>244</v>
-      </c>
-      <c r="H53" s="37" t="s">
-        <v>297</v>
-      </c>
-      <c r="I53" s="37"/>
-      <c r="J53" s="37"/>
-      <c r="K53" s="38" t="s">
-        <v>370</v>
-      </c>
-      <c r="L53" s="37">
-        <v>8</v>
-      </c>
-      <c r="M53" s="41">
+      <c r="E53" s="70" t="s">
+        <v>131</v>
+      </c>
+      <c r="F53" s="69" t="s">
+        <v>196</v>
+      </c>
+      <c r="G53" s="70" t="s">
+        <v>238</v>
+      </c>
+      <c r="H53" s="69" t="s">
+        <v>289</v>
+      </c>
+      <c r="I53" s="69" t="s">
+        <v>443</v>
+      </c>
+      <c r="J53" s="69" t="s">
+        <v>444</v>
+      </c>
+      <c r="K53" s="70" t="s">
+        <v>361</v>
+      </c>
+      <c r="L53" s="87">
+        <v>4</v>
+      </c>
+      <c r="M53" s="71">
         <f t="shared" si="1"/>
-        <v>160</v>
-      </c>
-      <c r="N53" s="41">
-        <f t="shared" si="35"/>
-        <v>176</v>
-      </c>
-      <c r="O53" s="41"/>
-      <c r="P53" s="41"/>
-      <c r="Q53" s="41">
+        <v>80</v>
+      </c>
+      <c r="N53" s="71">
+        <v>85</v>
+      </c>
+      <c r="O53" s="72" t="s">
+        <v>391</v>
+      </c>
+      <c r="P53" s="71">
+        <v>0.21740000000000001</v>
+      </c>
+      <c r="Q53" s="71">
         <f t="shared" ref="Q53" si="44">P53*N53</f>
-        <v>0</v>
-      </c>
-      <c r="R53" s="41"/>
-    </row>
-    <row r="54" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>18.478999999999999</v>
+      </c>
+      <c r="R53" s="71" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1"/>
       <c r="B54" s="53">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="C54" s="60" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D54" s="39" t="s">
         <v>51</v>
       </c>
       <c r="E54" s="40" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F54" s="39" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G54" s="40" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="H54" s="39" t="s">
-        <v>277</v>
-      </c>
-      <c r="I54" s="39"/>
-      <c r="J54" s="39"/>
+        <v>269</v>
+      </c>
+      <c r="I54" s="39" t="s">
+        <v>361</v>
+      </c>
+      <c r="J54" s="39" t="s">
+        <v>446</v>
+      </c>
       <c r="K54" s="40" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="L54" s="39">
         <v>2</v>
@@ -5023,45 +5259,52 @@
         <v>40</v>
       </c>
       <c r="N54" s="42">
-        <f t="shared" si="35"/>
-        <v>44</v>
-      </c>
-      <c r="O54" s="42"/>
-      <c r="P54" s="42"/>
+        <v>100</v>
+      </c>
+      <c r="O54" s="65" t="s">
+        <v>391</v>
+      </c>
+      <c r="P54" s="42">
+        <v>1E-3</v>
+      </c>
       <c r="Q54" s="42">
         <f t="shared" ref="Q54" si="45">N54*P54</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="R54" s="42"/>
     </row>
-    <row r="55" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1"/>
       <c r="B55" s="53">
         <f>ROW(B55) - ROW($B$9)</f>
         <v>46</v>
       </c>
       <c r="C55" s="61" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D55" s="37" t="s">
         <v>52</v>
       </c>
       <c r="E55" s="38" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F55" s="37" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G55" s="38" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="H55" s="37" t="s">
-        <v>277</v>
-      </c>
-      <c r="I55" s="37"/>
-      <c r="J55" s="37"/>
+        <v>269</v>
+      </c>
+      <c r="I55" s="37" t="s">
+        <v>361</v>
+      </c>
+      <c r="J55" s="37" t="s">
+        <v>447</v>
+      </c>
       <c r="K55" s="38" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="L55" s="37">
         <v>1</v>
@@ -5071,45 +5314,52 @@
         <v>20</v>
       </c>
       <c r="N55" s="41">
-        <f t="shared" si="35"/>
-        <v>22</v>
-      </c>
-      <c r="O55" s="41"/>
-      <c r="P55" s="41"/>
+        <v>100</v>
+      </c>
+      <c r="O55" s="64" t="s">
+        <v>391</v>
+      </c>
+      <c r="P55" s="41">
+        <v>1.4E-3</v>
+      </c>
       <c r="Q55" s="41">
         <f t="shared" ref="Q55" si="46">P55*N55</f>
-        <v>0</v>
+        <v>0.13999999999999999</v>
       </c>
       <c r="R55" s="41"/>
     </row>
-    <row r="56" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
       <c r="B56" s="53">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="C56" s="60" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D56" s="39" t="s">
         <v>53</v>
       </c>
       <c r="E56" s="40" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F56" s="39" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G56" s="40" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="H56" s="39" t="s">
-        <v>298</v>
-      </c>
-      <c r="I56" s="39"/>
-      <c r="J56" s="39"/>
+        <v>290</v>
+      </c>
+      <c r="I56" s="39" t="s">
+        <v>361</v>
+      </c>
+      <c r="J56" s="39" t="s">
+        <v>448</v>
+      </c>
       <c r="K56" s="40" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="L56" s="39">
         <v>1</v>
@@ -5119,45 +5369,52 @@
         <v>20</v>
       </c>
       <c r="N56" s="42">
-        <f t="shared" si="35"/>
-        <v>22</v>
-      </c>
-      <c r="O56" s="42"/>
-      <c r="P56" s="42"/>
+        <v>100</v>
+      </c>
+      <c r="O56" s="65" t="s">
+        <v>391</v>
+      </c>
+      <c r="P56" s="42">
+        <v>1.6000000000000001E-3</v>
+      </c>
       <c r="Q56" s="42">
         <f t="shared" ref="Q56" si="47">N56*P56</f>
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="R56" s="42"/>
     </row>
-    <row r="57" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1"/>
       <c r="B57" s="53">
         <f>ROW(B57) - ROW($B$9)</f>
         <v>48</v>
       </c>
       <c r="C57" s="61" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D57" s="37" t="s">
         <v>54</v>
       </c>
       <c r="E57" s="38" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F57" s="37" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G57" s="38" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="H57" s="37" t="s">
-        <v>277</v>
-      </c>
-      <c r="I57" s="37"/>
-      <c r="J57" s="37"/>
+        <v>269</v>
+      </c>
+      <c r="I57" s="37" t="s">
+        <v>361</v>
+      </c>
+      <c r="J57" s="37" t="s">
+        <v>449</v>
+      </c>
       <c r="K57" s="38" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="L57" s="37">
         <v>2</v>
@@ -5167,45 +5424,52 @@
         <v>40</v>
       </c>
       <c r="N57" s="41">
-        <f t="shared" si="35"/>
-        <v>44</v>
-      </c>
-      <c r="O57" s="41"/>
-      <c r="P57" s="41"/>
+        <v>100</v>
+      </c>
+      <c r="O57" s="64" t="s">
+        <v>391</v>
+      </c>
+      <c r="P57" s="41">
+        <v>1.4E-3</v>
+      </c>
       <c r="Q57" s="41">
         <f t="shared" ref="Q57" si="48">P57*N57</f>
-        <v>0</v>
+        <v>0.13999999999999999</v>
       </c>
       <c r="R57" s="41"/>
     </row>
-    <row r="58" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1"/>
       <c r="B58" s="53">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="C58" s="60" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D58" s="39" t="s">
         <v>55</v>
       </c>
       <c r="E58" s="40" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F58" s="39" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G58" s="40" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="H58" s="39" t="s">
-        <v>277</v>
-      </c>
-      <c r="I58" s="39"/>
-      <c r="J58" s="39"/>
+        <v>269</v>
+      </c>
+      <c r="I58" s="39" t="s">
+        <v>361</v>
+      </c>
+      <c r="J58" s="39" t="s">
+        <v>450</v>
+      </c>
       <c r="K58" s="40" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="L58" s="39">
         <v>4</v>
@@ -5215,45 +5479,52 @@
         <v>80</v>
       </c>
       <c r="N58" s="42">
-        <f t="shared" si="35"/>
-        <v>88</v>
-      </c>
-      <c r="O58" s="42"/>
-      <c r="P58" s="42"/>
+        <v>100</v>
+      </c>
+      <c r="O58" s="65" t="s">
+        <v>391</v>
+      </c>
+      <c r="P58" s="42">
+        <v>1.2999999999999999E-3</v>
+      </c>
       <c r="Q58" s="42">
         <f t="shared" ref="Q58" si="49">N58*P58</f>
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="R58" s="42"/>
     </row>
-    <row r="59" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1"/>
       <c r="B59" s="53">
         <f>ROW(B59) - ROW($B$9)</f>
         <v>50</v>
       </c>
       <c r="C59" s="61" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D59" s="37" t="s">
         <v>56</v>
       </c>
       <c r="E59" s="38" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F59" s="37" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="G59" s="38" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="H59" s="37" t="s">
-        <v>299</v>
-      </c>
-      <c r="I59" s="37"/>
-      <c r="J59" s="37"/>
+        <v>291</v>
+      </c>
+      <c r="I59" s="37" t="s">
+        <v>451</v>
+      </c>
+      <c r="J59" s="37" t="s">
+        <v>452</v>
+      </c>
       <c r="K59" s="38" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="L59" s="37">
         <v>4</v>
@@ -5263,93 +5534,107 @@
         <v>80</v>
       </c>
       <c r="N59" s="41">
-        <f t="shared" si="35"/>
-        <v>88</v>
-      </c>
-      <c r="O59" s="41"/>
-      <c r="P59" s="41"/>
+        <v>90</v>
+      </c>
+      <c r="O59" s="64" t="s">
+        <v>391</v>
+      </c>
+      <c r="P59" s="41">
+        <v>6.4500000000000002E-2</v>
+      </c>
       <c r="Q59" s="41">
         <f t="shared" ref="Q59" si="50">P59*N59</f>
-        <v>0</v>
+        <v>5.8049999999999997</v>
       </c>
       <c r="R59" s="41"/>
     </row>
-    <row r="60" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1"/>
       <c r="B60" s="53">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
       <c r="C60" s="60" t="s">
-        <v>381</v>
-      </c>
-      <c r="D60" s="39" t="s">
-        <v>57</v>
+        <v>372</v>
+      </c>
+      <c r="D60" s="75" t="s">
+        <v>464</v>
       </c>
       <c r="E60" s="40" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F60" s="39" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G60" s="40" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="H60" s="39" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="I60" s="39"/>
-      <c r="J60" s="39"/>
+      <c r="J60" s="39" t="s">
+        <v>453</v>
+      </c>
       <c r="K60" s="40" t="s">
-        <v>344</v>
-      </c>
-      <c r="L60" s="39">
-        <v>8</v>
+        <v>335</v>
+      </c>
+      <c r="L60" s="89">
+        <v>9</v>
       </c>
       <c r="M60" s="42">
         <f t="shared" si="1"/>
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="N60" s="42">
-        <f t="shared" si="35"/>
-        <v>176</v>
-      </c>
-      <c r="O60" s="42"/>
-      <c r="P60" s="42"/>
+        <v>200</v>
+      </c>
+      <c r="O60" s="65" t="s">
+        <v>391</v>
+      </c>
+      <c r="P60" s="42">
+        <v>1.5E-3</v>
+      </c>
       <c r="Q60" s="42">
         <f t="shared" ref="Q60" si="51">N60*P60</f>
-        <v>0</v>
-      </c>
-      <c r="R60" s="42"/>
-    </row>
-    <row r="61" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.3</v>
+      </c>
+      <c r="R60" s="42" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1"/>
       <c r="B61" s="53">
         <f>ROW(B61) - ROW($B$9)</f>
         <v>52</v>
       </c>
       <c r="C61" s="61" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D61" s="37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E61" s="38" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F61" s="37" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G61" s="38" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="H61" s="37" t="s">
-        <v>300</v>
-      </c>
-      <c r="I61" s="37"/>
-      <c r="J61" s="37"/>
+        <v>292</v>
+      </c>
+      <c r="I61" s="37" t="s">
+        <v>361</v>
+      </c>
+      <c r="J61" s="37" t="s">
+        <v>361</v>
+      </c>
       <c r="K61" s="38" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="L61" s="37">
         <v>1</v>
@@ -5359,45 +5644,52 @@
         <v>20</v>
       </c>
       <c r="N61" s="41">
-        <f t="shared" si="35"/>
-        <v>22</v>
-      </c>
-      <c r="O61" s="41"/>
-      <c r="P61" s="41"/>
+        <v>30</v>
+      </c>
+      <c r="O61" s="64" t="s">
+        <v>439</v>
+      </c>
+      <c r="P61" s="41">
+        <v>1.8589999999999999E-2</v>
+      </c>
       <c r="Q61" s="41">
         <f t="shared" ref="Q61" si="52">P61*N61</f>
-        <v>0</v>
+        <v>0.55769999999999997</v>
       </c>
       <c r="R61" s="41"/>
     </row>
-    <row r="62" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1"/>
       <c r="B62" s="53">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
       <c r="C62" s="60" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D62" s="39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E62" s="40" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F62" s="39" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G62" s="40" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="H62" s="39" t="s">
-        <v>277</v>
-      </c>
-      <c r="I62" s="39"/>
-      <c r="J62" s="39"/>
+        <v>269</v>
+      </c>
+      <c r="I62" s="39" t="s">
+        <v>361</v>
+      </c>
+      <c r="J62" s="39" t="s">
+        <v>454</v>
+      </c>
       <c r="K62" s="40" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="L62" s="39">
         <v>1</v>
@@ -5407,45 +5699,52 @@
         <v>20</v>
       </c>
       <c r="N62" s="42">
-        <f t="shared" si="35"/>
-        <v>22</v>
-      </c>
-      <c r="O62" s="42"/>
-      <c r="P62" s="42"/>
+        <v>100</v>
+      </c>
+      <c r="O62" s="65" t="s">
+        <v>391</v>
+      </c>
+      <c r="P62" s="42">
+        <v>1.4E-3</v>
+      </c>
       <c r="Q62" s="42">
         <f t="shared" ref="Q62" si="53">N62*P62</f>
-        <v>0</v>
+        <v>0.13999999999999999</v>
       </c>
       <c r="R62" s="42"/>
     </row>
-    <row r="63" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1"/>
       <c r="B63" s="53">
         <f>ROW(B63) - ROW($B$9)</f>
         <v>54</v>
       </c>
       <c r="C63" s="61" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D63" s="37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E63" s="38" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F63" s="37" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G63" s="38" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="H63" s="37" t="s">
-        <v>300</v>
-      </c>
-      <c r="I63" s="37"/>
-      <c r="J63" s="37"/>
+        <v>292</v>
+      </c>
+      <c r="I63" s="37" t="s">
+        <v>361</v>
+      </c>
+      <c r="J63" s="37" t="s">
+        <v>361</v>
+      </c>
       <c r="K63" s="38" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="L63" s="37">
         <v>1</v>
@@ -5455,45 +5754,52 @@
         <v>20</v>
       </c>
       <c r="N63" s="41">
-        <f t="shared" si="35"/>
-        <v>22</v>
-      </c>
-      <c r="O63" s="41"/>
-      <c r="P63" s="41"/>
+        <v>50</v>
+      </c>
+      <c r="O63" s="64" t="s">
+        <v>439</v>
+      </c>
+      <c r="P63" s="41">
+        <v>4.6699999999999997E-3</v>
+      </c>
       <c r="Q63" s="41">
         <f t="shared" ref="Q63" si="54">P63*N63</f>
-        <v>0</v>
+        <v>0.23349999999999999</v>
       </c>
       <c r="R63" s="41"/>
     </row>
-    <row r="64" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1"/>
       <c r="B64" s="53">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
       <c r="C64" s="60" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D64" s="39" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E64" s="40" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F64" s="39" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G64" s="40" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="H64" s="39" t="s">
-        <v>277</v>
-      </c>
-      <c r="I64" s="39"/>
-      <c r="J64" s="39"/>
+        <v>269</v>
+      </c>
+      <c r="I64" s="39" t="s">
+        <v>361</v>
+      </c>
+      <c r="J64" s="39" t="s">
+        <v>455</v>
+      </c>
       <c r="K64" s="40" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="L64" s="39">
         <v>1</v>
@@ -5503,45 +5809,52 @@
         <v>20</v>
       </c>
       <c r="N64" s="42">
-        <f t="shared" si="35"/>
-        <v>22</v>
-      </c>
-      <c r="O64" s="42"/>
-      <c r="P64" s="42"/>
+        <v>100</v>
+      </c>
+      <c r="O64" s="65" t="s">
+        <v>391</v>
+      </c>
+      <c r="P64" s="42">
+        <v>1.1999999999999999E-3</v>
+      </c>
       <c r="Q64" s="42">
         <f t="shared" ref="Q64" si="55">N64*P64</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="R64" s="42"/>
     </row>
-    <row r="65" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1"/>
       <c r="B65" s="53">
         <f>ROW(B65) - ROW($B$9)</f>
         <v>56</v>
       </c>
       <c r="C65" s="61" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D65" s="37" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E65" s="38" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F65" s="37" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G65" s="38" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="H65" s="37" t="s">
-        <v>300</v>
-      </c>
-      <c r="I65" s="37"/>
-      <c r="J65" s="37"/>
+        <v>292</v>
+      </c>
+      <c r="I65" s="37" t="s">
+        <v>361</v>
+      </c>
+      <c r="J65" s="37" t="s">
+        <v>361</v>
+      </c>
       <c r="K65" s="38" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="L65" s="37">
         <v>1</v>
@@ -5551,45 +5864,52 @@
         <v>20</v>
       </c>
       <c r="N65" s="41">
-        <f t="shared" si="35"/>
-        <v>22</v>
-      </c>
-      <c r="O65" s="41"/>
-      <c r="P65" s="41"/>
+        <v>50</v>
+      </c>
+      <c r="O65" s="64" t="s">
+        <v>439</v>
+      </c>
+      <c r="P65" s="41">
+        <v>1.11E-2</v>
+      </c>
       <c r="Q65" s="41">
         <f t="shared" ref="Q65" si="56">P65*N65</f>
-        <v>0</v>
+        <v>0.55500000000000005</v>
       </c>
       <c r="R65" s="41"/>
     </row>
-    <row r="66" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
       <c r="B66" s="53">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
       <c r="C66" s="60" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D66" s="39" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E66" s="40" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F66" s="39" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G66" s="40" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="H66" s="39" t="s">
-        <v>277</v>
-      </c>
-      <c r="I66" s="39"/>
-      <c r="J66" s="39"/>
+        <v>269</v>
+      </c>
+      <c r="I66" s="39" t="s">
+        <v>361</v>
+      </c>
+      <c r="J66" s="39" t="s">
+        <v>456</v>
+      </c>
       <c r="K66" s="40" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="L66" s="39">
         <v>1</v>
@@ -5599,45 +5919,52 @@
         <v>20</v>
       </c>
       <c r="N66" s="42">
-        <f t="shared" si="35"/>
-        <v>22</v>
-      </c>
-      <c r="O66" s="42"/>
-      <c r="P66" s="42"/>
+        <v>100</v>
+      </c>
+      <c r="O66" s="65" t="s">
+        <v>391</v>
+      </c>
+      <c r="P66" s="42">
+        <v>2.0999999999999999E-3</v>
+      </c>
       <c r="Q66" s="42">
         <f t="shared" ref="Q66" si="57">N66*P66</f>
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="R66" s="42"/>
     </row>
-    <row r="67" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1"/>
       <c r="B67" s="53">
         <f>ROW(B67) - ROW($B$9)</f>
         <v>58</v>
       </c>
       <c r="C67" s="61" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D67" s="37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E67" s="38" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F67" s="37" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G67" s="38" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="H67" s="37" t="s">
-        <v>277</v>
-      </c>
-      <c r="I67" s="37"/>
-      <c r="J67" s="37"/>
+        <v>269</v>
+      </c>
+      <c r="I67" s="37" t="s">
+        <v>361</v>
+      </c>
+      <c r="J67" s="37" t="s">
+        <v>457</v>
+      </c>
       <c r="K67" s="38" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="L67" s="37">
         <v>1</v>
@@ -5647,45 +5974,52 @@
         <v>20</v>
       </c>
       <c r="N67" s="41">
-        <f t="shared" si="35"/>
-        <v>22</v>
-      </c>
-      <c r="O67" s="41"/>
-      <c r="P67" s="41"/>
+        <v>100</v>
+      </c>
+      <c r="O67" s="64" t="s">
+        <v>391</v>
+      </c>
+      <c r="P67" s="41">
+        <v>1.6000000000000001E-3</v>
+      </c>
       <c r="Q67" s="41">
         <f t="shared" ref="Q67" si="58">P67*N67</f>
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="R67" s="41"/>
     </row>
-    <row r="68" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1"/>
       <c r="B68" s="53">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
       <c r="C68" s="60" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D68" s="39" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E68" s="40" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F68" s="39" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G68" s="40" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="H68" s="39" t="s">
-        <v>277</v>
-      </c>
-      <c r="I68" s="39"/>
-      <c r="J68" s="39"/>
+        <v>269</v>
+      </c>
+      <c r="I68" s="39" t="s">
+        <v>458</v>
+      </c>
+      <c r="J68" s="39" t="s">
+        <v>459</v>
+      </c>
       <c r="K68" s="40" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="L68" s="39">
         <v>1</v>
@@ -5695,141 +6029,164 @@
         <v>20</v>
       </c>
       <c r="N68" s="42">
-        <f t="shared" si="35"/>
-        <v>22</v>
-      </c>
-      <c r="O68" s="42"/>
-      <c r="P68" s="42"/>
+        <v>50</v>
+      </c>
+      <c r="O68" s="65" t="s">
+        <v>391</v>
+      </c>
+      <c r="P68" s="42">
+        <v>6.8999999999999999E-3</v>
+      </c>
       <c r="Q68" s="42">
         <f t="shared" ref="Q68" si="59">N68*P68</f>
-        <v>0</v>
+        <v>0.34499999999999997</v>
       </c>
       <c r="R68" s="42"/>
     </row>
-    <row r="69" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1"/>
       <c r="B69" s="53">
         <f>ROW(B69) - ROW($B$9)</f>
         <v>60</v>
       </c>
       <c r="C69" s="61" t="s">
-        <v>381</v>
-      </c>
-      <c r="D69" s="37" t="s">
-        <v>66</v>
+        <v>372</v>
+      </c>
+      <c r="D69" s="69" t="s">
+        <v>461</v>
       </c>
       <c r="E69" s="38" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F69" s="37" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G69" s="38" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="H69" s="37" t="s">
-        <v>277</v>
-      </c>
-      <c r="I69" s="37"/>
-      <c r="J69" s="37"/>
+        <v>269</v>
+      </c>
+      <c r="I69" s="37" t="s">
+        <v>361</v>
+      </c>
+      <c r="J69" s="37" t="s">
+        <v>460</v>
+      </c>
       <c r="K69" s="38" t="s">
-        <v>353</v>
-      </c>
-      <c r="L69" s="37">
-        <v>1</v>
+        <v>344</v>
+      </c>
+      <c r="L69" s="88">
+        <v>2</v>
       </c>
       <c r="M69" s="41">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N69" s="41">
-        <f t="shared" si="35"/>
-        <v>22</v>
-      </c>
-      <c r="O69" s="41"/>
-      <c r="P69" s="41"/>
+        <v>100</v>
+      </c>
+      <c r="O69" s="64" t="s">
+        <v>391</v>
+      </c>
+      <c r="P69" s="41">
+        <v>1.1000000000000001E-3</v>
+      </c>
       <c r="Q69" s="41">
         <f t="shared" ref="Q69" si="60">P69*N69</f>
-        <v>0</v>
-      </c>
-      <c r="R69" s="41"/>
-    </row>
-    <row r="70" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.11</v>
+      </c>
+      <c r="R69" s="41" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1"/>
       <c r="B70" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B70) - ROW($B$9)</f>
         <v>61</v>
       </c>
-      <c r="C70" s="60" t="s">
-        <v>381</v>
-      </c>
-      <c r="D70" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="E70" s="40" t="s">
-        <v>152</v>
-      </c>
-      <c r="F70" s="39" t="s">
-        <v>203</v>
-      </c>
-      <c r="G70" s="40" t="s">
-        <v>260</v>
-      </c>
-      <c r="H70" s="39" t="s">
-        <v>277</v>
-      </c>
-      <c r="I70" s="39"/>
-      <c r="J70" s="39"/>
-      <c r="K70" s="40" t="s">
-        <v>353</v>
-      </c>
-      <c r="L70" s="39">
-        <v>1</v>
-      </c>
-      <c r="M70" s="42">
+      <c r="C70" s="61" t="s">
+        <v>372</v>
+      </c>
+      <c r="D70" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="E70" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="F70" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="G70" s="38" t="s">
+        <v>254</v>
+      </c>
+      <c r="H70" s="37" t="s">
+        <v>269</v>
+      </c>
+      <c r="I70" s="37" t="s">
+        <v>361</v>
+      </c>
+      <c r="J70" s="37" t="s">
+        <v>462</v>
+      </c>
+      <c r="K70" s="38" t="s">
+        <v>345</v>
+      </c>
+      <c r="L70" s="37">
+        <v>2</v>
+      </c>
+      <c r="M70" s="41">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N70" s="42">
-        <f t="shared" si="35"/>
-        <v>22</v>
-      </c>
-      <c r="O70" s="42"/>
-      <c r="P70" s="42"/>
-      <c r="Q70" s="42">
-        <f t="shared" ref="Q70" si="61">N70*P70</f>
-        <v>0</v>
-      </c>
-      <c r="R70" s="42"/>
-    </row>
-    <row r="71" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="N70" s="41">
+        <v>100</v>
+      </c>
+      <c r="O70" s="64" t="s">
+        <v>391</v>
+      </c>
+      <c r="P70" s="41">
+        <v>1.5E-3</v>
+      </c>
+      <c r="Q70" s="41">
+        <f t="shared" ref="Q70" si="61">P70*N70</f>
+        <v>0.15</v>
+      </c>
+      <c r="R70" s="41"/>
+    </row>
+    <row r="71" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1"/>
       <c r="B71" s="53">
         <f>ROW(B71) - ROW($B$9)</f>
         <v>62</v>
       </c>
       <c r="C71" s="61" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D71" s="37" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E71" s="38" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F71" s="37" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G71" s="38" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="H71" s="37" t="s">
-        <v>277</v>
-      </c>
-      <c r="I71" s="37"/>
-      <c r="J71" s="37"/>
+        <v>269</v>
+      </c>
+      <c r="I71" s="37" t="s">
+        <v>361</v>
+      </c>
+      <c r="J71" s="37" t="s">
+        <v>466</v>
+      </c>
       <c r="K71" s="38" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="L71" s="37">
         <v>2</v>
@@ -5839,45 +6196,52 @@
         <v>40</v>
       </c>
       <c r="N71" s="41">
-        <f t="shared" si="35"/>
-        <v>44</v>
-      </c>
-      <c r="O71" s="41"/>
-      <c r="P71" s="41"/>
+        <v>100</v>
+      </c>
+      <c r="O71" s="64" t="s">
+        <v>391</v>
+      </c>
+      <c r="P71" s="41">
+        <v>1.5E-3</v>
+      </c>
       <c r="Q71" s="41">
         <f t="shared" ref="Q71" si="62">P71*N71</f>
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="R71" s="41"/>
     </row>
-    <row r="72" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1"/>
       <c r="B72" s="53">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
       <c r="C72" s="60" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D72" s="39" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E72" s="40" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F72" s="39" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="G72" s="40" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="H72" s="39" t="s">
-        <v>301</v>
-      </c>
-      <c r="I72" s="39"/>
-      <c r="J72" s="39"/>
+        <v>292</v>
+      </c>
+      <c r="I72" s="39" t="s">
+        <v>361</v>
+      </c>
+      <c r="J72" s="39" t="s">
+        <v>361</v>
+      </c>
       <c r="K72" s="40" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L72" s="39">
         <v>1</v>
@@ -5887,392 +6251,445 @@
         <v>20</v>
       </c>
       <c r="N72" s="42">
-        <f t="shared" si="35"/>
-        <v>22</v>
-      </c>
-      <c r="O72" s="42"/>
-      <c r="P72" s="42"/>
+        <v>25</v>
+      </c>
+      <c r="O72" s="65" t="s">
+        <v>467</v>
+      </c>
+      <c r="P72" s="42">
+        <v>8.5400000000000004E-2</v>
+      </c>
       <c r="Q72" s="42">
         <f t="shared" ref="Q72" si="63">N72*P72</f>
-        <v>0</v>
+        <v>2.1350000000000002</v>
       </c>
       <c r="R72" s="42"/>
     </row>
-    <row r="73" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1"/>
       <c r="B73" s="53">
         <f>ROW(B73) - ROW($B$9)</f>
         <v>64</v>
       </c>
       <c r="C73" s="61" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D73" s="37" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E73" s="38" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F73" s="37" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="G73" s="38" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="H73" s="37" t="s">
-        <v>277</v>
-      </c>
-      <c r="I73" s="37"/>
-      <c r="J73" s="37"/>
+        <v>269</v>
+      </c>
+      <c r="I73" s="37" t="s">
+        <v>361</v>
+      </c>
+      <c r="J73" s="37" t="s">
+        <v>468</v>
+      </c>
       <c r="K73" s="38" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="L73" s="37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M73" s="41">
-        <f t="shared" si="1"/>
-        <v>40</v>
+        <f t="shared" ref="M73:M91" si="64">L73*20</f>
+        <v>20</v>
       </c>
       <c r="N73" s="41">
-        <f t="shared" si="35"/>
-        <v>44</v>
-      </c>
-      <c r="O73" s="41"/>
-      <c r="P73" s="41"/>
+        <v>100</v>
+      </c>
+      <c r="O73" s="64" t="s">
+        <v>391</v>
+      </c>
+      <c r="P73" s="41">
+        <v>1.1999999999999999E-3</v>
+      </c>
       <c r="Q73" s="41">
-        <f t="shared" ref="Q73" si="64">P73*N73</f>
-        <v>0</v>
+        <f t="shared" ref="Q73" si="65">P73*N73</f>
+        <v>0.12</v>
       </c>
       <c r="R73" s="41"/>
     </row>
-    <row r="74" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1"/>
       <c r="B74" s="53">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
       <c r="C74" s="60" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D74" s="39" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E74" s="40" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="F74" s="39" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G74" s="40" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="H74" s="39" t="s">
-        <v>300</v>
-      </c>
-      <c r="I74" s="39"/>
-      <c r="J74" s="39"/>
+        <v>292</v>
+      </c>
+      <c r="I74" s="39" t="s">
+        <v>361</v>
+      </c>
+      <c r="J74" s="39" t="s">
+        <v>361</v>
+      </c>
       <c r="K74" s="40" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="L74" s="39">
         <v>1</v>
       </c>
       <c r="M74" s="42">
-        <f t="shared" si="1"/>
+        <f t="shared" si="64"/>
         <v>20</v>
       </c>
       <c r="N74" s="42">
-        <f t="shared" si="35"/>
-        <v>22</v>
-      </c>
-      <c r="O74" s="42"/>
-      <c r="P74" s="42"/>
+        <v>25</v>
+      </c>
+      <c r="O74" s="65" t="s">
+        <v>439</v>
+      </c>
+      <c r="P74" s="42">
+        <v>1.8589999999999999E-2</v>
+      </c>
       <c r="Q74" s="42">
-        <f t="shared" ref="Q74" si="65">N74*P74</f>
-        <v>0</v>
+        <f t="shared" ref="Q74" si="66">N74*P74</f>
+        <v>0.46475</v>
       </c>
       <c r="R74" s="42"/>
     </row>
-    <row r="75" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1"/>
       <c r="B75" s="53">
         <f>ROW(B75) - ROW($B$9)</f>
         <v>66</v>
       </c>
       <c r="C75" s="61" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D75" s="37" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E75" s="38" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F75" s="37" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="G75" s="38" t="s">
-        <v>265</v>
+        <v>378</v>
       </c>
       <c r="H75" s="37" t="s">
-        <v>277</v>
-      </c>
-      <c r="I75" s="37"/>
-      <c r="J75" s="37"/>
+        <v>293</v>
+      </c>
+      <c r="I75" s="37" t="s">
+        <v>361</v>
+      </c>
+      <c r="J75" s="37" t="s">
+        <v>469</v>
+      </c>
       <c r="K75" s="38" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="L75" s="37">
         <v>1</v>
       </c>
       <c r="M75" s="41">
-        <f t="shared" ref="M75:M93" si="66">L75*20</f>
+        <f t="shared" si="64"/>
         <v>20</v>
       </c>
       <c r="N75" s="41">
-        <f t="shared" ref="N75:N93" si="67">M75+(M75*0.1)</f>
-        <v>22</v>
-      </c>
-      <c r="O75" s="41"/>
-      <c r="P75" s="41"/>
+        <v>100</v>
+      </c>
+      <c r="O75" s="64" t="s">
+        <v>391</v>
+      </c>
+      <c r="P75" s="41">
+        <v>1E-3</v>
+      </c>
       <c r="Q75" s="41">
-        <f t="shared" ref="Q75" si="68">P75*N75</f>
-        <v>0</v>
+        <f t="shared" ref="Q75" si="67">P75*N75</f>
+        <v>0.1</v>
       </c>
       <c r="R75" s="41"/>
     </row>
-    <row r="76" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1"/>
       <c r="B76" s="53">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
       <c r="C76" s="60" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D76" s="39" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E76" s="40" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F76" s="39" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G76" s="40" t="s">
-        <v>266</v>
+        <v>379</v>
       </c>
       <c r="H76" s="39" t="s">
-        <v>300</v>
-      </c>
-      <c r="I76" s="39"/>
-      <c r="J76" s="39"/>
+        <v>294</v>
+      </c>
+      <c r="I76" s="39" t="s">
+        <v>361</v>
+      </c>
+      <c r="J76" s="39" t="s">
+        <v>470</v>
+      </c>
       <c r="K76" s="40" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="L76" s="39">
         <v>1</v>
       </c>
       <c r="M76" s="42">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>20</v>
       </c>
       <c r="N76" s="42">
-        <f t="shared" si="67"/>
-        <v>22</v>
-      </c>
-      <c r="O76" s="42"/>
-      <c r="P76" s="42"/>
+        <v>50</v>
+      </c>
+      <c r="O76" s="65" t="s">
+        <v>391</v>
+      </c>
+      <c r="P76" s="42">
+        <v>4.3E-3</v>
+      </c>
       <c r="Q76" s="42">
-        <f t="shared" ref="Q76" si="69">N76*P76</f>
-        <v>0</v>
+        <f t="shared" ref="Q76" si="68">N76*P76</f>
+        <v>0.215</v>
       </c>
       <c r="R76" s="42"/>
     </row>
-    <row r="77" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1"/>
       <c r="B77" s="53">
         <f>ROW(B77) - ROW($B$9)</f>
         <v>68</v>
       </c>
       <c r="C77" s="61" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D77" s="37" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E77" s="38" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F77" s="37" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G77" s="38" t="s">
-        <v>387</v>
+        <v>259</v>
       </c>
       <c r="H77" s="37" t="s">
-        <v>302</v>
-      </c>
-      <c r="I77" s="37"/>
-      <c r="J77" s="37"/>
+        <v>269</v>
+      </c>
+      <c r="I77" s="37" t="s">
+        <v>361</v>
+      </c>
+      <c r="J77" s="37" t="s">
+        <v>471</v>
+      </c>
       <c r="K77" s="38" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="L77" s="37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M77" s="41">
-        <f t="shared" si="66"/>
-        <v>20</v>
+        <f t="shared" si="64"/>
+        <v>80</v>
       </c>
       <c r="N77" s="41">
-        <f t="shared" si="67"/>
-        <v>22</v>
-      </c>
-      <c r="O77" s="41"/>
-      <c r="P77" s="41"/>
+        <v>100</v>
+      </c>
+      <c r="O77" s="64" t="s">
+        <v>391</v>
+      </c>
+      <c r="P77" s="41">
+        <v>1.1999999999999999E-3</v>
+      </c>
       <c r="Q77" s="41">
-        <f t="shared" ref="Q77" si="70">P77*N77</f>
-        <v>0</v>
+        <f t="shared" ref="Q77" si="69">P77*N77</f>
+        <v>0.12</v>
       </c>
       <c r="R77" s="41"/>
     </row>
-    <row r="78" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1"/>
       <c r="B78" s="53">
         <f t="shared" si="0"/>
         <v>69</v>
       </c>
       <c r="C78" s="60" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D78" s="39" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E78" s="40" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F78" s="39" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G78" s="40" t="s">
-        <v>388</v>
+        <v>260</v>
       </c>
       <c r="H78" s="39" t="s">
-        <v>303</v>
-      </c>
-      <c r="I78" s="39"/>
-      <c r="J78" s="39"/>
+        <v>269</v>
+      </c>
+      <c r="I78" s="39" t="s">
+        <v>361</v>
+      </c>
+      <c r="J78" s="39" t="s">
+        <v>472</v>
+      </c>
       <c r="K78" s="40" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="L78" s="39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M78" s="42">
-        <f t="shared" si="66"/>
-        <v>20</v>
+        <f t="shared" si="64"/>
+        <v>80</v>
       </c>
       <c r="N78" s="42">
-        <f t="shared" si="67"/>
-        <v>22</v>
-      </c>
-      <c r="O78" s="42"/>
-      <c r="P78" s="42"/>
+        <v>100</v>
+      </c>
+      <c r="O78" s="65" t="s">
+        <v>391</v>
+      </c>
+      <c r="P78" s="42">
+        <v>1.1999999999999999E-3</v>
+      </c>
       <c r="Q78" s="42">
-        <f t="shared" ref="Q78" si="71">N78*P78</f>
-        <v>0</v>
+        <f t="shared" ref="Q78" si="70">N78*P78</f>
+        <v>0.12</v>
       </c>
       <c r="R78" s="42"/>
     </row>
-    <row r="79" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1"/>
-      <c r="B79" s="53">
+      <c r="B79" s="82">
         <f>ROW(B79) - ROW($B$9)</f>
         <v>70</v>
       </c>
-      <c r="C79" s="61" t="s">
-        <v>381</v>
-      </c>
-      <c r="D79" s="37" t="s">
-        <v>76</v>
-      </c>
-      <c r="E79" s="38" t="s">
-        <v>161</v>
-      </c>
-      <c r="F79" s="37" t="s">
-        <v>206</v>
-      </c>
-      <c r="G79" s="38" t="s">
-        <v>267</v>
-      </c>
-      <c r="H79" s="37" t="s">
-        <v>277</v>
-      </c>
-      <c r="I79" s="37"/>
-      <c r="J79" s="37"/>
-      <c r="K79" s="38" t="s">
-        <v>361</v>
-      </c>
-      <c r="L79" s="37">
-        <v>4</v>
-      </c>
-      <c r="M79" s="41">
-        <f t="shared" si="66"/>
-        <v>80</v>
-      </c>
-      <c r="N79" s="41">
-        <f t="shared" si="67"/>
-        <v>88</v>
-      </c>
-      <c r="O79" s="41"/>
-      <c r="P79" s="41"/>
-      <c r="Q79" s="41">
+      <c r="C79" s="83" t="s">
+        <v>201</v>
+      </c>
+      <c r="D79" s="84" t="s">
+        <v>74</v>
+      </c>
+      <c r="E79" s="85" t="s">
+        <v>157</v>
+      </c>
+      <c r="F79" s="84" t="s">
+        <v>201</v>
+      </c>
+      <c r="G79" s="85" t="s">
+        <v>361</v>
+      </c>
+      <c r="H79" s="84" t="s">
+        <v>361</v>
+      </c>
+      <c r="I79" s="84" t="s">
+        <v>361</v>
+      </c>
+      <c r="J79" s="84" t="s">
+        <v>361</v>
+      </c>
+      <c r="K79" s="85" t="s">
+        <v>361</v>
+      </c>
+      <c r="L79" s="84">
+        <v>11</v>
+      </c>
+      <c r="M79" s="86">
+        <f t="shared" si="64"/>
+        <v>220</v>
+      </c>
+      <c r="N79" s="86">
+        <f t="shared" ref="N73:N91" si="71">M79+(M79*0.1)</f>
+        <v>242</v>
+      </c>
+      <c r="O79" s="86"/>
+      <c r="P79" s="86"/>
+      <c r="Q79" s="86">
         <f t="shared" ref="Q79" si="72">P79*N79</f>
         <v>0</v>
       </c>
-      <c r="R79" s="41"/>
-    </row>
-    <row r="80" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R79" s="90" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1"/>
       <c r="B80" s="53">
         <f t="shared" si="0"/>
         <v>71</v>
       </c>
       <c r="C80" s="60" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="D80" s="39" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E80" s="40" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F80" s="39" t="s">
-        <v>203</v>
-      </c>
-      <c r="G80" s="40" t="s">
-        <v>268</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="G80" s="40"/>
       <c r="H80" s="39" t="s">
-        <v>277</v>
-      </c>
-      <c r="I80" s="39"/>
-      <c r="J80" s="39"/>
+        <v>295</v>
+      </c>
+      <c r="I80" s="39" t="s">
+        <v>361</v>
+      </c>
+      <c r="J80" s="39" t="s">
+        <v>361</v>
+      </c>
       <c r="K80" s="40" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="L80" s="39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M80" s="42">
-        <f t="shared" si="66"/>
-        <v>80</v>
+        <f t="shared" si="64"/>
+        <v>20</v>
       </c>
       <c r="N80" s="42">
-        <f t="shared" si="67"/>
-        <v>88</v>
+        <f t="shared" si="71"/>
+        <v>22</v>
       </c>
       <c r="O80" s="42"/>
       <c r="P80" s="42"/>
@@ -6282,45 +6699,45 @@
       </c>
       <c r="R80" s="42"/>
     </row>
-    <row r="81" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1"/>
       <c r="B81" s="53">
         <f>ROW(B81) - ROW($B$9)</f>
         <v>72</v>
       </c>
       <c r="C81" s="61" t="s">
-        <v>207</v>
+        <v>375</v>
       </c>
       <c r="D81" s="37" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E81" s="38" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F81" s="37" t="s">
-        <v>207</v>
-      </c>
-      <c r="G81" s="38" t="s">
-        <v>370</v>
+        <v>355</v>
+      </c>
+      <c r="G81" s="38">
+        <v>750314597</v>
       </c>
       <c r="H81" s="37" t="s">
-        <v>370</v>
+        <v>296</v>
       </c>
       <c r="I81" s="37"/>
       <c r="J81" s="37"/>
       <c r="K81" s="38" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="L81" s="37">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M81" s="41">
-        <f t="shared" si="66"/>
-        <v>220</v>
+        <f t="shared" si="64"/>
+        <v>20</v>
       </c>
       <c r="N81" s="41">
-        <f t="shared" si="67"/>
-        <v>242</v>
+        <f t="shared" si="71"/>
+        <v>22</v>
       </c>
       <c r="O81" s="41"/>
       <c r="P81" s="41"/>
@@ -6330,43 +6747,48 @@
       </c>
       <c r="R81" s="41"/>
     </row>
-    <row r="82" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1"/>
       <c r="B82" s="53">
         <f t="shared" si="0"/>
         <v>73</v>
       </c>
       <c r="C82" s="60" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="D82" s="39" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E82" s="40" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F82" s="39" t="s">
-        <v>208</v>
-      </c>
-      <c r="G82" s="40"/>
+        <v>355</v>
+      </c>
+      <c r="G82" s="40" t="s">
+        <v>203</v>
+      </c>
       <c r="H82" s="39" t="s">
-        <v>304</v>
-      </c>
-      <c r="I82" s="39"/>
-      <c r="J82" s="39"/>
+        <v>297</v>
+      </c>
+      <c r="I82" s="39" t="s">
+        <v>361</v>
+      </c>
+      <c r="J82" s="39" t="s">
+        <v>361</v>
+      </c>
       <c r="K82" s="40" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="L82" s="39">
         <v>1</v>
       </c>
       <c r="M82" s="42">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>20</v>
       </c>
       <c r="N82" s="42">
-        <f t="shared" si="67"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O82" s="42"/>
       <c r="P82" s="42"/>
@@ -6376,44 +6798,44 @@
       </c>
       <c r="R82" s="42"/>
     </row>
-    <row r="83" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1"/>
       <c r="B83" s="53">
         <f>ROW(B83) - ROW($B$9)</f>
         <v>74</v>
       </c>
       <c r="C83" s="61" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="D83" s="37" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E83" s="38" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F83" s="37" t="s">
-        <v>364</v>
-      </c>
-      <c r="G83" s="38">
-        <v>750314597</v>
+        <v>204</v>
+      </c>
+      <c r="G83" s="38" t="s">
+        <v>261</v>
       </c>
       <c r="H83" s="37" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="I83" s="37"/>
       <c r="J83" s="37"/>
       <c r="K83" s="38" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="L83" s="37">
         <v>1</v>
       </c>
       <c r="M83" s="41">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>20</v>
       </c>
       <c r="N83" s="41">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>22</v>
       </c>
       <c r="O83" s="41"/>
@@ -6424,42 +6846,44 @@
       </c>
       <c r="R83" s="41"/>
     </row>
-    <row r="84" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="1"/>
       <c r="B84" s="53">
         <f t="shared" si="0"/>
         <v>75</v>
       </c>
       <c r="C84" s="60" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="D84" s="39" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E84" s="40" t="s">
-        <v>166</v>
-      </c>
-      <c r="F84" s="39"/>
+        <v>162</v>
+      </c>
+      <c r="F84" s="39" t="s">
+        <v>205</v>
+      </c>
       <c r="G84" s="40" t="s">
-        <v>209</v>
+        <v>262</v>
       </c>
       <c r="H84" s="39" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="I84" s="39"/>
       <c r="J84" s="39"/>
       <c r="K84" s="40" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="L84" s="39">
         <v>1</v>
       </c>
       <c r="M84" s="42">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>20</v>
       </c>
       <c r="N84" s="42">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>22</v>
       </c>
       <c r="O84" s="42"/>
@@ -6470,44 +6894,44 @@
       </c>
       <c r="R84" s="42"/>
     </row>
-    <row r="85" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="1"/>
       <c r="B85" s="53">
         <f>ROW(B85) - ROW($B$9)</f>
         <v>76</v>
       </c>
       <c r="C85" s="61" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="D85" s="37" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E85" s="38" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F85" s="37" t="s">
-        <v>210</v>
+        <v>357</v>
       </c>
       <c r="G85" s="38" t="s">
-        <v>269</v>
+        <v>206</v>
       </c>
       <c r="H85" s="37" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="I85" s="37"/>
       <c r="J85" s="37"/>
       <c r="K85" s="38" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="L85" s="37">
         <v>1</v>
       </c>
       <c r="M85" s="41">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>20</v>
       </c>
       <c r="N85" s="41">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>22</v>
       </c>
       <c r="O85" s="41"/>
@@ -6518,44 +6942,44 @@
       </c>
       <c r="R85" s="41"/>
     </row>
-    <row r="86" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="1"/>
       <c r="B86" s="53">
         <f t="shared" si="0"/>
         <v>77</v>
       </c>
       <c r="C86" s="60" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="D86" s="39" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E86" s="40" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F86" s="39" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="G86" s="40" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="H86" s="39" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="I86" s="39"/>
       <c r="J86" s="39"/>
       <c r="K86" s="40" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="L86" s="39">
         <v>1</v>
       </c>
       <c r="M86" s="42">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>20</v>
       </c>
       <c r="N86" s="42">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>22</v>
       </c>
       <c r="O86" s="42"/>
@@ -6566,44 +6990,44 @@
       </c>
       <c r="R86" s="42"/>
     </row>
-    <row r="87" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="1"/>
       <c r="B87" s="53">
         <f>ROW(B87) - ROW($B$9)</f>
         <v>78</v>
       </c>
       <c r="C87" s="61" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="D87" s="37" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E87" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F87" s="37" t="s">
-        <v>366</v>
+        <v>208</v>
       </c>
       <c r="G87" s="38" t="s">
-        <v>212</v>
+        <v>264</v>
       </c>
       <c r="H87" s="37" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="I87" s="37"/>
       <c r="J87" s="37"/>
       <c r="K87" s="38" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="L87" s="37">
         <v>1</v>
       </c>
       <c r="M87" s="41">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>20</v>
       </c>
       <c r="N87" s="41">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>22</v>
       </c>
       <c r="O87" s="41"/>
@@ -6614,44 +7038,44 @@
       </c>
       <c r="R87" s="41"/>
     </row>
-    <row r="88" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="1"/>
       <c r="B88" s="53">
         <f t="shared" si="0"/>
         <v>79</v>
       </c>
       <c r="C88" s="60" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="D88" s="39" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E88" s="40" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F88" s="39" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="G88" s="40" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="H88" s="39" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="I88" s="39"/>
       <c r="J88" s="39"/>
-      <c r="K88" s="40" t="s">
-        <v>370</v>
+      <c r="K88" s="58" t="s">
+        <v>362</v>
       </c>
       <c r="L88" s="39">
         <v>1</v>
       </c>
       <c r="M88" s="42">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>20</v>
       </c>
       <c r="N88" s="42">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>22</v>
       </c>
       <c r="O88" s="42"/>
@@ -6662,44 +7086,44 @@
       </c>
       <c r="R88" s="42"/>
     </row>
-    <row r="89" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="1"/>
       <c r="B89" s="53">
         <f>ROW(B89) - ROW($B$9)</f>
         <v>80</v>
       </c>
       <c r="C89" s="61" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="D89" s="37" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E89" s="38" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F89" s="37" t="s">
-        <v>214</v>
+        <v>358</v>
       </c>
       <c r="G89" s="38" t="s">
-        <v>272</v>
+        <v>210</v>
       </c>
       <c r="H89" s="37" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="I89" s="37"/>
       <c r="J89" s="37"/>
       <c r="K89" s="38" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="L89" s="37">
         <v>1</v>
       </c>
       <c r="M89" s="41">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>20</v>
       </c>
       <c r="N89" s="41">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>22</v>
       </c>
       <c r="O89" s="41"/>
@@ -6710,44 +7134,44 @@
       </c>
       <c r="R89" s="41"/>
     </row>
-    <row r="90" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="1"/>
       <c r="B90" s="53">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
       <c r="C90" s="60" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="D90" s="39" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E90" s="40" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F90" s="39" t="s">
-        <v>215</v>
+        <v>359</v>
       </c>
       <c r="G90" s="40" t="s">
-        <v>273</v>
+        <v>211</v>
       </c>
       <c r="H90" s="39" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="I90" s="39"/>
       <c r="J90" s="39"/>
-      <c r="K90" s="58" t="s">
-        <v>371</v>
+      <c r="K90" s="40" t="s">
+        <v>361</v>
       </c>
       <c r="L90" s="39">
         <v>1</v>
       </c>
       <c r="M90" s="42">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>20</v>
       </c>
       <c r="N90" s="42">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>22</v>
       </c>
       <c r="O90" s="42"/>
@@ -6758,44 +7182,44 @@
       </c>
       <c r="R90" s="42"/>
     </row>
-    <row r="91" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="1"/>
       <c r="B91" s="53">
         <f>ROW(B91) - ROW($B$9)</f>
         <v>82</v>
       </c>
       <c r="C91" s="61" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="D91" s="37" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E91" s="38" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F91" s="37" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="G91" s="38" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="H91" s="37" t="s">
-        <v>306</v>
-      </c>
-      <c r="I91" s="37"/>
-      <c r="J91" s="37"/>
+        <v>297</v>
+      </c>
+      <c r="I91" s="63"/>
+      <c r="J91" s="63"/>
       <c r="K91" s="38" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="L91" s="37">
         <v>1</v>
       </c>
       <c r="M91" s="41">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>20</v>
       </c>
       <c r="N91" s="41">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>22</v>
       </c>
       <c r="O91" s="41"/>
@@ -6806,145 +7230,49 @@
       </c>
       <c r="R91" s="41"/>
     </row>
-    <row r="92" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
-      <c r="B92" s="53">
-        <f t="shared" si="0"/>
-        <v>83</v>
-      </c>
-      <c r="C92" s="60" t="s">
-        <v>385</v>
-      </c>
-      <c r="D92" s="39" t="s">
-        <v>89</v>
-      </c>
-      <c r="E92" s="40" t="s">
-        <v>174</v>
-      </c>
-      <c r="F92" s="39" t="s">
-        <v>368</v>
-      </c>
-      <c r="G92" s="40" t="s">
-        <v>217</v>
-      </c>
-      <c r="H92" s="39" t="s">
-        <v>309</v>
-      </c>
-      <c r="I92" s="39"/>
-      <c r="J92" s="39"/>
-      <c r="K92" s="40" t="s">
-        <v>370</v>
-      </c>
-      <c r="L92" s="39">
-        <v>1</v>
-      </c>
-      <c r="M92" s="42">
-        <f t="shared" si="66"/>
-        <v>20</v>
-      </c>
-      <c r="N92" s="42">
-        <f t="shared" si="67"/>
-        <v>22</v>
-      </c>
-      <c r="O92" s="42"/>
-      <c r="P92" s="42"/>
-      <c r="Q92" s="42">
-        <f t="shared" ref="Q92" si="85">N92*P92</f>
-        <v>0</v>
-      </c>
-      <c r="R92" s="42"/>
-    </row>
-    <row r="93" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B92" s="32"/>
+      <c r="C92" s="51"/>
+      <c r="D92" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="E92" s="34"/>
+      <c r="F92" s="35"/>
+      <c r="G92" s="36"/>
+      <c r="H92" s="35"/>
+      <c r="I92" s="35"/>
+      <c r="J92" s="35"/>
+      <c r="K92" s="36"/>
+      <c r="L92" s="36"/>
+      <c r="M92" s="36"/>
+      <c r="N92" s="36"/>
+      <c r="O92" s="36"/>
+      <c r="P92" s="36"/>
+      <c r="Q92" s="36"/>
+      <c r="R92" s="44"/>
+    </row>
+    <row r="93" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="1"/>
-      <c r="B93" s="53">
-        <f>ROW(B93) - ROW($B$9)</f>
-        <v>84</v>
-      </c>
-      <c r="C93" s="61" t="s">
-        <v>385</v>
-      </c>
-      <c r="D93" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="E93" s="38" t="s">
-        <v>175</v>
-      </c>
-      <c r="F93" s="37" t="s">
-        <v>369</v>
-      </c>
-      <c r="G93" s="38" t="s">
-        <v>218</v>
-      </c>
-      <c r="H93" s="37" t="s">
-        <v>306</v>
-      </c>
-      <c r="I93" s="66"/>
-      <c r="J93" s="66"/>
-      <c r="K93" s="38" t="s">
-        <v>370</v>
-      </c>
-      <c r="L93" s="37">
-        <v>1</v>
-      </c>
-      <c r="M93" s="41">
-        <f t="shared" si="66"/>
-        <v>20</v>
-      </c>
-      <c r="N93" s="41">
-        <f t="shared" si="67"/>
-        <v>22</v>
-      </c>
-      <c r="O93" s="41"/>
-      <c r="P93" s="41"/>
-      <c r="Q93" s="41">
-        <f t="shared" ref="Q93" si="86">P93*N93</f>
-        <v>0</v>
-      </c>
-      <c r="R93" s="41"/>
-    </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A94" s="1"/>
-      <c r="B94" s="32"/>
-      <c r="C94" s="51"/>
-      <c r="D94" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="E94" s="34"/>
-      <c r="F94" s="35"/>
-      <c r="G94" s="36"/>
-      <c r="H94" s="35"/>
-      <c r="I94" s="35"/>
-      <c r="J94" s="35"/>
-      <c r="K94" s="36"/>
-      <c r="L94" s="36"/>
-      <c r="M94" s="36"/>
-      <c r="N94" s="36"/>
-      <c r="O94" s="36"/>
-      <c r="P94" s="36"/>
-      <c r="Q94" s="36"/>
-      <c r="R94" s="44"/>
-    </row>
-    <row r="95" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="1"/>
-      <c r="B95" s="24"/>
-      <c r="C95" s="52"/>
-      <c r="D95" s="8" t="s">
+      <c r="B93" s="24"/>
+      <c r="C93" s="52"/>
+      <c r="D93" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E95" s="9"/>
-      <c r="F95" s="9"/>
-      <c r="G95" s="9"/>
-      <c r="H95" s="9"/>
-      <c r="I95" s="9"/>
-      <c r="J95" s="9"/>
-      <c r="K95" s="9"/>
-      <c r="L95" s="9"/>
-      <c r="M95" s="9"/>
-      <c r="N95" s="9"/>
-      <c r="O95" s="9"/>
-      <c r="P95" s="9"/>
-      <c r="Q95" s="9"/>
-      <c r="R95" s="45"/>
+      <c r="E93" s="9"/>
+      <c r="F93" s="9"/>
+      <c r="G93" s="9"/>
+      <c r="H93" s="9"/>
+      <c r="I93" s="9"/>
+      <c r="J93" s="9"/>
+      <c r="K93" s="9"/>
+      <c r="L93" s="9"/>
+      <c r="M93" s="9"/>
+      <c r="N93" s="9"/>
+      <c r="O93" s="9"/>
+      <c r="P93" s="9"/>
+      <c r="Q93" s="9"/>
+      <c r="R93" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6987,9 +7315,42 @@
     <hyperlink ref="O42" r:id="rId33"/>
     <hyperlink ref="O43" r:id="rId34"/>
     <hyperlink ref="O44" r:id="rId35"/>
+    <hyperlink ref="O45" r:id="rId36"/>
+    <hyperlink ref="O46" r:id="rId37"/>
+    <hyperlink ref="O47" r:id="rId38"/>
+    <hyperlink ref="O48" r:id="rId39"/>
+    <hyperlink ref="O49" r:id="rId40"/>
+    <hyperlink ref="O50" r:id="rId41"/>
+    <hyperlink ref="O52" r:id="rId42"/>
+    <hyperlink ref="O53" r:id="rId43"/>
+    <hyperlink ref="O54" r:id="rId44"/>
+    <hyperlink ref="O55" r:id="rId45"/>
+    <hyperlink ref="O56" r:id="rId46"/>
+    <hyperlink ref="O57" r:id="rId47"/>
+    <hyperlink ref="O58" r:id="rId48"/>
+    <hyperlink ref="O59" r:id="rId49"/>
+    <hyperlink ref="O60" r:id="rId50"/>
+    <hyperlink ref="O61" r:id="rId51"/>
+    <hyperlink ref="O62" r:id="rId52"/>
+    <hyperlink ref="O63" r:id="rId53"/>
+    <hyperlink ref="O64" r:id="rId54"/>
+    <hyperlink ref="O65" r:id="rId55"/>
+    <hyperlink ref="O66" r:id="rId56"/>
+    <hyperlink ref="O67" r:id="rId57"/>
+    <hyperlink ref="O68" r:id="rId58"/>
+    <hyperlink ref="O69" r:id="rId59"/>
+    <hyperlink ref="O70" r:id="rId60"/>
+    <hyperlink ref="O71" r:id="rId61"/>
+    <hyperlink ref="O72" r:id="rId62"/>
+    <hyperlink ref="O73" r:id="rId63"/>
+    <hyperlink ref="O74" r:id="rId64"/>
+    <hyperlink ref="O75" r:id="rId65"/>
+    <hyperlink ref="O76" r:id="rId66"/>
+    <hyperlink ref="O77" r:id="rId67"/>
+    <hyperlink ref="O78" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId36"/>
-  <drawing r:id="rId37"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId69"/>
+  <drawing r:id="rId70"/>
 </worksheet>
 </file>
--- a/Deliverables/SM_Top Board/_BOM/eSpark BOM (20 Boards).xlsx
+++ b/Deliverables/SM_Top Board/_BOM/eSpark BOM (20 Boards).xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Faizan\GitHub\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SM COM\Desktop\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15480" windowHeight="7872"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="490">
   <si>
     <t>Component list</t>
   </si>
@@ -1485,6 +1485,57 @@
   <si>
     <t>C98220</t>
   </si>
+  <si>
+    <t>Winsource</t>
+  </si>
+  <si>
+    <t>TLV75733PDBVR</t>
+  </si>
+  <si>
+    <t>C485517</t>
+  </si>
+  <si>
+    <t>Design change required. May cause change in some other misc components</t>
+  </si>
+  <si>
+    <t>BD9876AEFJ-E2</t>
+  </si>
+  <si>
+    <t>C79958</t>
+  </si>
+  <si>
+    <t>C100023</t>
+  </si>
+  <si>
+    <t>C516354</t>
+  </si>
+  <si>
+    <t>Need confirmation from client regarding price</t>
+  </si>
+  <si>
+    <t>ISO7221ADR</t>
+  </si>
+  <si>
+    <t>C28037</t>
+  </si>
+  <si>
+    <t>Design change required. May cause change in some other misc components. Quantity also changed from 1/board to 2/board</t>
+  </si>
+  <si>
+    <t>ISO6761FDWR</t>
+  </si>
+  <si>
+    <t>Digikey</t>
+  </si>
+  <si>
+    <t>C7042</t>
+  </si>
+  <si>
+    <t>SUM</t>
+  </si>
+  <si>
+    <t>PER BOARD COST</t>
+  </si>
 </sst>
 </file>
 
@@ -1493,7 +1544,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1653,8 +1704,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1694,6 +1753,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1950,7 +2015,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -2165,6 +2230,33 @@
     <xf numFmtId="0" fontId="19" fillId="6" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2174,33 +2266,54 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2544,26 +2657,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:R93"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="3.109375" style="25" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" style="25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="30.109375" customWidth="1"/>
-    <col min="7" max="7" width="33.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="22.109375" customWidth="1"/>
-    <col min="11" max="11" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="16.6640625" customWidth="1"/>
-    <col min="16" max="16" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="29.44140625" customWidth="1"/>
+    <col min="6" max="6" width="30.140625" customWidth="1"/>
+    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="22.140625" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="16.7109375" customWidth="1"/>
+    <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -2574,16 +2687,16 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="79"/>
-      <c r="P1" s="79"/>
-      <c r="Q1" s="79"/>
-      <c r="R1" s="79"/>
-    </row>
-    <row r="2" spans="1:18" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="88"/>
+      <c r="P1" s="88"/>
+      <c r="Q1" s="88"/>
+      <c r="R1" s="88"/>
+    </row>
+    <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
       <c r="C2" s="46"/>
@@ -2607,7 +2720,7 @@
       <c r="Q2" s="3"/>
       <c r="R2" s="43"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
       <c r="C3" s="47"/>
@@ -2629,9 +2742,9 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="80"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R3" s="89"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
       <c r="C4" s="47"/>
@@ -2653,9 +2766,9 @@
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="Q4" s="62"/>
-      <c r="R4" s="81"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R4" s="90"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
       <c r="C5" s="47"/>
@@ -2675,9 +2788,9 @@
       <c r="O5" s="62"/>
       <c r="P5" s="62"/>
       <c r="Q5" s="62"/>
-      <c r="R5" s="81"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R5" s="90"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
       <c r="C6" s="48"/>
@@ -2695,9 +2808,9 @@
       <c r="O6" s="62"/>
       <c r="P6" s="62"/>
       <c r="Q6" s="62"/>
-      <c r="R6" s="81"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R6" s="90"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
       <c r="C7" s="49"/>
@@ -2715,9 +2828,9 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="81"/>
-    </row>
-    <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R7" s="90"/>
+    </row>
+    <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="26"/>
       <c r="C8" s="50"/>
@@ -2735,9 +2848,9 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="81"/>
-    </row>
-    <row r="9" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R8" s="90"/>
+    </row>
+    <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="29" t="s">
         <v>4</v>
@@ -2791,7 +2904,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="53">
         <f>ROW(B10) - ROW($B$9)</f>
@@ -2846,7 +2959,7 @@
       </c>
       <c r="R10" s="41"/>
     </row>
-    <row r="11" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="53">
         <f t="shared" ref="B11:B90" si="0">ROW(B11) - ROW($B$9)</f>
@@ -2901,7 +3014,7 @@
       </c>
       <c r="R11" s="42"/>
     </row>
-    <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="53">
         <f>ROW(B12) - ROW($B$9)</f>
@@ -2956,7 +3069,7 @@
       </c>
       <c r="R12" s="41"/>
     </row>
-    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="53">
         <f t="shared" si="0"/>
@@ -3011,7 +3124,7 @@
       </c>
       <c r="R13" s="42"/>
     </row>
-    <row r="14" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="53">
         <f>ROW(B14) - ROW($B$9)</f>
@@ -3066,7 +3179,7 @@
       </c>
       <c r="R14" s="41"/>
     </row>
-    <row r="15" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="53">
         <f t="shared" si="0"/>
@@ -3121,7 +3234,7 @@
       </c>
       <c r="R15" s="42"/>
     </row>
-    <row r="16" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="53">
         <f>ROW(B16) - ROW($B$9)</f>
@@ -3176,7 +3289,7 @@
       </c>
       <c r="R16" s="41"/>
     </row>
-    <row r="17" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="53">
         <f t="shared" si="0"/>
@@ -3231,7 +3344,7 @@
       </c>
       <c r="R17" s="42"/>
     </row>
-    <row r="18" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="53">
         <f>ROW(B18) - ROW($B$9)</f>
@@ -3286,7 +3399,7 @@
       </c>
       <c r="R18" s="41"/>
     </row>
-    <row r="19" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="53">
         <f t="shared" si="0"/>
@@ -3341,7 +3454,7 @@
       </c>
       <c r="R19" s="42"/>
     </row>
-    <row r="20" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="53">
         <f>ROW(B20) - ROW($B$9)</f>
@@ -3396,7 +3509,7 @@
       </c>
       <c r="R20" s="41"/>
     </row>
-    <row r="21" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="53">
         <f t="shared" si="0"/>
@@ -3451,7 +3564,7 @@
       </c>
       <c r="R21" s="42"/>
     </row>
-    <row r="22" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="53">
         <f>ROW(B22) - ROW($B$9)</f>
@@ -3506,7 +3619,7 @@
       </c>
       <c r="R22" s="41"/>
     </row>
-    <row r="23" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="53">
         <f>ROW(B23) - ROW($B$9)</f>
@@ -3561,7 +3674,7 @@
       </c>
       <c r="R23" s="41"/>
     </row>
-    <row r="24" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="53">
         <f t="shared" si="0"/>
@@ -3616,7 +3729,7 @@
       </c>
       <c r="R24" s="42"/>
     </row>
-    <row r="25" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="53">
         <f>ROW(B25) - ROW($B$9)</f>
@@ -3671,7 +3784,7 @@
       </c>
       <c r="R25" s="41"/>
     </row>
-    <row r="26" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="53">
         <f t="shared" si="0"/>
@@ -3726,7 +3839,7 @@
       </c>
       <c r="R26" s="42"/>
     </row>
-    <row r="27" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="53">
         <f>ROW(B27) - ROW($B$9)</f>
@@ -3781,7 +3894,7 @@
       </c>
       <c r="R27" s="41"/>
     </row>
-    <row r="28" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="53">
         <f t="shared" si="0"/>
@@ -3836,7 +3949,7 @@
       </c>
       <c r="R28" s="42"/>
     </row>
-    <row r="29" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="53">
         <f>ROW(B29) - ROW($B$9)</f>
@@ -3891,7 +4004,7 @@
       </c>
       <c r="R29" s="41"/>
     </row>
-    <row r="30" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="53">
         <f t="shared" si="0"/>
@@ -3946,7 +4059,7 @@
       </c>
       <c r="R30" s="42"/>
     </row>
-    <row r="31" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="53">
         <f>ROW(B31) - ROW($B$9)</f>
@@ -4001,7 +4114,7 @@
       </c>
       <c r="R31" s="41"/>
     </row>
-    <row r="32" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="53">
         <f t="shared" si="0"/>
@@ -4056,7 +4169,7 @@
       </c>
       <c r="R32" s="42"/>
     </row>
-    <row r="33" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="53">
         <f>ROW(B33) - ROW($B$9)</f>
@@ -4111,7 +4224,7 @@
       </c>
       <c r="R33" s="41"/>
     </row>
-    <row r="34" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="53">
         <f t="shared" si="0"/>
@@ -4166,7 +4279,7 @@
       </c>
       <c r="R34" s="42"/>
     </row>
-    <row r="35" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="53">
         <f>ROW(B35) - ROW($B$9)</f>
@@ -4221,7 +4334,7 @@
       </c>
       <c r="R35" s="41"/>
     </row>
-    <row r="36" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="53">
         <f t="shared" si="0"/>
@@ -4276,7 +4389,7 @@
       </c>
       <c r="R36" s="42"/>
     </row>
-    <row r="37" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="53">
         <f>ROW(B37) - ROW($B$9)</f>
@@ -4331,7 +4444,7 @@
       </c>
       <c r="R37" s="41"/>
     </row>
-    <row r="38" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="53">
         <f t="shared" si="0"/>
@@ -4386,7 +4499,7 @@
       </c>
       <c r="R38" s="42"/>
     </row>
-    <row r="39" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="67">
         <f>ROW(B39) - ROW($B$9)</f>
@@ -4443,7 +4556,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="53">
         <f t="shared" si="0"/>
@@ -4498,7 +4611,7 @@
       </c>
       <c r="R40" s="42"/>
     </row>
-    <row r="41" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="53">
         <f>ROW(B41) - ROW($B$9)</f>
@@ -4553,7 +4666,7 @@
       </c>
       <c r="R41" s="41"/>
     </row>
-    <row r="42" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="67">
         <f t="shared" si="0"/>
@@ -4610,7 +4723,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="67">
         <f>ROW(B43) - ROW($B$9)</f>
@@ -4667,7 +4780,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="53">
         <f t="shared" si="0"/>
@@ -4722,7 +4835,7 @@
       </c>
       <c r="R44" s="42"/>
     </row>
-    <row r="45" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="53">
         <f>ROW(B45) - ROW($B$9)</f>
@@ -4777,7 +4890,7 @@
       </c>
       <c r="R45" s="41"/>
     </row>
-    <row r="46" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="53">
         <f t="shared" si="0"/>
@@ -4832,7 +4945,7 @@
       </c>
       <c r="R46" s="42"/>
     </row>
-    <row r="47" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="53">
         <f>ROW(B47) - ROW($B$9)</f>
@@ -4887,7 +5000,7 @@
       </c>
       <c r="R47" s="41"/>
     </row>
-    <row r="48" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="53">
         <f t="shared" si="0"/>
@@ -4942,7 +5055,7 @@
       </c>
       <c r="R48" s="42"/>
     </row>
-    <row r="49" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="53">
         <f>ROW(B49) - ROW($B$9)</f>
@@ -4997,7 +5110,7 @@
       </c>
       <c r="R49" s="41"/>
     </row>
-    <row r="50" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="53">
         <f t="shared" si="0"/>
@@ -5054,57 +5167,57 @@
         <v>441</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
-      <c r="B51" s="82">
+      <c r="B51" s="79">
         <f>ROW(B51) - ROW($B$9)</f>
         <v>42</v>
       </c>
-      <c r="C51" s="83" t="s">
+      <c r="C51" s="80" t="s">
         <v>328</v>
       </c>
-      <c r="D51" s="84" t="s">
+      <c r="D51" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="E51" s="85" t="s">
+      <c r="E51" s="82" t="s">
         <v>129</v>
       </c>
-      <c r="F51" s="84" t="s">
+      <c r="F51" s="81" t="s">
         <v>194</v>
       </c>
-      <c r="G51" s="85" t="s">
-        <v>361</v>
-      </c>
-      <c r="H51" s="84" t="s">
-        <v>361</v>
-      </c>
-      <c r="I51" s="84"/>
-      <c r="J51" s="84"/>
-      <c r="K51" s="85" t="s">
-        <v>361</v>
-      </c>
-      <c r="L51" s="84">
+      <c r="G51" s="82" t="s">
+        <v>361</v>
+      </c>
+      <c r="H51" s="81" t="s">
+        <v>361</v>
+      </c>
+      <c r="I51" s="81"/>
+      <c r="J51" s="81"/>
+      <c r="K51" s="82" t="s">
+        <v>361</v>
+      </c>
+      <c r="L51" s="81">
         <v>4</v>
       </c>
-      <c r="M51" s="86">
+      <c r="M51" s="83">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N51" s="86">
-        <f t="shared" ref="N51:N72" si="41">M51+(M51*0.1)</f>
+      <c r="N51" s="83">
+        <f t="shared" ref="N51" si="41">M51+(M51*0.1)</f>
         <v>88</v>
       </c>
-      <c r="O51" s="86"/>
-      <c r="P51" s="86"/>
-      <c r="Q51" s="86">
+      <c r="O51" s="83"/>
+      <c r="P51" s="83"/>
+      <c r="Q51" s="83">
         <f t="shared" ref="Q51" si="42">P51*N51</f>
         <v>0</v>
       </c>
-      <c r="R51" s="90" t="s">
+      <c r="R51" s="87" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="53">
         <f t="shared" si="0"/>
@@ -5161,7 +5274,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="67">
         <f>ROW(B53) - ROW($B$9)</f>
@@ -5194,7 +5307,7 @@
       <c r="K53" s="70" t="s">
         <v>361</v>
       </c>
-      <c r="L53" s="87">
+      <c r="L53" s="84">
         <v>4</v>
       </c>
       <c r="M53" s="71">
@@ -5218,7 +5331,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="53">
         <f t="shared" si="0"/>
@@ -5273,7 +5386,7 @@
       </c>
       <c r="R54" s="42"/>
     </row>
-    <row r="55" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="53">
         <f>ROW(B55) - ROW($B$9)</f>
@@ -5328,7 +5441,7 @@
       </c>
       <c r="R55" s="41"/>
     </row>
-    <row r="56" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="53">
         <f t="shared" si="0"/>
@@ -5383,7 +5496,7 @@
       </c>
       <c r="R56" s="42"/>
     </row>
-    <row r="57" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="53">
         <f>ROW(B57) - ROW($B$9)</f>
@@ -5438,7 +5551,7 @@
       </c>
       <c r="R57" s="41"/>
     </row>
-    <row r="58" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="53">
         <f t="shared" si="0"/>
@@ -5493,7 +5606,7 @@
       </c>
       <c r="R58" s="42"/>
     </row>
-    <row r="59" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="53">
         <f>ROW(B59) - ROW($B$9)</f>
@@ -5548,7 +5661,7 @@
       </c>
       <c r="R59" s="41"/>
     </row>
-    <row r="60" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="53">
         <f t="shared" si="0"/>
@@ -5579,7 +5692,7 @@
       <c r="K60" s="40" t="s">
         <v>335</v>
       </c>
-      <c r="L60" s="89">
+      <c r="L60" s="86">
         <v>9</v>
       </c>
       <c r="M60" s="42">
@@ -5603,7 +5716,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="53">
         <f>ROW(B61) - ROW($B$9)</f>
@@ -5658,7 +5771,7 @@
       </c>
       <c r="R61" s="41"/>
     </row>
-    <row r="62" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="53">
         <f t="shared" si="0"/>
@@ -5713,7 +5826,7 @@
       </c>
       <c r="R62" s="42"/>
     </row>
-    <row r="63" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="53">
         <f>ROW(B63) - ROW($B$9)</f>
@@ -5768,7 +5881,7 @@
       </c>
       <c r="R63" s="41"/>
     </row>
-    <row r="64" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="53">
         <f t="shared" si="0"/>
@@ -5823,7 +5936,7 @@
       </c>
       <c r="R64" s="42"/>
     </row>
-    <row r="65" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="53">
         <f>ROW(B65) - ROW($B$9)</f>
@@ -5878,7 +5991,7 @@
       </c>
       <c r="R65" s="41"/>
     </row>
-    <row r="66" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="53">
         <f t="shared" si="0"/>
@@ -5933,7 +6046,7 @@
       </c>
       <c r="R66" s="42"/>
     </row>
-    <row r="67" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="53">
         <f>ROW(B67) - ROW($B$9)</f>
@@ -5988,7 +6101,7 @@
       </c>
       <c r="R67" s="41"/>
     </row>
-    <row r="68" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="53">
         <f t="shared" si="0"/>
@@ -6043,7 +6156,7 @@
       </c>
       <c r="R68" s="42"/>
     </row>
-    <row r="69" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="53">
         <f>ROW(B69) - ROW($B$9)</f>
@@ -6076,7 +6189,7 @@
       <c r="K69" s="38" t="s">
         <v>344</v>
       </c>
-      <c r="L69" s="88">
+      <c r="L69" s="85">
         <v>2</v>
       </c>
       <c r="M69" s="41">
@@ -6100,7 +6213,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="53">
         <f>ROW(B70) - ROW($B$9)</f>
@@ -6155,7 +6268,7 @@
       </c>
       <c r="R70" s="41"/>
     </row>
-    <row r="71" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="53">
         <f>ROW(B71) - ROW($B$9)</f>
@@ -6210,7 +6323,7 @@
       </c>
       <c r="R71" s="41"/>
     </row>
-    <row r="72" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="53">
         <f t="shared" si="0"/>
@@ -6265,7 +6378,7 @@
       </c>
       <c r="R72" s="42"/>
     </row>
-    <row r="73" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="53">
         <f>ROW(B73) - ROW($B$9)</f>
@@ -6320,7 +6433,7 @@
       </c>
       <c r="R73" s="41"/>
     </row>
-    <row r="74" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="53">
         <f t="shared" si="0"/>
@@ -6375,7 +6488,7 @@
       </c>
       <c r="R74" s="42"/>
     </row>
-    <row r="75" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="53">
         <f>ROW(B75) - ROW($B$9)</f>
@@ -6430,7 +6543,7 @@
       </c>
       <c r="R75" s="41"/>
     </row>
-    <row r="76" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="53">
         <f t="shared" si="0"/>
@@ -6485,7 +6598,7 @@
       </c>
       <c r="R76" s="42"/>
     </row>
-    <row r="77" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="53">
         <f>ROW(B77) - ROW($B$9)</f>
@@ -6540,7 +6653,7 @@
       </c>
       <c r="R77" s="41"/>
     </row>
-    <row r="78" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="53">
         <f t="shared" si="0"/>
@@ -6595,61 +6708,61 @@
       </c>
       <c r="R78" s="42"/>
     </row>
-    <row r="79" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
-      <c r="B79" s="82">
+      <c r="B79" s="79">
         <f>ROW(B79) - ROW($B$9)</f>
         <v>70</v>
       </c>
-      <c r="C79" s="83" t="s">
+      <c r="C79" s="80" t="s">
         <v>201</v>
       </c>
-      <c r="D79" s="84" t="s">
+      <c r="D79" s="81" t="s">
         <v>74</v>
       </c>
-      <c r="E79" s="85" t="s">
+      <c r="E79" s="82" t="s">
         <v>157</v>
       </c>
-      <c r="F79" s="84" t="s">
+      <c r="F79" s="81" t="s">
         <v>201</v>
       </c>
-      <c r="G79" s="85" t="s">
-        <v>361</v>
-      </c>
-      <c r="H79" s="84" t="s">
-        <v>361</v>
-      </c>
-      <c r="I79" s="84" t="s">
-        <v>361</v>
-      </c>
-      <c r="J79" s="84" t="s">
-        <v>361</v>
-      </c>
-      <c r="K79" s="85" t="s">
-        <v>361</v>
-      </c>
-      <c r="L79" s="84">
+      <c r="G79" s="82" t="s">
+        <v>361</v>
+      </c>
+      <c r="H79" s="81" t="s">
+        <v>361</v>
+      </c>
+      <c r="I79" s="81" t="s">
+        <v>361</v>
+      </c>
+      <c r="J79" s="81" t="s">
+        <v>361</v>
+      </c>
+      <c r="K79" s="82" t="s">
+        <v>361</v>
+      </c>
+      <c r="L79" s="81">
         <v>11</v>
       </c>
-      <c r="M79" s="86">
+      <c r="M79" s="83">
         <f t="shared" si="64"/>
         <v>220</v>
       </c>
-      <c r="N79" s="86">
-        <f t="shared" ref="N73:N91" si="71">M79+(M79*0.1)</f>
+      <c r="N79" s="83">
+        <f t="shared" ref="N79:N91" si="71">M79+(M79*0.1)</f>
         <v>242</v>
       </c>
-      <c r="O79" s="86"/>
-      <c r="P79" s="86"/>
-      <c r="Q79" s="86">
+      <c r="O79" s="83"/>
+      <c r="P79" s="83"/>
+      <c r="Q79" s="83">
         <f t="shared" ref="Q79" si="72">P79*N79</f>
         <v>0</v>
       </c>
-      <c r="R79" s="90" t="s">
+      <c r="R79" s="87" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="80" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="53">
         <f t="shared" si="0"/>
@@ -6699,7 +6812,7 @@
       </c>
       <c r="R80" s="42"/>
     </row>
-    <row r="81" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="53">
         <f>ROW(B81) - ROW($B$9)</f>
@@ -6723,8 +6836,12 @@
       <c r="H81" s="37" t="s">
         <v>296</v>
       </c>
-      <c r="I81" s="37"/>
-      <c r="J81" s="37"/>
+      <c r="I81" s="37" t="s">
+        <v>361</v>
+      </c>
+      <c r="J81" s="37" t="s">
+        <v>361</v>
+      </c>
       <c r="K81" s="38" t="s">
         <v>361</v>
       </c>
@@ -6736,18 +6853,21 @@
         <v>20</v>
       </c>
       <c r="N81" s="41">
-        <f t="shared" si="71"/>
-        <v>22</v>
-      </c>
-      <c r="O81" s="41"/>
-      <c r="P81" s="41"/>
+        <v>21</v>
+      </c>
+      <c r="O81" s="64" t="s">
+        <v>435</v>
+      </c>
+      <c r="P81" s="41">
+        <v>3.81</v>
+      </c>
       <c r="Q81" s="41">
         <f t="shared" ref="Q81" si="74">P81*N81</f>
-        <v>0</v>
+        <v>80.010000000000005</v>
       </c>
       <c r="R81" s="41"/>
     </row>
-    <row r="82" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="53">
         <f t="shared" si="0"/>
@@ -6790,111 +6910,133 @@
       <c r="N82" s="42">
         <v>21</v>
       </c>
-      <c r="O82" s="42"/>
-      <c r="P82" s="42"/>
+      <c r="O82" s="65" t="s">
+        <v>473</v>
+      </c>
+      <c r="P82" s="42">
+        <v>2.48</v>
+      </c>
       <c r="Q82" s="42">
         <f t="shared" ref="Q82" si="75">N82*P82</f>
-        <v>0</v>
+        <v>52.08</v>
       </c>
       <c r="R82" s="42"/>
     </row>
-    <row r="83" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
-      <c r="B83" s="53">
+      <c r="B83" s="91">
         <f>ROW(B83) - ROW($B$9)</f>
         <v>74</v>
       </c>
-      <c r="C83" s="61" t="s">
+      <c r="C83" s="92" t="s">
         <v>376</v>
       </c>
-      <c r="D83" s="37" t="s">
+      <c r="D83" s="93" t="s">
         <v>78</v>
       </c>
-      <c r="E83" s="38" t="s">
+      <c r="E83" s="94" t="s">
         <v>161</v>
       </c>
-      <c r="F83" s="37" t="s">
+      <c r="F83" s="93" t="s">
         <v>204</v>
       </c>
-      <c r="G83" s="38" t="s">
+      <c r="G83" s="94" t="s">
         <v>261</v>
       </c>
-      <c r="H83" s="37" t="s">
+      <c r="H83" s="93" t="s">
         <v>298</v>
       </c>
-      <c r="I83" s="37"/>
-      <c r="J83" s="37"/>
-      <c r="K83" s="38" t="s">
-        <v>361</v>
-      </c>
-      <c r="L83" s="37">
+      <c r="I83" s="93" t="s">
+        <v>474</v>
+      </c>
+      <c r="J83" s="93" t="s">
+        <v>475</v>
+      </c>
+      <c r="K83" s="94" t="s">
+        <v>361</v>
+      </c>
+      <c r="L83" s="93">
         <v>1</v>
       </c>
-      <c r="M83" s="41">
+      <c r="M83" s="95">
         <f t="shared" si="64"/>
         <v>20</v>
       </c>
-      <c r="N83" s="41">
-        <f t="shared" si="71"/>
-        <v>22</v>
-      </c>
-      <c r="O83" s="41"/>
-      <c r="P83" s="41"/>
-      <c r="Q83" s="41">
+      <c r="N83" s="95">
+        <v>21</v>
+      </c>
+      <c r="O83" s="96" t="s">
+        <v>391</v>
+      </c>
+      <c r="P83" s="95">
+        <v>1.3939999999999999</v>
+      </c>
+      <c r="Q83" s="95">
         <f t="shared" ref="Q83" si="76">P83*N83</f>
-        <v>0</v>
-      </c>
-      <c r="R83" s="41"/>
-    </row>
-    <row r="84" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+        <v>29.273999999999997</v>
+      </c>
+      <c r="R83" s="97" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
-      <c r="B84" s="53">
+      <c r="B84" s="91">
         <f t="shared" si="0"/>
         <v>75</v>
       </c>
-      <c r="C84" s="60" t="s">
+      <c r="C84" s="98" t="s">
         <v>376</v>
       </c>
-      <c r="D84" s="39" t="s">
+      <c r="D84" s="99" t="s">
         <v>79</v>
       </c>
-      <c r="E84" s="40" t="s">
+      <c r="E84" s="100" t="s">
         <v>162</v>
       </c>
-      <c r="F84" s="39" t="s">
+      <c r="F84" s="99" t="s">
         <v>205</v>
       </c>
-      <c r="G84" s="40" t="s">
+      <c r="G84" s="100" t="s">
         <v>262</v>
       </c>
-      <c r="H84" s="39" t="s">
+      <c r="H84" s="99" t="s">
         <v>297</v>
       </c>
-      <c r="I84" s="39"/>
-      <c r="J84" s="39"/>
-      <c r="K84" s="40" t="s">
-        <v>361</v>
-      </c>
-      <c r="L84" s="39">
+      <c r="I84" s="99" t="s">
+        <v>477</v>
+      </c>
+      <c r="J84" s="99" t="s">
+        <v>478</v>
+      </c>
+      <c r="K84" s="100" t="s">
+        <v>361</v>
+      </c>
+      <c r="L84" s="99">
         <v>1</v>
       </c>
-      <c r="M84" s="42">
+      <c r="M84" s="101">
         <f t="shared" si="64"/>
         <v>20</v>
       </c>
-      <c r="N84" s="42">
-        <f t="shared" si="71"/>
-        <v>22</v>
-      </c>
-      <c r="O84" s="42"/>
-      <c r="P84" s="42"/>
-      <c r="Q84" s="42">
+      <c r="N84" s="101">
+        <v>21</v>
+      </c>
+      <c r="O84" s="102" t="s">
+        <v>391</v>
+      </c>
+      <c r="P84" s="101">
+        <v>0.69430000000000003</v>
+      </c>
+      <c r="Q84" s="101">
         <f t="shared" ref="Q84" si="77">N84*P84</f>
-        <v>0</v>
-      </c>
-      <c r="R84" s="42"/>
-    </row>
-    <row r="85" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>14.580300000000001</v>
+      </c>
+      <c r="R84" s="97" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="53">
         <f>ROW(B85) - ROW($B$9)</f>
@@ -6918,8 +7060,12 @@
       <c r="H85" s="37" t="s">
         <v>297</v>
       </c>
-      <c r="I85" s="37"/>
-      <c r="J85" s="37"/>
+      <c r="I85" s="37" t="s">
+        <v>361</v>
+      </c>
+      <c r="J85" s="37" t="s">
+        <v>361</v>
+      </c>
       <c r="K85" s="38" t="s">
         <v>361</v>
       </c>
@@ -6931,18 +7077,21 @@
         <v>20</v>
       </c>
       <c r="N85" s="41">
-        <f t="shared" si="71"/>
-        <v>22</v>
-      </c>
-      <c r="O85" s="41"/>
-      <c r="P85" s="41"/>
+        <v>21</v>
+      </c>
+      <c r="O85" s="64" t="s">
+        <v>473</v>
+      </c>
+      <c r="P85" s="41">
+        <v>3.637</v>
+      </c>
       <c r="Q85" s="41">
         <f t="shared" ref="Q85" si="78">P85*N85</f>
-        <v>0</v>
+        <v>76.376999999999995</v>
       </c>
       <c r="R85" s="41"/>
     </row>
-    <row r="86" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="53">
         <f t="shared" si="0"/>
@@ -6966,8 +7115,12 @@
       <c r="H86" s="39" t="s">
         <v>297</v>
       </c>
-      <c r="I86" s="39"/>
-      <c r="J86" s="39"/>
+      <c r="I86" s="39" t="s">
+        <v>361</v>
+      </c>
+      <c r="J86" s="39" t="s">
+        <v>479</v>
+      </c>
       <c r="K86" s="40" t="s">
         <v>361</v>
       </c>
@@ -6979,66 +7132,78 @@
         <v>20</v>
       </c>
       <c r="N86" s="42">
-        <f t="shared" si="71"/>
-        <v>22</v>
-      </c>
-      <c r="O86" s="42"/>
-      <c r="P86" s="42"/>
+        <v>21</v>
+      </c>
+      <c r="O86" s="65" t="s">
+        <v>391</v>
+      </c>
+      <c r="P86" s="42">
+        <v>0.43280000000000002</v>
+      </c>
       <c r="Q86" s="42">
         <f t="shared" ref="Q86" si="79">N86*P86</f>
-        <v>0</v>
+        <v>9.0888000000000009</v>
       </c>
       <c r="R86" s="42"/>
     </row>
-    <row r="87" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
-      <c r="B87" s="53">
+      <c r="B87" s="91">
         <f>ROW(B87) - ROW($B$9)</f>
         <v>78</v>
       </c>
-      <c r="C87" s="61" t="s">
+      <c r="C87" s="92" t="s">
         <v>376</v>
       </c>
-      <c r="D87" s="37" t="s">
+      <c r="D87" s="93" t="s">
         <v>82</v>
       </c>
-      <c r="E87" s="38" t="s">
+      <c r="E87" s="94" t="s">
         <v>165</v>
       </c>
-      <c r="F87" s="37" t="s">
+      <c r="F87" s="93" t="s">
         <v>208</v>
       </c>
-      <c r="G87" s="38" t="s">
+      <c r="G87" s="94" t="s">
         <v>264</v>
       </c>
-      <c r="H87" s="37" t="s">
+      <c r="H87" s="93" t="s">
         <v>299</v>
       </c>
-      <c r="I87" s="37"/>
-      <c r="J87" s="37"/>
-      <c r="K87" s="38" t="s">
-        <v>361</v>
-      </c>
-      <c r="L87" s="37">
+      <c r="I87" s="93" t="s">
+        <v>361</v>
+      </c>
+      <c r="J87" s="93" t="s">
+        <v>480</v>
+      </c>
+      <c r="K87" s="94" t="s">
+        <v>361</v>
+      </c>
+      <c r="L87" s="93">
         <v>1</v>
       </c>
-      <c r="M87" s="41">
+      <c r="M87" s="95">
         <f t="shared" si="64"/>
         <v>20</v>
       </c>
-      <c r="N87" s="41">
-        <f t="shared" si="71"/>
-        <v>22</v>
-      </c>
-      <c r="O87" s="41"/>
-      <c r="P87" s="41"/>
-      <c r="Q87" s="41">
+      <c r="N87" s="95">
+        <v>21</v>
+      </c>
+      <c r="O87" s="96" t="s">
+        <v>391</v>
+      </c>
+      <c r="P87" s="95">
+        <v>7.4638</v>
+      </c>
+      <c r="Q87" s="95">
         <f t="shared" ref="Q87" si="80">P87*N87</f>
-        <v>0</v>
-      </c>
-      <c r="R87" s="41"/>
-    </row>
-    <row r="88" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>156.7398</v>
+      </c>
+      <c r="R87" s="95" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="53">
         <f t="shared" si="0"/>
@@ -7062,8 +7227,12 @@
       <c r="H88" s="39" t="s">
         <v>300</v>
       </c>
-      <c r="I88" s="39"/>
-      <c r="J88" s="39"/>
+      <c r="I88" s="39" t="s">
+        <v>361</v>
+      </c>
+      <c r="J88" s="39" t="s">
+        <v>361</v>
+      </c>
       <c r="K88" s="58" t="s">
         <v>362</v>
       </c>
@@ -7075,114 +7244,135 @@
         <v>20</v>
       </c>
       <c r="N88" s="42">
-        <f t="shared" si="71"/>
-        <v>22</v>
-      </c>
-      <c r="O88" s="42"/>
-      <c r="P88" s="42"/>
+        <v>21</v>
+      </c>
+      <c r="O88" s="65" t="s">
+        <v>473</v>
+      </c>
+      <c r="P88" s="42">
+        <v>2.6459999999999999</v>
+      </c>
       <c r="Q88" s="42">
         <f t="shared" ref="Q88" si="81">N88*P88</f>
-        <v>0</v>
+        <v>55.565999999999995</v>
       </c>
       <c r="R88" s="42"/>
     </row>
-    <row r="89" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
-      <c r="B89" s="53">
+      <c r="B89" s="91">
         <f>ROW(B89) - ROW($B$9)</f>
         <v>80</v>
       </c>
-      <c r="C89" s="61" t="s">
+      <c r="C89" s="92" t="s">
         <v>376</v>
       </c>
-      <c r="D89" s="37" t="s">
+      <c r="D89" s="93" t="s">
         <v>84</v>
       </c>
-      <c r="E89" s="38" t="s">
+      <c r="E89" s="94" t="s">
         <v>167</v>
       </c>
-      <c r="F89" s="37" t="s">
+      <c r="F89" s="93" t="s">
         <v>358</v>
       </c>
-      <c r="G89" s="38" t="s">
+      <c r="G89" s="94" t="s">
         <v>210</v>
       </c>
-      <c r="H89" s="37" t="s">
+      <c r="H89" s="93" t="s">
         <v>297</v>
       </c>
-      <c r="I89" s="37"/>
-      <c r="J89" s="37"/>
-      <c r="K89" s="38" t="s">
-        <v>361</v>
-      </c>
-      <c r="L89" s="37">
+      <c r="I89" s="93" t="s">
+        <v>482</v>
+      </c>
+      <c r="J89" s="93" t="s">
+        <v>483</v>
+      </c>
+      <c r="K89" s="94" t="s">
+        <v>361</v>
+      </c>
+      <c r="L89" s="103">
+        <v>2</v>
+      </c>
+      <c r="M89" s="95">
+        <f t="shared" si="64"/>
+        <v>40</v>
+      </c>
+      <c r="N89" s="95">
+        <v>42</v>
+      </c>
+      <c r="O89" s="96" t="s">
+        <v>391</v>
+      </c>
+      <c r="P89" s="95">
+        <v>2.2974000000000001</v>
+      </c>
+      <c r="Q89" s="95">
+        <f t="shared" ref="Q89" si="82">P89*N89</f>
+        <v>96.490800000000007</v>
+      </c>
+      <c r="R89" s="97" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="1"/>
+      <c r="B90" s="91">
+        <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
+      <c r="C90" s="98" t="s">
+        <v>376</v>
+      </c>
+      <c r="D90" s="99" t="s">
+        <v>85</v>
+      </c>
+      <c r="E90" s="100" t="s">
+        <v>168</v>
+      </c>
+      <c r="F90" s="99" t="s">
+        <v>359</v>
+      </c>
+      <c r="G90" s="100" t="s">
+        <v>211</v>
+      </c>
+      <c r="H90" s="99" t="s">
+        <v>300</v>
+      </c>
+      <c r="I90" s="99" t="s">
+        <v>485</v>
+      </c>
+      <c r="J90" s="99" t="s">
+        <v>361</v>
+      </c>
+      <c r="K90" s="100" t="s">
+        <v>361</v>
+      </c>
+      <c r="L90" s="99">
         <v>1</v>
       </c>
-      <c r="M89" s="41">
+      <c r="M90" s="101">
         <f t="shared" si="64"/>
         <v>20</v>
       </c>
-      <c r="N89" s="41">
-        <f t="shared" si="71"/>
-        <v>22</v>
-      </c>
-      <c r="O89" s="41"/>
-      <c r="P89" s="41"/>
-      <c r="Q89" s="41">
-        <f t="shared" ref="Q89" si="82">P89*N89</f>
-        <v>0</v>
-      </c>
-      <c r="R89" s="41"/>
-    </row>
-    <row r="90" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="1"/>
-      <c r="B90" s="53">
-        <f t="shared" si="0"/>
-        <v>81</v>
-      </c>
-      <c r="C90" s="60" t="s">
-        <v>376</v>
-      </c>
-      <c r="D90" s="39" t="s">
-        <v>85</v>
-      </c>
-      <c r="E90" s="40" t="s">
-        <v>168</v>
-      </c>
-      <c r="F90" s="39" t="s">
-        <v>359</v>
-      </c>
-      <c r="G90" s="40" t="s">
-        <v>211</v>
-      </c>
-      <c r="H90" s="39" t="s">
-        <v>300</v>
-      </c>
-      <c r="I90" s="39"/>
-      <c r="J90" s="39"/>
-      <c r="K90" s="40" t="s">
-        <v>361</v>
-      </c>
-      <c r="L90" s="39">
-        <v>1</v>
-      </c>
-      <c r="M90" s="42">
-        <f t="shared" si="64"/>
-        <v>20</v>
-      </c>
-      <c r="N90" s="42">
-        <f t="shared" si="71"/>
-        <v>22</v>
-      </c>
-      <c r="O90" s="42"/>
-      <c r="P90" s="42"/>
-      <c r="Q90" s="42">
+      <c r="N90" s="101">
+        <v>21</v>
+      </c>
+      <c r="O90" s="102" t="s">
+        <v>486</v>
+      </c>
+      <c r="P90" s="101">
+        <v>3.532</v>
+      </c>
+      <c r="Q90" s="101">
         <f t="shared" ref="Q90" si="83">N90*P90</f>
-        <v>0</v>
-      </c>
-      <c r="R90" s="42"/>
-    </row>
-    <row r="91" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>74.171999999999997</v>
+      </c>
+      <c r="R90" s="97" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="53">
         <f>ROW(B91) - ROW($B$9)</f>
@@ -7206,8 +7396,12 @@
       <c r="H91" s="37" t="s">
         <v>297</v>
       </c>
-      <c r="I91" s="63"/>
-      <c r="J91" s="63"/>
+      <c r="I91" s="63" t="s">
+        <v>361</v>
+      </c>
+      <c r="J91" s="63" t="s">
+        <v>487</v>
+      </c>
       <c r="K91" s="38" t="s">
         <v>361</v>
       </c>
@@ -7219,18 +7413,21 @@
         <v>20</v>
       </c>
       <c r="N91" s="41">
-        <f t="shared" si="71"/>
-        <v>22</v>
-      </c>
-      <c r="O91" s="41"/>
-      <c r="P91" s="41"/>
+        <v>21</v>
+      </c>
+      <c r="O91" s="64" t="s">
+        <v>391</v>
+      </c>
+      <c r="P91" s="41">
+        <v>0.39140000000000003</v>
+      </c>
       <c r="Q91" s="41">
         <f t="shared" ref="Q91" si="84">P91*N91</f>
-        <v>0</v>
+        <v>8.2194000000000003</v>
       </c>
       <c r="R91" s="41"/>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="32"/>
       <c r="C92" s="51"/>
@@ -7247,12 +7444,20 @@
       <c r="L92" s="36"/>
       <c r="M92" s="36"/>
       <c r="N92" s="36"/>
-      <c r="O92" s="36"/>
-      <c r="P92" s="36"/>
-      <c r="Q92" s="36"/>
+      <c r="O92" s="106" t="s">
+        <v>488</v>
+      </c>
+      <c r="P92" s="104">
+        <f>SUM(P10:P91)</f>
+        <v>37.098149999999997</v>
+      </c>
+      <c r="Q92" s="104">
+        <f>SUM(Q10:Q91)</f>
+        <v>976.02435000000014</v>
+      </c>
       <c r="R92" s="44"/>
     </row>
-    <row r="93" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
       <c r="B93" s="24"/>
       <c r="C93" s="52"/>
@@ -7269,9 +7474,14 @@
       <c r="L93" s="9"/>
       <c r="M93" s="9"/>
       <c r="N93" s="9"/>
-      <c r="O93" s="9"/>
-      <c r="P93" s="9"/>
-      <c r="Q93" s="9"/>
+      <c r="O93" s="107" t="s">
+        <v>489</v>
+      </c>
+      <c r="P93" s="105"/>
+      <c r="Q93" s="105">
+        <f>Q92/20</f>
+        <v>48.801217500000007</v>
+      </c>
       <c r="R93" s="45"/>
     </row>
   </sheetData>
@@ -7348,9 +7558,20 @@
     <hyperlink ref="O76" r:id="rId66"/>
     <hyperlink ref="O77" r:id="rId67"/>
     <hyperlink ref="O78" r:id="rId68"/>
+    <hyperlink ref="O81" r:id="rId69"/>
+    <hyperlink ref="O82" r:id="rId70"/>
+    <hyperlink ref="O83" r:id="rId71"/>
+    <hyperlink ref="O84" r:id="rId72"/>
+    <hyperlink ref="O85" r:id="rId73"/>
+    <hyperlink ref="O86" r:id="rId74"/>
+    <hyperlink ref="O87" r:id="rId75"/>
+    <hyperlink ref="O88" r:id="rId76"/>
+    <hyperlink ref="O89" r:id="rId77"/>
+    <hyperlink ref="O90" r:id="rId78"/>
+    <hyperlink ref="O91" r:id="rId79"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId69"/>
-  <drawing r:id="rId70"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId80"/>
+  <drawing r:id="rId81"/>
 </worksheet>
 </file>
--- a/Deliverables/SM_Top Board/_BOM/eSpark BOM (20 Boards).xlsx
+++ b/Deliverables/SM_Top Board/_BOM/eSpark BOM (20 Boards).xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SM COM\Desktop\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Faizan\GitHub\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="7656"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="513">
   <si>
     <t>Component list</t>
   </si>
@@ -61,21 +61,6 @@
     <t>C2, C13, C51, C52, C53, C54, C61, CF1, CF2</t>
   </si>
   <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>C4, C46</t>
-  </si>
-  <si>
-    <t>C5, C6, C14, C23, C24, C29, C34, C35, C56</t>
-  </si>
-  <si>
-    <t>C7</t>
-  </si>
-  <si>
-    <t>C8, C10, C11, C12</t>
-  </si>
-  <si>
     <t>C9</t>
   </si>
   <si>
@@ -94,9 +79,6 @@
     <t>C30</t>
   </si>
   <si>
-    <t>C33, C38, C39</t>
-  </si>
-  <si>
     <t>C36</t>
   </si>
   <si>
@@ -109,9 +91,6 @@
     <t>C42</t>
   </si>
   <si>
-    <t>C43, C45, C47</t>
-  </si>
-  <si>
     <t>C44</t>
   </si>
   <si>
@@ -136,12 +115,6 @@
     <t>D2</t>
   </si>
   <si>
-    <t>D3</t>
-  </si>
-  <si>
-    <t>D4, D5, D6, D7, D8, D9, D10, D11</t>
-  </si>
-  <si>
     <t>F1</t>
   </si>
   <si>
@@ -250,9 +223,6 @@
     <t>R42, R43, R44, R45</t>
   </si>
   <si>
-    <t>RF1, RF2, RF3, RF4</t>
-  </si>
-  <si>
     <t>SB1, SB2, SB3, SB4, SB5, SB6, SB7, SB8, SB9, SB10, SB11</t>
   </si>
   <si>
@@ -313,9 +283,6 @@
     <t>CAP CER 1UF 25V X5R 0603</t>
   </si>
   <si>
-    <t>CAP CER 10UF 25V X5R 0603</t>
-  </si>
-  <si>
     <t>CAP CER 0.082UF 50V X7R 0603</t>
   </si>
   <si>
@@ -349,9 +316,6 @@
     <t>CAP CER 4.7UF 100V X7S 1210</t>
   </si>
   <si>
-    <t>Surface Mount Ceramic Multilayer Capacitor 68pF 5% C0G 50V 0603 Paper T/R</t>
-  </si>
-  <si>
     <t>CAP CER 1206 47 uF 25 V ±20 % Tol. X5R</t>
   </si>
   <si>
@@ -406,9 +370,6 @@
     <t>Inductor Power Shielded Wirewound 220uH 20% 1KHz Ferrite 1.3A 310mOhm DCR Blister T/R</t>
   </si>
   <si>
-    <t>1A 15uH ±20% 190mΩ SMD Power Inductors ROHS</t>
-  </si>
-  <si>
     <t>Standard LEDs - SMD SMD LED Red/Grn/Blue 625/1550/260 mcd</t>
   </si>
   <si>
@@ -484,9 +445,6 @@
     <t>Res SMD 0603 51.1K Ohm 0.1% 1/10W</t>
   </si>
   <si>
-    <t>RES SMD 1M OHM 1% 1/20W 0201</t>
-  </si>
-  <si>
     <t>Res SMD 0603 90.9K Ohm 1% 1/10W</t>
   </si>
   <si>
@@ -601,9 +559,6 @@
     <t>SLF12575T-221M1R3-PF</t>
   </si>
   <si>
-    <t>MPIT4018-150M-LF</t>
-  </si>
-  <si>
     <t>LTST-G683GEBW</t>
   </si>
   <si>
@@ -628,9 +583,6 @@
     <t>RES 2512</t>
   </si>
   <si>
-    <t>Res-0201</t>
-  </si>
-  <si>
     <t>RES-0603</t>
   </si>
   <si>
@@ -688,9 +640,6 @@
     <t>CC0603KRX5R8BB105</t>
   </si>
   <si>
-    <t>CL10A106MA8NRNC</t>
-  </si>
-  <si>
     <t>CC0603KRX7R9BB823</t>
   </si>
   <si>
@@ -718,9 +667,6 @@
     <t>HMK325C7475KN-TE</t>
   </si>
   <si>
-    <t>CC0603JRNPO9BN680</t>
-  </si>
-  <si>
     <t>GRM31CR61E476ME44L</t>
   </si>
   <si>
@@ -802,9 +748,6 @@
     <t>ERA-3AEB5112V</t>
   </si>
   <si>
-    <t>RC0201FR-071ML</t>
-  </si>
-  <si>
     <t>ERJ-3EKF9092V</t>
   </si>
   <si>
@@ -886,9 +829,6 @@
     <t>JST</t>
   </si>
   <si>
-    <t>microgate</t>
-  </si>
-  <si>
     <t>Vishay Lite-On</t>
   </si>
   <si>
@@ -982,9 +922,6 @@
     <t>4.7uF</t>
   </si>
   <si>
-    <t>68pF</t>
-  </si>
-  <si>
     <t>47uF</t>
   </si>
   <si>
@@ -1012,9 +949,6 @@
     <t>220uH</t>
   </si>
   <si>
-    <t>15uH</t>
-  </si>
-  <si>
     <t>Test Point</t>
   </si>
   <si>
@@ -1075,9 +1009,6 @@
     <t>51.1K</t>
   </si>
   <si>
-    <t>1M</t>
-  </si>
-  <si>
     <t>90.9K</t>
   </si>
   <si>
@@ -1222,9 +1153,6 @@
     <t>C14664</t>
   </si>
   <si>
-    <t>C96446</t>
-  </si>
-  <si>
     <t>C107100</t>
   </si>
   <si>
@@ -1270,9 +1198,6 @@
     <t>C697607</t>
   </si>
   <si>
-    <t>C62782</t>
-  </si>
-  <si>
     <t>C403725</t>
   </si>
   <si>
@@ -1343,9 +1268,6 @@
   </si>
   <si>
     <t>C93225</t>
-  </si>
-  <si>
-    <t>C281265</t>
   </si>
   <si>
     <t>Chipmall</t>
@@ -1447,8 +1369,219 @@
     <t>Two different part numbers for 100K merged into single part number. Changes highlighted</t>
   </si>
   <si>
+    <t>C105576</t>
+  </si>
+  <si>
+    <t>TME</t>
+  </si>
+  <si>
+    <t>C22765</t>
+  </si>
+  <si>
+    <t>C103893</t>
+  </si>
+  <si>
+    <t>C22548</t>
+  </si>
+  <si>
+    <t>C98220</t>
+  </si>
+  <si>
+    <t>Winsource</t>
+  </si>
+  <si>
+    <t>TLV75733PDBVR</t>
+  </si>
+  <si>
+    <t>C485517</t>
+  </si>
+  <si>
+    <t>Design change required. May cause change in some other misc components</t>
+  </si>
+  <si>
+    <t>BD9876AEFJ-E2</t>
+  </si>
+  <si>
+    <t>C79958</t>
+  </si>
+  <si>
+    <t>C100023</t>
+  </si>
+  <si>
+    <t>C516354</t>
+  </si>
+  <si>
+    <t>ISO7221ADR</t>
+  </si>
+  <si>
+    <t>C28037</t>
+  </si>
+  <si>
+    <t>Design change required. May cause change in some other misc components. Quantity also changed from 1/board to 2/board</t>
+  </si>
+  <si>
+    <t>ISO6761FDWR</t>
+  </si>
+  <si>
+    <t>Digikey</t>
+  </si>
+  <si>
+    <t>C7042</t>
+  </si>
+  <si>
+    <t>SUM</t>
+  </si>
+  <si>
+    <t>PER BOARD COST</t>
+  </si>
+  <si>
+    <t>R14, R15, R16, R17, R18, R19, R20, R26</t>
+  </si>
+  <si>
+    <t>R34</t>
+  </si>
+  <si>
+    <t>Quantity changed from 9/board to 1/board. The remaining 8 resistors have been converted to 22ohms after calculation</t>
+  </si>
+  <si>
+    <t>RES SMD 22OHM 1/10W 0603</t>
+  </si>
+  <si>
+    <t>0603WAF220JT5E</t>
+  </si>
+  <si>
+    <t>C23345</t>
+  </si>
+  <si>
+    <t>22R</t>
+  </si>
+  <si>
+    <t>Resistor value changed from 150R to 22R after calculation. No footprint, only schematic change needed</t>
+  </si>
+  <si>
+    <t>C33</t>
+  </si>
+  <si>
+    <t>Quantity changed from 3/board to 1/board due to change in two capacitors value to 1uF after component change</t>
+  </si>
+  <si>
+    <t>Quantity changed from 1/board to 3/board due to change in two capacitors value to 1uF after component change</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">R14, R15, R16, R17, R18, R19, R20, R26, </t>
+      <t xml:space="preserve">C7, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C38, C39</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">D4, D5, D6, D7, D8, D9, D10, D11, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DF1</t>
+    </r>
+  </si>
+  <si>
+    <t>Design change required. Another diode added for reverse current protection across U2. Needs to be added in design as well</t>
+  </si>
+  <si>
+    <t>Design change required. Change reflected in misc. components</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">C5, C6, C14, C23, C24, C29, C34, C35, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <strike/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C56</t>
+    </r>
+  </si>
+  <si>
+    <t>Quantity changed from 9/board to 8/board due to removal of 1 x 2.2uF capacitor from U3</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">C3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C46</t>
+    </r>
+  </si>
+  <si>
+    <t>Quantity changed from 2/board to 1/board due to removal of 1 x 0.47uF capacitor from U3</t>
+  </si>
+  <si>
+    <t>Quantity changed from 1/board to 2/board due to addition of 1 x 10nF capacitor from U3</t>
+  </si>
+  <si>
+    <t>Removed after changes in circuitry of U3</t>
+  </si>
+  <si>
+    <t>CAP CER 6.8nF 50V X7R 0603</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CC0603JRNPO9BN680 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0603B682K500NT</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Yageo</t>
     </r>
     <r>
       <rPr>
@@ -1458,83 +1591,357 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>R34</t>
+      <t xml:space="preserve"> </t>
     </r>
-  </si>
-  <si>
-    <t>Two different part numbers for 150R merged into single part number. Changes highlighted</t>
-  </si>
-  <si>
-    <t>C105576</t>
-  </si>
-  <si>
-    <t>TME</t>
-  </si>
-  <si>
-    <t>C295786</t>
-  </si>
-  <si>
-    <t>C22765</t>
-  </si>
-  <si>
-    <t>C103893</t>
-  </si>
-  <si>
-    <t>C22548</t>
-  </si>
-  <si>
-    <t>C98220</t>
-  </si>
-  <si>
-    <t>Winsource</t>
-  </si>
-  <si>
-    <t>TLV75733PDBVR</t>
-  </si>
-  <si>
-    <t>C485517</t>
-  </si>
-  <si>
-    <t>Design change required. May cause change in some other misc components</t>
-  </si>
-  <si>
-    <t>BD9876AEFJ-E2</t>
-  </si>
-  <si>
-    <t>C79958</t>
-  </si>
-  <si>
-    <t>C100023</t>
-  </si>
-  <si>
-    <t>C516354</t>
-  </si>
-  <si>
-    <t>Need confirmation from client regarding price</t>
-  </si>
-  <si>
-    <t>ISO7221ADR</t>
-  </si>
-  <si>
-    <t>C28037</t>
-  </si>
-  <si>
-    <t>Design change required. May cause change in some other misc components. Quantity also changed from 1/board to 2/board</t>
-  </si>
-  <si>
-    <t>ISO6761FDWR</t>
-  </si>
-  <si>
-    <t>Digikey</t>
-  </si>
-  <si>
-    <t>C7042</t>
-  </si>
-  <si>
-    <t>SUM</t>
-  </si>
-  <si>
-    <t>PER BOARD COST</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FH</t>
+    </r>
+  </si>
+  <si>
+    <t>C1631</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>68pF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 6.8nF</t>
+    </r>
+  </si>
+  <si>
+    <t>Value changed from 68pF to 6.8nF due to change in circuitry of U3</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">C43, </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C45, C47</t>
+    </r>
+  </si>
+  <si>
+    <t>Quantity changed from 3/board to 1/board due to removal of two capacitors after changes in circuitry of U3</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">C8, C10, C11, C12, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C41</t>
+    </r>
+  </si>
+  <si>
+    <t>GRM188R6YA106MA73D</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CAP CER 10UF </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>35V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> X5R 0603</t>
+    </r>
+  </si>
+  <si>
+    <t>C194427</t>
+  </si>
+  <si>
+    <t>Quantity changed from 4/board to 5/board due to addition of 1 x 10uF capacitor from U3</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">RF1, RF2, RF3, RF4, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RF5,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R38</t>
+    </r>
+  </si>
+  <si>
+    <t>Quantity changed from 4/board to 6/board due to addition of 2 x 10K resistor from U3</t>
+  </si>
+  <si>
+    <t>RES SMD 110K OHM 0.5% 1/10W 0603</t>
+  </si>
+  <si>
+    <r>
+      <t>Res-0201</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, Res0603</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RC0201FR-071ML</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 0603WAD1103T5E</t>
+    </r>
+  </si>
+  <si>
+    <t>C423090</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">1M </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>110K</t>
+    </r>
+  </si>
+  <si>
+    <t>Value changed from 1Mohm to 110Kohm due to change in circuitry of U3</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1A </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">15uH </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>33uH</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ±20% </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">190mΩ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>356mΩ SMD Power Inductors ROHS</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MPIT4018-150M-LF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> PNLS5020-330</t>
+    </r>
+  </si>
+  <si>
+    <t>DMBJ</t>
+  </si>
+  <si>
+    <t>C2849490</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">15uH </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>33uH</t>
+    </r>
+  </si>
+  <si>
+    <t>Value changed from 15uH to 33uH due to change in circuitry of U3</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">D3, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DF2</t>
+    </r>
+  </si>
+  <si>
+    <t>Design change required. Another diode added as per U3 circuit requirements</t>
+  </si>
+  <si>
+    <t>Design change required. May cause change in some other misc components.</t>
+  </si>
+  <si>
+    <t>Will be provided by Robotshop for prototyping</t>
   </si>
 </sst>
 </file>
@@ -1544,7 +1951,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1690,13 +2097,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <strike/>
       <sz val="9"/>
       <color rgb="FFC00000"/>
@@ -1712,8 +2112,58 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1759,6 +2209,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2015,7 +2471,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -2245,26 +2701,8 @@
     <xf numFmtId="0" fontId="17" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2312,8 +2750,122 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2656,27 +3208,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R93"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:R94"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.109375" style="25" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" style="25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="30.140625" customWidth="1"/>
-    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="22.140625" customWidth="1"/>
-    <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="16.7109375" customWidth="1"/>
-    <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="29.42578125" customWidth="1"/>
+    <col min="6" max="6" width="30.109375" customWidth="1"/>
+    <col min="7" max="7" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="22.109375" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="16.6640625" customWidth="1"/>
+    <col min="16" max="16" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -2687,16 +3239,16 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="88"/>
-      <c r="P1" s="88"/>
-      <c r="Q1" s="88"/>
-      <c r="R1" s="88"/>
-    </row>
-    <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+    </row>
+    <row r="2" spans="1:18" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
       <c r="C2" s="46"/>
@@ -2705,7 +3257,7 @@
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="54" t="s">
-        <v>382</v>
+        <v>359</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
@@ -2720,7 +3272,7 @@
       <c r="Q2" s="3"/>
       <c r="R2" s="43"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
       <c r="C3" s="47"/>
@@ -2729,7 +3281,7 @@
       </c>
       <c r="E3" s="12"/>
       <c r="F3" s="55" t="s">
-        <v>380</v>
+        <v>357</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="4"/>
@@ -2742,9 +3294,9 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="89"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R3" s="103"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
       <c r="C4" s="47"/>
@@ -2753,7 +3305,7 @@
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="56" t="s">
-        <v>381</v>
+        <v>358</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="6"/>
@@ -2766,9 +3318,9 @@
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="Q4" s="62"/>
-      <c r="R4" s="90"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R4" s="104"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
       <c r="C5" s="47"/>
@@ -2788,9 +3340,9 @@
       <c r="O5" s="62"/>
       <c r="P5" s="62"/>
       <c r="Q5" s="62"/>
-      <c r="R5" s="90"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R5" s="104"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
       <c r="C6" s="48"/>
@@ -2808,9 +3360,9 @@
       <c r="O6" s="62"/>
       <c r="P6" s="62"/>
       <c r="Q6" s="62"/>
-      <c r="R6" s="90"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R6" s="104"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
       <c r="C7" s="49"/>
@@ -2828,9 +3380,9 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="90"/>
-    </row>
-    <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R7" s="104"/>
+    </row>
+    <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="B8" s="26"/>
       <c r="C8" s="50"/>
@@ -2848,94 +3400,94 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="90"/>
-    </row>
-    <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R8" s="104"/>
+    </row>
+    <row r="9" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
       <c r="B9" s="29" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>373</v>
+        <v>350</v>
       </c>
       <c r="D9" s="29" t="s">
         <v>7</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="I9" s="29" t="s">
-        <v>383</v>
+        <v>360</v>
       </c>
       <c r="J9" s="29" t="s">
-        <v>384</v>
+        <v>361</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="L9" s="29" t="s">
-        <v>354</v>
+        <v>331</v>
       </c>
       <c r="M9" s="31" t="s">
-        <v>385</v>
+        <v>362</v>
       </c>
       <c r="N9" s="31" t="s">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="O9" s="31" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
       <c r="P9" s="31" t="s">
-        <v>388</v>
+        <v>365</v>
       </c>
       <c r="Q9" s="31" t="s">
-        <v>389</v>
+        <v>366</v>
       </c>
       <c r="R9" s="31" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1"/>
       <c r="B10" s="53">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="D10" s="37" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="38" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="G10" s="38" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
       <c r="K10" s="38" t="s">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="L10" s="37">
         <v>1</v>
@@ -2948,7 +3500,7 @@
         <v>22</v>
       </c>
       <c r="O10" s="64" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P10" s="41">
         <v>0.25869999999999999</v>
@@ -2959,38 +3511,38 @@
       </c>
       <c r="R10" s="41"/>
     </row>
-    <row r="11" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
       <c r="B11" s="53">
-        <f t="shared" ref="B11:B90" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B91" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="60" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="D11" s="39" t="s">
         <v>9</v>
       </c>
       <c r="E11" s="40" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="F11" s="39" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="G11" s="40" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="H11" s="39" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="I11" s="39" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J11" s="39" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="K11" s="40" t="s">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="L11" s="39">
         <v>9</v>
@@ -3003,7 +3555,7 @@
         <v>198</v>
       </c>
       <c r="O11" s="65" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P11" s="42">
         <v>1.4E-3</v>
@@ -3014,313 +3566,323 @@
       </c>
       <c r="R11" s="42"/>
     </row>
-    <row r="12" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
-      <c r="B12" s="53">
+      <c r="B12" s="85">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="61" t="s">
-        <v>364</v>
-      </c>
-      <c r="D12" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="F12" s="37" t="s">
-        <v>173</v>
-      </c>
-      <c r="G12" s="38" t="s">
-        <v>215</v>
-      </c>
-      <c r="H12" s="37" t="s">
-        <v>269</v>
-      </c>
-      <c r="I12" s="37" t="s">
-        <v>361</v>
-      </c>
-      <c r="J12" s="37" t="s">
-        <v>393</v>
-      </c>
-      <c r="K12" s="38" t="s">
-        <v>304</v>
-      </c>
-      <c r="L12" s="37">
-        <v>1</v>
-      </c>
-      <c r="M12" s="41">
-        <f t="shared" ref="M12:M72" si="1">L12*20</f>
-        <v>20</v>
-      </c>
-      <c r="N12" s="41">
+      <c r="C12" s="86" t="s">
+        <v>341</v>
+      </c>
+      <c r="D12" s="87" t="s">
+        <v>478</v>
+      </c>
+      <c r="E12" s="88" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" s="87" t="s">
+        <v>159</v>
+      </c>
+      <c r="G12" s="88" t="s">
+        <v>199</v>
+      </c>
+      <c r="H12" s="87" t="s">
+        <v>250</v>
+      </c>
+      <c r="I12" s="87" t="s">
+        <v>338</v>
+      </c>
+      <c r="J12" s="87" t="s">
+        <v>370</v>
+      </c>
+      <c r="K12" s="88" t="s">
+        <v>284</v>
+      </c>
+      <c r="L12" s="109">
+        <v>2</v>
+      </c>
+      <c r="M12" s="89">
+        <f t="shared" ref="M12:M73" si="1">L12*20</f>
+        <v>40</v>
+      </c>
+      <c r="N12" s="89">
         <v>100</v>
       </c>
-      <c r="O12" s="64" t="s">
-        <v>391</v>
-      </c>
-      <c r="P12" s="41">
+      <c r="O12" s="90" t="s">
+        <v>368</v>
+      </c>
+      <c r="P12" s="89">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q12" s="41">
+      <c r="Q12" s="89">
         <f t="shared" ref="Q12" si="2">P12*N12</f>
         <v>0.13</v>
       </c>
-      <c r="R12" s="41"/>
-    </row>
-    <row r="13" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R12" s="106" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
-      <c r="B13" s="53">
+      <c r="B13" s="85">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="60" t="s">
-        <v>364</v>
-      </c>
-      <c r="D13" s="39" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="F13" s="39" t="s">
-        <v>173</v>
-      </c>
-      <c r="G13" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="H13" s="39" t="s">
-        <v>270</v>
-      </c>
-      <c r="I13" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="J13" s="39" t="s">
-        <v>394</v>
-      </c>
-      <c r="K13" s="40" t="s">
-        <v>305</v>
-      </c>
-      <c r="L13" s="39">
-        <v>2</v>
-      </c>
-      <c r="M13" s="42">
+      <c r="C13" s="92" t="s">
+        <v>341</v>
+      </c>
+      <c r="D13" s="93" t="s">
+        <v>477</v>
+      </c>
+      <c r="E13" s="94" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" s="93" t="s">
+        <v>159</v>
+      </c>
+      <c r="G13" s="94" t="s">
+        <v>200</v>
+      </c>
+      <c r="H13" s="93" t="s">
+        <v>251</v>
+      </c>
+      <c r="I13" s="93" t="s">
+        <v>338</v>
+      </c>
+      <c r="J13" s="93" t="s">
+        <v>371</v>
+      </c>
+      <c r="K13" s="94" t="s">
+        <v>285</v>
+      </c>
+      <c r="L13" s="108">
+        <v>1</v>
+      </c>
+      <c r="M13" s="95">
         <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N13" s="107">
         <v>40</v>
       </c>
-      <c r="N13" s="42">
-        <v>60</v>
-      </c>
-      <c r="O13" s="65" t="s">
-        <v>391</v>
-      </c>
-      <c r="P13" s="42">
+      <c r="O13" s="96" t="s">
+        <v>368</v>
+      </c>
+      <c r="P13" s="95">
         <v>3.5900000000000001E-2</v>
       </c>
-      <c r="Q13" s="42">
+      <c r="Q13" s="95">
         <f t="shared" ref="Q13" si="3">N13*P13</f>
-        <v>2.1539999999999999</v>
-      </c>
-      <c r="R13" s="42"/>
-    </row>
-    <row r="14" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1.4359999999999999</v>
+      </c>
+      <c r="R13" s="106" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1"/>
-      <c r="B14" s="53">
+      <c r="B14" s="85">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="61" t="s">
-        <v>364</v>
-      </c>
-      <c r="D14" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="F14" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="G14" s="38" t="s">
-        <v>217</v>
-      </c>
-      <c r="H14" s="37" t="s">
-        <v>271</v>
-      </c>
-      <c r="I14" s="37" t="s">
-        <v>361</v>
-      </c>
-      <c r="J14" s="37" t="s">
-        <v>395</v>
-      </c>
-      <c r="K14" s="38" t="s">
-        <v>306</v>
-      </c>
-      <c r="L14" s="37">
-        <v>9</v>
-      </c>
-      <c r="M14" s="41">
+      <c r="C14" s="86" t="s">
+        <v>341</v>
+      </c>
+      <c r="D14" s="87" t="s">
+        <v>475</v>
+      </c>
+      <c r="E14" s="88" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" s="87" t="s">
+        <v>158</v>
+      </c>
+      <c r="G14" s="88" t="s">
+        <v>201</v>
+      </c>
+      <c r="H14" s="87" t="s">
+        <v>252</v>
+      </c>
+      <c r="I14" s="87" t="s">
+        <v>338</v>
+      </c>
+      <c r="J14" s="87" t="s">
+        <v>372</v>
+      </c>
+      <c r="K14" s="88" t="s">
+        <v>286</v>
+      </c>
+      <c r="L14" s="87">
+        <v>8</v>
+      </c>
+      <c r="M14" s="89">
         <f t="shared" si="1"/>
-        <v>180</v>
-      </c>
-      <c r="N14" s="41">
+        <v>160</v>
+      </c>
+      <c r="N14" s="89">
         <v>200</v>
       </c>
-      <c r="O14" s="64" t="s">
-        <v>391</v>
-      </c>
-      <c r="P14" s="41">
+      <c r="O14" s="90" t="s">
+        <v>368</v>
+      </c>
+      <c r="P14" s="89">
         <v>4.0899999999999999E-2</v>
       </c>
-      <c r="Q14" s="41">
-        <f t="shared" ref="Q14" si="4">P14*N14</f>
+      <c r="Q14" s="89">
+        <f>P14*N14</f>
         <v>8.18</v>
       </c>
-      <c r="R14" s="41"/>
-    </row>
-    <row r="15" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R14" s="106" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
-      <c r="B15" s="53">
+      <c r="B15" s="85">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="60" t="s">
-        <v>364</v>
-      </c>
-      <c r="D15" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="40" t="s">
-        <v>93</v>
-      </c>
-      <c r="F15" s="39" t="s">
-        <v>172</v>
-      </c>
-      <c r="G15" s="40" t="s">
-        <v>218</v>
-      </c>
-      <c r="H15" s="39" t="s">
-        <v>269</v>
-      </c>
-      <c r="I15" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="J15" s="39" t="s">
-        <v>396</v>
-      </c>
-      <c r="K15" s="40" t="s">
-        <v>307</v>
-      </c>
-      <c r="L15" s="39">
-        <v>1</v>
-      </c>
-      <c r="M15" s="42">
+      <c r="C15" s="92" t="s">
+        <v>341</v>
+      </c>
+      <c r="D15" s="93" t="s">
+        <v>471</v>
+      </c>
+      <c r="E15" s="94" t="s">
+        <v>83</v>
+      </c>
+      <c r="F15" s="93" t="s">
+        <v>158</v>
+      </c>
+      <c r="G15" s="94" t="s">
+        <v>202</v>
+      </c>
+      <c r="H15" s="93" t="s">
+        <v>250</v>
+      </c>
+      <c r="I15" s="93" t="s">
+        <v>338</v>
+      </c>
+      <c r="J15" s="93" t="s">
+        <v>373</v>
+      </c>
+      <c r="K15" s="94" t="s">
+        <v>287</v>
+      </c>
+      <c r="L15" s="108">
+        <v>3</v>
+      </c>
+      <c r="M15" s="95">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N15" s="42">
-        <v>50</v>
-      </c>
-      <c r="O15" s="65" t="s">
-        <v>391</v>
-      </c>
-      <c r="P15" s="42">
+        <v>60</v>
+      </c>
+      <c r="N15" s="107">
+        <v>100</v>
+      </c>
+      <c r="O15" s="96" t="s">
+        <v>368</v>
+      </c>
+      <c r="P15" s="95">
         <v>5.8999999999999999E-3</v>
       </c>
-      <c r="Q15" s="42">
-        <f t="shared" ref="Q15" si="5">N15*P15</f>
-        <v>0.29499999999999998</v>
-      </c>
-      <c r="R15" s="42"/>
-    </row>
-    <row r="16" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q15" s="95">
+        <f t="shared" ref="Q15" si="4">N15*P15</f>
+        <v>0.59</v>
+      </c>
+      <c r="R15" s="106" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
-      <c r="B16" s="53">
+      <c r="B16" s="85">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="61" t="s">
-        <v>364</v>
-      </c>
-      <c r="D16" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="F16" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="G16" s="38" t="s">
-        <v>219</v>
-      </c>
-      <c r="H16" s="37" t="s">
-        <v>268</v>
-      </c>
-      <c r="I16" s="37" t="s">
-        <v>361</v>
-      </c>
-      <c r="J16" s="37" t="s">
-        <v>397</v>
-      </c>
-      <c r="K16" s="38" t="s">
-        <v>308</v>
-      </c>
-      <c r="L16" s="37">
-        <v>4</v>
-      </c>
-      <c r="M16" s="41">
+      <c r="C16" s="86" t="s">
+        <v>341</v>
+      </c>
+      <c r="D16" s="87" t="s">
+        <v>490</v>
+      </c>
+      <c r="E16" s="88" t="s">
+        <v>492</v>
+      </c>
+      <c r="F16" s="87" t="s">
+        <v>158</v>
+      </c>
+      <c r="G16" s="132" t="s">
+        <v>491</v>
+      </c>
+      <c r="H16" s="97" t="s">
+        <v>252</v>
+      </c>
+      <c r="I16" s="87" t="s">
+        <v>338</v>
+      </c>
+      <c r="J16" s="87" t="s">
+        <v>493</v>
+      </c>
+      <c r="K16" s="88" t="s">
+        <v>288</v>
+      </c>
+      <c r="L16" s="87">
+        <v>5</v>
+      </c>
+      <c r="M16" s="89">
         <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-      <c r="N16" s="41">
         <v>100</v>
       </c>
-      <c r="O16" s="64" t="s">
-        <v>391</v>
-      </c>
-      <c r="P16" s="41">
-        <v>1.44E-2</v>
-      </c>
-      <c r="Q16" s="41">
-        <f t="shared" ref="Q16" si="6">P16*N16</f>
-        <v>1.44</v>
-      </c>
-      <c r="R16" s="41"/>
-    </row>
-    <row r="17" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N16" s="89">
+        <v>110</v>
+      </c>
+      <c r="O16" s="90" t="s">
+        <v>368</v>
+      </c>
+      <c r="P16" s="89">
+        <v>3.32E-2</v>
+      </c>
+      <c r="Q16" s="89">
+        <f t="shared" ref="Q16" si="5">P16*N16</f>
+        <v>3.6520000000000001</v>
+      </c>
+      <c r="R16" s="106" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
       <c r="B17" s="53">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C17" s="60" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E17" s="40" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="G17" s="40" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="H17" s="39" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="I17" s="39" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J17" s="39" t="s">
-        <v>398</v>
+        <v>374</v>
       </c>
       <c r="K17" s="40" t="s">
-        <v>309</v>
+        <v>289</v>
       </c>
       <c r="L17" s="39">
         <v>1</v>
@@ -3333,49 +3895,49 @@
         <v>50</v>
       </c>
       <c r="O17" s="65" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P17" s="42">
         <v>9.9000000000000008E-3</v>
       </c>
       <c r="Q17" s="42">
-        <f t="shared" ref="Q17" si="7">N17*P17</f>
+        <f t="shared" ref="Q17" si="6">N17*P17</f>
         <v>0.49500000000000005</v>
       </c>
       <c r="R17" s="42"/>
     </row>
-    <row r="18" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" s="53">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
       <c r="C18" s="61" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E18" s="38" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="G18" s="38" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="I18" s="37" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J18" s="37" t="s">
-        <v>399</v>
+        <v>375</v>
       </c>
       <c r="K18" s="38" t="s">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="L18" s="37">
         <v>3</v>
@@ -3388,49 +3950,49 @@
         <v>100</v>
       </c>
       <c r="O18" s="64" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P18" s="41">
         <v>8.0999999999999996E-3</v>
       </c>
       <c r="Q18" s="41">
-        <f t="shared" ref="Q18" si="8">P18*N18</f>
+        <f t="shared" ref="Q18" si="7">P18*N18</f>
         <v>0.80999999999999994</v>
       </c>
       <c r="R18" s="41"/>
     </row>
-    <row r="19" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="53">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="C19" s="60" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>406</v>
+        <v>382</v>
       </c>
       <c r="E19" s="40" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="F19" s="39" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="G19" s="40" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="H19" s="39" t="s">
-        <v>272</v>
+        <v>253</v>
       </c>
       <c r="I19" s="39" t="s">
-        <v>401</v>
+        <v>377</v>
       </c>
       <c r="J19" s="39" t="s">
-        <v>400</v>
+        <v>376</v>
       </c>
       <c r="K19" s="40" t="s">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="L19" s="39">
         <v>8</v>
@@ -3443,49 +4005,49 @@
         <v>180</v>
       </c>
       <c r="O19" s="65" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P19" s="42">
         <v>3.09E-2</v>
       </c>
       <c r="Q19" s="42">
-        <f t="shared" ref="Q19" si="9">N19*P19</f>
+        <f t="shared" ref="Q19" si="8">N19*P19</f>
         <v>5.5620000000000003</v>
       </c>
       <c r="R19" s="42"/>
     </row>
-    <row r="20" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1"/>
       <c r="B20" s="53">
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
       <c r="C20" s="61" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="D20" s="37" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E20" s="38" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="G20" s="38" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="I20" s="37" t="s">
-        <v>402</v>
+        <v>378</v>
       </c>
       <c r="J20" s="37" t="s">
-        <v>403</v>
+        <v>379</v>
       </c>
       <c r="K20" s="38" t="s">
-        <v>311</v>
+        <v>291</v>
       </c>
       <c r="L20" s="37">
         <v>1</v>
@@ -3498,49 +4060,49 @@
         <v>50</v>
       </c>
       <c r="O20" s="64" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P20" s="41">
         <v>5.3E-3</v>
       </c>
       <c r="Q20" s="41">
-        <f t="shared" ref="Q20" si="10">P20*N20</f>
+        <f t="shared" ref="Q20" si="9">P20*N20</f>
         <v>0.26500000000000001</v>
       </c>
       <c r="R20" s="41"/>
     </row>
-    <row r="21" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
       <c r="B21" s="53">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="C21" s="60" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E21" s="40" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="F21" s="39" t="s">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="G21" s="39" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="H21" s="39" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
       <c r="I21" s="39" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J21" s="39" t="s">
-        <v>404</v>
+        <v>380</v>
       </c>
       <c r="K21" s="40" t="s">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="L21" s="39">
         <v>1</v>
@@ -3553,49 +4115,49 @@
         <v>22</v>
       </c>
       <c r="O21" s="65" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P21" s="42">
         <v>0.22189999999999999</v>
       </c>
       <c r="Q21" s="42">
-        <f t="shared" ref="Q21" si="11">N21*P21</f>
+        <f t="shared" ref="Q21" si="10">N21*P21</f>
         <v>4.8818000000000001</v>
       </c>
       <c r="R21" s="42"/>
     </row>
-    <row r="22" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1"/>
       <c r="B22" s="53">
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
       <c r="C22" s="61" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E22" s="38" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J22" s="37" t="s">
-        <v>405</v>
+        <v>381</v>
       </c>
       <c r="K22" s="38" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="L22" s="37">
         <v>2</v>
@@ -3608,49 +4170,49 @@
         <v>50</v>
       </c>
       <c r="O22" s="64" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P22" s="41">
         <v>7.7000000000000002E-3</v>
       </c>
       <c r="Q22" s="41">
-        <f t="shared" ref="Q22" si="12">P22*N22</f>
+        <f t="shared" ref="Q22" si="11">P22*N22</f>
         <v>0.38500000000000001</v>
       </c>
       <c r="R22" s="41"/>
     </row>
-    <row r="23" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
       <c r="B23" s="53">
         <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
       </c>
       <c r="C23" s="61" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="D23" s="37" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E23" s="38" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="F23" s="37" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="G23" s="38" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="H23" s="37" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="I23" s="37" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J23" s="37" t="s">
-        <v>407</v>
+        <v>383</v>
       </c>
       <c r="K23" s="38" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L23" s="37">
         <v>1</v>
@@ -3663,104 +4225,106 @@
         <v>40</v>
       </c>
       <c r="O23" s="64" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P23" s="41">
         <v>3.49E-2</v>
       </c>
       <c r="Q23" s="41">
-        <f t="shared" ref="Q23" si="13">P23*N23</f>
+        <f t="shared" ref="Q23" si="12">P23*N23</f>
         <v>1.3959999999999999</v>
       </c>
       <c r="R23" s="41"/>
     </row>
-    <row r="24" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
-      <c r="B24" s="53">
+      <c r="B24" s="85">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="60" t="s">
-        <v>364</v>
-      </c>
-      <c r="D24" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" s="40" t="s">
-        <v>102</v>
-      </c>
-      <c r="F24" s="39" t="s">
-        <v>172</v>
-      </c>
-      <c r="G24" s="40" t="s">
-        <v>226</v>
-      </c>
-      <c r="H24" s="39" t="s">
-        <v>268</v>
-      </c>
-      <c r="I24" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="J24" s="39" t="s">
-        <v>408</v>
-      </c>
-      <c r="K24" s="40" t="s">
-        <v>313</v>
-      </c>
-      <c r="L24" s="39">
-        <v>3</v>
-      </c>
-      <c r="M24" s="42">
+      <c r="C24" s="92" t="s">
+        <v>341</v>
+      </c>
+      <c r="D24" s="93" t="s">
+        <v>468</v>
+      </c>
+      <c r="E24" s="94" t="s">
+        <v>91</v>
+      </c>
+      <c r="F24" s="93" t="s">
+        <v>158</v>
+      </c>
+      <c r="G24" s="94" t="s">
+        <v>209</v>
+      </c>
+      <c r="H24" s="93" t="s">
+        <v>249</v>
+      </c>
+      <c r="I24" s="93" t="s">
+        <v>338</v>
+      </c>
+      <c r="J24" s="93" t="s">
+        <v>384</v>
+      </c>
+      <c r="K24" s="94" t="s">
+        <v>293</v>
+      </c>
+      <c r="L24" s="108">
+        <v>1</v>
+      </c>
+      <c r="M24" s="95">
         <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
-      <c r="N24" s="42">
-        <v>80</v>
-      </c>
-      <c r="O24" s="65" t="s">
-        <v>391</v>
-      </c>
-      <c r="P24" s="42">
+        <v>20</v>
+      </c>
+      <c r="N24" s="107">
+        <v>40</v>
+      </c>
+      <c r="O24" s="96" t="s">
+        <v>368</v>
+      </c>
+      <c r="P24" s="95">
         <v>1.9199999999999998E-2</v>
       </c>
-      <c r="Q24" s="42">
-        <f t="shared" ref="Q24" si="14">N24*P24</f>
-        <v>1.5359999999999998</v>
-      </c>
-      <c r="R24" s="42"/>
-    </row>
-    <row r="25" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q24" s="95">
+        <f t="shared" ref="Q24" si="13">N24*P24</f>
+        <v>0.7679999999999999</v>
+      </c>
+      <c r="R24" s="106" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
       <c r="B25" s="53">
         <f>ROW(B25) - ROW($B$9)</f>
         <v>16</v>
       </c>
       <c r="C25" s="61" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="D25" s="37" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E25" s="38" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="F25" s="37" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="G25" s="66">
         <v>885012205080</v>
       </c>
       <c r="H25" s="37" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="I25" s="37" t="s">
-        <v>409</v>
+        <v>385</v>
       </c>
       <c r="J25" s="37" t="s">
-        <v>410</v>
+        <v>386</v>
       </c>
       <c r="K25" s="38" t="s">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="L25" s="37">
         <v>1</v>
@@ -3773,49 +4337,49 @@
         <v>50</v>
       </c>
       <c r="O25" s="64" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P25" s="41">
         <v>5.1999999999999998E-3</v>
       </c>
       <c r="Q25" s="41">
-        <f t="shared" ref="Q25" si="15">P25*N25</f>
+        <f t="shared" ref="Q25" si="14">P25*N25</f>
         <v>0.26</v>
       </c>
       <c r="R25" s="41"/>
     </row>
-    <row r="26" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
       <c r="B26" s="53">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="C26" s="60" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="D26" s="39" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E26" s="40" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="F26" s="39" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="G26" s="40" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="H26" s="39" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="I26" s="39" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J26" s="39" t="s">
-        <v>411</v>
+        <v>387</v>
       </c>
       <c r="K26" s="40" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="L26" s="39">
         <v>1</v>
@@ -3828,269 +4392,277 @@
         <v>100</v>
       </c>
       <c r="O26" s="65" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P26" s="42">
         <v>3.2000000000000002E-3</v>
       </c>
       <c r="Q26" s="42">
-        <f t="shared" ref="Q26" si="16">N26*P26</f>
+        <f t="shared" ref="Q26" si="15">N26*P26</f>
         <v>0.32</v>
       </c>
       <c r="R26" s="42"/>
     </row>
-    <row r="27" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
-      <c r="B27" s="53">
+      <c r="B27" s="113">
         <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
-      <c r="C27" s="61" t="s">
-        <v>364</v>
-      </c>
-      <c r="D27" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="38" t="s">
-        <v>105</v>
-      </c>
-      <c r="F27" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="G27" s="38" t="s">
-        <v>228</v>
-      </c>
-      <c r="H27" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I27" s="37" t="s">
-        <v>361</v>
-      </c>
-      <c r="J27" s="37" t="s">
-        <v>412</v>
-      </c>
-      <c r="K27" s="38" t="s">
-        <v>316</v>
-      </c>
-      <c r="L27" s="37">
+      <c r="C27" s="133" t="s">
+        <v>341</v>
+      </c>
+      <c r="D27" s="134" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="135" t="s">
+        <v>94</v>
+      </c>
+      <c r="F27" s="134" t="s">
+        <v>162</v>
+      </c>
+      <c r="G27" s="135" t="s">
+        <v>211</v>
+      </c>
+      <c r="H27" s="134" t="s">
+        <v>251</v>
+      </c>
+      <c r="I27" s="134" t="s">
+        <v>338</v>
+      </c>
+      <c r="J27" s="134" t="s">
+        <v>388</v>
+      </c>
+      <c r="K27" s="135" t="s">
+        <v>296</v>
+      </c>
+      <c r="L27" s="134">
         <v>1</v>
       </c>
-      <c r="M27" s="41">
+      <c r="M27" s="136">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N27" s="41">
-        <v>22</v>
-      </c>
-      <c r="O27" s="64" t="s">
-        <v>391</v>
-      </c>
-      <c r="P27" s="41">
+      <c r="N27" s="136">
+        <v>0</v>
+      </c>
+      <c r="O27" s="137" t="s">
+        <v>368</v>
+      </c>
+      <c r="P27" s="136">
         <v>0.1653</v>
       </c>
-      <c r="Q27" s="41">
-        <f t="shared" ref="Q27" si="17">P27*N27</f>
-        <v>3.6366000000000001</v>
-      </c>
-      <c r="R27" s="41"/>
-    </row>
-    <row r="28" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q27" s="136">
+        <f t="shared" ref="Q27" si="16">P27*N27</f>
+        <v>0</v>
+      </c>
+      <c r="R27" s="136" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
-      <c r="B28" s="53">
+      <c r="B28" s="85">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="60" t="s">
-        <v>364</v>
-      </c>
-      <c r="D28" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="F28" s="39" t="s">
-        <v>172</v>
-      </c>
-      <c r="G28" s="40" t="s">
-        <v>229</v>
-      </c>
-      <c r="H28" s="39" t="s">
-        <v>269</v>
-      </c>
-      <c r="I28" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="J28" s="39" t="s">
-        <v>413</v>
-      </c>
-      <c r="K28" s="40" t="s">
-        <v>317</v>
-      </c>
-      <c r="L28" s="39">
+      <c r="C28" s="92" t="s">
+        <v>341</v>
+      </c>
+      <c r="D28" s="93" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" s="112" t="s">
+        <v>482</v>
+      </c>
+      <c r="F28" s="93" t="s">
+        <v>158</v>
+      </c>
+      <c r="G28" s="116" t="s">
+        <v>483</v>
+      </c>
+      <c r="H28" s="105" t="s">
+        <v>484</v>
+      </c>
+      <c r="I28" s="93" t="s">
+        <v>338</v>
+      </c>
+      <c r="J28" s="93" t="s">
+        <v>485</v>
+      </c>
+      <c r="K28" s="94" t="s">
+        <v>486</v>
+      </c>
+      <c r="L28" s="93">
         <v>1</v>
       </c>
-      <c r="M28" s="42">
+      <c r="M28" s="95">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N28" s="42">
+      <c r="N28" s="95">
         <v>100</v>
       </c>
-      <c r="O28" s="65" t="s">
-        <v>391</v>
-      </c>
-      <c r="P28" s="42">
+      <c r="O28" s="96" t="s">
+        <v>368</v>
+      </c>
+      <c r="P28" s="95">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="Q28" s="42">
-        <f t="shared" ref="Q28" si="18">N28*P28</f>
+      <c r="Q28" s="95">
+        <f t="shared" ref="Q28" si="17">N28*P28</f>
         <v>0.33999999999999997</v>
       </c>
-      <c r="R28" s="42"/>
-    </row>
-    <row r="29" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R28" s="106" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
-      <c r="B29" s="53">
+      <c r="B29" s="85">
         <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
-      <c r="C29" s="61" t="s">
-        <v>364</v>
-      </c>
-      <c r="D29" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="E29" s="38" t="s">
-        <v>107</v>
-      </c>
-      <c r="F29" s="37" t="s">
-        <v>177</v>
-      </c>
-      <c r="G29" s="38" t="s">
-        <v>230</v>
-      </c>
-      <c r="H29" s="37" t="s">
-        <v>271</v>
-      </c>
-      <c r="I29" s="37" t="s">
-        <v>361</v>
-      </c>
-      <c r="J29" s="37" t="s">
-        <v>414</v>
-      </c>
-      <c r="K29" s="38" t="s">
-        <v>318</v>
-      </c>
-      <c r="L29" s="37">
-        <v>3</v>
-      </c>
-      <c r="M29" s="41">
+      <c r="C29" s="86" t="s">
+        <v>341</v>
+      </c>
+      <c r="D29" s="87" t="s">
+        <v>488</v>
+      </c>
+      <c r="E29" s="88" t="s">
+        <v>95</v>
+      </c>
+      <c r="F29" s="87" t="s">
+        <v>163</v>
+      </c>
+      <c r="G29" s="88" t="s">
+        <v>212</v>
+      </c>
+      <c r="H29" s="87" t="s">
+        <v>252</v>
+      </c>
+      <c r="I29" s="87" t="s">
+        <v>338</v>
+      </c>
+      <c r="J29" s="87" t="s">
+        <v>389</v>
+      </c>
+      <c r="K29" s="88" t="s">
+        <v>297</v>
+      </c>
+      <c r="L29" s="109">
+        <v>1</v>
+      </c>
+      <c r="M29" s="89">
         <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
-      <c r="N29" s="41">
-        <v>70</v>
-      </c>
-      <c r="O29" s="64" t="s">
-        <v>391</v>
-      </c>
-      <c r="P29" s="41">
+        <v>20</v>
+      </c>
+      <c r="N29" s="119">
+        <v>30</v>
+      </c>
+      <c r="O29" s="90" t="s">
+        <v>368</v>
+      </c>
+      <c r="P29" s="89">
         <v>0.2525</v>
       </c>
-      <c r="Q29" s="41">
-        <f t="shared" ref="Q29" si="19">P29*N29</f>
-        <v>17.675000000000001</v>
-      </c>
-      <c r="R29" s="41"/>
-    </row>
-    <row r="30" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q29" s="89">
+        <f t="shared" ref="Q29" si="18">P29*N29</f>
+        <v>7.5750000000000002</v>
+      </c>
+      <c r="R29" s="91" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
-      <c r="B30" s="53">
+      <c r="B30" s="113">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="60" t="s">
-        <v>364</v>
-      </c>
-      <c r="D30" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="E30" s="40" t="s">
-        <v>108</v>
-      </c>
-      <c r="F30" s="39" t="s">
-        <v>172</v>
-      </c>
-      <c r="G30" s="40" t="s">
-        <v>231</v>
-      </c>
-      <c r="H30" s="39" t="s">
-        <v>269</v>
-      </c>
-      <c r="I30" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="J30" s="39" t="s">
-        <v>415</v>
-      </c>
-      <c r="K30" s="40" t="s">
-        <v>319</v>
-      </c>
-      <c r="L30" s="39">
+      <c r="C30" s="114" t="s">
+        <v>341</v>
+      </c>
+      <c r="D30" s="115" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="116" t="s">
+        <v>96</v>
+      </c>
+      <c r="F30" s="115" t="s">
+        <v>158</v>
+      </c>
+      <c r="G30" s="116" t="s">
+        <v>213</v>
+      </c>
+      <c r="H30" s="115" t="s">
+        <v>250</v>
+      </c>
+      <c r="I30" s="115" t="s">
+        <v>338</v>
+      </c>
+      <c r="J30" s="115" t="s">
+        <v>390</v>
+      </c>
+      <c r="K30" s="116" t="s">
+        <v>298</v>
+      </c>
+      <c r="L30" s="115">
         <v>1</v>
       </c>
-      <c r="M30" s="42">
+      <c r="M30" s="117">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N30" s="42">
-        <v>50</v>
-      </c>
-      <c r="O30" s="65" t="s">
-        <v>391</v>
-      </c>
-      <c r="P30" s="42">
+      <c r="N30" s="117">
+        <v>0</v>
+      </c>
+      <c r="O30" s="118" t="s">
+        <v>368</v>
+      </c>
+      <c r="P30" s="117">
         <v>4.1999999999999997E-3</v>
       </c>
-      <c r="Q30" s="42">
-        <f t="shared" ref="Q30" si="20">N30*P30</f>
-        <v>0.21</v>
-      </c>
-      <c r="R30" s="42"/>
-    </row>
-    <row r="31" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q30" s="117">
+        <f t="shared" ref="Q30" si="19">N30*P30</f>
+        <v>0</v>
+      </c>
+      <c r="R30" s="106" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1"/>
       <c r="B31" s="53">
         <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
       <c r="C31" s="61" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="D31" s="37" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E31" s="38" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="F31" s="37" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G31" s="38" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="H31" s="37" t="s">
-        <v>272</v>
+        <v>253</v>
       </c>
       <c r="I31" s="37" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J31" s="37" t="s">
-        <v>416</v>
+        <v>391</v>
       </c>
       <c r="K31" s="38" t="s">
-        <v>320</v>
+        <v>299</v>
       </c>
       <c r="L31" s="37">
         <v>1</v>
@@ -4103,49 +4675,49 @@
         <v>22</v>
       </c>
       <c r="O31" s="64" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P31" s="41">
         <v>0.89629999999999999</v>
       </c>
       <c r="Q31" s="41">
-        <f t="shared" ref="Q31" si="21">P31*N31</f>
+        <f t="shared" ref="Q31" si="20">P31*N31</f>
         <v>19.718599999999999</v>
       </c>
       <c r="R31" s="41"/>
     </row>
-    <row r="32" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1"/>
       <c r="B32" s="53">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="C32" s="60" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="D32" s="39" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E32" s="40" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="F32" s="39" t="s">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="G32" s="39" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="H32" s="39" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="I32" s="39" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J32" s="39" t="s">
-        <v>417</v>
+        <v>392</v>
       </c>
       <c r="K32" s="40" t="s">
-        <v>321</v>
+        <v>300</v>
       </c>
       <c r="L32" s="39">
         <v>1</v>
@@ -4158,49 +4730,49 @@
         <v>21</v>
       </c>
       <c r="O32" s="65" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P32" s="42">
         <v>0.47249999999999998</v>
       </c>
       <c r="Q32" s="42">
-        <f t="shared" ref="Q32" si="22">N32*P32</f>
+        <f t="shared" ref="Q32" si="21">N32*P32</f>
         <v>9.9224999999999994</v>
       </c>
       <c r="R32" s="42"/>
     </row>
-    <row r="33" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1"/>
       <c r="B33" s="53">
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
       <c r="C33" s="61" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="D33" s="37" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E33" s="38" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="G33" s="38" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="H33" s="37" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J33" s="37" t="s">
-        <v>418</v>
+        <v>393</v>
       </c>
       <c r="K33" s="38" t="s">
-        <v>322</v>
+        <v>301</v>
       </c>
       <c r="L33" s="37">
         <v>1</v>
@@ -4213,104 +4785,106 @@
         <v>100</v>
       </c>
       <c r="O33" s="64" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P33" s="41">
         <v>3.0999999999999999E-3</v>
       </c>
       <c r="Q33" s="41">
-        <f t="shared" ref="Q33" si="23">P33*N33</f>
+        <f t="shared" ref="Q33" si="22">P33*N33</f>
         <v>0.31</v>
       </c>
       <c r="R33" s="41"/>
     </row>
-    <row r="34" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
-      <c r="B34" s="53">
+      <c r="B34" s="120">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="60" t="s">
-        <v>364</v>
-      </c>
-      <c r="D34" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="E34" s="40" t="s">
-        <v>112</v>
-      </c>
-      <c r="F34" s="39" t="s">
-        <v>174</v>
-      </c>
-      <c r="G34" s="40" t="s">
-        <v>234</v>
-      </c>
-      <c r="H34" s="39" t="s">
-        <v>273</v>
-      </c>
-      <c r="I34" s="39" t="s">
-        <v>420</v>
-      </c>
-      <c r="J34" s="39" t="s">
-        <v>419</v>
-      </c>
-      <c r="K34" s="40" t="s">
-        <v>307</v>
-      </c>
-      <c r="L34" s="39">
+      <c r="C34" s="121" t="s">
+        <v>341</v>
+      </c>
+      <c r="D34" s="122" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="123" t="s">
+        <v>100</v>
+      </c>
+      <c r="F34" s="122" t="s">
+        <v>160</v>
+      </c>
+      <c r="G34" s="123" t="s">
+        <v>216</v>
+      </c>
+      <c r="H34" s="122" t="s">
+        <v>254</v>
+      </c>
+      <c r="I34" s="122" t="s">
+        <v>395</v>
+      </c>
+      <c r="J34" s="122" t="s">
+        <v>394</v>
+      </c>
+      <c r="K34" s="123" t="s">
+        <v>287</v>
+      </c>
+      <c r="L34" s="122">
         <v>1</v>
       </c>
-      <c r="M34" s="42">
+      <c r="M34" s="124">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N34" s="42">
-        <v>25</v>
-      </c>
-      <c r="O34" s="65" t="s">
-        <v>391</v>
-      </c>
-      <c r="P34" s="42">
+      <c r="N34" s="124">
+        <v>0</v>
+      </c>
+      <c r="O34" s="125" t="s">
+        <v>368</v>
+      </c>
+      <c r="P34" s="124">
         <v>9.1899999999999996E-2</v>
       </c>
-      <c r="Q34" s="42">
-        <f t="shared" ref="Q34" si="24">N34*P34</f>
-        <v>2.2974999999999999</v>
-      </c>
-      <c r="R34" s="42"/>
-    </row>
-    <row r="35" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q34" s="124">
+        <f t="shared" ref="Q34" si="23">N34*P34</f>
+        <v>0</v>
+      </c>
+      <c r="R34" s="124" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1"/>
       <c r="B35" s="53">
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
       <c r="C35" s="61" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="D35" s="37" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E35" s="38" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="F35" s="37" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="G35" s="38" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="H35" s="37" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="I35" s="37" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J35" s="37" t="s">
-        <v>421</v>
+        <v>396</v>
       </c>
       <c r="K35" s="38" t="s">
-        <v>323</v>
+        <v>302</v>
       </c>
       <c r="L35" s="37">
         <v>4</v>
@@ -4323,49 +4897,49 @@
         <v>100</v>
       </c>
       <c r="O35" s="64" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P35" s="41">
         <v>5.4999999999999997E-3</v>
       </c>
       <c r="Q35" s="41">
-        <f t="shared" ref="Q35" si="25">P35*N35</f>
+        <f t="shared" ref="Q35" si="24">P35*N35</f>
         <v>0.54999999999999993</v>
       </c>
       <c r="R35" s="41"/>
     </row>
-    <row r="36" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1"/>
       <c r="B36" s="53">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="C36" s="60" t="s">
-        <v>365</v>
+        <v>342</v>
       </c>
       <c r="D36" s="39" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E36" s="40" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="F36" s="39" t="s">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="G36" s="40" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="H36" s="39" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="I36" s="39" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J36" s="39" t="s">
-        <v>422</v>
+        <v>397</v>
       </c>
       <c r="K36" s="40" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="L36" s="39">
         <v>1</v>
@@ -4378,49 +4952,49 @@
         <v>30</v>
       </c>
       <c r="O36" s="65" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P36" s="42">
         <v>4.87E-2</v>
       </c>
       <c r="Q36" s="42">
-        <f t="shared" ref="Q36" si="26">N36*P36</f>
+        <f t="shared" ref="Q36" si="25">N36*P36</f>
         <v>1.4610000000000001</v>
       </c>
       <c r="R36" s="42"/>
     </row>
-    <row r="37" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1"/>
       <c r="B37" s="53">
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
       <c r="C37" s="61" t="s">
-        <v>365</v>
+        <v>342</v>
       </c>
       <c r="D37" s="37" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E37" s="38" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="F37" s="37" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="G37" s="38" t="s">
-        <v>324</v>
+        <v>303</v>
       </c>
       <c r="H37" s="37" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="I37" s="37" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J37" s="37" t="s">
-        <v>423</v>
+        <v>398</v>
       </c>
       <c r="K37" s="38" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="L37" s="37">
         <v>1</v>
@@ -4433,161 +5007,163 @@
         <v>30</v>
       </c>
       <c r="O37" s="64" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P37" s="41">
         <v>7.4300000000000005E-2</v>
       </c>
       <c r="Q37" s="41">
-        <f t="shared" ref="Q37" si="27">P37*N37</f>
+        <f t="shared" ref="Q37" si="26">P37*N37</f>
         <v>2.2290000000000001</v>
       </c>
       <c r="R37" s="41"/>
     </row>
-    <row r="38" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1"/>
-      <c r="B38" s="53">
+      <c r="B38" s="85">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="60" t="s">
-        <v>365</v>
-      </c>
-      <c r="D38" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="E38" s="40" t="s">
-        <v>116</v>
-      </c>
-      <c r="F38" s="39" t="s">
-        <v>181</v>
-      </c>
-      <c r="G38" s="40" t="s">
-        <v>325</v>
-      </c>
-      <c r="H38" s="39" t="s">
-        <v>278</v>
-      </c>
-      <c r="I38" s="39" t="s">
-        <v>325</v>
-      </c>
-      <c r="J38" s="39" t="s">
-        <v>424</v>
-      </c>
-      <c r="K38" s="40" t="s">
-        <v>361</v>
-      </c>
-      <c r="L38" s="39">
-        <v>1</v>
-      </c>
-      <c r="M38" s="42">
+      <c r="C38" s="92" t="s">
+        <v>342</v>
+      </c>
+      <c r="D38" s="93" t="s">
+        <v>509</v>
+      </c>
+      <c r="E38" s="94" t="s">
+        <v>104</v>
+      </c>
+      <c r="F38" s="93" t="s">
+        <v>167</v>
+      </c>
+      <c r="G38" s="94" t="s">
+        <v>304</v>
+      </c>
+      <c r="H38" s="93" t="s">
+        <v>259</v>
+      </c>
+      <c r="I38" s="93" t="s">
+        <v>304</v>
+      </c>
+      <c r="J38" s="93" t="s">
+        <v>399</v>
+      </c>
+      <c r="K38" s="94" t="s">
+        <v>338</v>
+      </c>
+      <c r="L38" s="108">
+        <v>2</v>
+      </c>
+      <c r="M38" s="95">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N38" s="42">
         <v>40</v>
       </c>
-      <c r="O38" s="65" t="s">
-        <v>391</v>
-      </c>
-      <c r="P38" s="42">
+      <c r="N38" s="107">
+        <v>60</v>
+      </c>
+      <c r="O38" s="96" t="s">
+        <v>368</v>
+      </c>
+      <c r="P38" s="95">
         <v>2.8899999999999999E-2</v>
       </c>
-      <c r="Q38" s="42">
-        <f t="shared" ref="Q38" si="28">N38*P38</f>
-        <v>1.1559999999999999</v>
-      </c>
-      <c r="R38" s="42"/>
-    </row>
-    <row r="39" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q38" s="95">
+        <f t="shared" ref="Q38" si="27">N38*P38</f>
+        <v>1.734</v>
+      </c>
+      <c r="R38" s="91" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1"/>
       <c r="B39" s="67">
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
       <c r="C39" s="68" t="s">
-        <v>365</v>
+        <v>342</v>
       </c>
       <c r="D39" s="69" t="s">
-        <v>36</v>
+        <v>472</v>
       </c>
       <c r="E39" s="70" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="F39" s="69" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="G39" s="70" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="H39" s="69" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="I39" s="69" t="s">
-        <v>426</v>
+        <v>401</v>
       </c>
       <c r="J39" s="69" t="s">
-        <v>427</v>
+        <v>402</v>
       </c>
       <c r="K39" s="70" t="s">
-        <v>361</v>
-      </c>
-      <c r="L39" s="69">
-        <v>8</v>
+        <v>338</v>
+      </c>
+      <c r="L39" s="110">
+        <v>9</v>
       </c>
       <c r="M39" s="71">
         <f t="shared" si="1"/>
-        <v>160</v>
-      </c>
-      <c r="N39" s="71">
-        <v>170</v>
+        <v>180</v>
+      </c>
+      <c r="N39" s="139">
+        <v>190</v>
       </c>
       <c r="O39" s="72" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P39" s="71">
         <v>0.12590000000000001</v>
       </c>
       <c r="Q39" s="71">
-        <f t="shared" ref="Q39" si="29">P39*N39</f>
-        <v>21.403000000000002</v>
+        <f t="shared" ref="Q39" si="28">P39*N39</f>
+        <v>23.921000000000003</v>
       </c>
       <c r="R39" s="73" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1"/>
       <c r="B40" s="53">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="C40" s="60" t="s">
-        <v>367</v>
+        <v>344</v>
       </c>
       <c r="D40" s="39" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E40" s="40" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="F40" s="39" t="s">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="G40" s="40" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="H40" s="39" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="I40" s="39" t="s">
-        <v>428</v>
+        <v>403</v>
       </c>
       <c r="J40" s="39" t="s">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="K40" s="40" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="L40" s="39">
         <v>1</v>
@@ -4600,49 +5176,49 @@
         <v>30</v>
       </c>
       <c r="O40" s="65" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P40" s="42">
         <v>5.6000000000000001E-2</v>
       </c>
       <c r="Q40" s="42">
-        <f t="shared" ref="Q40" si="30">N40*P40</f>
+        <f t="shared" ref="Q40" si="29">N40*P40</f>
         <v>1.68</v>
       </c>
       <c r="R40" s="42"/>
     </row>
-    <row r="41" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1"/>
       <c r="B41" s="53">
         <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
       <c r="C41" s="61" t="s">
-        <v>366</v>
+        <v>343</v>
       </c>
       <c r="D41" s="37" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E41" s="38" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="F41" s="37" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="G41" s="38" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="H41" s="37" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="I41" s="37" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J41" s="37" t="s">
-        <v>430</v>
+        <v>405</v>
       </c>
       <c r="K41" s="38" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="L41" s="37">
         <v>4</v>
@@ -4655,49 +5231,49 @@
         <v>100</v>
       </c>
       <c r="O41" s="64" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P41" s="41">
         <v>2.9499999999999998E-2</v>
       </c>
       <c r="Q41" s="41">
-        <f t="shared" ref="Q41" si="31">P41*N41</f>
+        <f t="shared" ref="Q41" si="30">P41*N41</f>
         <v>2.9499999999999997</v>
       </c>
       <c r="R41" s="41"/>
     </row>
-    <row r="42" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1"/>
       <c r="B42" s="67">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="C42" s="74" t="s">
-        <v>368</v>
+        <v>345</v>
       </c>
       <c r="D42" s="75" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E42" s="76" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="F42" s="75" t="s">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="G42" s="76" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="H42" s="75" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="I42" s="75" t="s">
-        <v>431</v>
+        <v>406</v>
       </c>
       <c r="J42" s="75" t="s">
-        <v>432</v>
+        <v>407</v>
       </c>
       <c r="K42" s="76" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="L42" s="75">
         <v>1</v>
@@ -4710,51 +5286,51 @@
         <v>21</v>
       </c>
       <c r="O42" s="78" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P42" s="77">
         <v>0.53559999999999997</v>
       </c>
       <c r="Q42" s="77">
-        <f t="shared" ref="Q42" si="32">N42*P42</f>
+        <f t="shared" ref="Q42" si="31">N42*P42</f>
         <v>11.247599999999998</v>
       </c>
       <c r="R42" s="73" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
       <c r="B43" s="67">
         <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
       </c>
       <c r="C43" s="68" t="s">
-        <v>368</v>
+        <v>345</v>
       </c>
       <c r="D43" s="69" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E43" s="70" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="F43" s="69" t="s">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="G43" s="70" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="H43" s="69" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="I43" s="69" t="s">
-        <v>433</v>
+        <v>408</v>
       </c>
       <c r="J43" s="69" t="s">
-        <v>434</v>
+        <v>409</v>
       </c>
       <c r="K43" s="70" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="L43" s="69">
         <v>2</v>
@@ -4767,51 +5343,51 @@
         <v>42</v>
       </c>
       <c r="O43" s="72" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P43" s="71">
         <v>0.65639999999999998</v>
       </c>
       <c r="Q43" s="71">
-        <f t="shared" ref="Q43" si="33">P43*N43</f>
+        <f t="shared" ref="Q43" si="32">P43*N43</f>
         <v>27.5688</v>
       </c>
       <c r="R43" s="73" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
       <c r="B44" s="53">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="C44" s="60" t="s">
-        <v>369</v>
+        <v>346</v>
       </c>
       <c r="D44" s="39" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E44" s="40" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="F44" s="39" t="s">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="G44" s="40" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H44" s="39" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="I44" s="39" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J44" s="39" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="K44" s="40" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="L44" s="39">
         <v>1</v>
@@ -4824,49 +5400,49 @@
         <v>21</v>
       </c>
       <c r="O44" s="65" t="s">
-        <v>435</v>
+        <v>410</v>
       </c>
       <c r="P44" s="42">
         <v>1.2</v>
       </c>
       <c r="Q44" s="42">
-        <f t="shared" ref="Q44" si="34">N44*P44</f>
+        <f t="shared" ref="Q44" si="33">N44*P44</f>
         <v>25.2</v>
       </c>
       <c r="R44" s="42"/>
     </row>
-    <row r="45" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
       <c r="B45" s="53">
         <f>ROW(B45) - ROW($B$9)</f>
         <v>36</v>
       </c>
       <c r="C45" s="61" t="s">
-        <v>369</v>
+        <v>346</v>
       </c>
       <c r="D45" s="37" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E45" s="38" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="F45" s="37" t="s">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="G45" s="38" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="H45" s="37" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="I45" s="37" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J45" s="37" t="s">
-        <v>436</v>
+        <v>411</v>
       </c>
       <c r="K45" s="38" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="L45" s="37">
         <v>1</v>
@@ -4879,49 +5455,49 @@
         <v>25</v>
       </c>
       <c r="O45" s="64" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P45" s="41">
         <v>9.2200000000000004E-2</v>
       </c>
       <c r="Q45" s="41">
-        <f t="shared" ref="Q45" si="35">P45*N45</f>
+        <f t="shared" ref="Q45" si="34">P45*N45</f>
         <v>2.3050000000000002</v>
       </c>
       <c r="R45" s="41"/>
     </row>
-    <row r="46" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1"/>
       <c r="B46" s="53">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="C46" s="60" t="s">
-        <v>366</v>
+        <v>343</v>
       </c>
       <c r="D46" s="39" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E46" s="40" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F46" s="39" t="s">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="G46" s="40" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="H46" s="39" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="I46" s="39" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J46" s="39" t="s">
-        <v>437</v>
+        <v>412</v>
       </c>
       <c r="K46" s="40" t="s">
-        <v>326</v>
+        <v>305</v>
       </c>
       <c r="L46" s="39">
         <v>1</v>
@@ -4934,104 +5510,106 @@
         <v>21</v>
       </c>
       <c r="O46" s="65" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P46" s="42">
         <v>0.45629999999999998</v>
       </c>
       <c r="Q46" s="42">
-        <f t="shared" ref="Q46" si="36">N46*P46</f>
+        <f t="shared" ref="Q46" si="35">N46*P46</f>
         <v>9.5823</v>
       </c>
       <c r="R46" s="42"/>
     </row>
-    <row r="47" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
-      <c r="B47" s="53">
+      <c r="B47" s="85">
         <f>ROW(B47) - ROW($B$9)</f>
         <v>38</v>
       </c>
-      <c r="C47" s="61" t="s">
-        <v>366</v>
-      </c>
-      <c r="D47" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="E47" s="38" t="s">
-        <v>125</v>
-      </c>
-      <c r="F47" s="37" t="s">
-        <v>355</v>
-      </c>
-      <c r="G47" s="38" t="s">
-        <v>190</v>
-      </c>
-      <c r="H47" s="37" t="s">
-        <v>285</v>
-      </c>
-      <c r="I47" s="37" t="s">
-        <v>361</v>
-      </c>
-      <c r="J47" s="37" t="s">
-        <v>438</v>
-      </c>
-      <c r="K47" s="38" t="s">
-        <v>327</v>
-      </c>
-      <c r="L47" s="37">
+      <c r="C47" s="86" t="s">
+        <v>343</v>
+      </c>
+      <c r="D47" s="87" t="s">
+        <v>35</v>
+      </c>
+      <c r="E47" s="88" t="s">
+        <v>503</v>
+      </c>
+      <c r="F47" s="87" t="s">
+        <v>332</v>
+      </c>
+      <c r="G47" s="88" t="s">
+        <v>504</v>
+      </c>
+      <c r="H47" s="97" t="s">
+        <v>505</v>
+      </c>
+      <c r="I47" s="87" t="s">
+        <v>338</v>
+      </c>
+      <c r="J47" s="87" t="s">
+        <v>506</v>
+      </c>
+      <c r="K47" s="88" t="s">
+        <v>507</v>
+      </c>
+      <c r="L47" s="87">
         <v>1</v>
       </c>
-      <c r="M47" s="41">
+      <c r="M47" s="89">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N47" s="41">
-        <v>30</v>
-      </c>
-      <c r="O47" s="64" t="s">
-        <v>391</v>
-      </c>
-      <c r="P47" s="41">
-        <v>9.5500000000000002E-2</v>
-      </c>
-      <c r="Q47" s="41">
-        <f t="shared" ref="Q47" si="37">P47*N47</f>
-        <v>2.8650000000000002</v>
-      </c>
-      <c r="R47" s="41"/>
-    </row>
-    <row r="48" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N47" s="119">
+        <v>25</v>
+      </c>
+      <c r="O47" s="90" t="s">
+        <v>368</v>
+      </c>
+      <c r="P47" s="89">
+        <v>0.1012</v>
+      </c>
+      <c r="Q47" s="89">
+        <f t="shared" ref="Q47" si="36">P47*N47</f>
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="R47" s="106" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1"/>
       <c r="B48" s="53">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="C48" s="60" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="D48" s="39" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E48" s="40" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="F48" s="39" t="s">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="G48" s="40" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="H48" s="39" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="I48" s="39" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J48" s="39" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="K48" s="40" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="L48" s="39">
         <v>1</v>
@@ -5044,49 +5622,49 @@
         <v>30</v>
       </c>
       <c r="O48" s="65" t="s">
-        <v>439</v>
+        <v>413</v>
       </c>
       <c r="P48" s="42">
         <v>0.156</v>
       </c>
       <c r="Q48" s="42">
-        <f t="shared" ref="Q48" si="38">N48*P48</f>
+        <f t="shared" ref="Q48" si="37">N48*P48</f>
         <v>4.68</v>
       </c>
       <c r="R48" s="42"/>
     </row>
-    <row r="49" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1"/>
       <c r="B49" s="53">
         <f>ROW(B49) - ROW($B$9)</f>
         <v>40</v>
       </c>
       <c r="C49" s="61" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="D49" s="37" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E49" s="38" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="F49" s="37" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="G49" s="38" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="H49" s="37" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="I49" s="37" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J49" s="37" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="K49" s="38" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="L49" s="37">
         <v>1</v>
@@ -5099,49 +5677,49 @@
         <v>30</v>
       </c>
       <c r="O49" s="64" t="s">
-        <v>440</v>
+        <v>414</v>
       </c>
       <c r="P49" s="41">
         <v>0.08</v>
       </c>
       <c r="Q49" s="41">
-        <f t="shared" ref="Q49" si="39">P49*N49</f>
+        <f t="shared" ref="Q49" si="38">P49*N49</f>
         <v>2.4</v>
       </c>
       <c r="R49" s="41"/>
     </row>
-    <row r="50" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1"/>
       <c r="B50" s="53">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="C50" s="60" t="s">
-        <v>368</v>
+        <v>345</v>
       </c>
       <c r="D50" s="39" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E50" s="40" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="F50" s="39" t="s">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="G50" s="40" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="H50" s="39" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="I50" s="39" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J50" s="39" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="K50" s="40" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="L50" s="39">
         <v>2</v>
@@ -5154,47 +5732,47 @@
         <v>50</v>
       </c>
       <c r="O50" s="65" t="s">
-        <v>435</v>
+        <v>410</v>
       </c>
       <c r="P50" s="42">
         <v>1.5</v>
       </c>
       <c r="Q50" s="42">
-        <f t="shared" ref="Q50" si="40">N50*P50</f>
+        <f t="shared" ref="Q50" si="39">N50*P50</f>
         <v>75</v>
       </c>
       <c r="R50" s="42" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1"/>
       <c r="B51" s="79">
         <f>ROW(B51) - ROW($B$9)</f>
         <v>42</v>
       </c>
       <c r="C51" s="80" t="s">
-        <v>328</v>
+        <v>306</v>
       </c>
       <c r="D51" s="81" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E51" s="82" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="F51" s="81" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="G51" s="82" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="H51" s="81" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="I51" s="81"/>
       <c r="J51" s="81"/>
       <c r="K51" s="82" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="L51" s="81">
         <v>4</v>
@@ -5204,51 +5782,51 @@
         <v>80</v>
       </c>
       <c r="N51" s="83">
-        <f t="shared" ref="N51" si="41">M51+(M51*0.1)</f>
+        <f t="shared" ref="N51" si="40">M51+(M51*0.1)</f>
         <v>88</v>
       </c>
       <c r="O51" s="83"/>
       <c r="P51" s="83"/>
       <c r="Q51" s="83">
-        <f t="shared" ref="Q51" si="42">P51*N51</f>
+        <f t="shared" ref="Q51" si="41">P51*N51</f>
         <v>0</v>
       </c>
-      <c r="R51" s="87" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R51" s="84" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1"/>
       <c r="B52" s="53">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="C52" s="60" t="s">
-        <v>369</v>
+        <v>346</v>
       </c>
       <c r="D52" s="39" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E52" s="40" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="F52" s="39" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="G52" s="40">
         <v>61300211121</v>
       </c>
       <c r="H52" s="39" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="I52" s="39" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J52" s="39" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="K52" s="40" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="L52" s="39">
         <v>4</v>
@@ -5261,53 +5839,53 @@
         <v>90</v>
       </c>
       <c r="O52" s="65" t="s">
-        <v>435</v>
+        <v>410</v>
       </c>
       <c r="P52" s="42">
         <v>0.13</v>
       </c>
       <c r="Q52" s="42">
-        <f t="shared" ref="Q52" si="43">N52*P52</f>
+        <f t="shared" ref="Q52" si="42">N52*P52</f>
         <v>11.700000000000001</v>
       </c>
       <c r="R52" s="42" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1"/>
       <c r="B53" s="67">
         <f>ROW(B53) - ROW($B$9)</f>
         <v>44</v>
       </c>
       <c r="C53" s="68" t="s">
-        <v>371</v>
+        <v>348</v>
       </c>
       <c r="D53" s="69" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="E53" s="70" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="F53" s="69" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="G53" s="70" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="H53" s="69" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="I53" s="69" t="s">
-        <v>443</v>
+        <v>417</v>
       </c>
       <c r="J53" s="69" t="s">
-        <v>444</v>
+        <v>418</v>
       </c>
       <c r="K53" s="70" t="s">
-        <v>361</v>
-      </c>
-      <c r="L53" s="84">
+        <v>338</v>
+      </c>
+      <c r="L53" s="110">
         <v>4</v>
       </c>
       <c r="M53" s="71">
@@ -5318,51 +5896,51 @@
         <v>85</v>
       </c>
       <c r="O53" s="72" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P53" s="71">
         <v>0.21740000000000001</v>
       </c>
       <c r="Q53" s="71">
-        <f t="shared" ref="Q53" si="44">P53*N53</f>
+        <f t="shared" ref="Q53" si="43">P53*N53</f>
         <v>18.478999999999999</v>
       </c>
       <c r="R53" s="71" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1"/>
       <c r="B54" s="53">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="C54" s="60" t="s">
-        <v>372</v>
+        <v>349</v>
       </c>
       <c r="D54" s="39" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E54" s="40" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="F54" s="39" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="G54" s="40" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="H54" s="39" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="I54" s="39" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J54" s="39" t="s">
-        <v>446</v>
+        <v>420</v>
       </c>
       <c r="K54" s="40" t="s">
-        <v>329</v>
+        <v>307</v>
       </c>
       <c r="L54" s="39">
         <v>2</v>
@@ -5375,49 +5953,49 @@
         <v>100</v>
       </c>
       <c r="O54" s="65" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P54" s="42">
         <v>1E-3</v>
       </c>
       <c r="Q54" s="42">
-        <f t="shared" ref="Q54" si="45">N54*P54</f>
+        <f t="shared" ref="Q54" si="44">N54*P54</f>
         <v>0.1</v>
       </c>
       <c r="R54" s="42"/>
     </row>
-    <row r="55" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1"/>
       <c r="B55" s="53">
         <f>ROW(B55) - ROW($B$9)</f>
         <v>46</v>
       </c>
       <c r="C55" s="61" t="s">
-        <v>372</v>
+        <v>349</v>
       </c>
       <c r="D55" s="37" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="E55" s="38" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="F55" s="37" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="G55" s="38" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="H55" s="37" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="I55" s="37" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J55" s="37" t="s">
-        <v>447</v>
+        <v>421</v>
       </c>
       <c r="K55" s="38" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="L55" s="37">
         <v>1</v>
@@ -5430,49 +6008,49 @@
         <v>100</v>
       </c>
       <c r="O55" s="64" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P55" s="41">
         <v>1.4E-3</v>
       </c>
       <c r="Q55" s="41">
-        <f t="shared" ref="Q55" si="46">P55*N55</f>
+        <f t="shared" ref="Q55" si="45">P55*N55</f>
         <v>0.13999999999999999</v>
       </c>
       <c r="R55" s="41"/>
     </row>
-    <row r="56" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
       <c r="B56" s="53">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="C56" s="60" t="s">
-        <v>372</v>
+        <v>349</v>
       </c>
       <c r="D56" s="39" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="E56" s="40" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="F56" s="39" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="G56" s="40" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="H56" s="39" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="I56" s="39" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J56" s="39" t="s">
-        <v>448</v>
+        <v>422</v>
       </c>
       <c r="K56" s="40" t="s">
-        <v>331</v>
+        <v>309</v>
       </c>
       <c r="L56" s="39">
         <v>1</v>
@@ -5485,49 +6063,49 @@
         <v>100</v>
       </c>
       <c r="O56" s="65" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P56" s="42">
         <v>1.6000000000000001E-3</v>
       </c>
       <c r="Q56" s="42">
-        <f t="shared" ref="Q56" si="47">N56*P56</f>
+        <f t="shared" ref="Q56" si="46">N56*P56</f>
         <v>0.16</v>
       </c>
       <c r="R56" s="42"/>
     </row>
-    <row r="57" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1"/>
       <c r="B57" s="53">
         <f>ROW(B57) - ROW($B$9)</f>
         <v>48</v>
       </c>
       <c r="C57" s="61" t="s">
-        <v>372</v>
+        <v>349</v>
       </c>
       <c r="D57" s="37" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E57" s="38" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="F57" s="37" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="G57" s="38" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="H57" s="37" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="I57" s="37" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J57" s="37" t="s">
-        <v>449</v>
+        <v>423</v>
       </c>
       <c r="K57" s="38" t="s">
-        <v>332</v>
+        <v>310</v>
       </c>
       <c r="L57" s="37">
         <v>2</v>
@@ -5540,49 +6118,49 @@
         <v>100</v>
       </c>
       <c r="O57" s="64" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P57" s="41">
         <v>1.4E-3</v>
       </c>
       <c r="Q57" s="41">
-        <f t="shared" ref="Q57" si="48">P57*N57</f>
+        <f t="shared" ref="Q57" si="47">P57*N57</f>
         <v>0.13999999999999999</v>
       </c>
       <c r="R57" s="41"/>
     </row>
-    <row r="58" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1"/>
       <c r="B58" s="53">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="C58" s="60" t="s">
-        <v>372</v>
+        <v>349</v>
       </c>
       <c r="D58" s="39" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="E58" s="40" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="F58" s="39" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="G58" s="40" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="H58" s="39" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="I58" s="39" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J58" s="39" t="s">
-        <v>450</v>
+        <v>424</v>
       </c>
       <c r="K58" s="40" t="s">
-        <v>333</v>
+        <v>311</v>
       </c>
       <c r="L58" s="39">
         <v>4</v>
@@ -5595,49 +6173,49 @@
         <v>100</v>
       </c>
       <c r="O58" s="65" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P58" s="42">
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q58" s="42">
-        <f t="shared" ref="Q58" si="49">N58*P58</f>
+        <f t="shared" ref="Q58" si="48">N58*P58</f>
         <v>0.13</v>
       </c>
       <c r="R58" s="42"/>
     </row>
-    <row r="59" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1"/>
       <c r="B59" s="53">
         <f>ROW(B59) - ROW($B$9)</f>
         <v>50</v>
       </c>
       <c r="C59" s="61" t="s">
-        <v>372</v>
+        <v>349</v>
       </c>
       <c r="D59" s="37" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E59" s="38" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="F59" s="37" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="G59" s="38" t="s">
-        <v>377</v>
+        <v>354</v>
       </c>
       <c r="H59" s="37" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="I59" s="37" t="s">
-        <v>451</v>
+        <v>425</v>
       </c>
       <c r="J59" s="37" t="s">
-        <v>452</v>
+        <v>426</v>
       </c>
       <c r="K59" s="38" t="s">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="L59" s="37">
         <v>4</v>
@@ -5650,603 +6228,603 @@
         <v>90</v>
       </c>
       <c r="O59" s="64" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P59" s="41">
         <v>6.4500000000000002E-2</v>
       </c>
       <c r="Q59" s="41">
-        <f t="shared" ref="Q59" si="50">P59*N59</f>
+        <f t="shared" ref="Q59" si="49">P59*N59</f>
         <v>5.8049999999999997</v>
       </c>
       <c r="R59" s="41"/>
     </row>
-    <row r="60" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1"/>
-      <c r="B60" s="53">
+      <c r="B60" s="85">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="C60" s="60" t="s">
-        <v>372</v>
-      </c>
-      <c r="D60" s="75" t="s">
-        <v>464</v>
-      </c>
-      <c r="E60" s="40" t="s">
-        <v>138</v>
-      </c>
-      <c r="F60" s="39" t="s">
-        <v>197</v>
-      </c>
-      <c r="G60" s="40" t="s">
-        <v>244</v>
-      </c>
-      <c r="H60" s="39" t="s">
-        <v>269</v>
-      </c>
-      <c r="I60" s="39"/>
-      <c r="J60" s="39" t="s">
-        <v>453</v>
-      </c>
-      <c r="K60" s="40" t="s">
-        <v>335</v>
-      </c>
-      <c r="L60" s="86">
-        <v>9</v>
-      </c>
-      <c r="M60" s="42">
+      <c r="C60" s="92" t="s">
+        <v>349</v>
+      </c>
+      <c r="D60" s="105" t="s">
+        <v>461</v>
+      </c>
+      <c r="E60" s="94" t="s">
+        <v>125</v>
+      </c>
+      <c r="F60" s="93" t="s">
+        <v>182</v>
+      </c>
+      <c r="G60" s="94" t="s">
+        <v>226</v>
+      </c>
+      <c r="H60" s="93" t="s">
+        <v>250</v>
+      </c>
+      <c r="I60" s="93"/>
+      <c r="J60" s="93" t="s">
+        <v>427</v>
+      </c>
+      <c r="K60" s="94" t="s">
+        <v>313</v>
+      </c>
+      <c r="L60" s="108">
+        <v>1</v>
+      </c>
+      <c r="M60" s="95">
         <f t="shared" si="1"/>
-        <v>180</v>
-      </c>
-      <c r="N60" s="42">
-        <v>200</v>
-      </c>
-      <c r="O60" s="65" t="s">
-        <v>391</v>
-      </c>
-      <c r="P60" s="42">
+        <v>20</v>
+      </c>
+      <c r="N60" s="107">
+        <v>100</v>
+      </c>
+      <c r="O60" s="96" t="s">
+        <v>368</v>
+      </c>
+      <c r="P60" s="95">
         <v>1.5E-3</v>
       </c>
-      <c r="Q60" s="42">
-        <f t="shared" ref="Q60" si="51">N60*P60</f>
-        <v>0.3</v>
-      </c>
-      <c r="R60" s="42" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="61" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q60" s="95">
+        <f t="shared" ref="Q60:Q61" si="50">N60*P60</f>
+        <v>0.15</v>
+      </c>
+      <c r="R60" s="106" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1"/>
-      <c r="B61" s="53">
+      <c r="B61" s="85">
         <f>ROW(B61) - ROW($B$9)</f>
         <v>52</v>
       </c>
-      <c r="C61" s="61" t="s">
-        <v>372</v>
-      </c>
-      <c r="D61" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="E61" s="38" t="s">
-        <v>139</v>
-      </c>
-      <c r="F61" s="37" t="s">
-        <v>197</v>
-      </c>
-      <c r="G61" s="38" t="s">
-        <v>245</v>
-      </c>
-      <c r="H61" s="37" t="s">
-        <v>292</v>
-      </c>
-      <c r="I61" s="37" t="s">
-        <v>361</v>
-      </c>
-      <c r="J61" s="37" t="s">
-        <v>361</v>
-      </c>
-      <c r="K61" s="38" t="s">
-        <v>336</v>
-      </c>
-      <c r="L61" s="37">
+      <c r="C61" s="86" t="s">
+        <v>349</v>
+      </c>
+      <c r="D61" s="87" t="s">
+        <v>460</v>
+      </c>
+      <c r="E61" s="87" t="s">
+        <v>463</v>
+      </c>
+      <c r="F61" s="87" t="s">
+        <v>182</v>
+      </c>
+      <c r="G61" s="87" t="s">
+        <v>464</v>
+      </c>
+      <c r="H61" s="87" t="s">
+        <v>273</v>
+      </c>
+      <c r="I61" s="87" t="s">
+        <v>338</v>
+      </c>
+      <c r="J61" s="87" t="s">
+        <v>465</v>
+      </c>
+      <c r="K61" s="87" t="s">
+        <v>466</v>
+      </c>
+      <c r="L61" s="109">
+        <v>8</v>
+      </c>
+      <c r="M61" s="87">
+        <f t="shared" si="1"/>
+        <v>160</v>
+      </c>
+      <c r="N61" s="107">
+        <v>100</v>
+      </c>
+      <c r="O61" s="111" t="s">
+        <v>368</v>
+      </c>
+      <c r="P61" s="87">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q61" s="87">
+        <f t="shared" si="50"/>
+        <v>0.11</v>
+      </c>
+      <c r="R61" s="106" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="1"/>
+      <c r="B62" s="53">
+        <f>ROW(B62) - ROW($B$9)</f>
+        <v>53</v>
+      </c>
+      <c r="C62" s="61" t="s">
+        <v>349</v>
+      </c>
+      <c r="D62" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="E62" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="F62" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="G62" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="H62" s="37" t="s">
+        <v>272</v>
+      </c>
+      <c r="I62" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="J62" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="K62" s="38" t="s">
+        <v>314</v>
+      </c>
+      <c r="L62" s="37">
         <v>1</v>
       </c>
-      <c r="M61" s="41">
+      <c r="M62" s="41">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N61" s="41">
+      <c r="N62" s="41">
         <v>30</v>
       </c>
-      <c r="O61" s="64" t="s">
-        <v>439</v>
-      </c>
-      <c r="P61" s="41">
+      <c r="O62" s="64" t="s">
+        <v>413</v>
+      </c>
+      <c r="P62" s="41">
         <v>1.8589999999999999E-2</v>
       </c>
-      <c r="Q61" s="41">
-        <f t="shared" ref="Q61" si="52">P61*N61</f>
+      <c r="Q62" s="41">
+        <f t="shared" ref="Q62" si="51">P62*N62</f>
         <v>0.55769999999999997</v>
       </c>
-      <c r="R61" s="41"/>
-    </row>
-    <row r="62" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="1"/>
-      <c r="B62" s="53">
+      <c r="R62" s="41"/>
+    </row>
+    <row r="63" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="1"/>
+      <c r="B63" s="53">
         <f t="shared" si="0"/>
-        <v>53</v>
-      </c>
-      <c r="C62" s="60" t="s">
-        <v>372</v>
-      </c>
-      <c r="D62" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="E62" s="40" t="s">
-        <v>140</v>
-      </c>
-      <c r="F62" s="39" t="s">
-        <v>197</v>
-      </c>
-      <c r="G62" s="40" t="s">
-        <v>246</v>
-      </c>
-      <c r="H62" s="39" t="s">
-        <v>269</v>
-      </c>
-      <c r="I62" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="J62" s="39" t="s">
-        <v>454</v>
-      </c>
-      <c r="K62" s="40" t="s">
-        <v>337</v>
-      </c>
-      <c r="L62" s="39">
+        <v>54</v>
+      </c>
+      <c r="C63" s="60" t="s">
+        <v>349</v>
+      </c>
+      <c r="D63" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="E63" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="F63" s="39" t="s">
+        <v>182</v>
+      </c>
+      <c r="G63" s="40" t="s">
+        <v>228</v>
+      </c>
+      <c r="H63" s="39" t="s">
+        <v>250</v>
+      </c>
+      <c r="I63" s="39" t="s">
+        <v>338</v>
+      </c>
+      <c r="J63" s="39" t="s">
+        <v>428</v>
+      </c>
+      <c r="K63" s="40" t="s">
+        <v>315</v>
+      </c>
+      <c r="L63" s="39">
         <v>1</v>
       </c>
-      <c r="M62" s="42">
+      <c r="M63" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N62" s="42">
+      <c r="N63" s="42">
         <v>100</v>
       </c>
-      <c r="O62" s="65" t="s">
-        <v>391</v>
-      </c>
-      <c r="P62" s="42">
+      <c r="O63" s="65" t="s">
+        <v>368</v>
+      </c>
+      <c r="P63" s="42">
         <v>1.4E-3</v>
       </c>
-      <c r="Q62" s="42">
-        <f t="shared" ref="Q62" si="53">N62*P62</f>
+      <c r="Q63" s="42">
+        <f t="shared" ref="Q63" si="52">N63*P63</f>
         <v>0.13999999999999999</v>
       </c>
-      <c r="R62" s="42"/>
-    </row>
-    <row r="63" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="1"/>
-      <c r="B63" s="53">
-        <f>ROW(B63) - ROW($B$9)</f>
-        <v>54</v>
-      </c>
-      <c r="C63" s="61" t="s">
-        <v>372</v>
-      </c>
-      <c r="D63" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="E63" s="38" t="s">
-        <v>141</v>
-      </c>
-      <c r="F63" s="37" t="s">
-        <v>197</v>
-      </c>
-      <c r="G63" s="38" t="s">
-        <v>247</v>
-      </c>
-      <c r="H63" s="37" t="s">
-        <v>292</v>
-      </c>
-      <c r="I63" s="37" t="s">
-        <v>361</v>
-      </c>
-      <c r="J63" s="37" t="s">
-        <v>361</v>
-      </c>
-      <c r="K63" s="38" t="s">
-        <v>338</v>
-      </c>
-      <c r="L63" s="37">
+      <c r="R63" s="42"/>
+    </row>
+    <row r="64" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="1"/>
+      <c r="B64" s="53">
+        <f>ROW(B64) - ROW($B$9)</f>
+        <v>55</v>
+      </c>
+      <c r="C64" s="61" t="s">
+        <v>349</v>
+      </c>
+      <c r="D64" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="E64" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="F64" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="G64" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="H64" s="37" t="s">
+        <v>272</v>
+      </c>
+      <c r="I64" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="J64" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="K64" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="L64" s="37">
         <v>1</v>
       </c>
-      <c r="M63" s="41">
+      <c r="M64" s="41">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N63" s="41">
+      <c r="N64" s="41">
         <v>50</v>
       </c>
-      <c r="O63" s="64" t="s">
-        <v>439</v>
-      </c>
-      <c r="P63" s="41">
+      <c r="O64" s="64" t="s">
+        <v>413</v>
+      </c>
+      <c r="P64" s="41">
         <v>4.6699999999999997E-3</v>
       </c>
-      <c r="Q63" s="41">
-        <f t="shared" ref="Q63" si="54">P63*N63</f>
+      <c r="Q64" s="41">
+        <f t="shared" ref="Q64" si="53">P64*N64</f>
         <v>0.23349999999999999</v>
       </c>
-      <c r="R63" s="41"/>
-    </row>
-    <row r="64" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="1"/>
-      <c r="B64" s="53">
+      <c r="R64" s="41"/>
+    </row>
+    <row r="65" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="1"/>
+      <c r="B65" s="53">
         <f t="shared" si="0"/>
-        <v>55</v>
-      </c>
-      <c r="C64" s="60" t="s">
-        <v>372</v>
-      </c>
-      <c r="D64" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="E64" s="40" t="s">
-        <v>142</v>
-      </c>
-      <c r="F64" s="39" t="s">
-        <v>197</v>
-      </c>
-      <c r="G64" s="40" t="s">
-        <v>248</v>
-      </c>
-      <c r="H64" s="39" t="s">
-        <v>269</v>
-      </c>
-      <c r="I64" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="J64" s="39" t="s">
-        <v>455</v>
-      </c>
-      <c r="K64" s="40" t="s">
-        <v>339</v>
-      </c>
-      <c r="L64" s="39">
+        <v>56</v>
+      </c>
+      <c r="C65" s="60" t="s">
+        <v>349</v>
+      </c>
+      <c r="D65" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="E65" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="F65" s="39" t="s">
+        <v>182</v>
+      </c>
+      <c r="G65" s="40" t="s">
+        <v>230</v>
+      </c>
+      <c r="H65" s="39" t="s">
+        <v>250</v>
+      </c>
+      <c r="I65" s="39" t="s">
+        <v>338</v>
+      </c>
+      <c r="J65" s="39" t="s">
+        <v>429</v>
+      </c>
+      <c r="K65" s="40" t="s">
+        <v>317</v>
+      </c>
+      <c r="L65" s="39">
         <v>1</v>
       </c>
-      <c r="M64" s="42">
+      <c r="M65" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N64" s="42">
+      <c r="N65" s="42">
         <v>100</v>
       </c>
-      <c r="O64" s="65" t="s">
-        <v>391</v>
-      </c>
-      <c r="P64" s="42">
+      <c r="O65" s="65" t="s">
+        <v>368</v>
+      </c>
+      <c r="P65" s="42">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q64" s="42">
-        <f t="shared" ref="Q64" si="55">N64*P64</f>
+      <c r="Q65" s="42">
+        <f t="shared" ref="Q65" si="54">N65*P65</f>
         <v>0.12</v>
       </c>
-      <c r="R64" s="42"/>
-    </row>
-    <row r="65" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="1"/>
-      <c r="B65" s="53">
-        <f>ROW(B65) - ROW($B$9)</f>
-        <v>56</v>
-      </c>
-      <c r="C65" s="61" t="s">
-        <v>372</v>
-      </c>
-      <c r="D65" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="E65" s="38" t="s">
-        <v>143</v>
-      </c>
-      <c r="F65" s="37" t="s">
-        <v>197</v>
-      </c>
-      <c r="G65" s="38" t="s">
-        <v>249</v>
-      </c>
-      <c r="H65" s="37" t="s">
-        <v>292</v>
-      </c>
-      <c r="I65" s="37" t="s">
-        <v>361</v>
-      </c>
-      <c r="J65" s="37" t="s">
-        <v>361</v>
-      </c>
-      <c r="K65" s="38" t="s">
-        <v>340</v>
-      </c>
-      <c r="L65" s="37">
+      <c r="R65" s="42"/>
+    </row>
+    <row r="66" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="1"/>
+      <c r="B66" s="53">
+        <f>ROW(B66) - ROW($B$9)</f>
+        <v>57</v>
+      </c>
+      <c r="C66" s="61" t="s">
+        <v>349</v>
+      </c>
+      <c r="D66" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="E66" s="38" t="s">
+        <v>130</v>
+      </c>
+      <c r="F66" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="G66" s="38" t="s">
+        <v>231</v>
+      </c>
+      <c r="H66" s="37" t="s">
+        <v>272</v>
+      </c>
+      <c r="I66" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="J66" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="K66" s="38" t="s">
+        <v>318</v>
+      </c>
+      <c r="L66" s="37">
         <v>1</v>
       </c>
-      <c r="M65" s="41">
+      <c r="M66" s="41">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N65" s="41">
+      <c r="N66" s="41">
         <v>50</v>
       </c>
-      <c r="O65" s="64" t="s">
-        <v>439</v>
-      </c>
-      <c r="P65" s="41">
+      <c r="O66" s="64" t="s">
+        <v>413</v>
+      </c>
+      <c r="P66" s="41">
         <v>1.11E-2</v>
       </c>
-      <c r="Q65" s="41">
-        <f t="shared" ref="Q65" si="56">P65*N65</f>
+      <c r="Q66" s="41">
+        <f t="shared" ref="Q66" si="55">P66*N66</f>
         <v>0.55500000000000005</v>
       </c>
-      <c r="R65" s="41"/>
-    </row>
-    <row r="66" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="1"/>
-      <c r="B66" s="53">
+      <c r="R66" s="41"/>
+    </row>
+    <row r="67" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="1"/>
+      <c r="B67" s="53">
         <f t="shared" si="0"/>
-        <v>57</v>
-      </c>
-      <c r="C66" s="60" t="s">
-        <v>372</v>
-      </c>
-      <c r="D66" s="39" t="s">
-        <v>62</v>
-      </c>
-      <c r="E66" s="40" t="s">
-        <v>144</v>
-      </c>
-      <c r="F66" s="39" t="s">
-        <v>197</v>
-      </c>
-      <c r="G66" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="C67" s="60" t="s">
+        <v>349</v>
+      </c>
+      <c r="D67" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="E67" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="F67" s="39" t="s">
+        <v>182</v>
+      </c>
+      <c r="G67" s="40" t="s">
+        <v>232</v>
+      </c>
+      <c r="H67" s="39" t="s">
         <v>250</v>
       </c>
-      <c r="H66" s="39" t="s">
-        <v>269</v>
-      </c>
-      <c r="I66" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="J66" s="39" t="s">
-        <v>456</v>
-      </c>
-      <c r="K66" s="40" t="s">
-        <v>341</v>
-      </c>
-      <c r="L66" s="39">
+      <c r="I67" s="39" t="s">
+        <v>338</v>
+      </c>
+      <c r="J67" s="39" t="s">
+        <v>430</v>
+      </c>
+      <c r="K67" s="40" t="s">
+        <v>319</v>
+      </c>
+      <c r="L67" s="39">
         <v>1</v>
       </c>
-      <c r="M66" s="42">
+      <c r="M67" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N66" s="42">
+      <c r="N67" s="42">
         <v>100</v>
       </c>
-      <c r="O66" s="65" t="s">
-        <v>391</v>
-      </c>
-      <c r="P66" s="42">
+      <c r="O67" s="65" t="s">
+        <v>368</v>
+      </c>
+      <c r="P67" s="42">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="Q66" s="42">
-        <f t="shared" ref="Q66" si="57">N66*P66</f>
+      <c r="Q67" s="42">
+        <f t="shared" ref="Q67" si="56">N67*P67</f>
         <v>0.21</v>
       </c>
-      <c r="R66" s="42"/>
-    </row>
-    <row r="67" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="1"/>
-      <c r="B67" s="53">
-        <f>ROW(B67) - ROW($B$9)</f>
-        <v>58</v>
-      </c>
-      <c r="C67" s="61" t="s">
-        <v>372</v>
-      </c>
-      <c r="D67" s="37" t="s">
-        <v>63</v>
-      </c>
-      <c r="E67" s="38" t="s">
-        <v>145</v>
-      </c>
-      <c r="F67" s="37" t="s">
-        <v>197</v>
-      </c>
-      <c r="G67" s="38" t="s">
-        <v>251</v>
-      </c>
-      <c r="H67" s="37" t="s">
-        <v>269</v>
-      </c>
-      <c r="I67" s="37" t="s">
-        <v>361</v>
-      </c>
-      <c r="J67" s="37" t="s">
-        <v>457</v>
-      </c>
-      <c r="K67" s="38" t="s">
-        <v>342</v>
-      </c>
-      <c r="L67" s="37">
+      <c r="R67" s="42"/>
+    </row>
+    <row r="68" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="1"/>
+      <c r="B68" s="53">
+        <f>ROW(B68) - ROW($B$9)</f>
+        <v>59</v>
+      </c>
+      <c r="C68" s="61" t="s">
+        <v>349</v>
+      </c>
+      <c r="D68" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="E68" s="38" t="s">
+        <v>132</v>
+      </c>
+      <c r="F68" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="G68" s="38" t="s">
+        <v>233</v>
+      </c>
+      <c r="H68" s="37" t="s">
+        <v>250</v>
+      </c>
+      <c r="I68" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="J68" s="37" t="s">
+        <v>431</v>
+      </c>
+      <c r="K68" s="38" t="s">
+        <v>320</v>
+      </c>
+      <c r="L68" s="37">
         <v>1</v>
       </c>
-      <c r="M67" s="41">
+      <c r="M68" s="41">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N67" s="41">
+      <c r="N68" s="41">
         <v>100</v>
       </c>
-      <c r="O67" s="64" t="s">
-        <v>391</v>
-      </c>
-      <c r="P67" s="41">
+      <c r="O68" s="64" t="s">
+        <v>368</v>
+      </c>
+      <c r="P68" s="41">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="Q67" s="41">
-        <f t="shared" ref="Q67" si="58">P67*N67</f>
+      <c r="Q68" s="41">
+        <f t="shared" ref="Q68" si="57">P68*N68</f>
         <v>0.16</v>
       </c>
-      <c r="R67" s="41"/>
-    </row>
-    <row r="68" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="1"/>
-      <c r="B68" s="53">
+      <c r="R68" s="41"/>
+    </row>
+    <row r="69" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="1"/>
+      <c r="B69" s="53">
         <f t="shared" si="0"/>
-        <v>59</v>
-      </c>
-      <c r="C68" s="60" t="s">
-        <v>372</v>
-      </c>
-      <c r="D68" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="E68" s="40" t="s">
-        <v>146</v>
-      </c>
-      <c r="F68" s="39" t="s">
-        <v>197</v>
-      </c>
-      <c r="G68" s="40" t="s">
-        <v>252</v>
-      </c>
-      <c r="H68" s="39" t="s">
-        <v>269</v>
-      </c>
-      <c r="I68" s="39" t="s">
-        <v>458</v>
-      </c>
-      <c r="J68" s="39" t="s">
-        <v>459</v>
-      </c>
-      <c r="K68" s="40" t="s">
-        <v>343</v>
-      </c>
-      <c r="L68" s="39">
+        <v>60</v>
+      </c>
+      <c r="C69" s="60" t="s">
+        <v>349</v>
+      </c>
+      <c r="D69" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="E69" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="F69" s="39" t="s">
+        <v>182</v>
+      </c>
+      <c r="G69" s="40" t="s">
+        <v>234</v>
+      </c>
+      <c r="H69" s="39" t="s">
+        <v>250</v>
+      </c>
+      <c r="I69" s="39" t="s">
+        <v>432</v>
+      </c>
+      <c r="J69" s="39" t="s">
+        <v>433</v>
+      </c>
+      <c r="K69" s="40" t="s">
+        <v>321</v>
+      </c>
+      <c r="L69" s="39">
         <v>1</v>
       </c>
-      <c r="M68" s="42">
+      <c r="M69" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N68" s="42">
+      <c r="N69" s="42">
         <v>50</v>
       </c>
-      <c r="O68" s="65" t="s">
-        <v>391</v>
-      </c>
-      <c r="P68" s="42">
+      <c r="O69" s="65" t="s">
+        <v>368</v>
+      </c>
+      <c r="P69" s="42">
         <v>6.8999999999999999E-3</v>
       </c>
-      <c r="Q68" s="42">
-        <f t="shared" ref="Q68" si="59">N68*P68</f>
+      <c r="Q69" s="42">
+        <f t="shared" ref="Q69" si="58">N69*P69</f>
         <v>0.34499999999999997</v>
       </c>
-      <c r="R68" s="42"/>
-    </row>
-    <row r="69" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="1"/>
-      <c r="B69" s="53">
-        <f>ROW(B69) - ROW($B$9)</f>
-        <v>60</v>
-      </c>
-      <c r="C69" s="61" t="s">
-        <v>372</v>
-      </c>
-      <c r="D69" s="69" t="s">
-        <v>461</v>
-      </c>
-      <c r="E69" s="38" t="s">
-        <v>147</v>
-      </c>
-      <c r="F69" s="37" t="s">
-        <v>197</v>
-      </c>
-      <c r="G69" s="38" t="s">
-        <v>253</v>
-      </c>
-      <c r="H69" s="37" t="s">
-        <v>269</v>
-      </c>
-      <c r="I69" s="37" t="s">
-        <v>361</v>
-      </c>
-      <c r="J69" s="37" t="s">
-        <v>460</v>
-      </c>
-      <c r="K69" s="38" t="s">
-        <v>344</v>
-      </c>
-      <c r="L69" s="85">
-        <v>2</v>
-      </c>
-      <c r="M69" s="41">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N69" s="41">
-        <v>100</v>
-      </c>
-      <c r="O69" s="64" t="s">
-        <v>391</v>
-      </c>
-      <c r="P69" s="41">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="Q69" s="41">
-        <f t="shared" ref="Q69" si="60">P69*N69</f>
-        <v>0.11</v>
-      </c>
-      <c r="R69" s="41" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="70" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R69" s="42"/>
+    </row>
+    <row r="70" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1"/>
       <c r="B70" s="53">
         <f>ROW(B70) - ROW($B$9)</f>
         <v>61</v>
       </c>
       <c r="C70" s="61" t="s">
-        <v>372</v>
-      </c>
-      <c r="D70" s="37" t="s">
-        <v>65</v>
+        <v>349</v>
+      </c>
+      <c r="D70" s="69" t="s">
+        <v>435</v>
       </c>
       <c r="E70" s="38" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="F70" s="37" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="G70" s="38" t="s">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="H70" s="37" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="I70" s="37" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J70" s="37" t="s">
-        <v>462</v>
+        <v>434</v>
       </c>
       <c r="K70" s="38" t="s">
-        <v>345</v>
-      </c>
-      <c r="L70" s="37">
+        <v>322</v>
+      </c>
+      <c r="L70" s="110">
         <v>2</v>
       </c>
       <c r="M70" s="41">
@@ -6257,49 +6835,51 @@
         <v>100</v>
       </c>
       <c r="O70" s="64" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P70" s="41">
-        <v>1.5E-3</v>
+        <v>1.1000000000000001E-3</v>
       </c>
       <c r="Q70" s="41">
-        <f t="shared" ref="Q70" si="61">P70*N70</f>
-        <v>0.15</v>
-      </c>
-      <c r="R70" s="41"/>
-    </row>
-    <row r="71" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" ref="Q70" si="59">P70*N70</f>
+        <v>0.11</v>
+      </c>
+      <c r="R70" s="41" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1"/>
       <c r="B71" s="53">
         <f>ROW(B71) - ROW($B$9)</f>
         <v>62</v>
       </c>
       <c r="C71" s="61" t="s">
-        <v>372</v>
+        <v>349</v>
       </c>
       <c r="D71" s="37" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E71" s="38" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="F71" s="37" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="G71" s="38" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="H71" s="37" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="I71" s="37" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="J71" s="37" t="s">
-        <v>466</v>
+        <v>436</v>
       </c>
       <c r="K71" s="38" t="s">
-        <v>346</v>
+        <v>323</v>
       </c>
       <c r="L71" s="37">
         <v>2</v>
@@ -6312,1177 +6892,1235 @@
         <v>100</v>
       </c>
       <c r="O71" s="64" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P71" s="41">
         <v>1.5E-3</v>
       </c>
       <c r="Q71" s="41">
-        <f t="shared" ref="Q71" si="62">P71*N71</f>
+        <f t="shared" ref="Q71" si="60">P71*N71</f>
         <v>0.15</v>
       </c>
       <c r="R71" s="41"/>
     </row>
-    <row r="72" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1"/>
       <c r="B72" s="53">
+        <f>ROW(B72) - ROW($B$9)</f>
+        <v>63</v>
+      </c>
+      <c r="C72" s="61" t="s">
+        <v>349</v>
+      </c>
+      <c r="D72" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="E72" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="F72" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="G72" s="38" t="s">
+        <v>237</v>
+      </c>
+      <c r="H72" s="37" t="s">
+        <v>250</v>
+      </c>
+      <c r="I72" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="J72" s="37" t="s">
+        <v>438</v>
+      </c>
+      <c r="K72" s="38" t="s">
+        <v>324</v>
+      </c>
+      <c r="L72" s="37">
+        <v>2</v>
+      </c>
+      <c r="M72" s="41">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="N72" s="41">
+        <v>100</v>
+      </c>
+      <c r="O72" s="64" t="s">
+        <v>368</v>
+      </c>
+      <c r="P72" s="41">
+        <v>1.5E-3</v>
+      </c>
+      <c r="Q72" s="41">
+        <f t="shared" ref="Q72" si="61">P72*N72</f>
+        <v>0.15</v>
+      </c>
+      <c r="R72" s="41"/>
+    </row>
+    <row r="73" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="1"/>
+      <c r="B73" s="53">
         <f t="shared" si="0"/>
-        <v>63</v>
-      </c>
-      <c r="C72" s="60" t="s">
-        <v>372</v>
-      </c>
-      <c r="D72" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="E72" s="40" t="s">
-        <v>150</v>
-      </c>
-      <c r="F72" s="39" t="s">
-        <v>197</v>
-      </c>
-      <c r="G72" s="40" t="s">
-        <v>256</v>
-      </c>
-      <c r="H72" s="39" t="s">
-        <v>292</v>
-      </c>
-      <c r="I72" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="J72" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="K72" s="40" t="s">
-        <v>347</v>
-      </c>
-      <c r="L72" s="39">
+        <v>64</v>
+      </c>
+      <c r="C73" s="60" t="s">
+        <v>349</v>
+      </c>
+      <c r="D73" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="E73" s="40" t="s">
+        <v>137</v>
+      </c>
+      <c r="F73" s="39" t="s">
+        <v>182</v>
+      </c>
+      <c r="G73" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H73" s="39" t="s">
+        <v>272</v>
+      </c>
+      <c r="I73" s="39" t="s">
+        <v>338</v>
+      </c>
+      <c r="J73" s="39" t="s">
+        <v>338</v>
+      </c>
+      <c r="K73" s="40" t="s">
+        <v>325</v>
+      </c>
+      <c r="L73" s="39">
         <v>1</v>
       </c>
-      <c r="M72" s="42">
+      <c r="M73" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N72" s="42">
+      <c r="N73" s="42">
         <v>25</v>
       </c>
-      <c r="O72" s="65" t="s">
-        <v>467</v>
-      </c>
-      <c r="P72" s="42">
+      <c r="O73" s="65" t="s">
+        <v>439</v>
+      </c>
+      <c r="P73" s="42">
         <v>8.5400000000000004E-2</v>
       </c>
-      <c r="Q72" s="42">
-        <f t="shared" ref="Q72" si="63">N72*P72</f>
+      <c r="Q73" s="42">
+        <f t="shared" ref="Q73" si="62">N73*P73</f>
         <v>2.1350000000000002</v>
       </c>
-      <c r="R72" s="42"/>
-    </row>
-    <row r="73" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="1"/>
-      <c r="B73" s="53">
-        <f>ROW(B73) - ROW($B$9)</f>
-        <v>64</v>
-      </c>
-      <c r="C73" s="61" t="s">
-        <v>372</v>
-      </c>
-      <c r="D73" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="E73" s="38" t="s">
-        <v>151</v>
-      </c>
-      <c r="F73" s="37" t="s">
-        <v>199</v>
-      </c>
-      <c r="G73" s="38" t="s">
-        <v>257</v>
-      </c>
-      <c r="H73" s="37" t="s">
-        <v>269</v>
-      </c>
-      <c r="I73" s="37" t="s">
-        <v>361</v>
-      </c>
-      <c r="J73" s="37" t="s">
-        <v>468</v>
-      </c>
-      <c r="K73" s="38" t="s">
-        <v>348</v>
-      </c>
-      <c r="L73" s="37">
+      <c r="R73" s="42"/>
+    </row>
+    <row r="74" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="1"/>
+      <c r="B74" s="85">
+        <f>ROW(B74) - ROW($B$9)</f>
+        <v>65</v>
+      </c>
+      <c r="C74" s="86" t="s">
+        <v>349</v>
+      </c>
+      <c r="D74" s="87" t="s">
+        <v>59</v>
+      </c>
+      <c r="E74" s="132" t="s">
+        <v>497</v>
+      </c>
+      <c r="F74" s="138" t="s">
+        <v>498</v>
+      </c>
+      <c r="G74" s="88" t="s">
+        <v>499</v>
+      </c>
+      <c r="H74" s="97" t="s">
+        <v>273</v>
+      </c>
+      <c r="I74" s="87" t="s">
+        <v>338</v>
+      </c>
+      <c r="J74" s="87" t="s">
+        <v>500</v>
+      </c>
+      <c r="K74" s="88" t="s">
+        <v>501</v>
+      </c>
+      <c r="L74" s="87">
         <v>1</v>
       </c>
-      <c r="M73" s="41">
-        <f t="shared" ref="M73:M91" si="64">L73*20</f>
+      <c r="M74" s="89">
+        <f t="shared" ref="M74:M92" si="63">L74*20</f>
         <v>20</v>
       </c>
-      <c r="N73" s="41">
-        <v>100</v>
-      </c>
-      <c r="O73" s="64" t="s">
-        <v>391</v>
-      </c>
-      <c r="P73" s="41">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q73" s="41">
-        <f t="shared" ref="Q73" si="65">P73*N73</f>
-        <v>0.12</v>
-      </c>
-      <c r="R73" s="41"/>
-    </row>
-    <row r="74" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="1"/>
-      <c r="B74" s="53">
+      <c r="N74" s="119">
+        <v>50</v>
+      </c>
+      <c r="O74" s="90" t="s">
+        <v>368</v>
+      </c>
+      <c r="P74" s="89">
+        <v>3.8E-3</v>
+      </c>
+      <c r="Q74" s="89">
+        <f t="shared" ref="Q74" si="64">P74*N74</f>
+        <v>0.19</v>
+      </c>
+      <c r="R74" s="106" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="1"/>
+      <c r="B75" s="113">
         <f t="shared" si="0"/>
-        <v>65</v>
-      </c>
-      <c r="C74" s="60" t="s">
-        <v>372</v>
-      </c>
-      <c r="D74" s="39" t="s">
-        <v>69</v>
-      </c>
-      <c r="E74" s="40" t="s">
-        <v>152</v>
-      </c>
-      <c r="F74" s="39" t="s">
-        <v>197</v>
-      </c>
-      <c r="G74" s="40" t="s">
-        <v>258</v>
-      </c>
-      <c r="H74" s="39" t="s">
-        <v>292</v>
-      </c>
-      <c r="I74" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="J74" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="K74" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="C75" s="114" t="s">
         <v>349</v>
       </c>
-      <c r="L74" s="39">
+      <c r="D75" s="115" t="s">
+        <v>60</v>
+      </c>
+      <c r="E75" s="116" t="s">
+        <v>138</v>
+      </c>
+      <c r="F75" s="115" t="s">
+        <v>182</v>
+      </c>
+      <c r="G75" s="116" t="s">
+        <v>239</v>
+      </c>
+      <c r="H75" s="115" t="s">
+        <v>272</v>
+      </c>
+      <c r="I75" s="115" t="s">
+        <v>338</v>
+      </c>
+      <c r="J75" s="115" t="s">
+        <v>338</v>
+      </c>
+      <c r="K75" s="116" t="s">
+        <v>326</v>
+      </c>
+      <c r="L75" s="115">
         <v>1</v>
       </c>
-      <c r="M74" s="42">
-        <f t="shared" si="64"/>
+      <c r="M75" s="117">
+        <f t="shared" si="63"/>
         <v>20</v>
       </c>
-      <c r="N74" s="42">
-        <v>25</v>
-      </c>
-      <c r="O74" s="65" t="s">
-        <v>439</v>
-      </c>
-      <c r="P74" s="42">
+      <c r="N75" s="117">
+        <v>0</v>
+      </c>
+      <c r="O75" s="118" t="s">
+        <v>413</v>
+      </c>
+      <c r="P75" s="117">
         <v>1.8589999999999999E-2</v>
       </c>
-      <c r="Q74" s="42">
-        <f t="shared" ref="Q74" si="66">N74*P74</f>
-        <v>0.46475</v>
-      </c>
-      <c r="R74" s="42"/>
-    </row>
-    <row r="75" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="1"/>
-      <c r="B75" s="53">
-        <f>ROW(B75) - ROW($B$9)</f>
-        <v>66</v>
-      </c>
-      <c r="C75" s="61" t="s">
-        <v>372</v>
-      </c>
-      <c r="D75" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="E75" s="38" t="s">
-        <v>153</v>
-      </c>
-      <c r="F75" s="37" t="s">
-        <v>197</v>
-      </c>
-      <c r="G75" s="38" t="s">
-        <v>378</v>
-      </c>
-      <c r="H75" s="37" t="s">
-        <v>293</v>
-      </c>
-      <c r="I75" s="37" t="s">
-        <v>361</v>
-      </c>
-      <c r="J75" s="37" t="s">
-        <v>469</v>
-      </c>
-      <c r="K75" s="38" t="s">
-        <v>350</v>
-      </c>
-      <c r="L75" s="37">
-        <v>1</v>
-      </c>
-      <c r="M75" s="41">
-        <f t="shared" si="64"/>
-        <v>20</v>
-      </c>
-      <c r="N75" s="41">
-        <v>100</v>
-      </c>
-      <c r="O75" s="64" t="s">
-        <v>391</v>
-      </c>
-      <c r="P75" s="41">
-        <v>1E-3</v>
-      </c>
-      <c r="Q75" s="41">
-        <f t="shared" ref="Q75" si="67">P75*N75</f>
-        <v>0.1</v>
-      </c>
-      <c r="R75" s="41"/>
-    </row>
-    <row r="76" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q75" s="117">
+        <f t="shared" ref="Q75" si="65">N75*P75</f>
+        <v>0</v>
+      </c>
+      <c r="R75" s="106" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1"/>
       <c r="B76" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B76) - ROW($B$9)</f>
         <v>67</v>
       </c>
-      <c r="C76" s="60" t="s">
-        <v>372</v>
-      </c>
-      <c r="D76" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="E76" s="40" t="s">
-        <v>154</v>
-      </c>
-      <c r="F76" s="39" t="s">
-        <v>197</v>
-      </c>
-      <c r="G76" s="40" t="s">
-        <v>379</v>
-      </c>
-      <c r="H76" s="39" t="s">
-        <v>294</v>
-      </c>
-      <c r="I76" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="J76" s="39" t="s">
-        <v>470</v>
-      </c>
-      <c r="K76" s="40" t="s">
-        <v>351</v>
-      </c>
-      <c r="L76" s="39">
+      <c r="C76" s="61" t="s">
+        <v>349</v>
+      </c>
+      <c r="D76" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="E76" s="38" t="s">
+        <v>139</v>
+      </c>
+      <c r="F76" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="G76" s="38" t="s">
+        <v>355</v>
+      </c>
+      <c r="H76" s="37" t="s">
+        <v>273</v>
+      </c>
+      <c r="I76" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="J76" s="37" t="s">
+        <v>440</v>
+      </c>
+      <c r="K76" s="38" t="s">
+        <v>327</v>
+      </c>
+      <c r="L76" s="37">
         <v>1</v>
       </c>
-      <c r="M76" s="42">
-        <f t="shared" si="64"/>
+      <c r="M76" s="41">
+        <f t="shared" si="63"/>
         <v>20</v>
       </c>
-      <c r="N76" s="42">
-        <v>50</v>
-      </c>
-      <c r="O76" s="65" t="s">
-        <v>391</v>
-      </c>
-      <c r="P76" s="42">
-        <v>4.3E-3</v>
-      </c>
-      <c r="Q76" s="42">
-        <f t="shared" ref="Q76" si="68">N76*P76</f>
-        <v>0.215</v>
-      </c>
-      <c r="R76" s="42"/>
-    </row>
-    <row r="77" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N76" s="41">
+        <v>100</v>
+      </c>
+      <c r="O76" s="64" t="s">
+        <v>368</v>
+      </c>
+      <c r="P76" s="41">
+        <v>1E-3</v>
+      </c>
+      <c r="Q76" s="41">
+        <f t="shared" ref="Q76" si="66">P76*N76</f>
+        <v>0.1</v>
+      </c>
+      <c r="R76" s="41"/>
+    </row>
+    <row r="77" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1"/>
       <c r="B77" s="53">
-        <f>ROW(B77) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="C77" s="61" t="s">
-        <v>372</v>
-      </c>
-      <c r="D77" s="37" t="s">
-        <v>72</v>
-      </c>
-      <c r="E77" s="38" t="s">
-        <v>155</v>
-      </c>
-      <c r="F77" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="G77" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="H77" s="37" t="s">
-        <v>269</v>
-      </c>
-      <c r="I77" s="37" t="s">
-        <v>361</v>
-      </c>
-      <c r="J77" s="37" t="s">
-        <v>471</v>
-      </c>
-      <c r="K77" s="38" t="s">
-        <v>352</v>
-      </c>
-      <c r="L77" s="37">
-        <v>4</v>
-      </c>
-      <c r="M77" s="41">
-        <f t="shared" si="64"/>
-        <v>80</v>
-      </c>
-      <c r="N77" s="41">
-        <v>100</v>
-      </c>
-      <c r="O77" s="64" t="s">
-        <v>391</v>
-      </c>
-      <c r="P77" s="41">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q77" s="41">
-        <f t="shared" ref="Q77" si="69">P77*N77</f>
-        <v>0.12</v>
-      </c>
-      <c r="R77" s="41"/>
-    </row>
-    <row r="78" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C77" s="60" t="s">
+        <v>349</v>
+      </c>
+      <c r="D77" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="E77" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="F77" s="39" t="s">
+        <v>182</v>
+      </c>
+      <c r="G77" s="40" t="s">
+        <v>356</v>
+      </c>
+      <c r="H77" s="39" t="s">
+        <v>274</v>
+      </c>
+      <c r="I77" s="39" t="s">
+        <v>338</v>
+      </c>
+      <c r="J77" s="39" t="s">
+        <v>441</v>
+      </c>
+      <c r="K77" s="40" t="s">
+        <v>328</v>
+      </c>
+      <c r="L77" s="39">
+        <v>1</v>
+      </c>
+      <c r="M77" s="42">
+        <f t="shared" si="63"/>
+        <v>20</v>
+      </c>
+      <c r="N77" s="42">
+        <v>50</v>
+      </c>
+      <c r="O77" s="65" t="s">
+        <v>368</v>
+      </c>
+      <c r="P77" s="42">
+        <v>4.3E-3</v>
+      </c>
+      <c r="Q77" s="42">
+        <f t="shared" ref="Q77" si="67">N77*P77</f>
+        <v>0.215</v>
+      </c>
+      <c r="R77" s="42"/>
+    </row>
+    <row r="78" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1"/>
       <c r="B78" s="53">
+        <f>ROW(B78) - ROW($B$9)</f>
+        <v>69</v>
+      </c>
+      <c r="C78" s="61" t="s">
+        <v>349</v>
+      </c>
+      <c r="D78" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="E78" s="38" t="s">
+        <v>141</v>
+      </c>
+      <c r="F78" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="G78" s="38" t="s">
+        <v>240</v>
+      </c>
+      <c r="H78" s="37" t="s">
+        <v>250</v>
+      </c>
+      <c r="I78" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="J78" s="37" t="s">
+        <v>442</v>
+      </c>
+      <c r="K78" s="38" t="s">
+        <v>329</v>
+      </c>
+      <c r="L78" s="37">
+        <v>4</v>
+      </c>
+      <c r="M78" s="41">
+        <f t="shared" si="63"/>
+        <v>80</v>
+      </c>
+      <c r="N78" s="41">
+        <v>100</v>
+      </c>
+      <c r="O78" s="64" t="s">
+        <v>368</v>
+      </c>
+      <c r="P78" s="41">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q78" s="41">
+        <f t="shared" ref="Q78" si="68">P78*N78</f>
+        <v>0.12</v>
+      </c>
+      <c r="R78" s="41"/>
+    </row>
+    <row r="79" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="1"/>
+      <c r="B79" s="85">
         <f t="shared" si="0"/>
-        <v>69</v>
-      </c>
-      <c r="C78" s="60" t="s">
-        <v>372</v>
-      </c>
-      <c r="D78" s="39" t="s">
-        <v>73</v>
-      </c>
-      <c r="E78" s="40" t="s">
-        <v>156</v>
-      </c>
-      <c r="F78" s="39" t="s">
-        <v>197</v>
-      </c>
-      <c r="G78" s="40" t="s">
-        <v>260</v>
-      </c>
-      <c r="H78" s="39" t="s">
-        <v>269</v>
-      </c>
-      <c r="I78" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="J78" s="39" t="s">
-        <v>472</v>
-      </c>
-      <c r="K78" s="40" t="s">
-        <v>353</v>
-      </c>
-      <c r="L78" s="39">
-        <v>4</v>
-      </c>
-      <c r="M78" s="42">
-        <f t="shared" si="64"/>
-        <v>80</v>
-      </c>
-      <c r="N78" s="42">
-        <v>100</v>
-      </c>
-      <c r="O78" s="65" t="s">
-        <v>391</v>
-      </c>
-      <c r="P78" s="42">
+        <v>70</v>
+      </c>
+      <c r="C79" s="92" t="s">
+        <v>349</v>
+      </c>
+      <c r="D79" s="93" t="s">
+        <v>495</v>
+      </c>
+      <c r="E79" s="94" t="s">
+        <v>142</v>
+      </c>
+      <c r="F79" s="93" t="s">
+        <v>182</v>
+      </c>
+      <c r="G79" s="94" t="s">
+        <v>241</v>
+      </c>
+      <c r="H79" s="93" t="s">
+        <v>250</v>
+      </c>
+      <c r="I79" s="93" t="s">
+        <v>338</v>
+      </c>
+      <c r="J79" s="93" t="s">
+        <v>443</v>
+      </c>
+      <c r="K79" s="94" t="s">
+        <v>330</v>
+      </c>
+      <c r="L79" s="93">
+        <v>6</v>
+      </c>
+      <c r="M79" s="95">
+        <f t="shared" si="63"/>
+        <v>120</v>
+      </c>
+      <c r="N79" s="95">
+        <v>200</v>
+      </c>
+      <c r="O79" s="96" t="s">
+        <v>368</v>
+      </c>
+      <c r="P79" s="95">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q78" s="42">
-        <f t="shared" ref="Q78" si="70">N78*P78</f>
-        <v>0.12</v>
-      </c>
-      <c r="R78" s="42"/>
-    </row>
-    <row r="79" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="1"/>
-      <c r="B79" s="79">
-        <f>ROW(B79) - ROW($B$9)</f>
-        <v>70</v>
-      </c>
-      <c r="C79" s="80" t="s">
-        <v>201</v>
-      </c>
-      <c r="D79" s="81" t="s">
-        <v>74</v>
-      </c>
-      <c r="E79" s="82" t="s">
-        <v>157</v>
-      </c>
-      <c r="F79" s="81" t="s">
-        <v>201</v>
-      </c>
-      <c r="G79" s="82" t="s">
-        <v>361</v>
-      </c>
-      <c r="H79" s="81" t="s">
-        <v>361</v>
-      </c>
-      <c r="I79" s="81" t="s">
-        <v>361</v>
-      </c>
-      <c r="J79" s="81" t="s">
-        <v>361</v>
-      </c>
-      <c r="K79" s="82" t="s">
-        <v>361</v>
-      </c>
-      <c r="L79" s="81">
+      <c r="Q79" s="95">
+        <f t="shared" ref="Q79" si="69">N79*P79</f>
+        <v>0.24</v>
+      </c>
+      <c r="R79" s="106" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="1"/>
+      <c r="B80" s="79">
+        <f>ROW(B80) - ROW($B$9)</f>
+        <v>71</v>
+      </c>
+      <c r="C80" s="80" t="s">
+        <v>185</v>
+      </c>
+      <c r="D80" s="81" t="s">
+        <v>64</v>
+      </c>
+      <c r="E80" s="82" t="s">
+        <v>143</v>
+      </c>
+      <c r="F80" s="81" t="s">
+        <v>185</v>
+      </c>
+      <c r="G80" s="82" t="s">
+        <v>338</v>
+      </c>
+      <c r="H80" s="81" t="s">
+        <v>338</v>
+      </c>
+      <c r="I80" s="81" t="s">
+        <v>338</v>
+      </c>
+      <c r="J80" s="81" t="s">
+        <v>338</v>
+      </c>
+      <c r="K80" s="82" t="s">
+        <v>338</v>
+      </c>
+      <c r="L80" s="81">
         <v>11</v>
       </c>
-      <c r="M79" s="83">
-        <f t="shared" si="64"/>
+      <c r="M80" s="83">
+        <f t="shared" si="63"/>
         <v>220</v>
       </c>
-      <c r="N79" s="83">
-        <f t="shared" ref="N79:N91" si="71">M79+(M79*0.1)</f>
+      <c r="N80" s="83">
+        <f t="shared" ref="N80:N81" si="70">M80+(M80*0.1)</f>
         <v>242</v>
       </c>
-      <c r="O79" s="83"/>
-      <c r="P79" s="83"/>
-      <c r="Q79" s="83">
-        <f t="shared" ref="Q79" si="72">P79*N79</f>
+      <c r="O80" s="83"/>
+      <c r="P80" s="83"/>
+      <c r="Q80" s="83">
+        <f t="shared" ref="Q80" si="71">P80*N80</f>
         <v>0</v>
       </c>
-      <c r="R79" s="87" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="80" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="1"/>
-      <c r="B80" s="53">
-        <f t="shared" si="0"/>
-        <v>71</v>
-      </c>
-      <c r="C80" s="60" t="s">
-        <v>374</v>
-      </c>
-      <c r="D80" s="39" t="s">
-        <v>75</v>
-      </c>
-      <c r="E80" s="40" t="s">
-        <v>158</v>
-      </c>
-      <c r="F80" s="39" t="s">
-        <v>202</v>
-      </c>
-      <c r="G80" s="40"/>
-      <c r="H80" s="39" t="s">
-        <v>295</v>
-      </c>
-      <c r="I80" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="J80" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="K80" s="40" t="s">
-        <v>361</v>
-      </c>
-      <c r="L80" s="39">
-        <v>1</v>
-      </c>
-      <c r="M80" s="42">
-        <f t="shared" si="64"/>
-        <v>20</v>
-      </c>
-      <c r="N80" s="42">
-        <f t="shared" si="71"/>
-        <v>22</v>
-      </c>
-      <c r="O80" s="42"/>
-      <c r="P80" s="42"/>
-      <c r="Q80" s="42">
-        <f t="shared" ref="Q80" si="73">N80*P80</f>
-        <v>0</v>
-      </c>
-      <c r="R80" s="42"/>
-    </row>
-    <row r="81" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R80" s="84" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1"/>
       <c r="B81" s="53">
-        <f>ROW(B81) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="C81" s="61" t="s">
-        <v>375</v>
-      </c>
-      <c r="D81" s="37" t="s">
-        <v>76</v>
-      </c>
-      <c r="E81" s="38" t="s">
-        <v>159</v>
-      </c>
-      <c r="F81" s="37" t="s">
-        <v>355</v>
-      </c>
-      <c r="G81" s="38">
-        <v>750314597</v>
-      </c>
-      <c r="H81" s="37" t="s">
-        <v>296</v>
-      </c>
-      <c r="I81" s="37" t="s">
-        <v>361</v>
-      </c>
-      <c r="J81" s="37" t="s">
-        <v>361</v>
-      </c>
-      <c r="K81" s="38" t="s">
-        <v>361</v>
-      </c>
-      <c r="L81" s="37">
+      <c r="C81" s="60" t="s">
+        <v>351</v>
+      </c>
+      <c r="D81" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="E81" s="40" t="s">
+        <v>144</v>
+      </c>
+      <c r="F81" s="39" t="s">
+        <v>186</v>
+      </c>
+      <c r="G81" s="40"/>
+      <c r="H81" s="39" t="s">
+        <v>275</v>
+      </c>
+      <c r="I81" s="39" t="s">
+        <v>338</v>
+      </c>
+      <c r="J81" s="39" t="s">
+        <v>338</v>
+      </c>
+      <c r="K81" s="40" t="s">
+        <v>338</v>
+      </c>
+      <c r="L81" s="39">
         <v>1</v>
       </c>
-      <c r="M81" s="41">
-        <f t="shared" si="64"/>
+      <c r="M81" s="42">
+        <f t="shared" si="63"/>
         <v>20</v>
       </c>
-      <c r="N81" s="41">
-        <v>21</v>
-      </c>
-      <c r="O81" s="64" t="s">
-        <v>435</v>
-      </c>
-      <c r="P81" s="41">
-        <v>3.81</v>
-      </c>
-      <c r="Q81" s="41">
-        <f t="shared" ref="Q81" si="74">P81*N81</f>
-        <v>80.010000000000005</v>
-      </c>
-      <c r="R81" s="41"/>
-    </row>
-    <row r="82" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N81" s="42">
+        <f t="shared" si="70"/>
+        <v>22</v>
+      </c>
+      <c r="O81" s="42"/>
+      <c r="P81" s="42"/>
+      <c r="Q81" s="42">
+        <f t="shared" ref="Q81" si="72">N81*P81</f>
+        <v>0</v>
+      </c>
+      <c r="R81" s="42"/>
+    </row>
+    <row r="82" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1"/>
       <c r="B82" s="53">
+        <f>ROW(B82) - ROW($B$9)</f>
+        <v>73</v>
+      </c>
+      <c r="C82" s="61" t="s">
+        <v>352</v>
+      </c>
+      <c r="D82" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="E82" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="F82" s="37" t="s">
+        <v>332</v>
+      </c>
+      <c r="G82" s="38">
+        <v>750314597</v>
+      </c>
+      <c r="H82" s="37" t="s">
+        <v>276</v>
+      </c>
+      <c r="I82" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="J82" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="K82" s="38" t="s">
+        <v>338</v>
+      </c>
+      <c r="L82" s="37">
+        <v>1</v>
+      </c>
+      <c r="M82" s="41">
+        <f t="shared" si="63"/>
+        <v>20</v>
+      </c>
+      <c r="N82" s="41">
+        <v>21</v>
+      </c>
+      <c r="O82" s="64" t="s">
+        <v>410</v>
+      </c>
+      <c r="P82" s="41">
+        <v>3.81</v>
+      </c>
+      <c r="Q82" s="41">
+        <f t="shared" ref="Q82" si="73">P82*N82</f>
+        <v>80.010000000000005</v>
+      </c>
+      <c r="R82" s="41"/>
+    </row>
+    <row r="83" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="1"/>
+      <c r="B83" s="53">
         <f t="shared" si="0"/>
-        <v>73</v>
-      </c>
-      <c r="C82" s="60" t="s">
-        <v>376</v>
-      </c>
-      <c r="D82" s="39" t="s">
-        <v>77</v>
-      </c>
-      <c r="E82" s="40" t="s">
-        <v>160</v>
-      </c>
-      <c r="F82" s="39" t="s">
-        <v>355</v>
-      </c>
-      <c r="G82" s="40" t="s">
-        <v>203</v>
-      </c>
-      <c r="H82" s="39" t="s">
-        <v>297</v>
-      </c>
-      <c r="I82" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="J82" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="K82" s="40" t="s">
-        <v>361</v>
-      </c>
-      <c r="L82" s="39">
+        <v>74</v>
+      </c>
+      <c r="C83" s="60" t="s">
+        <v>353</v>
+      </c>
+      <c r="D83" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="E83" s="40" t="s">
+        <v>146</v>
+      </c>
+      <c r="F83" s="39" t="s">
+        <v>332</v>
+      </c>
+      <c r="G83" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="H83" s="39" t="s">
+        <v>277</v>
+      </c>
+      <c r="I83" s="39" t="s">
+        <v>338</v>
+      </c>
+      <c r="J83" s="39" t="s">
+        <v>338</v>
+      </c>
+      <c r="K83" s="40" t="s">
+        <v>338</v>
+      </c>
+      <c r="L83" s="39">
         <v>1</v>
       </c>
-      <c r="M82" s="42">
-        <f t="shared" si="64"/>
+      <c r="M83" s="42">
+        <f t="shared" si="63"/>
         <v>20</v>
       </c>
-      <c r="N82" s="42">
+      <c r="N83" s="42">
         <v>21</v>
       </c>
-      <c r="O82" s="65" t="s">
-        <v>473</v>
-      </c>
-      <c r="P82" s="42">
+      <c r="O83" s="65" t="s">
+        <v>444</v>
+      </c>
+      <c r="P83" s="42">
         <v>2.48</v>
       </c>
-      <c r="Q82" s="42">
-        <f t="shared" ref="Q82" si="75">N82*P82</f>
+      <c r="Q83" s="42">
+        <f t="shared" ref="Q83" si="74">N83*P83</f>
         <v>52.08</v>
       </c>
-      <c r="R82" s="42"/>
-    </row>
-    <row r="83" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="1"/>
-      <c r="B83" s="91">
-        <f>ROW(B83) - ROW($B$9)</f>
-        <v>74</v>
-      </c>
-      <c r="C83" s="92" t="s">
-        <v>376</v>
-      </c>
-      <c r="D83" s="93" t="s">
-        <v>78</v>
-      </c>
-      <c r="E83" s="94" t="s">
-        <v>161</v>
-      </c>
-      <c r="F83" s="93" t="s">
-        <v>204</v>
-      </c>
-      <c r="G83" s="94" t="s">
-        <v>261</v>
-      </c>
-      <c r="H83" s="93" t="s">
-        <v>298</v>
-      </c>
-      <c r="I83" s="93" t="s">
+      <c r="R83" s="42"/>
+    </row>
+    <row r="84" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="1"/>
+      <c r="B84" s="85">
+        <f>ROW(B84) - ROW($B$9)</f>
+        <v>75</v>
+      </c>
+      <c r="C84" s="86" t="s">
+        <v>353</v>
+      </c>
+      <c r="D84" s="87" t="s">
+        <v>68</v>
+      </c>
+      <c r="E84" s="88" t="s">
+        <v>147</v>
+      </c>
+      <c r="F84" s="87" t="s">
+        <v>188</v>
+      </c>
+      <c r="G84" s="88" t="s">
+        <v>242</v>
+      </c>
+      <c r="H84" s="87" t="s">
+        <v>278</v>
+      </c>
+      <c r="I84" s="87" t="s">
+        <v>445</v>
+      </c>
+      <c r="J84" s="87" t="s">
+        <v>446</v>
+      </c>
+      <c r="K84" s="88" t="s">
+        <v>338</v>
+      </c>
+      <c r="L84" s="87">
+        <v>1</v>
+      </c>
+      <c r="M84" s="89">
+        <f t="shared" si="63"/>
+        <v>20</v>
+      </c>
+      <c r="N84" s="89">
+        <v>21</v>
+      </c>
+      <c r="O84" s="90" t="s">
+        <v>368</v>
+      </c>
+      <c r="P84" s="89">
+        <v>1.3939999999999999</v>
+      </c>
+      <c r="Q84" s="89">
+        <f t="shared" ref="Q84" si="75">P84*N84</f>
+        <v>29.273999999999997</v>
+      </c>
+      <c r="R84" s="91" t="s">
         <v>474</v>
       </c>
-      <c r="J83" s="93" t="s">
-        <v>475</v>
-      </c>
-      <c r="K83" s="94" t="s">
-        <v>361</v>
-      </c>
-      <c r="L83" s="93">
+    </row>
+    <row r="85" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="1"/>
+      <c r="B85" s="85">
+        <f t="shared" si="0"/>
+        <v>76</v>
+      </c>
+      <c r="C85" s="92" t="s">
+        <v>353</v>
+      </c>
+      <c r="D85" s="93" t="s">
+        <v>69</v>
+      </c>
+      <c r="E85" s="94" t="s">
+        <v>148</v>
+      </c>
+      <c r="F85" s="93" t="s">
+        <v>189</v>
+      </c>
+      <c r="G85" s="94" t="s">
+        <v>243</v>
+      </c>
+      <c r="H85" s="93" t="s">
+        <v>277</v>
+      </c>
+      <c r="I85" s="93" t="s">
+        <v>448</v>
+      </c>
+      <c r="J85" s="93" t="s">
+        <v>449</v>
+      </c>
+      <c r="K85" s="94" t="s">
+        <v>338</v>
+      </c>
+      <c r="L85" s="93">
         <v>1</v>
       </c>
-      <c r="M83" s="95">
-        <f t="shared" si="64"/>
+      <c r="M85" s="95">
+        <f t="shared" si="63"/>
         <v>20</v>
       </c>
-      <c r="N83" s="95">
+      <c r="N85" s="95">
         <v>21</v>
       </c>
-      <c r="O83" s="96" t="s">
-        <v>391</v>
-      </c>
-      <c r="P83" s="95">
-        <v>1.3939999999999999</v>
-      </c>
-      <c r="Q83" s="95">
-        <f t="shared" ref="Q83" si="76">P83*N83</f>
-        <v>29.273999999999997</v>
-      </c>
-      <c r="R83" s="97" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="84" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="1"/>
-      <c r="B84" s="91">
-        <f t="shared" si="0"/>
-        <v>75</v>
-      </c>
-      <c r="C84" s="98" t="s">
-        <v>376</v>
-      </c>
-      <c r="D84" s="99" t="s">
-        <v>79</v>
-      </c>
-      <c r="E84" s="100" t="s">
-        <v>162</v>
-      </c>
-      <c r="F84" s="99" t="s">
-        <v>205</v>
-      </c>
-      <c r="G84" s="100" t="s">
-        <v>262</v>
-      </c>
-      <c r="H84" s="99" t="s">
-        <v>297</v>
-      </c>
-      <c r="I84" s="99" t="s">
-        <v>477</v>
-      </c>
-      <c r="J84" s="99" t="s">
-        <v>478</v>
-      </c>
-      <c r="K84" s="100" t="s">
-        <v>361</v>
-      </c>
-      <c r="L84" s="99">
-        <v>1</v>
-      </c>
-      <c r="M84" s="101">
-        <f t="shared" si="64"/>
-        <v>20</v>
-      </c>
-      <c r="N84" s="101">
-        <v>21</v>
-      </c>
-      <c r="O84" s="102" t="s">
-        <v>391</v>
-      </c>
-      <c r="P84" s="101">
+      <c r="O85" s="96" t="s">
+        <v>368</v>
+      </c>
+      <c r="P85" s="95">
         <v>0.69430000000000003</v>
       </c>
-      <c r="Q84" s="101">
-        <f t="shared" ref="Q84" si="77">N84*P84</f>
+      <c r="Q85" s="95">
+        <f t="shared" ref="Q85" si="76">N85*P85</f>
         <v>14.580300000000001</v>
       </c>
-      <c r="R84" s="97" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="85" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="1"/>
-      <c r="B85" s="53">
-        <f>ROW(B85) - ROW($B$9)</f>
-        <v>76</v>
-      </c>
-      <c r="C85" s="61" t="s">
-        <v>376</v>
-      </c>
-      <c r="D85" s="37" t="s">
-        <v>80</v>
-      </c>
-      <c r="E85" s="38" t="s">
-        <v>163</v>
-      </c>
-      <c r="F85" s="37" t="s">
-        <v>357</v>
-      </c>
-      <c r="G85" s="38" t="s">
-        <v>206</v>
-      </c>
-      <c r="H85" s="37" t="s">
-        <v>297</v>
-      </c>
-      <c r="I85" s="37" t="s">
-        <v>361</v>
-      </c>
-      <c r="J85" s="37" t="s">
-        <v>361</v>
-      </c>
-      <c r="K85" s="38" t="s">
-        <v>361</v>
-      </c>
-      <c r="L85" s="37">
-        <v>1</v>
-      </c>
-      <c r="M85" s="41">
-        <f t="shared" si="64"/>
-        <v>20</v>
-      </c>
-      <c r="N85" s="41">
-        <v>21</v>
-      </c>
-      <c r="O85" s="64" t="s">
-        <v>473</v>
-      </c>
-      <c r="P85" s="41">
-        <v>3.637</v>
-      </c>
-      <c r="Q85" s="41">
-        <f t="shared" ref="Q85" si="78">P85*N85</f>
-        <v>76.376999999999995</v>
-      </c>
-      <c r="R85" s="41"/>
-    </row>
-    <row r="86" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R85" s="91" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="1"/>
       <c r="B86" s="53">
+        <f>ROW(B86) - ROW($B$9)</f>
+        <v>77</v>
+      </c>
+      <c r="C86" s="61" t="s">
+        <v>353</v>
+      </c>
+      <c r="D86" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="E86" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="F86" s="37" t="s">
+        <v>334</v>
+      </c>
+      <c r="G86" s="38" t="s">
+        <v>190</v>
+      </c>
+      <c r="H86" s="37" t="s">
+        <v>277</v>
+      </c>
+      <c r="I86" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="J86" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="K86" s="38" t="s">
+        <v>338</v>
+      </c>
+      <c r="L86" s="37">
+        <v>1</v>
+      </c>
+      <c r="M86" s="41">
+        <f t="shared" si="63"/>
+        <v>20</v>
+      </c>
+      <c r="N86" s="41">
+        <v>21</v>
+      </c>
+      <c r="O86" s="64" t="s">
+        <v>444</v>
+      </c>
+      <c r="P86" s="41">
+        <v>3.637</v>
+      </c>
+      <c r="Q86" s="41">
+        <f t="shared" ref="Q86" si="77">P86*N86</f>
+        <v>76.376999999999995</v>
+      </c>
+      <c r="R86" s="41"/>
+    </row>
+    <row r="87" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="1"/>
+      <c r="B87" s="53">
         <f t="shared" si="0"/>
-        <v>77</v>
-      </c>
-      <c r="C86" s="60" t="s">
-        <v>376</v>
-      </c>
-      <c r="D86" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="C87" s="60" t="s">
+        <v>353</v>
+      </c>
+      <c r="D87" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="E87" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="F87" s="39" t="s">
+        <v>191</v>
+      </c>
+      <c r="G87" s="40" t="s">
+        <v>244</v>
+      </c>
+      <c r="H87" s="39" t="s">
+        <v>277</v>
+      </c>
+      <c r="I87" s="39" t="s">
+        <v>338</v>
+      </c>
+      <c r="J87" s="39" t="s">
+        <v>450</v>
+      </c>
+      <c r="K87" s="40" t="s">
+        <v>338</v>
+      </c>
+      <c r="L87" s="39">
+        <v>1</v>
+      </c>
+      <c r="M87" s="42">
+        <f t="shared" si="63"/>
+        <v>20</v>
+      </c>
+      <c r="N87" s="42">
+        <v>21</v>
+      </c>
+      <c r="O87" s="65" t="s">
+        <v>368</v>
+      </c>
+      <c r="P87" s="42">
+        <v>0.43280000000000002</v>
+      </c>
+      <c r="Q87" s="42">
+        <f t="shared" ref="Q87" si="78">N87*P87</f>
+        <v>9.0888000000000009</v>
+      </c>
+      <c r="R87" s="42"/>
+    </row>
+    <row r="88" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="1"/>
+      <c r="B88" s="126">
+        <f>ROW(B88) - ROW($B$9)</f>
+        <v>79</v>
+      </c>
+      <c r="C88" s="127" t="s">
+        <v>353</v>
+      </c>
+      <c r="D88" s="128" t="s">
+        <v>72</v>
+      </c>
+      <c r="E88" s="129" t="s">
+        <v>151</v>
+      </c>
+      <c r="F88" s="128" t="s">
+        <v>192</v>
+      </c>
+      <c r="G88" s="129" t="s">
+        <v>245</v>
+      </c>
+      <c r="H88" s="128" t="s">
+        <v>279</v>
+      </c>
+      <c r="I88" s="128" t="s">
+        <v>338</v>
+      </c>
+      <c r="J88" s="128" t="s">
+        <v>451</v>
+      </c>
+      <c r="K88" s="129" t="s">
+        <v>338</v>
+      </c>
+      <c r="L88" s="128">
+        <v>1</v>
+      </c>
+      <c r="M88" s="130">
+        <f t="shared" si="63"/>
+        <v>20</v>
+      </c>
+      <c r="N88" s="130">
+        <v>21</v>
+      </c>
+      <c r="O88" s="131" t="s">
+        <v>368</v>
+      </c>
+      <c r="P88" s="130">
+        <v>7.4638</v>
+      </c>
+      <c r="Q88" s="130">
+        <f t="shared" ref="Q88" si="79">P88*N88</f>
+        <v>156.7398</v>
+      </c>
+      <c r="R88" s="130" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="1"/>
+      <c r="B89" s="53">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="C89" s="60" t="s">
+        <v>353</v>
+      </c>
+      <c r="D89" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="E89" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="F89" s="39" t="s">
+        <v>193</v>
+      </c>
+      <c r="G89" s="40" t="s">
+        <v>246</v>
+      </c>
+      <c r="H89" s="39" t="s">
+        <v>280</v>
+      </c>
+      <c r="I89" s="39" t="s">
+        <v>338</v>
+      </c>
+      <c r="J89" s="39" t="s">
+        <v>338</v>
+      </c>
+      <c r="K89" s="58" t="s">
+        <v>339</v>
+      </c>
+      <c r="L89" s="39">
+        <v>1</v>
+      </c>
+      <c r="M89" s="42">
+        <f t="shared" si="63"/>
+        <v>20</v>
+      </c>
+      <c r="N89" s="42">
+        <v>21</v>
+      </c>
+      <c r="O89" s="65" t="s">
+        <v>444</v>
+      </c>
+      <c r="P89" s="42">
+        <v>2.6459999999999999</v>
+      </c>
+      <c r="Q89" s="42">
+        <f t="shared" ref="Q89" si="80">N89*P89</f>
+        <v>55.565999999999995</v>
+      </c>
+      <c r="R89" s="42"/>
+    </row>
+    <row r="90" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="1"/>
+      <c r="B90" s="85">
+        <f>ROW(B90) - ROW($B$9)</f>
         <v>81</v>
       </c>
-      <c r="E86" s="40" t="s">
-        <v>164</v>
-      </c>
-      <c r="F86" s="39" t="s">
-        <v>207</v>
-      </c>
-      <c r="G86" s="40" t="s">
-        <v>263</v>
-      </c>
-      <c r="H86" s="39" t="s">
-        <v>297</v>
-      </c>
-      <c r="I86" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="J86" s="39" t="s">
-        <v>479</v>
-      </c>
-      <c r="K86" s="40" t="s">
-        <v>361</v>
-      </c>
-      <c r="L86" s="39">
+      <c r="C90" s="86" t="s">
+        <v>353</v>
+      </c>
+      <c r="D90" s="87" t="s">
+        <v>74</v>
+      </c>
+      <c r="E90" s="88" t="s">
+        <v>153</v>
+      </c>
+      <c r="F90" s="87" t="s">
+        <v>335</v>
+      </c>
+      <c r="G90" s="88" t="s">
+        <v>194</v>
+      </c>
+      <c r="H90" s="87" t="s">
+        <v>277</v>
+      </c>
+      <c r="I90" s="87" t="s">
+        <v>452</v>
+      </c>
+      <c r="J90" s="87" t="s">
+        <v>453</v>
+      </c>
+      <c r="K90" s="88" t="s">
+        <v>338</v>
+      </c>
+      <c r="L90" s="109">
+        <v>2</v>
+      </c>
+      <c r="M90" s="89">
+        <f t="shared" si="63"/>
+        <v>40</v>
+      </c>
+      <c r="N90" s="89">
+        <v>42</v>
+      </c>
+      <c r="O90" s="90" t="s">
+        <v>368</v>
+      </c>
+      <c r="P90" s="89">
+        <v>2.2974000000000001</v>
+      </c>
+      <c r="Q90" s="89">
+        <f t="shared" ref="Q90" si="81">P90*N90</f>
+        <v>96.490800000000007</v>
+      </c>
+      <c r="R90" s="91" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="1"/>
+      <c r="B91" s="85">
+        <f t="shared" si="0"/>
+        <v>82</v>
+      </c>
+      <c r="C91" s="92" t="s">
+        <v>353</v>
+      </c>
+      <c r="D91" s="93" t="s">
+        <v>75</v>
+      </c>
+      <c r="E91" s="94" t="s">
+        <v>154</v>
+      </c>
+      <c r="F91" s="93" t="s">
+        <v>336</v>
+      </c>
+      <c r="G91" s="94" t="s">
+        <v>195</v>
+      </c>
+      <c r="H91" s="93" t="s">
+        <v>280</v>
+      </c>
+      <c r="I91" s="93" t="s">
+        <v>455</v>
+      </c>
+      <c r="J91" s="93" t="s">
+        <v>338</v>
+      </c>
+      <c r="K91" s="94" t="s">
+        <v>338</v>
+      </c>
+      <c r="L91" s="93">
         <v>1</v>
       </c>
-      <c r="M86" s="42">
-        <f t="shared" si="64"/>
+      <c r="M91" s="95">
+        <f t="shared" si="63"/>
         <v>20</v>
       </c>
-      <c r="N86" s="42">
+      <c r="N91" s="95">
         <v>21</v>
       </c>
-      <c r="O86" s="65" t="s">
-        <v>391</v>
-      </c>
-      <c r="P86" s="42">
-        <v>0.43280000000000002</v>
-      </c>
-      <c r="Q86" s="42">
-        <f t="shared" ref="Q86" si="79">N86*P86</f>
-        <v>9.0888000000000009</v>
-      </c>
-      <c r="R86" s="42"/>
-    </row>
-    <row r="87" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="1"/>
-      <c r="B87" s="91">
-        <f>ROW(B87) - ROW($B$9)</f>
-        <v>78</v>
-      </c>
-      <c r="C87" s="92" t="s">
-        <v>376</v>
-      </c>
-      <c r="D87" s="93" t="s">
-        <v>82</v>
-      </c>
-      <c r="E87" s="94" t="s">
-        <v>165</v>
-      </c>
-      <c r="F87" s="93" t="s">
-        <v>208</v>
-      </c>
-      <c r="G87" s="94" t="s">
-        <v>264</v>
-      </c>
-      <c r="H87" s="93" t="s">
-        <v>299</v>
-      </c>
-      <c r="I87" s="93" t="s">
-        <v>361</v>
-      </c>
-      <c r="J87" s="93" t="s">
-        <v>480</v>
-      </c>
-      <c r="K87" s="94" t="s">
-        <v>361</v>
-      </c>
-      <c r="L87" s="93">
+      <c r="O91" s="96" t="s">
+        <v>456</v>
+      </c>
+      <c r="P91" s="95">
+        <v>3.532</v>
+      </c>
+      <c r="Q91" s="95">
+        <f t="shared" ref="Q91" si="82">N91*P91</f>
+        <v>74.171999999999997</v>
+      </c>
+      <c r="R91" s="91" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="1"/>
+      <c r="B92" s="53">
+        <f>ROW(B92) - ROW($B$9)</f>
+        <v>83</v>
+      </c>
+      <c r="C92" s="61" t="s">
+        <v>353</v>
+      </c>
+      <c r="D92" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="E92" s="38" t="s">
+        <v>155</v>
+      </c>
+      <c r="F92" s="37" t="s">
+        <v>337</v>
+      </c>
+      <c r="G92" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="H92" s="37" t="s">
+        <v>277</v>
+      </c>
+      <c r="I92" s="63" t="s">
+        <v>338</v>
+      </c>
+      <c r="J92" s="63" t="s">
+        <v>457</v>
+      </c>
+      <c r="K92" s="38" t="s">
+        <v>338</v>
+      </c>
+      <c r="L92" s="37">
         <v>1</v>
       </c>
-      <c r="M87" s="95">
-        <f t="shared" si="64"/>
+      <c r="M92" s="41">
+        <f t="shared" si="63"/>
         <v>20</v>
       </c>
-      <c r="N87" s="95">
+      <c r="N92" s="41">
         <v>21</v>
       </c>
-      <c r="O87" s="96" t="s">
-        <v>391</v>
-      </c>
-      <c r="P87" s="95">
-        <v>7.4638</v>
-      </c>
-      <c r="Q87" s="95">
-        <f t="shared" ref="Q87" si="80">P87*N87</f>
-        <v>156.7398</v>
-      </c>
-      <c r="R87" s="95" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="88" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="1"/>
-      <c r="B88" s="53">
-        <f t="shared" si="0"/>
-        <v>79</v>
-      </c>
-      <c r="C88" s="60" t="s">
-        <v>376</v>
-      </c>
-      <c r="D88" s="39" t="s">
-        <v>83</v>
-      </c>
-      <c r="E88" s="40" t="s">
-        <v>166</v>
-      </c>
-      <c r="F88" s="39" t="s">
-        <v>209</v>
-      </c>
-      <c r="G88" s="40" t="s">
-        <v>265</v>
-      </c>
-      <c r="H88" s="39" t="s">
-        <v>300</v>
-      </c>
-      <c r="I88" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="J88" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="K88" s="58" t="s">
-        <v>362</v>
-      </c>
-      <c r="L88" s="39">
-        <v>1</v>
-      </c>
-      <c r="M88" s="42">
-        <f t="shared" si="64"/>
-        <v>20</v>
-      </c>
-      <c r="N88" s="42">
-        <v>21</v>
-      </c>
-      <c r="O88" s="65" t="s">
-        <v>473</v>
-      </c>
-      <c r="P88" s="42">
-        <v>2.6459999999999999</v>
-      </c>
-      <c r="Q88" s="42">
-        <f t="shared" ref="Q88" si="81">N88*P88</f>
-        <v>55.565999999999995</v>
-      </c>
-      <c r="R88" s="42"/>
-    </row>
-    <row r="89" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="1"/>
-      <c r="B89" s="91">
-        <f>ROW(B89) - ROW($B$9)</f>
-        <v>80</v>
-      </c>
-      <c r="C89" s="92" t="s">
-        <v>376</v>
-      </c>
-      <c r="D89" s="93" t="s">
-        <v>84</v>
-      </c>
-      <c r="E89" s="94" t="s">
-        <v>167</v>
-      </c>
-      <c r="F89" s="93" t="s">
-        <v>358</v>
-      </c>
-      <c r="G89" s="94" t="s">
-        <v>210</v>
-      </c>
-      <c r="H89" s="93" t="s">
-        <v>297</v>
-      </c>
-      <c r="I89" s="93" t="s">
-        <v>482</v>
-      </c>
-      <c r="J89" s="93" t="s">
-        <v>483</v>
-      </c>
-      <c r="K89" s="94" t="s">
-        <v>361</v>
-      </c>
-      <c r="L89" s="103">
-        <v>2</v>
-      </c>
-      <c r="M89" s="95">
-        <f t="shared" si="64"/>
-        <v>40</v>
-      </c>
-      <c r="N89" s="95">
-        <v>42</v>
-      </c>
-      <c r="O89" s="96" t="s">
-        <v>391</v>
-      </c>
-      <c r="P89" s="95">
-        <v>2.2974000000000001</v>
-      </c>
-      <c r="Q89" s="95">
-        <f t="shared" ref="Q89" si="82">P89*N89</f>
-        <v>96.490800000000007</v>
-      </c>
-      <c r="R89" s="97" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="90" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="1"/>
-      <c r="B90" s="91">
-        <f t="shared" si="0"/>
-        <v>81</v>
-      </c>
-      <c r="C90" s="98" t="s">
-        <v>376</v>
-      </c>
-      <c r="D90" s="99" t="s">
-        <v>85</v>
-      </c>
-      <c r="E90" s="100" t="s">
-        <v>168</v>
-      </c>
-      <c r="F90" s="99" t="s">
-        <v>359</v>
-      </c>
-      <c r="G90" s="100" t="s">
-        <v>211</v>
-      </c>
-      <c r="H90" s="99" t="s">
-        <v>300</v>
-      </c>
-      <c r="I90" s="99" t="s">
-        <v>485</v>
-      </c>
-      <c r="J90" s="99" t="s">
-        <v>361</v>
-      </c>
-      <c r="K90" s="100" t="s">
-        <v>361</v>
-      </c>
-      <c r="L90" s="99">
-        <v>1</v>
-      </c>
-      <c r="M90" s="101">
-        <f t="shared" si="64"/>
-        <v>20</v>
-      </c>
-      <c r="N90" s="101">
-        <v>21</v>
-      </c>
-      <c r="O90" s="102" t="s">
-        <v>486</v>
-      </c>
-      <c r="P90" s="101">
-        <v>3.532</v>
-      </c>
-      <c r="Q90" s="101">
-        <f t="shared" ref="Q90" si="83">N90*P90</f>
-        <v>74.171999999999997</v>
-      </c>
-      <c r="R90" s="97" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="91" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="1"/>
-      <c r="B91" s="53">
-        <f>ROW(B91) - ROW($B$9)</f>
-        <v>82</v>
-      </c>
-      <c r="C91" s="61" t="s">
-        <v>376</v>
-      </c>
-      <c r="D91" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="E91" s="38" t="s">
-        <v>169</v>
-      </c>
-      <c r="F91" s="37" t="s">
-        <v>360</v>
-      </c>
-      <c r="G91" s="38" t="s">
-        <v>212</v>
-      </c>
-      <c r="H91" s="37" t="s">
-        <v>297</v>
-      </c>
-      <c r="I91" s="63" t="s">
-        <v>361</v>
-      </c>
-      <c r="J91" s="63" t="s">
-        <v>487</v>
-      </c>
-      <c r="K91" s="38" t="s">
-        <v>361</v>
-      </c>
-      <c r="L91" s="37">
-        <v>1</v>
-      </c>
-      <c r="M91" s="41">
-        <f t="shared" si="64"/>
-        <v>20</v>
-      </c>
-      <c r="N91" s="41">
-        <v>21</v>
-      </c>
-      <c r="O91" s="64" t="s">
-        <v>391</v>
-      </c>
-      <c r="P91" s="41">
+      <c r="O92" s="64" t="s">
+        <v>368</v>
+      </c>
+      <c r="P92" s="41">
         <v>0.39140000000000003</v>
       </c>
-      <c r="Q91" s="41">
-        <f t="shared" ref="Q91" si="84">P91*N91</f>
+      <c r="Q92" s="41">
+        <f t="shared" ref="Q92" si="83">P92*N92</f>
         <v>8.2194000000000003</v>
       </c>
-      <c r="R91" s="41"/>
-    </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A92" s="1"/>
-      <c r="B92" s="32"/>
-      <c r="C92" s="51"/>
-      <c r="D92" s="33" t="s">
+      <c r="R92" s="41"/>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A93" s="1"/>
+      <c r="B93" s="32"/>
+      <c r="C93" s="51"/>
+      <c r="D93" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="E92" s="34"/>
-      <c r="F92" s="35"/>
-      <c r="G92" s="36"/>
-      <c r="H92" s="35"/>
-      <c r="I92" s="35"/>
-      <c r="J92" s="35"/>
-      <c r="K92" s="36"/>
-      <c r="L92" s="36"/>
-      <c r="M92" s="36"/>
-      <c r="N92" s="36"/>
-      <c r="O92" s="106" t="s">
-        <v>488</v>
-      </c>
-      <c r="P92" s="104">
-        <f>SUM(P10:P91)</f>
-        <v>37.098149999999997</v>
-      </c>
-      <c r="Q92" s="104">
-        <f>SUM(Q10:Q91)</f>
-        <v>976.02435000000014</v>
-      </c>
-      <c r="R92" s="44"/>
-    </row>
-    <row r="93" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="1"/>
-      <c r="B93" s="24"/>
-      <c r="C93" s="52"/>
-      <c r="D93" s="8" t="s">
+      <c r="E93" s="34"/>
+      <c r="F93" s="35"/>
+      <c r="G93" s="36"/>
+      <c r="H93" s="35"/>
+      <c r="I93" s="35"/>
+      <c r="J93" s="35"/>
+      <c r="K93" s="36"/>
+      <c r="L93" s="36"/>
+      <c r="M93" s="36"/>
+      <c r="N93" s="36"/>
+      <c r="O93" s="100" t="s">
+        <v>458</v>
+      </c>
+      <c r="P93" s="98"/>
+      <c r="Q93" s="98">
+        <f>SUM(Q10:Q92)</f>
+        <v>963.24749999999995</v>
+      </c>
+      <c r="R93" s="44"/>
+    </row>
+    <row r="94" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="1"/>
+      <c r="B94" s="24"/>
+      <c r="C94" s="52"/>
+      <c r="D94" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E93" s="9"/>
-      <c r="F93" s="9"/>
-      <c r="G93" s="9"/>
-      <c r="H93" s="9"/>
-      <c r="I93" s="9"/>
-      <c r="J93" s="9"/>
-      <c r="K93" s="9"/>
-      <c r="L93" s="9"/>
-      <c r="M93" s="9"/>
-      <c r="N93" s="9"/>
-      <c r="O93" s="107" t="s">
-        <v>489</v>
-      </c>
-      <c r="P93" s="105"/>
-      <c r="Q93" s="105">
-        <f>Q92/20</f>
-        <v>48.801217500000007</v>
-      </c>
-      <c r="R93" s="45"/>
+      <c r="E94" s="9"/>
+      <c r="F94" s="9"/>
+      <c r="G94" s="9"/>
+      <c r="H94" s="9"/>
+      <c r="I94" s="9"/>
+      <c r="J94" s="9"/>
+      <c r="K94" s="9"/>
+      <c r="L94" s="9"/>
+      <c r="M94" s="9"/>
+      <c r="N94" s="9"/>
+      <c r="O94" s="101" t="s">
+        <v>459</v>
+      </c>
+      <c r="P94" s="99"/>
+      <c r="Q94" s="99">
+        <f>Q93/20</f>
+        <v>48.162374999999997</v>
+      </c>
+      <c r="R94" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7540,38 +8178,39 @@
     <hyperlink ref="O58" r:id="rId48"/>
     <hyperlink ref="O59" r:id="rId49"/>
     <hyperlink ref="O60" r:id="rId50"/>
-    <hyperlink ref="O61" r:id="rId51"/>
-    <hyperlink ref="O62" r:id="rId52"/>
-    <hyperlink ref="O63" r:id="rId53"/>
-    <hyperlink ref="O64" r:id="rId54"/>
-    <hyperlink ref="O65" r:id="rId55"/>
-    <hyperlink ref="O66" r:id="rId56"/>
-    <hyperlink ref="O67" r:id="rId57"/>
-    <hyperlink ref="O68" r:id="rId58"/>
-    <hyperlink ref="O69" r:id="rId59"/>
-    <hyperlink ref="O70" r:id="rId60"/>
-    <hyperlink ref="O71" r:id="rId61"/>
-    <hyperlink ref="O72" r:id="rId62"/>
-    <hyperlink ref="O73" r:id="rId63"/>
-    <hyperlink ref="O74" r:id="rId64"/>
-    <hyperlink ref="O75" r:id="rId65"/>
-    <hyperlink ref="O76" r:id="rId66"/>
-    <hyperlink ref="O77" r:id="rId67"/>
-    <hyperlink ref="O78" r:id="rId68"/>
-    <hyperlink ref="O81" r:id="rId69"/>
-    <hyperlink ref="O82" r:id="rId70"/>
-    <hyperlink ref="O83" r:id="rId71"/>
-    <hyperlink ref="O84" r:id="rId72"/>
-    <hyperlink ref="O85" r:id="rId73"/>
-    <hyperlink ref="O86" r:id="rId74"/>
-    <hyperlink ref="O87" r:id="rId75"/>
-    <hyperlink ref="O88" r:id="rId76"/>
-    <hyperlink ref="O89" r:id="rId77"/>
-    <hyperlink ref="O90" r:id="rId78"/>
-    <hyperlink ref="O91" r:id="rId79"/>
+    <hyperlink ref="O62" r:id="rId51"/>
+    <hyperlink ref="O63" r:id="rId52"/>
+    <hyperlink ref="O64" r:id="rId53"/>
+    <hyperlink ref="O65" r:id="rId54"/>
+    <hyperlink ref="O66" r:id="rId55"/>
+    <hyperlink ref="O67" r:id="rId56"/>
+    <hyperlink ref="O68" r:id="rId57"/>
+    <hyperlink ref="O69" r:id="rId58"/>
+    <hyperlink ref="O70" r:id="rId59"/>
+    <hyperlink ref="O71" r:id="rId60"/>
+    <hyperlink ref="O72" r:id="rId61"/>
+    <hyperlink ref="O73" r:id="rId62"/>
+    <hyperlink ref="O74" r:id="rId63"/>
+    <hyperlink ref="O75" r:id="rId64"/>
+    <hyperlink ref="O76" r:id="rId65"/>
+    <hyperlink ref="O77" r:id="rId66"/>
+    <hyperlink ref="O78" r:id="rId67"/>
+    <hyperlink ref="O79" r:id="rId68"/>
+    <hyperlink ref="O82" r:id="rId69"/>
+    <hyperlink ref="O83" r:id="rId70"/>
+    <hyperlink ref="O84" r:id="rId71"/>
+    <hyperlink ref="O85" r:id="rId72"/>
+    <hyperlink ref="O86" r:id="rId73"/>
+    <hyperlink ref="O87" r:id="rId74"/>
+    <hyperlink ref="O88" r:id="rId75"/>
+    <hyperlink ref="O89" r:id="rId76"/>
+    <hyperlink ref="O90" r:id="rId77"/>
+    <hyperlink ref="O91" r:id="rId78"/>
+    <hyperlink ref="O92" r:id="rId79"/>
+    <hyperlink ref="O61" r:id="rId80"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId80"/>
-  <drawing r:id="rId81"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId81"/>
+  <drawing r:id="rId82"/>
 </worksheet>
 </file>
--- a/Deliverables/SM_Top Board/_BOM/eSpark BOM (20 Boards).xlsx
+++ b/Deliverables/SM_Top Board/_BOM/eSpark BOM (20 Boards).xlsx
@@ -1653,22 +1653,6 @@
     <t>Quantity changed from 3/board to 1/board due to removal of two capacitors after changes in circuitry of U3</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">C8, C10, C11, C12, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C41</t>
-    </r>
-  </si>
-  <si>
     <t>GRM188R6YA106MA73D</t>
   </si>
   <si>
@@ -1698,9 +1682,6 @@
   </si>
   <si>
     <t>C194427</t>
-  </si>
-  <si>
-    <t>Quantity changed from 4/board to 5/board due to addition of 1 x 10uF capacitor from U3</t>
   </si>
   <si>
     <r>
@@ -1942,6 +1923,25 @@
   </si>
   <si>
     <t>Will be provided by Robotshop for prototyping</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">C8, C10, C11, C12, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C41, CF3</t>
+    </r>
+  </si>
+  <si>
+    <t>Quantity changed from 4/board to 6/board due to addition of 2 x 10uF capacitor from U3</t>
   </si>
 </sst>
 </file>
@@ -2471,7 +2471,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -2740,9 +2740,6 @@
     <xf numFmtId="0" fontId="19" fillId="8" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2752,6 +2749,63 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2761,109 +2815,73 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3239,14 +3257,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
     </row>
     <row r="2" spans="1:18" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
@@ -3294,7 +3312,7 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="103"/>
+      <c r="R3" s="121"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
@@ -3318,7 +3336,7 @@
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="Q4" s="62"/>
-      <c r="R4" s="104"/>
+      <c r="R4" s="122"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
@@ -3340,7 +3358,7 @@
       <c r="O5" s="62"/>
       <c r="P5" s="62"/>
       <c r="Q5" s="62"/>
-      <c r="R5" s="104"/>
+      <c r="R5" s="122"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
@@ -3360,7 +3378,7 @@
       <c r="O6" s="62"/>
       <c r="P6" s="62"/>
       <c r="Q6" s="62"/>
-      <c r="R6" s="104"/>
+      <c r="R6" s="122"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
@@ -3380,7 +3398,7 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="104"/>
+      <c r="R7" s="122"/>
     </row>
     <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
@@ -3400,7 +3418,7 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="104"/>
+      <c r="R8" s="122"/>
     </row>
     <row r="9" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
@@ -3568,287 +3586,287 @@
     </row>
     <row r="12" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
-      <c r="B12" s="85">
+      <c r="B12" s="53">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="86" t="s">
+      <c r="C12" s="61" t="s">
         <v>341</v>
       </c>
-      <c r="D12" s="87" t="s">
+      <c r="D12" s="37" t="s">
         <v>478</v>
       </c>
-      <c r="E12" s="88" t="s">
+      <c r="E12" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="F12" s="87" t="s">
+      <c r="F12" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="G12" s="88" t="s">
+      <c r="G12" s="38" t="s">
         <v>199</v>
       </c>
-      <c r="H12" s="87" t="s">
+      <c r="H12" s="37" t="s">
         <v>250</v>
       </c>
-      <c r="I12" s="87" t="s">
-        <v>338</v>
-      </c>
-      <c r="J12" s="87" t="s">
+      <c r="I12" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="J12" s="37" t="s">
         <v>370</v>
       </c>
-      <c r="K12" s="88" t="s">
+      <c r="K12" s="38" t="s">
         <v>284</v>
       </c>
-      <c r="L12" s="109">
+      <c r="L12" s="123">
         <v>2</v>
       </c>
-      <c r="M12" s="89">
+      <c r="M12" s="41">
         <f t="shared" ref="M12:M73" si="1">L12*20</f>
         <v>40</v>
       </c>
-      <c r="N12" s="89">
+      <c r="N12" s="41">
         <v>100</v>
       </c>
-      <c r="O12" s="90" t="s">
+      <c r="O12" s="64" t="s">
         <v>368</v>
       </c>
-      <c r="P12" s="89">
+      <c r="P12" s="41">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q12" s="89">
+      <c r="Q12" s="41">
         <f t="shared" ref="Q12" si="2">P12*N12</f>
         <v>0.13</v>
       </c>
-      <c r="R12" s="106" t="s">
+      <c r="R12" s="124" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
-      <c r="B13" s="85">
+      <c r="B13" s="53">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="92" t="s">
+      <c r="C13" s="60" t="s">
         <v>341</v>
       </c>
-      <c r="D13" s="93" t="s">
+      <c r="D13" s="39" t="s">
         <v>477</v>
       </c>
-      <c r="E13" s="94" t="s">
+      <c r="E13" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="F13" s="93" t="s">
+      <c r="F13" s="39" t="s">
         <v>159</v>
       </c>
-      <c r="G13" s="94" t="s">
+      <c r="G13" s="40" t="s">
         <v>200</v>
       </c>
-      <c r="H13" s="93" t="s">
+      <c r="H13" s="39" t="s">
         <v>251</v>
       </c>
-      <c r="I13" s="93" t="s">
-        <v>338</v>
-      </c>
-      <c r="J13" s="93" t="s">
+      <c r="I13" s="39" t="s">
+        <v>338</v>
+      </c>
+      <c r="J13" s="39" t="s">
         <v>371</v>
       </c>
-      <c r="K13" s="94" t="s">
+      <c r="K13" s="40" t="s">
         <v>285</v>
       </c>
-      <c r="L13" s="108">
+      <c r="L13" s="127">
         <v>1</v>
       </c>
-      <c r="M13" s="95">
+      <c r="M13" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N13" s="107">
+      <c r="N13" s="128">
         <v>40</v>
       </c>
-      <c r="O13" s="96" t="s">
+      <c r="O13" s="65" t="s">
         <v>368</v>
       </c>
-      <c r="P13" s="95">
+      <c r="P13" s="42">
         <v>3.5900000000000001E-2</v>
       </c>
-      <c r="Q13" s="95">
+      <c r="Q13" s="42">
         <f t="shared" ref="Q13" si="3">N13*P13</f>
         <v>1.4359999999999999</v>
       </c>
-      <c r="R13" s="106" t="s">
+      <c r="R13" s="129" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1"/>
-      <c r="B14" s="85">
+      <c r="B14" s="53">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="86" t="s">
+      <c r="C14" s="61" t="s">
         <v>341</v>
       </c>
-      <c r="D14" s="87" t="s">
+      <c r="D14" s="37" t="s">
         <v>475</v>
       </c>
-      <c r="E14" s="88" t="s">
+      <c r="E14" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="F14" s="87" t="s">
+      <c r="F14" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="G14" s="88" t="s">
+      <c r="G14" s="38" t="s">
         <v>201</v>
       </c>
-      <c r="H14" s="87" t="s">
+      <c r="H14" s="37" t="s">
         <v>252</v>
       </c>
-      <c r="I14" s="87" t="s">
-        <v>338</v>
-      </c>
-      <c r="J14" s="87" t="s">
+      <c r="I14" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="J14" s="37" t="s">
         <v>372</v>
       </c>
-      <c r="K14" s="88" t="s">
+      <c r="K14" s="38" t="s">
         <v>286</v>
       </c>
-      <c r="L14" s="87">
+      <c r="L14" s="37">
         <v>8</v>
       </c>
-      <c r="M14" s="89">
+      <c r="M14" s="41">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="N14" s="89">
+      <c r="N14" s="41">
         <v>200</v>
       </c>
-      <c r="O14" s="90" t="s">
+      <c r="O14" s="64" t="s">
         <v>368</v>
       </c>
-      <c r="P14" s="89">
+      <c r="P14" s="41">
         <v>4.0899999999999999E-2</v>
       </c>
-      <c r="Q14" s="89">
+      <c r="Q14" s="41">
         <f>P14*N14</f>
         <v>8.18</v>
       </c>
-      <c r="R14" s="106" t="s">
+      <c r="R14" s="124" t="s">
         <v>476</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
-      <c r="B15" s="85">
+      <c r="B15" s="53">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="92" t="s">
+      <c r="C15" s="60" t="s">
         <v>341</v>
       </c>
-      <c r="D15" s="93" t="s">
+      <c r="D15" s="39" t="s">
         <v>471</v>
       </c>
-      <c r="E15" s="94" t="s">
+      <c r="E15" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="F15" s="93" t="s">
+      <c r="F15" s="39" t="s">
         <v>158</v>
       </c>
-      <c r="G15" s="94" t="s">
+      <c r="G15" s="40" t="s">
         <v>202</v>
       </c>
-      <c r="H15" s="93" t="s">
+      <c r="H15" s="39" t="s">
         <v>250</v>
       </c>
-      <c r="I15" s="93" t="s">
-        <v>338</v>
-      </c>
-      <c r="J15" s="93" t="s">
+      <c r="I15" s="39" t="s">
+        <v>338</v>
+      </c>
+      <c r="J15" s="39" t="s">
         <v>373</v>
       </c>
-      <c r="K15" s="94" t="s">
+      <c r="K15" s="40" t="s">
         <v>287</v>
       </c>
-      <c r="L15" s="108">
+      <c r="L15" s="127">
         <v>3</v>
       </c>
-      <c r="M15" s="95">
+      <c r="M15" s="42">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="N15" s="107">
+      <c r="N15" s="128">
         <v>100</v>
       </c>
-      <c r="O15" s="96" t="s">
+      <c r="O15" s="65" t="s">
         <v>368</v>
       </c>
-      <c r="P15" s="95">
+      <c r="P15" s="42">
         <v>5.8999999999999999E-3</v>
       </c>
-      <c r="Q15" s="95">
+      <c r="Q15" s="42">
         <f t="shared" ref="Q15" si="4">N15*P15</f>
         <v>0.59</v>
       </c>
-      <c r="R15" s="106" t="s">
+      <c r="R15" s="129" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
-      <c r="B16" s="85">
+      <c r="B16" s="53">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="86" t="s">
+      <c r="C16" s="61" t="s">
         <v>341</v>
       </c>
-      <c r="D16" s="87" t="s">
+      <c r="D16" s="37" t="s">
+        <v>511</v>
+      </c>
+      <c r="E16" s="38" t="s">
+        <v>491</v>
+      </c>
+      <c r="F16" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="G16" s="125" t="s">
         <v>490</v>
       </c>
-      <c r="E16" s="88" t="s">
+      <c r="H16" s="126" t="s">
+        <v>252</v>
+      </c>
+      <c r="I16" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="J16" s="37" t="s">
         <v>492</v>
       </c>
-      <c r="F16" s="87" t="s">
-        <v>158</v>
-      </c>
-      <c r="G16" s="132" t="s">
-        <v>491</v>
-      </c>
-      <c r="H16" s="97" t="s">
-        <v>252</v>
-      </c>
-      <c r="I16" s="87" t="s">
-        <v>338</v>
-      </c>
-      <c r="J16" s="87" t="s">
-        <v>493</v>
-      </c>
-      <c r="K16" s="88" t="s">
+      <c r="K16" s="38" t="s">
         <v>288</v>
       </c>
-      <c r="L16" s="87">
-        <v>5</v>
-      </c>
-      <c r="M16" s="89">
+      <c r="L16" s="37">
+        <v>6</v>
+      </c>
+      <c r="M16" s="41">
         <f t="shared" si="1"/>
-        <v>100</v>
-      </c>
-      <c r="N16" s="89">
-        <v>110</v>
-      </c>
-      <c r="O16" s="90" t="s">
+        <v>120</v>
+      </c>
+      <c r="N16" s="41">
+        <v>130</v>
+      </c>
+      <c r="O16" s="64" t="s">
         <v>368</v>
       </c>
-      <c r="P16" s="89">
+      <c r="P16" s="41">
         <v>3.32E-2</v>
       </c>
-      <c r="Q16" s="89">
+      <c r="Q16" s="41">
         <f t="shared" ref="Q16" si="5">P16*N16</f>
-        <v>3.6520000000000001</v>
-      </c>
-      <c r="R16" s="106" t="s">
-        <v>494</v>
+        <v>4.3159999999999998</v>
+      </c>
+      <c r="R16" s="124" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4238,58 +4256,58 @@
     </row>
     <row r="24" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
-      <c r="B24" s="85">
+      <c r="B24" s="53">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="92" t="s">
+      <c r="C24" s="60" t="s">
         <v>341</v>
       </c>
-      <c r="D24" s="93" t="s">
+      <c r="D24" s="39" t="s">
         <v>468</v>
       </c>
-      <c r="E24" s="94" t="s">
+      <c r="E24" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="F24" s="93" t="s">
+      <c r="F24" s="39" t="s">
         <v>158</v>
       </c>
-      <c r="G24" s="94" t="s">
+      <c r="G24" s="40" t="s">
         <v>209</v>
       </c>
-      <c r="H24" s="93" t="s">
+      <c r="H24" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="I24" s="93" t="s">
-        <v>338</v>
-      </c>
-      <c r="J24" s="93" t="s">
+      <c r="I24" s="39" t="s">
+        <v>338</v>
+      </c>
+      <c r="J24" s="39" t="s">
         <v>384</v>
       </c>
-      <c r="K24" s="94" t="s">
+      <c r="K24" s="40" t="s">
         <v>293</v>
       </c>
-      <c r="L24" s="108">
+      <c r="L24" s="127">
         <v>1</v>
       </c>
-      <c r="M24" s="95">
+      <c r="M24" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N24" s="107">
+      <c r="N24" s="128">
         <v>40</v>
       </c>
-      <c r="O24" s="96" t="s">
+      <c r="O24" s="65" t="s">
         <v>368</v>
       </c>
-      <c r="P24" s="95">
+      <c r="P24" s="42">
         <v>1.9199999999999998E-2</v>
       </c>
-      <c r="Q24" s="95">
+      <c r="Q24" s="42">
         <f t="shared" ref="Q24" si="13">N24*P24</f>
         <v>0.7679999999999999</v>
       </c>
-      <c r="R24" s="106" t="s">
+      <c r="R24" s="129" t="s">
         <v>469</v>
       </c>
     </row>
@@ -4405,229 +4423,229 @@
     </row>
     <row r="27" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
-      <c r="B27" s="113">
+      <c r="B27" s="53">
         <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
-      <c r="C27" s="133" t="s">
+      <c r="C27" s="130" t="s">
         <v>341</v>
       </c>
-      <c r="D27" s="134" t="s">
+      <c r="D27" s="131" t="s">
         <v>18</v>
       </c>
-      <c r="E27" s="135" t="s">
+      <c r="E27" s="132" t="s">
         <v>94</v>
       </c>
-      <c r="F27" s="134" t="s">
+      <c r="F27" s="131" t="s">
         <v>162</v>
       </c>
-      <c r="G27" s="135" t="s">
+      <c r="G27" s="132" t="s">
         <v>211</v>
       </c>
-      <c r="H27" s="134" t="s">
+      <c r="H27" s="131" t="s">
         <v>251</v>
       </c>
-      <c r="I27" s="134" t="s">
-        <v>338</v>
-      </c>
-      <c r="J27" s="134" t="s">
+      <c r="I27" s="131" t="s">
+        <v>338</v>
+      </c>
+      <c r="J27" s="131" t="s">
         <v>388</v>
       </c>
-      <c r="K27" s="135" t="s">
+      <c r="K27" s="132" t="s">
         <v>296</v>
       </c>
-      <c r="L27" s="134">
+      <c r="L27" s="131">
         <v>1</v>
       </c>
-      <c r="M27" s="136">
+      <c r="M27" s="133">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N27" s="136">
+      <c r="N27" s="133">
         <v>0</v>
       </c>
-      <c r="O27" s="137" t="s">
+      <c r="O27" s="134" t="s">
         <v>368</v>
       </c>
-      <c r="P27" s="136">
+      <c r="P27" s="133">
         <v>0.1653</v>
       </c>
-      <c r="Q27" s="136">
+      <c r="Q27" s="133">
         <f t="shared" ref="Q27" si="16">P27*N27</f>
         <v>0</v>
       </c>
-      <c r="R27" s="136" t="s">
+      <c r="R27" s="133" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
-      <c r="B28" s="85">
+      <c r="B28" s="53">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="92" t="s">
+      <c r="C28" s="60" t="s">
         <v>341</v>
       </c>
-      <c r="D28" s="93" t="s">
+      <c r="D28" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="E28" s="112" t="s">
+      <c r="E28" s="137" t="s">
         <v>482</v>
       </c>
-      <c r="F28" s="93" t="s">
+      <c r="F28" s="39" t="s">
         <v>158</v>
       </c>
-      <c r="G28" s="116" t="s">
+      <c r="G28" s="138" t="s">
         <v>483</v>
       </c>
-      <c r="H28" s="105" t="s">
+      <c r="H28" s="139" t="s">
         <v>484</v>
       </c>
-      <c r="I28" s="93" t="s">
-        <v>338</v>
-      </c>
-      <c r="J28" s="93" t="s">
+      <c r="I28" s="39" t="s">
+        <v>338</v>
+      </c>
+      <c r="J28" s="39" t="s">
         <v>485</v>
       </c>
-      <c r="K28" s="94" t="s">
+      <c r="K28" s="40" t="s">
         <v>486</v>
       </c>
-      <c r="L28" s="93">
+      <c r="L28" s="39">
         <v>1</v>
       </c>
-      <c r="M28" s="95">
+      <c r="M28" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N28" s="95">
+      <c r="N28" s="42">
         <v>100</v>
       </c>
-      <c r="O28" s="96" t="s">
+      <c r="O28" s="65" t="s">
         <v>368</v>
       </c>
-      <c r="P28" s="95">
+      <c r="P28" s="42">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="Q28" s="95">
+      <c r="Q28" s="42">
         <f t="shared" ref="Q28" si="17">N28*P28</f>
         <v>0.33999999999999997</v>
       </c>
-      <c r="R28" s="106" t="s">
+      <c r="R28" s="129" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="29" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
-      <c r="B29" s="85">
+      <c r="B29" s="53">
         <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
-      <c r="C29" s="86" t="s">
+      <c r="C29" s="61" t="s">
         <v>341</v>
       </c>
-      <c r="D29" s="87" t="s">
+      <c r="D29" s="37" t="s">
         <v>488</v>
       </c>
-      <c r="E29" s="88" t="s">
+      <c r="E29" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="F29" s="87" t="s">
+      <c r="F29" s="37" t="s">
         <v>163</v>
       </c>
-      <c r="G29" s="88" t="s">
+      <c r="G29" s="38" t="s">
         <v>212</v>
       </c>
-      <c r="H29" s="87" t="s">
+      <c r="H29" s="37" t="s">
         <v>252</v>
       </c>
-      <c r="I29" s="87" t="s">
-        <v>338</v>
-      </c>
-      <c r="J29" s="87" t="s">
+      <c r="I29" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="J29" s="37" t="s">
         <v>389</v>
       </c>
-      <c r="K29" s="88" t="s">
+      <c r="K29" s="38" t="s">
         <v>297</v>
       </c>
-      <c r="L29" s="109">
+      <c r="L29" s="123">
         <v>1</v>
       </c>
-      <c r="M29" s="89">
+      <c r="M29" s="41">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N29" s="119">
+      <c r="N29" s="135">
         <v>30</v>
       </c>
-      <c r="O29" s="90" t="s">
+      <c r="O29" s="64" t="s">
         <v>368</v>
       </c>
-      <c r="P29" s="89">
+      <c r="P29" s="41">
         <v>0.2525</v>
       </c>
-      <c r="Q29" s="89">
+      <c r="Q29" s="41">
         <f t="shared" ref="Q29" si="18">P29*N29</f>
         <v>7.5750000000000002</v>
       </c>
-      <c r="R29" s="91" t="s">
+      <c r="R29" s="136" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
-      <c r="B30" s="113">
+      <c r="B30" s="53">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="114" t="s">
+      <c r="C30" s="140" t="s">
         <v>341</v>
       </c>
-      <c r="D30" s="115" t="s">
+      <c r="D30" s="141" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="116" t="s">
+      <c r="E30" s="138" t="s">
         <v>96</v>
       </c>
-      <c r="F30" s="115" t="s">
+      <c r="F30" s="141" t="s">
         <v>158</v>
       </c>
-      <c r="G30" s="116" t="s">
+      <c r="G30" s="138" t="s">
         <v>213</v>
       </c>
-      <c r="H30" s="115" t="s">
+      <c r="H30" s="141" t="s">
         <v>250</v>
       </c>
-      <c r="I30" s="115" t="s">
-        <v>338</v>
-      </c>
-      <c r="J30" s="115" t="s">
+      <c r="I30" s="141" t="s">
+        <v>338</v>
+      </c>
+      <c r="J30" s="141" t="s">
         <v>390</v>
       </c>
-      <c r="K30" s="116" t="s">
+      <c r="K30" s="138" t="s">
         <v>298</v>
       </c>
-      <c r="L30" s="115">
+      <c r="L30" s="141">
         <v>1</v>
       </c>
-      <c r="M30" s="117">
+      <c r="M30" s="142">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N30" s="117">
+      <c r="N30" s="142">
         <v>0</v>
       </c>
-      <c r="O30" s="118" t="s">
+      <c r="O30" s="143" t="s">
         <v>368</v>
       </c>
-      <c r="P30" s="117">
+      <c r="P30" s="142">
         <v>4.1999999999999997E-3</v>
       </c>
-      <c r="Q30" s="117">
+      <c r="Q30" s="142">
         <f t="shared" ref="Q30" si="19">N30*P30</f>
         <v>0</v>
       </c>
-      <c r="R30" s="106" t="s">
+      <c r="R30" s="129" t="s">
         <v>481</v>
       </c>
     </row>
@@ -4798,58 +4816,58 @@
     </row>
     <row r="34" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
-      <c r="B34" s="120">
+      <c r="B34" s="53">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="121" t="s">
+      <c r="C34" s="109" t="s">
         <v>341</v>
       </c>
-      <c r="D34" s="122" t="s">
+      <c r="D34" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="E34" s="123" t="s">
+      <c r="E34" s="111" t="s">
         <v>100</v>
       </c>
-      <c r="F34" s="122" t="s">
+      <c r="F34" s="110" t="s">
         <v>160</v>
       </c>
-      <c r="G34" s="123" t="s">
+      <c r="G34" s="111" t="s">
         <v>216</v>
       </c>
-      <c r="H34" s="122" t="s">
+      <c r="H34" s="110" t="s">
         <v>254</v>
       </c>
-      <c r="I34" s="122" t="s">
+      <c r="I34" s="110" t="s">
         <v>395</v>
       </c>
-      <c r="J34" s="122" t="s">
+      <c r="J34" s="110" t="s">
         <v>394</v>
       </c>
-      <c r="K34" s="123" t="s">
+      <c r="K34" s="111" t="s">
         <v>287</v>
       </c>
-      <c r="L34" s="122">
+      <c r="L34" s="110">
         <v>1</v>
       </c>
-      <c r="M34" s="124">
+      <c r="M34" s="112">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N34" s="124">
+      <c r="N34" s="112">
         <v>0</v>
       </c>
-      <c r="O34" s="125" t="s">
+      <c r="O34" s="113" t="s">
         <v>368</v>
       </c>
-      <c r="P34" s="124">
+      <c r="P34" s="112">
         <v>9.1899999999999996E-2</v>
       </c>
-      <c r="Q34" s="124">
+      <c r="Q34" s="112">
         <f t="shared" ref="Q34" si="23">N34*P34</f>
         <v>0</v>
       </c>
-      <c r="R34" s="124" t="s">
+      <c r="R34" s="112" t="s">
         <v>416</v>
       </c>
     </row>
@@ -5020,115 +5038,115 @@
     </row>
     <row r="38" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1"/>
-      <c r="B38" s="85">
+      <c r="B38" s="53">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="92" t="s">
+      <c r="C38" s="60" t="s">
         <v>342</v>
       </c>
-      <c r="D38" s="93" t="s">
-        <v>509</v>
-      </c>
-      <c r="E38" s="94" t="s">
+      <c r="D38" s="39" t="s">
+        <v>507</v>
+      </c>
+      <c r="E38" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="F38" s="93" t="s">
+      <c r="F38" s="39" t="s">
         <v>167</v>
       </c>
-      <c r="G38" s="94" t="s">
+      <c r="G38" s="40" t="s">
         <v>304</v>
       </c>
-      <c r="H38" s="93" t="s">
+      <c r="H38" s="39" t="s">
         <v>259</v>
       </c>
-      <c r="I38" s="93" t="s">
+      <c r="I38" s="39" t="s">
         <v>304</v>
       </c>
-      <c r="J38" s="93" t="s">
+      <c r="J38" s="39" t="s">
         <v>399</v>
       </c>
-      <c r="K38" s="94" t="s">
-        <v>338</v>
-      </c>
-      <c r="L38" s="108">
+      <c r="K38" s="40" t="s">
+        <v>338</v>
+      </c>
+      <c r="L38" s="127">
         <v>2</v>
       </c>
-      <c r="M38" s="95">
+      <c r="M38" s="42">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N38" s="107">
+      <c r="N38" s="128">
         <v>60</v>
       </c>
-      <c r="O38" s="96" t="s">
+      <c r="O38" s="65" t="s">
         <v>368</v>
       </c>
-      <c r="P38" s="95">
+      <c r="P38" s="42">
         <v>2.8899999999999999E-2</v>
       </c>
-      <c r="Q38" s="95">
+      <c r="Q38" s="42">
         <f t="shared" ref="Q38" si="27">N38*P38</f>
         <v>1.734</v>
       </c>
-      <c r="R38" s="91" t="s">
-        <v>510</v>
+      <c r="R38" s="144" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="39" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1"/>
-      <c r="B39" s="67">
+      <c r="B39" s="53">
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="68" t="s">
+      <c r="C39" s="61" t="s">
         <v>342</v>
       </c>
-      <c r="D39" s="69" t="s">
+      <c r="D39" s="37" t="s">
         <v>472</v>
       </c>
-      <c r="E39" s="70" t="s">
+      <c r="E39" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="F39" s="69" t="s">
+      <c r="F39" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="G39" s="70" t="s">
+      <c r="G39" s="38" t="s">
         <v>218</v>
       </c>
-      <c r="H39" s="69" t="s">
+      <c r="H39" s="37" t="s">
         <v>260</v>
       </c>
-      <c r="I39" s="69" t="s">
+      <c r="I39" s="37" t="s">
         <v>401</v>
       </c>
-      <c r="J39" s="69" t="s">
+      <c r="J39" s="37" t="s">
         <v>402</v>
       </c>
-      <c r="K39" s="70" t="s">
-        <v>338</v>
-      </c>
-      <c r="L39" s="110">
+      <c r="K39" s="38" t="s">
+        <v>338</v>
+      </c>
+      <c r="L39" s="123">
         <v>9</v>
       </c>
-      <c r="M39" s="71">
+      <c r="M39" s="41">
         <f t="shared" si="1"/>
         <v>180</v>
       </c>
-      <c r="N39" s="139">
+      <c r="N39" s="135">
         <v>190</v>
       </c>
-      <c r="O39" s="72" t="s">
+      <c r="O39" s="64" t="s">
         <v>368</v>
       </c>
-      <c r="P39" s="71">
+      <c r="P39" s="41">
         <v>0.12590000000000001</v>
       </c>
-      <c r="Q39" s="71">
+      <c r="Q39" s="41">
         <f t="shared" ref="Q39" si="28">P39*N39</f>
         <v>23.921000000000003</v>
       </c>
-      <c r="R39" s="73" t="s">
+      <c r="R39" s="136" t="s">
         <v>473</v>
       </c>
     </row>
@@ -5244,7 +5262,7 @@
     </row>
     <row r="42" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1"/>
-      <c r="B42" s="67">
+      <c r="B42" s="53">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
@@ -5301,58 +5319,58 @@
     </row>
     <row r="43" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
-      <c r="B43" s="67">
+      <c r="B43" s="53">
         <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
       </c>
-      <c r="C43" s="68" t="s">
+      <c r="C43" s="61" t="s">
         <v>345</v>
       </c>
-      <c r="D43" s="69" t="s">
+      <c r="D43" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="E43" s="70" t="s">
+      <c r="E43" s="38" t="s">
         <v>109</v>
       </c>
-      <c r="F43" s="69" t="s">
+      <c r="F43" s="37" t="s">
         <v>332</v>
       </c>
-      <c r="G43" s="70" t="s">
+      <c r="G43" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="H43" s="69" t="s">
+      <c r="H43" s="37" t="s">
         <v>263</v>
       </c>
-      <c r="I43" s="69" t="s">
+      <c r="I43" s="37" t="s">
         <v>408</v>
       </c>
-      <c r="J43" s="69" t="s">
+      <c r="J43" s="37" t="s">
         <v>409</v>
       </c>
-      <c r="K43" s="70" t="s">
-        <v>338</v>
-      </c>
-      <c r="L43" s="69">
+      <c r="K43" s="38" t="s">
+        <v>338</v>
+      </c>
+      <c r="L43" s="37">
         <v>2</v>
       </c>
-      <c r="M43" s="71">
+      <c r="M43" s="41">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N43" s="71">
+      <c r="N43" s="41">
         <v>42</v>
       </c>
-      <c r="O43" s="72" t="s">
+      <c r="O43" s="64" t="s">
         <v>368</v>
       </c>
-      <c r="P43" s="71">
+      <c r="P43" s="41">
         <v>0.65639999999999998</v>
       </c>
-      <c r="Q43" s="71">
+      <c r="Q43" s="41">
         <f t="shared" ref="Q43" si="32">P43*N43</f>
         <v>27.5688</v>
       </c>
-      <c r="R43" s="73" t="s">
+      <c r="R43" s="136" t="s">
         <v>400</v>
       </c>
     </row>
@@ -5523,59 +5541,59 @@
     </row>
     <row r="47" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
-      <c r="B47" s="85">
+      <c r="B47" s="53">
         <f>ROW(B47) - ROW($B$9)</f>
         <v>38</v>
       </c>
-      <c r="C47" s="86" t="s">
+      <c r="C47" s="61" t="s">
         <v>343</v>
       </c>
-      <c r="D47" s="87" t="s">
+      <c r="D47" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="E47" s="88" t="s">
+      <c r="E47" s="38" t="s">
+        <v>501</v>
+      </c>
+      <c r="F47" s="37" t="s">
+        <v>332</v>
+      </c>
+      <c r="G47" s="38" t="s">
+        <v>502</v>
+      </c>
+      <c r="H47" s="126" t="s">
         <v>503</v>
       </c>
-      <c r="F47" s="87" t="s">
-        <v>332</v>
-      </c>
-      <c r="G47" s="88" t="s">
+      <c r="I47" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="J47" s="37" t="s">
         <v>504</v>
       </c>
-      <c r="H47" s="97" t="s">
+      <c r="K47" s="38" t="s">
         <v>505</v>
       </c>
-      <c r="I47" s="87" t="s">
-        <v>338</v>
-      </c>
-      <c r="J47" s="87" t="s">
-        <v>506</v>
-      </c>
-      <c r="K47" s="88" t="s">
-        <v>507</v>
-      </c>
-      <c r="L47" s="87">
+      <c r="L47" s="37">
         <v>1</v>
       </c>
-      <c r="M47" s="89">
+      <c r="M47" s="41">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N47" s="119">
+      <c r="N47" s="135">
         <v>25</v>
       </c>
-      <c r="O47" s="90" t="s">
+      <c r="O47" s="64" t="s">
         <v>368</v>
       </c>
-      <c r="P47" s="89">
+      <c r="P47" s="41">
         <v>0.1012</v>
       </c>
-      <c r="Q47" s="89">
+      <c r="Q47" s="41">
         <f t="shared" ref="Q47" si="36">P47*N47</f>
         <v>2.5299999999999998</v>
       </c>
-      <c r="R47" s="106" t="s">
-        <v>508</v>
+      <c r="R47" s="124" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -5885,7 +5903,7 @@
       <c r="K53" s="70" t="s">
         <v>338</v>
       </c>
-      <c r="L53" s="110">
+      <c r="L53" s="106">
         <v>4</v>
       </c>
       <c r="M53" s="71">
@@ -6248,7 +6266,7 @@
       <c r="C60" s="92" t="s">
         <v>349</v>
       </c>
-      <c r="D60" s="105" t="s">
+      <c r="D60" s="101" t="s">
         <v>461</v>
       </c>
       <c r="E60" s="94" t="s">
@@ -6270,14 +6288,14 @@
       <c r="K60" s="94" t="s">
         <v>313</v>
       </c>
-      <c r="L60" s="108">
+      <c r="L60" s="104">
         <v>1</v>
       </c>
       <c r="M60" s="95">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N60" s="107">
+      <c r="N60" s="103">
         <v>100</v>
       </c>
       <c r="O60" s="96" t="s">
@@ -6290,7 +6308,7 @@
         <f t="shared" ref="Q60:Q61" si="50">N60*P60</f>
         <v>0.15</v>
       </c>
-      <c r="R60" s="106" t="s">
+      <c r="R60" s="102" t="s">
         <v>462</v>
       </c>
     </row>
@@ -6327,17 +6345,17 @@
       <c r="K61" s="87" t="s">
         <v>466</v>
       </c>
-      <c r="L61" s="109">
+      <c r="L61" s="105">
         <v>8</v>
       </c>
       <c r="M61" s="87">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="N61" s="107">
+      <c r="N61" s="103">
         <v>100</v>
       </c>
-      <c r="O61" s="111" t="s">
+      <c r="O61" s="107" t="s">
         <v>368</v>
       </c>
       <c r="P61" s="87">
@@ -6347,7 +6365,7 @@
         <f t="shared" si="50"/>
         <v>0.11</v>
       </c>
-      <c r="R61" s="106" t="s">
+      <c r="R61" s="102" t="s">
         <v>467</v>
       </c>
     </row>
@@ -6800,7 +6818,7 @@
       <c r="C70" s="61" t="s">
         <v>349</v>
       </c>
-      <c r="D70" s="69" t="s">
+      <c r="D70" s="37" t="s">
         <v>435</v>
       </c>
       <c r="E70" s="38" t="s">
@@ -6824,7 +6842,7 @@
       <c r="K70" s="38" t="s">
         <v>322</v>
       </c>
-      <c r="L70" s="110">
+      <c r="L70" s="123">
         <v>2</v>
       </c>
       <c r="M70" s="41">
@@ -7019,111 +7037,111 @@
         <f>ROW(B74) - ROW($B$9)</f>
         <v>65</v>
       </c>
-      <c r="C74" s="86" t="s">
+      <c r="C74" s="61" t="s">
         <v>349</v>
       </c>
-      <c r="D74" s="87" t="s">
+      <c r="D74" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E74" s="132" t="s">
+      <c r="E74" s="125" t="s">
+        <v>495</v>
+      </c>
+      <c r="F74" s="145" t="s">
+        <v>496</v>
+      </c>
+      <c r="G74" s="38" t="s">
         <v>497</v>
       </c>
-      <c r="F74" s="138" t="s">
+      <c r="H74" s="126" t="s">
+        <v>273</v>
+      </c>
+      <c r="I74" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="J74" s="37" t="s">
         <v>498</v>
       </c>
-      <c r="G74" s="88" t="s">
+      <c r="K74" s="38" t="s">
         <v>499</v>
       </c>
-      <c r="H74" s="97" t="s">
-        <v>273</v>
-      </c>
-      <c r="I74" s="87" t="s">
-        <v>338</v>
-      </c>
-      <c r="J74" s="87" t="s">
-        <v>500</v>
-      </c>
-      <c r="K74" s="88" t="s">
-        <v>501</v>
-      </c>
-      <c r="L74" s="87">
+      <c r="L74" s="37">
         <v>1</v>
       </c>
-      <c r="M74" s="89">
+      <c r="M74" s="41">
         <f t="shared" ref="M74:M92" si="63">L74*20</f>
         <v>20</v>
       </c>
-      <c r="N74" s="119">
+      <c r="N74" s="135">
         <v>50</v>
       </c>
-      <c r="O74" s="90" t="s">
+      <c r="O74" s="64" t="s">
         <v>368</v>
       </c>
-      <c r="P74" s="89">
+      <c r="P74" s="41">
         <v>3.8E-3</v>
       </c>
-      <c r="Q74" s="89">
+      <c r="Q74" s="41">
         <f t="shared" ref="Q74" si="64">P74*N74</f>
         <v>0.19</v>
       </c>
-      <c r="R74" s="106" t="s">
-        <v>502</v>
+      <c r="R74" s="124" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="75" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1"/>
-      <c r="B75" s="113">
+      <c r="B75" s="108">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="C75" s="114" t="s">
+      <c r="C75" s="140" t="s">
         <v>349</v>
       </c>
-      <c r="D75" s="115" t="s">
+      <c r="D75" s="141" t="s">
         <v>60</v>
       </c>
-      <c r="E75" s="116" t="s">
+      <c r="E75" s="138" t="s">
         <v>138</v>
       </c>
-      <c r="F75" s="115" t="s">
+      <c r="F75" s="141" t="s">
         <v>182</v>
       </c>
-      <c r="G75" s="116" t="s">
+      <c r="G75" s="138" t="s">
         <v>239</v>
       </c>
-      <c r="H75" s="115" t="s">
+      <c r="H75" s="141" t="s">
         <v>272</v>
       </c>
-      <c r="I75" s="115" t="s">
-        <v>338</v>
-      </c>
-      <c r="J75" s="115" t="s">
-        <v>338</v>
-      </c>
-      <c r="K75" s="116" t="s">
+      <c r="I75" s="141" t="s">
+        <v>338</v>
+      </c>
+      <c r="J75" s="141" t="s">
+        <v>338</v>
+      </c>
+      <c r="K75" s="138" t="s">
         <v>326</v>
       </c>
-      <c r="L75" s="115">
+      <c r="L75" s="141">
         <v>1</v>
       </c>
-      <c r="M75" s="117">
+      <c r="M75" s="142">
         <f t="shared" si="63"/>
         <v>20</v>
       </c>
-      <c r="N75" s="117">
+      <c r="N75" s="142">
         <v>0</v>
       </c>
-      <c r="O75" s="118" t="s">
+      <c r="O75" s="143" t="s">
         <v>413</v>
       </c>
-      <c r="P75" s="117">
+      <c r="P75" s="142">
         <v>1.8589999999999999E-2</v>
       </c>
-      <c r="Q75" s="117">
+      <c r="Q75" s="142">
         <f t="shared" ref="Q75" si="65">N75*P75</f>
         <v>0</v>
       </c>
-      <c r="R75" s="106" t="s">
+      <c r="R75" s="129" t="s">
         <v>481</v>
       </c>
     </row>
@@ -7298,55 +7316,55 @@
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="C79" s="92" t="s">
+      <c r="C79" s="60" t="s">
         <v>349</v>
       </c>
-      <c r="D79" s="93" t="s">
-        <v>495</v>
-      </c>
-      <c r="E79" s="94" t="s">
+      <c r="D79" s="39" t="s">
+        <v>493</v>
+      </c>
+      <c r="E79" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="F79" s="93" t="s">
+      <c r="F79" s="39" t="s">
         <v>182</v>
       </c>
-      <c r="G79" s="94" t="s">
+      <c r="G79" s="40" t="s">
         <v>241</v>
       </c>
-      <c r="H79" s="93" t="s">
+      <c r="H79" s="39" t="s">
         <v>250</v>
       </c>
-      <c r="I79" s="93" t="s">
-        <v>338</v>
-      </c>
-      <c r="J79" s="93" t="s">
+      <c r="I79" s="39" t="s">
+        <v>338</v>
+      </c>
+      <c r="J79" s="39" t="s">
         <v>443</v>
       </c>
-      <c r="K79" s="94" t="s">
+      <c r="K79" s="40" t="s">
         <v>330</v>
       </c>
-      <c r="L79" s="93">
+      <c r="L79" s="39">
         <v>6</v>
       </c>
-      <c r="M79" s="95">
+      <c r="M79" s="42">
         <f t="shared" si="63"/>
         <v>120</v>
       </c>
-      <c r="N79" s="95">
+      <c r="N79" s="42">
         <v>200</v>
       </c>
-      <c r="O79" s="96" t="s">
+      <c r="O79" s="65" t="s">
         <v>368</v>
       </c>
-      <c r="P79" s="95">
+      <c r="P79" s="42">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q79" s="95">
+      <c r="Q79" s="42">
         <f t="shared" ref="Q79" si="69">N79*P79</f>
         <v>0.24</v>
       </c>
-      <c r="R79" s="106" t="s">
-        <v>496</v>
+      <c r="R79" s="129" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="80" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -7569,54 +7587,54 @@
         <f>ROW(B84) - ROW($B$9)</f>
         <v>75</v>
       </c>
-      <c r="C84" s="86" t="s">
+      <c r="C84" s="61" t="s">
         <v>353</v>
       </c>
-      <c r="D84" s="87" t="s">
+      <c r="D84" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="E84" s="88" t="s">
+      <c r="E84" s="38" t="s">
         <v>147</v>
       </c>
-      <c r="F84" s="87" t="s">
+      <c r="F84" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="G84" s="88" t="s">
+      <c r="G84" s="38" t="s">
         <v>242</v>
       </c>
-      <c r="H84" s="87" t="s">
+      <c r="H84" s="37" t="s">
         <v>278</v>
       </c>
-      <c r="I84" s="87" t="s">
+      <c r="I84" s="37" t="s">
         <v>445</v>
       </c>
-      <c r="J84" s="87" t="s">
+      <c r="J84" s="37" t="s">
         <v>446</v>
       </c>
-      <c r="K84" s="88" t="s">
-        <v>338</v>
-      </c>
-      <c r="L84" s="87">
+      <c r="K84" s="38" t="s">
+        <v>338</v>
+      </c>
+      <c r="L84" s="37">
         <v>1</v>
       </c>
-      <c r="M84" s="89">
+      <c r="M84" s="41">
         <f t="shared" si="63"/>
         <v>20</v>
       </c>
-      <c r="N84" s="89">
+      <c r="N84" s="41">
         <v>21</v>
       </c>
-      <c r="O84" s="90" t="s">
+      <c r="O84" s="64" t="s">
         <v>368</v>
       </c>
-      <c r="P84" s="89">
+      <c r="P84" s="41">
         <v>1.3939999999999999</v>
       </c>
-      <c r="Q84" s="89">
+      <c r="Q84" s="41">
         <f t="shared" ref="Q84" si="75">P84*N84</f>
         <v>29.273999999999997</v>
       </c>
-      <c r="R84" s="91" t="s">
+      <c r="R84" s="136" t="s">
         <v>474</v>
       </c>
     </row>
@@ -7626,54 +7644,54 @@
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
-      <c r="C85" s="92" t="s">
+      <c r="C85" s="60" t="s">
         <v>353</v>
       </c>
-      <c r="D85" s="93" t="s">
+      <c r="D85" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="E85" s="94" t="s">
+      <c r="E85" s="40" t="s">
         <v>148</v>
       </c>
-      <c r="F85" s="93" t="s">
+      <c r="F85" s="39" t="s">
         <v>189</v>
       </c>
-      <c r="G85" s="94" t="s">
+      <c r="G85" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="H85" s="93" t="s">
+      <c r="H85" s="39" t="s">
         <v>277</v>
       </c>
-      <c r="I85" s="93" t="s">
+      <c r="I85" s="39" t="s">
         <v>448</v>
       </c>
-      <c r="J85" s="93" t="s">
+      <c r="J85" s="39" t="s">
         <v>449</v>
       </c>
-      <c r="K85" s="94" t="s">
-        <v>338</v>
-      </c>
-      <c r="L85" s="93">
+      <c r="K85" s="40" t="s">
+        <v>338</v>
+      </c>
+      <c r="L85" s="39">
         <v>1</v>
       </c>
-      <c r="M85" s="95">
+      <c r="M85" s="42">
         <f t="shared" si="63"/>
         <v>20</v>
       </c>
-      <c r="N85" s="95">
+      <c r="N85" s="42">
         <v>21</v>
       </c>
-      <c r="O85" s="96" t="s">
+      <c r="O85" s="65" t="s">
         <v>368</v>
       </c>
-      <c r="P85" s="95">
+      <c r="P85" s="42">
         <v>0.69430000000000003</v>
       </c>
-      <c r="Q85" s="95">
+      <c r="Q85" s="42">
         <f t="shared" ref="Q85" si="76">N85*P85</f>
         <v>14.580300000000001</v>
       </c>
-      <c r="R85" s="91" t="s">
+      <c r="R85" s="144" t="s">
         <v>447</v>
       </c>
     </row>
@@ -7789,59 +7807,59 @@
     </row>
     <row r="88" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="1"/>
-      <c r="B88" s="126">
+      <c r="B88" s="114">
         <f>ROW(B88) - ROW($B$9)</f>
         <v>79</v>
       </c>
-      <c r="C88" s="127" t="s">
+      <c r="C88" s="115" t="s">
         <v>353</v>
       </c>
-      <c r="D88" s="128" t="s">
+      <c r="D88" s="116" t="s">
         <v>72</v>
       </c>
-      <c r="E88" s="129" t="s">
+      <c r="E88" s="117" t="s">
         <v>151</v>
       </c>
-      <c r="F88" s="128" t="s">
+      <c r="F88" s="116" t="s">
         <v>192</v>
       </c>
-      <c r="G88" s="129" t="s">
+      <c r="G88" s="117" t="s">
         <v>245</v>
       </c>
-      <c r="H88" s="128" t="s">
+      <c r="H88" s="116" t="s">
         <v>279</v>
       </c>
-      <c r="I88" s="128" t="s">
-        <v>338</v>
-      </c>
-      <c r="J88" s="128" t="s">
+      <c r="I88" s="116" t="s">
+        <v>338</v>
+      </c>
+      <c r="J88" s="116" t="s">
         <v>451</v>
       </c>
-      <c r="K88" s="129" t="s">
-        <v>338</v>
-      </c>
-      <c r="L88" s="128">
+      <c r="K88" s="117" t="s">
+        <v>338</v>
+      </c>
+      <c r="L88" s="116">
         <v>1</v>
       </c>
-      <c r="M88" s="130">
+      <c r="M88" s="118">
         <f t="shared" si="63"/>
         <v>20</v>
       </c>
-      <c r="N88" s="130">
+      <c r="N88" s="118">
         <v>21</v>
       </c>
-      <c r="O88" s="131" t="s">
+      <c r="O88" s="119" t="s">
         <v>368</v>
       </c>
-      <c r="P88" s="130">
+      <c r="P88" s="118">
         <v>7.4638</v>
       </c>
-      <c r="Q88" s="130">
+      <c r="Q88" s="118">
         <f t="shared" ref="Q88" si="79">P88*N88</f>
         <v>156.7398</v>
       </c>
-      <c r="R88" s="130" t="s">
-        <v>512</v>
+      <c r="R88" s="118" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="89" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7932,7 +7950,7 @@
       <c r="K90" s="88" t="s">
         <v>338</v>
       </c>
-      <c r="L90" s="109">
+      <c r="L90" s="105">
         <v>2</v>
       </c>
       <c r="M90" s="89">
@@ -8010,7 +8028,7 @@
         <v>74.171999999999997</v>
       </c>
       <c r="R91" s="91" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="92" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8085,13 +8103,13 @@
       <c r="L93" s="36"/>
       <c r="M93" s="36"/>
       <c r="N93" s="36"/>
-      <c r="O93" s="100" t="s">
+      <c r="O93" s="99" t="s">
         <v>458</v>
       </c>
-      <c r="P93" s="98"/>
-      <c r="Q93" s="98">
+      <c r="P93" s="97"/>
+      <c r="Q93" s="97">
         <f>SUM(Q10:Q92)</f>
-        <v>963.24749999999995</v>
+        <v>963.91150000000016</v>
       </c>
       <c r="R93" s="44"/>
     </row>
@@ -8112,13 +8130,13 @@
       <c r="L94" s="9"/>
       <c r="M94" s="9"/>
       <c r="N94" s="9"/>
-      <c r="O94" s="101" t="s">
+      <c r="O94" s="100" t="s">
         <v>459</v>
       </c>
-      <c r="P94" s="99"/>
-      <c r="Q94" s="99">
+      <c r="P94" s="98"/>
+      <c r="Q94" s="98">
         <f>Q93/20</f>
-        <v>48.162374999999997</v>
+        <v>48.195575000000005</v>
       </c>
       <c r="R94" s="45"/>
     </row>

--- a/Deliverables/SM_Top Board/_BOM/eSpark BOM (20 Boards).xlsx
+++ b/Deliverables/SM_Top Board/_BOM/eSpark BOM (20 Boards).xlsx
@@ -5,16 +5,16 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Faizan\GitHub\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="7656"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="7650"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -154,9 +154,6 @@
     <t>P7, P8, P9, P10</t>
   </si>
   <si>
-    <t>Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9</t>
-  </si>
-  <si>
     <t>R1, R2</t>
   </si>
   <si>
@@ -1442,9 +1439,6 @@
   </si>
   <si>
     <t>Quantity changed from 9/board to 1/board. The remaining 8 resistors have been converted to 22ohms after calculation</t>
-  </si>
-  <si>
-    <t>RES SMD 22OHM 1/10W 0603</t>
   </si>
   <si>
     <t>0603WAF220JT5E</t>
@@ -1943,11 +1937,17 @@
   <si>
     <t>Quantity changed from 4/board to 6/board due to addition of 2 x 10uF capacitor from U3</t>
   </si>
+  <si>
+    <t>Q2, Q3, Q4, Q5</t>
+  </si>
+  <si>
+    <t>RES SMD 22HM 1/10W 0603</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
@@ -2163,7 +2163,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2196,19 +2196,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2471,7 +2459,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -2650,9 +2638,6 @@
     <xf numFmtId="1" fontId="17" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2665,79 +2650,7 @@
     <xf numFmtId="0" fontId="17" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2749,61 +2662,103 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2815,73 +2770,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2928,7 +2820,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3227,26 +3119,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:R94"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="3.109375" style="25" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" style="25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="30.109375" customWidth="1"/>
-    <col min="7" max="7" width="33.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="22.109375" customWidth="1"/>
-    <col min="11" max="11" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="16.6640625" customWidth="1"/>
-    <col min="16" max="16" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="29.44140625" customWidth="1"/>
+    <col min="6" max="6" width="30.140625" customWidth="1"/>
+    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="22.140625" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="16.7109375" customWidth="1"/>
+    <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -3257,16 +3149,16 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-    </row>
-    <row r="2" spans="1:18" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+    </row>
+    <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
       <c r="C2" s="46"/>
@@ -3275,7 +3167,7 @@
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="54" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
@@ -3290,7 +3182,7 @@
       <c r="Q2" s="3"/>
       <c r="R2" s="43"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
       <c r="C3" s="47"/>
@@ -3299,7 +3191,7 @@
       </c>
       <c r="E3" s="12"/>
       <c r="F3" s="55" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="4"/>
@@ -3312,9 +3204,9 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="121"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R3" s="110"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
       <c r="C4" s="47"/>
@@ -3323,7 +3215,7 @@
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="56" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="6"/>
@@ -3336,9 +3228,9 @@
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="Q4" s="62"/>
-      <c r="R4" s="122"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R4" s="111"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
       <c r="C5" s="47"/>
@@ -3358,9 +3250,9 @@
       <c r="O5" s="62"/>
       <c r="P5" s="62"/>
       <c r="Q5" s="62"/>
-      <c r="R5" s="122"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R5" s="111"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
       <c r="C6" s="48"/>
@@ -3378,9 +3270,9 @@
       <c r="O6" s="62"/>
       <c r="P6" s="62"/>
       <c r="Q6" s="62"/>
-      <c r="R6" s="122"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R6" s="111"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
       <c r="C7" s="49"/>
@@ -3398,9 +3290,9 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="122"/>
-    </row>
-    <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R7" s="111"/>
+    </row>
+    <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="26"/>
       <c r="C8" s="50"/>
@@ -3418,94 +3310,94 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="122"/>
-    </row>
-    <row r="9" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R8" s="111"/>
+    </row>
+    <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="29" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D9" s="29" t="s">
         <v>7</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I9" s="29" t="s">
+        <v>359</v>
+      </c>
+      <c r="J9" s="29" t="s">
         <v>360</v>
       </c>
-      <c r="J9" s="29" t="s">
+      <c r="K9" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="L9" s="29" t="s">
+        <v>330</v>
+      </c>
+      <c r="M9" s="31" t="s">
         <v>361</v>
       </c>
-      <c r="K9" s="30" t="s">
-        <v>281</v>
-      </c>
-      <c r="L9" s="29" t="s">
-        <v>331</v>
-      </c>
-      <c r="M9" s="31" t="s">
+      <c r="N9" s="31" t="s">
         <v>362</v>
       </c>
-      <c r="N9" s="31" t="s">
+      <c r="O9" s="31" t="s">
         <v>363</v>
       </c>
-      <c r="O9" s="31" t="s">
+      <c r="P9" s="31" t="s">
         <v>364</v>
       </c>
-      <c r="P9" s="31" t="s">
+      <c r="Q9" s="31" t="s">
         <v>365</v>
       </c>
-      <c r="Q9" s="31" t="s">
-        <v>366</v>
-      </c>
       <c r="R9" s="31" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="53">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D10" s="37" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="38" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G10" s="38" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="K10" s="38" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L10" s="37">
         <v>1</v>
@@ -3518,7 +3410,7 @@
         <v>22</v>
       </c>
       <c r="O10" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P10" s="41">
         <v>0.25869999999999999</v>
@@ -3529,38 +3421,38 @@
       </c>
       <c r="R10" s="41"/>
     </row>
-    <row r="11" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="53">
         <f t="shared" ref="B11:B91" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="60" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D11" s="39" t="s">
         <v>9</v>
       </c>
       <c r="E11" s="40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F11" s="39" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G11" s="40" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H11" s="39" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I11" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J11" s="39" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="K11" s="40" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L11" s="39">
         <v>9</v>
@@ -3573,7 +3465,7 @@
         <v>198</v>
       </c>
       <c r="O11" s="65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P11" s="42">
         <v>1.4E-3</v>
@@ -3584,40 +3476,40 @@
       </c>
       <c r="R11" s="42"/>
     </row>
-    <row r="12" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="53">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
       <c r="C12" s="61" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="K12" s="38" t="s">
-        <v>284</v>
-      </c>
-      <c r="L12" s="123">
+        <v>283</v>
+      </c>
+      <c r="L12" s="86">
         <v>2</v>
       </c>
       <c r="M12" s="41">
@@ -3628,7 +3520,7 @@
         <v>100</v>
       </c>
       <c r="O12" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P12" s="41">
         <v>1.2999999999999999E-3</v>
@@ -3637,55 +3529,55 @@
         <f t="shared" ref="Q12" si="2">P12*N12</f>
         <v>0.13</v>
       </c>
-      <c r="R12" s="124" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R12" s="87" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="53">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C13" s="60" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E13" s="40" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G13" s="40" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I13" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J13" s="39" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="K13" s="40" t="s">
-        <v>285</v>
-      </c>
-      <c r="L13" s="127">
+        <v>284</v>
+      </c>
+      <c r="L13" s="90">
         <v>1</v>
       </c>
       <c r="M13" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N13" s="128">
+      <c r="N13" s="91">
         <v>40</v>
       </c>
       <c r="O13" s="65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P13" s="42">
         <v>3.5900000000000001E-2</v>
@@ -3694,42 +3586,42 @@
         <f t="shared" ref="Q13" si="3">N13*P13</f>
         <v>1.4359999999999999</v>
       </c>
-      <c r="R13" s="129" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R13" s="92" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="53">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
       <c r="C14" s="61" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J14" s="37" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="K14" s="38" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L14" s="37">
         <v>8</v>
@@ -3742,7 +3634,7 @@
         <v>200</v>
       </c>
       <c r="O14" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P14" s="41">
         <v>4.0899999999999999E-2</v>
@@ -3751,55 +3643,55 @@
         <f>P14*N14</f>
         <v>8.18</v>
       </c>
-      <c r="R14" s="124" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R14" s="87" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="53">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C15" s="60" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E15" s="40" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G15" s="40" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H15" s="39" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I15" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J15" s="39" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="K15" s="40" t="s">
-        <v>287</v>
-      </c>
-      <c r="L15" s="127">
+        <v>286</v>
+      </c>
+      <c r="L15" s="90">
         <v>3</v>
       </c>
       <c r="M15" s="42">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="N15" s="128">
+      <c r="N15" s="91">
         <v>100</v>
       </c>
       <c r="O15" s="65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P15" s="42">
         <v>5.8999999999999999E-3</v>
@@ -3808,42 +3700,42 @@
         <f t="shared" ref="Q15" si="4">N15*P15</f>
         <v>0.59</v>
       </c>
-      <c r="R15" s="129" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R15" s="92" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="53">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
       <c r="C16" s="61" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>158</v>
-      </c>
-      <c r="G16" s="125" t="s">
+        <v>157</v>
+      </c>
+      <c r="G16" s="88" t="s">
+        <v>488</v>
+      </c>
+      <c r="H16" s="89" t="s">
+        <v>251</v>
+      </c>
+      <c r="I16" s="37" t="s">
+        <v>337</v>
+      </c>
+      <c r="J16" s="37" t="s">
         <v>490</v>
       </c>
-      <c r="H16" s="126" t="s">
-        <v>252</v>
-      </c>
-      <c r="I16" s="37" t="s">
-        <v>338</v>
-      </c>
-      <c r="J16" s="37" t="s">
-        <v>492</v>
-      </c>
       <c r="K16" s="38" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L16" s="37">
         <v>6</v>
@@ -3856,7 +3748,7 @@
         <v>130</v>
       </c>
       <c r="O16" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P16" s="41">
         <v>3.32E-2</v>
@@ -3865,42 +3757,42 @@
         <f t="shared" ref="Q16" si="5">P16*N16</f>
         <v>4.3159999999999998</v>
       </c>
-      <c r="R16" s="124" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R16" s="87" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="53">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C17" s="60" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D17" s="39" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="40" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G17" s="40" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H17" s="39" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I17" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J17" s="39" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K17" s="40" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L17" s="39">
         <v>1</v>
@@ -3913,7 +3805,7 @@
         <v>50</v>
       </c>
       <c r="O17" s="65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P17" s="42">
         <v>9.9000000000000008E-3</v>
@@ -3924,38 +3816,38 @@
       </c>
       <c r="R17" s="42"/>
     </row>
-    <row r="18" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="53">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
       <c r="C18" s="61" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D18" s="37" t="s">
         <v>11</v>
       </c>
       <c r="E18" s="38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G18" s="38" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I18" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J18" s="37" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="K18" s="38" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L18" s="37">
         <v>3</v>
@@ -3968,7 +3860,7 @@
         <v>100</v>
       </c>
       <c r="O18" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P18" s="41">
         <v>8.0999999999999996E-3</v>
@@ -3979,38 +3871,38 @@
       </c>
       <c r="R18" s="41"/>
     </row>
-    <row r="19" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="53">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="C19" s="60" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E19" s="40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F19" s="39" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G19" s="40" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H19" s="39" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I19" s="39" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J19" s="39" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="K19" s="40" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L19" s="39">
         <v>8</v>
@@ -4023,7 +3915,7 @@
         <v>180</v>
       </c>
       <c r="O19" s="65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P19" s="42">
         <v>3.09E-2</v>
@@ -4034,38 +3926,38 @@
       </c>
       <c r="R19" s="42"/>
     </row>
-    <row r="20" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="53">
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
       <c r="C20" s="61" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D20" s="37" t="s">
         <v>12</v>
       </c>
       <c r="E20" s="38" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G20" s="38" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I20" s="37" t="s">
+        <v>377</v>
+      </c>
+      <c r="J20" s="37" t="s">
         <v>378</v>
       </c>
-      <c r="J20" s="37" t="s">
-        <v>379</v>
-      </c>
       <c r="K20" s="38" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L20" s="37">
         <v>1</v>
@@ -4078,7 +3970,7 @@
         <v>50</v>
       </c>
       <c r="O20" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P20" s="41">
         <v>5.3E-3</v>
@@ -4089,38 +3981,38 @@
       </c>
       <c r="R20" s="41"/>
     </row>
-    <row r="21" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="53">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="C21" s="60" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D21" s="39" t="s">
         <v>13</v>
       </c>
       <c r="E21" s="40" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F21" s="39" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G21" s="39" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H21" s="39" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I21" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J21" s="39" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="K21" s="40" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L21" s="39">
         <v>1</v>
@@ -4133,7 +4025,7 @@
         <v>22</v>
       </c>
       <c r="O21" s="65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P21" s="42">
         <v>0.22189999999999999</v>
@@ -4144,38 +4036,38 @@
       </c>
       <c r="R21" s="42"/>
     </row>
-    <row r="22" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="53">
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
       <c r="C22" s="61" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D22" s="37" t="s">
         <v>14</v>
       </c>
       <c r="E22" s="38" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J22" s="37" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="K22" s="38" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L22" s="37">
         <v>2</v>
@@ -4188,7 +4080,7 @@
         <v>50</v>
       </c>
       <c r="O22" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P22" s="41">
         <v>7.7000000000000002E-3</v>
@@ -4199,38 +4091,38 @@
       </c>
       <c r="R22" s="41"/>
     </row>
-    <row r="23" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="53">
         <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
       </c>
       <c r="C23" s="61" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D23" s="37" t="s">
         <v>15</v>
       </c>
       <c r="E23" s="38" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F23" s="37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G23" s="38" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H23" s="37" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I23" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J23" s="37" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="K23" s="38" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L23" s="37">
         <v>1</v>
@@ -4243,7 +4135,7 @@
         <v>40</v>
       </c>
       <c r="O23" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P23" s="41">
         <v>3.49E-2</v>
@@ -4254,51 +4146,51 @@
       </c>
       <c r="R23" s="41"/>
     </row>
-    <row r="24" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="53">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="C24" s="60" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D24" s="39" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E24" s="40" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F24" s="39" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G24" s="40" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H24" s="39" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I24" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J24" s="39" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="K24" s="40" t="s">
-        <v>293</v>
-      </c>
-      <c r="L24" s="127">
+        <v>292</v>
+      </c>
+      <c r="L24" s="90">
         <v>1</v>
       </c>
       <c r="M24" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N24" s="128">
+      <c r="N24" s="91">
         <v>40</v>
       </c>
       <c r="O24" s="65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P24" s="42">
         <v>1.9199999999999998E-2</v>
@@ -4307,42 +4199,42 @@
         <f t="shared" ref="Q24" si="13">N24*P24</f>
         <v>0.7679999999999999</v>
       </c>
-      <c r="R24" s="129" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R24" s="92" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="53">
         <f>ROW(B25) - ROW($B$9)</f>
         <v>16</v>
       </c>
       <c r="C25" s="61" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D25" s="37" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="38" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F25" s="37" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G25" s="66">
         <v>885012205080</v>
       </c>
       <c r="H25" s="37" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I25" s="37" t="s">
+        <v>384</v>
+      </c>
+      <c r="J25" s="37" t="s">
         <v>385</v>
       </c>
-      <c r="J25" s="37" t="s">
-        <v>386</v>
-      </c>
       <c r="K25" s="38" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L25" s="37">
         <v>1</v>
@@ -4355,7 +4247,7 @@
         <v>50</v>
       </c>
       <c r="O25" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P25" s="41">
         <v>5.1999999999999998E-3</v>
@@ -4366,38 +4258,38 @@
       </c>
       <c r="R25" s="41"/>
     </row>
-    <row r="26" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="53">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="C26" s="60" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D26" s="39" t="s">
         <v>17</v>
       </c>
       <c r="E26" s="40" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F26" s="39" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G26" s="40" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H26" s="39" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I26" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J26" s="39" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K26" s="40" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L26" s="39">
         <v>1</v>
@@ -4410,7 +4302,7 @@
         <v>100</v>
       </c>
       <c r="O26" s="65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P26" s="42">
         <v>3.2000000000000002E-3</v>
@@ -4421,95 +4313,95 @@
       </c>
       <c r="R26" s="42"/>
     </row>
-    <row r="27" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="53">
         <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
-      <c r="C27" s="130" t="s">
-        <v>341</v>
-      </c>
-      <c r="D27" s="131" t="s">
+      <c r="C27" s="93" t="s">
+        <v>340</v>
+      </c>
+      <c r="D27" s="94" t="s">
         <v>18</v>
       </c>
-      <c r="E27" s="132" t="s">
-        <v>94</v>
-      </c>
-      <c r="F27" s="131" t="s">
-        <v>162</v>
-      </c>
-      <c r="G27" s="132" t="s">
-        <v>211</v>
-      </c>
-      <c r="H27" s="131" t="s">
-        <v>251</v>
-      </c>
-      <c r="I27" s="131" t="s">
-        <v>338</v>
-      </c>
-      <c r="J27" s="131" t="s">
-        <v>388</v>
-      </c>
-      <c r="K27" s="132" t="s">
-        <v>296</v>
-      </c>
-      <c r="L27" s="131">
+      <c r="E27" s="95" t="s">
+        <v>93</v>
+      </c>
+      <c r="F27" s="94" t="s">
+        <v>161</v>
+      </c>
+      <c r="G27" s="95" t="s">
+        <v>210</v>
+      </c>
+      <c r="H27" s="94" t="s">
+        <v>250</v>
+      </c>
+      <c r="I27" s="94" t="s">
+        <v>337</v>
+      </c>
+      <c r="J27" s="94" t="s">
+        <v>387</v>
+      </c>
+      <c r="K27" s="95" t="s">
+        <v>295</v>
+      </c>
+      <c r="L27" s="94">
         <v>1</v>
       </c>
-      <c r="M27" s="133">
+      <c r="M27" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N27" s="133">
+      <c r="N27" s="96">
         <v>0</v>
       </c>
-      <c r="O27" s="134" t="s">
-        <v>368</v>
-      </c>
-      <c r="P27" s="133">
+      <c r="O27" s="97" t="s">
+        <v>367</v>
+      </c>
+      <c r="P27" s="96">
         <v>0.1653</v>
       </c>
-      <c r="Q27" s="133">
+      <c r="Q27" s="96">
         <f t="shared" ref="Q27" si="16">P27*N27</f>
         <v>0</v>
       </c>
-      <c r="R27" s="133" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R27" s="96" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="53">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="C28" s="60" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D28" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="E28" s="137" t="s">
+      <c r="E28" s="100" t="s">
+        <v>480</v>
+      </c>
+      <c r="F28" s="39" t="s">
+        <v>157</v>
+      </c>
+      <c r="G28" s="101" t="s">
+        <v>481</v>
+      </c>
+      <c r="H28" s="102" t="s">
         <v>482</v>
       </c>
-      <c r="F28" s="39" t="s">
-        <v>158</v>
-      </c>
-      <c r="G28" s="138" t="s">
+      <c r="I28" s="39" t="s">
+        <v>337</v>
+      </c>
+      <c r="J28" s="39" t="s">
         <v>483</v>
       </c>
-      <c r="H28" s="139" t="s">
+      <c r="K28" s="40" t="s">
         <v>484</v>
-      </c>
-      <c r="I28" s="39" t="s">
-        <v>338</v>
-      </c>
-      <c r="J28" s="39" t="s">
-        <v>485</v>
-      </c>
-      <c r="K28" s="40" t="s">
-        <v>486</v>
       </c>
       <c r="L28" s="39">
         <v>1</v>
@@ -4522,7 +4414,7 @@
         <v>100</v>
       </c>
       <c r="O28" s="65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P28" s="42">
         <v>3.3999999999999998E-3</v>
@@ -4531,55 +4423,55 @@
         <f t="shared" ref="Q28" si="17">N28*P28</f>
         <v>0.33999999999999997</v>
       </c>
-      <c r="R28" s="129" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R28" s="92" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="53">
         <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
       <c r="C29" s="61" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D29" s="37" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E29" s="38" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F29" s="37" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G29" s="38" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H29" s="37" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I29" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J29" s="37" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="K29" s="38" t="s">
-        <v>297</v>
-      </c>
-      <c r="L29" s="123">
+        <v>296</v>
+      </c>
+      <c r="L29" s="86">
         <v>1</v>
       </c>
       <c r="M29" s="41">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N29" s="135">
+      <c r="N29" s="98">
         <v>30</v>
       </c>
       <c r="O29" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P29" s="41">
         <v>0.2525</v>
@@ -4588,99 +4480,99 @@
         <f t="shared" ref="Q29" si="18">P29*N29</f>
         <v>7.5750000000000002</v>
       </c>
-      <c r="R29" s="136" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R29" s="99" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="53">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="140" t="s">
-        <v>341</v>
-      </c>
-      <c r="D30" s="141" t="s">
+      <c r="C30" s="103" t="s">
+        <v>340</v>
+      </c>
+      <c r="D30" s="104" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="138" t="s">
-        <v>96</v>
-      </c>
-      <c r="F30" s="141" t="s">
-        <v>158</v>
-      </c>
-      <c r="G30" s="138" t="s">
-        <v>213</v>
-      </c>
-      <c r="H30" s="141" t="s">
-        <v>250</v>
-      </c>
-      <c r="I30" s="141" t="s">
-        <v>338</v>
-      </c>
-      <c r="J30" s="141" t="s">
-        <v>390</v>
-      </c>
-      <c r="K30" s="138" t="s">
-        <v>298</v>
-      </c>
-      <c r="L30" s="141">
+      <c r="E30" s="101" t="s">
+        <v>95</v>
+      </c>
+      <c r="F30" s="104" t="s">
+        <v>157</v>
+      </c>
+      <c r="G30" s="101" t="s">
+        <v>212</v>
+      </c>
+      <c r="H30" s="104" t="s">
+        <v>249</v>
+      </c>
+      <c r="I30" s="104" t="s">
+        <v>337</v>
+      </c>
+      <c r="J30" s="104" t="s">
+        <v>389</v>
+      </c>
+      <c r="K30" s="101" t="s">
+        <v>297</v>
+      </c>
+      <c r="L30" s="104">
         <v>1</v>
       </c>
-      <c r="M30" s="142">
+      <c r="M30" s="105">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N30" s="142">
+      <c r="N30" s="105">
         <v>0</v>
       </c>
-      <c r="O30" s="143" t="s">
-        <v>368</v>
-      </c>
-      <c r="P30" s="142">
+      <c r="O30" s="106" t="s">
+        <v>367</v>
+      </c>
+      <c r="P30" s="105">
         <v>4.1999999999999997E-3</v>
       </c>
-      <c r="Q30" s="142">
+      <c r="Q30" s="105">
         <f t="shared" ref="Q30" si="19">N30*P30</f>
         <v>0</v>
       </c>
-      <c r="R30" s="129" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R30" s="92" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="53">
         <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
       <c r="C31" s="61" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D31" s="37" t="s">
         <v>21</v>
       </c>
       <c r="E31" s="38" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F31" s="37" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G31" s="38" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H31" s="37" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I31" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J31" s="37" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="K31" s="38" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L31" s="37">
         <v>1</v>
@@ -4693,7 +4585,7 @@
         <v>22</v>
       </c>
       <c r="O31" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P31" s="41">
         <v>0.89629999999999999</v>
@@ -4704,38 +4596,38 @@
       </c>
       <c r="R31" s="41"/>
     </row>
-    <row r="32" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="53">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="C32" s="60" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D32" s="39" t="s">
         <v>22</v>
       </c>
       <c r="E32" s="40" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F32" s="39" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G32" s="39" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H32" s="39" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I32" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J32" s="39" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="K32" s="40" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L32" s="39">
         <v>1</v>
@@ -4748,7 +4640,7 @@
         <v>21</v>
       </c>
       <c r="O32" s="65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P32" s="42">
         <v>0.47249999999999998</v>
@@ -4759,38 +4651,38 @@
       </c>
       <c r="R32" s="42"/>
     </row>
-    <row r="33" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="53">
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
       <c r="C33" s="61" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D33" s="37" t="s">
         <v>23</v>
       </c>
       <c r="E33" s="38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G33" s="38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H33" s="37" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J33" s="37" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K33" s="38" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L33" s="37">
         <v>1</v>
@@ -4803,7 +4695,7 @@
         <v>100</v>
       </c>
       <c r="O33" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P33" s="41">
         <v>3.0999999999999999E-3</v>
@@ -4814,95 +4706,95 @@
       </c>
       <c r="R33" s="41"/>
     </row>
-    <row r="34" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="53">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="109" t="s">
-        <v>341</v>
-      </c>
-      <c r="D34" s="110" t="s">
+      <c r="C34" s="76" t="s">
+        <v>340</v>
+      </c>
+      <c r="D34" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="E34" s="111" t="s">
-        <v>100</v>
-      </c>
-      <c r="F34" s="110" t="s">
-        <v>160</v>
-      </c>
-      <c r="G34" s="111" t="s">
-        <v>216</v>
-      </c>
-      <c r="H34" s="110" t="s">
-        <v>254</v>
-      </c>
-      <c r="I34" s="110" t="s">
-        <v>395</v>
-      </c>
-      <c r="J34" s="110" t="s">
+      <c r="E34" s="78" t="s">
+        <v>99</v>
+      </c>
+      <c r="F34" s="77" t="s">
+        <v>159</v>
+      </c>
+      <c r="G34" s="78" t="s">
+        <v>215</v>
+      </c>
+      <c r="H34" s="77" t="s">
+        <v>253</v>
+      </c>
+      <c r="I34" s="77" t="s">
         <v>394</v>
       </c>
-      <c r="K34" s="111" t="s">
-        <v>287</v>
-      </c>
-      <c r="L34" s="110">
+      <c r="J34" s="77" t="s">
+        <v>393</v>
+      </c>
+      <c r="K34" s="78" t="s">
+        <v>286</v>
+      </c>
+      <c r="L34" s="77">
         <v>1</v>
       </c>
-      <c r="M34" s="112">
+      <c r="M34" s="79">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N34" s="112">
+      <c r="N34" s="79">
         <v>0</v>
       </c>
-      <c r="O34" s="113" t="s">
-        <v>368</v>
-      </c>
-      <c r="P34" s="112">
+      <c r="O34" s="80" t="s">
+        <v>367</v>
+      </c>
+      <c r="P34" s="79">
         <v>9.1899999999999996E-2</v>
       </c>
-      <c r="Q34" s="112">
+      <c r="Q34" s="79">
         <f t="shared" ref="Q34" si="23">N34*P34</f>
         <v>0</v>
       </c>
-      <c r="R34" s="112" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R34" s="79" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="53">
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
       <c r="C35" s="61" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D35" s="37" t="s">
         <v>25</v>
       </c>
       <c r="E35" s="38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F35" s="37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G35" s="38" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H35" s="37" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I35" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J35" s="37" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K35" s="38" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L35" s="37">
         <v>4</v>
@@ -4915,7 +4807,7 @@
         <v>100</v>
       </c>
       <c r="O35" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P35" s="41">
         <v>5.4999999999999997E-3</v>
@@ -4926,38 +4818,38 @@
       </c>
       <c r="R35" s="41"/>
     </row>
-    <row r="36" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="53">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="C36" s="60" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D36" s="39" t="s">
         <v>26</v>
       </c>
       <c r="E36" s="40" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F36" s="39" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G36" s="40" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H36" s="39" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I36" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J36" s="39" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K36" s="40" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L36" s="39">
         <v>1</v>
@@ -4970,7 +4862,7 @@
         <v>30</v>
       </c>
       <c r="O36" s="65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P36" s="42">
         <v>4.87E-2</v>
@@ -4981,38 +4873,38 @@
       </c>
       <c r="R36" s="42"/>
     </row>
-    <row r="37" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="53">
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
       <c r="C37" s="61" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D37" s="37" t="s">
         <v>27</v>
       </c>
       <c r="E37" s="38" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F37" s="37" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G37" s="38" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H37" s="37" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I37" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J37" s="37" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="K37" s="38" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L37" s="37">
         <v>1</v>
@@ -5025,7 +4917,7 @@
         <v>30</v>
       </c>
       <c r="O37" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P37" s="41">
         <v>7.4300000000000005E-2</v>
@@ -5036,51 +4928,51 @@
       </c>
       <c r="R37" s="41"/>
     </row>
-    <row r="38" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="53">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="C38" s="60" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D38" s="39" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E38" s="40" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F38" s="39" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G38" s="40" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H38" s="39" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I38" s="39" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J38" s="39" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K38" s="40" t="s">
-        <v>338</v>
-      </c>
-      <c r="L38" s="127">
+        <v>337</v>
+      </c>
+      <c r="L38" s="90">
         <v>2</v>
       </c>
       <c r="M38" s="42">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N38" s="128">
+      <c r="N38" s="91">
         <v>60</v>
       </c>
       <c r="O38" s="65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P38" s="42">
         <v>2.8899999999999999E-2</v>
@@ -5089,55 +4981,55 @@
         <f t="shared" ref="Q38" si="27">N38*P38</f>
         <v>1.734</v>
       </c>
-      <c r="R38" s="144" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R38" s="107" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="53">
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
       <c r="C39" s="61" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E39" s="38" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G39" s="38" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H39" s="37" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I39" s="37" t="s">
+        <v>400</v>
+      </c>
+      <c r="J39" s="37" t="s">
         <v>401</v>
       </c>
-      <c r="J39" s="37" t="s">
-        <v>402</v>
-      </c>
       <c r="K39" s="38" t="s">
-        <v>338</v>
-      </c>
-      <c r="L39" s="123">
+        <v>337</v>
+      </c>
+      <c r="L39" s="86">
         <v>9</v>
       </c>
       <c r="M39" s="41">
         <f t="shared" si="1"/>
         <v>180</v>
       </c>
-      <c r="N39" s="135">
+      <c r="N39" s="98">
         <v>190</v>
       </c>
       <c r="O39" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P39" s="41">
         <v>0.12590000000000001</v>
@@ -5146,42 +5038,42 @@
         <f t="shared" ref="Q39" si="28">P39*N39</f>
         <v>23.921000000000003</v>
       </c>
-      <c r="R39" s="136" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R39" s="99" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="53">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="C40" s="60" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D40" s="39" t="s">
         <v>28</v>
       </c>
       <c r="E40" s="40" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F40" s="39" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G40" s="40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H40" s="39" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I40" s="39" t="s">
+        <v>402</v>
+      </c>
+      <c r="J40" s="39" t="s">
         <v>403</v>
       </c>
-      <c r="J40" s="39" t="s">
-        <v>404</v>
-      </c>
       <c r="K40" s="40" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L40" s="39">
         <v>1</v>
@@ -5194,7 +5086,7 @@
         <v>30</v>
       </c>
       <c r="O40" s="65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P40" s="42">
         <v>5.6000000000000001E-2</v>
@@ -5205,38 +5097,38 @@
       </c>
       <c r="R40" s="42"/>
     </row>
-    <row r="41" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="53">
         <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
       <c r="C41" s="61" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D41" s="37" t="s">
         <v>29</v>
       </c>
       <c r="E41" s="38" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F41" s="37" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G41" s="38" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H41" s="37" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I41" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J41" s="37" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="K41" s="38" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L41" s="37">
         <v>4</v>
@@ -5249,7 +5141,7 @@
         <v>100</v>
       </c>
       <c r="O41" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P41" s="41">
         <v>2.9499999999999998E-2</v>
@@ -5260,95 +5152,95 @@
       </c>
       <c r="R41" s="41"/>
     </row>
-    <row r="42" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="53">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="74" t="s">
-        <v>345</v>
-      </c>
-      <c r="D42" s="75" t="s">
+      <c r="C42" s="60" t="s">
+        <v>344</v>
+      </c>
+      <c r="D42" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="E42" s="76" t="s">
-        <v>108</v>
-      </c>
-      <c r="F42" s="75" t="s">
-        <v>332</v>
-      </c>
-      <c r="G42" s="76" t="s">
-        <v>171</v>
-      </c>
-      <c r="H42" s="75" t="s">
-        <v>262</v>
-      </c>
-      <c r="I42" s="75" t="s">
+      <c r="E42" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="F42" s="39" t="s">
+        <v>331</v>
+      </c>
+      <c r="G42" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="H42" s="39" t="s">
+        <v>261</v>
+      </c>
+      <c r="I42" s="39" t="s">
+        <v>405</v>
+      </c>
+      <c r="J42" s="39" t="s">
         <v>406</v>
       </c>
-      <c r="J42" s="75" t="s">
-        <v>407</v>
-      </c>
-      <c r="K42" s="76" t="s">
-        <v>338</v>
-      </c>
-      <c r="L42" s="75">
+      <c r="K42" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="L42" s="39">
         <v>1</v>
       </c>
-      <c r="M42" s="77">
+      <c r="M42" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N42" s="77">
+      <c r="N42" s="42">
         <v>21</v>
       </c>
-      <c r="O42" s="78" t="s">
-        <v>368</v>
-      </c>
-      <c r="P42" s="77">
+      <c r="O42" s="65" t="s">
+        <v>367</v>
+      </c>
+      <c r="P42" s="42">
         <v>0.53559999999999997</v>
       </c>
-      <c r="Q42" s="77">
+      <c r="Q42" s="42">
         <f t="shared" ref="Q42" si="31">N42*P42</f>
         <v>11.247599999999998</v>
       </c>
-      <c r="R42" s="73" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R42" s="107" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="53">
         <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
       </c>
       <c r="C43" s="61" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D43" s="37" t="s">
         <v>31</v>
       </c>
       <c r="E43" s="38" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F43" s="37" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G43" s="38" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H43" s="37" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I43" s="37" t="s">
+        <v>407</v>
+      </c>
+      <c r="J43" s="37" t="s">
         <v>408</v>
       </c>
-      <c r="J43" s="37" t="s">
-        <v>409</v>
-      </c>
       <c r="K43" s="38" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L43" s="37">
         <v>2</v>
@@ -5361,7 +5253,7 @@
         <v>42</v>
       </c>
       <c r="O43" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P43" s="41">
         <v>0.65639999999999998</v>
@@ -5370,42 +5262,42 @@
         <f t="shared" ref="Q43" si="32">P43*N43</f>
         <v>27.5688</v>
       </c>
-      <c r="R43" s="136" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R43" s="99" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="53">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="C44" s="60" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D44" s="39" t="s">
         <v>32</v>
       </c>
       <c r="E44" s="40" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F44" s="39" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G44" s="40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H44" s="39" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I44" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J44" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K44" s="40" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L44" s="39">
         <v>1</v>
@@ -5418,7 +5310,7 @@
         <v>21</v>
       </c>
       <c r="O44" s="65" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="P44" s="42">
         <v>1.2</v>
@@ -5429,38 +5321,38 @@
       </c>
       <c r="R44" s="42"/>
     </row>
-    <row r="45" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="53">
         <f>ROW(B45) - ROW($B$9)</f>
         <v>36</v>
       </c>
       <c r="C45" s="61" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D45" s="37" t="s">
         <v>33</v>
       </c>
       <c r="E45" s="38" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F45" s="37" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G45" s="38" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H45" s="37" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I45" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J45" s="37" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="K45" s="38" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L45" s="37">
         <v>1</v>
@@ -5473,7 +5365,7 @@
         <v>25</v>
       </c>
       <c r="O45" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P45" s="41">
         <v>9.2200000000000004E-2</v>
@@ -5484,38 +5376,38 @@
       </c>
       <c r="R45" s="41"/>
     </row>
-    <row r="46" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="53">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="C46" s="60" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D46" s="39" t="s">
         <v>34</v>
       </c>
       <c r="E46" s="40" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F46" s="39" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G46" s="40" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H46" s="39" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I46" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J46" s="39" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="K46" s="40" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L46" s="39">
         <v>1</v>
@@ -5528,7 +5420,7 @@
         <v>21</v>
       </c>
       <c r="O46" s="65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P46" s="42">
         <v>0.45629999999999998</v>
@@ -5539,38 +5431,38 @@
       </c>
       <c r="R46" s="42"/>
     </row>
-    <row r="47" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="53">
         <f>ROW(B47) - ROW($B$9)</f>
         <v>38</v>
       </c>
       <c r="C47" s="61" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D47" s="37" t="s">
         <v>35</v>
       </c>
       <c r="E47" s="38" t="s">
+        <v>499</v>
+      </c>
+      <c r="F47" s="37" t="s">
+        <v>331</v>
+      </c>
+      <c r="G47" s="38" t="s">
+        <v>500</v>
+      </c>
+      <c r="H47" s="89" t="s">
         <v>501</v>
       </c>
-      <c r="F47" s="37" t="s">
-        <v>332</v>
-      </c>
-      <c r="G47" s="38" t="s">
+      <c r="I47" s="37" t="s">
+        <v>337</v>
+      </c>
+      <c r="J47" s="37" t="s">
         <v>502</v>
       </c>
-      <c r="H47" s="126" t="s">
+      <c r="K47" s="38" t="s">
         <v>503</v>
-      </c>
-      <c r="I47" s="37" t="s">
-        <v>338</v>
-      </c>
-      <c r="J47" s="37" t="s">
-        <v>504</v>
-      </c>
-      <c r="K47" s="38" t="s">
-        <v>505</v>
       </c>
       <c r="L47" s="37">
         <v>1</v>
@@ -5579,11 +5471,11 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N47" s="135">
+      <c r="N47" s="98">
         <v>25</v>
       </c>
       <c r="O47" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P47" s="41">
         <v>0.1012</v>
@@ -5592,42 +5484,42 @@
         <f t="shared" ref="Q47" si="36">P47*N47</f>
         <v>2.5299999999999998</v>
       </c>
-      <c r="R47" s="124" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R47" s="87" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="53">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="C48" s="60" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D48" s="39" t="s">
         <v>36</v>
       </c>
       <c r="E48" s="40" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F48" s="39" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G48" s="40" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H48" s="39" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I48" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J48" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K48" s="40" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L48" s="39">
         <v>1</v>
@@ -5640,7 +5532,7 @@
         <v>30</v>
       </c>
       <c r="O48" s="65" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="P48" s="42">
         <v>0.156</v>
@@ -5651,38 +5543,38 @@
       </c>
       <c r="R48" s="42"/>
     </row>
-    <row r="49" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="53">
         <f>ROW(B49) - ROW($B$9)</f>
         <v>40</v>
       </c>
       <c r="C49" s="61" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D49" s="37" t="s">
         <v>37</v>
       </c>
       <c r="E49" s="38" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F49" s="37" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G49" s="38" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H49" s="37" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I49" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J49" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K49" s="38" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L49" s="37">
         <v>1</v>
@@ -5695,7 +5587,7 @@
         <v>30</v>
       </c>
       <c r="O49" s="64" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="P49" s="41">
         <v>0.08</v>
@@ -5706,38 +5598,38 @@
       </c>
       <c r="R49" s="41"/>
     </row>
-    <row r="50" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="53">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="C50" s="60" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D50" s="39" t="s">
         <v>38</v>
       </c>
       <c r="E50" s="40" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F50" s="39" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G50" s="40" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H50" s="39" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I50" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J50" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K50" s="40" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L50" s="39">
         <v>2</v>
@@ -5750,7 +5642,7 @@
         <v>50</v>
       </c>
       <c r="O50" s="65" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="P50" s="42">
         <v>1.5</v>
@@ -5760,91 +5652,91 @@
         <v>75</v>
       </c>
       <c r="R50" s="42" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
-      <c r="B51" s="79">
+      <c r="B51" s="53">
         <f>ROW(B51) - ROW($B$9)</f>
         <v>42</v>
       </c>
-      <c r="C51" s="80" t="s">
-        <v>306</v>
-      </c>
-      <c r="D51" s="81" t="s">
+      <c r="C51" s="67" t="s">
+        <v>305</v>
+      </c>
+      <c r="D51" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="E51" s="82" t="s">
-        <v>116</v>
-      </c>
-      <c r="F51" s="81" t="s">
-        <v>179</v>
-      </c>
-      <c r="G51" s="82" t="s">
-        <v>338</v>
-      </c>
-      <c r="H51" s="81" t="s">
-        <v>338</v>
-      </c>
-      <c r="I51" s="81"/>
-      <c r="J51" s="81"/>
-      <c r="K51" s="82" t="s">
-        <v>338</v>
-      </c>
-      <c r="L51" s="81">
+      <c r="E51" s="69" t="s">
+        <v>115</v>
+      </c>
+      <c r="F51" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="G51" s="69" t="s">
+        <v>337</v>
+      </c>
+      <c r="H51" s="68" t="s">
+        <v>337</v>
+      </c>
+      <c r="I51" s="68"/>
+      <c r="J51" s="68"/>
+      <c r="K51" s="69" t="s">
+        <v>337</v>
+      </c>
+      <c r="L51" s="68">
         <v>4</v>
       </c>
-      <c r="M51" s="83">
+      <c r="M51" s="70">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N51" s="83">
+      <c r="N51" s="70">
         <f t="shared" ref="N51" si="40">M51+(M51*0.1)</f>
         <v>88</v>
       </c>
-      <c r="O51" s="83"/>
-      <c r="P51" s="83"/>
-      <c r="Q51" s="83">
+      <c r="O51" s="70"/>
+      <c r="P51" s="70"/>
+      <c r="Q51" s="70">
         <f t="shared" ref="Q51" si="41">P51*N51</f>
         <v>0</v>
       </c>
-      <c r="R51" s="84" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R51" s="71" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="53">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="C52" s="60" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D52" s="39" t="s">
         <v>40</v>
       </c>
       <c r="E52" s="40" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F52" s="39" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G52" s="40">
         <v>61300211121</v>
       </c>
       <c r="H52" s="39" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I52" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J52" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K52" s="40" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L52" s="39">
         <v>4</v>
@@ -5857,7 +5749,7 @@
         <v>90</v>
       </c>
       <c r="O52" s="65" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="P52" s="42">
         <v>0.13</v>
@@ -5867,98 +5759,98 @@
         <v>11.700000000000001</v>
       </c>
       <c r="R52" s="42" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
-      <c r="B53" s="67">
+      <c r="B53" s="53">
         <f>ROW(B53) - ROW($B$9)</f>
         <v>44</v>
       </c>
-      <c r="C53" s="68" t="s">
-        <v>348</v>
-      </c>
-      <c r="D53" s="69" t="s">
-        <v>41</v>
-      </c>
-      <c r="E53" s="70" t="s">
-        <v>118</v>
-      </c>
-      <c r="F53" s="69" t="s">
-        <v>181</v>
-      </c>
-      <c r="G53" s="70" t="s">
-        <v>220</v>
-      </c>
-      <c r="H53" s="69" t="s">
-        <v>269</v>
-      </c>
-      <c r="I53" s="69" t="s">
+      <c r="C53" s="61" t="s">
+        <v>347</v>
+      </c>
+      <c r="D53" s="37" t="s">
+        <v>511</v>
+      </c>
+      <c r="E53" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="F53" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="G53" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="H53" s="37" t="s">
+        <v>268</v>
+      </c>
+      <c r="I53" s="37" t="s">
+        <v>416</v>
+      </c>
+      <c r="J53" s="37" t="s">
         <v>417</v>
       </c>
-      <c r="J53" s="69" t="s">
-        <v>418</v>
-      </c>
-      <c r="K53" s="70" t="s">
-        <v>338</v>
-      </c>
-      <c r="L53" s="106">
+      <c r="K53" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="L53" s="86">
         <v>4</v>
       </c>
-      <c r="M53" s="71">
+      <c r="M53" s="41">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N53" s="71">
+      <c r="N53" s="41">
         <v>85</v>
       </c>
-      <c r="O53" s="72" t="s">
-        <v>368</v>
-      </c>
-      <c r="P53" s="71">
+      <c r="O53" s="64" t="s">
+        <v>367</v>
+      </c>
+      <c r="P53" s="41">
         <v>0.21740000000000001</v>
       </c>
-      <c r="Q53" s="71">
+      <c r="Q53" s="41">
         <f t="shared" ref="Q53" si="43">P53*N53</f>
         <v>18.478999999999999</v>
       </c>
-      <c r="R53" s="71" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R53" s="41" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="53">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="C54" s="60" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D54" s="39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E54" s="40" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F54" s="39" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G54" s="40" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H54" s="39" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I54" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J54" s="39" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="K54" s="40" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L54" s="39">
         <v>2</v>
@@ -5971,7 +5863,7 @@
         <v>100</v>
       </c>
       <c r="O54" s="65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P54" s="42">
         <v>1E-3</v>
@@ -5982,38 +5874,38 @@
       </c>
       <c r="R54" s="42"/>
     </row>
-    <row r="55" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="53">
         <f>ROW(B55) - ROW($B$9)</f>
         <v>46</v>
       </c>
       <c r="C55" s="61" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D55" s="37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E55" s="38" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F55" s="37" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G55" s="38" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H55" s="37" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I55" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J55" s="37" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="K55" s="38" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L55" s="37">
         <v>1</v>
@@ -6026,7 +5918,7 @@
         <v>100</v>
       </c>
       <c r="O55" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P55" s="41">
         <v>1.4E-3</v>
@@ -6037,38 +5929,38 @@
       </c>
       <c r="R55" s="41"/>
     </row>
-    <row r="56" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="53">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="C56" s="60" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D56" s="39" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E56" s="40" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F56" s="39" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G56" s="40" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H56" s="39" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I56" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J56" s="39" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="K56" s="40" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L56" s="39">
         <v>1</v>
@@ -6081,7 +5973,7 @@
         <v>100</v>
       </c>
       <c r="O56" s="65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P56" s="42">
         <v>1.6000000000000001E-3</v>
@@ -6092,38 +5984,38 @@
       </c>
       <c r="R56" s="42"/>
     </row>
-    <row r="57" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="53">
         <f>ROW(B57) - ROW($B$9)</f>
         <v>48</v>
       </c>
       <c r="C57" s="61" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D57" s="37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E57" s="38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F57" s="37" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G57" s="38" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H57" s="37" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I57" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J57" s="37" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="K57" s="38" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="L57" s="37">
         <v>2</v>
@@ -6136,7 +6028,7 @@
         <v>100</v>
       </c>
       <c r="O57" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P57" s="41">
         <v>1.4E-3</v>
@@ -6147,38 +6039,38 @@
       </c>
       <c r="R57" s="41"/>
     </row>
-    <row r="58" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="53">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="C58" s="60" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D58" s="39" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E58" s="40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F58" s="39" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G58" s="40" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H58" s="39" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I58" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J58" s="39" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="K58" s="40" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L58" s="39">
         <v>4</v>
@@ -6191,7 +6083,7 @@
         <v>100</v>
       </c>
       <c r="O58" s="65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P58" s="42">
         <v>1.2999999999999999E-3</v>
@@ -6202,38 +6094,38 @@
       </c>
       <c r="R58" s="42"/>
     </row>
-    <row r="59" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="53">
         <f>ROW(B59) - ROW($B$9)</f>
         <v>50</v>
       </c>
       <c r="C59" s="61" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D59" s="37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E59" s="38" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F59" s="37" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G59" s="38" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H59" s="37" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I59" s="37" t="s">
+        <v>424</v>
+      </c>
+      <c r="J59" s="37" t="s">
         <v>425</v>
       </c>
-      <c r="J59" s="37" t="s">
-        <v>426</v>
-      </c>
       <c r="K59" s="38" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="L59" s="37">
         <v>4</v>
@@ -6246,7 +6138,7 @@
         <v>90</v>
       </c>
       <c r="O59" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P59" s="41">
         <v>6.4500000000000002E-2</v>
@@ -6257,150 +6149,150 @@
       </c>
       <c r="R59" s="41"/>
     </row>
-    <row r="60" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
-      <c r="B60" s="85">
+      <c r="B60" s="53">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="C60" s="92" t="s">
-        <v>349</v>
-      </c>
-      <c r="D60" s="101" t="s">
-        <v>461</v>
-      </c>
-      <c r="E60" s="94" t="s">
-        <v>125</v>
-      </c>
-      <c r="F60" s="93" t="s">
-        <v>182</v>
-      </c>
-      <c r="G60" s="94" t="s">
-        <v>226</v>
-      </c>
-      <c r="H60" s="93" t="s">
-        <v>250</v>
-      </c>
-      <c r="I60" s="93"/>
-      <c r="J60" s="93" t="s">
-        <v>427</v>
-      </c>
-      <c r="K60" s="94" t="s">
-        <v>313</v>
-      </c>
-      <c r="L60" s="104">
+      <c r="C60" s="60" t="s">
+        <v>348</v>
+      </c>
+      <c r="D60" s="102" t="s">
+        <v>460</v>
+      </c>
+      <c r="E60" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="F60" s="39" t="s">
+        <v>181</v>
+      </c>
+      <c r="G60" s="40" t="s">
+        <v>225</v>
+      </c>
+      <c r="H60" s="39" t="s">
+        <v>249</v>
+      </c>
+      <c r="I60" s="39"/>
+      <c r="J60" s="39" t="s">
+        <v>426</v>
+      </c>
+      <c r="K60" s="40" t="s">
+        <v>312</v>
+      </c>
+      <c r="L60" s="90">
         <v>1</v>
       </c>
-      <c r="M60" s="95">
+      <c r="M60" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N60" s="103">
+      <c r="N60" s="91">
         <v>100</v>
       </c>
-      <c r="O60" s="96" t="s">
-        <v>368</v>
-      </c>
-      <c r="P60" s="95">
+      <c r="O60" s="65" t="s">
+        <v>367</v>
+      </c>
+      <c r="P60" s="42">
         <v>1.5E-3</v>
       </c>
-      <c r="Q60" s="95">
+      <c r="Q60" s="42">
         <f t="shared" ref="Q60:Q61" si="50">N60*P60</f>
         <v>0.15</v>
       </c>
-      <c r="R60" s="102" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="61" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R60" s="92" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
-      <c r="B61" s="85">
+      <c r="B61" s="53">
         <f>ROW(B61) - ROW($B$9)</f>
         <v>52</v>
       </c>
-      <c r="C61" s="86" t="s">
-        <v>349</v>
-      </c>
-      <c r="D61" s="87" t="s">
-        <v>460</v>
-      </c>
-      <c r="E61" s="87" t="s">
+      <c r="C61" s="61" t="s">
+        <v>348</v>
+      </c>
+      <c r="D61" s="37" t="s">
+        <v>459</v>
+      </c>
+      <c r="E61" s="37" t="s">
+        <v>512</v>
+      </c>
+      <c r="F61" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="G61" s="37" t="s">
+        <v>462</v>
+      </c>
+      <c r="H61" s="37" t="s">
+        <v>272</v>
+      </c>
+      <c r="I61" s="37" t="s">
+        <v>337</v>
+      </c>
+      <c r="J61" s="37" t="s">
         <v>463</v>
       </c>
-      <c r="F61" s="87" t="s">
-        <v>182</v>
-      </c>
-      <c r="G61" s="87" t="s">
+      <c r="K61" s="37" t="s">
         <v>464</v>
       </c>
-      <c r="H61" s="87" t="s">
-        <v>273</v>
-      </c>
-      <c r="I61" s="87" t="s">
-        <v>338</v>
-      </c>
-      <c r="J61" s="87" t="s">
-        <v>465</v>
-      </c>
-      <c r="K61" s="87" t="s">
-        <v>466</v>
-      </c>
-      <c r="L61" s="105">
+      <c r="L61" s="86">
         <v>8</v>
       </c>
-      <c r="M61" s="87">
+      <c r="M61" s="37">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="N61" s="103">
+      <c r="N61" s="112">
         <v>100</v>
       </c>
-      <c r="O61" s="107" t="s">
-        <v>368</v>
-      </c>
-      <c r="P61" s="87">
+      <c r="O61" s="113" t="s">
+        <v>367</v>
+      </c>
+      <c r="P61" s="37">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="Q61" s="87">
+      <c r="Q61" s="37">
         <f t="shared" si="50"/>
         <v>0.11</v>
       </c>
-      <c r="R61" s="102" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R61" s="87" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="53">
         <f>ROW(B62) - ROW($B$9)</f>
         <v>53</v>
       </c>
       <c r="C62" s="61" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D62" s="37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E62" s="38" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F62" s="37" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G62" s="38" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H62" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I62" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J62" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K62" s="38" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L62" s="37">
         <v>1</v>
@@ -6413,7 +6305,7 @@
         <v>30</v>
       </c>
       <c r="O62" s="64" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="P62" s="41">
         <v>1.8589999999999999E-2</v>
@@ -6424,38 +6316,38 @@
       </c>
       <c r="R62" s="41"/>
     </row>
-    <row r="63" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="53">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
       <c r="C63" s="60" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D63" s="39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E63" s="40" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F63" s="39" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G63" s="40" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H63" s="39" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I63" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J63" s="39" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="K63" s="40" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L63" s="39">
         <v>1</v>
@@ -6468,7 +6360,7 @@
         <v>100</v>
       </c>
       <c r="O63" s="65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P63" s="42">
         <v>1.4E-3</v>
@@ -6479,38 +6371,38 @@
       </c>
       <c r="R63" s="42"/>
     </row>
-    <row r="64" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="53">
         <f>ROW(B64) - ROW($B$9)</f>
         <v>55</v>
       </c>
       <c r="C64" s="61" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D64" s="37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E64" s="38" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F64" s="37" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G64" s="38" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H64" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I64" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J64" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K64" s="38" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="L64" s="37">
         <v>1</v>
@@ -6523,7 +6415,7 @@
         <v>50</v>
       </c>
       <c r="O64" s="64" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="P64" s="41">
         <v>4.6699999999999997E-3</v>
@@ -6534,38 +6426,38 @@
       </c>
       <c r="R64" s="41"/>
     </row>
-    <row r="65" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="53">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="C65" s="60" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D65" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E65" s="40" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F65" s="39" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G65" s="40" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H65" s="39" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I65" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J65" s="39" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="K65" s="40" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L65" s="39">
         <v>1</v>
@@ -6578,7 +6470,7 @@
         <v>100</v>
       </c>
       <c r="O65" s="65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P65" s="42">
         <v>1.1999999999999999E-3</v>
@@ -6589,38 +6481,38 @@
       </c>
       <c r="R65" s="42"/>
     </row>
-    <row r="66" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="53">
         <f>ROW(B66) - ROW($B$9)</f>
         <v>57</v>
       </c>
       <c r="C66" s="61" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D66" s="37" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E66" s="38" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F66" s="37" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G66" s="38" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H66" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I66" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J66" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K66" s="38" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L66" s="37">
         <v>1</v>
@@ -6633,7 +6525,7 @@
         <v>50</v>
       </c>
       <c r="O66" s="64" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="P66" s="41">
         <v>1.11E-2</v>
@@ -6644,38 +6536,38 @@
       </c>
       <c r="R66" s="41"/>
     </row>
-    <row r="67" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="53">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="C67" s="60" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D67" s="39" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E67" s="40" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F67" s="39" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G67" s="40" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H67" s="39" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I67" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J67" s="39" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="K67" s="40" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="L67" s="39">
         <v>1</v>
@@ -6688,7 +6580,7 @@
         <v>100</v>
       </c>
       <c r="O67" s="65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P67" s="42">
         <v>2.0999999999999999E-3</v>
@@ -6699,38 +6591,38 @@
       </c>
       <c r="R67" s="42"/>
     </row>
-    <row r="68" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="53">
         <f>ROW(B68) - ROW($B$9)</f>
         <v>59</v>
       </c>
       <c r="C68" s="61" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D68" s="37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E68" s="38" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F68" s="37" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G68" s="38" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H68" s="37" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I68" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J68" s="37" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="K68" s="38" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L68" s="37">
         <v>1</v>
@@ -6743,7 +6635,7 @@
         <v>100</v>
       </c>
       <c r="O68" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P68" s="41">
         <v>1.6000000000000001E-3</v>
@@ -6754,38 +6646,38 @@
       </c>
       <c r="R68" s="41"/>
     </row>
-    <row r="69" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="53">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="C69" s="60" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D69" s="39" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E69" s="40" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F69" s="39" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G69" s="40" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H69" s="39" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I69" s="39" t="s">
+        <v>431</v>
+      </c>
+      <c r="J69" s="39" t="s">
         <v>432</v>
       </c>
-      <c r="J69" s="39" t="s">
-        <v>433</v>
-      </c>
       <c r="K69" s="40" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L69" s="39">
         <v>1</v>
@@ -6798,7 +6690,7 @@
         <v>50</v>
       </c>
       <c r="O69" s="65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P69" s="42">
         <v>6.8999999999999999E-3</v>
@@ -6809,40 +6701,40 @@
       </c>
       <c r="R69" s="42"/>
     </row>
-    <row r="70" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="53">
         <f>ROW(B70) - ROW($B$9)</f>
         <v>61</v>
       </c>
       <c r="C70" s="61" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D70" s="37" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E70" s="38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F70" s="37" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G70" s="38" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H70" s="37" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I70" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J70" s="37" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="K70" s="38" t="s">
-        <v>322</v>
-      </c>
-      <c r="L70" s="123">
+        <v>321</v>
+      </c>
+      <c r="L70" s="86">
         <v>2</v>
       </c>
       <c r="M70" s="41">
@@ -6853,7 +6745,7 @@
         <v>100</v>
       </c>
       <c r="O70" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P70" s="41">
         <v>1.1000000000000001E-3</v>
@@ -6863,41 +6755,41 @@
         <v>0.11</v>
       </c>
       <c r="R70" s="41" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="71" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="53">
         <f>ROW(B71) - ROW($B$9)</f>
         <v>62</v>
       </c>
       <c r="C71" s="61" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D71" s="37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E71" s="38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F71" s="37" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G71" s="38" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H71" s="37" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I71" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J71" s="37" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K71" s="38" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L71" s="37">
         <v>2</v>
@@ -6910,7 +6802,7 @@
         <v>100</v>
       </c>
       <c r="O71" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P71" s="41">
         <v>1.5E-3</v>
@@ -6921,38 +6813,38 @@
       </c>
       <c r="R71" s="41"/>
     </row>
-    <row r="72" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="53">
         <f>ROW(B72) - ROW($B$9)</f>
         <v>63</v>
       </c>
       <c r="C72" s="61" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D72" s="37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E72" s="38" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F72" s="37" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G72" s="38" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H72" s="37" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I72" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J72" s="37" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K72" s="38" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L72" s="37">
         <v>2</v>
@@ -6965,7 +6857,7 @@
         <v>100</v>
       </c>
       <c r="O72" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P72" s="41">
         <v>1.5E-3</v>
@@ -6976,38 +6868,38 @@
       </c>
       <c r="R72" s="41"/>
     </row>
-    <row r="73" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="53">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="C73" s="60" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D73" s="39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E73" s="40" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F73" s="39" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G73" s="40" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H73" s="39" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I73" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J73" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K73" s="40" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L73" s="39">
         <v>1</v>
@@ -7020,7 +6912,7 @@
         <v>25</v>
       </c>
       <c r="O73" s="65" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="P73" s="42">
         <v>8.5400000000000004E-2</v>
@@ -7031,38 +6923,38 @@
       </c>
       <c r="R73" s="42"/>
     </row>
-    <row r="74" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
-      <c r="B74" s="85">
+      <c r="B74" s="53">
         <f>ROW(B74) - ROW($B$9)</f>
         <v>65</v>
       </c>
       <c r="C74" s="61" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D74" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="E74" s="125" t="s">
+        <v>58</v>
+      </c>
+      <c r="E74" s="88" t="s">
+        <v>493</v>
+      </c>
+      <c r="F74" s="108" t="s">
+        <v>494</v>
+      </c>
+      <c r="G74" s="38" t="s">
         <v>495</v>
       </c>
-      <c r="F74" s="145" t="s">
+      <c r="H74" s="89" t="s">
+        <v>272</v>
+      </c>
+      <c r="I74" s="37" t="s">
+        <v>337</v>
+      </c>
+      <c r="J74" s="37" t="s">
         <v>496</v>
       </c>
-      <c r="G74" s="38" t="s">
+      <c r="K74" s="38" t="s">
         <v>497</v>
-      </c>
-      <c r="H74" s="126" t="s">
-        <v>273</v>
-      </c>
-      <c r="I74" s="37" t="s">
-        <v>338</v>
-      </c>
-      <c r="J74" s="37" t="s">
-        <v>498</v>
-      </c>
-      <c r="K74" s="38" t="s">
-        <v>499</v>
       </c>
       <c r="L74" s="37">
         <v>1</v>
@@ -7071,11 +6963,11 @@
         <f t="shared" ref="M74:M92" si="63">L74*20</f>
         <v>20</v>
       </c>
-      <c r="N74" s="135">
+      <c r="N74" s="98">
         <v>50</v>
       </c>
       <c r="O74" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P74" s="41">
         <v>3.8E-3</v>
@@ -7084,99 +6976,99 @@
         <f t="shared" ref="Q74" si="64">P74*N74</f>
         <v>0.19</v>
       </c>
-      <c r="R74" s="124" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="75" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R74" s="87" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
-      <c r="B75" s="108">
+      <c r="B75" s="53">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="C75" s="140" t="s">
-        <v>349</v>
-      </c>
-      <c r="D75" s="141" t="s">
-        <v>60</v>
-      </c>
-      <c r="E75" s="138" t="s">
-        <v>138</v>
-      </c>
-      <c r="F75" s="141" t="s">
-        <v>182</v>
-      </c>
-      <c r="G75" s="138" t="s">
-        <v>239</v>
-      </c>
-      <c r="H75" s="141" t="s">
-        <v>272</v>
-      </c>
-      <c r="I75" s="141" t="s">
-        <v>338</v>
-      </c>
-      <c r="J75" s="141" t="s">
-        <v>338</v>
-      </c>
-      <c r="K75" s="138" t="s">
-        <v>326</v>
-      </c>
-      <c r="L75" s="141">
+      <c r="C75" s="103" t="s">
+        <v>348</v>
+      </c>
+      <c r="D75" s="104" t="s">
+        <v>59</v>
+      </c>
+      <c r="E75" s="101" t="s">
+        <v>137</v>
+      </c>
+      <c r="F75" s="104" t="s">
+        <v>181</v>
+      </c>
+      <c r="G75" s="101" t="s">
+        <v>238</v>
+      </c>
+      <c r="H75" s="104" t="s">
+        <v>271</v>
+      </c>
+      <c r="I75" s="104" t="s">
+        <v>337</v>
+      </c>
+      <c r="J75" s="104" t="s">
+        <v>337</v>
+      </c>
+      <c r="K75" s="101" t="s">
+        <v>325</v>
+      </c>
+      <c r="L75" s="104">
         <v>1</v>
       </c>
-      <c r="M75" s="142">
+      <c r="M75" s="105">
         <f t="shared" si="63"/>
         <v>20</v>
       </c>
-      <c r="N75" s="142">
+      <c r="N75" s="105">
         <v>0</v>
       </c>
-      <c r="O75" s="143" t="s">
-        <v>413</v>
-      </c>
-      <c r="P75" s="142">
+      <c r="O75" s="106" t="s">
+        <v>412</v>
+      </c>
+      <c r="P75" s="105">
         <v>1.8589999999999999E-2</v>
       </c>
-      <c r="Q75" s="142">
+      <c r="Q75" s="105">
         <f t="shared" ref="Q75" si="65">N75*P75</f>
         <v>0</v>
       </c>
-      <c r="R75" s="129" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="76" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R75" s="92" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="53">
         <f>ROW(B76) - ROW($B$9)</f>
         <v>67</v>
       </c>
       <c r="C76" s="61" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D76" s="37" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E76" s="38" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F76" s="37" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G76" s="38" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H76" s="37" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I76" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J76" s="37" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K76" s="38" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L76" s="37">
         <v>1</v>
@@ -7189,7 +7081,7 @@
         <v>100</v>
       </c>
       <c r="O76" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P76" s="41">
         <v>1E-3</v>
@@ -7200,38 +7092,38 @@
       </c>
       <c r="R76" s="41"/>
     </row>
-    <row r="77" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="53">
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
       <c r="C77" s="60" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D77" s="39" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E77" s="40" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F77" s="39" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G77" s="40" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H77" s="39" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I77" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J77" s="39" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K77" s="40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="L77" s="39">
         <v>1</v>
@@ -7244,7 +7136,7 @@
         <v>50</v>
       </c>
       <c r="O77" s="65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P77" s="42">
         <v>4.3E-3</v>
@@ -7255,38 +7147,38 @@
       </c>
       <c r="R77" s="42"/>
     </row>
-    <row r="78" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="53">
         <f>ROW(B78) - ROW($B$9)</f>
         <v>69</v>
       </c>
       <c r="C78" s="61" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D78" s="37" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E78" s="38" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F78" s="37" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G78" s="38" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H78" s="37" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I78" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J78" s="37" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="K78" s="38" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L78" s="37">
         <v>4</v>
@@ -7299,7 +7191,7 @@
         <v>100</v>
       </c>
       <c r="O78" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P78" s="41">
         <v>1.1999999999999999E-3</v>
@@ -7310,38 +7202,38 @@
       </c>
       <c r="R78" s="41"/>
     </row>
-    <row r="79" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
-      <c r="B79" s="85">
+      <c r="B79" s="53">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
       <c r="C79" s="60" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D79" s="39" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E79" s="40" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F79" s="39" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G79" s="40" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H79" s="39" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I79" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J79" s="39" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="K79" s="40" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L79" s="39">
         <v>6</v>
@@ -7354,7 +7246,7 @@
         <v>200</v>
       </c>
       <c r="O79" s="65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P79" s="42">
         <v>1.1999999999999999E-3</v>
@@ -7363,94 +7255,94 @@
         <f t="shared" ref="Q79" si="69">N79*P79</f>
         <v>0.24</v>
       </c>
-      <c r="R79" s="129" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="80" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R79" s="92" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
-      <c r="B80" s="79">
+      <c r="B80" s="53">
         <f>ROW(B80) - ROW($B$9)</f>
         <v>71</v>
       </c>
-      <c r="C80" s="80" t="s">
-        <v>185</v>
-      </c>
-      <c r="D80" s="81" t="s">
-        <v>64</v>
-      </c>
-      <c r="E80" s="82" t="s">
-        <v>143</v>
-      </c>
-      <c r="F80" s="81" t="s">
-        <v>185</v>
-      </c>
-      <c r="G80" s="82" t="s">
-        <v>338</v>
-      </c>
-      <c r="H80" s="81" t="s">
-        <v>338</v>
-      </c>
-      <c r="I80" s="81" t="s">
-        <v>338</v>
-      </c>
-      <c r="J80" s="81" t="s">
-        <v>338</v>
-      </c>
-      <c r="K80" s="82" t="s">
-        <v>338</v>
-      </c>
-      <c r="L80" s="81">
+      <c r="C80" s="67" t="s">
+        <v>184</v>
+      </c>
+      <c r="D80" s="68" t="s">
+        <v>63</v>
+      </c>
+      <c r="E80" s="69" t="s">
+        <v>142</v>
+      </c>
+      <c r="F80" s="68" t="s">
+        <v>184</v>
+      </c>
+      <c r="G80" s="69" t="s">
+        <v>337</v>
+      </c>
+      <c r="H80" s="68" t="s">
+        <v>337</v>
+      </c>
+      <c r="I80" s="68" t="s">
+        <v>337</v>
+      </c>
+      <c r="J80" s="68" t="s">
+        <v>337</v>
+      </c>
+      <c r="K80" s="69" t="s">
+        <v>337</v>
+      </c>
+      <c r="L80" s="68">
         <v>11</v>
       </c>
-      <c r="M80" s="83">
+      <c r="M80" s="70">
         <f t="shared" si="63"/>
         <v>220</v>
       </c>
-      <c r="N80" s="83">
+      <c r="N80" s="70">
         <f t="shared" ref="N80:N81" si="70">M80+(M80*0.1)</f>
         <v>242</v>
       </c>
-      <c r="O80" s="83"/>
-      <c r="P80" s="83"/>
-      <c r="Q80" s="83">
+      <c r="O80" s="70"/>
+      <c r="P80" s="70"/>
+      <c r="Q80" s="70">
         <f t="shared" ref="Q80" si="71">P80*N80</f>
         <v>0</v>
       </c>
-      <c r="R80" s="84" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="81" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R80" s="71" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="53">
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
       <c r="C81" s="60" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D81" s="39" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E81" s="40" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F81" s="39" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G81" s="40"/>
       <c r="H81" s="39" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I81" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J81" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K81" s="40" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L81" s="39">
         <v>1</v>
@@ -7471,38 +7363,38 @@
       </c>
       <c r="R81" s="42"/>
     </row>
-    <row r="82" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="53">
         <f>ROW(B82) - ROW($B$9)</f>
         <v>73</v>
       </c>
       <c r="C82" s="61" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D82" s="37" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E82" s="38" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F82" s="37" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G82" s="38">
         <v>750314597</v>
       </c>
       <c r="H82" s="37" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I82" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J82" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K82" s="38" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L82" s="37">
         <v>1</v>
@@ -7515,7 +7407,7 @@
         <v>21</v>
       </c>
       <c r="O82" s="64" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="P82" s="41">
         <v>3.81</v>
@@ -7526,38 +7418,38 @@
       </c>
       <c r="R82" s="41"/>
     </row>
-    <row r="83" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="53">
         <f t="shared" si="0"/>
         <v>74</v>
       </c>
       <c r="C83" s="60" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D83" s="39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E83" s="40" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F83" s="39" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G83" s="40" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H83" s="39" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I83" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J83" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K83" s="40" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L83" s="39">
         <v>1</v>
@@ -7570,7 +7462,7 @@
         <v>21</v>
       </c>
       <c r="O83" s="65" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="P83" s="42">
         <v>2.48</v>
@@ -7581,38 +7473,38 @@
       </c>
       <c r="R83" s="42"/>
     </row>
-    <row r="84" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
-      <c r="B84" s="85">
+      <c r="B84" s="53">
         <f>ROW(B84) - ROW($B$9)</f>
         <v>75</v>
       </c>
       <c r="C84" s="61" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D84" s="37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E84" s="38" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F84" s="37" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G84" s="38" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H84" s="37" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I84" s="37" t="s">
+        <v>444</v>
+      </c>
+      <c r="J84" s="37" t="s">
         <v>445</v>
       </c>
-      <c r="J84" s="37" t="s">
-        <v>446</v>
-      </c>
       <c r="K84" s="38" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L84" s="37">
         <v>1</v>
@@ -7625,7 +7517,7 @@
         <v>21</v>
       </c>
       <c r="O84" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P84" s="41">
         <v>1.3939999999999999</v>
@@ -7634,42 +7526,42 @@
         <f t="shared" ref="Q84" si="75">P84*N84</f>
         <v>29.273999999999997</v>
       </c>
-      <c r="R84" s="136" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="85" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R84" s="99" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
-      <c r="B85" s="85">
+      <c r="B85" s="53">
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
       <c r="C85" s="60" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D85" s="39" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E85" s="40" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F85" s="39" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G85" s="40" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H85" s="39" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I85" s="39" t="s">
+        <v>447</v>
+      </c>
+      <c r="J85" s="39" t="s">
         <v>448</v>
       </c>
-      <c r="J85" s="39" t="s">
-        <v>449</v>
-      </c>
       <c r="K85" s="40" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L85" s="39">
         <v>1</v>
@@ -7682,7 +7574,7 @@
         <v>21</v>
       </c>
       <c r="O85" s="65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P85" s="42">
         <v>0.69430000000000003</v>
@@ -7691,42 +7583,42 @@
         <f t="shared" ref="Q85" si="76">N85*P85</f>
         <v>14.580300000000001</v>
       </c>
-      <c r="R85" s="144" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="86" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R85" s="107" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="53">
         <f>ROW(B86) - ROW($B$9)</f>
         <v>77</v>
       </c>
       <c r="C86" s="61" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D86" s="37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E86" s="38" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F86" s="37" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G86" s="38" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H86" s="37" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I86" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J86" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K86" s="38" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L86" s="37">
         <v>1</v>
@@ -7739,7 +7631,7 @@
         <v>21</v>
       </c>
       <c r="O86" s="64" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="P86" s="41">
         <v>3.637</v>
@@ -7750,38 +7642,38 @@
       </c>
       <c r="R86" s="41"/>
     </row>
-    <row r="87" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="53">
         <f t="shared" si="0"/>
         <v>78</v>
       </c>
       <c r="C87" s="60" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D87" s="39" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E87" s="40" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F87" s="39" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G87" s="40" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H87" s="39" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I87" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J87" s="39" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="K87" s="40" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L87" s="39">
         <v>1</v>
@@ -7794,7 +7686,7 @@
         <v>21</v>
       </c>
       <c r="O87" s="65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P87" s="42">
         <v>0.43280000000000002</v>
@@ -7805,95 +7697,95 @@
       </c>
       <c r="R87" s="42"/>
     </row>
-    <row r="88" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
-      <c r="B88" s="114">
+      <c r="B88" s="53">
         <f>ROW(B88) - ROW($B$9)</f>
         <v>79</v>
       </c>
-      <c r="C88" s="115" t="s">
-        <v>353</v>
-      </c>
-      <c r="D88" s="116" t="s">
-        <v>72</v>
-      </c>
-      <c r="E88" s="117" t="s">
-        <v>151</v>
-      </c>
-      <c r="F88" s="116" t="s">
-        <v>192</v>
-      </c>
-      <c r="G88" s="117" t="s">
-        <v>245</v>
-      </c>
-      <c r="H88" s="116" t="s">
-        <v>279</v>
-      </c>
-      <c r="I88" s="116" t="s">
-        <v>338</v>
-      </c>
-      <c r="J88" s="116" t="s">
-        <v>451</v>
-      </c>
-      <c r="K88" s="117" t="s">
-        <v>338</v>
-      </c>
-      <c r="L88" s="116">
+      <c r="C88" s="81" t="s">
+        <v>352</v>
+      </c>
+      <c r="D88" s="82" t="s">
+        <v>71</v>
+      </c>
+      <c r="E88" s="83" t="s">
+        <v>150</v>
+      </c>
+      <c r="F88" s="82" t="s">
+        <v>191</v>
+      </c>
+      <c r="G88" s="83" t="s">
+        <v>244</v>
+      </c>
+      <c r="H88" s="82" t="s">
+        <v>278</v>
+      </c>
+      <c r="I88" s="82" t="s">
+        <v>337</v>
+      </c>
+      <c r="J88" s="82" t="s">
+        <v>450</v>
+      </c>
+      <c r="K88" s="83" t="s">
+        <v>337</v>
+      </c>
+      <c r="L88" s="82">
         <v>1</v>
       </c>
-      <c r="M88" s="118">
+      <c r="M88" s="84">
         <f t="shared" si="63"/>
         <v>20</v>
       </c>
-      <c r="N88" s="118">
+      <c r="N88" s="84">
         <v>21</v>
       </c>
-      <c r="O88" s="119" t="s">
-        <v>368</v>
-      </c>
-      <c r="P88" s="118">
+      <c r="O88" s="85" t="s">
+        <v>367</v>
+      </c>
+      <c r="P88" s="84">
         <v>7.4638</v>
       </c>
-      <c r="Q88" s="118">
+      <c r="Q88" s="84">
         <f t="shared" ref="Q88" si="79">P88*N88</f>
         <v>156.7398</v>
       </c>
-      <c r="R88" s="118" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="89" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R88" s="84" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="53">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
       <c r="C89" s="60" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D89" s="39" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E89" s="40" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F89" s="39" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G89" s="40" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H89" s="39" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I89" s="39" t="s">
+        <v>337</v>
+      </c>
+      <c r="J89" s="39" t="s">
+        <v>337</v>
+      </c>
+      <c r="K89" s="58" t="s">
         <v>338</v>
-      </c>
-      <c r="J89" s="39" t="s">
-        <v>338</v>
-      </c>
-      <c r="K89" s="58" t="s">
-        <v>339</v>
       </c>
       <c r="L89" s="39">
         <v>1</v>
@@ -7906,7 +7798,7 @@
         <v>21</v>
       </c>
       <c r="O89" s="65" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="P89" s="42">
         <v>2.6459999999999999</v>
@@ -7917,152 +7809,152 @@
       </c>
       <c r="R89" s="42"/>
     </row>
-    <row r="90" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
-      <c r="B90" s="85">
+      <c r="B90" s="53">
         <f>ROW(B90) - ROW($B$9)</f>
         <v>81</v>
       </c>
-      <c r="C90" s="86" t="s">
-        <v>353</v>
-      </c>
-      <c r="D90" s="87" t="s">
-        <v>74</v>
-      </c>
-      <c r="E90" s="88" t="s">
-        <v>153</v>
-      </c>
-      <c r="F90" s="87" t="s">
-        <v>335</v>
-      </c>
-      <c r="G90" s="88" t="s">
-        <v>194</v>
-      </c>
-      <c r="H90" s="87" t="s">
-        <v>277</v>
-      </c>
-      <c r="I90" s="87" t="s">
+      <c r="C90" s="61" t="s">
+        <v>352</v>
+      </c>
+      <c r="D90" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="E90" s="38" t="s">
+        <v>152</v>
+      </c>
+      <c r="F90" s="37" t="s">
+        <v>334</v>
+      </c>
+      <c r="G90" s="38" t="s">
+        <v>193</v>
+      </c>
+      <c r="H90" s="37" t="s">
+        <v>276</v>
+      </c>
+      <c r="I90" s="37" t="s">
+        <v>451</v>
+      </c>
+      <c r="J90" s="37" t="s">
         <v>452</v>
       </c>
-      <c r="J90" s="87" t="s">
-        <v>453</v>
-      </c>
-      <c r="K90" s="88" t="s">
-        <v>338</v>
-      </c>
-      <c r="L90" s="105">
+      <c r="K90" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="L90" s="86">
         <v>2</v>
       </c>
-      <c r="M90" s="89">
+      <c r="M90" s="41">
         <f t="shared" si="63"/>
         <v>40</v>
       </c>
-      <c r="N90" s="89">
+      <c r="N90" s="41">
         <v>42</v>
       </c>
-      <c r="O90" s="90" t="s">
-        <v>368</v>
-      </c>
-      <c r="P90" s="89">
+      <c r="O90" s="64" t="s">
+        <v>367</v>
+      </c>
+      <c r="P90" s="41">
         <v>2.2974000000000001</v>
       </c>
-      <c r="Q90" s="89">
+      <c r="Q90" s="41">
         <f t="shared" ref="Q90" si="81">P90*N90</f>
         <v>96.490800000000007</v>
       </c>
-      <c r="R90" s="91" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="91" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R90" s="99" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
-      <c r="B91" s="85">
+      <c r="B91" s="53">
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
-      <c r="C91" s="92" t="s">
-        <v>353</v>
-      </c>
-      <c r="D91" s="93" t="s">
-        <v>75</v>
-      </c>
-      <c r="E91" s="94" t="s">
-        <v>154</v>
-      </c>
-      <c r="F91" s="93" t="s">
-        <v>336</v>
-      </c>
-      <c r="G91" s="94" t="s">
-        <v>195</v>
-      </c>
-      <c r="H91" s="93" t="s">
-        <v>280</v>
-      </c>
-      <c r="I91" s="93" t="s">
-        <v>455</v>
-      </c>
-      <c r="J91" s="93" t="s">
-        <v>338</v>
-      </c>
-      <c r="K91" s="94" t="s">
-        <v>338</v>
-      </c>
-      <c r="L91" s="93">
+      <c r="C91" s="60" t="s">
+        <v>352</v>
+      </c>
+      <c r="D91" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="E91" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="F91" s="39" t="s">
+        <v>335</v>
+      </c>
+      <c r="G91" s="40" t="s">
+        <v>194</v>
+      </c>
+      <c r="H91" s="39" t="s">
+        <v>279</v>
+      </c>
+      <c r="I91" s="39" t="s">
+        <v>454</v>
+      </c>
+      <c r="J91" s="39" t="s">
+        <v>337</v>
+      </c>
+      <c r="K91" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="L91" s="39">
         <v>1</v>
       </c>
-      <c r="M91" s="95">
+      <c r="M91" s="42">
         <f t="shared" si="63"/>
         <v>20</v>
       </c>
-      <c r="N91" s="95">
+      <c r="N91" s="42">
         <v>21</v>
       </c>
-      <c r="O91" s="96" t="s">
-        <v>456</v>
-      </c>
-      <c r="P91" s="95">
+      <c r="O91" s="65" t="s">
+        <v>455</v>
+      </c>
+      <c r="P91" s="42">
         <v>3.532</v>
       </c>
-      <c r="Q91" s="95">
+      <c r="Q91" s="42">
         <f t="shared" ref="Q91" si="82">N91*P91</f>
         <v>74.171999999999997</v>
       </c>
-      <c r="R91" s="91" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="92" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R91" s="107" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="53">
         <f>ROW(B92) - ROW($B$9)</f>
         <v>83</v>
       </c>
       <c r="C92" s="61" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D92" s="37" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E92" s="38" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F92" s="37" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G92" s="38" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H92" s="37" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I92" s="63" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J92" s="63" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K92" s="38" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L92" s="37">
         <v>1</v>
@@ -8075,7 +7967,7 @@
         <v>21</v>
       </c>
       <c r="O92" s="64" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P92" s="41">
         <v>0.39140000000000003</v>
@@ -8086,7 +7978,7 @@
       </c>
       <c r="R92" s="41"/>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="32"/>
       <c r="C93" s="51"/>
@@ -8103,17 +7995,17 @@
       <c r="L93" s="36"/>
       <c r="M93" s="36"/>
       <c r="N93" s="36"/>
-      <c r="O93" s="99" t="s">
-        <v>458</v>
-      </c>
-      <c r="P93" s="97"/>
-      <c r="Q93" s="97">
+      <c r="O93" s="74" t="s">
+        <v>457</v>
+      </c>
+      <c r="P93" s="72"/>
+      <c r="Q93" s="72">
         <f>SUM(Q10:Q92)</f>
         <v>963.91150000000016</v>
       </c>
       <c r="R93" s="44"/>
     </row>
-    <row r="94" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
       <c r="B94" s="24"/>
       <c r="C94" s="52"/>
@@ -8130,11 +8022,11 @@
       <c r="L94" s="9"/>
       <c r="M94" s="9"/>
       <c r="N94" s="9"/>
-      <c r="O94" s="100" t="s">
-        <v>459</v>
-      </c>
-      <c r="P94" s="98"/>
-      <c r="Q94" s="98">
+      <c r="O94" s="75" t="s">
+        <v>458</v>
+      </c>
+      <c r="P94" s="73"/>
+      <c r="Q94" s="73">
         <f>Q93/20</f>
         <v>48.195575000000005</v>
       </c>

--- a/Deliverables/SM_Top Board/_BOM/eSpark BOM (20 Boards).xlsx
+++ b/Deliverables/SM_Top Board/_BOM/eSpark BOM (20 Boards).xlsx
@@ -5,16 +5,16 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Faizan\GitHub\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="7650"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="7656"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="501">
   <si>
     <t>Component list</t>
   </si>
@@ -58,15 +58,9 @@
     <t>C1</t>
   </si>
   <si>
-    <t>C2, C13, C51, C52, C53, C54, C61, CF1, CF2</t>
-  </si>
-  <si>
     <t>C9</t>
   </si>
   <si>
-    <t>C15, C20, C40</t>
-  </si>
-  <si>
     <t>C17</t>
   </si>
   <si>
@@ -103,9 +97,6 @@
     <t>C50</t>
   </si>
   <si>
-    <t>C55</t>
-  </si>
-  <si>
     <t>C57, C58, C59, C60</t>
   </si>
   <si>
@@ -283,9 +274,6 @@
     <t>CAP CER 0.082UF 50V X7R 0603</t>
   </si>
   <si>
-    <t>CAP CER 0.1UF 100V X7R 0603</t>
-  </si>
-  <si>
     <t>Cap Ceramic 0.22uF 100V X7R 10% SMD 0805 125°C Embossed T/R</t>
   </si>
   <si>
@@ -328,9 +316,6 @@
     <t>CAP CER 470pF 10% X7R 50V 0603 SMD</t>
   </si>
   <si>
-    <t>CAP CER 1UF 100V X7S 0805</t>
-  </si>
-  <si>
     <t>CAP CER 1nF 100V X7R 0603</t>
   </si>
   <si>
@@ -640,9 +625,6 @@
     <t>CC0603KRX7R9BB823</t>
   </si>
   <si>
-    <t>CC0603KRX7R0BB104</t>
-  </si>
-  <si>
     <t>08051C224K4T2A</t>
   </si>
   <si>
@@ -676,9 +658,6 @@
     <t>CC0603KRX7R9BB471</t>
   </si>
   <si>
-    <t>C2012X7S2A105K125AB</t>
-  </si>
-  <si>
     <t>CL10B102KC8NNNC</t>
   </si>
   <si>
@@ -1153,9 +1132,6 @@
     <t>C107100</t>
   </si>
   <si>
-    <t>C113803</t>
-  </si>
-  <si>
     <t>C513710</t>
   </si>
   <si>
@@ -1208,12 +1184,6 @@
   </si>
   <si>
     <t>C107092</t>
-  </si>
-  <si>
-    <t>C2991905</t>
-  </si>
-  <si>
-    <t>C0805R105K101TDF</t>
   </si>
   <si>
     <t>C153291</t>
@@ -1457,9 +1427,6 @@
   </si>
   <si>
     <t>Quantity changed from 3/board to 1/board due to change in two capacitors value to 1uF after component change</t>
-  </si>
-  <si>
-    <t>Quantity changed from 1/board to 3/board due to change in two capacitors value to 1uF after component change</t>
   </si>
   <si>
     <r>
@@ -1517,9 +1484,6 @@
     </r>
   </si>
   <si>
-    <t>Quantity changed from 9/board to 8/board due to removal of 1 x 2.2uF capacitor from U3</t>
-  </si>
-  <si>
     <t>C4</t>
   </si>
   <si>
@@ -1537,12 +1501,6 @@
       </rPr>
       <t>C46</t>
     </r>
-  </si>
-  <si>
-    <t>Quantity changed from 2/board to 1/board due to removal of 1 x 0.47uF capacitor from U3</t>
-  </si>
-  <si>
-    <t>Quantity changed from 1/board to 2/board due to addition of 1 x 10nF capacitor from U3</t>
   </si>
   <si>
     <t>Removed after changes in circuitry of U3</t>
@@ -1943,11 +1901,17 @@
   <si>
     <t>RES SMD 22HM 1/10W 0603</t>
   </si>
+  <si>
+    <t>C2, C13, C15, C20, C40, C51, C52, C53, C54, C55, C61, CF1, CF2</t>
+  </si>
+  <si>
+    <t>Quantity changed from 9 to 13. C15, C20 and C40 merged into this due to same value. C55 changed from 1uF to 0.1uF</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
@@ -2163,7 +2127,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2203,6 +2167,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2459,7 +2429,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -2662,21 +2632,6 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2761,6 +2716,12 @@
     <xf numFmtId="0" fontId="24" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2770,10 +2731,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2820,7 +2799,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3118,27 +3097,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R94"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:R92"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.109375" style="25" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" style="25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="30.140625" customWidth="1"/>
-    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="22.140625" customWidth="1"/>
-    <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="16.7109375" customWidth="1"/>
-    <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="29.42578125" customWidth="1"/>
+    <col min="6" max="6" width="30.109375" customWidth="1"/>
+    <col min="7" max="7" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="22.109375" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="16.6640625" customWidth="1"/>
+    <col min="16" max="16" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -3149,16 +3128,16 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-    </row>
-    <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+    </row>
+    <row r="2" spans="1:18" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
       <c r="C2" s="46"/>
@@ -3167,7 +3146,7 @@
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="54" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
@@ -3182,7 +3161,7 @@
       <c r="Q2" s="3"/>
       <c r="R2" s="43"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
       <c r="C3" s="47"/>
@@ -3191,7 +3170,7 @@
       </c>
       <c r="E3" s="12"/>
       <c r="F3" s="55" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="4"/>
@@ -3204,9 +3183,9 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="110"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R3" s="107"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
       <c r="C4" s="47"/>
@@ -3215,7 +3194,7 @@
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="56" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="6"/>
@@ -3228,9 +3207,9 @@
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="Q4" s="62"/>
-      <c r="R4" s="111"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R4" s="108"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
       <c r="C5" s="47"/>
@@ -3250,9 +3229,9 @@
       <c r="O5" s="62"/>
       <c r="P5" s="62"/>
       <c r="Q5" s="62"/>
-      <c r="R5" s="111"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R5" s="108"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
       <c r="C6" s="48"/>
@@ -3270,9 +3249,9 @@
       <c r="O6" s="62"/>
       <c r="P6" s="62"/>
       <c r="Q6" s="62"/>
-      <c r="R6" s="111"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R6" s="108"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
       <c r="C7" s="49"/>
@@ -3290,9 +3269,9 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="111"/>
-    </row>
-    <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R7" s="108"/>
+    </row>
+    <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="B8" s="26"/>
       <c r="C8" s="50"/>
@@ -3310,94 +3289,94 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="111"/>
-    </row>
-    <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R8" s="108"/>
+    </row>
+    <row r="9" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
       <c r="B9" s="29" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="D9" s="29" t="s">
         <v>7</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="I9" s="29" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="J9" s="29" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="L9" s="29" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="M9" s="31" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="N9" s="31" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="O9" s="31" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="P9" s="31" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="Q9" s="31" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="R9" s="31" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1"/>
       <c r="B10" s="53">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="D10" s="37" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="38" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="G10" s="38" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="K10" s="38" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="L10" s="37">
         <v>1</v>
@@ -3410,7 +3389,7 @@
         <v>22</v>
       </c>
       <c r="O10" s="64" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P10" s="41">
         <v>0.25869999999999999</v>
@@ -3421,106 +3400,108 @@
       </c>
       <c r="R10" s="41"/>
     </row>
-    <row r="11" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
       <c r="B11" s="53">
-        <f t="shared" ref="B11:B91" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B89" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="60" t="s">
-        <v>340</v>
-      </c>
-      <c r="D11" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="40" t="s">
-        <v>78</v>
-      </c>
-      <c r="F11" s="39" t="s">
-        <v>157</v>
-      </c>
-      <c r="G11" s="40" t="s">
-        <v>197</v>
-      </c>
-      <c r="H11" s="39" t="s">
-        <v>248</v>
-      </c>
-      <c r="I11" s="39" t="s">
-        <v>337</v>
-      </c>
-      <c r="J11" s="39" t="s">
-        <v>368</v>
-      </c>
-      <c r="K11" s="40" t="s">
-        <v>282</v>
-      </c>
-      <c r="L11" s="39">
-        <v>9</v>
-      </c>
-      <c r="M11" s="42">
+      <c r="C11" s="109" t="s">
+        <v>333</v>
+      </c>
+      <c r="D11" s="110" t="s">
+        <v>499</v>
+      </c>
+      <c r="E11" s="111" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" s="110" t="s">
+        <v>152</v>
+      </c>
+      <c r="G11" s="111" t="s">
+        <v>192</v>
+      </c>
+      <c r="H11" s="110" t="s">
+        <v>241</v>
+      </c>
+      <c r="I11" s="110" t="s">
+        <v>330</v>
+      </c>
+      <c r="J11" s="110" t="s">
+        <v>361</v>
+      </c>
+      <c r="K11" s="111" t="s">
+        <v>275</v>
+      </c>
+      <c r="L11" s="110">
+        <v>13</v>
+      </c>
+      <c r="M11" s="112">
         <f>L11*20</f>
-        <v>180</v>
-      </c>
-      <c r="N11" s="42">
-        <v>198</v>
-      </c>
-      <c r="O11" s="65" t="s">
-        <v>367</v>
-      </c>
-      <c r="P11" s="42">
+        <v>260</v>
+      </c>
+      <c r="N11" s="112">
+        <v>300</v>
+      </c>
+      <c r="O11" s="113" t="s">
+        <v>360</v>
+      </c>
+      <c r="P11" s="112">
         <v>1.4E-3</v>
       </c>
-      <c r="Q11" s="42">
+      <c r="Q11" s="112">
         <f>N11*P11</f>
-        <v>0.2772</v>
-      </c>
-      <c r="R11" s="42"/>
-    </row>
-    <row r="12" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.42</v>
+      </c>
+      <c r="R11" s="112" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
       <c r="B12" s="53">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
       <c r="C12" s="61" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K12" s="38" t="s">
-        <v>283</v>
-      </c>
-      <c r="L12" s="86">
+        <v>276</v>
+      </c>
+      <c r="L12" s="114">
         <v>2</v>
       </c>
       <c r="M12" s="41">
-        <f t="shared" ref="M12:M73" si="1">L12*20</f>
+        <f t="shared" ref="M12:M71" si="1">L12*20</f>
         <v>40</v>
       </c>
       <c r="N12" s="41">
         <v>100</v>
       </c>
       <c r="O12" s="64" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P12" s="41">
         <v>1.2999999999999999E-3</v>
@@ -3529,55 +3510,53 @@
         <f t="shared" ref="Q12" si="2">P12*N12</f>
         <v>0.13</v>
       </c>
-      <c r="R12" s="87" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R12" s="82"/>
+    </row>
+    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
       <c r="B13" s="53">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C13" s="60" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="E13" s="40" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G13" s="40" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="I13" s="39" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J13" s="39" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="K13" s="40" t="s">
-        <v>284</v>
-      </c>
-      <c r="L13" s="90">
+        <v>277</v>
+      </c>
+      <c r="L13" s="115">
         <v>1</v>
       </c>
       <c r="M13" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N13" s="91">
+      <c r="N13" s="116">
         <v>40</v>
       </c>
       <c r="O13" s="65" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P13" s="42">
         <v>3.5900000000000001E-2</v>
@@ -3586,42 +3565,40 @@
         <f t="shared" ref="Q13" si="3">N13*P13</f>
         <v>1.4359999999999999</v>
       </c>
-      <c r="R13" s="92" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R13" s="87"/>
+    </row>
+    <row r="14" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1"/>
       <c r="B14" s="53">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
       <c r="C14" s="61" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J14" s="37" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="K14" s="38" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="L14" s="37">
         <v>8</v>
@@ -3634,7 +3611,7 @@
         <v>200</v>
       </c>
       <c r="O14" s="64" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P14" s="41">
         <v>4.0899999999999999E-2</v>
@@ -3643,55 +3620,53 @@
         <f>P14*N14</f>
         <v>8.18</v>
       </c>
-      <c r="R14" s="87" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R14" s="82"/>
+    </row>
+    <row r="15" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
       <c r="B15" s="53">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C15" s="60" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="E15" s="40" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G15" s="40" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="H15" s="39" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="I15" s="39" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J15" s="39" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="K15" s="40" t="s">
-        <v>286</v>
-      </c>
-      <c r="L15" s="90">
+        <v>279</v>
+      </c>
+      <c r="L15" s="115">
         <v>3</v>
       </c>
       <c r="M15" s="42">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="N15" s="91">
+      <c r="N15" s="116">
         <v>100</v>
       </c>
       <c r="O15" s="65" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P15" s="42">
         <v>5.8999999999999999E-3</v>
@@ -3700,42 +3675,40 @@
         <f t="shared" ref="Q15" si="4">N15*P15</f>
         <v>0.59</v>
       </c>
-      <c r="R15" s="92" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R15" s="87"/>
+    </row>
+    <row r="16" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
       <c r="B16" s="53">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
       <c r="C16" s="61" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>509</v>
+        <v>495</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>489</v>
+        <v>475</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="G16" s="88" t="s">
-        <v>488</v>
-      </c>
-      <c r="H16" s="89" t="s">
-        <v>251</v>
+        <v>152</v>
+      </c>
+      <c r="G16" s="83" t="s">
+        <v>474</v>
+      </c>
+      <c r="H16" s="84" t="s">
+        <v>244</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>490</v>
+        <v>476</v>
       </c>
       <c r="K16" s="38" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="L16" s="37">
         <v>6</v>
@@ -3748,7 +3721,7 @@
         <v>130</v>
       </c>
       <c r="O16" s="64" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P16" s="41">
         <v>3.32E-2</v>
@@ -3757,42 +3730,42 @@
         <f t="shared" ref="Q16" si="5">P16*N16</f>
         <v>4.3159999999999998</v>
       </c>
-      <c r="R16" s="87" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R16" s="82" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
       <c r="B17" s="53">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C17" s="60" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E17" s="40" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G17" s="40" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="H17" s="39" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="I17" s="39" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J17" s="39" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="K17" s="40" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="L17" s="39">
         <v>1</v>
@@ -3805,7 +3778,7 @@
         <v>50</v>
       </c>
       <c r="O17" s="65" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P17" s="42">
         <v>9.9000000000000008E-3</v>
@@ -3816,1264 +3789,1262 @@
       </c>
       <c r="R17" s="42"/>
     </row>
-    <row r="18" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" s="53">
-        <f>ROW(B18) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="61" t="s">
-        <v>340</v>
-      </c>
-      <c r="D18" s="37" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="F18" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="G18" s="38" t="s">
-        <v>203</v>
-      </c>
-      <c r="H18" s="37" t="s">
-        <v>249</v>
-      </c>
-      <c r="I18" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="J18" s="37" t="s">
-        <v>374</v>
-      </c>
-      <c r="K18" s="38" t="s">
+      <c r="C18" s="60" t="s">
+        <v>333</v>
+      </c>
+      <c r="D18" s="39" t="s">
+        <v>373</v>
+      </c>
+      <c r="E18" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="F18" s="39" t="s">
+        <v>154</v>
+      </c>
+      <c r="G18" s="40" t="s">
+        <v>198</v>
+      </c>
+      <c r="H18" s="39" t="s">
+        <v>245</v>
+      </c>
+      <c r="I18" s="39" t="s">
+        <v>368</v>
+      </c>
+      <c r="J18" s="39" t="s">
+        <v>367</v>
+      </c>
+      <c r="K18" s="40" t="s">
         <v>282</v>
       </c>
-      <c r="L18" s="37">
-        <v>3</v>
-      </c>
-      <c r="M18" s="41">
+      <c r="L18" s="39">
+        <v>8</v>
+      </c>
+      <c r="M18" s="42">
         <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
-      <c r="N18" s="41">
-        <v>100</v>
-      </c>
-      <c r="O18" s="64" t="s">
-        <v>367</v>
-      </c>
-      <c r="P18" s="41">
-        <v>8.0999999999999996E-3</v>
-      </c>
-      <c r="Q18" s="41">
-        <f t="shared" ref="Q18" si="7">P18*N18</f>
-        <v>0.80999999999999994</v>
-      </c>
-      <c r="R18" s="41"/>
-    </row>
-    <row r="19" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>160</v>
+      </c>
+      <c r="N18" s="42">
+        <v>180</v>
+      </c>
+      <c r="O18" s="65" t="s">
+        <v>360</v>
+      </c>
+      <c r="P18" s="42">
+        <v>3.09E-2</v>
+      </c>
+      <c r="Q18" s="42">
+        <f t="shared" ref="Q18" si="7">N18*P18</f>
+        <v>5.5620000000000003</v>
+      </c>
+      <c r="R18" s="42"/>
+    </row>
+    <row r="19" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B19) - ROW($B$9)</f>
         <v>10</v>
       </c>
-      <c r="C19" s="60" t="s">
-        <v>340</v>
-      </c>
-      <c r="D19" s="39" t="s">
-        <v>381</v>
-      </c>
-      <c r="E19" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="F19" s="39" t="s">
-        <v>159</v>
-      </c>
-      <c r="G19" s="40" t="s">
-        <v>204</v>
-      </c>
-      <c r="H19" s="39" t="s">
-        <v>252</v>
-      </c>
-      <c r="I19" s="39" t="s">
-        <v>376</v>
-      </c>
-      <c r="J19" s="39" t="s">
-        <v>375</v>
-      </c>
-      <c r="K19" s="40" t="s">
-        <v>289</v>
-      </c>
-      <c r="L19" s="39">
-        <v>8</v>
-      </c>
-      <c r="M19" s="42">
+      <c r="C19" s="61" t="s">
+        <v>333</v>
+      </c>
+      <c r="D19" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="F19" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="G19" s="38" t="s">
+        <v>199</v>
+      </c>
+      <c r="H19" s="37" t="s">
+        <v>246</v>
+      </c>
+      <c r="I19" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="J19" s="37" t="s">
+        <v>370</v>
+      </c>
+      <c r="K19" s="38" t="s">
+        <v>283</v>
+      </c>
+      <c r="L19" s="37">
+        <v>1</v>
+      </c>
+      <c r="M19" s="41">
         <f t="shared" si="1"/>
-        <v>160</v>
-      </c>
-      <c r="N19" s="42">
-        <v>180</v>
-      </c>
-      <c r="O19" s="65" t="s">
-        <v>367</v>
-      </c>
-      <c r="P19" s="42">
-        <v>3.09E-2</v>
-      </c>
-      <c r="Q19" s="42">
-        <f t="shared" ref="Q19" si="8">N19*P19</f>
-        <v>5.5620000000000003</v>
-      </c>
-      <c r="R19" s="42"/>
-    </row>
-    <row r="20" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="N19" s="41">
+        <v>50</v>
+      </c>
+      <c r="O19" s="64" t="s">
+        <v>360</v>
+      </c>
+      <c r="P19" s="41">
+        <v>5.3E-3</v>
+      </c>
+      <c r="Q19" s="41">
+        <f t="shared" ref="Q19" si="8">P19*N19</f>
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="R19" s="41"/>
+    </row>
+    <row r="20" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1"/>
       <c r="B20" s="53">
-        <f>ROW(B20) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="61" t="s">
-        <v>340</v>
-      </c>
-      <c r="D20" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="F20" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="G20" s="38" t="s">
-        <v>205</v>
-      </c>
-      <c r="H20" s="37" t="s">
-        <v>253</v>
-      </c>
-      <c r="I20" s="37" t="s">
-        <v>377</v>
-      </c>
-      <c r="J20" s="37" t="s">
-        <v>378</v>
-      </c>
-      <c r="K20" s="38" t="s">
-        <v>290</v>
-      </c>
-      <c r="L20" s="37">
+      <c r="C20" s="60" t="s">
+        <v>333</v>
+      </c>
+      <c r="D20" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="F20" s="39" t="s">
+        <v>324</v>
+      </c>
+      <c r="G20" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="H20" s="39" t="s">
+        <v>247</v>
+      </c>
+      <c r="I20" s="39" t="s">
+        <v>330</v>
+      </c>
+      <c r="J20" s="39" t="s">
+        <v>371</v>
+      </c>
+      <c r="K20" s="40" t="s">
+        <v>274</v>
+      </c>
+      <c r="L20" s="39">
         <v>1</v>
       </c>
-      <c r="M20" s="41">
+      <c r="M20" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N20" s="41">
-        <v>50</v>
-      </c>
-      <c r="O20" s="64" t="s">
-        <v>367</v>
-      </c>
-      <c r="P20" s="41">
-        <v>5.3E-3</v>
-      </c>
-      <c r="Q20" s="41">
-        <f t="shared" ref="Q20" si="9">P20*N20</f>
-        <v>0.26500000000000001</v>
-      </c>
-      <c r="R20" s="41"/>
-    </row>
-    <row r="21" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N20" s="42">
+        <v>22</v>
+      </c>
+      <c r="O20" s="65" t="s">
+        <v>360</v>
+      </c>
+      <c r="P20" s="42">
+        <v>0.22189999999999999</v>
+      </c>
+      <c r="Q20" s="42">
+        <f t="shared" ref="Q20" si="9">N20*P20</f>
+        <v>4.8818000000000001</v>
+      </c>
+      <c r="R20" s="42"/>
+    </row>
+    <row r="21" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
       <c r="B21" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B21) - ROW($B$9)</f>
         <v>12</v>
       </c>
-      <c r="C21" s="60" t="s">
-        <v>340</v>
-      </c>
-      <c r="D21" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="40" t="s">
-        <v>87</v>
-      </c>
-      <c r="F21" s="39" t="s">
-        <v>331</v>
-      </c>
-      <c r="G21" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="H21" s="39" t="s">
-        <v>254</v>
-      </c>
-      <c r="I21" s="39" t="s">
-        <v>337</v>
-      </c>
-      <c r="J21" s="39" t="s">
-        <v>379</v>
-      </c>
-      <c r="K21" s="40" t="s">
-        <v>281</v>
-      </c>
-      <c r="L21" s="39">
-        <v>1</v>
-      </c>
-      <c r="M21" s="42">
+      <c r="C21" s="61" t="s">
+        <v>333</v>
+      </c>
+      <c r="D21" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="F21" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="G21" s="38" t="s">
+        <v>200</v>
+      </c>
+      <c r="H21" s="37" t="s">
+        <v>241</v>
+      </c>
+      <c r="I21" s="37" t="s">
+        <v>330</v>
+      </c>
+      <c r="J21" s="37" t="s">
+        <v>372</v>
+      </c>
+      <c r="K21" s="38" t="s">
+        <v>284</v>
+      </c>
+      <c r="L21" s="37">
+        <v>2</v>
+      </c>
+      <c r="M21" s="41">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N21" s="42">
-        <v>22</v>
-      </c>
-      <c r="O21" s="65" t="s">
-        <v>367</v>
-      </c>
-      <c r="P21" s="42">
-        <v>0.22189999999999999</v>
-      </c>
-      <c r="Q21" s="42">
-        <f t="shared" ref="Q21" si="10">N21*P21</f>
-        <v>4.8818000000000001</v>
-      </c>
-      <c r="R21" s="42"/>
-    </row>
-    <row r="22" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="N21" s="41">
+        <v>50</v>
+      </c>
+      <c r="O21" s="64" t="s">
+        <v>360</v>
+      </c>
+      <c r="P21" s="41">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="Q21" s="41">
+        <f t="shared" ref="Q21" si="10">P21*N21</f>
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="R21" s="41"/>
+    </row>
+    <row r="22" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1"/>
       <c r="B22" s="53">
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
       <c r="C22" s="61" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E22" s="38" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J22" s="37" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="K22" s="38" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="L22" s="37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M22" s="41">
         <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N22" s="41">
         <v>40</v>
       </c>
-      <c r="N22" s="41">
-        <v>50</v>
-      </c>
       <c r="O22" s="64" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P22" s="41">
-        <v>7.7000000000000002E-3</v>
+        <v>3.49E-2</v>
       </c>
       <c r="Q22" s="41">
         <f t="shared" ref="Q22" si="11">P22*N22</f>
-        <v>0.38500000000000001</v>
+        <v>1.3959999999999999</v>
       </c>
       <c r="R22" s="41"/>
     </row>
-    <row r="23" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
       <c r="B23" s="53">
-        <f>ROW(B23) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="61" t="s">
-        <v>340</v>
-      </c>
-      <c r="D23" s="37" t="s">
-        <v>15</v>
-      </c>
-      <c r="E23" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="F23" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="G23" s="38" t="s">
-        <v>207</v>
-      </c>
-      <c r="H23" s="37" t="s">
-        <v>250</v>
-      </c>
-      <c r="I23" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="J23" s="37" t="s">
-        <v>382</v>
-      </c>
-      <c r="K23" s="38" t="s">
-        <v>284</v>
-      </c>
-      <c r="L23" s="37">
+      <c r="C23" s="60" t="s">
+        <v>333</v>
+      </c>
+      <c r="D23" s="39" t="s">
+        <v>456</v>
+      </c>
+      <c r="E23" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="F23" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="G23" s="40" t="s">
+        <v>202</v>
+      </c>
+      <c r="H23" s="39" t="s">
+        <v>241</v>
+      </c>
+      <c r="I23" s="39" t="s">
+        <v>330</v>
+      </c>
+      <c r="J23" s="39" t="s">
+        <v>375</v>
+      </c>
+      <c r="K23" s="40" t="s">
+        <v>285</v>
+      </c>
+      <c r="L23" s="85">
         <v>1</v>
       </c>
-      <c r="M23" s="41">
+      <c r="M23" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N23" s="41">
+      <c r="N23" s="86">
         <v>40</v>
       </c>
-      <c r="O23" s="64" t="s">
-        <v>367</v>
-      </c>
-      <c r="P23" s="41">
-        <v>3.49E-2</v>
-      </c>
-      <c r="Q23" s="41">
-        <f t="shared" ref="Q23" si="12">P23*N23</f>
-        <v>1.3959999999999999</v>
-      </c>
-      <c r="R23" s="41"/>
-    </row>
-    <row r="24" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O23" s="65" t="s">
+        <v>360</v>
+      </c>
+      <c r="P23" s="42">
+        <v>1.9199999999999998E-2</v>
+      </c>
+      <c r="Q23" s="42">
+        <f t="shared" ref="Q23" si="12">N23*P23</f>
+        <v>0.7679999999999999</v>
+      </c>
+      <c r="R23" s="87" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
       <c r="B24" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="60" t="s">
-        <v>340</v>
-      </c>
-      <c r="D24" s="39" t="s">
-        <v>466</v>
-      </c>
-      <c r="E24" s="40" t="s">
-        <v>90</v>
-      </c>
-      <c r="F24" s="39" t="s">
-        <v>157</v>
-      </c>
-      <c r="G24" s="40" t="s">
-        <v>208</v>
-      </c>
-      <c r="H24" s="39" t="s">
+      <c r="C24" s="61" t="s">
+        <v>333</v>
+      </c>
+      <c r="D24" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="F24" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="G24" s="66">
+        <v>885012205080</v>
+      </c>
+      <c r="H24" s="37" t="s">
         <v>248</v>
       </c>
-      <c r="I24" s="39" t="s">
-        <v>337</v>
-      </c>
-      <c r="J24" s="39" t="s">
-        <v>383</v>
-      </c>
-      <c r="K24" s="40" t="s">
-        <v>292</v>
-      </c>
-      <c r="L24" s="90">
+      <c r="I24" s="37" t="s">
+        <v>376</v>
+      </c>
+      <c r="J24" s="37" t="s">
+        <v>377</v>
+      </c>
+      <c r="K24" s="38" t="s">
+        <v>286</v>
+      </c>
+      <c r="L24" s="37">
         <v>1</v>
       </c>
-      <c r="M24" s="42">
+      <c r="M24" s="41">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N24" s="91">
-        <v>40</v>
-      </c>
-      <c r="O24" s="65" t="s">
-        <v>367</v>
-      </c>
-      <c r="P24" s="42">
-        <v>1.9199999999999998E-2</v>
-      </c>
-      <c r="Q24" s="42">
-        <f t="shared" ref="Q24" si="13">N24*P24</f>
-        <v>0.7679999999999999</v>
-      </c>
-      <c r="R24" s="92" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N24" s="41">
+        <v>50</v>
+      </c>
+      <c r="O24" s="64" t="s">
+        <v>360</v>
+      </c>
+      <c r="P24" s="41">
+        <v>5.1999999999999998E-3</v>
+      </c>
+      <c r="Q24" s="41">
+        <f t="shared" ref="Q24" si="13">P24*N24</f>
+        <v>0.26</v>
+      </c>
+      <c r="R24" s="41"/>
+    </row>
+    <row r="25" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
       <c r="B25" s="53">
-        <f>ROW(B25) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="61" t="s">
-        <v>340</v>
-      </c>
-      <c r="D25" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="E25" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="F25" s="37" t="s">
-        <v>158</v>
-      </c>
-      <c r="G25" s="66">
-        <v>885012205080</v>
-      </c>
-      <c r="H25" s="37" t="s">
-        <v>255</v>
-      </c>
-      <c r="I25" s="37" t="s">
-        <v>384</v>
-      </c>
-      <c r="J25" s="37" t="s">
-        <v>385</v>
-      </c>
-      <c r="K25" s="38" t="s">
-        <v>293</v>
-      </c>
-      <c r="L25" s="37">
+      <c r="C25" s="60" t="s">
+        <v>333</v>
+      </c>
+      <c r="D25" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="F25" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="G25" s="40" t="s">
+        <v>203</v>
+      </c>
+      <c r="H25" s="39" t="s">
+        <v>242</v>
+      </c>
+      <c r="I25" s="39" t="s">
+        <v>330</v>
+      </c>
+      <c r="J25" s="39" t="s">
+        <v>378</v>
+      </c>
+      <c r="K25" s="40" t="s">
+        <v>287</v>
+      </c>
+      <c r="L25" s="39">
         <v>1</v>
       </c>
-      <c r="M25" s="41">
+      <c r="M25" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N25" s="41">
-        <v>50</v>
-      </c>
-      <c r="O25" s="64" t="s">
-        <v>367</v>
-      </c>
-      <c r="P25" s="41">
-        <v>5.1999999999999998E-3</v>
-      </c>
-      <c r="Q25" s="41">
-        <f t="shared" ref="Q25" si="14">P25*N25</f>
-        <v>0.26</v>
-      </c>
-      <c r="R25" s="41"/>
-    </row>
-    <row r="26" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N25" s="42">
+        <v>100</v>
+      </c>
+      <c r="O25" s="65" t="s">
+        <v>360</v>
+      </c>
+      <c r="P25" s="42">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="Q25" s="42">
+        <f t="shared" ref="Q25" si="14">N25*P25</f>
+        <v>0.32</v>
+      </c>
+      <c r="R25" s="42"/>
+    </row>
+    <row r="26" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
       <c r="B26" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="60" t="s">
-        <v>340</v>
-      </c>
-      <c r="D26" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="E26" s="40" t="s">
-        <v>92</v>
-      </c>
-      <c r="F26" s="39" t="s">
-        <v>157</v>
-      </c>
-      <c r="G26" s="40" t="s">
-        <v>209</v>
-      </c>
-      <c r="H26" s="39" t="s">
-        <v>249</v>
-      </c>
-      <c r="I26" s="39" t="s">
-        <v>337</v>
-      </c>
-      <c r="J26" s="39" t="s">
-        <v>386</v>
-      </c>
-      <c r="K26" s="40" t="s">
-        <v>294</v>
-      </c>
-      <c r="L26" s="39">
+      <c r="C26" s="88" t="s">
+        <v>333</v>
+      </c>
+      <c r="D26" s="89" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="90" t="s">
+        <v>89</v>
+      </c>
+      <c r="F26" s="89" t="s">
+        <v>156</v>
+      </c>
+      <c r="G26" s="90" t="s">
+        <v>204</v>
+      </c>
+      <c r="H26" s="89" t="s">
+        <v>243</v>
+      </c>
+      <c r="I26" s="89" t="s">
+        <v>330</v>
+      </c>
+      <c r="J26" s="89" t="s">
+        <v>379</v>
+      </c>
+      <c r="K26" s="90" t="s">
+        <v>288</v>
+      </c>
+      <c r="L26" s="89">
         <v>1</v>
       </c>
-      <c r="M26" s="42">
+      <c r="M26" s="91">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N26" s="42">
-        <v>100</v>
-      </c>
-      <c r="O26" s="65" t="s">
-        <v>367</v>
-      </c>
-      <c r="P26" s="42">
-        <v>3.2000000000000002E-3</v>
-      </c>
-      <c r="Q26" s="42">
-        <f t="shared" ref="Q26" si="15">N26*P26</f>
-        <v>0.32</v>
-      </c>
-      <c r="R26" s="42"/>
-    </row>
-    <row r="27" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N26" s="91">
+        <v>0</v>
+      </c>
+      <c r="O26" s="92" t="s">
+        <v>360</v>
+      </c>
+      <c r="P26" s="91">
+        <v>0.1653</v>
+      </c>
+      <c r="Q26" s="91">
+        <f t="shared" ref="Q26" si="15">P26*N26</f>
+        <v>0</v>
+      </c>
+      <c r="R26" s="91" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
       <c r="B27" s="53">
-        <f>ROW(B27) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="93" t="s">
-        <v>340</v>
-      </c>
-      <c r="D27" s="94" t="s">
-        <v>18</v>
+      <c r="C27" s="60" t="s">
+        <v>333</v>
+      </c>
+      <c r="D27" s="39" t="s">
+        <v>17</v>
       </c>
       <c r="E27" s="95" t="s">
-        <v>93</v>
-      </c>
-      <c r="F27" s="94" t="s">
-        <v>161</v>
-      </c>
-      <c r="G27" s="95" t="s">
-        <v>210</v>
-      </c>
-      <c r="H27" s="94" t="s">
-        <v>250</v>
-      </c>
-      <c r="I27" s="94" t="s">
-        <v>337</v>
-      </c>
-      <c r="J27" s="94" t="s">
-        <v>387</v>
-      </c>
-      <c r="K27" s="95" t="s">
-        <v>295</v>
-      </c>
-      <c r="L27" s="94">
+        <v>466</v>
+      </c>
+      <c r="F27" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="G27" s="96" t="s">
+        <v>467</v>
+      </c>
+      <c r="H27" s="97" t="s">
+        <v>468</v>
+      </c>
+      <c r="I27" s="39" t="s">
+        <v>330</v>
+      </c>
+      <c r="J27" s="39" t="s">
+        <v>469</v>
+      </c>
+      <c r="K27" s="40" t="s">
+        <v>470</v>
+      </c>
+      <c r="L27" s="39">
         <v>1</v>
       </c>
-      <c r="M27" s="96">
+      <c r="M27" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N27" s="96">
-        <v>0</v>
-      </c>
-      <c r="O27" s="97" t="s">
-        <v>367</v>
-      </c>
-      <c r="P27" s="96">
-        <v>0.1653</v>
-      </c>
-      <c r="Q27" s="96">
-        <f t="shared" ref="Q27" si="16">P27*N27</f>
-        <v>0</v>
-      </c>
-      <c r="R27" s="96" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N27" s="42">
+        <v>100</v>
+      </c>
+      <c r="O27" s="65" t="s">
+        <v>360</v>
+      </c>
+      <c r="P27" s="42">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="Q27" s="42">
+        <f t="shared" ref="Q27" si="16">N27*P27</f>
+        <v>0.33999999999999997</v>
+      </c>
+      <c r="R27" s="87" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
       <c r="B28" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="60" t="s">
-        <v>340</v>
-      </c>
-      <c r="D28" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="E28" s="100" t="s">
-        <v>480</v>
-      </c>
-      <c r="F28" s="39" t="s">
+      <c r="C28" s="61" t="s">
+        <v>333</v>
+      </c>
+      <c r="D28" s="37" t="s">
+        <v>472</v>
+      </c>
+      <c r="E28" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="F28" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="G28" s="101" t="s">
-        <v>481</v>
-      </c>
-      <c r="H28" s="102" t="s">
-        <v>482</v>
-      </c>
-      <c r="I28" s="39" t="s">
-        <v>337</v>
-      </c>
-      <c r="J28" s="39" t="s">
-        <v>483</v>
-      </c>
-      <c r="K28" s="40" t="s">
-        <v>484</v>
-      </c>
-      <c r="L28" s="39">
+      <c r="G28" s="38" t="s">
+        <v>205</v>
+      </c>
+      <c r="H28" s="37" t="s">
+        <v>244</v>
+      </c>
+      <c r="I28" s="37" t="s">
+        <v>330</v>
+      </c>
+      <c r="J28" s="37" t="s">
+        <v>380</v>
+      </c>
+      <c r="K28" s="38" t="s">
+        <v>289</v>
+      </c>
+      <c r="L28" s="81">
         <v>1</v>
       </c>
-      <c r="M28" s="42">
+      <c r="M28" s="41">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N28" s="42">
-        <v>100</v>
-      </c>
-      <c r="O28" s="65" t="s">
-        <v>367</v>
-      </c>
-      <c r="P28" s="42">
-        <v>3.3999999999999998E-3</v>
-      </c>
-      <c r="Q28" s="42">
-        <f t="shared" ref="Q28" si="17">N28*P28</f>
-        <v>0.33999999999999997</v>
-      </c>
-      <c r="R28" s="92" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N28" s="93">
+        <v>30</v>
+      </c>
+      <c r="O28" s="64" t="s">
+        <v>360</v>
+      </c>
+      <c r="P28" s="41">
+        <v>0.2525</v>
+      </c>
+      <c r="Q28" s="41">
+        <f t="shared" ref="Q28" si="17">P28*N28</f>
+        <v>7.5750000000000002</v>
+      </c>
+      <c r="R28" s="94" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
       <c r="B29" s="53">
-        <f>ROW(B29) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="61" t="s">
-        <v>340</v>
-      </c>
-      <c r="D29" s="37" t="s">
-        <v>486</v>
-      </c>
-      <c r="E29" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="F29" s="37" t="s">
-        <v>162</v>
-      </c>
-      <c r="G29" s="38" t="s">
-        <v>211</v>
-      </c>
-      <c r="H29" s="37" t="s">
-        <v>251</v>
-      </c>
-      <c r="I29" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="J29" s="37" t="s">
-        <v>388</v>
-      </c>
-      <c r="K29" s="38" t="s">
-        <v>296</v>
-      </c>
-      <c r="L29" s="86">
+      <c r="C29" s="98" t="s">
+        <v>333</v>
+      </c>
+      <c r="D29" s="99" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="96" t="s">
+        <v>91</v>
+      </c>
+      <c r="F29" s="99" t="s">
+        <v>152</v>
+      </c>
+      <c r="G29" s="96" t="s">
+        <v>206</v>
+      </c>
+      <c r="H29" s="99" t="s">
+        <v>242</v>
+      </c>
+      <c r="I29" s="99" t="s">
+        <v>330</v>
+      </c>
+      <c r="J29" s="99" t="s">
+        <v>381</v>
+      </c>
+      <c r="K29" s="96" t="s">
+        <v>290</v>
+      </c>
+      <c r="L29" s="99">
         <v>1</v>
       </c>
-      <c r="M29" s="41">
+      <c r="M29" s="100">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N29" s="98">
-        <v>30</v>
-      </c>
-      <c r="O29" s="64" t="s">
-        <v>367</v>
-      </c>
-      <c r="P29" s="41">
-        <v>0.2525</v>
-      </c>
-      <c r="Q29" s="41">
-        <f t="shared" ref="Q29" si="18">P29*N29</f>
-        <v>7.5750000000000002</v>
-      </c>
-      <c r="R29" s="99" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N29" s="100">
+        <v>0</v>
+      </c>
+      <c r="O29" s="101" t="s">
+        <v>360</v>
+      </c>
+      <c r="P29" s="100">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="Q29" s="100">
+        <f t="shared" ref="Q29" si="18">N29*P29</f>
+        <v>0</v>
+      </c>
+      <c r="R29" s="87" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
       <c r="B30" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="103" t="s">
-        <v>340</v>
-      </c>
-      <c r="D30" s="104" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="101" t="s">
-        <v>95</v>
-      </c>
-      <c r="F30" s="104" t="s">
-        <v>157</v>
-      </c>
-      <c r="G30" s="101" t="s">
-        <v>212</v>
-      </c>
-      <c r="H30" s="104" t="s">
-        <v>249</v>
-      </c>
-      <c r="I30" s="104" t="s">
-        <v>337</v>
-      </c>
-      <c r="J30" s="104" t="s">
-        <v>389</v>
-      </c>
-      <c r="K30" s="101" t="s">
-        <v>297</v>
-      </c>
-      <c r="L30" s="104">
+      <c r="C30" s="61" t="s">
+        <v>333</v>
+      </c>
+      <c r="D30" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="F30" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="G30" s="38" t="s">
+        <v>207</v>
+      </c>
+      <c r="H30" s="37" t="s">
+        <v>245</v>
+      </c>
+      <c r="I30" s="37" t="s">
+        <v>330</v>
+      </c>
+      <c r="J30" s="37" t="s">
+        <v>382</v>
+      </c>
+      <c r="K30" s="38" t="s">
+        <v>291</v>
+      </c>
+      <c r="L30" s="37">
         <v>1</v>
       </c>
-      <c r="M30" s="105">
+      <c r="M30" s="41">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N30" s="105">
-        <v>0</v>
-      </c>
-      <c r="O30" s="106" t="s">
-        <v>367</v>
-      </c>
-      <c r="P30" s="105">
-        <v>4.1999999999999997E-3</v>
-      </c>
-      <c r="Q30" s="105">
-        <f t="shared" ref="Q30" si="19">N30*P30</f>
-        <v>0</v>
-      </c>
-      <c r="R30" s="92" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N30" s="41">
+        <v>22</v>
+      </c>
+      <c r="O30" s="64" t="s">
+        <v>360</v>
+      </c>
+      <c r="P30" s="41">
+        <v>0.89629999999999999</v>
+      </c>
+      <c r="Q30" s="41">
+        <f t="shared" ref="Q30" si="19">P30*N30</f>
+        <v>19.718599999999999</v>
+      </c>
+      <c r="R30" s="41"/>
+    </row>
+    <row r="31" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1"/>
       <c r="B31" s="53">
-        <f>ROW(B31) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="61" t="s">
-        <v>340</v>
-      </c>
-      <c r="D31" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="F31" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="G31" s="38" t="s">
-        <v>213</v>
-      </c>
-      <c r="H31" s="37" t="s">
-        <v>252</v>
-      </c>
-      <c r="I31" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="J31" s="37" t="s">
-        <v>390</v>
-      </c>
-      <c r="K31" s="38" t="s">
-        <v>298</v>
-      </c>
-      <c r="L31" s="37">
+      <c r="C31" s="60" t="s">
+        <v>333</v>
+      </c>
+      <c r="D31" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="F31" s="39" t="s">
+        <v>324</v>
+      </c>
+      <c r="G31" s="39" t="s">
+        <v>159</v>
+      </c>
+      <c r="H31" s="39" t="s">
+        <v>249</v>
+      </c>
+      <c r="I31" s="39" t="s">
+        <v>330</v>
+      </c>
+      <c r="J31" s="39" t="s">
+        <v>383</v>
+      </c>
+      <c r="K31" s="40" t="s">
+        <v>292</v>
+      </c>
+      <c r="L31" s="39">
         <v>1</v>
       </c>
-      <c r="M31" s="41">
+      <c r="M31" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N31" s="41">
-        <v>22</v>
-      </c>
-      <c r="O31" s="64" t="s">
-        <v>367</v>
-      </c>
-      <c r="P31" s="41">
-        <v>0.89629999999999999</v>
-      </c>
-      <c r="Q31" s="41">
-        <f t="shared" ref="Q31" si="20">P31*N31</f>
-        <v>19.718599999999999</v>
-      </c>
-      <c r="R31" s="41"/>
-    </row>
-    <row r="32" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N31" s="42">
+        <v>21</v>
+      </c>
+      <c r="O31" s="65" t="s">
+        <v>360</v>
+      </c>
+      <c r="P31" s="42">
+        <v>0.47249999999999998</v>
+      </c>
+      <c r="Q31" s="42">
+        <f t="shared" ref="Q31" si="20">N31*P31</f>
+        <v>9.9224999999999994</v>
+      </c>
+      <c r="R31" s="42"/>
+    </row>
+    <row r="32" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1"/>
       <c r="B32" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="60" t="s">
-        <v>340</v>
-      </c>
-      <c r="D32" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="E32" s="40" t="s">
-        <v>97</v>
-      </c>
-      <c r="F32" s="39" t="s">
-        <v>331</v>
-      </c>
-      <c r="G32" s="39" t="s">
-        <v>164</v>
-      </c>
-      <c r="H32" s="39" t="s">
-        <v>256</v>
-      </c>
-      <c r="I32" s="39" t="s">
-        <v>337</v>
-      </c>
-      <c r="J32" s="39" t="s">
-        <v>391</v>
-      </c>
-      <c r="K32" s="40" t="s">
-        <v>299</v>
-      </c>
-      <c r="L32" s="39">
+      <c r="C32" s="61" t="s">
+        <v>333</v>
+      </c>
+      <c r="D32" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="F32" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="G32" s="38" t="s">
+        <v>208</v>
+      </c>
+      <c r="H32" s="37" t="s">
+        <v>242</v>
+      </c>
+      <c r="I32" s="37" t="s">
+        <v>330</v>
+      </c>
+      <c r="J32" s="37" t="s">
+        <v>384</v>
+      </c>
+      <c r="K32" s="38" t="s">
+        <v>293</v>
+      </c>
+      <c r="L32" s="37">
         <v>1</v>
       </c>
-      <c r="M32" s="42">
+      <c r="M32" s="41">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N32" s="42">
-        <v>21</v>
-      </c>
-      <c r="O32" s="65" t="s">
-        <v>367</v>
-      </c>
-      <c r="P32" s="42">
-        <v>0.47249999999999998</v>
-      </c>
-      <c r="Q32" s="42">
-        <f t="shared" ref="Q32" si="21">N32*P32</f>
-        <v>9.9224999999999994</v>
-      </c>
-      <c r="R32" s="42"/>
-    </row>
-    <row r="33" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N32" s="41">
+        <v>100</v>
+      </c>
+      <c r="O32" s="64" t="s">
+        <v>360</v>
+      </c>
+      <c r="P32" s="41">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="Q32" s="41">
+        <f t="shared" ref="Q32" si="21">P32*N32</f>
+        <v>0.31</v>
+      </c>
+      <c r="R32" s="41"/>
+    </row>
+    <row r="33" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1"/>
       <c r="B33" s="53">
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
       <c r="C33" s="61" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="D33" s="37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E33" s="38" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G33" s="38" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="H33" s="37" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J33" s="37" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="K33" s="38" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="L33" s="37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M33" s="41">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="N33" s="41">
         <v>100</v>
       </c>
       <c r="O33" s="64" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P33" s="41">
-        <v>3.0999999999999999E-3</v>
+        <v>5.4999999999999997E-3</v>
       </c>
       <c r="Q33" s="41">
         <f t="shared" ref="Q33" si="22">P33*N33</f>
-        <v>0.31</v>
+        <v>0.54999999999999993</v>
       </c>
       <c r="R33" s="41"/>
     </row>
-    <row r="34" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
       <c r="B34" s="53">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="76" t="s">
-        <v>340</v>
-      </c>
-      <c r="D34" s="77" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="78" t="s">
-        <v>99</v>
-      </c>
-      <c r="F34" s="77" t="s">
-        <v>159</v>
-      </c>
-      <c r="G34" s="78" t="s">
-        <v>215</v>
-      </c>
-      <c r="H34" s="77" t="s">
-        <v>253</v>
-      </c>
-      <c r="I34" s="77" t="s">
-        <v>394</v>
-      </c>
-      <c r="J34" s="77" t="s">
-        <v>393</v>
-      </c>
-      <c r="K34" s="78" t="s">
-        <v>286</v>
-      </c>
-      <c r="L34" s="77">
+      <c r="C34" s="60" t="s">
+        <v>334</v>
+      </c>
+      <c r="D34" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="F34" s="39" t="s">
+        <v>324</v>
+      </c>
+      <c r="G34" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="H34" s="39" t="s">
+        <v>250</v>
+      </c>
+      <c r="I34" s="39" t="s">
+        <v>330</v>
+      </c>
+      <c r="J34" s="39" t="s">
+        <v>386</v>
+      </c>
+      <c r="K34" s="40" t="s">
+        <v>330</v>
+      </c>
+      <c r="L34" s="39">
         <v>1</v>
       </c>
-      <c r="M34" s="79">
+      <c r="M34" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N34" s="79">
-        <v>0</v>
-      </c>
-      <c r="O34" s="80" t="s">
-        <v>367</v>
-      </c>
-      <c r="P34" s="79">
-        <v>9.1899999999999996E-2</v>
-      </c>
-      <c r="Q34" s="79">
+      <c r="N34" s="42">
+        <v>30</v>
+      </c>
+      <c r="O34" s="65" t="s">
+        <v>360</v>
+      </c>
+      <c r="P34" s="42">
+        <v>4.87E-2</v>
+      </c>
+      <c r="Q34" s="42">
         <f t="shared" ref="Q34" si="23">N34*P34</f>
-        <v>0</v>
-      </c>
-      <c r="R34" s="79" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1.4610000000000001</v>
+      </c>
+      <c r="R34" s="42"/>
+    </row>
+    <row r="35" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1"/>
       <c r="B35" s="53">
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
       <c r="C35" s="61" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="D35" s="37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E35" s="38" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F35" s="37" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G35" s="38" t="s">
-        <v>216</v>
+        <v>295</v>
       </c>
       <c r="H35" s="37" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="I35" s="37" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J35" s="37" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="K35" s="38" t="s">
-        <v>301</v>
+        <v>330</v>
       </c>
       <c r="L35" s="37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M35" s="41">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="N35" s="41">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="O35" s="64" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P35" s="41">
-        <v>5.4999999999999997E-3</v>
+        <v>7.4300000000000005E-2</v>
       </c>
       <c r="Q35" s="41">
         <f t="shared" ref="Q35" si="24">P35*N35</f>
-        <v>0.54999999999999993</v>
+        <v>2.2290000000000001</v>
       </c>
       <c r="R35" s="41"/>
     </row>
-    <row r="36" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1"/>
       <c r="B36" s="53">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="C36" s="60" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="D36" s="39" t="s">
-        <v>26</v>
+        <v>491</v>
       </c>
       <c r="E36" s="40" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F36" s="39" t="s">
-        <v>331</v>
+        <v>161</v>
       </c>
       <c r="G36" s="40" t="s">
-        <v>165</v>
+        <v>296</v>
       </c>
       <c r="H36" s="39" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="I36" s="39" t="s">
-        <v>337</v>
+        <v>296</v>
       </c>
       <c r="J36" s="39" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="K36" s="40" t="s">
-        <v>337</v>
-      </c>
-      <c r="L36" s="39">
-        <v>1</v>
+        <v>330</v>
+      </c>
+      <c r="L36" s="85">
+        <v>2</v>
       </c>
       <c r="M36" s="42">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N36" s="42">
-        <v>30</v>
+        <v>40</v>
+      </c>
+      <c r="N36" s="86">
+        <v>60</v>
       </c>
       <c r="O36" s="65" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P36" s="42">
-        <v>4.87E-2</v>
+        <v>2.8899999999999999E-2</v>
       </c>
       <c r="Q36" s="42">
         <f t="shared" ref="Q36" si="25">N36*P36</f>
-        <v>1.4610000000000001</v>
-      </c>
-      <c r="R36" s="42"/>
-    </row>
-    <row r="37" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1.734</v>
+      </c>
+      <c r="R36" s="102" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1"/>
       <c r="B37" s="53">
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
       <c r="C37" s="61" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="D37" s="37" t="s">
-        <v>27</v>
+        <v>459</v>
       </c>
       <c r="E37" s="38" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F37" s="37" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G37" s="38" t="s">
-        <v>302</v>
+        <v>210</v>
       </c>
       <c r="H37" s="37" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="I37" s="37" t="s">
-        <v>337</v>
+        <v>390</v>
       </c>
       <c r="J37" s="37" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="K37" s="38" t="s">
-        <v>337</v>
-      </c>
-      <c r="L37" s="37">
-        <v>1</v>
+        <v>330</v>
+      </c>
+      <c r="L37" s="81">
+        <v>9</v>
       </c>
       <c r="M37" s="41">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N37" s="41">
-        <v>30</v>
+        <v>180</v>
+      </c>
+      <c r="N37" s="93">
+        <v>190</v>
       </c>
       <c r="O37" s="64" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P37" s="41">
-        <v>7.4300000000000005E-2</v>
+        <v>0.12590000000000001</v>
       </c>
       <c r="Q37" s="41">
         <f t="shared" ref="Q37" si="26">P37*N37</f>
-        <v>2.2290000000000001</v>
-      </c>
-      <c r="R37" s="41"/>
-    </row>
-    <row r="38" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>23.921000000000003</v>
+      </c>
+      <c r="R37" s="94" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1"/>
       <c r="B38" s="53">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="C38" s="60" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="D38" s="39" t="s">
-        <v>505</v>
+        <v>25</v>
       </c>
       <c r="E38" s="40" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F38" s="39" t="s">
-        <v>166</v>
+        <v>324</v>
       </c>
       <c r="G38" s="40" t="s">
-        <v>303</v>
+        <v>163</v>
       </c>
       <c r="H38" s="39" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="I38" s="39" t="s">
-        <v>303</v>
+        <v>392</v>
       </c>
       <c r="J38" s="39" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="K38" s="40" t="s">
-        <v>337</v>
-      </c>
-      <c r="L38" s="90">
-        <v>2</v>
+        <v>330</v>
+      </c>
+      <c r="L38" s="39">
+        <v>1</v>
       </c>
       <c r="M38" s="42">
         <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N38" s="91">
-        <v>60</v>
+        <v>20</v>
+      </c>
+      <c r="N38" s="42">
+        <v>30</v>
       </c>
       <c r="O38" s="65" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P38" s="42">
-        <v>2.8899999999999999E-2</v>
+        <v>5.6000000000000001E-2</v>
       </c>
       <c r="Q38" s="42">
         <f t="shared" ref="Q38" si="27">N38*P38</f>
-        <v>1.734</v>
-      </c>
-      <c r="R38" s="107" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1.68</v>
+      </c>
+      <c r="R38" s="42"/>
+    </row>
+    <row r="39" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1"/>
       <c r="B39" s="53">
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
       <c r="C39" s="61" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>470</v>
+        <v>26</v>
       </c>
       <c r="E39" s="38" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>167</v>
+        <v>325</v>
       </c>
       <c r="G39" s="38" t="s">
-        <v>217</v>
+        <v>164</v>
       </c>
       <c r="H39" s="37" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="I39" s="37" t="s">
-        <v>400</v>
+        <v>330</v>
       </c>
       <c r="J39" s="37" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="K39" s="38" t="s">
-        <v>337</v>
-      </c>
-      <c r="L39" s="86">
-        <v>9</v>
+        <v>330</v>
+      </c>
+      <c r="L39" s="37">
+        <v>4</v>
       </c>
       <c r="M39" s="41">
         <f t="shared" si="1"/>
-        <v>180</v>
-      </c>
-      <c r="N39" s="98">
-        <v>190</v>
+        <v>80</v>
+      </c>
+      <c r="N39" s="41">
+        <v>100</v>
       </c>
       <c r="O39" s="64" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P39" s="41">
-        <v>0.12590000000000001</v>
+        <v>2.9499999999999998E-2</v>
       </c>
       <c r="Q39" s="41">
         <f t="shared" ref="Q39" si="28">P39*N39</f>
-        <v>23.921000000000003</v>
-      </c>
-      <c r="R39" s="99" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2.9499999999999997</v>
+      </c>
+      <c r="R39" s="41"/>
+    </row>
+    <row r="40" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1"/>
       <c r="B40" s="53">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="C40" s="60" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="D40" s="39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E40" s="40" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F40" s="39" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="G40" s="40" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="H40" s="39" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="I40" s="39" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="J40" s="39" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="K40" s="40" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="L40" s="39">
         <v>1</v>
@@ -5083,107 +5054,111 @@
         <v>20</v>
       </c>
       <c r="N40" s="42">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="O40" s="65" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P40" s="42">
-        <v>5.6000000000000001E-2</v>
+        <v>0.53559999999999997</v>
       </c>
       <c r="Q40" s="42">
         <f t="shared" ref="Q40" si="29">N40*P40</f>
-        <v>1.68</v>
-      </c>
-      <c r="R40" s="42"/>
-    </row>
-    <row r="41" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>11.247599999999998</v>
+      </c>
+      <c r="R40" s="102" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1"/>
       <c r="B41" s="53">
         <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
       <c r="C41" s="61" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="D41" s="37" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E41" s="38" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F41" s="37" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="G41" s="38" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="H41" s="37" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="I41" s="37" t="s">
-        <v>337</v>
+        <v>397</v>
       </c>
       <c r="J41" s="37" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="K41" s="38" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="L41" s="37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M41" s="41">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="N41" s="41">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="O41" s="64" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P41" s="41">
-        <v>2.9499999999999998E-2</v>
+        <v>0.65639999999999998</v>
       </c>
       <c r="Q41" s="41">
         <f t="shared" ref="Q41" si="30">P41*N41</f>
-        <v>2.9499999999999997</v>
-      </c>
-      <c r="R41" s="41"/>
-    </row>
-    <row r="42" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>27.5688</v>
+      </c>
+      <c r="R41" s="94" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1"/>
       <c r="B42" s="53">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="C42" s="60" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="D42" s="39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E42" s="40" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F42" s="39" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="G42" s="40" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H42" s="39" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="I42" s="39" t="s">
-        <v>405</v>
+        <v>330</v>
       </c>
       <c r="J42" s="39" t="s">
-        <v>406</v>
+        <v>330</v>
       </c>
       <c r="K42" s="40" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="L42" s="39">
         <v>1</v>
@@ -5196,108 +5171,104 @@
         <v>21</v>
       </c>
       <c r="O42" s="65" t="s">
-        <v>367</v>
+        <v>399</v>
       </c>
       <c r="P42" s="42">
-        <v>0.53559999999999997</v>
+        <v>1.2</v>
       </c>
       <c r="Q42" s="42">
         <f t="shared" ref="Q42" si="31">N42*P42</f>
-        <v>11.247599999999998</v>
-      </c>
-      <c r="R42" s="107" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>25.2</v>
+      </c>
+      <c r="R42" s="42"/>
+    </row>
+    <row r="43" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
       <c r="B43" s="53">
         <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
       </c>
       <c r="C43" s="61" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="D43" s="37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E43" s="38" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F43" s="37" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="G43" s="38" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H43" s="37" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="I43" s="37" t="s">
-        <v>407</v>
+        <v>330</v>
       </c>
       <c r="J43" s="37" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="K43" s="38" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="L43" s="37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M43" s="41">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="N43" s="41">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="O43" s="64" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P43" s="41">
-        <v>0.65639999999999998</v>
+        <v>9.2200000000000004E-2</v>
       </c>
       <c r="Q43" s="41">
         <f t="shared" ref="Q43" si="32">P43*N43</f>
-        <v>27.5688</v>
-      </c>
-      <c r="R43" s="99" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2.3050000000000002</v>
+      </c>
+      <c r="R43" s="41"/>
+    </row>
+    <row r="44" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
       <c r="B44" s="53">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="C44" s="60" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="D44" s="39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E44" s="40" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F44" s="39" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="G44" s="40" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H44" s="39" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="I44" s="39" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J44" s="39" t="s">
-        <v>337</v>
+        <v>401</v>
       </c>
       <c r="K44" s="40" t="s">
-        <v>337</v>
+        <v>297</v>
       </c>
       <c r="L44" s="39">
         <v>1</v>
@@ -5310,49 +5281,49 @@
         <v>21</v>
       </c>
       <c r="O44" s="65" t="s">
-        <v>409</v>
+        <v>360</v>
       </c>
       <c r="P44" s="42">
-        <v>1.2</v>
+        <v>0.45629999999999998</v>
       </c>
       <c r="Q44" s="42">
         <f t="shared" ref="Q44" si="33">N44*P44</f>
-        <v>25.2</v>
+        <v>9.5823</v>
       </c>
       <c r="R44" s="42"/>
     </row>
-    <row r="45" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
       <c r="B45" s="53">
         <f>ROW(B45) - ROW($B$9)</f>
         <v>36</v>
       </c>
       <c r="C45" s="61" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="D45" s="37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E45" s="38" t="s">
-        <v>110</v>
+        <v>485</v>
       </c>
       <c r="F45" s="37" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="G45" s="38" t="s">
-        <v>173</v>
-      </c>
-      <c r="H45" s="37" t="s">
-        <v>264</v>
+        <v>486</v>
+      </c>
+      <c r="H45" s="84" t="s">
+        <v>487</v>
       </c>
       <c r="I45" s="37" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J45" s="37" t="s">
-        <v>410</v>
+        <v>488</v>
       </c>
       <c r="K45" s="38" t="s">
-        <v>337</v>
+        <v>489</v>
       </c>
       <c r="L45" s="37">
         <v>1</v>
@@ -5361,53 +5332,55 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N45" s="41">
+      <c r="N45" s="93">
         <v>25</v>
       </c>
       <c r="O45" s="64" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P45" s="41">
-        <v>9.2200000000000004E-2</v>
+        <v>0.1012</v>
       </c>
       <c r="Q45" s="41">
         <f t="shared" ref="Q45" si="34">P45*N45</f>
-        <v>2.3050000000000002</v>
-      </c>
-      <c r="R45" s="41"/>
-    </row>
-    <row r="46" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="R45" s="82" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1"/>
       <c r="B46" s="53">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="C46" s="60" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D46" s="39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E46" s="40" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F46" s="39" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="G46" s="40" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="H46" s="39" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="I46" s="39" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J46" s="39" t="s">
-        <v>411</v>
+        <v>330</v>
       </c>
       <c r="K46" s="40" t="s">
-        <v>304</v>
+        <v>330</v>
       </c>
       <c r="L46" s="39">
         <v>1</v>
@@ -5417,52 +5390,52 @@
         <v>20</v>
       </c>
       <c r="N46" s="42">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="O46" s="65" t="s">
-        <v>367</v>
+        <v>402</v>
       </c>
       <c r="P46" s="42">
-        <v>0.45629999999999998</v>
+        <v>0.156</v>
       </c>
       <c r="Q46" s="42">
         <f t="shared" ref="Q46" si="35">N46*P46</f>
-        <v>9.5823</v>
+        <v>4.68</v>
       </c>
       <c r="R46" s="42"/>
     </row>
-    <row r="47" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
       <c r="B47" s="53">
         <f>ROW(B47) - ROW($B$9)</f>
         <v>38</v>
       </c>
       <c r="C47" s="61" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D47" s="37" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E47" s="38" t="s">
-        <v>499</v>
+        <v>108</v>
       </c>
       <c r="F47" s="37" t="s">
-        <v>331</v>
+        <v>171</v>
       </c>
       <c r="G47" s="38" t="s">
-        <v>500</v>
-      </c>
-      <c r="H47" s="89" t="s">
-        <v>501</v>
+        <v>211</v>
+      </c>
+      <c r="H47" s="37" t="s">
+        <v>259</v>
       </c>
       <c r="I47" s="37" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J47" s="37" t="s">
-        <v>502</v>
+        <v>330</v>
       </c>
       <c r="K47" s="38" t="s">
-        <v>503</v>
+        <v>330</v>
       </c>
       <c r="L47" s="37">
         <v>1</v>
@@ -5471,454 +5444,452 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N47" s="98">
-        <v>25</v>
+      <c r="N47" s="41">
+        <v>30</v>
       </c>
       <c r="O47" s="64" t="s">
-        <v>367</v>
+        <v>403</v>
       </c>
       <c r="P47" s="41">
-        <v>0.1012</v>
+        <v>0.08</v>
       </c>
       <c r="Q47" s="41">
         <f t="shared" ref="Q47" si="36">P47*N47</f>
-        <v>2.5299999999999998</v>
-      </c>
-      <c r="R47" s="87" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2.4</v>
+      </c>
+      <c r="R47" s="41"/>
+    </row>
+    <row r="48" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1"/>
       <c r="B48" s="53">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="C48" s="60" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="D48" s="39" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E48" s="40" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F48" s="39" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="G48" s="40" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H48" s="39" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="I48" s="39" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J48" s="39" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K48" s="40" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="L48" s="39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M48" s="42">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N48" s="42">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="O48" s="65" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="P48" s="42">
-        <v>0.156</v>
+        <v>1.5</v>
       </c>
       <c r="Q48" s="42">
         <f t="shared" ref="Q48" si="37">N48*P48</f>
-        <v>4.68</v>
-      </c>
-      <c r="R48" s="42"/>
-    </row>
-    <row r="49" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+      <c r="R48" s="42" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1"/>
       <c r="B49" s="53">
         <f>ROW(B49) - ROW($B$9)</f>
         <v>40</v>
       </c>
-      <c r="C49" s="61" t="s">
-        <v>346</v>
-      </c>
-      <c r="D49" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="E49" s="38" t="s">
-        <v>113</v>
-      </c>
-      <c r="F49" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="G49" s="38" t="s">
-        <v>218</v>
-      </c>
-      <c r="H49" s="37" t="s">
-        <v>266</v>
-      </c>
-      <c r="I49" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="J49" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="K49" s="38" t="s">
-        <v>337</v>
-      </c>
-      <c r="L49" s="37">
-        <v>1</v>
-      </c>
-      <c r="M49" s="41">
+      <c r="C49" s="67" t="s">
+        <v>298</v>
+      </c>
+      <c r="D49" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="E49" s="69" t="s">
+        <v>110</v>
+      </c>
+      <c r="F49" s="68" t="s">
+        <v>173</v>
+      </c>
+      <c r="G49" s="69" t="s">
+        <v>330</v>
+      </c>
+      <c r="H49" s="68" t="s">
+        <v>330</v>
+      </c>
+      <c r="I49" s="68"/>
+      <c r="J49" s="68"/>
+      <c r="K49" s="69" t="s">
+        <v>330</v>
+      </c>
+      <c r="L49" s="68">
+        <v>4</v>
+      </c>
+      <c r="M49" s="70">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N49" s="41">
-        <v>30</v>
-      </c>
-      <c r="O49" s="64" t="s">
-        <v>413</v>
-      </c>
-      <c r="P49" s="41">
-        <v>0.08</v>
-      </c>
-      <c r="Q49" s="41">
-        <f t="shared" ref="Q49" si="38">P49*N49</f>
-        <v>2.4</v>
-      </c>
-      <c r="R49" s="41"/>
-    </row>
-    <row r="50" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="N49" s="70">
+        <f t="shared" ref="N49" si="38">M49+(M49*0.1)</f>
+        <v>88</v>
+      </c>
+      <c r="O49" s="70"/>
+      <c r="P49" s="70"/>
+      <c r="Q49" s="70">
+        <f t="shared" ref="Q49" si="39">P49*N49</f>
+        <v>0</v>
+      </c>
+      <c r="R49" s="71" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1"/>
       <c r="B50" s="53">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="C50" s="60" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="D50" s="39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E50" s="40" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F50" s="39" t="s">
-        <v>331</v>
-      </c>
-      <c r="G50" s="40" t="s">
-        <v>177</v>
+        <v>174</v>
+      </c>
+      <c r="G50" s="40">
+        <v>61300211121</v>
       </c>
       <c r="H50" s="39" t="s">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="I50" s="39" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J50" s="39" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K50" s="40" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="L50" s="39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M50" s="42">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="N50" s="42">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="O50" s="65" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="P50" s="42">
-        <v>1.5</v>
+        <v>0.13</v>
       </c>
       <c r="Q50" s="42">
-        <f t="shared" ref="Q50" si="39">N50*P50</f>
-        <v>75</v>
+        <f t="shared" ref="Q50" si="40">N50*P50</f>
+        <v>11.700000000000001</v>
       </c>
       <c r="R50" s="42" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1"/>
       <c r="B51" s="53">
         <f>ROW(B51) - ROW($B$9)</f>
         <v>42</v>
       </c>
-      <c r="C51" s="67" t="s">
-        <v>305</v>
-      </c>
-      <c r="D51" s="68" t="s">
-        <v>39</v>
-      </c>
-      <c r="E51" s="69" t="s">
-        <v>115</v>
-      </c>
-      <c r="F51" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="G51" s="69" t="s">
-        <v>337</v>
-      </c>
-      <c r="H51" s="68" t="s">
-        <v>337</v>
-      </c>
-      <c r="I51" s="68"/>
-      <c r="J51" s="68"/>
-      <c r="K51" s="69" t="s">
-        <v>337</v>
-      </c>
-      <c r="L51" s="68">
+      <c r="C51" s="61" t="s">
+        <v>340</v>
+      </c>
+      <c r="D51" s="37" t="s">
+        <v>497</v>
+      </c>
+      <c r="E51" s="38" t="s">
+        <v>112</v>
+      </c>
+      <c r="F51" s="37" t="s">
+        <v>175</v>
+      </c>
+      <c r="G51" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="H51" s="37" t="s">
+        <v>261</v>
+      </c>
+      <c r="I51" s="37" t="s">
+        <v>406</v>
+      </c>
+      <c r="J51" s="37" t="s">
+        <v>407</v>
+      </c>
+      <c r="K51" s="38" t="s">
+        <v>330</v>
+      </c>
+      <c r="L51" s="81">
         <v>4</v>
       </c>
-      <c r="M51" s="70">
+      <c r="M51" s="41">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N51" s="70">
-        <f t="shared" ref="N51" si="40">M51+(M51*0.1)</f>
-        <v>88</v>
-      </c>
-      <c r="O51" s="70"/>
-      <c r="P51" s="70"/>
-      <c r="Q51" s="70">
+      <c r="N51" s="41">
+        <v>85</v>
+      </c>
+      <c r="O51" s="64" t="s">
+        <v>360</v>
+      </c>
+      <c r="P51" s="41">
+        <v>0.21740000000000001</v>
+      </c>
+      <c r="Q51" s="41">
         <f t="shared" ref="Q51" si="41">P51*N51</f>
-        <v>0</v>
-      </c>
-      <c r="R51" s="71" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>18.478999999999999</v>
+      </c>
+      <c r="R51" s="41" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1"/>
       <c r="B52" s="53">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="C52" s="60" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="D52" s="39" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E52" s="40" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F52" s="39" t="s">
-        <v>179</v>
-      </c>
-      <c r="G52" s="40">
-        <v>61300211121</v>
+        <v>176</v>
+      </c>
+      <c r="G52" s="40" t="s">
+        <v>213</v>
       </c>
       <c r="H52" s="39" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="I52" s="39" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J52" s="39" t="s">
-        <v>337</v>
+        <v>409</v>
       </c>
       <c r="K52" s="40" t="s">
-        <v>337</v>
+        <v>299</v>
       </c>
       <c r="L52" s="39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M52" s="42">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="N52" s="42">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="O52" s="65" t="s">
-        <v>409</v>
+        <v>360</v>
       </c>
       <c r="P52" s="42">
-        <v>0.13</v>
+        <v>1E-3</v>
       </c>
       <c r="Q52" s="42">
         <f t="shared" ref="Q52" si="42">N52*P52</f>
-        <v>11.700000000000001</v>
-      </c>
-      <c r="R52" s="42" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+      <c r="R52" s="42"/>
+    </row>
+    <row r="53" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1"/>
       <c r="B53" s="53">
         <f>ROW(B53) - ROW($B$9)</f>
         <v>44</v>
       </c>
       <c r="C53" s="61" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="D53" s="37" t="s">
-        <v>511</v>
+        <v>39</v>
       </c>
       <c r="E53" s="38" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F53" s="37" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="G53" s="38" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="H53" s="37" t="s">
-        <v>268</v>
+        <v>242</v>
       </c>
       <c r="I53" s="37" t="s">
-        <v>416</v>
+        <v>330</v>
       </c>
       <c r="J53" s="37" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="K53" s="38" t="s">
-        <v>337</v>
-      </c>
-      <c r="L53" s="86">
-        <v>4</v>
+        <v>300</v>
+      </c>
+      <c r="L53" s="37">
+        <v>1</v>
       </c>
       <c r="M53" s="41">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="N53" s="41">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="O53" s="64" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P53" s="41">
-        <v>0.21740000000000001</v>
+        <v>1.4E-3</v>
       </c>
       <c r="Q53" s="41">
         <f t="shared" ref="Q53" si="43">P53*N53</f>
-        <v>18.478999999999999</v>
-      </c>
-      <c r="R53" s="41" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="R53" s="41"/>
+    </row>
+    <row r="54" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1"/>
       <c r="B54" s="53">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="C54" s="60" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="D54" s="39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E54" s="40" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F54" s="39" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G54" s="40" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="H54" s="39" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="I54" s="39" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J54" s="39" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="K54" s="40" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="L54" s="39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M54" s="42">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="N54" s="42">
         <v>100</v>
       </c>
       <c r="O54" s="65" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P54" s="42">
-        <v>1E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="Q54" s="42">
         <f t="shared" ref="Q54" si="44">N54*P54</f>
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="R54" s="42"/>
     </row>
-    <row r="55" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1"/>
       <c r="B55" s="53">
         <f>ROW(B55) - ROW($B$9)</f>
         <v>46</v>
       </c>
       <c r="C55" s="61" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="D55" s="37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E55" s="38" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F55" s="37" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G55" s="38" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="H55" s="37" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="I55" s="37" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J55" s="37" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="K55" s="38" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="L55" s="37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M55" s="41">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N55" s="41">
         <v>100</v>
       </c>
       <c r="O55" s="64" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P55" s="41">
         <v>1.4E-3</v>
@@ -5929,370 +5900,370 @@
       </c>
       <c r="R55" s="41"/>
     </row>
-    <row r="56" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
       <c r="B56" s="53">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="C56" s="60" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="D56" s="39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E56" s="40" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F56" s="39" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G56" s="40" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="H56" s="39" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="I56" s="39" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J56" s="39" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="K56" s="40" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="L56" s="39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M56" s="42">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="N56" s="42">
         <v>100</v>
       </c>
       <c r="O56" s="65" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P56" s="42">
-        <v>1.6000000000000001E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q56" s="42">
         <f t="shared" ref="Q56" si="46">N56*P56</f>
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="R56" s="42"/>
     </row>
-    <row r="57" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1"/>
       <c r="B57" s="53">
         <f>ROW(B57) - ROW($B$9)</f>
         <v>48</v>
       </c>
       <c r="C57" s="61" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="D57" s="37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E57" s="38" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F57" s="37" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="G57" s="38" t="s">
-        <v>223</v>
+        <v>346</v>
       </c>
       <c r="H57" s="37" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="I57" s="37" t="s">
-        <v>337</v>
+        <v>414</v>
       </c>
       <c r="J57" s="37" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="K57" s="38" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="L57" s="37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M57" s="41">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="N57" s="41">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="O57" s="64" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P57" s="41">
-        <v>1.4E-3</v>
+        <v>6.4500000000000002E-2</v>
       </c>
       <c r="Q57" s="41">
         <f t="shared" ref="Q57" si="47">P57*N57</f>
-        <v>0.13999999999999999</v>
+        <v>5.8049999999999997</v>
       </c>
       <c r="R57" s="41"/>
     </row>
-    <row r="58" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1"/>
       <c r="B58" s="53">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="C58" s="60" t="s">
-        <v>348</v>
-      </c>
-      <c r="D58" s="39" t="s">
-        <v>45</v>
+        <v>341</v>
+      </c>
+      <c r="D58" s="97" t="s">
+        <v>450</v>
       </c>
       <c r="E58" s="40" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F58" s="39" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G58" s="40" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="H58" s="39" t="s">
-        <v>249</v>
-      </c>
-      <c r="I58" s="39" t="s">
-        <v>337</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="I58" s="39"/>
       <c r="J58" s="39" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="K58" s="40" t="s">
-        <v>310</v>
-      </c>
-      <c r="L58" s="39">
-        <v>4</v>
+        <v>305</v>
+      </c>
+      <c r="L58" s="85">
+        <v>1</v>
       </c>
       <c r="M58" s="42">
         <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-      <c r="N58" s="42">
+        <v>20</v>
+      </c>
+      <c r="N58" s="86">
         <v>100</v>
       </c>
       <c r="O58" s="65" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P58" s="42">
-        <v>1.2999999999999999E-3</v>
+        <v>1.5E-3</v>
       </c>
       <c r="Q58" s="42">
-        <f t="shared" ref="Q58" si="48">N58*P58</f>
-        <v>0.13</v>
-      </c>
-      <c r="R58" s="42"/>
-    </row>
-    <row r="59" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" ref="Q58:Q59" si="48">N58*P58</f>
+        <v>0.15</v>
+      </c>
+      <c r="R58" s="87" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1"/>
       <c r="B59" s="53">
         <f>ROW(B59) - ROW($B$9)</f>
         <v>50</v>
       </c>
       <c r="C59" s="61" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="D59" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="E59" s="38" t="s">
-        <v>123</v>
+        <v>449</v>
+      </c>
+      <c r="E59" s="37" t="s">
+        <v>498</v>
       </c>
       <c r="F59" s="37" t="s">
-        <v>182</v>
-      </c>
-      <c r="G59" s="38" t="s">
-        <v>353</v>
+        <v>176</v>
+      </c>
+      <c r="G59" s="37" t="s">
+        <v>452</v>
       </c>
       <c r="H59" s="37" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="I59" s="37" t="s">
-        <v>424</v>
+        <v>330</v>
       </c>
       <c r="J59" s="37" t="s">
-        <v>425</v>
-      </c>
-      <c r="K59" s="38" t="s">
-        <v>311</v>
-      </c>
-      <c r="L59" s="37">
-        <v>4</v>
-      </c>
-      <c r="M59" s="41">
+        <v>453</v>
+      </c>
+      <c r="K59" s="37" t="s">
+        <v>454</v>
+      </c>
+      <c r="L59" s="81">
+        <v>8</v>
+      </c>
+      <c r="M59" s="37">
         <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-      <c r="N59" s="41">
-        <v>90</v>
-      </c>
-      <c r="O59" s="64" t="s">
-        <v>367</v>
-      </c>
-      <c r="P59" s="41">
-        <v>6.4500000000000002E-2</v>
-      </c>
-      <c r="Q59" s="41">
-        <f t="shared" ref="Q59" si="49">P59*N59</f>
-        <v>5.8049999999999997</v>
-      </c>
-      <c r="R59" s="41"/>
-    </row>
-    <row r="60" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>160</v>
+      </c>
+      <c r="N59" s="104">
+        <v>100</v>
+      </c>
+      <c r="O59" s="105" t="s">
+        <v>360</v>
+      </c>
+      <c r="P59" s="37">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q59" s="37">
+        <f t="shared" si="48"/>
+        <v>0.11</v>
+      </c>
+      <c r="R59" s="82" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1"/>
       <c r="B60" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B60) - ROW($B$9)</f>
         <v>51</v>
       </c>
-      <c r="C60" s="60" t="s">
-        <v>348</v>
-      </c>
-      <c r="D60" s="102" t="s">
-        <v>460</v>
-      </c>
-      <c r="E60" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="F60" s="39" t="s">
-        <v>181</v>
-      </c>
-      <c r="G60" s="40" t="s">
-        <v>225</v>
-      </c>
-      <c r="H60" s="39" t="s">
-        <v>249</v>
-      </c>
-      <c r="I60" s="39"/>
-      <c r="J60" s="39" t="s">
-        <v>426</v>
-      </c>
-      <c r="K60" s="40" t="s">
-        <v>312</v>
-      </c>
-      <c r="L60" s="90">
+      <c r="C60" s="61" t="s">
+        <v>341</v>
+      </c>
+      <c r="D60" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="E60" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="F60" s="37" t="s">
+        <v>176</v>
+      </c>
+      <c r="G60" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="H60" s="37" t="s">
+        <v>264</v>
+      </c>
+      <c r="I60" s="37" t="s">
+        <v>330</v>
+      </c>
+      <c r="J60" s="37" t="s">
+        <v>330</v>
+      </c>
+      <c r="K60" s="38" t="s">
+        <v>306</v>
+      </c>
+      <c r="L60" s="37">
         <v>1</v>
       </c>
-      <c r="M60" s="42">
+      <c r="M60" s="41">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N60" s="91">
-        <v>100</v>
-      </c>
-      <c r="O60" s="65" t="s">
-        <v>367</v>
-      </c>
-      <c r="P60" s="42">
-        <v>1.5E-3</v>
-      </c>
-      <c r="Q60" s="42">
-        <f t="shared" ref="Q60:Q61" si="50">N60*P60</f>
-        <v>0.15</v>
-      </c>
-      <c r="R60" s="92" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="61" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N60" s="41">
+        <v>30</v>
+      </c>
+      <c r="O60" s="64" t="s">
+        <v>402</v>
+      </c>
+      <c r="P60" s="41">
+        <v>1.8589999999999999E-2</v>
+      </c>
+      <c r="Q60" s="41">
+        <f t="shared" ref="Q60" si="49">P60*N60</f>
+        <v>0.55769999999999997</v>
+      </c>
+      <c r="R60" s="41"/>
+    </row>
+    <row r="61" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1"/>
       <c r="B61" s="53">
-        <f>ROW(B61) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="C61" s="61" t="s">
-        <v>348</v>
-      </c>
-      <c r="D61" s="37" t="s">
-        <v>459</v>
-      </c>
-      <c r="E61" s="37" t="s">
-        <v>512</v>
-      </c>
-      <c r="F61" s="37" t="s">
-        <v>181</v>
-      </c>
-      <c r="G61" s="37" t="s">
-        <v>462</v>
-      </c>
-      <c r="H61" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="I61" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="J61" s="37" t="s">
-        <v>463</v>
-      </c>
-      <c r="K61" s="37" t="s">
-        <v>464</v>
-      </c>
-      <c r="L61" s="86">
-        <v>8</v>
-      </c>
-      <c r="M61" s="37">
+      <c r="C61" s="60" t="s">
+        <v>341</v>
+      </c>
+      <c r="D61" s="39" t="s">
+        <v>45</v>
+      </c>
+      <c r="E61" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="F61" s="39" t="s">
+        <v>176</v>
+      </c>
+      <c r="G61" s="40" t="s">
+        <v>220</v>
+      </c>
+      <c r="H61" s="39" t="s">
+        <v>242</v>
+      </c>
+      <c r="I61" s="39" t="s">
+        <v>330</v>
+      </c>
+      <c r="J61" s="39" t="s">
+        <v>417</v>
+      </c>
+      <c r="K61" s="40" t="s">
+        <v>307</v>
+      </c>
+      <c r="L61" s="39">
+        <v>1</v>
+      </c>
+      <c r="M61" s="42">
         <f t="shared" si="1"/>
-        <v>160</v>
-      </c>
-      <c r="N61" s="112">
+        <v>20</v>
+      </c>
+      <c r="N61" s="42">
         <v>100</v>
       </c>
-      <c r="O61" s="113" t="s">
-        <v>367</v>
-      </c>
-      <c r="P61" s="37">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="Q61" s="37">
-        <f t="shared" si="50"/>
-        <v>0.11</v>
-      </c>
-      <c r="R61" s="87" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O61" s="65" t="s">
+        <v>360</v>
+      </c>
+      <c r="P61" s="42">
+        <v>1.4E-3</v>
+      </c>
+      <c r="Q61" s="42">
+        <f t="shared" ref="Q61" si="50">N61*P61</f>
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="R61" s="42"/>
+    </row>
+    <row r="62" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1"/>
       <c r="B62" s="53">
         <f>ROW(B62) - ROW($B$9)</f>
         <v>53</v>
       </c>
       <c r="C62" s="61" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="D62" s="37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E62" s="38" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F62" s="37" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G62" s="38" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H62" s="37" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="I62" s="37" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J62" s="37" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K62" s="38" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="L62" s="37">
         <v>1</v>
@@ -6302,52 +6273,52 @@
         <v>20</v>
       </c>
       <c r="N62" s="41">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="O62" s="64" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="P62" s="41">
-        <v>1.8589999999999999E-2</v>
+        <v>4.6699999999999997E-3</v>
       </c>
       <c r="Q62" s="41">
         <f t="shared" ref="Q62" si="51">P62*N62</f>
-        <v>0.55769999999999997</v>
+        <v>0.23349999999999999</v>
       </c>
       <c r="R62" s="41"/>
     </row>
-    <row r="63" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1"/>
       <c r="B63" s="53">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
       <c r="C63" s="60" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="D63" s="39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E63" s="40" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F63" s="39" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G63" s="40" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H63" s="39" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="I63" s="39" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J63" s="39" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="K63" s="40" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="L63" s="39">
         <v>1</v>
@@ -6360,49 +6331,49 @@
         <v>100</v>
       </c>
       <c r="O63" s="65" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P63" s="42">
-        <v>1.4E-3</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q63" s="42">
         <f t="shared" ref="Q63" si="52">N63*P63</f>
-        <v>0.13999999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="R63" s="42"/>
     </row>
-    <row r="64" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1"/>
       <c r="B64" s="53">
         <f>ROW(B64) - ROW($B$9)</f>
         <v>55</v>
       </c>
       <c r="C64" s="61" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="D64" s="37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E64" s="38" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F64" s="37" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G64" s="38" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="H64" s="37" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="I64" s="37" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J64" s="37" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K64" s="38" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="L64" s="37">
         <v>1</v>
@@ -6415,49 +6386,49 @@
         <v>50</v>
       </c>
       <c r="O64" s="64" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="P64" s="41">
-        <v>4.6699999999999997E-3</v>
+        <v>1.11E-2</v>
       </c>
       <c r="Q64" s="41">
         <f t="shared" ref="Q64" si="53">P64*N64</f>
-        <v>0.23349999999999999</v>
+        <v>0.55500000000000005</v>
       </c>
       <c r="R64" s="41"/>
     </row>
-    <row r="65" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1"/>
       <c r="B65" s="53">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="C65" s="60" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="D65" s="39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E65" s="40" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F65" s="39" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G65" s="40" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="H65" s="39" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="I65" s="39" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J65" s="39" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="K65" s="40" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="L65" s="39">
         <v>1</v>
@@ -6470,49 +6441,49 @@
         <v>100</v>
       </c>
       <c r="O65" s="65" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P65" s="42">
-        <v>1.1999999999999999E-3</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="Q65" s="42">
         <f t="shared" ref="Q65" si="54">N65*P65</f>
-        <v>0.12</v>
+        <v>0.21</v>
       </c>
       <c r="R65" s="42"/>
     </row>
-    <row r="66" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
       <c r="B66" s="53">
         <f>ROW(B66) - ROW($B$9)</f>
         <v>57</v>
       </c>
       <c r="C66" s="61" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="D66" s="37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E66" s="38" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F66" s="37" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G66" s="38" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="H66" s="37" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="I66" s="37" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J66" s="37" t="s">
-        <v>337</v>
+        <v>420</v>
       </c>
       <c r="K66" s="38" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="L66" s="37">
         <v>1</v>
@@ -6522,52 +6493,52 @@
         <v>20</v>
       </c>
       <c r="N66" s="41">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O66" s="64" t="s">
-        <v>412</v>
+        <v>360</v>
       </c>
       <c r="P66" s="41">
-        <v>1.11E-2</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="Q66" s="41">
         <f t="shared" ref="Q66" si="55">P66*N66</f>
-        <v>0.55500000000000005</v>
+        <v>0.16</v>
       </c>
       <c r="R66" s="41"/>
     </row>
-    <row r="67" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1"/>
       <c r="B67" s="53">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="C67" s="60" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="D67" s="39" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E67" s="40" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F67" s="39" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G67" s="40" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="H67" s="39" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="I67" s="39" t="s">
-        <v>337</v>
+        <v>421</v>
       </c>
       <c r="J67" s="39" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="K67" s="40" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="L67" s="39">
         <v>1</v>
@@ -6577,164 +6548,166 @@
         <v>20</v>
       </c>
       <c r="N67" s="42">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O67" s="65" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P67" s="42">
-        <v>2.0999999999999999E-3</v>
+        <v>6.8999999999999999E-3</v>
       </c>
       <c r="Q67" s="42">
         <f t="shared" ref="Q67" si="56">N67*P67</f>
-        <v>0.21</v>
+        <v>0.34499999999999997</v>
       </c>
       <c r="R67" s="42"/>
     </row>
-    <row r="68" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1"/>
       <c r="B68" s="53">
         <f>ROW(B68) - ROW($B$9)</f>
         <v>59</v>
       </c>
       <c r="C68" s="61" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="D68" s="37" t="s">
-        <v>53</v>
+        <v>424</v>
       </c>
       <c r="E68" s="38" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F68" s="37" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G68" s="38" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="H68" s="37" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="I68" s="37" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J68" s="37" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="K68" s="38" t="s">
-        <v>319</v>
-      </c>
-      <c r="L68" s="37">
-        <v>1</v>
+        <v>314</v>
+      </c>
+      <c r="L68" s="81">
+        <v>2</v>
       </c>
       <c r="M68" s="41">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N68" s="41">
         <v>100</v>
       </c>
       <c r="O68" s="64" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P68" s="41">
-        <v>1.6000000000000001E-3</v>
+        <v>1.1000000000000001E-3</v>
       </c>
       <c r="Q68" s="41">
         <f t="shared" ref="Q68" si="57">P68*N68</f>
-        <v>0.16</v>
-      </c>
-      <c r="R68" s="41"/>
-    </row>
-    <row r="69" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.11</v>
+      </c>
+      <c r="R68" s="41" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1"/>
       <c r="B69" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B69) - ROW($B$9)</f>
         <v>60</v>
       </c>
-      <c r="C69" s="60" t="s">
-        <v>348</v>
-      </c>
-      <c r="D69" s="39" t="s">
-        <v>54</v>
-      </c>
-      <c r="E69" s="40" t="s">
-        <v>132</v>
-      </c>
-      <c r="F69" s="39" t="s">
-        <v>181</v>
-      </c>
-      <c r="G69" s="40" t="s">
-        <v>233</v>
-      </c>
-      <c r="H69" s="39" t="s">
-        <v>249</v>
-      </c>
-      <c r="I69" s="39" t="s">
-        <v>431</v>
-      </c>
-      <c r="J69" s="39" t="s">
-        <v>432</v>
-      </c>
-      <c r="K69" s="40" t="s">
-        <v>320</v>
-      </c>
-      <c r="L69" s="39">
-        <v>1</v>
-      </c>
-      <c r="M69" s="42">
+      <c r="C69" s="61" t="s">
+        <v>341</v>
+      </c>
+      <c r="D69" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="E69" s="38" t="s">
+        <v>129</v>
+      </c>
+      <c r="F69" s="37" t="s">
+        <v>176</v>
+      </c>
+      <c r="G69" s="38" t="s">
+        <v>228</v>
+      </c>
+      <c r="H69" s="37" t="s">
+        <v>242</v>
+      </c>
+      <c r="I69" s="37" t="s">
+        <v>330</v>
+      </c>
+      <c r="J69" s="37" t="s">
+        <v>425</v>
+      </c>
+      <c r="K69" s="38" t="s">
+        <v>315</v>
+      </c>
+      <c r="L69" s="37">
+        <v>2</v>
+      </c>
+      <c r="M69" s="41">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N69" s="42">
-        <v>50</v>
-      </c>
-      <c r="O69" s="65" t="s">
-        <v>367</v>
-      </c>
-      <c r="P69" s="42">
-        <v>6.8999999999999999E-3</v>
-      </c>
-      <c r="Q69" s="42">
-        <f t="shared" ref="Q69" si="58">N69*P69</f>
-        <v>0.34499999999999997</v>
-      </c>
-      <c r="R69" s="42"/>
-    </row>
-    <row r="70" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="N69" s="41">
+        <v>100</v>
+      </c>
+      <c r="O69" s="64" t="s">
+        <v>360</v>
+      </c>
+      <c r="P69" s="41">
+        <v>1.5E-3</v>
+      </c>
+      <c r="Q69" s="41">
+        <f t="shared" ref="Q69" si="58">P69*N69</f>
+        <v>0.15</v>
+      </c>
+      <c r="R69" s="41"/>
+    </row>
+    <row r="70" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1"/>
       <c r="B70" s="53">
         <f>ROW(B70) - ROW($B$9)</f>
         <v>61</v>
       </c>
       <c r="C70" s="61" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="D70" s="37" t="s">
-        <v>434</v>
+        <v>53</v>
       </c>
       <c r="E70" s="38" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F70" s="37" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G70" s="38" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="H70" s="37" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="I70" s="37" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J70" s="37" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="K70" s="38" t="s">
-        <v>321</v>
-      </c>
-      <c r="L70" s="86">
+        <v>316</v>
+      </c>
+      <c r="L70" s="37">
         <v>2</v>
       </c>
       <c r="M70" s="41">
@@ -6745,1292 +6718,1180 @@
         <v>100</v>
       </c>
       <c r="O70" s="64" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P70" s="41">
-        <v>1.1000000000000001E-3</v>
+        <v>1.5E-3</v>
       </c>
       <c r="Q70" s="41">
         <f t="shared" ref="Q70" si="59">P70*N70</f>
-        <v>0.11</v>
-      </c>
-      <c r="R70" s="41" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="71" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.15</v>
+      </c>
+      <c r="R70" s="41"/>
+    </row>
+    <row r="71" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1"/>
       <c r="B71" s="53">
-        <f>ROW(B71) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="C71" s="61" t="s">
-        <v>348</v>
-      </c>
-      <c r="D71" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="E71" s="38" t="s">
-        <v>134</v>
-      </c>
-      <c r="F71" s="37" t="s">
-        <v>181</v>
-      </c>
-      <c r="G71" s="38" t="s">
-        <v>235</v>
-      </c>
-      <c r="H71" s="37" t="s">
-        <v>249</v>
-      </c>
-      <c r="I71" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="J71" s="37" t="s">
-        <v>435</v>
-      </c>
-      <c r="K71" s="38" t="s">
-        <v>322</v>
-      </c>
-      <c r="L71" s="37">
-        <v>2</v>
-      </c>
-      <c r="M71" s="41">
+      <c r="C71" s="60" t="s">
+        <v>341</v>
+      </c>
+      <c r="D71" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="E71" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="F71" s="39" t="s">
+        <v>176</v>
+      </c>
+      <c r="G71" s="40" t="s">
+        <v>230</v>
+      </c>
+      <c r="H71" s="39" t="s">
+        <v>264</v>
+      </c>
+      <c r="I71" s="39" t="s">
+        <v>330</v>
+      </c>
+      <c r="J71" s="39" t="s">
+        <v>330</v>
+      </c>
+      <c r="K71" s="40" t="s">
+        <v>317</v>
+      </c>
+      <c r="L71" s="39">
+        <v>1</v>
+      </c>
+      <c r="M71" s="42">
         <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N71" s="41">
-        <v>100</v>
-      </c>
-      <c r="O71" s="64" t="s">
-        <v>367</v>
-      </c>
-      <c r="P71" s="41">
-        <v>1.5E-3</v>
-      </c>
-      <c r="Q71" s="41">
-        <f t="shared" ref="Q71" si="60">P71*N71</f>
-        <v>0.15</v>
-      </c>
-      <c r="R71" s="41"/>
-    </row>
-    <row r="72" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="N71" s="42">
+        <v>25</v>
+      </c>
+      <c r="O71" s="65" t="s">
+        <v>428</v>
+      </c>
+      <c r="P71" s="42">
+        <v>8.5400000000000004E-2</v>
+      </c>
+      <c r="Q71" s="42">
+        <f t="shared" ref="Q71" si="60">N71*P71</f>
+        <v>2.1350000000000002</v>
+      </c>
+      <c r="R71" s="42"/>
+    </row>
+    <row r="72" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1"/>
       <c r="B72" s="53">
         <f>ROW(B72) - ROW($B$9)</f>
         <v>63</v>
       </c>
       <c r="C72" s="61" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="D72" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="E72" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="F72" s="37" t="s">
-        <v>181</v>
+        <v>55</v>
+      </c>
+      <c r="E72" s="83" t="s">
+        <v>479</v>
+      </c>
+      <c r="F72" s="103" t="s">
+        <v>480</v>
       </c>
       <c r="G72" s="38" t="s">
-        <v>236</v>
-      </c>
-      <c r="H72" s="37" t="s">
-        <v>249</v>
+        <v>481</v>
+      </c>
+      <c r="H72" s="84" t="s">
+        <v>265</v>
       </c>
       <c r="I72" s="37" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J72" s="37" t="s">
-        <v>437</v>
+        <v>482</v>
       </c>
       <c r="K72" s="38" t="s">
-        <v>323</v>
+        <v>483</v>
       </c>
       <c r="L72" s="37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M72" s="41">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N72" s="41">
-        <v>100</v>
+        <f t="shared" ref="M72:M90" si="61">L72*20</f>
+        <v>20</v>
+      </c>
+      <c r="N72" s="93">
+        <v>50</v>
       </c>
       <c r="O72" s="64" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P72" s="41">
-        <v>1.5E-3</v>
+        <v>3.8E-3</v>
       </c>
       <c r="Q72" s="41">
-        <f t="shared" ref="Q72" si="61">P72*N72</f>
-        <v>0.15</v>
-      </c>
-      <c r="R72" s="41"/>
-    </row>
-    <row r="73" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" ref="Q72" si="62">P72*N72</f>
+        <v>0.19</v>
+      </c>
+      <c r="R72" s="82" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1"/>
       <c r="B73" s="53">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="C73" s="60" t="s">
-        <v>348</v>
-      </c>
-      <c r="D73" s="39" t="s">
-        <v>57</v>
-      </c>
-      <c r="E73" s="40" t="s">
-        <v>136</v>
-      </c>
-      <c r="F73" s="39" t="s">
-        <v>181</v>
-      </c>
-      <c r="G73" s="40" t="s">
-        <v>237</v>
-      </c>
-      <c r="H73" s="39" t="s">
-        <v>271</v>
-      </c>
-      <c r="I73" s="39" t="s">
-        <v>337</v>
-      </c>
-      <c r="J73" s="39" t="s">
-        <v>337</v>
-      </c>
-      <c r="K73" s="40" t="s">
-        <v>324</v>
-      </c>
-      <c r="L73" s="39">
+      <c r="C73" s="98" t="s">
+        <v>341</v>
+      </c>
+      <c r="D73" s="99" t="s">
+        <v>56</v>
+      </c>
+      <c r="E73" s="96" t="s">
+        <v>132</v>
+      </c>
+      <c r="F73" s="99" t="s">
+        <v>176</v>
+      </c>
+      <c r="G73" s="96" t="s">
+        <v>231</v>
+      </c>
+      <c r="H73" s="99" t="s">
+        <v>264</v>
+      </c>
+      <c r="I73" s="99" t="s">
+        <v>330</v>
+      </c>
+      <c r="J73" s="99" t="s">
+        <v>330</v>
+      </c>
+      <c r="K73" s="96" t="s">
+        <v>318</v>
+      </c>
+      <c r="L73" s="99">
         <v>1</v>
       </c>
-      <c r="M73" s="42">
-        <f t="shared" si="1"/>
+      <c r="M73" s="100">
+        <f t="shared" si="61"/>
         <v>20</v>
       </c>
-      <c r="N73" s="42">
-        <v>25</v>
-      </c>
-      <c r="O73" s="65" t="s">
-        <v>438</v>
-      </c>
-      <c r="P73" s="42">
-        <v>8.5400000000000004E-2</v>
-      </c>
-      <c r="Q73" s="42">
-        <f t="shared" ref="Q73" si="62">N73*P73</f>
-        <v>2.1350000000000002</v>
-      </c>
-      <c r="R73" s="42"/>
-    </row>
-    <row r="74" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N73" s="100">
+        <v>0</v>
+      </c>
+      <c r="O73" s="101" t="s">
+        <v>402</v>
+      </c>
+      <c r="P73" s="100">
+        <v>1.8589999999999999E-2</v>
+      </c>
+      <c r="Q73" s="100">
+        <f t="shared" ref="Q73" si="63">N73*P73</f>
+        <v>0</v>
+      </c>
+      <c r="R73" s="87" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1"/>
       <c r="B74" s="53">
         <f>ROW(B74) - ROW($B$9)</f>
         <v>65</v>
       </c>
       <c r="C74" s="61" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="D74" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="E74" s="88" t="s">
-        <v>493</v>
-      </c>
-      <c r="F74" s="108" t="s">
-        <v>494</v>
+        <v>57</v>
+      </c>
+      <c r="E74" s="38" t="s">
+        <v>133</v>
+      </c>
+      <c r="F74" s="37" t="s">
+        <v>176</v>
       </c>
       <c r="G74" s="38" t="s">
-        <v>495</v>
-      </c>
-      <c r="H74" s="89" t="s">
-        <v>272</v>
+        <v>347</v>
+      </c>
+      <c r="H74" s="37" t="s">
+        <v>265</v>
       </c>
       <c r="I74" s="37" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J74" s="37" t="s">
-        <v>496</v>
+        <v>429</v>
       </c>
       <c r="K74" s="38" t="s">
-        <v>497</v>
+        <v>319</v>
       </c>
       <c r="L74" s="37">
         <v>1</v>
       </c>
       <c r="M74" s="41">
-        <f t="shared" ref="M74:M92" si="63">L74*20</f>
+        <f t="shared" si="61"/>
         <v>20</v>
       </c>
-      <c r="N74" s="98">
-        <v>50</v>
+      <c r="N74" s="41">
+        <v>100</v>
       </c>
       <c r="O74" s="64" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P74" s="41">
-        <v>3.8E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="Q74" s="41">
         <f t="shared" ref="Q74" si="64">P74*N74</f>
-        <v>0.19</v>
-      </c>
-      <c r="R74" s="87" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="75" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.1</v>
+      </c>
+      <c r="R74" s="41"/>
+    </row>
+    <row r="75" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1"/>
       <c r="B75" s="53">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="C75" s="103" t="s">
+      <c r="C75" s="60" t="s">
+        <v>341</v>
+      </c>
+      <c r="D75" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="E75" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="F75" s="39" t="s">
+        <v>176</v>
+      </c>
+      <c r="G75" s="40" t="s">
         <v>348</v>
       </c>
-      <c r="D75" s="104" t="s">
-        <v>59</v>
-      </c>
-      <c r="E75" s="101" t="s">
-        <v>137</v>
-      </c>
-      <c r="F75" s="104" t="s">
-        <v>181</v>
-      </c>
-      <c r="G75" s="101" t="s">
-        <v>238</v>
-      </c>
-      <c r="H75" s="104" t="s">
-        <v>271</v>
-      </c>
-      <c r="I75" s="104" t="s">
-        <v>337</v>
-      </c>
-      <c r="J75" s="104" t="s">
-        <v>337</v>
-      </c>
-      <c r="K75" s="101" t="s">
-        <v>325</v>
-      </c>
-      <c r="L75" s="104">
+      <c r="H75" s="39" t="s">
+        <v>266</v>
+      </c>
+      <c r="I75" s="39" t="s">
+        <v>330</v>
+      </c>
+      <c r="J75" s="39" t="s">
+        <v>430</v>
+      </c>
+      <c r="K75" s="40" t="s">
+        <v>320</v>
+      </c>
+      <c r="L75" s="39">
         <v>1</v>
       </c>
-      <c r="M75" s="105">
-        <f t="shared" si="63"/>
+      <c r="M75" s="42">
+        <f t="shared" si="61"/>
         <v>20</v>
       </c>
-      <c r="N75" s="105">
-        <v>0</v>
-      </c>
-      <c r="O75" s="106" t="s">
-        <v>412</v>
-      </c>
-      <c r="P75" s="105">
-        <v>1.8589999999999999E-2</v>
-      </c>
-      <c r="Q75" s="105">
+      <c r="N75" s="42">
+        <v>50</v>
+      </c>
+      <c r="O75" s="65" t="s">
+        <v>360</v>
+      </c>
+      <c r="P75" s="42">
+        <v>4.3E-3</v>
+      </c>
+      <c r="Q75" s="42">
         <f t="shared" ref="Q75" si="65">N75*P75</f>
-        <v>0</v>
-      </c>
-      <c r="R75" s="92" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="76" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.215</v>
+      </c>
+      <c r="R75" s="42"/>
+    </row>
+    <row r="76" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1"/>
       <c r="B76" s="53">
         <f>ROW(B76) - ROW($B$9)</f>
         <v>67</v>
       </c>
       <c r="C76" s="61" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="D76" s="37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E76" s="38" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F76" s="37" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G76" s="38" t="s">
-        <v>354</v>
+        <v>232</v>
       </c>
       <c r="H76" s="37" t="s">
-        <v>272</v>
+        <v>242</v>
       </c>
       <c r="I76" s="37" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J76" s="37" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="K76" s="38" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="L76" s="37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M76" s="41">
-        <f t="shared" si="63"/>
-        <v>20</v>
+        <f t="shared" si="61"/>
+        <v>80</v>
       </c>
       <c r="N76" s="41">
         <v>100</v>
       </c>
       <c r="O76" s="64" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P76" s="41">
-        <v>1E-3</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q76" s="41">
         <f t="shared" ref="Q76" si="66">P76*N76</f>
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="R76" s="41"/>
     </row>
-    <row r="77" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1"/>
       <c r="B77" s="53">
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
       <c r="C77" s="60" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="D77" s="39" t="s">
-        <v>61</v>
+        <v>477</v>
       </c>
       <c r="E77" s="40" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F77" s="39" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G77" s="40" t="s">
-        <v>355</v>
+        <v>233</v>
       </c>
       <c r="H77" s="39" t="s">
-        <v>273</v>
+        <v>242</v>
       </c>
       <c r="I77" s="39" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J77" s="39" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="K77" s="40" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="L77" s="39">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M77" s="42">
-        <f t="shared" si="63"/>
-        <v>20</v>
+        <f t="shared" si="61"/>
+        <v>120</v>
       </c>
       <c r="N77" s="42">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="O77" s="65" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P77" s="42">
-        <v>4.3E-3</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q77" s="42">
         <f t="shared" ref="Q77" si="67">N77*P77</f>
-        <v>0.215</v>
-      </c>
-      <c r="R77" s="42"/>
-    </row>
-    <row r="78" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.24</v>
+      </c>
+      <c r="R77" s="87" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1"/>
       <c r="B78" s="53">
         <f>ROW(B78) - ROW($B$9)</f>
         <v>69</v>
       </c>
-      <c r="C78" s="61" t="s">
-        <v>348</v>
-      </c>
-      <c r="D78" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="E78" s="38" t="s">
-        <v>140</v>
-      </c>
-      <c r="F78" s="37" t="s">
-        <v>183</v>
-      </c>
-      <c r="G78" s="38" t="s">
-        <v>239</v>
-      </c>
-      <c r="H78" s="37" t="s">
-        <v>249</v>
-      </c>
-      <c r="I78" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="J78" s="37" t="s">
-        <v>441</v>
-      </c>
-      <c r="K78" s="38" t="s">
-        <v>328</v>
-      </c>
-      <c r="L78" s="37">
-        <v>4</v>
-      </c>
-      <c r="M78" s="41">
-        <f t="shared" si="63"/>
-        <v>80</v>
-      </c>
-      <c r="N78" s="41">
-        <v>100</v>
-      </c>
-      <c r="O78" s="64" t="s">
-        <v>367</v>
-      </c>
-      <c r="P78" s="41">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q78" s="41">
-        <f t="shared" ref="Q78" si="68">P78*N78</f>
-        <v>0.12</v>
-      </c>
-      <c r="R78" s="41"/>
-    </row>
-    <row r="79" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C78" s="67" t="s">
+        <v>179</v>
+      </c>
+      <c r="D78" s="68" t="s">
+        <v>60</v>
+      </c>
+      <c r="E78" s="69" t="s">
+        <v>137</v>
+      </c>
+      <c r="F78" s="68" t="s">
+        <v>179</v>
+      </c>
+      <c r="G78" s="69" t="s">
+        <v>330</v>
+      </c>
+      <c r="H78" s="68" t="s">
+        <v>330</v>
+      </c>
+      <c r="I78" s="68" t="s">
+        <v>330</v>
+      </c>
+      <c r="J78" s="68" t="s">
+        <v>330</v>
+      </c>
+      <c r="K78" s="69" t="s">
+        <v>330</v>
+      </c>
+      <c r="L78" s="68">
+        <v>11</v>
+      </c>
+      <c r="M78" s="70">
+        <f t="shared" si="61"/>
+        <v>220</v>
+      </c>
+      <c r="N78" s="70">
+        <f t="shared" ref="N78:N79" si="68">M78+(M78*0.1)</f>
+        <v>242</v>
+      </c>
+      <c r="O78" s="70"/>
+      <c r="P78" s="70"/>
+      <c r="Q78" s="70">
+        <f t="shared" ref="Q78" si="69">P78*N78</f>
+        <v>0</v>
+      </c>
+      <c r="R78" s="71" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1"/>
       <c r="B79" s="53">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
       <c r="C79" s="60" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="D79" s="39" t="s">
-        <v>491</v>
+        <v>61</v>
       </c>
       <c r="E79" s="40" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F79" s="39" t="s">
-        <v>181</v>
-      </c>
-      <c r="G79" s="40" t="s">
-        <v>240</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="G79" s="40"/>
       <c r="H79" s="39" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="I79" s="39" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J79" s="39" t="s">
-        <v>442</v>
+        <v>330</v>
       </c>
       <c r="K79" s="40" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L79" s="39">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M79" s="42">
-        <f t="shared" si="63"/>
-        <v>120</v>
+        <f t="shared" si="61"/>
+        <v>20</v>
       </c>
       <c r="N79" s="42">
-        <v>200</v>
-      </c>
-      <c r="O79" s="65" t="s">
-        <v>367</v>
-      </c>
-      <c r="P79" s="42">
-        <v>1.1999999999999999E-3</v>
-      </c>
+        <f t="shared" si="68"/>
+        <v>22</v>
+      </c>
+      <c r="O79" s="42"/>
+      <c r="P79" s="42"/>
       <c r="Q79" s="42">
-        <f t="shared" ref="Q79" si="69">N79*P79</f>
-        <v>0.24</v>
-      </c>
-      <c r="R79" s="92" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="80" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" ref="Q79" si="70">N79*P79</f>
+        <v>0</v>
+      </c>
+      <c r="R79" s="42"/>
+    </row>
+    <row r="80" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1"/>
       <c r="B80" s="53">
         <f>ROW(B80) - ROW($B$9)</f>
         <v>71</v>
       </c>
-      <c r="C80" s="67" t="s">
-        <v>184</v>
-      </c>
-      <c r="D80" s="68" t="s">
-        <v>63</v>
-      </c>
-      <c r="E80" s="69" t="s">
-        <v>142</v>
-      </c>
-      <c r="F80" s="68" t="s">
-        <v>184</v>
-      </c>
-      <c r="G80" s="69" t="s">
-        <v>337</v>
-      </c>
-      <c r="H80" s="68" t="s">
-        <v>337</v>
-      </c>
-      <c r="I80" s="68" t="s">
-        <v>337</v>
-      </c>
-      <c r="J80" s="68" t="s">
-        <v>337</v>
-      </c>
-      <c r="K80" s="69" t="s">
-        <v>337</v>
-      </c>
-      <c r="L80" s="68">
-        <v>11</v>
-      </c>
-      <c r="M80" s="70">
-        <f t="shared" si="63"/>
-        <v>220</v>
-      </c>
-      <c r="N80" s="70">
-        <f t="shared" ref="N80:N81" si="70">M80+(M80*0.1)</f>
-        <v>242</v>
-      </c>
-      <c r="O80" s="70"/>
-      <c r="P80" s="70"/>
-      <c r="Q80" s="70">
+      <c r="C80" s="61" t="s">
+        <v>344</v>
+      </c>
+      <c r="D80" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="E80" s="38" t="s">
+        <v>139</v>
+      </c>
+      <c r="F80" s="37" t="s">
+        <v>324</v>
+      </c>
+      <c r="G80" s="38">
+        <v>750314597</v>
+      </c>
+      <c r="H80" s="37" t="s">
+        <v>268</v>
+      </c>
+      <c r="I80" s="37" t="s">
+        <v>330</v>
+      </c>
+      <c r="J80" s="37" t="s">
+        <v>330</v>
+      </c>
+      <c r="K80" s="38" t="s">
+        <v>330</v>
+      </c>
+      <c r="L80" s="37">
+        <v>1</v>
+      </c>
+      <c r="M80" s="41">
+        <f t="shared" si="61"/>
+        <v>20</v>
+      </c>
+      <c r="N80" s="41">
+        <v>21</v>
+      </c>
+      <c r="O80" s="64" t="s">
+        <v>399</v>
+      </c>
+      <c r="P80" s="41">
+        <v>3.81</v>
+      </c>
+      <c r="Q80" s="41">
         <f t="shared" ref="Q80" si="71">P80*N80</f>
-        <v>0</v>
-      </c>
-      <c r="R80" s="71" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="81" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>80.010000000000005</v>
+      </c>
+      <c r="R80" s="41"/>
+    </row>
+    <row r="81" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1"/>
       <c r="B81" s="53">
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
       <c r="C81" s="60" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="D81" s="39" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E81" s="40" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F81" s="39" t="s">
-        <v>185</v>
-      </c>
-      <c r="G81" s="40"/>
+        <v>324</v>
+      </c>
+      <c r="G81" s="40" t="s">
+        <v>181</v>
+      </c>
       <c r="H81" s="39" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="I81" s="39" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J81" s="39" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K81" s="40" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="L81" s="39">
         <v>1</v>
       </c>
       <c r="M81" s="42">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>20</v>
       </c>
       <c r="N81" s="42">
-        <f t="shared" si="70"/>
-        <v>22</v>
-      </c>
-      <c r="O81" s="42"/>
-      <c r="P81" s="42"/>
+        <v>21</v>
+      </c>
+      <c r="O81" s="65" t="s">
+        <v>433</v>
+      </c>
+      <c r="P81" s="42">
+        <v>2.48</v>
+      </c>
       <c r="Q81" s="42">
         <f t="shared" ref="Q81" si="72">N81*P81</f>
-        <v>0</v>
+        <v>52.08</v>
       </c>
       <c r="R81" s="42"/>
     </row>
-    <row r="82" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1"/>
       <c r="B82" s="53">
         <f>ROW(B82) - ROW($B$9)</f>
         <v>73</v>
       </c>
       <c r="C82" s="61" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="D82" s="37" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E82" s="38" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F82" s="37" t="s">
-        <v>331</v>
-      </c>
-      <c r="G82" s="38">
-        <v>750314597</v>
+        <v>182</v>
+      </c>
+      <c r="G82" s="38" t="s">
+        <v>234</v>
       </c>
       <c r="H82" s="37" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="I82" s="37" t="s">
-        <v>337</v>
+        <v>434</v>
       </c>
       <c r="J82" s="37" t="s">
-        <v>337</v>
+        <v>435</v>
       </c>
       <c r="K82" s="38" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="L82" s="37">
         <v>1</v>
       </c>
       <c r="M82" s="41">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>20</v>
       </c>
       <c r="N82" s="41">
         <v>21</v>
       </c>
       <c r="O82" s="64" t="s">
-        <v>409</v>
+        <v>360</v>
       </c>
       <c r="P82" s="41">
-        <v>3.81</v>
+        <v>1.3939999999999999</v>
       </c>
       <c r="Q82" s="41">
         <f t="shared" ref="Q82" si="73">P82*N82</f>
-        <v>80.010000000000005</v>
-      </c>
-      <c r="R82" s="41"/>
-    </row>
-    <row r="83" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>29.273999999999997</v>
+      </c>
+      <c r="R82" s="94" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1"/>
       <c r="B83" s="53">
         <f t="shared" si="0"/>
         <v>74</v>
       </c>
       <c r="C83" s="60" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="D83" s="39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E83" s="40" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F83" s="39" t="s">
-        <v>331</v>
+        <v>183</v>
       </c>
       <c r="G83" s="40" t="s">
-        <v>186</v>
+        <v>235</v>
       </c>
       <c r="H83" s="39" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="I83" s="39" t="s">
-        <v>337</v>
+        <v>437</v>
       </c>
       <c r="J83" s="39" t="s">
-        <v>337</v>
+        <v>438</v>
       </c>
       <c r="K83" s="40" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="L83" s="39">
         <v>1</v>
       </c>
       <c r="M83" s="42">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>20</v>
       </c>
       <c r="N83" s="42">
         <v>21</v>
       </c>
       <c r="O83" s="65" t="s">
-        <v>443</v>
+        <v>360</v>
       </c>
       <c r="P83" s="42">
-        <v>2.48</v>
+        <v>0.69430000000000003</v>
       </c>
       <c r="Q83" s="42">
         <f t="shared" ref="Q83" si="74">N83*P83</f>
-        <v>52.08</v>
-      </c>
-      <c r="R83" s="42"/>
-    </row>
-    <row r="84" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>14.580300000000001</v>
+      </c>
+      <c r="R83" s="102" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="1"/>
       <c r="B84" s="53">
         <f>ROW(B84) - ROW($B$9)</f>
         <v>75</v>
       </c>
       <c r="C84" s="61" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="D84" s="37" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E84" s="38" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F84" s="37" t="s">
-        <v>187</v>
+        <v>326</v>
       </c>
       <c r="G84" s="38" t="s">
-        <v>241</v>
+        <v>184</v>
       </c>
       <c r="H84" s="37" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="I84" s="37" t="s">
-        <v>444</v>
+        <v>330</v>
       </c>
       <c r="J84" s="37" t="s">
-        <v>445</v>
+        <v>330</v>
       </c>
       <c r="K84" s="38" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="L84" s="37">
         <v>1</v>
       </c>
       <c r="M84" s="41">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>20</v>
       </c>
       <c r="N84" s="41">
         <v>21</v>
       </c>
       <c r="O84" s="64" t="s">
-        <v>367</v>
+        <v>433</v>
       </c>
       <c r="P84" s="41">
-        <v>1.3939999999999999</v>
+        <v>3.637</v>
       </c>
       <c r="Q84" s="41">
         <f t="shared" ref="Q84" si="75">P84*N84</f>
-        <v>29.273999999999997</v>
-      </c>
-      <c r="R84" s="99" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="85" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>76.376999999999995</v>
+      </c>
+      <c r="R84" s="41"/>
+    </row>
+    <row r="85" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="1"/>
       <c r="B85" s="53">
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
       <c r="C85" s="60" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="D85" s="39" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E85" s="40" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F85" s="39" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G85" s="40" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="H85" s="39" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="I85" s="39" t="s">
-        <v>447</v>
+        <v>330</v>
       </c>
       <c r="J85" s="39" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="K85" s="40" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="L85" s="39">
         <v>1</v>
       </c>
       <c r="M85" s="42">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>20</v>
       </c>
       <c r="N85" s="42">
         <v>21</v>
       </c>
       <c r="O85" s="65" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P85" s="42">
-        <v>0.69430000000000003</v>
+        <v>0.43280000000000002</v>
       </c>
       <c r="Q85" s="42">
         <f t="shared" ref="Q85" si="76">N85*P85</f>
-        <v>14.580300000000001</v>
-      </c>
-      <c r="R85" s="107" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="86" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>9.0888000000000009</v>
+      </c>
+      <c r="R85" s="42"/>
+    </row>
+    <row r="86" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="1"/>
       <c r="B86" s="53">
         <f>ROW(B86) - ROW($B$9)</f>
         <v>77</v>
       </c>
-      <c r="C86" s="61" t="s">
-        <v>352</v>
-      </c>
-      <c r="D86" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="E86" s="38" t="s">
-        <v>148</v>
-      </c>
-      <c r="F86" s="37" t="s">
-        <v>333</v>
-      </c>
-      <c r="G86" s="38" t="s">
-        <v>189</v>
-      </c>
-      <c r="H86" s="37" t="s">
-        <v>276</v>
-      </c>
-      <c r="I86" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="J86" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="K86" s="38" t="s">
-        <v>337</v>
-      </c>
-      <c r="L86" s="37">
+      <c r="C86" s="76" t="s">
+        <v>345</v>
+      </c>
+      <c r="D86" s="77" t="s">
+        <v>68</v>
+      </c>
+      <c r="E86" s="78" t="s">
+        <v>145</v>
+      </c>
+      <c r="F86" s="77" t="s">
+        <v>186</v>
+      </c>
+      <c r="G86" s="78" t="s">
+        <v>237</v>
+      </c>
+      <c r="H86" s="77" t="s">
+        <v>271</v>
+      </c>
+      <c r="I86" s="77" t="s">
+        <v>330</v>
+      </c>
+      <c r="J86" s="77" t="s">
+        <v>440</v>
+      </c>
+      <c r="K86" s="78" t="s">
+        <v>330</v>
+      </c>
+      <c r="L86" s="77">
         <v>1</v>
       </c>
-      <c r="M86" s="41">
-        <f t="shared" si="63"/>
+      <c r="M86" s="79">
+        <f t="shared" si="61"/>
         <v>20</v>
       </c>
-      <c r="N86" s="41">
+      <c r="N86" s="79">
         <v>21</v>
       </c>
-      <c r="O86" s="64" t="s">
-        <v>443</v>
-      </c>
-      <c r="P86" s="41">
-        <v>3.637</v>
-      </c>
-      <c r="Q86" s="41">
+      <c r="O86" s="80" t="s">
+        <v>360</v>
+      </c>
+      <c r="P86" s="79">
+        <v>7.4638</v>
+      </c>
+      <c r="Q86" s="79">
         <f t="shared" ref="Q86" si="77">P86*N86</f>
-        <v>76.376999999999995</v>
-      </c>
-      <c r="R86" s="41"/>
-    </row>
-    <row r="87" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>156.7398</v>
+      </c>
+      <c r="R86" s="79" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="1"/>
       <c r="B87" s="53">
         <f t="shared" si="0"/>
         <v>78</v>
       </c>
       <c r="C87" s="60" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="D87" s="39" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E87" s="40" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F87" s="39" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G87" s="40" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="H87" s="39" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="I87" s="39" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J87" s="39" t="s">
-        <v>449</v>
-      </c>
-      <c r="K87" s="40" t="s">
-        <v>337</v>
+        <v>330</v>
+      </c>
+      <c r="K87" s="58" t="s">
+        <v>331</v>
       </c>
       <c r="L87" s="39">
         <v>1</v>
       </c>
       <c r="M87" s="42">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>20</v>
       </c>
       <c r="N87" s="42">
         <v>21</v>
       </c>
       <c r="O87" s="65" t="s">
-        <v>367</v>
+        <v>433</v>
       </c>
       <c r="P87" s="42">
-        <v>0.43280000000000002</v>
+        <v>2.6459999999999999</v>
       </c>
       <c r="Q87" s="42">
         <f t="shared" ref="Q87" si="78">N87*P87</f>
-        <v>9.0888000000000009</v>
+        <v>55.565999999999995</v>
       </c>
       <c r="R87" s="42"/>
     </row>
-    <row r="88" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="1"/>
       <c r="B88" s="53">
         <f>ROW(B88) - ROW($B$9)</f>
         <v>79</v>
       </c>
-      <c r="C88" s="81" t="s">
-        <v>352</v>
-      </c>
-      <c r="D88" s="82" t="s">
-        <v>71</v>
-      </c>
-      <c r="E88" s="83" t="s">
-        <v>150</v>
-      </c>
-      <c r="F88" s="82" t="s">
-        <v>191</v>
-      </c>
-      <c r="G88" s="83" t="s">
-        <v>244</v>
-      </c>
-      <c r="H88" s="82" t="s">
-        <v>278</v>
-      </c>
-      <c r="I88" s="82" t="s">
-        <v>337</v>
-      </c>
-      <c r="J88" s="82" t="s">
-        <v>450</v>
-      </c>
-      <c r="K88" s="83" t="s">
-        <v>337</v>
-      </c>
-      <c r="L88" s="82">
-        <v>1</v>
-      </c>
-      <c r="M88" s="84">
-        <f t="shared" si="63"/>
-        <v>20</v>
-      </c>
-      <c r="N88" s="84">
-        <v>21</v>
-      </c>
-      <c r="O88" s="85" t="s">
-        <v>367</v>
-      </c>
-      <c r="P88" s="84">
-        <v>7.4638</v>
-      </c>
-      <c r="Q88" s="84">
+      <c r="C88" s="61" t="s">
+        <v>345</v>
+      </c>
+      <c r="D88" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="E88" s="38" t="s">
+        <v>147</v>
+      </c>
+      <c r="F88" s="37" t="s">
+        <v>327</v>
+      </c>
+      <c r="G88" s="38" t="s">
+        <v>188</v>
+      </c>
+      <c r="H88" s="37" t="s">
+        <v>269</v>
+      </c>
+      <c r="I88" s="37" t="s">
+        <v>441</v>
+      </c>
+      <c r="J88" s="37" t="s">
+        <v>442</v>
+      </c>
+      <c r="K88" s="38" t="s">
+        <v>330</v>
+      </c>
+      <c r="L88" s="81">
+        <v>2</v>
+      </c>
+      <c r="M88" s="41">
+        <f t="shared" si="61"/>
+        <v>40</v>
+      </c>
+      <c r="N88" s="41">
+        <v>42</v>
+      </c>
+      <c r="O88" s="64" t="s">
+        <v>360</v>
+      </c>
+      <c r="P88" s="41">
+        <v>2.2974000000000001</v>
+      </c>
+      <c r="Q88" s="41">
         <f t="shared" ref="Q88" si="79">P88*N88</f>
-        <v>156.7398</v>
-      </c>
-      <c r="R88" s="84" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="89" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>96.490800000000007</v>
+      </c>
+      <c r="R88" s="94" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="1"/>
       <c r="B89" s="53">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
       <c r="C89" s="60" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="D89" s="39" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E89" s="40" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F89" s="39" t="s">
-        <v>192</v>
+        <v>328</v>
       </c>
       <c r="G89" s="40" t="s">
-        <v>245</v>
+        <v>189</v>
       </c>
       <c r="H89" s="39" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="I89" s="39" t="s">
-        <v>337</v>
+        <v>444</v>
       </c>
       <c r="J89" s="39" t="s">
-        <v>337</v>
-      </c>
-      <c r="K89" s="58" t="s">
-        <v>338</v>
+        <v>330</v>
+      </c>
+      <c r="K89" s="40" t="s">
+        <v>330</v>
       </c>
       <c r="L89" s="39">
         <v>1</v>
       </c>
       <c r="M89" s="42">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>20</v>
       </c>
       <c r="N89" s="42">
         <v>21</v>
       </c>
       <c r="O89" s="65" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="P89" s="42">
-        <v>2.6459999999999999</v>
+        <v>3.532</v>
       </c>
       <c r="Q89" s="42">
         <f t="shared" ref="Q89" si="80">N89*P89</f>
-        <v>55.565999999999995</v>
-      </c>
-      <c r="R89" s="42"/>
-    </row>
-    <row r="90" spans="1:18" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>74.171999999999997</v>
+      </c>
+      <c r="R89" s="102" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="1"/>
       <c r="B90" s="53">
         <f>ROW(B90) - ROW($B$9)</f>
         <v>81</v>
       </c>
       <c r="C90" s="61" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="D90" s="37" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E90" s="38" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F90" s="37" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G90" s="38" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H90" s="37" t="s">
-        <v>276</v>
-      </c>
-      <c r="I90" s="37" t="s">
-        <v>451</v>
-      </c>
-      <c r="J90" s="37" t="s">
-        <v>452</v>
+        <v>269</v>
+      </c>
+      <c r="I90" s="63" t="s">
+        <v>330</v>
+      </c>
+      <c r="J90" s="63" t="s">
+        <v>446</v>
       </c>
       <c r="K90" s="38" t="s">
-        <v>337</v>
-      </c>
-      <c r="L90" s="86">
-        <v>2</v>
+        <v>330</v>
+      </c>
+      <c r="L90" s="37">
+        <v>1</v>
       </c>
       <c r="M90" s="41">
-        <f t="shared" si="63"/>
-        <v>40</v>
+        <f t="shared" si="61"/>
+        <v>20</v>
       </c>
       <c r="N90" s="41">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="O90" s="64" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P90" s="41">
-        <v>2.2974000000000001</v>
+        <v>0.39140000000000003</v>
       </c>
       <c r="Q90" s="41">
         <f t="shared" ref="Q90" si="81">P90*N90</f>
-        <v>96.490800000000007</v>
-      </c>
-      <c r="R90" s="99" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="91" spans="1:18" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>8.2194000000000003</v>
+      </c>
+      <c r="R90" s="41"/>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
-      <c r="B91" s="53">
-        <f t="shared" si="0"/>
-        <v>82</v>
-      </c>
-      <c r="C91" s="60" t="s">
-        <v>352</v>
-      </c>
-      <c r="D91" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="E91" s="40" t="s">
-        <v>153</v>
-      </c>
-      <c r="F91" s="39" t="s">
-        <v>335</v>
-      </c>
-      <c r="G91" s="40" t="s">
-        <v>194</v>
-      </c>
-      <c r="H91" s="39" t="s">
-        <v>279</v>
-      </c>
-      <c r="I91" s="39" t="s">
-        <v>454</v>
-      </c>
-      <c r="J91" s="39" t="s">
-        <v>337</v>
-      </c>
-      <c r="K91" s="40" t="s">
-        <v>337</v>
-      </c>
-      <c r="L91" s="39">
-        <v>1</v>
-      </c>
-      <c r="M91" s="42">
-        <f t="shared" si="63"/>
-        <v>20</v>
-      </c>
-      <c r="N91" s="42">
-        <v>21</v>
-      </c>
-      <c r="O91" s="65" t="s">
-        <v>455</v>
-      </c>
-      <c r="P91" s="42">
-        <v>3.532</v>
-      </c>
-      <c r="Q91" s="42">
-        <f t="shared" ref="Q91" si="82">N91*P91</f>
-        <v>74.171999999999997</v>
-      </c>
-      <c r="R91" s="107" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="92" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B91" s="32"/>
+      <c r="C91" s="51"/>
+      <c r="D91" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="34"/>
+      <c r="F91" s="35"/>
+      <c r="G91" s="36"/>
+      <c r="H91" s="35"/>
+      <c r="I91" s="35"/>
+      <c r="J91" s="35"/>
+      <c r="K91" s="36"/>
+      <c r="L91" s="36"/>
+      <c r="M91" s="36"/>
+      <c r="N91" s="36"/>
+      <c r="O91" s="74" t="s">
+        <v>447</v>
+      </c>
+      <c r="P91" s="72"/>
+      <c r="Q91" s="72">
+        <f>SUM(Q10:Q90)</f>
+        <v>963.24430000000007</v>
+      </c>
+      <c r="R91" s="44"/>
+    </row>
+    <row r="92" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="1"/>
-      <c r="B92" s="53">
-        <f>ROW(B92) - ROW($B$9)</f>
-        <v>83</v>
-      </c>
-      <c r="C92" s="61" t="s">
-        <v>352</v>
-      </c>
-      <c r="D92" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="E92" s="38" t="s">
-        <v>154</v>
-      </c>
-      <c r="F92" s="37" t="s">
-        <v>336</v>
-      </c>
-      <c r="G92" s="38" t="s">
-        <v>195</v>
-      </c>
-      <c r="H92" s="37" t="s">
-        <v>276</v>
-      </c>
-      <c r="I92" s="63" t="s">
-        <v>337</v>
-      </c>
-      <c r="J92" s="63" t="s">
-        <v>456</v>
-      </c>
-      <c r="K92" s="38" t="s">
-        <v>337</v>
-      </c>
-      <c r="L92" s="37">
-        <v>1</v>
-      </c>
-      <c r="M92" s="41">
-        <f t="shared" si="63"/>
-        <v>20</v>
-      </c>
-      <c r="N92" s="41">
-        <v>21</v>
-      </c>
-      <c r="O92" s="64" t="s">
-        <v>367</v>
-      </c>
-      <c r="P92" s="41">
-        <v>0.39140000000000003</v>
-      </c>
-      <c r="Q92" s="41">
-        <f t="shared" ref="Q92" si="83">P92*N92</f>
-        <v>8.2194000000000003</v>
-      </c>
-      <c r="R92" s="41"/>
-    </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A93" s="1"/>
-      <c r="B93" s="32"/>
-      <c r="C93" s="51"/>
-      <c r="D93" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="E93" s="34"/>
-      <c r="F93" s="35"/>
-      <c r="G93" s="36"/>
-      <c r="H93" s="35"/>
-      <c r="I93" s="35"/>
-      <c r="J93" s="35"/>
-      <c r="K93" s="36"/>
-      <c r="L93" s="36"/>
-      <c r="M93" s="36"/>
-      <c r="N93" s="36"/>
-      <c r="O93" s="74" t="s">
-        <v>457</v>
-      </c>
-      <c r="P93" s="72"/>
-      <c r="Q93" s="72">
-        <f>SUM(Q10:Q92)</f>
-        <v>963.91150000000016</v>
-      </c>
-      <c r="R93" s="44"/>
-    </row>
-    <row r="94" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="1"/>
-      <c r="B94" s="24"/>
-      <c r="C94" s="52"/>
-      <c r="D94" s="8" t="s">
+      <c r="B92" s="24"/>
+      <c r="C92" s="52"/>
+      <c r="D92" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E94" s="9"/>
-      <c r="F94" s="9"/>
-      <c r="G94" s="9"/>
-      <c r="H94" s="9"/>
-      <c r="I94" s="9"/>
-      <c r="J94" s="9"/>
-      <c r="K94" s="9"/>
-      <c r="L94" s="9"/>
-      <c r="M94" s="9"/>
-      <c r="N94" s="9"/>
-      <c r="O94" s="75" t="s">
-        <v>458</v>
-      </c>
-      <c r="P94" s="73"/>
-      <c r="Q94" s="73">
-        <f>Q93/20</f>
-        <v>48.195575000000005</v>
-      </c>
-      <c r="R94" s="45"/>
+      <c r="E92" s="9"/>
+      <c r="F92" s="9"/>
+      <c r="G92" s="9"/>
+      <c r="H92" s="9"/>
+      <c r="I92" s="9"/>
+      <c r="J92" s="9"/>
+      <c r="K92" s="9"/>
+      <c r="L92" s="9"/>
+      <c r="M92" s="9"/>
+      <c r="N92" s="9"/>
+      <c r="O92" s="75" t="s">
+        <v>448</v>
+      </c>
+      <c r="P92" s="73"/>
+      <c r="Q92" s="73">
+        <f>Q91/20</f>
+        <v>48.162215000000003</v>
+      </c>
+      <c r="R92" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8077,8 +7938,8 @@
     <hyperlink ref="O46" r:id="rId37"/>
     <hyperlink ref="O47" r:id="rId38"/>
     <hyperlink ref="O48" r:id="rId39"/>
-    <hyperlink ref="O49" r:id="rId40"/>
-    <hyperlink ref="O50" r:id="rId41"/>
+    <hyperlink ref="O50" r:id="rId40"/>
+    <hyperlink ref="O51" r:id="rId41"/>
     <hyperlink ref="O52" r:id="rId42"/>
     <hyperlink ref="O53" r:id="rId43"/>
     <hyperlink ref="O54" r:id="rId44"/>
@@ -8086,8 +7947,8 @@
     <hyperlink ref="O56" r:id="rId46"/>
     <hyperlink ref="O57" r:id="rId47"/>
     <hyperlink ref="O58" r:id="rId48"/>
-    <hyperlink ref="O59" r:id="rId49"/>
-    <hyperlink ref="O60" r:id="rId50"/>
+    <hyperlink ref="O60" r:id="rId49"/>
+    <hyperlink ref="O61" r:id="rId50"/>
     <hyperlink ref="O62" r:id="rId51"/>
     <hyperlink ref="O63" r:id="rId52"/>
     <hyperlink ref="O64" r:id="rId53"/>
@@ -8104,8 +7965,8 @@
     <hyperlink ref="O75" r:id="rId64"/>
     <hyperlink ref="O76" r:id="rId65"/>
     <hyperlink ref="O77" r:id="rId66"/>
-    <hyperlink ref="O78" r:id="rId67"/>
-    <hyperlink ref="O79" r:id="rId68"/>
+    <hyperlink ref="O80" r:id="rId67"/>
+    <hyperlink ref="O81" r:id="rId68"/>
     <hyperlink ref="O82" r:id="rId69"/>
     <hyperlink ref="O83" r:id="rId70"/>
     <hyperlink ref="O84" r:id="rId71"/>
@@ -8115,12 +7976,10 @@
     <hyperlink ref="O88" r:id="rId75"/>
     <hyperlink ref="O89" r:id="rId76"/>
     <hyperlink ref="O90" r:id="rId77"/>
-    <hyperlink ref="O91" r:id="rId78"/>
-    <hyperlink ref="O92" r:id="rId79"/>
-    <hyperlink ref="O61" r:id="rId80"/>
+    <hyperlink ref="O59" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId81"/>
-  <drawing r:id="rId82"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId79"/>
+  <drawing r:id="rId80"/>
 </worksheet>
 </file>
--- a/Deliverables/SM_Top Board/_BOM/eSpark BOM (20 Boards).xlsx
+++ b/Deliverables/SM_Top Board/_BOM/eSpark BOM (20 Boards).xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="468">
   <si>
     <t>Component list</t>
   </si>
@@ -79,15 +79,9 @@
     <t>C37</t>
   </si>
   <si>
-    <t>C41</t>
-  </si>
-  <si>
     <t>C42</t>
   </si>
   <si>
-    <t>C44</t>
-  </si>
-  <si>
     <t>C48</t>
   </si>
   <si>
@@ -199,9 +193,6 @@
     <t>R37</t>
   </si>
   <si>
-    <t>R38</t>
-  </si>
-  <si>
     <t>R40</t>
   </si>
   <si>
@@ -211,9 +202,6 @@
     <t>R42, R43, R44, R45</t>
   </si>
   <si>
-    <t>SB1, SB2, SB3, SB4, SB5, SB6, SB7, SB8, SB9, SB10, SB11</t>
-  </si>
-  <si>
     <t>SW1</t>
   </si>
   <si>
@@ -241,12 +229,6 @@
     <t>U7</t>
   </si>
   <si>
-    <t>U8</t>
-  </si>
-  <si>
-    <t>U9</t>
-  </si>
-  <si>
     <t>U10</t>
   </si>
   <si>
@@ -298,15 +280,9 @@
     <t>CAP CER 2200PF 50V X7R 0603</t>
   </si>
   <si>
-    <t>CAP CER 4.7UF 100V X7S 1210</t>
-  </si>
-  <si>
     <t>CAP CER 1206 47 uF 25 V ±20 % Tol. X5R</t>
   </si>
   <si>
-    <t>CAP CER 0.02uF 50V X7R 10% SMD 0603 125°C Paper T/R</t>
-  </si>
-  <si>
     <t>CAP TANT 100UF 20% 25V 2917</t>
   </si>
   <si>
@@ -427,9 +403,6 @@
     <t>Res SMD 0603 51.1K Ohm 0.1% 1/10W</t>
   </si>
   <si>
-    <t>Res SMD 0603 90.9K Ohm 1% 1/10W</t>
-  </si>
-  <si>
     <t>±1% 1/10W Thick Film Resistors 75V ±100ppm/℃ -55℃~+155℃ 1.2kΩ 0603 Chip Resistor - Surface Mount ROHS</t>
   </si>
   <si>
@@ -499,9 +472,6 @@
     <t>VKME1451J221MV</t>
   </si>
   <si>
-    <t>Cap1210</t>
-  </si>
-  <si>
     <t>Cap1206</t>
   </si>
   <si>
@@ -643,15 +613,9 @@
     <t>CC0603KRX7R9BB222</t>
   </si>
   <si>
-    <t>HMK325C7475KN-TE</t>
-  </si>
-  <si>
     <t>GRM31CR61E476ME44L</t>
   </si>
   <si>
-    <t>CC0603KRX7R9BB203</t>
-  </si>
-  <si>
     <t>TAJE107M025RNJ</t>
   </si>
   <si>
@@ -724,9 +688,6 @@
     <t>ERA-3AEB5112V</t>
   </si>
   <si>
-    <t>ERJ-3EKF9092V</t>
-  </si>
-  <si>
     <t>RC0603FR-071KL</t>
   </si>
   <si>
@@ -895,15 +856,9 @@
     <t>2.2nF</t>
   </si>
   <si>
-    <t>4.7uF</t>
-  </si>
-  <si>
     <t>47uF</t>
   </si>
   <si>
-    <t>20nF</t>
-  </si>
-  <si>
     <t>100uF</t>
   </si>
   <si>
@@ -985,9 +940,6 @@
     <t>51.1K</t>
   </si>
   <si>
-    <t>90.9K</t>
-  </si>
-  <si>
     <t>1.2K</t>
   </si>
   <si>
@@ -1168,15 +1120,9 @@
     <t>C107082</t>
   </si>
   <si>
-    <t>C697607</t>
-  </si>
-  <si>
     <t>C403725</t>
   </si>
   <si>
-    <t>C282065</t>
-  </si>
-  <si>
     <t>C7230</t>
   </si>
   <si>
@@ -1198,9 +1144,6 @@
     <t>C842786</t>
   </si>
   <si>
-    <t>Design change required</t>
-  </si>
-  <si>
     <t>PMEG3010EP,115</t>
   </si>
   <si>
@@ -1243,9 +1186,6 @@
     <t>NACSemi</t>
   </si>
   <si>
-    <t>Available for Lower cost in China</t>
-  </si>
-  <si>
     <t>DO NOT MOUNT</t>
   </si>
   <si>
@@ -1253,21 +1193,6 @@
   </si>
   <si>
     <t>C2847038</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Quantity changed from 8/board to 4/board because alternate part is MOSFET 2N Array. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Design change required</t>
-    </r>
   </si>
   <si>
     <t>C14677</t>
@@ -1333,9 +1258,6 @@
     <t>C114628</t>
   </si>
   <si>
-    <t>Two different part numbers for 100K merged into single part number. Changes highlighted</t>
-  </si>
-  <si>
     <t>C105576</t>
   </si>
   <si>
@@ -1363,9 +1285,6 @@
     <t>C485517</t>
   </si>
   <si>
-    <t>Design change required. May cause change in some other misc components</t>
-  </si>
-  <si>
     <t>BD9876AEFJ-E2</t>
   </si>
   <si>
@@ -1384,9 +1303,6 @@
     <t>C28037</t>
   </si>
   <si>
-    <t>Design change required. May cause change in some other misc components. Quantity also changed from 1/board to 2/board</t>
-  </si>
-  <si>
     <t>ISO6761FDWR</t>
   </si>
   <si>
@@ -1408,9 +1324,6 @@
     <t>R34</t>
   </si>
   <si>
-    <t>Quantity changed from 9/board to 1/board. The remaining 8 resistors have been converted to 22ohms after calculation</t>
-  </si>
-  <si>
     <t>0603WAF220JT5E</t>
   </si>
   <si>
@@ -1420,13 +1333,7 @@
     <t>22R</t>
   </si>
   <si>
-    <t>Resistor value changed from 150R to 22R after calculation. No footprint, only schematic change needed</t>
-  </si>
-  <si>
     <t>C33</t>
-  </si>
-  <si>
-    <t>Quantity changed from 3/board to 1/board due to change in two capacitors value to 1uF after component change</t>
   </si>
   <si>
     <r>
@@ -1445,65 +1352,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">D4, D5, D6, D7, D8, D9, D10, D11, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>DF1</t>
-    </r>
-  </si>
-  <si>
-    <t>Design change required. Another diode added for reverse current protection across U2. Needs to be added in design as well</t>
-  </si>
-  <si>
-    <t>Design change required. Change reflected in misc. components</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">C5, C6, C14, C23, C24, C29, C34, C35, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <strike/>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C56</t>
-    </r>
-  </si>
-  <si>
     <t>C4</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">C3. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C46</t>
-    </r>
-  </si>
-  <si>
-    <t>Removed after changes in circuitry of U3</t>
   </si>
   <si>
     <t>CAP CER 6.8nF 50V X7R 0603</t>
@@ -1560,51 +1409,6 @@
     <t>C1631</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>68pF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 6.8nF</t>
-    </r>
-  </si>
-  <si>
-    <t>Value changed from 68pF to 6.8nF due to change in circuitry of U3</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">C43, </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C45, C47</t>
-    </r>
-  </si>
-  <si>
-    <t>Quantity changed from 3/board to 1/board due to removal of two capacitors after changes in circuitry of U3</t>
-  </si>
-  <si>
     <t>GRM188R6YA106MA73D</t>
   </si>
   <si>
@@ -1636,8 +1440,20 @@
     <t>C194427</t>
   </si>
   <si>
+    <t>RES SMD 110K OHM 0.5% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>C423090</t>
+  </si>
+  <si>
+    <t>DMBJ</t>
+  </si>
+  <si>
+    <t>C2849490</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">RF1, RF2, RF3, RF4, </t>
+      <t xml:space="preserve">D3, </t>
     </r>
     <r>
       <rPr>
@@ -1648,16 +1464,18 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>RF5,</t>
+      <t>DF2</t>
     </r>
+  </si>
+  <si>
+    <t>Design change required. May cause change in some other misc components.</t>
+  </si>
+  <si>
+    <t>Will be provided by Robotshop for prototyping</t>
+  </si>
+  <si>
     <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve">C8, C10, C11, C12, </t>
     </r>
     <r>
       <rPr>
@@ -1668,84 +1486,61 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>R38</t>
+      <t>C41, CF3</t>
     </r>
   </si>
   <si>
-    <t>Quantity changed from 4/board to 6/board due to addition of 2 x 10K resistor from U3</t>
-  </si>
-  <si>
-    <t>RES SMD 110K OHM 0.5% 1/10W 0603</t>
+    <t>Q2, Q3, Q4, Q5</t>
+  </si>
+  <si>
+    <t>RES SMD 22HM 1/10W 0603</t>
+  </si>
+  <si>
+    <t>C2, C13, C15, C20, C40, C51, C52, C53, C54, C55, C61, CF1, CF2</t>
+  </si>
+  <si>
+    <t>Quantity changed from 9 to 13. C15, C20 and C40 merged into this due to same value. C55 changed from 1uF to 0.1uF</t>
   </si>
   <si>
     <r>
-      <t>Res-0201</t>
+      <t xml:space="preserve">C3, </t>
     </r>
     <r>
       <rPr>
         <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, Res0603</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <strike/>
         <sz val="9"/>
         <color rgb="FFC00000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>RC0201FR-071ML</t>
+      <t>C46</t>
     </r>
+  </si>
+  <si>
+    <t>C5, C6, C14, C23, C24, C29, C34, C35</t>
+  </si>
+  <si>
+    <t>C43</t>
+  </si>
+  <si>
+    <t>6.8nF</t>
+  </si>
+  <si>
+    <t>D4, D5, D6, D7, D8, D9, D10, D11</t>
+  </si>
+  <si>
+    <t>Quantity changed from 9 to 8. DF2 removed from design as found un-necessary</t>
+  </si>
+  <si>
+    <t>33uH</t>
+  </si>
+  <si>
+    <t>PNLS5020-330</t>
+  </si>
+  <si>
     <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 0603WAD1103T5E</t>
-    </r>
-  </si>
-  <si>
-    <t>C423090</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">1M </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>110K</t>
-    </r>
-  </si>
-  <si>
-    <t>Value changed from 1Mohm to 110Kohm due to change in circuitry of U3</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1A </t>
+      <t>1A</t>
     </r>
     <r>
       <rPr>
@@ -1756,7 +1551,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">15uH </t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -1779,17 +1574,6 @@
     </r>
     <r>
       <rPr>
-        <strike/>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">190mΩ </t>
-    </r>
-    <r>
-      <rPr>
         <sz val="9"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -1799,113 +1583,25 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>MPIT4018-150M-LF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> PNLS5020-330</t>
-    </r>
-  </si>
-  <si>
-    <t>DMBJ</t>
-  </si>
-  <si>
-    <t>C2849490</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">15uH </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>33uH</t>
-    </r>
-  </si>
-  <si>
-    <t>Value changed from 15uH to 33uH due to change in circuitry of U3</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">D3, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>DF2</t>
-    </r>
-  </si>
-  <si>
-    <t>Design change required. Another diode added as per U3 circuit requirements</t>
-  </si>
-  <si>
-    <t>Design change required. May cause change in some other misc components.</t>
-  </si>
-  <si>
-    <t>Will be provided by Robotshop for prototyping</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">C8, C10, C11, C12, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C41, CF3</t>
-    </r>
-  </si>
-  <si>
-    <t>Quantity changed from 4/board to 6/board due to addition of 2 x 10uF capacitor from U3</t>
-  </si>
-  <si>
-    <t>Q2, Q3, Q4, Q5</t>
-  </si>
-  <si>
-    <t>RES SMD 22HM 1/10W 0603</t>
-  </si>
-  <si>
-    <t>C2, C13, C15, C20, C40, C51, C52, C53, C54, C55, C61, CF1, CF2</t>
-  </si>
-  <si>
-    <t>Quantity changed from 9 to 13. C15, C20 and C40 merged into this due to same value. C55 changed from 1uF to 0.1uF</t>
+    <t>110K</t>
+  </si>
+  <si>
+    <t>0603WAD1103T5E</t>
+  </si>
+  <si>
+    <t>R38, RF1, RF2, RF3, RF4, RF5</t>
+  </si>
+  <si>
+    <t>DO NOT MOUNT BUT ORDER</t>
+  </si>
+  <si>
+    <t>SB1, SB2, SB3, SB4, SB5, SB6, SB7, SB8, SB9, SB10, SB11, SBx1, SBx2, SBx3, SBx4</t>
+  </si>
+  <si>
+    <t>U8, U9</t>
+  </si>
+  <si>
+    <t>U11</t>
   </si>
 </sst>
 </file>
@@ -1915,7 +1611,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2087,15 +1783,6 @@
     <font>
       <b/>
       <strike/>
-      <sz val="9"/>
-      <color rgb="FFC00000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <strike/>
       <sz val="10"/>
       <color rgb="FFC00000"/>
       <name val="Calibri"/>
@@ -2112,14 +1799,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -2429,7 +2108,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -2647,9 +2326,6 @@
     <xf numFmtId="0" fontId="19" fillId="7" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2659,33 +2335,9 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2698,30 +2350,36 @@
     <xf numFmtId="0" fontId="20" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2731,28 +2389,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3097,7 +2770,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R92"/>
+  <dimension ref="A1:R89"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="3.109375" style="25" customWidth="1"/>
@@ -3128,14 +2801,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
+      <c r="K1" s="99"/>
+      <c r="L1" s="99"/>
+      <c r="M1" s="99"/>
+      <c r="N1" s="99"/>
+      <c r="O1" s="99"/>
+      <c r="P1" s="99"/>
+      <c r="Q1" s="99"/>
+      <c r="R1" s="99"/>
     </row>
     <row r="2" spans="1:18" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
@@ -3146,7 +2819,7 @@
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="54" t="s">
-        <v>351</v>
+        <v>335</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
@@ -3170,7 +2843,7 @@
       </c>
       <c r="E3" s="12"/>
       <c r="F3" s="55" t="s">
-        <v>349</v>
+        <v>333</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="4"/>
@@ -3183,7 +2856,7 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="107"/>
+      <c r="R3" s="100"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
@@ -3194,7 +2867,7 @@
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="56" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="6"/>
@@ -3207,7 +2880,7 @@
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="Q4" s="62"/>
-      <c r="R4" s="108"/>
+      <c r="R4" s="101"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
@@ -3229,7 +2902,7 @@
       <c r="O5" s="62"/>
       <c r="P5" s="62"/>
       <c r="Q5" s="62"/>
-      <c r="R5" s="108"/>
+      <c r="R5" s="101"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
@@ -3249,7 +2922,7 @@
       <c r="O6" s="62"/>
       <c r="P6" s="62"/>
       <c r="Q6" s="62"/>
-      <c r="R6" s="108"/>
+      <c r="R6" s="101"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
@@ -3269,7 +2942,7 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="108"/>
+      <c r="R7" s="101"/>
     </row>
     <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
@@ -3289,7 +2962,7 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="108"/>
+      <c r="R8" s="101"/>
     </row>
     <row r="9" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
@@ -3297,52 +2970,52 @@
         <v>4</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>342</v>
+        <v>326</v>
       </c>
       <c r="D9" s="29" t="s">
         <v>7</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="I9" s="29" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="J9" s="29" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="L9" s="29" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="M9" s="31" t="s">
-        <v>354</v>
+        <v>338</v>
       </c>
       <c r="N9" s="31" t="s">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="O9" s="31" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="P9" s="31" t="s">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="Q9" s="31" t="s">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="R9" s="31" t="s">
-        <v>332</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3352,31 +3025,31 @@
         <v>1</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="D10" s="37" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="38" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="G10" s="38" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="K10" s="38" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="L10" s="37">
         <v>1</v>
@@ -3389,7 +3062,7 @@
         <v>22</v>
       </c>
       <c r="O10" s="64" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P10" s="41">
         <v>0.25869999999999999</v>
@@ -3403,58 +3076,58 @@
     <row r="11" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
       <c r="B11" s="53">
-        <f t="shared" ref="B11:B89" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B86" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="109" t="s">
-        <v>333</v>
-      </c>
-      <c r="D11" s="110" t="s">
-        <v>499</v>
-      </c>
-      <c r="E11" s="111" t="s">
-        <v>75</v>
-      </c>
-      <c r="F11" s="110" t="s">
-        <v>152</v>
-      </c>
-      <c r="G11" s="111" t="s">
-        <v>192</v>
-      </c>
-      <c r="H11" s="110" t="s">
-        <v>241</v>
-      </c>
-      <c r="I11" s="110" t="s">
-        <v>330</v>
-      </c>
-      <c r="J11" s="110" t="s">
-        <v>361</v>
-      </c>
-      <c r="K11" s="111" t="s">
-        <v>275</v>
-      </c>
-      <c r="L11" s="110">
+      <c r="C11" s="91" t="s">
+        <v>317</v>
+      </c>
+      <c r="D11" s="92" t="s">
+        <v>450</v>
+      </c>
+      <c r="E11" s="93" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" s="92" t="s">
+        <v>143</v>
+      </c>
+      <c r="G11" s="93" t="s">
+        <v>182</v>
+      </c>
+      <c r="H11" s="92" t="s">
+        <v>228</v>
+      </c>
+      <c r="I11" s="92" t="s">
+        <v>314</v>
+      </c>
+      <c r="J11" s="92" t="s">
+        <v>345</v>
+      </c>
+      <c r="K11" s="93" t="s">
+        <v>262</v>
+      </c>
+      <c r="L11" s="92">
         <v>13</v>
       </c>
-      <c r="M11" s="112">
+      <c r="M11" s="94">
         <f>L11*20</f>
         <v>260</v>
       </c>
-      <c r="N11" s="112">
+      <c r="N11" s="94">
         <v>300</v>
       </c>
-      <c r="O11" s="113" t="s">
-        <v>360</v>
-      </c>
-      <c r="P11" s="112">
+      <c r="O11" s="95" t="s">
+        <v>344</v>
+      </c>
+      <c r="P11" s="94">
         <v>1.4E-3</v>
       </c>
-      <c r="Q11" s="112">
+      <c r="Q11" s="94">
         <f>N11*P11</f>
         <v>0.42</v>
       </c>
-      <c r="R11" s="112" t="s">
-        <v>500</v>
+      <c r="R11" s="94" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3464,44 +3137,44 @@
         <v>3</v>
       </c>
       <c r="C12" s="61" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="K12" s="38" t="s">
-        <v>276</v>
-      </c>
-      <c r="L12" s="114">
+        <v>263</v>
+      </c>
+      <c r="L12" s="96">
         <v>2</v>
       </c>
       <c r="M12" s="41">
-        <f t="shared" ref="M12:M71" si="1">L12*20</f>
+        <f t="shared" ref="M12:M69" si="1">L12*20</f>
         <v>40</v>
       </c>
       <c r="N12" s="41">
         <v>100</v>
       </c>
       <c r="O12" s="64" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P12" s="41">
         <v>1.2999999999999999E-3</v>
@@ -3510,7 +3183,7 @@
         <f t="shared" ref="Q12" si="2">P12*N12</f>
         <v>0.13</v>
       </c>
-      <c r="R12" s="82"/>
+      <c r="R12" s="81"/>
     </row>
     <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
@@ -3519,44 +3192,44 @@
         <v>4</v>
       </c>
       <c r="C13" s="60" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>463</v>
+        <v>432</v>
       </c>
       <c r="E13" s="40" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="G13" s="40" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="I13" s="39" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J13" s="39" t="s">
-        <v>363</v>
+        <v>347</v>
       </c>
       <c r="K13" s="40" t="s">
-        <v>277</v>
-      </c>
-      <c r="L13" s="115">
+        <v>264</v>
+      </c>
+      <c r="L13" s="97">
         <v>1</v>
       </c>
       <c r="M13" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N13" s="116">
+      <c r="N13" s="98">
         <v>40</v>
       </c>
       <c r="O13" s="65" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P13" s="42">
         <v>3.5900000000000001E-2</v>
@@ -3565,7 +3238,7 @@
         <f t="shared" ref="Q13" si="3">N13*P13</f>
         <v>1.4359999999999999</v>
       </c>
-      <c r="R13" s="87"/>
+      <c r="R13" s="84"/>
     </row>
     <row r="14" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1"/>
@@ -3574,31 +3247,31 @@
         <v>5</v>
       </c>
       <c r="C14" s="61" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J14" s="37" t="s">
-        <v>364</v>
+        <v>348</v>
       </c>
       <c r="K14" s="38" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="L14" s="37">
         <v>8</v>
@@ -3611,7 +3284,7 @@
         <v>200</v>
       </c>
       <c r="O14" s="64" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P14" s="41">
         <v>4.0899999999999999E-2</v>
@@ -3620,7 +3293,7 @@
         <f>P14*N14</f>
         <v>8.18</v>
       </c>
-      <c r="R14" s="82"/>
+      <c r="R14" s="81"/>
     </row>
     <row r="15" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
@@ -3629,44 +3302,44 @@
         <v>6</v>
       </c>
       <c r="C15" s="60" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>458</v>
+        <v>431</v>
       </c>
       <c r="E15" s="40" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="G15" s="40" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="H15" s="39" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="I15" s="39" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J15" s="39" t="s">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="K15" s="40" t="s">
-        <v>279</v>
-      </c>
-      <c r="L15" s="115">
+        <v>266</v>
+      </c>
+      <c r="L15" s="97">
         <v>3</v>
       </c>
       <c r="M15" s="42">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="N15" s="116">
+      <c r="N15" s="98">
         <v>100</v>
       </c>
       <c r="O15" s="65" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P15" s="42">
         <v>5.8999999999999999E-3</v>
@@ -3675,40 +3348,40 @@
         <f t="shared" ref="Q15" si="4">N15*P15</f>
         <v>0.59</v>
       </c>
-      <c r="R15" s="87"/>
-    </row>
-    <row r="16" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R15" s="84"/>
+    </row>
+    <row r="16" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
       <c r="B16" s="53">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
       <c r="C16" s="61" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>495</v>
+        <v>447</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>475</v>
+        <v>438</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="G16" s="83" t="s">
-        <v>474</v>
-      </c>
-      <c r="H16" s="84" t="s">
-        <v>244</v>
+        <v>143</v>
+      </c>
+      <c r="G16" s="82" t="s">
+        <v>437</v>
+      </c>
+      <c r="H16" s="83" t="s">
+        <v>231</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>476</v>
+        <v>439</v>
       </c>
       <c r="K16" s="38" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="L16" s="37">
         <v>6</v>
@@ -3721,7 +3394,7 @@
         <v>130</v>
       </c>
       <c r="O16" s="64" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P16" s="41">
         <v>3.32E-2</v>
@@ -3730,9 +3403,7 @@
         <f t="shared" ref="Q16" si="5">P16*N16</f>
         <v>4.3159999999999998</v>
       </c>
-      <c r="R16" s="82" t="s">
-        <v>496</v>
-      </c>
+      <c r="R16" s="81"/>
     </row>
     <row r="17" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
@@ -3741,31 +3412,31 @@
         <v>8</v>
       </c>
       <c r="C17" s="60" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="D17" s="39" t="s">
         <v>9</v>
       </c>
       <c r="E17" s="40" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="G17" s="40" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="H17" s="39" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="I17" s="39" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J17" s="39" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="K17" s="40" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="L17" s="39">
         <v>1</v>
@@ -3778,7 +3449,7 @@
         <v>50</v>
       </c>
       <c r="O17" s="65" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P17" s="42">
         <v>9.9000000000000008E-3</v>
@@ -3796,31 +3467,31 @@
         <v>9</v>
       </c>
       <c r="C18" s="60" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="E18" s="40" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F18" s="39" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="G18" s="40" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="H18" s="39" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="I18" s="39" t="s">
-        <v>368</v>
+        <v>352</v>
       </c>
       <c r="J18" s="39" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="K18" s="40" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="L18" s="39">
         <v>8</v>
@@ -3833,7 +3504,7 @@
         <v>180</v>
       </c>
       <c r="O18" s="65" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P18" s="42">
         <v>3.09E-2</v>
@@ -3851,31 +3522,31 @@
         <v>10</v>
       </c>
       <c r="C19" s="61" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="D19" s="37" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="38" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F19" s="37" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="G19" s="38" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H19" s="37" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="I19" s="37" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="J19" s="37" t="s">
-        <v>370</v>
+        <v>354</v>
       </c>
       <c r="K19" s="38" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="L19" s="37">
         <v>1</v>
@@ -3888,7 +3559,7 @@
         <v>50</v>
       </c>
       <c r="O19" s="64" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P19" s="41">
         <v>5.3E-3</v>
@@ -3906,31 +3577,31 @@
         <v>11</v>
       </c>
       <c r="C20" s="60" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="D20" s="39" t="s">
         <v>11</v>
       </c>
       <c r="E20" s="40" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F20" s="39" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="H20" s="39" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="I20" s="39" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J20" s="39" t="s">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="K20" s="40" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="L20" s="39">
         <v>1</v>
@@ -3943,7 +3614,7 @@
         <v>22</v>
       </c>
       <c r="O20" s="65" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P20" s="42">
         <v>0.22189999999999999</v>
@@ -3961,31 +3632,31 @@
         <v>12</v>
       </c>
       <c r="C21" s="61" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="D21" s="37" t="s">
         <v>12</v>
       </c>
       <c r="E21" s="38" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F21" s="37" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="G21" s="38" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="H21" s="37" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="I21" s="37" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J21" s="37" t="s">
-        <v>372</v>
+        <v>356</v>
       </c>
       <c r="K21" s="38" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="L21" s="37">
         <v>2</v>
@@ -3998,7 +3669,7 @@
         <v>50</v>
       </c>
       <c r="O21" s="64" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P21" s="41">
         <v>7.7000000000000002E-3</v>
@@ -4016,31 +3687,31 @@
         <v>13</v>
       </c>
       <c r="C22" s="61" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="D22" s="37" t="s">
         <v>13</v>
       </c>
       <c r="E22" s="38" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J22" s="37" t="s">
-        <v>374</v>
+        <v>358</v>
       </c>
       <c r="K22" s="38" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="L22" s="37">
         <v>1</v>
@@ -4053,7 +3724,7 @@
         <v>40</v>
       </c>
       <c r="O22" s="64" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P22" s="41">
         <v>3.49E-2</v>
@@ -4064,51 +3735,51 @@
       </c>
       <c r="R22" s="41"/>
     </row>
-    <row r="23" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
       <c r="B23" s="53">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="C23" s="60" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>456</v>
+        <v>430</v>
       </c>
       <c r="E23" s="40" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F23" s="39" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="G23" s="40" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="H23" s="39" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="I23" s="39" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J23" s="39" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="K23" s="40" t="s">
-        <v>285</v>
-      </c>
-      <c r="L23" s="85">
+        <v>272</v>
+      </c>
+      <c r="L23" s="39">
         <v>1</v>
       </c>
       <c r="M23" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N23" s="86">
+      <c r="N23" s="42">
         <v>40</v>
       </c>
       <c r="O23" s="65" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P23" s="42">
         <v>1.9199999999999998E-2</v>
@@ -4117,9 +3788,7 @@
         <f t="shared" ref="Q23" si="12">N23*P23</f>
         <v>0.7679999999999999</v>
       </c>
-      <c r="R23" s="87" t="s">
-        <v>457</v>
-      </c>
+      <c r="R23" s="84"/>
     </row>
     <row r="24" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
@@ -4128,31 +3797,31 @@
         <v>15</v>
       </c>
       <c r="C24" s="61" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="D24" s="37" t="s">
         <v>14</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="G24" s="66">
         <v>885012205080</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="J24" s="37" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="K24" s="38" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="L24" s="37">
         <v>1</v>
@@ -4165,7 +3834,7 @@
         <v>50</v>
       </c>
       <c r="O24" s="64" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P24" s="41">
         <v>5.1999999999999998E-3</v>
@@ -4183,31 +3852,31 @@
         <v>16</v>
       </c>
       <c r="C25" s="60" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="D25" s="39" t="s">
         <v>15</v>
       </c>
       <c r="E25" s="40" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F25" s="39" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="G25" s="40" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="H25" s="39" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="I25" s="39" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J25" s="39" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="K25" s="40" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="L25" s="39">
         <v>1</v>
@@ -4220,7 +3889,7 @@
         <v>100</v>
       </c>
       <c r="O25" s="65" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P25" s="42">
         <v>3.2000000000000002E-3</v>
@@ -4234,230 +3903,222 @@
     <row r="26" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
       <c r="B26" s="53">
-        <f>ROW(B26) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="88" t="s">
-        <v>333</v>
-      </c>
-      <c r="D26" s="89" t="s">
+      <c r="C26" s="60" t="s">
+        <v>317</v>
+      </c>
+      <c r="D26" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="E26" s="90" t="s">
-        <v>89</v>
-      </c>
-      <c r="F26" s="89" t="s">
-        <v>156</v>
-      </c>
-      <c r="G26" s="90" t="s">
-        <v>204</v>
-      </c>
-      <c r="H26" s="89" t="s">
-        <v>243</v>
-      </c>
-      <c r="I26" s="89" t="s">
-        <v>330</v>
-      </c>
-      <c r="J26" s="89" t="s">
-        <v>379</v>
-      </c>
-      <c r="K26" s="90" t="s">
-        <v>288</v>
-      </c>
-      <c r="L26" s="89">
+      <c r="E26" s="86" t="s">
+        <v>433</v>
+      </c>
+      <c r="F26" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="G26" s="87" t="s">
+        <v>434</v>
+      </c>
+      <c r="H26" s="88" t="s">
+        <v>435</v>
+      </c>
+      <c r="I26" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="J26" s="39" t="s">
+        <v>436</v>
+      </c>
+      <c r="K26" s="102" t="s">
+        <v>455</v>
+      </c>
+      <c r="L26" s="39">
         <v>1</v>
       </c>
-      <c r="M26" s="91">
+      <c r="M26" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N26" s="91">
-        <v>0</v>
-      </c>
-      <c r="O26" s="92" t="s">
-        <v>360</v>
-      </c>
-      <c r="P26" s="91">
-        <v>0.1653</v>
-      </c>
-      <c r="Q26" s="91">
-        <f t="shared" ref="Q26" si="15">P26*N26</f>
-        <v>0</v>
-      </c>
-      <c r="R26" s="91" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N26" s="42">
+        <v>100</v>
+      </c>
+      <c r="O26" s="65" t="s">
+        <v>344</v>
+      </c>
+      <c r="P26" s="42">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="Q26" s="42">
+        <f t="shared" ref="Q26" si="15">N26*P26</f>
+        <v>0.33999999999999997</v>
+      </c>
+      <c r="R26" s="84"/>
+    </row>
+    <row r="27" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
       <c r="B27" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
-      <c r="C27" s="60" t="s">
-        <v>333</v>
-      </c>
-      <c r="D27" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" s="95" t="s">
-        <v>466</v>
-      </c>
-      <c r="F27" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="G27" s="96" t="s">
-        <v>467</v>
-      </c>
-      <c r="H27" s="97" t="s">
-        <v>468</v>
-      </c>
-      <c r="I27" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="J27" s="39" t="s">
-        <v>469</v>
-      </c>
-      <c r="K27" s="40" t="s">
-        <v>470</v>
-      </c>
-      <c r="L27" s="39">
+      <c r="C27" s="61" t="s">
+        <v>317</v>
+      </c>
+      <c r="D27" s="37" t="s">
+        <v>454</v>
+      </c>
+      <c r="E27" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="F27" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="G27" s="38" t="s">
+        <v>194</v>
+      </c>
+      <c r="H27" s="37" t="s">
+        <v>231</v>
+      </c>
+      <c r="I27" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="J27" s="37" t="s">
+        <v>363</v>
+      </c>
+      <c r="K27" s="38" t="s">
+        <v>275</v>
+      </c>
+      <c r="L27" s="37">
         <v>1</v>
       </c>
-      <c r="M27" s="42">
+      <c r="M27" s="41">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N27" s="42">
-        <v>100</v>
-      </c>
-      <c r="O27" s="65" t="s">
-        <v>360</v>
-      </c>
-      <c r="P27" s="42">
-        <v>3.3999999999999998E-3</v>
-      </c>
-      <c r="Q27" s="42">
-        <f t="shared" ref="Q27" si="16">N27*P27</f>
-        <v>0.33999999999999997</v>
-      </c>
-      <c r="R27" s="87" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N27" s="41">
+        <v>30</v>
+      </c>
+      <c r="O27" s="64" t="s">
+        <v>344</v>
+      </c>
+      <c r="P27" s="41">
+        <v>0.2525</v>
+      </c>
+      <c r="Q27" s="41">
+        <f t="shared" ref="Q27" si="16">P27*N27</f>
+        <v>7.5750000000000002</v>
+      </c>
+      <c r="R27" s="85"/>
+    </row>
+    <row r="28" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
       <c r="B28" s="53">
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
       <c r="C28" s="61" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="D28" s="37" t="s">
-        <v>472</v>
+        <v>17</v>
       </c>
       <c r="E28" s="38" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="G28" s="38" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="H28" s="37" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="I28" s="37" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J28" s="37" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="K28" s="38" t="s">
-        <v>289</v>
-      </c>
-      <c r="L28" s="81">
+        <v>276</v>
+      </c>
+      <c r="L28" s="37">
         <v>1</v>
       </c>
       <c r="M28" s="41">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N28" s="93">
-        <v>30</v>
+      <c r="N28" s="41">
+        <v>22</v>
       </c>
       <c r="O28" s="64" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P28" s="41">
-        <v>0.2525</v>
+        <v>0.89629999999999999</v>
       </c>
       <c r="Q28" s="41">
         <f t="shared" ref="Q28" si="17">P28*N28</f>
-        <v>7.5750000000000002</v>
-      </c>
-      <c r="R28" s="94" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+        <v>19.718599999999999</v>
+      </c>
+      <c r="R28" s="41"/>
+    </row>
+    <row r="29" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
       <c r="B29" s="53">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="98" t="s">
-        <v>333</v>
-      </c>
-      <c r="D29" s="99" t="s">
+      <c r="C29" s="60" t="s">
+        <v>317</v>
+      </c>
+      <c r="D29" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="E29" s="96" t="s">
-        <v>91</v>
-      </c>
-      <c r="F29" s="99" t="s">
-        <v>152</v>
-      </c>
-      <c r="G29" s="96" t="s">
-        <v>206</v>
-      </c>
-      <c r="H29" s="99" t="s">
-        <v>242</v>
-      </c>
-      <c r="I29" s="99" t="s">
-        <v>330</v>
-      </c>
-      <c r="J29" s="99" t="s">
-        <v>381</v>
-      </c>
-      <c r="K29" s="96" t="s">
-        <v>290</v>
-      </c>
-      <c r="L29" s="99">
+      <c r="E29" s="40" t="s">
+        <v>85</v>
+      </c>
+      <c r="F29" s="39" t="s">
+        <v>308</v>
+      </c>
+      <c r="G29" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="H29" s="39" t="s">
+        <v>236</v>
+      </c>
+      <c r="I29" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="J29" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="K29" s="40" t="s">
+        <v>277</v>
+      </c>
+      <c r="L29" s="39">
         <v>1</v>
       </c>
-      <c r="M29" s="100">
+      <c r="M29" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N29" s="100">
-        <v>0</v>
-      </c>
-      <c r="O29" s="101" t="s">
-        <v>360</v>
-      </c>
-      <c r="P29" s="100">
-        <v>4.1999999999999997E-3</v>
-      </c>
-      <c r="Q29" s="100">
+      <c r="N29" s="42">
+        <v>21</v>
+      </c>
+      <c r="O29" s="65" t="s">
+        <v>344</v>
+      </c>
+      <c r="P29" s="42">
+        <v>0.47249999999999998</v>
+      </c>
+      <c r="Q29" s="42">
         <f t="shared" ref="Q29" si="18">N29*P29</f>
-        <v>0</v>
-      </c>
-      <c r="R29" s="87" t="s">
-        <v>465</v>
-      </c>
+        <v>9.9224999999999994</v>
+      </c>
+      <c r="R29" s="42"/>
     </row>
     <row r="30" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
@@ -4466,31 +4127,31 @@
         <v>21</v>
       </c>
       <c r="C30" s="61" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="D30" s="37" t="s">
         <v>19</v>
       </c>
       <c r="E30" s="38" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="G30" s="38" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J30" s="37" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="K30" s="38" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="L30" s="37">
         <v>1</v>
@@ -4500,441 +4161,439 @@
         <v>20</v>
       </c>
       <c r="N30" s="41">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="O30" s="64" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P30" s="41">
-        <v>0.89629999999999999</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="Q30" s="41">
         <f t="shared" ref="Q30" si="19">P30*N30</f>
-        <v>19.718599999999999</v>
+        <v>0.31</v>
       </c>
       <c r="R30" s="41"/>
     </row>
-    <row r="31" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1"/>
       <c r="B31" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
-      <c r="C31" s="60" t="s">
-        <v>333</v>
-      </c>
-      <c r="D31" s="39" t="s">
+      <c r="C31" s="61" t="s">
+        <v>317</v>
+      </c>
+      <c r="D31" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="40" t="s">
-        <v>93</v>
-      </c>
-      <c r="F31" s="39" t="s">
-        <v>324</v>
-      </c>
-      <c r="G31" s="39" t="s">
-        <v>159</v>
-      </c>
-      <c r="H31" s="39" t="s">
-        <v>249</v>
-      </c>
-      <c r="I31" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="J31" s="39" t="s">
-        <v>383</v>
-      </c>
-      <c r="K31" s="40" t="s">
-        <v>292</v>
-      </c>
-      <c r="L31" s="39">
-        <v>1</v>
-      </c>
-      <c r="M31" s="42">
+      <c r="E31" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="F31" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="G31" s="38" t="s">
+        <v>197</v>
+      </c>
+      <c r="H31" s="37" t="s">
+        <v>228</v>
+      </c>
+      <c r="I31" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="J31" s="37" t="s">
+        <v>367</v>
+      </c>
+      <c r="K31" s="38" t="s">
+        <v>279</v>
+      </c>
+      <c r="L31" s="37">
+        <v>4</v>
+      </c>
+      <c r="M31" s="41">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N31" s="42">
-        <v>21</v>
-      </c>
-      <c r="O31" s="65" t="s">
-        <v>360</v>
-      </c>
-      <c r="P31" s="42">
-        <v>0.47249999999999998</v>
-      </c>
-      <c r="Q31" s="42">
-        <f t="shared" ref="Q31" si="20">N31*P31</f>
-        <v>9.9224999999999994</v>
-      </c>
-      <c r="R31" s="42"/>
+        <v>80</v>
+      </c>
+      <c r="N31" s="41">
+        <v>100</v>
+      </c>
+      <c r="O31" s="64" t="s">
+        <v>344</v>
+      </c>
+      <c r="P31" s="41">
+        <v>5.4999999999999997E-3</v>
+      </c>
+      <c r="Q31" s="41">
+        <f t="shared" ref="Q31" si="20">P31*N31</f>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="R31" s="41"/>
     </row>
     <row r="32" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1"/>
       <c r="B32" s="53">
-        <f>ROW(B32) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="61" t="s">
-        <v>333</v>
-      </c>
-      <c r="D32" s="37" t="s">
+      <c r="C32" s="60" t="s">
+        <v>318</v>
+      </c>
+      <c r="D32" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="E32" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="F32" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="G32" s="38" t="s">
-        <v>208</v>
-      </c>
-      <c r="H32" s="37" t="s">
-        <v>242</v>
-      </c>
-      <c r="I32" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="J32" s="37" t="s">
-        <v>384</v>
-      </c>
-      <c r="K32" s="38" t="s">
-        <v>293</v>
-      </c>
-      <c r="L32" s="37">
+      <c r="E32" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="F32" s="39" t="s">
+        <v>308</v>
+      </c>
+      <c r="G32" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="H32" s="39" t="s">
+        <v>237</v>
+      </c>
+      <c r="I32" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="J32" s="39" t="s">
+        <v>368</v>
+      </c>
+      <c r="K32" s="40" t="s">
+        <v>314</v>
+      </c>
+      <c r="L32" s="39">
         <v>1</v>
       </c>
-      <c r="M32" s="41">
+      <c r="M32" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N32" s="41">
-        <v>100</v>
-      </c>
-      <c r="O32" s="64" t="s">
-        <v>360</v>
-      </c>
-      <c r="P32" s="41">
-        <v>3.0999999999999999E-3</v>
-      </c>
-      <c r="Q32" s="41">
-        <f t="shared" ref="Q32" si="21">P32*N32</f>
-        <v>0.31</v>
-      </c>
-      <c r="R32" s="41"/>
-    </row>
-    <row r="33" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N32" s="42">
+        <v>30</v>
+      </c>
+      <c r="O32" s="65" t="s">
+        <v>344</v>
+      </c>
+      <c r="P32" s="42">
+        <v>4.87E-2</v>
+      </c>
+      <c r="Q32" s="42">
+        <f t="shared" ref="Q32" si="21">N32*P32</f>
+        <v>1.4610000000000001</v>
+      </c>
+      <c r="R32" s="42"/>
+    </row>
+    <row r="33" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1"/>
       <c r="B33" s="53">
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
       <c r="C33" s="61" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="D33" s="37" t="s">
         <v>22</v>
       </c>
       <c r="E33" s="38" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G33" s="38" t="s">
-        <v>209</v>
+        <v>280</v>
       </c>
       <c r="H33" s="37" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J33" s="37" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
       <c r="K33" s="38" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="L33" s="37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M33" s="41">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="N33" s="41">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="O33" s="64" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P33" s="41">
-        <v>5.4999999999999997E-3</v>
+        <v>7.4300000000000005E-2</v>
       </c>
       <c r="Q33" s="41">
         <f t="shared" ref="Q33" si="22">P33*N33</f>
-        <v>0.54999999999999993</v>
+        <v>2.2290000000000001</v>
       </c>
       <c r="R33" s="41"/>
     </row>
-    <row r="34" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
       <c r="B34" s="53">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="C34" s="60" t="s">
-        <v>334</v>
+        <v>318</v>
       </c>
       <c r="D34" s="39" t="s">
-        <v>23</v>
+        <v>444</v>
       </c>
       <c r="E34" s="40" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="F34" s="39" t="s">
-        <v>324</v>
+        <v>151</v>
       </c>
       <c r="G34" s="40" t="s">
-        <v>160</v>
+        <v>281</v>
       </c>
       <c r="H34" s="39" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="I34" s="39" t="s">
-        <v>330</v>
+        <v>281</v>
       </c>
       <c r="J34" s="39" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
       <c r="K34" s="40" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="L34" s="39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M34" s="42">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N34" s="42">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="O34" s="65" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P34" s="42">
-        <v>4.87E-2</v>
+        <v>2.8899999999999999E-2</v>
       </c>
       <c r="Q34" s="42">
         <f t="shared" ref="Q34" si="23">N34*P34</f>
-        <v>1.4610000000000001</v>
-      </c>
-      <c r="R34" s="42"/>
-    </row>
-    <row r="35" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1.734</v>
+      </c>
+      <c r="R34" s="89"/>
+    </row>
+    <row r="35" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1"/>
       <c r="B35" s="53">
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="61" t="s">
-        <v>334</v>
-      </c>
-      <c r="D35" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35" s="38" t="s">
-        <v>97</v>
-      </c>
-      <c r="F35" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="G35" s="38" t="s">
-        <v>295</v>
-      </c>
-      <c r="H35" s="37" t="s">
-        <v>251</v>
-      </c>
-      <c r="I35" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="J35" s="37" t="s">
-        <v>387</v>
-      </c>
-      <c r="K35" s="38" t="s">
-        <v>330</v>
-      </c>
-      <c r="L35" s="37">
-        <v>1</v>
-      </c>
-      <c r="M35" s="41">
+      <c r="C35" s="103" t="s">
+        <v>318</v>
+      </c>
+      <c r="D35" s="104" t="s">
+        <v>456</v>
+      </c>
+      <c r="E35" s="105" t="s">
+        <v>91</v>
+      </c>
+      <c r="F35" s="104" t="s">
+        <v>152</v>
+      </c>
+      <c r="G35" s="105" t="s">
+        <v>198</v>
+      </c>
+      <c r="H35" s="104" t="s">
+        <v>239</v>
+      </c>
+      <c r="I35" s="104" t="s">
+        <v>371</v>
+      </c>
+      <c r="J35" s="104" t="s">
+        <v>372</v>
+      </c>
+      <c r="K35" s="105" t="s">
+        <v>314</v>
+      </c>
+      <c r="L35" s="106">
+        <v>8</v>
+      </c>
+      <c r="M35" s="107">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N35" s="41">
-        <v>30</v>
-      </c>
-      <c r="O35" s="64" t="s">
-        <v>360</v>
-      </c>
-      <c r="P35" s="41">
-        <v>7.4300000000000005E-2</v>
-      </c>
-      <c r="Q35" s="41">
+        <v>160</v>
+      </c>
+      <c r="N35" s="108">
+        <v>170</v>
+      </c>
+      <c r="O35" s="109" t="s">
+        <v>344</v>
+      </c>
+      <c r="P35" s="107">
+        <v>0.12590000000000001</v>
+      </c>
+      <c r="Q35" s="107">
         <f t="shared" ref="Q35" si="24">P35*N35</f>
-        <v>2.2290000000000001</v>
-      </c>
-      <c r="R35" s="41"/>
-    </row>
-    <row r="36" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+        <v>21.403000000000002</v>
+      </c>
+      <c r="R35" s="94" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1"/>
       <c r="B36" s="53">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="C36" s="60" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="D36" s="39" t="s">
-        <v>491</v>
+        <v>23</v>
       </c>
       <c r="E36" s="40" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F36" s="39" t="s">
-        <v>161</v>
+        <v>308</v>
       </c>
       <c r="G36" s="40" t="s">
-        <v>296</v>
+        <v>153</v>
       </c>
       <c r="H36" s="39" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="I36" s="39" t="s">
-        <v>296</v>
+        <v>373</v>
       </c>
       <c r="J36" s="39" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="K36" s="40" t="s">
-        <v>330</v>
-      </c>
-      <c r="L36" s="85">
-        <v>2</v>
+        <v>314</v>
+      </c>
+      <c r="L36" s="39">
+        <v>1</v>
       </c>
       <c r="M36" s="42">
         <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N36" s="86">
-        <v>60</v>
+        <v>20</v>
+      </c>
+      <c r="N36" s="42">
+        <v>30</v>
       </c>
       <c r="O36" s="65" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P36" s="42">
-        <v>2.8899999999999999E-2</v>
+        <v>5.6000000000000001E-2</v>
       </c>
       <c r="Q36" s="42">
         <f t="shared" ref="Q36" si="25">N36*P36</f>
-        <v>1.734</v>
-      </c>
-      <c r="R36" s="102" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1.68</v>
+      </c>
+      <c r="R36" s="42"/>
+    </row>
+    <row r="37" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1"/>
       <c r="B37" s="53">
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
       <c r="C37" s="61" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="D37" s="37" t="s">
-        <v>459</v>
+        <v>24</v>
       </c>
       <c r="E37" s="38" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="F37" s="37" t="s">
-        <v>162</v>
+        <v>309</v>
       </c>
       <c r="G37" s="38" t="s">
-        <v>210</v>
+        <v>154</v>
       </c>
       <c r="H37" s="37" t="s">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="I37" s="37" t="s">
-        <v>390</v>
+        <v>314</v>
       </c>
       <c r="J37" s="37" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="K37" s="38" t="s">
-        <v>330</v>
-      </c>
-      <c r="L37" s="81">
-        <v>9</v>
+        <v>314</v>
+      </c>
+      <c r="L37" s="37">
+        <v>4</v>
       </c>
       <c r="M37" s="41">
         <f t="shared" si="1"/>
-        <v>180</v>
-      </c>
-      <c r="N37" s="93">
-        <v>190</v>
+        <v>80</v>
+      </c>
+      <c r="N37" s="41">
+        <v>100</v>
       </c>
       <c r="O37" s="64" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P37" s="41">
-        <v>0.12590000000000001</v>
+        <v>2.9499999999999998E-2</v>
       </c>
       <c r="Q37" s="41">
         <f t="shared" ref="Q37" si="26">P37*N37</f>
-        <v>23.921000000000003</v>
-      </c>
-      <c r="R37" s="94" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2.9499999999999997</v>
+      </c>
+      <c r="R37" s="41"/>
+    </row>
+    <row r="38" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1"/>
       <c r="B38" s="53">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="C38" s="60" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="D38" s="39" t="s">
         <v>25</v>
       </c>
       <c r="E38" s="40" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F38" s="39" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="G38" s="40" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="H38" s="39" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="I38" s="39" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
       <c r="J38" s="39" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="K38" s="40" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="L38" s="39">
         <v>1</v>
@@ -4944,107 +4603,107 @@
         <v>20</v>
       </c>
       <c r="N38" s="42">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="O38" s="65" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P38" s="42">
-        <v>5.6000000000000001E-2</v>
+        <v>0.53559999999999997</v>
       </c>
       <c r="Q38" s="42">
         <f t="shared" ref="Q38" si="27">N38*P38</f>
-        <v>1.68</v>
-      </c>
-      <c r="R38" s="42"/>
-    </row>
-    <row r="39" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+        <v>11.247599999999998</v>
+      </c>
+      <c r="R38" s="89"/>
+    </row>
+    <row r="39" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1"/>
       <c r="B39" s="53">
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
       <c r="C39" s="61" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="D39" s="37" t="s">
         <v>26</v>
       </c>
       <c r="E39" s="38" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="G39" s="38" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="H39" s="37" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="I39" s="37" t="s">
-        <v>330</v>
+        <v>378</v>
       </c>
       <c r="J39" s="37" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="K39" s="38" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="L39" s="37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M39" s="41">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="N39" s="41">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="O39" s="64" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P39" s="41">
-        <v>2.9499999999999998E-2</v>
+        <v>0.65639999999999998</v>
       </c>
       <c r="Q39" s="41">
         <f t="shared" ref="Q39" si="28">P39*N39</f>
-        <v>2.9499999999999997</v>
-      </c>
-      <c r="R39" s="41"/>
-    </row>
-    <row r="40" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+        <v>27.5688</v>
+      </c>
+      <c r="R39" s="85"/>
+    </row>
+    <row r="40" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1"/>
       <c r="B40" s="53">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="C40" s="60" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="D40" s="39" t="s">
         <v>27</v>
       </c>
       <c r="E40" s="40" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="F40" s="39" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="G40" s="40" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="H40" s="39" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="I40" s="39" t="s">
-        <v>395</v>
+        <v>314</v>
       </c>
       <c r="J40" s="39" t="s">
-        <v>396</v>
+        <v>314</v>
       </c>
       <c r="K40" s="40" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="L40" s="39">
         <v>1</v>
@@ -5057,108 +4716,104 @@
         <v>21</v>
       </c>
       <c r="O40" s="65" t="s">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="P40" s="42">
-        <v>0.53559999999999997</v>
+        <v>1.2</v>
       </c>
       <c r="Q40" s="42">
         <f t="shared" ref="Q40" si="29">N40*P40</f>
-        <v>11.247599999999998</v>
-      </c>
-      <c r="R40" s="102" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+        <v>25.2</v>
+      </c>
+      <c r="R40" s="42"/>
+    </row>
+    <row r="41" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1"/>
       <c r="B41" s="53">
         <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
       <c r="C41" s="61" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="D41" s="37" t="s">
         <v>28</v>
       </c>
       <c r="E41" s="38" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="F41" s="37" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="G41" s="38" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="H41" s="37" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="I41" s="37" t="s">
-        <v>397</v>
+        <v>314</v>
       </c>
       <c r="J41" s="37" t="s">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="K41" s="38" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="L41" s="37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M41" s="41">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="N41" s="41">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="O41" s="64" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P41" s="41">
-        <v>0.65639999999999998</v>
+        <v>9.2200000000000004E-2</v>
       </c>
       <c r="Q41" s="41">
         <f t="shared" ref="Q41" si="30">P41*N41</f>
-        <v>27.5688</v>
-      </c>
-      <c r="R41" s="94" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2.3050000000000002</v>
+      </c>
+      <c r="R41" s="41"/>
+    </row>
+    <row r="42" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1"/>
       <c r="B42" s="53">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="C42" s="60" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="D42" s="39" t="s">
         <v>29</v>
       </c>
       <c r="E42" s="40" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="F42" s="39" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="G42" s="40" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="H42" s="39" t="s">
-        <v>256</v>
+        <v>233</v>
       </c>
       <c r="I42" s="39" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J42" s="39" t="s">
-        <v>330</v>
+        <v>382</v>
       </c>
       <c r="K42" s="40" t="s">
-        <v>330</v>
+        <v>282</v>
       </c>
       <c r="L42" s="39">
         <v>1</v>
@@ -5171,49 +4826,49 @@
         <v>21</v>
       </c>
       <c r="O42" s="65" t="s">
-        <v>399</v>
+        <v>344</v>
       </c>
       <c r="P42" s="42">
-        <v>1.2</v>
+        <v>0.45629999999999998</v>
       </c>
       <c r="Q42" s="42">
         <f t="shared" ref="Q42" si="31">N42*P42</f>
-        <v>25.2</v>
+        <v>9.5823</v>
       </c>
       <c r="R42" s="42"/>
     </row>
-    <row r="43" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
       <c r="B43" s="53">
         <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
       </c>
       <c r="C43" s="61" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="D43" s="37" t="s">
         <v>30</v>
       </c>
       <c r="E43" s="38" t="s">
-        <v>105</v>
+        <v>460</v>
       </c>
       <c r="F43" s="37" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="G43" s="38" t="s">
-        <v>168</v>
+        <v>459</v>
       </c>
       <c r="H43" s="37" t="s">
-        <v>257</v>
+        <v>442</v>
       </c>
       <c r="I43" s="37" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J43" s="37" t="s">
-        <v>400</v>
+        <v>443</v>
       </c>
       <c r="K43" s="38" t="s">
-        <v>330</v>
+        <v>458</v>
       </c>
       <c r="L43" s="37">
         <v>1</v>
@@ -5226,49 +4881,49 @@
         <v>25</v>
       </c>
       <c r="O43" s="64" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P43" s="41">
-        <v>9.2200000000000004E-2</v>
+        <v>0.1012</v>
       </c>
       <c r="Q43" s="41">
         <f t="shared" ref="Q43" si="32">P43*N43</f>
-        <v>2.3050000000000002</v>
-      </c>
-      <c r="R43" s="41"/>
-    </row>
-    <row r="44" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="R43" s="81"/>
+    </row>
+    <row r="44" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
       <c r="B44" s="53">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="C44" s="60" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="D44" s="39" t="s">
         <v>31</v>
       </c>
       <c r="E44" s="40" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="F44" s="39" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="G44" s="40" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="H44" s="39" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I44" s="39" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J44" s="39" t="s">
-        <v>401</v>
+        <v>314</v>
       </c>
       <c r="K44" s="40" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="L44" s="39">
         <v>1</v>
@@ -5278,52 +4933,52 @@
         <v>20</v>
       </c>
       <c r="N44" s="42">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="O44" s="65" t="s">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="P44" s="42">
-        <v>0.45629999999999998</v>
+        <v>0.156</v>
       </c>
       <c r="Q44" s="42">
         <f t="shared" ref="Q44" si="33">N44*P44</f>
-        <v>9.5823</v>
+        <v>4.68</v>
       </c>
       <c r="R44" s="42"/>
     </row>
-    <row r="45" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
       <c r="B45" s="53">
         <f>ROW(B45) - ROW($B$9)</f>
         <v>36</v>
       </c>
       <c r="C45" s="61" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="D45" s="37" t="s">
         <v>32</v>
       </c>
       <c r="E45" s="38" t="s">
-        <v>485</v>
+        <v>100</v>
       </c>
       <c r="F45" s="37" t="s">
-        <v>324</v>
+        <v>161</v>
       </c>
       <c r="G45" s="38" t="s">
-        <v>486</v>
-      </c>
-      <c r="H45" s="84" t="s">
-        <v>487</v>
+        <v>199</v>
+      </c>
+      <c r="H45" s="37" t="s">
+        <v>246</v>
       </c>
       <c r="I45" s="37" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J45" s="37" t="s">
-        <v>488</v>
+        <v>314</v>
       </c>
       <c r="K45" s="38" t="s">
-        <v>489</v>
+        <v>314</v>
       </c>
       <c r="L45" s="37">
         <v>1</v>
@@ -5332,75 +4987,73 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N45" s="93">
-        <v>25</v>
+      <c r="N45" s="41">
+        <v>30</v>
       </c>
       <c r="O45" s="64" t="s">
-        <v>360</v>
+        <v>384</v>
       </c>
       <c r="P45" s="41">
-        <v>0.1012</v>
+        <v>0.08</v>
       </c>
       <c r="Q45" s="41">
         <f t="shared" ref="Q45" si="34">P45*N45</f>
-        <v>2.5299999999999998</v>
-      </c>
-      <c r="R45" s="82" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2.4</v>
+      </c>
+      <c r="R45" s="41"/>
+    </row>
+    <row r="46" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1"/>
       <c r="B46" s="53">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="C46" s="60" t="s">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="D46" s="39" t="s">
         <v>33</v>
       </c>
       <c r="E46" s="40" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F46" s="39" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="G46" s="40" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="H46" s="39" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="I46" s="39" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J46" s="39" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="K46" s="40" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="L46" s="39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M46" s="42">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N46" s="42">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="O46" s="65" t="s">
-        <v>402</v>
+        <v>380</v>
       </c>
       <c r="P46" s="42">
-        <v>0.156</v>
+        <v>1.5</v>
       </c>
       <c r="Q46" s="42">
         <f t="shared" ref="Q46" si="35">N46*P46</f>
-        <v>4.68</v>
+        <v>75</v>
       </c>
       <c r="R46" s="42"/>
     </row>
@@ -5410,54 +5063,49 @@
         <f>ROW(B47) - ROW($B$9)</f>
         <v>38</v>
       </c>
-      <c r="C47" s="61" t="s">
-        <v>339</v>
-      </c>
-      <c r="D47" s="37" t="s">
+      <c r="C47" s="67" t="s">
+        <v>283</v>
+      </c>
+      <c r="D47" s="68" t="s">
         <v>34</v>
       </c>
-      <c r="E47" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="F47" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="G47" s="38" t="s">
-        <v>211</v>
-      </c>
-      <c r="H47" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="I47" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="J47" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="K47" s="38" t="s">
-        <v>330</v>
-      </c>
-      <c r="L47" s="37">
-        <v>1</v>
-      </c>
-      <c r="M47" s="41">
+      <c r="E47" s="69" t="s">
+        <v>102</v>
+      </c>
+      <c r="F47" s="68" t="s">
+        <v>163</v>
+      </c>
+      <c r="G47" s="69" t="s">
+        <v>314</v>
+      </c>
+      <c r="H47" s="68" t="s">
+        <v>314</v>
+      </c>
+      <c r="I47" s="68"/>
+      <c r="J47" s="68"/>
+      <c r="K47" s="69" t="s">
+        <v>314</v>
+      </c>
+      <c r="L47" s="68">
+        <v>4</v>
+      </c>
+      <c r="M47" s="70">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N47" s="41">
-        <v>30</v>
-      </c>
-      <c r="O47" s="64" t="s">
-        <v>403</v>
-      </c>
-      <c r="P47" s="41">
-        <v>0.08</v>
-      </c>
-      <c r="Q47" s="41">
-        <f t="shared" ref="Q47" si="36">P47*N47</f>
-        <v>2.4</v>
-      </c>
-      <c r="R47" s="41"/>
+        <v>80</v>
+      </c>
+      <c r="N47" s="70">
+        <f t="shared" ref="N47" si="36">M47+(M47*0.1)</f>
+        <v>88</v>
+      </c>
+      <c r="O47" s="70"/>
+      <c r="P47" s="70"/>
+      <c r="Q47" s="70">
+        <f t="shared" ref="Q47" si="37">P47*N47</f>
+        <v>0</v>
+      </c>
+      <c r="R47" s="71" t="s">
+        <v>385</v>
+      </c>
     </row>
     <row r="48" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1"/>
@@ -5466,55 +5114,53 @@
         <v>39</v>
       </c>
       <c r="C48" s="60" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="D48" s="39" t="s">
         <v>35</v>
       </c>
       <c r="E48" s="40" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="F48" s="39" t="s">
-        <v>324</v>
-      </c>
-      <c r="G48" s="40" t="s">
-        <v>172</v>
+        <v>164</v>
+      </c>
+      <c r="G48" s="40">
+        <v>61300211121</v>
       </c>
       <c r="H48" s="39" t="s">
-        <v>260</v>
+        <v>235</v>
       </c>
       <c r="I48" s="39" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J48" s="39" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="K48" s="40" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="L48" s="39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M48" s="42">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="N48" s="42">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="O48" s="65" t="s">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="P48" s="42">
-        <v>1.5</v>
+        <v>0.13</v>
       </c>
       <c r="Q48" s="42">
-        <f t="shared" ref="Q48" si="37">N48*P48</f>
-        <v>75</v>
-      </c>
-      <c r="R48" s="42" t="s">
-        <v>404</v>
-      </c>
+        <f t="shared" ref="Q48" si="38">N48*P48</f>
+        <v>11.700000000000001</v>
+      </c>
+      <c r="R48" s="42"/>
     </row>
     <row r="49" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1"/>
@@ -5522,49 +5168,54 @@
         <f>ROW(B49) - ROW($B$9)</f>
         <v>40</v>
       </c>
-      <c r="C49" s="67" t="s">
-        <v>298</v>
-      </c>
-      <c r="D49" s="68" t="s">
-        <v>36</v>
-      </c>
-      <c r="E49" s="69" t="s">
-        <v>110</v>
-      </c>
-      <c r="F49" s="68" t="s">
-        <v>173</v>
-      </c>
-      <c r="G49" s="69" t="s">
-        <v>330</v>
-      </c>
-      <c r="H49" s="68" t="s">
-        <v>330</v>
-      </c>
-      <c r="I49" s="68"/>
-      <c r="J49" s="68"/>
-      <c r="K49" s="69" t="s">
-        <v>330</v>
-      </c>
-      <c r="L49" s="68">
+      <c r="C49" s="61" t="s">
+        <v>324</v>
+      </c>
+      <c r="D49" s="37" t="s">
+        <v>448</v>
+      </c>
+      <c r="E49" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="F49" s="37" t="s">
+        <v>165</v>
+      </c>
+      <c r="G49" s="38" t="s">
+        <v>200</v>
+      </c>
+      <c r="H49" s="37" t="s">
+        <v>248</v>
+      </c>
+      <c r="I49" s="37" t="s">
+        <v>386</v>
+      </c>
+      <c r="J49" s="37" t="s">
+        <v>387</v>
+      </c>
+      <c r="K49" s="38" t="s">
+        <v>314</v>
+      </c>
+      <c r="L49" s="37">
         <v>4</v>
       </c>
-      <c r="M49" s="70">
+      <c r="M49" s="41">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N49" s="70">
-        <f t="shared" ref="N49" si="38">M49+(M49*0.1)</f>
-        <v>88</v>
-      </c>
-      <c r="O49" s="70"/>
-      <c r="P49" s="70"/>
-      <c r="Q49" s="70">
+      <c r="N49" s="41">
+        <v>85</v>
+      </c>
+      <c r="O49" s="64" t="s">
+        <v>344</v>
+      </c>
+      <c r="P49" s="41">
+        <v>0.21740000000000001</v>
+      </c>
+      <c r="Q49" s="41">
         <f t="shared" ref="Q49" si="39">P49*N49</f>
-        <v>0</v>
-      </c>
-      <c r="R49" s="71" t="s">
-        <v>405</v>
-      </c>
+        <v>18.478999999999999</v>
+      </c>
+      <c r="R49" s="41"/>
     </row>
     <row r="50" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1"/>
@@ -5573,213 +5224,209 @@
         <v>41</v>
       </c>
       <c r="C50" s="60" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="D50" s="39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E50" s="40" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="F50" s="39" t="s">
-        <v>174</v>
-      </c>
-      <c r="G50" s="40">
-        <v>61300211121</v>
+        <v>166</v>
+      </c>
+      <c r="G50" s="40" t="s">
+        <v>201</v>
       </c>
       <c r="H50" s="39" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="I50" s="39" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J50" s="39" t="s">
-        <v>330</v>
+        <v>388</v>
       </c>
       <c r="K50" s="40" t="s">
-        <v>330</v>
+        <v>284</v>
       </c>
       <c r="L50" s="39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M50" s="42">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="N50" s="42">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="O50" s="65" t="s">
-        <v>399</v>
+        <v>344</v>
       </c>
       <c r="P50" s="42">
-        <v>0.13</v>
+        <v>1E-3</v>
       </c>
       <c r="Q50" s="42">
         <f t="shared" ref="Q50" si="40">N50*P50</f>
-        <v>11.700000000000001</v>
-      </c>
-      <c r="R50" s="42" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0.1</v>
+      </c>
+      <c r="R50" s="42"/>
+    </row>
+    <row r="51" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1"/>
       <c r="B51" s="53">
         <f>ROW(B51) - ROW($B$9)</f>
         <v>42</v>
       </c>
       <c r="C51" s="61" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="D51" s="37" t="s">
-        <v>497</v>
+        <v>37</v>
       </c>
       <c r="E51" s="38" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F51" s="37" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="G51" s="38" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="H51" s="37" t="s">
-        <v>261</v>
+        <v>229</v>
       </c>
       <c r="I51" s="37" t="s">
-        <v>406</v>
+        <v>314</v>
       </c>
       <c r="J51" s="37" t="s">
-        <v>407</v>
+        <v>389</v>
       </c>
       <c r="K51" s="38" t="s">
-        <v>330</v>
-      </c>
-      <c r="L51" s="81">
-        <v>4</v>
+        <v>285</v>
+      </c>
+      <c r="L51" s="37">
+        <v>1</v>
       </c>
       <c r="M51" s="41">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="N51" s="41">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="O51" s="64" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P51" s="41">
-        <v>0.21740000000000001</v>
+        <v>1.4E-3</v>
       </c>
       <c r="Q51" s="41">
         <f t="shared" ref="Q51" si="41">P51*N51</f>
-        <v>18.478999999999999</v>
-      </c>
-      <c r="R51" s="41" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="R51" s="41"/>
+    </row>
+    <row r="52" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1"/>
       <c r="B52" s="53">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="C52" s="60" t="s">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="D52" s="39" t="s">
         <v>38</v>
       </c>
       <c r="E52" s="40" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="F52" s="39" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="G52" s="40" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="H52" s="39" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="I52" s="39" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J52" s="39" t="s">
-        <v>409</v>
+        <v>390</v>
       </c>
       <c r="K52" s="40" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="L52" s="39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M52" s="42">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="N52" s="42">
         <v>100</v>
       </c>
       <c r="O52" s="65" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P52" s="42">
-        <v>1E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="Q52" s="42">
         <f t="shared" ref="Q52" si="42">N52*P52</f>
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="R52" s="42"/>
     </row>
-    <row r="53" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1"/>
       <c r="B53" s="53">
         <f>ROW(B53) - ROW($B$9)</f>
         <v>44</v>
       </c>
       <c r="C53" s="61" t="s">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="D53" s="37" t="s">
         <v>39</v>
       </c>
       <c r="E53" s="38" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="F53" s="37" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="G53" s="38" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="H53" s="37" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="I53" s="37" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J53" s="37" t="s">
-        <v>410</v>
+        <v>391</v>
       </c>
       <c r="K53" s="38" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="L53" s="37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M53" s="41">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N53" s="41">
         <v>100</v>
       </c>
       <c r="O53" s="64" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P53" s="41">
         <v>1.4E-3</v>
@@ -5790,667 +5437,665 @@
       </c>
       <c r="R53" s="41"/>
     </row>
-    <row r="54" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1"/>
       <c r="B54" s="53">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="C54" s="60" t="s">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="D54" s="39" t="s">
         <v>40</v>
       </c>
       <c r="E54" s="40" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="F54" s="39" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="G54" s="40" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="H54" s="39" t="s">
-        <v>262</v>
+        <v>229</v>
       </c>
       <c r="I54" s="39" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J54" s="39" t="s">
-        <v>411</v>
+        <v>392</v>
       </c>
       <c r="K54" s="40" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="L54" s="39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M54" s="42">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="N54" s="42">
         <v>100</v>
       </c>
       <c r="O54" s="65" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P54" s="42">
-        <v>1.6000000000000001E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q54" s="42">
         <f t="shared" ref="Q54" si="44">N54*P54</f>
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="R54" s="42"/>
     </row>
-    <row r="55" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1"/>
       <c r="B55" s="53">
         <f>ROW(B55) - ROW($B$9)</f>
         <v>46</v>
       </c>
       <c r="C55" s="61" t="s">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="D55" s="37" t="s">
         <v>41</v>
       </c>
       <c r="E55" s="38" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="F55" s="37" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="G55" s="38" t="s">
-        <v>216</v>
+        <v>330</v>
       </c>
       <c r="H55" s="37" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="I55" s="37" t="s">
-        <v>330</v>
+        <v>393</v>
       </c>
       <c r="J55" s="37" t="s">
-        <v>412</v>
+        <v>394</v>
       </c>
       <c r="K55" s="38" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="L55" s="37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M55" s="41">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="N55" s="41">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="O55" s="64" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P55" s="41">
-        <v>1.4E-3</v>
+        <v>6.4500000000000002E-2</v>
       </c>
       <c r="Q55" s="41">
         <f t="shared" ref="Q55" si="45">P55*N55</f>
-        <v>0.13999999999999999</v>
+        <v>5.8049999999999997</v>
       </c>
       <c r="R55" s="41"/>
     </row>
     <row r="56" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
       <c r="B56" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B56) - ROW($B$9)</f>
         <v>47</v>
       </c>
-      <c r="C56" s="60" t="s">
-        <v>341</v>
-      </c>
-      <c r="D56" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="E56" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="F56" s="39" t="s">
-        <v>176</v>
-      </c>
-      <c r="G56" s="40" t="s">
-        <v>217</v>
-      </c>
-      <c r="H56" s="39" t="s">
-        <v>242</v>
-      </c>
-      <c r="I56" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="J56" s="39" t="s">
-        <v>413</v>
-      </c>
-      <c r="K56" s="40" t="s">
-        <v>303</v>
-      </c>
-      <c r="L56" s="39">
-        <v>4</v>
-      </c>
-      <c r="M56" s="42">
+      <c r="C56" s="61" t="s">
+        <v>325</v>
+      </c>
+      <c r="D56" s="37" t="s">
+        <v>425</v>
+      </c>
+      <c r="E56" s="37" t="s">
+        <v>449</v>
+      </c>
+      <c r="F56" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="G56" s="37" t="s">
+        <v>427</v>
+      </c>
+      <c r="H56" s="37" t="s">
+        <v>252</v>
+      </c>
+      <c r="I56" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="J56" s="37" t="s">
+        <v>428</v>
+      </c>
+      <c r="K56" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="L56" s="37">
+        <v>8</v>
+      </c>
+      <c r="M56" s="37">
         <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-      <c r="N56" s="42">
+        <v>160</v>
+      </c>
+      <c r="N56" s="110">
         <v>100</v>
       </c>
-      <c r="O56" s="65" t="s">
-        <v>360</v>
-      </c>
-      <c r="P56" s="42">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Q56" s="42">
+      <c r="O56" s="90" t="s">
+        <v>344</v>
+      </c>
+      <c r="P56" s="37">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q56" s="37">
         <f t="shared" ref="Q56" si="46">N56*P56</f>
-        <v>0.13</v>
-      </c>
-      <c r="R56" s="42"/>
-    </row>
-    <row r="57" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0.11</v>
+      </c>
+      <c r="R56" s="81"/>
+    </row>
+    <row r="57" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1"/>
       <c r="B57" s="53">
         <f>ROW(B57) - ROW($B$9)</f>
         <v>48</v>
       </c>
       <c r="C57" s="61" t="s">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="D57" s="37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E57" s="38" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="F57" s="37" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="G57" s="38" t="s">
-        <v>346</v>
+        <v>207</v>
       </c>
       <c r="H57" s="37" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="I57" s="37" t="s">
-        <v>414</v>
+        <v>314</v>
       </c>
       <c r="J57" s="37" t="s">
-        <v>415</v>
+        <v>314</v>
       </c>
       <c r="K57" s="38" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="L57" s="37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M57" s="41">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="N57" s="41">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="O57" s="64" t="s">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="P57" s="41">
-        <v>6.4500000000000002E-2</v>
+        <v>1.8589999999999999E-2</v>
       </c>
       <c r="Q57" s="41">
         <f t="shared" ref="Q57" si="47">P57*N57</f>
-        <v>5.8049999999999997</v>
+        <v>0.55769999999999997</v>
       </c>
       <c r="R57" s="41"/>
     </row>
-    <row r="58" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1"/>
       <c r="B58" s="53">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="C58" s="60" t="s">
-        <v>341</v>
-      </c>
-      <c r="D58" s="97" t="s">
-        <v>450</v>
+        <v>325</v>
+      </c>
+      <c r="D58" s="39" t="s">
+        <v>43</v>
       </c>
       <c r="E58" s="40" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="F58" s="39" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="G58" s="40" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="H58" s="39" t="s">
-        <v>242</v>
-      </c>
-      <c r="I58" s="39"/>
+        <v>229</v>
+      </c>
+      <c r="I58" s="39" t="s">
+        <v>314</v>
+      </c>
       <c r="J58" s="39" t="s">
-        <v>416</v>
+        <v>396</v>
       </c>
       <c r="K58" s="40" t="s">
-        <v>305</v>
-      </c>
-      <c r="L58" s="85">
+        <v>292</v>
+      </c>
+      <c r="L58" s="39">
         <v>1</v>
       </c>
       <c r="M58" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N58" s="86">
+      <c r="N58" s="42">
         <v>100</v>
       </c>
       <c r="O58" s="65" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P58" s="42">
-        <v>1.5E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="Q58" s="42">
-        <f t="shared" ref="Q58:Q59" si="48">N58*P58</f>
-        <v>0.15</v>
-      </c>
-      <c r="R58" s="87" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="59" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" ref="Q58" si="48">N58*P58</f>
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="R58" s="42"/>
+    </row>
+    <row r="59" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1"/>
       <c r="B59" s="53">
         <f>ROW(B59) - ROW($B$9)</f>
         <v>50</v>
       </c>
       <c r="C59" s="61" t="s">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="D59" s="37" t="s">
-        <v>449</v>
-      </c>
-      <c r="E59" s="37" t="s">
-        <v>498</v>
+        <v>44</v>
+      </c>
+      <c r="E59" s="38" t="s">
+        <v>114</v>
       </c>
       <c r="F59" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="G59" s="37" t="s">
-        <v>452</v>
+        <v>166</v>
+      </c>
+      <c r="G59" s="38" t="s">
+        <v>209</v>
       </c>
       <c r="H59" s="37" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="I59" s="37" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J59" s="37" t="s">
-        <v>453</v>
-      </c>
-      <c r="K59" s="37" t="s">
-        <v>454</v>
-      </c>
-      <c r="L59" s="81">
-        <v>8</v>
-      </c>
-      <c r="M59" s="37">
+        <v>314</v>
+      </c>
+      <c r="K59" s="38" t="s">
+        <v>293</v>
+      </c>
+      <c r="L59" s="37">
+        <v>1</v>
+      </c>
+      <c r="M59" s="41">
         <f t="shared" si="1"/>
-        <v>160</v>
-      </c>
-      <c r="N59" s="104">
-        <v>100</v>
-      </c>
-      <c r="O59" s="105" t="s">
-        <v>360</v>
-      </c>
-      <c r="P59" s="37">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="Q59" s="37">
-        <f t="shared" si="48"/>
-        <v>0.11</v>
-      </c>
-      <c r="R59" s="82" t="s">
-        <v>455</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="N59" s="41">
+        <v>50</v>
+      </c>
+      <c r="O59" s="64" t="s">
+        <v>383</v>
+      </c>
+      <c r="P59" s="41">
+        <v>4.6699999999999997E-3</v>
+      </c>
+      <c r="Q59" s="41">
+        <f t="shared" ref="Q59" si="49">P59*N59</f>
+        <v>0.23349999999999999</v>
+      </c>
+      <c r="R59" s="41"/>
     </row>
     <row r="60" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1"/>
       <c r="B60" s="53">
-        <f>ROW(B60) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="C60" s="61" t="s">
-        <v>341</v>
-      </c>
-      <c r="D60" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="E60" s="38" t="s">
-        <v>120</v>
-      </c>
-      <c r="F60" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="G60" s="38" t="s">
-        <v>219</v>
-      </c>
-      <c r="H60" s="37" t="s">
-        <v>264</v>
-      </c>
-      <c r="I60" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="J60" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="K60" s="38" t="s">
-        <v>306</v>
-      </c>
-      <c r="L60" s="37">
+      <c r="C60" s="60" t="s">
+        <v>325</v>
+      </c>
+      <c r="D60" s="39" t="s">
+        <v>45</v>
+      </c>
+      <c r="E60" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="F60" s="39" t="s">
+        <v>166</v>
+      </c>
+      <c r="G60" s="40" t="s">
+        <v>210</v>
+      </c>
+      <c r="H60" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="I60" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="J60" s="39" t="s">
+        <v>397</v>
+      </c>
+      <c r="K60" s="40" t="s">
+        <v>294</v>
+      </c>
+      <c r="L60" s="39">
         <v>1</v>
       </c>
-      <c r="M60" s="41">
+      <c r="M60" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N60" s="41">
-        <v>30</v>
-      </c>
-      <c r="O60" s="64" t="s">
-        <v>402</v>
-      </c>
-      <c r="P60" s="41">
-        <v>1.8589999999999999E-2</v>
-      </c>
-      <c r="Q60" s="41">
-        <f t="shared" ref="Q60" si="49">P60*N60</f>
-        <v>0.55769999999999997</v>
-      </c>
-      <c r="R60" s="41"/>
+      <c r="N60" s="42">
+        <v>100</v>
+      </c>
+      <c r="O60" s="65" t="s">
+        <v>344</v>
+      </c>
+      <c r="P60" s="42">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q60" s="42">
+        <f t="shared" ref="Q60" si="50">N60*P60</f>
+        <v>0.12</v>
+      </c>
+      <c r="R60" s="42"/>
     </row>
     <row r="61" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1"/>
       <c r="B61" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B61) - ROW($B$9)</f>
         <v>52</v>
       </c>
-      <c r="C61" s="60" t="s">
-        <v>341</v>
-      </c>
-      <c r="D61" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="E61" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F61" s="39" t="s">
-        <v>176</v>
-      </c>
-      <c r="G61" s="40" t="s">
-        <v>220</v>
-      </c>
-      <c r="H61" s="39" t="s">
-        <v>242</v>
-      </c>
-      <c r="I61" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="J61" s="39" t="s">
-        <v>417</v>
-      </c>
-      <c r="K61" s="40" t="s">
-        <v>307</v>
-      </c>
-      <c r="L61" s="39">
+      <c r="C61" s="61" t="s">
+        <v>325</v>
+      </c>
+      <c r="D61" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="E61" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="F61" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="G61" s="38" t="s">
+        <v>211</v>
+      </c>
+      <c r="H61" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="I61" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="J61" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="K61" s="38" t="s">
+        <v>295</v>
+      </c>
+      <c r="L61" s="37">
         <v>1</v>
       </c>
-      <c r="M61" s="42">
+      <c r="M61" s="41">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N61" s="42">
-        <v>100</v>
-      </c>
-      <c r="O61" s="65" t="s">
-        <v>360</v>
-      </c>
-      <c r="P61" s="42">
-        <v>1.4E-3</v>
-      </c>
-      <c r="Q61" s="42">
-        <f t="shared" ref="Q61" si="50">N61*P61</f>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="R61" s="42"/>
+      <c r="N61" s="41">
+        <v>50</v>
+      </c>
+      <c r="O61" s="64" t="s">
+        <v>383</v>
+      </c>
+      <c r="P61" s="41">
+        <v>1.11E-2</v>
+      </c>
+      <c r="Q61" s="41">
+        <f t="shared" ref="Q61" si="51">P61*N61</f>
+        <v>0.55500000000000005</v>
+      </c>
+      <c r="R61" s="41"/>
     </row>
     <row r="62" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1"/>
       <c r="B62" s="53">
-        <f>ROW(B62) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="C62" s="61" t="s">
-        <v>341</v>
-      </c>
-      <c r="D62" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="E62" s="38" t="s">
-        <v>122</v>
-      </c>
-      <c r="F62" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="G62" s="38" t="s">
-        <v>221</v>
-      </c>
-      <c r="H62" s="37" t="s">
-        <v>264</v>
-      </c>
-      <c r="I62" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="J62" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="K62" s="38" t="s">
-        <v>308</v>
-      </c>
-      <c r="L62" s="37">
+      <c r="C62" s="60" t="s">
+        <v>325</v>
+      </c>
+      <c r="D62" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="E62" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="F62" s="39" t="s">
+        <v>166</v>
+      </c>
+      <c r="G62" s="40" t="s">
+        <v>212</v>
+      </c>
+      <c r="H62" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="I62" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="J62" s="39" t="s">
+        <v>398</v>
+      </c>
+      <c r="K62" s="40" t="s">
+        <v>296</v>
+      </c>
+      <c r="L62" s="39">
         <v>1</v>
       </c>
-      <c r="M62" s="41">
+      <c r="M62" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N62" s="41">
-        <v>50</v>
-      </c>
-      <c r="O62" s="64" t="s">
-        <v>402</v>
-      </c>
-      <c r="P62" s="41">
-        <v>4.6699999999999997E-3</v>
-      </c>
-      <c r="Q62" s="41">
-        <f t="shared" ref="Q62" si="51">P62*N62</f>
-        <v>0.23349999999999999</v>
-      </c>
-      <c r="R62" s="41"/>
+      <c r="N62" s="42">
+        <v>100</v>
+      </c>
+      <c r="O62" s="65" t="s">
+        <v>344</v>
+      </c>
+      <c r="P62" s="42">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="Q62" s="42">
+        <f t="shared" ref="Q62" si="52">N62*P62</f>
+        <v>0.21</v>
+      </c>
+      <c r="R62" s="42"/>
     </row>
     <row r="63" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1"/>
       <c r="B63" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B63) - ROW($B$9)</f>
         <v>54</v>
       </c>
-      <c r="C63" s="60" t="s">
-        <v>341</v>
-      </c>
-      <c r="D63" s="39" t="s">
-        <v>47</v>
-      </c>
-      <c r="E63" s="40" t="s">
-        <v>123</v>
-      </c>
-      <c r="F63" s="39" t="s">
-        <v>176</v>
-      </c>
-      <c r="G63" s="40" t="s">
-        <v>222</v>
-      </c>
-      <c r="H63" s="39" t="s">
-        <v>242</v>
-      </c>
-      <c r="I63" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="J63" s="39" t="s">
-        <v>418</v>
-      </c>
-      <c r="K63" s="40" t="s">
-        <v>309</v>
-      </c>
-      <c r="L63" s="39">
+      <c r="C63" s="61" t="s">
+        <v>325</v>
+      </c>
+      <c r="D63" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="E63" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="F63" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="G63" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="H63" s="37" t="s">
+        <v>229</v>
+      </c>
+      <c r="I63" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="J63" s="37" t="s">
+        <v>399</v>
+      </c>
+      <c r="K63" s="38" t="s">
+        <v>297</v>
+      </c>
+      <c r="L63" s="37">
         <v>1</v>
       </c>
-      <c r="M63" s="42">
+      <c r="M63" s="41">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N63" s="42">
+      <c r="N63" s="41">
         <v>100</v>
       </c>
-      <c r="O63" s="65" t="s">
-        <v>360</v>
-      </c>
-      <c r="P63" s="42">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q63" s="42">
-        <f t="shared" ref="Q63" si="52">N63*P63</f>
-        <v>0.12</v>
-      </c>
-      <c r="R63" s="42"/>
+      <c r="O63" s="64" t="s">
+        <v>344</v>
+      </c>
+      <c r="P63" s="41">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="Q63" s="41">
+        <f t="shared" ref="Q63" si="53">P63*N63</f>
+        <v>0.16</v>
+      </c>
+      <c r="R63" s="41"/>
     </row>
     <row r="64" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1"/>
       <c r="B64" s="53">
-        <f>ROW(B64) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="C64" s="61" t="s">
-        <v>341</v>
-      </c>
-      <c r="D64" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="E64" s="38" t="s">
-        <v>124</v>
-      </c>
-      <c r="F64" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="G64" s="38" t="s">
-        <v>223</v>
-      </c>
-      <c r="H64" s="37" t="s">
-        <v>264</v>
-      </c>
-      <c r="I64" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="J64" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="K64" s="38" t="s">
-        <v>310</v>
-      </c>
-      <c r="L64" s="37">
+      <c r="C64" s="60" t="s">
+        <v>325</v>
+      </c>
+      <c r="D64" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="E64" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="F64" s="39" t="s">
+        <v>166</v>
+      </c>
+      <c r="G64" s="40" t="s">
+        <v>214</v>
+      </c>
+      <c r="H64" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="I64" s="39" t="s">
+        <v>400</v>
+      </c>
+      <c r="J64" s="39" t="s">
+        <v>401</v>
+      </c>
+      <c r="K64" s="40" t="s">
+        <v>298</v>
+      </c>
+      <c r="L64" s="39">
         <v>1</v>
       </c>
-      <c r="M64" s="41">
+      <c r="M64" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N64" s="41">
+      <c r="N64" s="42">
         <v>50</v>
       </c>
-      <c r="O64" s="64" t="s">
-        <v>402</v>
-      </c>
-      <c r="P64" s="41">
-        <v>1.11E-2</v>
-      </c>
-      <c r="Q64" s="41">
-        <f t="shared" ref="Q64" si="53">P64*N64</f>
-        <v>0.55500000000000005</v>
-      </c>
-      <c r="R64" s="41"/>
-    </row>
-    <row r="65" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O64" s="65" t="s">
+        <v>344</v>
+      </c>
+      <c r="P64" s="42">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="Q64" s="42">
+        <f t="shared" ref="Q64" si="54">N64*P64</f>
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="R64" s="42"/>
+    </row>
+    <row r="65" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1"/>
       <c r="B65" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B65) - ROW($B$9)</f>
         <v>56</v>
       </c>
-      <c r="C65" s="60" t="s">
-        <v>341</v>
-      </c>
-      <c r="D65" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="E65" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="F65" s="39" t="s">
-        <v>176</v>
-      </c>
-      <c r="G65" s="40" t="s">
-        <v>224</v>
-      </c>
-      <c r="H65" s="39" t="s">
-        <v>242</v>
-      </c>
-      <c r="I65" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="J65" s="39" t="s">
-        <v>419</v>
-      </c>
-      <c r="K65" s="40" t="s">
-        <v>311</v>
-      </c>
-      <c r="L65" s="39">
-        <v>1</v>
-      </c>
-      <c r="M65" s="42">
+      <c r="C65" s="61" t="s">
+        <v>325</v>
+      </c>
+      <c r="D65" s="37" t="s">
+        <v>403</v>
+      </c>
+      <c r="E65" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="F65" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="G65" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="H65" s="37" t="s">
+        <v>229</v>
+      </c>
+      <c r="I65" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="J65" s="37" t="s">
+        <v>402</v>
+      </c>
+      <c r="K65" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="L65" s="37">
+        <v>2</v>
+      </c>
+      <c r="M65" s="41">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N65" s="42">
+        <v>40</v>
+      </c>
+      <c r="N65" s="41">
         <v>100</v>
       </c>
-      <c r="O65" s="65" t="s">
-        <v>360</v>
-      </c>
-      <c r="P65" s="42">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="Q65" s="42">
-        <f t="shared" ref="Q65" si="54">N65*P65</f>
-        <v>0.21</v>
-      </c>
-      <c r="R65" s="42"/>
+      <c r="O65" s="64" t="s">
+        <v>344</v>
+      </c>
+      <c r="P65" s="41">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q65" s="41">
+        <f t="shared" ref="Q65" si="55">P65*N65</f>
+        <v>0.11</v>
+      </c>
+      <c r="R65" s="41"/>
     </row>
     <row r="66" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
@@ -6459,143 +6104,141 @@
         <v>57</v>
       </c>
       <c r="C66" s="61" t="s">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="D66" s="37" t="s">
         <v>50</v>
       </c>
       <c r="E66" s="38" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="F66" s="37" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="G66" s="38" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="H66" s="37" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="I66" s="37" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J66" s="37" t="s">
-        <v>420</v>
+        <v>404</v>
       </c>
       <c r="K66" s="38" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="L66" s="37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M66" s="41">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N66" s="41">
         <v>100</v>
       </c>
       <c r="O66" s="64" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P66" s="41">
-        <v>1.6000000000000001E-3</v>
+        <v>1.5E-3</v>
       </c>
       <c r="Q66" s="41">
-        <f t="shared" ref="Q66" si="55">P66*N66</f>
-        <v>0.16</v>
+        <f t="shared" ref="Q66" si="56">P66*N66</f>
+        <v>0.15</v>
       </c>
       <c r="R66" s="41"/>
     </row>
     <row r="67" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1"/>
       <c r="B67" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B67) - ROW($B$9)</f>
         <v>58</v>
       </c>
       <c r="C67" s="60" t="s">
-        <v>341</v>
-      </c>
-      <c r="D67" s="39" t="s">
-        <v>51</v>
+        <v>325</v>
+      </c>
+      <c r="D67" s="88" t="s">
+        <v>426</v>
       </c>
       <c r="E67" s="40" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="F67" s="39" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="G67" s="40" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="H67" s="39" t="s">
-        <v>242</v>
-      </c>
-      <c r="I67" s="39" t="s">
-        <v>421</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="I67" s="39"/>
       <c r="J67" s="39" t="s">
-        <v>422</v>
+        <v>395</v>
       </c>
       <c r="K67" s="40" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="L67" s="39">
         <v>1</v>
       </c>
       <c r="M67" s="42">
-        <f t="shared" si="1"/>
+        <f>L67*20</f>
         <v>20</v>
       </c>
       <c r="N67" s="42">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O67" s="65" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P67" s="42">
-        <v>6.8999999999999999E-3</v>
+        <v>1.5E-3</v>
       </c>
       <c r="Q67" s="42">
-        <f t="shared" ref="Q67" si="56">N67*P67</f>
-        <v>0.34499999999999997</v>
-      </c>
-      <c r="R67" s="42"/>
-    </row>
-    <row r="68" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+        <f>N67*P67</f>
+        <v>0.15</v>
+      </c>
+      <c r="R67" s="84"/>
+    </row>
+    <row r="68" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1"/>
       <c r="B68" s="53">
         <f>ROW(B68) - ROW($B$9)</f>
         <v>59</v>
       </c>
       <c r="C68" s="61" t="s">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="D68" s="37" t="s">
-        <v>424</v>
+        <v>51</v>
       </c>
       <c r="E68" s="38" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="F68" s="37" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="G68" s="38" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="H68" s="37" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="I68" s="37" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J68" s="37" t="s">
-        <v>423</v>
+        <v>405</v>
       </c>
       <c r="K68" s="38" t="s">
-        <v>314</v>
-      </c>
-      <c r="L68" s="81">
+        <v>301</v>
+      </c>
+      <c r="L68" s="37">
         <v>2</v>
       </c>
       <c r="M68" s="41">
@@ -6606,73 +6249,71 @@
         <v>100</v>
       </c>
       <c r="O68" s="64" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P68" s="41">
-        <v>1.1000000000000001E-3</v>
+        <v>1.5E-3</v>
       </c>
       <c r="Q68" s="41">
         <f t="shared" ref="Q68" si="57">P68*N68</f>
-        <v>0.11</v>
-      </c>
-      <c r="R68" s="41" t="s">
-        <v>426</v>
-      </c>
+        <v>0.15</v>
+      </c>
+      <c r="R68" s="41"/>
     </row>
     <row r="69" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1"/>
       <c r="B69" s="53">
-        <f>ROW(B69) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="C69" s="61" t="s">
-        <v>341</v>
-      </c>
-      <c r="D69" s="37" t="s">
+      <c r="C69" s="60" t="s">
+        <v>325</v>
+      </c>
+      <c r="D69" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="E69" s="38" t="s">
-        <v>129</v>
-      </c>
-      <c r="F69" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="G69" s="38" t="s">
-        <v>228</v>
-      </c>
-      <c r="H69" s="37" t="s">
-        <v>242</v>
-      </c>
-      <c r="I69" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="J69" s="37" t="s">
-        <v>425</v>
-      </c>
-      <c r="K69" s="38" t="s">
-        <v>315</v>
-      </c>
-      <c r="L69" s="37">
-        <v>2</v>
-      </c>
-      <c r="M69" s="41">
+      <c r="E69" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="F69" s="39" t="s">
+        <v>166</v>
+      </c>
+      <c r="G69" s="40" t="s">
+        <v>218</v>
+      </c>
+      <c r="H69" s="39" t="s">
+        <v>251</v>
+      </c>
+      <c r="I69" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="J69" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="K69" s="40" t="s">
+        <v>302</v>
+      </c>
+      <c r="L69" s="39">
+        <v>1</v>
+      </c>
+      <c r="M69" s="42">
         <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N69" s="41">
-        <v>100</v>
-      </c>
-      <c r="O69" s="64" t="s">
-        <v>360</v>
-      </c>
-      <c r="P69" s="41">
-        <v>1.5E-3</v>
-      </c>
-      <c r="Q69" s="41">
-        <f t="shared" ref="Q69" si="58">P69*N69</f>
-        <v>0.15</v>
-      </c>
-      <c r="R69" s="41"/>
+        <v>20</v>
+      </c>
+      <c r="N69" s="42">
+        <v>25</v>
+      </c>
+      <c r="O69" s="65" t="s">
+        <v>406</v>
+      </c>
+      <c r="P69" s="42">
+        <v>8.5400000000000004E-2</v>
+      </c>
+      <c r="Q69" s="42">
+        <f t="shared" ref="Q69" si="58">N69*P69</f>
+        <v>2.1350000000000002</v>
+      </c>
+      <c r="R69" s="42"/>
     </row>
     <row r="70" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1"/>
@@ -6681,1217 +6322,1042 @@
         <v>61</v>
       </c>
       <c r="C70" s="61" t="s">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="D70" s="37" t="s">
         <v>53</v>
       </c>
       <c r="E70" s="38" t="s">
-        <v>130</v>
-      </c>
-      <c r="F70" s="37" t="s">
-        <v>176</v>
+        <v>440</v>
+      </c>
+      <c r="F70" s="96" t="s">
+        <v>166</v>
       </c>
       <c r="G70" s="38" t="s">
-        <v>229</v>
+        <v>462</v>
       </c>
       <c r="H70" s="37" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="I70" s="37" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J70" s="37" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="K70" s="38" t="s">
-        <v>316</v>
+        <v>461</v>
       </c>
       <c r="L70" s="37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M70" s="41">
-        <f t="shared" si="1"/>
-        <v>40</v>
+        <f t="shared" ref="M70:M87" si="59">L70*20</f>
+        <v>20</v>
       </c>
       <c r="N70" s="41">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O70" s="64" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P70" s="41">
-        <v>1.5E-3</v>
+        <v>3.8E-3</v>
       </c>
       <c r="Q70" s="41">
-        <f t="shared" ref="Q70" si="59">P70*N70</f>
-        <v>0.15</v>
-      </c>
-      <c r="R70" s="41"/>
+        <f t="shared" ref="Q70" si="60">P70*N70</f>
+        <v>0.19</v>
+      </c>
+      <c r="R70" s="81"/>
     </row>
     <row r="71" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1"/>
       <c r="B71" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B71) - ROW($B$9)</f>
         <v>62</v>
       </c>
       <c r="C71" s="60" t="s">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="D71" s="39" t="s">
-        <v>54</v>
+        <v>463</v>
       </c>
       <c r="E71" s="40" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F71" s="39" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="G71" s="40" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="H71" s="39" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="I71" s="39" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J71" s="39" t="s">
-        <v>330</v>
+        <v>410</v>
       </c>
       <c r="K71" s="40" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="L71" s="39">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M71" s="42">
-        <f t="shared" si="1"/>
-        <v>20</v>
+        <f>L71*20</f>
+        <v>120</v>
       </c>
       <c r="N71" s="42">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="O71" s="65" t="s">
-        <v>428</v>
+        <v>344</v>
       </c>
       <c r="P71" s="42">
-        <v>8.5400000000000004E-2</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q71" s="42">
-        <f t="shared" ref="Q71" si="60">N71*P71</f>
-        <v>2.1350000000000002</v>
-      </c>
-      <c r="R71" s="42"/>
-    </row>
-    <row r="72" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" ref="Q71" si="61">N71*P71</f>
+        <v>0.24</v>
+      </c>
+      <c r="R71" s="84"/>
+    </row>
+    <row r="72" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1"/>
       <c r="B72" s="53">
         <f>ROW(B72) - ROW($B$9)</f>
         <v>63</v>
       </c>
       <c r="C72" s="61" t="s">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="D72" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="E72" s="83" t="s">
-        <v>479</v>
-      </c>
-      <c r="F72" s="103" t="s">
-        <v>480</v>
+        <v>54</v>
+      </c>
+      <c r="E72" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="F72" s="37" t="s">
+        <v>166</v>
       </c>
       <c r="G72" s="38" t="s">
-        <v>481</v>
-      </c>
-      <c r="H72" s="84" t="s">
-        <v>265</v>
+        <v>331</v>
+      </c>
+      <c r="H72" s="37" t="s">
+        <v>252</v>
       </c>
       <c r="I72" s="37" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="J72" s="37" t="s">
-        <v>482</v>
+        <v>407</v>
       </c>
       <c r="K72" s="38" t="s">
-        <v>483</v>
+        <v>303</v>
       </c>
       <c r="L72" s="37">
         <v>1</v>
       </c>
       <c r="M72" s="41">
-        <f t="shared" ref="M72:M90" si="61">L72*20</f>
+        <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N72" s="93">
-        <v>50</v>
+      <c r="N72" s="41">
+        <v>100</v>
       </c>
       <c r="O72" s="64" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="P72" s="41">
-        <v>3.8E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="Q72" s="41">
         <f t="shared" ref="Q72" si="62">P72*N72</f>
-        <v>0.19</v>
-      </c>
-      <c r="R72" s="82" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="73" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0.1</v>
+      </c>
+      <c r="R72" s="41"/>
+    </row>
+    <row r="73" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1"/>
       <c r="B73" s="53">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="C73" s="98" t="s">
-        <v>341</v>
-      </c>
-      <c r="D73" s="99" t="s">
-        <v>56</v>
-      </c>
-      <c r="E73" s="96" t="s">
-        <v>132</v>
-      </c>
-      <c r="F73" s="99" t="s">
-        <v>176</v>
-      </c>
-      <c r="G73" s="96" t="s">
-        <v>231</v>
-      </c>
-      <c r="H73" s="99" t="s">
-        <v>264</v>
-      </c>
-      <c r="I73" s="99" t="s">
-        <v>330</v>
-      </c>
-      <c r="J73" s="99" t="s">
-        <v>330</v>
-      </c>
-      <c r="K73" s="96" t="s">
-        <v>318</v>
-      </c>
-      <c r="L73" s="99">
+      <c r="C73" s="60" t="s">
+        <v>325</v>
+      </c>
+      <c r="D73" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="E73" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="F73" s="39" t="s">
+        <v>166</v>
+      </c>
+      <c r="G73" s="40" t="s">
+        <v>332</v>
+      </c>
+      <c r="H73" s="39" t="s">
+        <v>253</v>
+      </c>
+      <c r="I73" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="J73" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="K73" s="40" t="s">
+        <v>304</v>
+      </c>
+      <c r="L73" s="39">
         <v>1</v>
       </c>
-      <c r="M73" s="100">
-        <f t="shared" si="61"/>
+      <c r="M73" s="42">
+        <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N73" s="100">
-        <v>0</v>
-      </c>
-      <c r="O73" s="101" t="s">
-        <v>402</v>
-      </c>
-      <c r="P73" s="100">
-        <v>1.8589999999999999E-2</v>
-      </c>
-      <c r="Q73" s="100">
+      <c r="N73" s="42">
+        <v>50</v>
+      </c>
+      <c r="O73" s="65" t="s">
+        <v>344</v>
+      </c>
+      <c r="P73" s="42">
+        <v>4.3E-3</v>
+      </c>
+      <c r="Q73" s="42">
         <f t="shared" ref="Q73" si="63">N73*P73</f>
-        <v>0</v>
-      </c>
-      <c r="R73" s="87" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="74" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0.215</v>
+      </c>
+      <c r="R73" s="42"/>
+    </row>
+    <row r="74" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1"/>
       <c r="B74" s="53">
         <f>ROW(B74) - ROW($B$9)</f>
         <v>65</v>
       </c>
-      <c r="C74" s="61" t="s">
-        <v>341</v>
-      </c>
-      <c r="D74" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="E74" s="38" t="s">
-        <v>133</v>
-      </c>
-      <c r="F74" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="G74" s="38" t="s">
-        <v>347</v>
-      </c>
-      <c r="H74" s="37" t="s">
-        <v>265</v>
-      </c>
-      <c r="I74" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="J74" s="37" t="s">
-        <v>429</v>
-      </c>
-      <c r="K74" s="38" t="s">
-        <v>319</v>
-      </c>
-      <c r="L74" s="37">
-        <v>1</v>
-      </c>
-      <c r="M74" s="41">
-        <f t="shared" si="61"/>
-        <v>20</v>
-      </c>
-      <c r="N74" s="41">
+      <c r="C74" s="111" t="s">
+        <v>325</v>
+      </c>
+      <c r="D74" s="112" t="s">
+        <v>56</v>
+      </c>
+      <c r="E74" s="113" t="s">
+        <v>126</v>
+      </c>
+      <c r="F74" s="112" t="s">
+        <v>168</v>
+      </c>
+      <c r="G74" s="113" t="s">
+        <v>219</v>
+      </c>
+      <c r="H74" s="112" t="s">
+        <v>229</v>
+      </c>
+      <c r="I74" s="112" t="s">
+        <v>314</v>
+      </c>
+      <c r="J74" s="112" t="s">
+        <v>409</v>
+      </c>
+      <c r="K74" s="113" t="s">
+        <v>305</v>
+      </c>
+      <c r="L74" s="112">
+        <v>4</v>
+      </c>
+      <c r="M74" s="71">
+        <f t="shared" si="59"/>
+        <v>80</v>
+      </c>
+      <c r="N74" s="71">
         <v>100</v>
       </c>
-      <c r="O74" s="64" t="s">
-        <v>360</v>
-      </c>
-      <c r="P74" s="41">
-        <v>1E-3</v>
-      </c>
-      <c r="Q74" s="41">
+      <c r="O74" s="114" t="s">
+        <v>344</v>
+      </c>
+      <c r="P74" s="71">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q74" s="71">
         <f t="shared" ref="Q74" si="64">P74*N74</f>
-        <v>0.1</v>
-      </c>
-      <c r="R74" s="41"/>
-    </row>
-    <row r="75" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0.12</v>
+      </c>
+      <c r="R74" s="71" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1"/>
       <c r="B75" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B75) - ROW($B$9)</f>
         <v>66</v>
       </c>
-      <c r="C75" s="60" t="s">
-        <v>341</v>
-      </c>
-      <c r="D75" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="E75" s="40" t="s">
-        <v>134</v>
-      </c>
-      <c r="F75" s="39" t="s">
-        <v>176</v>
-      </c>
-      <c r="G75" s="40" t="s">
-        <v>348</v>
-      </c>
-      <c r="H75" s="39" t="s">
-        <v>266</v>
-      </c>
-      <c r="I75" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="J75" s="39" t="s">
-        <v>430</v>
-      </c>
-      <c r="K75" s="40" t="s">
-        <v>320</v>
-      </c>
-      <c r="L75" s="39">
-        <v>1</v>
-      </c>
-      <c r="M75" s="42">
-        <f t="shared" si="61"/>
-        <v>20</v>
-      </c>
-      <c r="N75" s="42">
-        <v>50</v>
-      </c>
-      <c r="O75" s="65" t="s">
-        <v>360</v>
-      </c>
-      <c r="P75" s="42">
-        <v>4.3E-3</v>
-      </c>
-      <c r="Q75" s="42">
-        <f t="shared" ref="Q75" si="65">N75*P75</f>
-        <v>0.215</v>
-      </c>
-      <c r="R75" s="42"/>
-    </row>
-    <row r="76" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C75" s="111" t="s">
+        <v>169</v>
+      </c>
+      <c r="D75" s="112" t="s">
+        <v>465</v>
+      </c>
+      <c r="E75" s="113" t="s">
+        <v>128</v>
+      </c>
+      <c r="F75" s="112" t="s">
+        <v>169</v>
+      </c>
+      <c r="G75" s="113" t="s">
+        <v>314</v>
+      </c>
+      <c r="H75" s="112" t="s">
+        <v>314</v>
+      </c>
+      <c r="I75" s="112" t="s">
+        <v>314</v>
+      </c>
+      <c r="J75" s="112" t="s">
+        <v>314</v>
+      </c>
+      <c r="K75" s="113" t="s">
+        <v>314</v>
+      </c>
+      <c r="L75" s="112">
+        <v>11</v>
+      </c>
+      <c r="M75" s="71">
+        <f t="shared" si="59"/>
+        <v>220</v>
+      </c>
+      <c r="N75" s="71">
+        <f t="shared" ref="N75:N76" si="65">M75+(M75*0.1)</f>
+        <v>242</v>
+      </c>
+      <c r="O75" s="71"/>
+      <c r="P75" s="71"/>
+      <c r="Q75" s="71">
+        <f t="shared" ref="Q75" si="66">P75*N75</f>
+        <v>0</v>
+      </c>
+      <c r="R75" s="71" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1"/>
       <c r="B76" s="53">
-        <f>ROW(B76) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="C76" s="61" t="s">
-        <v>341</v>
-      </c>
-      <c r="D76" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="E76" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="F76" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="G76" s="38" t="s">
-        <v>232</v>
-      </c>
-      <c r="H76" s="37" t="s">
-        <v>242</v>
-      </c>
-      <c r="I76" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="J76" s="37" t="s">
-        <v>431</v>
-      </c>
-      <c r="K76" s="38" t="s">
-        <v>321</v>
-      </c>
-      <c r="L76" s="37">
-        <v>4</v>
-      </c>
-      <c r="M76" s="41">
-        <f t="shared" si="61"/>
-        <v>80</v>
-      </c>
-      <c r="N76" s="41">
-        <v>100</v>
-      </c>
-      <c r="O76" s="64" t="s">
-        <v>360</v>
-      </c>
-      <c r="P76" s="41">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q76" s="41">
-        <f t="shared" ref="Q76" si="66">P76*N76</f>
-        <v>0.12</v>
-      </c>
-      <c r="R76" s="41"/>
-    </row>
-    <row r="77" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C76" s="60" t="s">
+        <v>327</v>
+      </c>
+      <c r="D76" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="E76" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="F76" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="G76" s="40"/>
+      <c r="H76" s="39" t="s">
+        <v>254</v>
+      </c>
+      <c r="I76" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="J76" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="K76" s="40" t="s">
+        <v>314</v>
+      </c>
+      <c r="L76" s="39">
+        <v>1</v>
+      </c>
+      <c r="M76" s="42">
+        <f t="shared" si="59"/>
+        <v>20</v>
+      </c>
+      <c r="N76" s="42">
+        <f t="shared" si="65"/>
+        <v>22</v>
+      </c>
+      <c r="O76" s="42"/>
+      <c r="P76" s="42"/>
+      <c r="Q76" s="42">
+        <f t="shared" ref="Q76" si="67">N76*P76</f>
+        <v>0</v>
+      </c>
+      <c r="R76" s="42"/>
+    </row>
+    <row r="77" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1"/>
       <c r="B77" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B77) - ROW($B$9)</f>
         <v>68</v>
       </c>
-      <c r="C77" s="60" t="s">
-        <v>341</v>
-      </c>
-      <c r="D77" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="E77" s="40" t="s">
-        <v>136</v>
-      </c>
-      <c r="F77" s="39" t="s">
-        <v>176</v>
-      </c>
-      <c r="G77" s="40" t="s">
-        <v>233</v>
-      </c>
-      <c r="H77" s="39" t="s">
-        <v>242</v>
-      </c>
-      <c r="I77" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="J77" s="39" t="s">
-        <v>432</v>
-      </c>
-      <c r="K77" s="40" t="s">
-        <v>322</v>
-      </c>
-      <c r="L77" s="39">
-        <v>6</v>
-      </c>
-      <c r="M77" s="42">
-        <f t="shared" si="61"/>
-        <v>120</v>
-      </c>
-      <c r="N77" s="42">
-        <v>200</v>
-      </c>
-      <c r="O77" s="65" t="s">
-        <v>360</v>
-      </c>
-      <c r="P77" s="42">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q77" s="42">
-        <f t="shared" ref="Q77" si="67">N77*P77</f>
-        <v>0.24</v>
-      </c>
-      <c r="R77" s="87" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="78" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C77" s="61" t="s">
+        <v>328</v>
+      </c>
+      <c r="D77" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="E77" s="38" t="s">
+        <v>130</v>
+      </c>
+      <c r="F77" s="37" t="s">
+        <v>308</v>
+      </c>
+      <c r="G77" s="38">
+        <v>750314597</v>
+      </c>
+      <c r="H77" s="37" t="s">
+        <v>255</v>
+      </c>
+      <c r="I77" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="J77" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="K77" s="38" t="s">
+        <v>314</v>
+      </c>
+      <c r="L77" s="37">
+        <v>1</v>
+      </c>
+      <c r="M77" s="41">
+        <f t="shared" si="59"/>
+        <v>20</v>
+      </c>
+      <c r="N77" s="41">
+        <v>21</v>
+      </c>
+      <c r="O77" s="64" t="s">
+        <v>380</v>
+      </c>
+      <c r="P77" s="41">
+        <v>3.81</v>
+      </c>
+      <c r="Q77" s="41">
+        <f t="shared" ref="Q77" si="68">P77*N77</f>
+        <v>80.010000000000005</v>
+      </c>
+      <c r="R77" s="41"/>
+    </row>
+    <row r="78" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1"/>
       <c r="B78" s="53">
-        <f>ROW(B78) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>69</v>
       </c>
-      <c r="C78" s="67" t="s">
-        <v>179</v>
-      </c>
-      <c r="D78" s="68" t="s">
-        <v>60</v>
-      </c>
-      <c r="E78" s="69" t="s">
-        <v>137</v>
-      </c>
-      <c r="F78" s="68" t="s">
-        <v>179</v>
-      </c>
-      <c r="G78" s="69" t="s">
-        <v>330</v>
-      </c>
-      <c r="H78" s="68" t="s">
-        <v>330</v>
-      </c>
-      <c r="I78" s="68" t="s">
-        <v>330</v>
-      </c>
-      <c r="J78" s="68" t="s">
-        <v>330</v>
-      </c>
-      <c r="K78" s="69" t="s">
-        <v>330</v>
-      </c>
-      <c r="L78" s="68">
-        <v>11</v>
-      </c>
-      <c r="M78" s="70">
-        <f t="shared" si="61"/>
-        <v>220</v>
-      </c>
-      <c r="N78" s="70">
-        <f t="shared" ref="N78:N79" si="68">M78+(M78*0.1)</f>
-        <v>242</v>
-      </c>
-      <c r="O78" s="70"/>
-      <c r="P78" s="70"/>
-      <c r="Q78" s="70">
-        <f t="shared" ref="Q78" si="69">P78*N78</f>
-        <v>0</v>
-      </c>
-      <c r="R78" s="71" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="79" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C78" s="60" t="s">
+        <v>329</v>
+      </c>
+      <c r="D78" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="E78" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="F78" s="39" t="s">
+        <v>308</v>
+      </c>
+      <c r="G78" s="40" t="s">
+        <v>171</v>
+      </c>
+      <c r="H78" s="39" t="s">
+        <v>256</v>
+      </c>
+      <c r="I78" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="J78" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="K78" s="40" t="s">
+        <v>314</v>
+      </c>
+      <c r="L78" s="39">
+        <v>1</v>
+      </c>
+      <c r="M78" s="42">
+        <f t="shared" si="59"/>
+        <v>20</v>
+      </c>
+      <c r="N78" s="42">
+        <v>21</v>
+      </c>
+      <c r="O78" s="65" t="s">
+        <v>411</v>
+      </c>
+      <c r="P78" s="42">
+        <v>2.48</v>
+      </c>
+      <c r="Q78" s="42">
+        <f t="shared" ref="Q78" si="69">N78*P78</f>
+        <v>52.08</v>
+      </c>
+      <c r="R78" s="42"/>
+    </row>
+    <row r="79" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1"/>
       <c r="B79" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B79) - ROW($B$9)</f>
         <v>70</v>
       </c>
-      <c r="C79" s="60" t="s">
-        <v>343</v>
-      </c>
-      <c r="D79" s="39" t="s">
-        <v>61</v>
-      </c>
-      <c r="E79" s="40" t="s">
-        <v>138</v>
-      </c>
-      <c r="F79" s="39" t="s">
-        <v>180</v>
-      </c>
-      <c r="G79" s="40"/>
-      <c r="H79" s="39" t="s">
-        <v>267</v>
-      </c>
-      <c r="I79" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="J79" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="K79" s="40" t="s">
-        <v>330</v>
-      </c>
-      <c r="L79" s="39">
+      <c r="C79" s="61" t="s">
+        <v>329</v>
+      </c>
+      <c r="D79" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="E79" s="38" t="s">
+        <v>132</v>
+      </c>
+      <c r="F79" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="G79" s="38" t="s">
+        <v>221</v>
+      </c>
+      <c r="H79" s="37" t="s">
+        <v>257</v>
+      </c>
+      <c r="I79" s="37" t="s">
+        <v>412</v>
+      </c>
+      <c r="J79" s="37" t="s">
+        <v>413</v>
+      </c>
+      <c r="K79" s="38" t="s">
+        <v>314</v>
+      </c>
+      <c r="L79" s="37">
         <v>1</v>
       </c>
-      <c r="M79" s="42">
-        <f t="shared" si="61"/>
+      <c r="M79" s="41">
+        <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N79" s="42">
-        <f t="shared" si="68"/>
-        <v>22</v>
-      </c>
-      <c r="O79" s="42"/>
-      <c r="P79" s="42"/>
-      <c r="Q79" s="42">
-        <f t="shared" ref="Q79" si="70">N79*P79</f>
-        <v>0</v>
-      </c>
-      <c r="R79" s="42"/>
-    </row>
-    <row r="80" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N79" s="41">
+        <v>21</v>
+      </c>
+      <c r="O79" s="64" t="s">
+        <v>344</v>
+      </c>
+      <c r="P79" s="41">
+        <v>1.3939999999999999</v>
+      </c>
+      <c r="Q79" s="41">
+        <f t="shared" ref="Q79" si="70">P79*N79</f>
+        <v>29.273999999999997</v>
+      </c>
+      <c r="R79" s="85"/>
+    </row>
+    <row r="80" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1"/>
       <c r="B80" s="53">
-        <f>ROW(B80) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>71</v>
       </c>
-      <c r="C80" s="61" t="s">
+      <c r="C80" s="60" t="s">
+        <v>329</v>
+      </c>
+      <c r="D80" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="E80" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="F80" s="39" t="s">
+        <v>173</v>
+      </c>
+      <c r="G80" s="40" t="s">
+        <v>222</v>
+      </c>
+      <c r="H80" s="39" t="s">
+        <v>256</v>
+      </c>
+      <c r="I80" s="39" t="s">
+        <v>414</v>
+      </c>
+      <c r="J80" s="39" t="s">
+        <v>415</v>
+      </c>
+      <c r="K80" s="40" t="s">
+        <v>314</v>
+      </c>
+      <c r="L80" s="39">
+        <v>1</v>
+      </c>
+      <c r="M80" s="42">
+        <f t="shared" si="59"/>
+        <v>20</v>
+      </c>
+      <c r="N80" s="42">
+        <v>21</v>
+      </c>
+      <c r="O80" s="65" t="s">
         <v>344</v>
       </c>
-      <c r="D80" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="E80" s="38" t="s">
-        <v>139</v>
-      </c>
-      <c r="F80" s="37" t="s">
-        <v>324</v>
-      </c>
-      <c r="G80" s="38">
-        <v>750314597</v>
-      </c>
-      <c r="H80" s="37" t="s">
-        <v>268</v>
-      </c>
-      <c r="I80" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="J80" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="K80" s="38" t="s">
-        <v>330</v>
-      </c>
-      <c r="L80" s="37">
-        <v>1</v>
-      </c>
-      <c r="M80" s="41">
-        <f t="shared" si="61"/>
-        <v>20</v>
-      </c>
-      <c r="N80" s="41">
-        <v>21</v>
-      </c>
-      <c r="O80" s="64" t="s">
-        <v>399</v>
-      </c>
-      <c r="P80" s="41">
-        <v>3.81</v>
-      </c>
-      <c r="Q80" s="41">
-        <f t="shared" ref="Q80" si="71">P80*N80</f>
-        <v>80.010000000000005</v>
-      </c>
-      <c r="R80" s="41"/>
+      <c r="P80" s="42">
+        <v>0.69430000000000003</v>
+      </c>
+      <c r="Q80" s="42">
+        <f t="shared" ref="Q80" si="71">N80*P80</f>
+        <v>14.580300000000001</v>
+      </c>
+      <c r="R80" s="89"/>
     </row>
     <row r="81" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1"/>
       <c r="B81" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B81) - ROW($B$9)</f>
         <v>72</v>
       </c>
-      <c r="C81" s="60" t="s">
-        <v>345</v>
-      </c>
-      <c r="D81" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="E81" s="40" t="s">
-        <v>140</v>
-      </c>
-      <c r="F81" s="39" t="s">
-        <v>324</v>
-      </c>
-      <c r="G81" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="H81" s="39" t="s">
-        <v>269</v>
-      </c>
-      <c r="I81" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="J81" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="K81" s="40" t="s">
-        <v>330</v>
-      </c>
-      <c r="L81" s="39">
+      <c r="C81" s="61" t="s">
+        <v>329</v>
+      </c>
+      <c r="D81" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="E81" s="38" t="s">
+        <v>134</v>
+      </c>
+      <c r="F81" s="37" t="s">
+        <v>310</v>
+      </c>
+      <c r="G81" s="38" t="s">
+        <v>174</v>
+      </c>
+      <c r="H81" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="I81" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="J81" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="K81" s="38" t="s">
+        <v>314</v>
+      </c>
+      <c r="L81" s="37">
         <v>1</v>
       </c>
-      <c r="M81" s="42">
-        <f t="shared" si="61"/>
+      <c r="M81" s="41">
+        <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N81" s="42">
+      <c r="N81" s="41">
         <v>21</v>
       </c>
-      <c r="O81" s="65" t="s">
-        <v>433</v>
-      </c>
-      <c r="P81" s="42">
-        <v>2.48</v>
-      </c>
-      <c r="Q81" s="42">
-        <f t="shared" ref="Q81" si="72">N81*P81</f>
-        <v>52.08</v>
-      </c>
-      <c r="R81" s="42"/>
-    </row>
-    <row r="82" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O81" s="64" t="s">
+        <v>411</v>
+      </c>
+      <c r="P81" s="41">
+        <v>3.637</v>
+      </c>
+      <c r="Q81" s="41">
+        <f t="shared" ref="Q81" si="72">P81*N81</f>
+        <v>76.376999999999995</v>
+      </c>
+      <c r="R81" s="41"/>
+    </row>
+    <row r="82" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1"/>
       <c r="B82" s="53">
-        <f>ROW(B82) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>73</v>
       </c>
-      <c r="C82" s="61" t="s">
-        <v>345</v>
-      </c>
-      <c r="D82" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="E82" s="38" t="s">
-        <v>141</v>
-      </c>
-      <c r="F82" s="37" t="s">
-        <v>182</v>
-      </c>
-      <c r="G82" s="38" t="s">
-        <v>234</v>
-      </c>
-      <c r="H82" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I82" s="37" t="s">
-        <v>434</v>
-      </c>
-      <c r="J82" s="37" t="s">
-        <v>435</v>
-      </c>
-      <c r="K82" s="38" t="s">
-        <v>330</v>
-      </c>
-      <c r="L82" s="37">
+      <c r="C82" s="60" t="s">
+        <v>329</v>
+      </c>
+      <c r="D82" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="E82" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="F82" s="39" t="s">
+        <v>175</v>
+      </c>
+      <c r="G82" s="40" t="s">
+        <v>223</v>
+      </c>
+      <c r="H82" s="39" t="s">
+        <v>256</v>
+      </c>
+      <c r="I82" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="J82" s="39" t="s">
+        <v>416</v>
+      </c>
+      <c r="K82" s="40" t="s">
+        <v>314</v>
+      </c>
+      <c r="L82" s="39">
         <v>1</v>
       </c>
-      <c r="M82" s="41">
-        <f t="shared" si="61"/>
+      <c r="M82" s="42">
+        <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N82" s="41">
+      <c r="N82" s="42">
         <v>21</v>
       </c>
-      <c r="O82" s="64" t="s">
-        <v>360</v>
-      </c>
-      <c r="P82" s="41">
-        <v>1.3939999999999999</v>
-      </c>
-      <c r="Q82" s="41">
-        <f t="shared" ref="Q82" si="73">P82*N82</f>
-        <v>29.273999999999997</v>
-      </c>
-      <c r="R82" s="94" t="s">
-        <v>461</v>
-      </c>
+      <c r="O82" s="65" t="s">
+        <v>344</v>
+      </c>
+      <c r="P82" s="42">
+        <v>0.43280000000000002</v>
+      </c>
+      <c r="Q82" s="42">
+        <f t="shared" ref="Q82" si="73">N82*P82</f>
+        <v>9.0888000000000009</v>
+      </c>
+      <c r="R82" s="42"/>
     </row>
     <row r="83" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1"/>
       <c r="B83" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B83) - ROW($B$9)</f>
         <v>74</v>
       </c>
-      <c r="C83" s="60" t="s">
-        <v>345</v>
-      </c>
-      <c r="D83" s="39" t="s">
-        <v>65</v>
-      </c>
-      <c r="E83" s="40" t="s">
-        <v>142</v>
-      </c>
-      <c r="F83" s="39" t="s">
-        <v>183</v>
-      </c>
-      <c r="G83" s="40" t="s">
-        <v>235</v>
-      </c>
-      <c r="H83" s="39" t="s">
-        <v>269</v>
-      </c>
-      <c r="I83" s="39" t="s">
-        <v>437</v>
-      </c>
-      <c r="J83" s="39" t="s">
-        <v>438</v>
-      </c>
-      <c r="K83" s="40" t="s">
-        <v>330</v>
-      </c>
-      <c r="L83" s="39">
+      <c r="C83" s="76" t="s">
+        <v>329</v>
+      </c>
+      <c r="D83" s="77" t="s">
+        <v>64</v>
+      </c>
+      <c r="E83" s="78" t="s">
+        <v>136</v>
+      </c>
+      <c r="F83" s="77" t="s">
+        <v>176</v>
+      </c>
+      <c r="G83" s="78" t="s">
+        <v>224</v>
+      </c>
+      <c r="H83" s="77" t="s">
+        <v>258</v>
+      </c>
+      <c r="I83" s="77" t="s">
+        <v>314</v>
+      </c>
+      <c r="J83" s="77" t="s">
+        <v>417</v>
+      </c>
+      <c r="K83" s="78" t="s">
+        <v>314</v>
+      </c>
+      <c r="L83" s="77">
         <v>1</v>
       </c>
-      <c r="M83" s="42">
-        <f t="shared" si="61"/>
+      <c r="M83" s="79">
+        <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N83" s="42">
+      <c r="N83" s="79">
         <v>21</v>
       </c>
-      <c r="O83" s="65" t="s">
-        <v>360</v>
-      </c>
-      <c r="P83" s="42">
-        <v>0.69430000000000003</v>
-      </c>
-      <c r="Q83" s="42">
-        <f t="shared" ref="Q83" si="74">N83*P83</f>
-        <v>14.580300000000001</v>
-      </c>
-      <c r="R83" s="102" t="s">
-        <v>436</v>
+      <c r="O83" s="80" t="s">
+        <v>344</v>
+      </c>
+      <c r="P83" s="79">
+        <v>7.4638</v>
+      </c>
+      <c r="Q83" s="79">
+        <f t="shared" ref="Q83" si="74">P83*N83</f>
+        <v>156.7398</v>
+      </c>
+      <c r="R83" s="79" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="84" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="1"/>
       <c r="B84" s="53">
-        <f>ROW(B84) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>75</v>
       </c>
-      <c r="C84" s="61" t="s">
-        <v>345</v>
-      </c>
-      <c r="D84" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="E84" s="38" t="s">
-        <v>143</v>
-      </c>
-      <c r="F84" s="37" t="s">
-        <v>326</v>
-      </c>
-      <c r="G84" s="38" t="s">
-        <v>184</v>
-      </c>
-      <c r="H84" s="37" t="s">
-        <v>269</v>
-      </c>
-      <c r="I84" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="J84" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="K84" s="38" t="s">
-        <v>330</v>
-      </c>
-      <c r="L84" s="37">
+      <c r="C84" s="60" t="s">
+        <v>329</v>
+      </c>
+      <c r="D84" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="E84" s="40" t="s">
+        <v>137</v>
+      </c>
+      <c r="F84" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="G84" s="40" t="s">
+        <v>225</v>
+      </c>
+      <c r="H84" s="39" t="s">
+        <v>259</v>
+      </c>
+      <c r="I84" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="J84" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="K84" s="58" t="s">
+        <v>315</v>
+      </c>
+      <c r="L84" s="39">
         <v>1</v>
       </c>
-      <c r="M84" s="41">
-        <f t="shared" si="61"/>
+      <c r="M84" s="42">
+        <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N84" s="41">
+      <c r="N84" s="42">
         <v>21</v>
       </c>
-      <c r="O84" s="64" t="s">
-        <v>433</v>
-      </c>
-      <c r="P84" s="41">
-        <v>3.637</v>
-      </c>
-      <c r="Q84" s="41">
-        <f t="shared" ref="Q84" si="75">P84*N84</f>
-        <v>76.376999999999995</v>
-      </c>
-      <c r="R84" s="41"/>
-    </row>
-    <row r="85" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O84" s="65" t="s">
+        <v>411</v>
+      </c>
+      <c r="P84" s="42">
+        <v>2.6459999999999999</v>
+      </c>
+      <c r="Q84" s="42">
+        <f t="shared" ref="Q84" si="75">N84*P84</f>
+        <v>55.565999999999995</v>
+      </c>
+      <c r="R84" s="42"/>
+    </row>
+    <row r="85" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="1"/>
       <c r="B85" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B85) - ROW($B$9)</f>
         <v>76</v>
       </c>
-      <c r="C85" s="60" t="s">
-        <v>345</v>
-      </c>
-      <c r="D85" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="E85" s="40" t="s">
-        <v>144</v>
-      </c>
-      <c r="F85" s="39" t="s">
-        <v>185</v>
-      </c>
-      <c r="G85" s="40" t="s">
-        <v>236</v>
-      </c>
-      <c r="H85" s="39" t="s">
-        <v>269</v>
-      </c>
-      <c r="I85" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="J85" s="39" t="s">
-        <v>439</v>
-      </c>
-      <c r="K85" s="40" t="s">
-        <v>330</v>
-      </c>
-      <c r="L85" s="39">
-        <v>1</v>
-      </c>
-      <c r="M85" s="42">
-        <f t="shared" si="61"/>
-        <v>20</v>
-      </c>
-      <c r="N85" s="42">
-        <v>21</v>
-      </c>
-      <c r="O85" s="65" t="s">
-        <v>360</v>
-      </c>
-      <c r="P85" s="42">
-        <v>0.43280000000000002</v>
-      </c>
-      <c r="Q85" s="42">
-        <f t="shared" ref="Q85" si="76">N85*P85</f>
-        <v>9.0888000000000009</v>
-      </c>
-      <c r="R85" s="42"/>
+      <c r="C85" s="61" t="s">
+        <v>329</v>
+      </c>
+      <c r="D85" s="37" t="s">
+        <v>466</v>
+      </c>
+      <c r="E85" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="F85" s="37" t="s">
+        <v>311</v>
+      </c>
+      <c r="G85" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="H85" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="I85" s="37" t="s">
+        <v>418</v>
+      </c>
+      <c r="J85" s="37" t="s">
+        <v>419</v>
+      </c>
+      <c r="K85" s="38" t="s">
+        <v>314</v>
+      </c>
+      <c r="L85" s="96">
+        <v>2</v>
+      </c>
+      <c r="M85" s="41">
+        <f t="shared" si="59"/>
+        <v>40</v>
+      </c>
+      <c r="N85" s="41">
+        <v>42</v>
+      </c>
+      <c r="O85" s="64" t="s">
+        <v>344</v>
+      </c>
+      <c r="P85" s="41">
+        <v>2.2974000000000001</v>
+      </c>
+      <c r="Q85" s="41">
+        <f t="shared" ref="Q85" si="76">P85*N85</f>
+        <v>96.490800000000007</v>
+      </c>
+      <c r="R85" s="85"/>
     </row>
     <row r="86" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="1"/>
       <c r="B86" s="53">
-        <f>ROW(B86) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>77</v>
       </c>
-      <c r="C86" s="76" t="s">
-        <v>345</v>
-      </c>
-      <c r="D86" s="77" t="s">
-        <v>68</v>
-      </c>
-      <c r="E86" s="78" t="s">
-        <v>145</v>
-      </c>
-      <c r="F86" s="77" t="s">
-        <v>186</v>
-      </c>
-      <c r="G86" s="78" t="s">
-        <v>237</v>
-      </c>
-      <c r="H86" s="77" t="s">
-        <v>271</v>
-      </c>
-      <c r="I86" s="77" t="s">
-        <v>330</v>
-      </c>
-      <c r="J86" s="77" t="s">
-        <v>440</v>
-      </c>
-      <c r="K86" s="78" t="s">
-        <v>330</v>
-      </c>
-      <c r="L86" s="77">
+      <c r="C86" s="60" t="s">
+        <v>329</v>
+      </c>
+      <c r="D86" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="E86" s="40" t="s">
+        <v>139</v>
+      </c>
+      <c r="F86" s="39" t="s">
+        <v>312</v>
+      </c>
+      <c r="G86" s="40" t="s">
+        <v>179</v>
+      </c>
+      <c r="H86" s="39" t="s">
+        <v>259</v>
+      </c>
+      <c r="I86" s="39" t="s">
+        <v>420</v>
+      </c>
+      <c r="J86" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="K86" s="40" t="s">
+        <v>314</v>
+      </c>
+      <c r="L86" s="39">
         <v>1</v>
       </c>
-      <c r="M86" s="79">
-        <f t="shared" si="61"/>
+      <c r="M86" s="42">
+        <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N86" s="79">
+      <c r="N86" s="42">
         <v>21</v>
       </c>
-      <c r="O86" s="80" t="s">
-        <v>360</v>
-      </c>
-      <c r="P86" s="79">
-        <v>7.4638</v>
-      </c>
-      <c r="Q86" s="79">
-        <f t="shared" ref="Q86" si="77">P86*N86</f>
-        <v>156.7398</v>
-      </c>
-      <c r="R86" s="79" t="s">
-        <v>494</v>
+      <c r="O86" s="65" t="s">
+        <v>421</v>
+      </c>
+      <c r="P86" s="42">
+        <v>3.532</v>
+      </c>
+      <c r="Q86" s="42">
+        <f t="shared" ref="Q86" si="77">N86*P86</f>
+        <v>74.171999999999997</v>
+      </c>
+      <c r="R86" s="89" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="87" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="1"/>
       <c r="B87" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B87) - ROW($B$9)</f>
         <v>78</v>
       </c>
-      <c r="C87" s="60" t="s">
-        <v>345</v>
-      </c>
-      <c r="D87" s="39" t="s">
-        <v>69</v>
-      </c>
-      <c r="E87" s="40" t="s">
-        <v>146</v>
-      </c>
-      <c r="F87" s="39" t="s">
-        <v>187</v>
-      </c>
-      <c r="G87" s="40" t="s">
-        <v>238</v>
-      </c>
-      <c r="H87" s="39" t="s">
-        <v>272</v>
-      </c>
-      <c r="I87" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="J87" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="K87" s="58" t="s">
-        <v>331</v>
-      </c>
-      <c r="L87" s="39">
+      <c r="C87" s="61" t="s">
+        <v>329</v>
+      </c>
+      <c r="D87" s="37" t="s">
+        <v>467</v>
+      </c>
+      <c r="E87" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="F87" s="37" t="s">
+        <v>313</v>
+      </c>
+      <c r="G87" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="H87" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="I87" s="63" t="s">
+        <v>314</v>
+      </c>
+      <c r="J87" s="63" t="s">
+        <v>422</v>
+      </c>
+      <c r="K87" s="38" t="s">
+        <v>314</v>
+      </c>
+      <c r="L87" s="37">
         <v>1</v>
       </c>
-      <c r="M87" s="42">
-        <f t="shared" si="61"/>
+      <c r="M87" s="41">
+        <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N87" s="42">
+      <c r="N87" s="41">
         <v>21</v>
       </c>
-      <c r="O87" s="65" t="s">
-        <v>433</v>
-      </c>
-      <c r="P87" s="42">
-        <v>2.6459999999999999</v>
-      </c>
-      <c r="Q87" s="42">
-        <f t="shared" ref="Q87" si="78">N87*P87</f>
-        <v>55.565999999999995</v>
-      </c>
-      <c r="R87" s="42"/>
-    </row>
-    <row r="88" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O87" s="64" t="s">
+        <v>344</v>
+      </c>
+      <c r="P87" s="41">
+        <v>0.39140000000000003</v>
+      </c>
+      <c r="Q87" s="41">
+        <f t="shared" ref="Q87" si="78">P87*N87</f>
+        <v>8.2194000000000003</v>
+      </c>
+      <c r="R87" s="41"/>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
-      <c r="B88" s="53">
-        <f>ROW(B88) - ROW($B$9)</f>
-        <v>79</v>
-      </c>
-      <c r="C88" s="61" t="s">
-        <v>345</v>
-      </c>
-      <c r="D88" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="E88" s="38" t="s">
-        <v>147</v>
-      </c>
-      <c r="F88" s="37" t="s">
-        <v>327</v>
-      </c>
-      <c r="G88" s="38" t="s">
-        <v>188</v>
-      </c>
-      <c r="H88" s="37" t="s">
-        <v>269</v>
-      </c>
-      <c r="I88" s="37" t="s">
-        <v>441</v>
-      </c>
-      <c r="J88" s="37" t="s">
-        <v>442</v>
-      </c>
-      <c r="K88" s="38" t="s">
-        <v>330</v>
-      </c>
-      <c r="L88" s="81">
-        <v>2</v>
-      </c>
-      <c r="M88" s="41">
-        <f t="shared" si="61"/>
-        <v>40</v>
-      </c>
-      <c r="N88" s="41">
-        <v>42</v>
-      </c>
-      <c r="O88" s="64" t="s">
-        <v>360</v>
-      </c>
-      <c r="P88" s="41">
-        <v>2.2974000000000001</v>
-      </c>
-      <c r="Q88" s="41">
-        <f t="shared" ref="Q88" si="79">P88*N88</f>
-        <v>96.490800000000007</v>
-      </c>
-      <c r="R88" s="94" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="89" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B88" s="32"/>
+      <c r="C88" s="51"/>
+      <c r="D88" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="E88" s="34"/>
+      <c r="F88" s="35"/>
+      <c r="G88" s="36"/>
+      <c r="H88" s="35"/>
+      <c r="I88" s="35"/>
+      <c r="J88" s="35"/>
+      <c r="K88" s="36"/>
+      <c r="L88" s="36"/>
+      <c r="M88" s="36"/>
+      <c r="N88" s="36"/>
+      <c r="O88" s="74" t="s">
+        <v>423</v>
+      </c>
+      <c r="P88" s="72"/>
+      <c r="Q88" s="72">
+        <f>SUM(Q10:Q87)</f>
+        <v>960.72630000000004</v>
+      </c>
+      <c r="R88" s="44"/>
+    </row>
+    <row r="89" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="1"/>
-      <c r="B89" s="53">
-        <f t="shared" si="0"/>
-        <v>80</v>
-      </c>
-      <c r="C89" s="60" t="s">
-        <v>345</v>
-      </c>
-      <c r="D89" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="E89" s="40" t="s">
-        <v>148</v>
-      </c>
-      <c r="F89" s="39" t="s">
-        <v>328</v>
-      </c>
-      <c r="G89" s="40" t="s">
-        <v>189</v>
-      </c>
-      <c r="H89" s="39" t="s">
-        <v>272</v>
-      </c>
-      <c r="I89" s="39" t="s">
-        <v>444</v>
-      </c>
-      <c r="J89" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="K89" s="40" t="s">
-        <v>330</v>
-      </c>
-      <c r="L89" s="39">
-        <v>1</v>
-      </c>
-      <c r="M89" s="42">
-        <f t="shared" si="61"/>
-        <v>20</v>
-      </c>
-      <c r="N89" s="42">
-        <v>21</v>
-      </c>
-      <c r="O89" s="65" t="s">
-        <v>445</v>
-      </c>
-      <c r="P89" s="42">
-        <v>3.532</v>
-      </c>
-      <c r="Q89" s="42">
-        <f t="shared" ref="Q89" si="80">N89*P89</f>
-        <v>74.171999999999997</v>
-      </c>
-      <c r="R89" s="102" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="90" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="1"/>
-      <c r="B90" s="53">
-        <f>ROW(B90) - ROW($B$9)</f>
-        <v>81</v>
-      </c>
-      <c r="C90" s="61" t="s">
-        <v>345</v>
-      </c>
-      <c r="D90" s="37" t="s">
-        <v>72</v>
-      </c>
-      <c r="E90" s="38" t="s">
-        <v>149</v>
-      </c>
-      <c r="F90" s="37" t="s">
-        <v>329</v>
-      </c>
-      <c r="G90" s="38" t="s">
-        <v>190</v>
-      </c>
-      <c r="H90" s="37" t="s">
-        <v>269</v>
-      </c>
-      <c r="I90" s="63" t="s">
-        <v>330</v>
-      </c>
-      <c r="J90" s="63" t="s">
-        <v>446</v>
-      </c>
-      <c r="K90" s="38" t="s">
-        <v>330</v>
-      </c>
-      <c r="L90" s="37">
-        <v>1</v>
-      </c>
-      <c r="M90" s="41">
-        <f t="shared" si="61"/>
-        <v>20</v>
-      </c>
-      <c r="N90" s="41">
-        <v>21</v>
-      </c>
-      <c r="O90" s="64" t="s">
-        <v>360</v>
-      </c>
-      <c r="P90" s="41">
-        <v>0.39140000000000003</v>
-      </c>
-      <c r="Q90" s="41">
-        <f t="shared" ref="Q90" si="81">P90*N90</f>
-        <v>8.2194000000000003</v>
-      </c>
-      <c r="R90" s="41"/>
-    </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A91" s="1"/>
-      <c r="B91" s="32"/>
-      <c r="C91" s="51"/>
-      <c r="D91" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="E91" s="34"/>
-      <c r="F91" s="35"/>
-      <c r="G91" s="36"/>
-      <c r="H91" s="35"/>
-      <c r="I91" s="35"/>
-      <c r="J91" s="35"/>
-      <c r="K91" s="36"/>
-      <c r="L91" s="36"/>
-      <c r="M91" s="36"/>
-      <c r="N91" s="36"/>
-      <c r="O91" s="74" t="s">
-        <v>447</v>
-      </c>
-      <c r="P91" s="72"/>
-      <c r="Q91" s="72">
-        <f>SUM(Q10:Q90)</f>
-        <v>963.24430000000007</v>
-      </c>
-      <c r="R91" s="44"/>
-    </row>
-    <row r="92" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="1"/>
-      <c r="B92" s="24"/>
-      <c r="C92" s="52"/>
-      <c r="D92" s="8" t="s">
+      <c r="B89" s="24"/>
+      <c r="C89" s="52"/>
+      <c r="D89" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E92" s="9"/>
-      <c r="F92" s="9"/>
-      <c r="G92" s="9"/>
-      <c r="H92" s="9"/>
-      <c r="I92" s="9"/>
-      <c r="J92" s="9"/>
-      <c r="K92" s="9"/>
-      <c r="L92" s="9"/>
-      <c r="M92" s="9"/>
-      <c r="N92" s="9"/>
-      <c r="O92" s="75" t="s">
-        <v>448</v>
-      </c>
-      <c r="P92" s="73"/>
-      <c r="Q92" s="73">
-        <f>Q91/20</f>
-        <v>48.162215000000003</v>
-      </c>
-      <c r="R92" s="45"/>
+      <c r="E89" s="9"/>
+      <c r="F89" s="9"/>
+      <c r="G89" s="9"/>
+      <c r="H89" s="9"/>
+      <c r="I89" s="9"/>
+      <c r="J89" s="9"/>
+      <c r="K89" s="9"/>
+      <c r="L89" s="9"/>
+      <c r="M89" s="9"/>
+      <c r="N89" s="9"/>
+      <c r="O89" s="75" t="s">
+        <v>424</v>
+      </c>
+      <c r="P89" s="73"/>
+      <c r="Q89" s="73">
+        <f>Q88/20</f>
+        <v>48.036315000000002</v>
+      </c>
+      <c r="R89" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7936,50 +7402,46 @@
     <hyperlink ref="O44" r:id="rId35"/>
     <hyperlink ref="O45" r:id="rId36"/>
     <hyperlink ref="O46" r:id="rId37"/>
-    <hyperlink ref="O47" r:id="rId38"/>
-    <hyperlink ref="O48" r:id="rId39"/>
+    <hyperlink ref="O48" r:id="rId38"/>
+    <hyperlink ref="O49" r:id="rId39"/>
     <hyperlink ref="O50" r:id="rId40"/>
     <hyperlink ref="O51" r:id="rId41"/>
     <hyperlink ref="O52" r:id="rId42"/>
     <hyperlink ref="O53" r:id="rId43"/>
     <hyperlink ref="O54" r:id="rId44"/>
     <hyperlink ref="O55" r:id="rId45"/>
-    <hyperlink ref="O56" r:id="rId46"/>
+    <hyperlink ref="O67" r:id="rId46"/>
     <hyperlink ref="O57" r:id="rId47"/>
     <hyperlink ref="O58" r:id="rId48"/>
-    <hyperlink ref="O60" r:id="rId49"/>
-    <hyperlink ref="O61" r:id="rId50"/>
-    <hyperlink ref="O62" r:id="rId51"/>
-    <hyperlink ref="O63" r:id="rId52"/>
-    <hyperlink ref="O64" r:id="rId53"/>
-    <hyperlink ref="O65" r:id="rId54"/>
-    <hyperlink ref="O66" r:id="rId55"/>
-    <hyperlink ref="O67" r:id="rId56"/>
+    <hyperlink ref="O59" r:id="rId49"/>
+    <hyperlink ref="O60" r:id="rId50"/>
+    <hyperlink ref="O61" r:id="rId51"/>
+    <hyperlink ref="O62" r:id="rId52"/>
+    <hyperlink ref="O63" r:id="rId53"/>
+    <hyperlink ref="O64" r:id="rId54"/>
+    <hyperlink ref="O65" r:id="rId55"/>
+    <hyperlink ref="O66" r:id="rId56"/>
     <hyperlink ref="O68" r:id="rId57"/>
     <hyperlink ref="O69" r:id="rId58"/>
     <hyperlink ref="O70" r:id="rId59"/>
-    <hyperlink ref="O71" r:id="rId60"/>
-    <hyperlink ref="O72" r:id="rId61"/>
-    <hyperlink ref="O73" r:id="rId62"/>
-    <hyperlink ref="O74" r:id="rId63"/>
-    <hyperlink ref="O75" r:id="rId64"/>
-    <hyperlink ref="O76" r:id="rId65"/>
-    <hyperlink ref="O77" r:id="rId66"/>
-    <hyperlink ref="O80" r:id="rId67"/>
-    <hyperlink ref="O81" r:id="rId68"/>
-    <hyperlink ref="O82" r:id="rId69"/>
-    <hyperlink ref="O83" r:id="rId70"/>
-    <hyperlink ref="O84" r:id="rId71"/>
-    <hyperlink ref="O85" r:id="rId72"/>
-    <hyperlink ref="O86" r:id="rId73"/>
-    <hyperlink ref="O87" r:id="rId74"/>
-    <hyperlink ref="O88" r:id="rId75"/>
-    <hyperlink ref="O89" r:id="rId76"/>
-    <hyperlink ref="O90" r:id="rId77"/>
-    <hyperlink ref="O59" r:id="rId78"/>
+    <hyperlink ref="O73" r:id="rId60"/>
+    <hyperlink ref="O74" r:id="rId61"/>
+    <hyperlink ref="O71" r:id="rId62"/>
+    <hyperlink ref="O77" r:id="rId63"/>
+    <hyperlink ref="O78" r:id="rId64"/>
+    <hyperlink ref="O79" r:id="rId65"/>
+    <hyperlink ref="O80" r:id="rId66"/>
+    <hyperlink ref="O81" r:id="rId67"/>
+    <hyperlink ref="O82" r:id="rId68"/>
+    <hyperlink ref="O83" r:id="rId69"/>
+    <hyperlink ref="O84" r:id="rId70"/>
+    <hyperlink ref="O85" r:id="rId71"/>
+    <hyperlink ref="O86" r:id="rId72"/>
+    <hyperlink ref="O87" r:id="rId73"/>
+    <hyperlink ref="O56" r:id="rId74"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId79"/>
-  <drawing r:id="rId80"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId75"/>
+  <drawing r:id="rId76"/>
 </worksheet>
 </file>
--- a/Deliverables/SM_Top Board/_BOM/eSpark BOM (20 Boards).xlsx
+++ b/Deliverables/SM_Top Board/_BOM/eSpark BOM (20 Boards).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="7656"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11496" windowHeight="7596"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="466">
   <si>
     <t>Component list</t>
   </si>
@@ -1240,21 +1240,6 @@
     <t>C100048</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">R30, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>R31</t>
-    </r>
-  </si>
-  <si>
     <t>C114628</t>
   </si>
   <si>
@@ -1336,107 +1321,18 @@
     <t>C33</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">C7, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C38, C39</t>
-    </r>
-  </si>
-  <si>
     <t>C4</t>
   </si>
   <si>
     <t>CAP CER 6.8nF 50V X7R 0603</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">CC0603JRNPO9BN680 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>0603B682K500NT</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Yageo</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>FH</t>
-    </r>
-  </si>
-  <si>
     <t>C1631</t>
   </si>
   <si>
     <t>GRM188R6YA106MA73D</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">CAP CER 10UF </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>35V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> X5R 0603</t>
-    </r>
-  </si>
-  <si>
     <t>C194427</t>
   </si>
   <si>
@@ -1452,44 +1348,9 @@
     <t>C2849490</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">D3, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>DF2</t>
-    </r>
-  </si>
-  <si>
-    <t>Design change required. May cause change in some other misc components.</t>
-  </si>
-  <si>
     <t>Will be provided by Robotshop for prototyping</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">C8, C10, C11, C12, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C41, CF3</t>
-    </r>
-  </si>
-  <si>
     <t>Q2, Q3, Q4, Q5</t>
   </si>
   <si>
@@ -1500,22 +1361,6 @@
   </si>
   <si>
     <t>Quantity changed from 9 to 13. C15, C20 and C40 merged into this due to same value. C55 changed from 1uF to 0.1uF</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">C3, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C46</t>
-    </r>
   </si>
   <si>
     <t>C5, C6, C14, C23, C24, C29, C34, C35</t>
@@ -1602,6 +1447,108 @@
   </si>
   <si>
     <t>U11</t>
+  </si>
+  <si>
+    <t>0603B682K500NT</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CAP CER 10UF </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>35V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> X5R 0603</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>C8, C10, C11, C12,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> C41, CF3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">C7, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C38, C39</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">C3, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C46</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>D3,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> DF2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">R30, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R31</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -2108,7 +2055,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -2262,9 +2209,6 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2285,18 +2229,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="17" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2329,27 +2261,12 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2380,6 +2297,42 @@
     <xf numFmtId="0" fontId="26" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2389,43 +2342,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2801,14 +2760,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
     </row>
     <row r="2" spans="1:18" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
@@ -2856,7 +2815,7 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="100"/>
+      <c r="R3" s="102"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
@@ -2875,12 +2834,12 @@
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
-      <c r="M4" s="62"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="62"/>
-      <c r="P4" s="62"/>
-      <c r="Q4" s="62"/>
-      <c r="R4" s="101"/>
+      <c r="M4" s="61"/>
+      <c r="N4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="61"/>
+      <c r="Q4" s="61"/>
+      <c r="R4" s="103"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
@@ -2897,12 +2856,12 @@
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
-      <c r="M5" s="62"/>
-      <c r="N5" s="62"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="62"/>
-      <c r="Q5" s="62"/>
-      <c r="R5" s="101"/>
+      <c r="M5" s="61"/>
+      <c r="N5" s="61"/>
+      <c r="O5" s="61"/>
+      <c r="P5" s="61"/>
+      <c r="Q5" s="61"/>
+      <c r="R5" s="103"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
@@ -2917,12 +2876,12 @@
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
-      <c r="M6" s="62"/>
-      <c r="N6" s="62"/>
-      <c r="O6" s="62"/>
-      <c r="P6" s="62"/>
-      <c r="Q6" s="62"/>
-      <c r="R6" s="101"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="61"/>
+      <c r="O6" s="61"/>
+      <c r="P6" s="61"/>
+      <c r="Q6" s="61"/>
+      <c r="R6" s="103"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
@@ -2942,7 +2901,7 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="101"/>
+      <c r="R7" s="103"/>
     </row>
     <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
@@ -2962,7 +2921,7 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="101"/>
+      <c r="R8" s="103"/>
     </row>
     <row r="9" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
@@ -3024,7 +2983,7 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="59" t="s">
+      <c r="C10" s="58" t="s">
         <v>317</v>
       </c>
       <c r="D10" s="37" t="s">
@@ -3061,7 +3020,7 @@
       <c r="N10" s="41">
         <v>22</v>
       </c>
-      <c r="O10" s="64" t="s">
+      <c r="O10" s="63" t="s">
         <v>344</v>
       </c>
       <c r="P10" s="41">
@@ -3076,58 +3035,58 @@
     <row r="11" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
       <c r="B11" s="53">
-        <f t="shared" ref="B11:B86" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B87" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="91" t="s">
+      <c r="C11" s="81" t="s">
         <v>317</v>
       </c>
-      <c r="D11" s="92" t="s">
-        <v>450</v>
-      </c>
-      <c r="E11" s="93" t="s">
+      <c r="D11" s="82" t="s">
+        <v>442</v>
+      </c>
+      <c r="E11" s="83" t="s">
         <v>69</v>
       </c>
-      <c r="F11" s="92" t="s">
+      <c r="F11" s="82" t="s">
         <v>143</v>
       </c>
-      <c r="G11" s="93" t="s">
+      <c r="G11" s="83" t="s">
         <v>182</v>
       </c>
-      <c r="H11" s="92" t="s">
+      <c r="H11" s="82" t="s">
         <v>228</v>
       </c>
-      <c r="I11" s="92" t="s">
-        <v>314</v>
-      </c>
-      <c r="J11" s="92" t="s">
+      <c r="I11" s="82" t="s">
+        <v>314</v>
+      </c>
+      <c r="J11" s="82" t="s">
         <v>345</v>
       </c>
-      <c r="K11" s="93" t="s">
+      <c r="K11" s="83" t="s">
         <v>262</v>
       </c>
-      <c r="L11" s="92">
+      <c r="L11" s="82">
         <v>13</v>
       </c>
-      <c r="M11" s="94">
+      <c r="M11" s="84">
         <f>L11*20</f>
         <v>260</v>
       </c>
-      <c r="N11" s="94">
+      <c r="N11" s="84">
         <v>300</v>
       </c>
-      <c r="O11" s="95" t="s">
+      <c r="O11" s="85" t="s">
         <v>344</v>
       </c>
-      <c r="P11" s="94">
+      <c r="P11" s="84">
         <v>1.4E-3</v>
       </c>
-      <c r="Q11" s="94">
+      <c r="Q11" s="84">
         <f>N11*P11</f>
         <v>0.42</v>
       </c>
-      <c r="R11" s="94" t="s">
-        <v>451</v>
+      <c r="R11" s="84" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3136,11 +3095,11 @@
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="61" t="s">
+      <c r="C12" s="60" t="s">
         <v>317</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="E12" s="38" t="s">
         <v>70</v>
@@ -3163,7 +3122,7 @@
       <c r="K12" s="38" t="s">
         <v>263</v>
       </c>
-      <c r="L12" s="96">
+      <c r="L12" s="86">
         <v>2</v>
       </c>
       <c r="M12" s="41">
@@ -3173,7 +3132,7 @@
       <c r="N12" s="41">
         <v>100</v>
       </c>
-      <c r="O12" s="64" t="s">
+      <c r="O12" s="63" t="s">
         <v>344</v>
       </c>
       <c r="P12" s="41">
@@ -3183,7 +3142,7 @@
         <f t="shared" ref="Q12" si="2">P12*N12</f>
         <v>0.13</v>
       </c>
-      <c r="R12" s="81"/>
+      <c r="R12" s="76"/>
     </row>
     <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
@@ -3191,11 +3150,11 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="60" t="s">
+      <c r="C13" s="59" t="s">
         <v>317</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E13" s="40" t="s">
         <v>71</v>
@@ -3218,17 +3177,17 @@
       <c r="K13" s="40" t="s">
         <v>264</v>
       </c>
-      <c r="L13" s="97">
+      <c r="L13" s="87">
         <v>1</v>
       </c>
       <c r="M13" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N13" s="98">
+      <c r="N13" s="88">
         <v>40</v>
       </c>
-      <c r="O13" s="65" t="s">
+      <c r="O13" s="64" t="s">
         <v>344</v>
       </c>
       <c r="P13" s="42">
@@ -3238,7 +3197,7 @@
         <f t="shared" ref="Q13" si="3">N13*P13</f>
         <v>1.4359999999999999</v>
       </c>
-      <c r="R13" s="84"/>
+      <c r="R13" s="77"/>
     </row>
     <row r="14" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1"/>
@@ -3246,11 +3205,11 @@
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="61" t="s">
+      <c r="C14" s="60" t="s">
         <v>317</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="E14" s="38" t="s">
         <v>72</v>
@@ -3283,7 +3242,7 @@
       <c r="N14" s="41">
         <v>200</v>
       </c>
-      <c r="O14" s="64" t="s">
+      <c r="O14" s="63" t="s">
         <v>344</v>
       </c>
       <c r="P14" s="41">
@@ -3293,7 +3252,7 @@
         <f>P14*N14</f>
         <v>8.18</v>
       </c>
-      <c r="R14" s="81"/>
+      <c r="R14" s="76"/>
     </row>
     <row r="15" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
@@ -3301,11 +3260,11 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="60" t="s">
+      <c r="C15" s="59" t="s">
         <v>317</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>431</v>
+        <v>462</v>
       </c>
       <c r="E15" s="40" t="s">
         <v>73</v>
@@ -3328,17 +3287,17 @@
       <c r="K15" s="40" t="s">
         <v>266</v>
       </c>
-      <c r="L15" s="97">
+      <c r="L15" s="87">
         <v>3</v>
       </c>
       <c r="M15" s="42">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="N15" s="98">
+      <c r="N15" s="88">
         <v>100</v>
       </c>
-      <c r="O15" s="65" t="s">
+      <c r="O15" s="64" t="s">
         <v>344</v>
       </c>
       <c r="P15" s="42">
@@ -3348,7 +3307,7 @@
         <f t="shared" ref="Q15" si="4">N15*P15</f>
         <v>0.59</v>
       </c>
-      <c r="R15" s="84"/>
+      <c r="R15" s="77"/>
     </row>
     <row r="16" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
@@ -3356,29 +3315,29 @@
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="61" t="s">
+      <c r="C16" s="60" t="s">
         <v>317</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>438</v>
+        <v>460</v>
       </c>
       <c r="F16" s="37" t="s">
         <v>143</v>
       </c>
-      <c r="G16" s="82" t="s">
-        <v>437</v>
-      </c>
-      <c r="H16" s="83" t="s">
+      <c r="G16" s="104" t="s">
+        <v>433</v>
+      </c>
+      <c r="H16" s="86" t="s">
         <v>231</v>
       </c>
       <c r="I16" s="37" t="s">
         <v>314</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="K16" s="38" t="s">
         <v>267</v>
@@ -3393,7 +3352,7 @@
       <c r="N16" s="41">
         <v>130</v>
       </c>
-      <c r="O16" s="64" t="s">
+      <c r="O16" s="63" t="s">
         <v>344</v>
       </c>
       <c r="P16" s="41">
@@ -3403,7 +3362,7 @@
         <f t="shared" ref="Q16" si="5">P16*N16</f>
         <v>4.3159999999999998</v>
       </c>
-      <c r="R16" s="81"/>
+      <c r="R16" s="76"/>
     </row>
     <row r="17" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
@@ -3411,7 +3370,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="60" t="s">
+      <c r="C17" s="59" t="s">
         <v>317</v>
       </c>
       <c r="D17" s="39" t="s">
@@ -3448,7 +3407,7 @@
       <c r="N17" s="42">
         <v>50</v>
       </c>
-      <c r="O17" s="65" t="s">
+      <c r="O17" s="64" t="s">
         <v>344</v>
       </c>
       <c r="P17" s="42">
@@ -3466,54 +3425,54 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="60" t="s">
+      <c r="C18" s="105" t="s">
         <v>317</v>
       </c>
-      <c r="D18" s="39" t="s">
+      <c r="D18" s="106" t="s">
         <v>357</v>
       </c>
-      <c r="E18" s="40" t="s">
+      <c r="E18" s="107" t="s">
         <v>75</v>
       </c>
-      <c r="F18" s="39" t="s">
+      <c r="F18" s="106" t="s">
         <v>145</v>
       </c>
-      <c r="G18" s="40" t="s">
+      <c r="G18" s="107" t="s">
         <v>188</v>
       </c>
-      <c r="H18" s="39" t="s">
+      <c r="H18" s="106" t="s">
         <v>232</v>
       </c>
-      <c r="I18" s="39" t="s">
+      <c r="I18" s="106" t="s">
         <v>352</v>
       </c>
-      <c r="J18" s="39" t="s">
+      <c r="J18" s="106" t="s">
         <v>351</v>
       </c>
-      <c r="K18" s="40" t="s">
+      <c r="K18" s="107" t="s">
         <v>269</v>
       </c>
-      <c r="L18" s="39">
+      <c r="L18" s="106">
         <v>8</v>
       </c>
-      <c r="M18" s="42">
+      <c r="M18" s="96">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="N18" s="42">
+      <c r="N18" s="96">
         <v>180</v>
       </c>
-      <c r="O18" s="65" t="s">
+      <c r="O18" s="108" t="s">
         <v>344</v>
       </c>
-      <c r="P18" s="42">
+      <c r="P18" s="96">
         <v>3.09E-2</v>
       </c>
-      <c r="Q18" s="42">
+      <c r="Q18" s="96">
         <f t="shared" ref="Q18" si="7">N18*P18</f>
         <v>5.5620000000000003</v>
       </c>
-      <c r="R18" s="42"/>
+      <c r="R18" s="96"/>
     </row>
     <row r="19" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
@@ -3521,50 +3480,50 @@
         <f>ROW(B19) - ROW($B$9)</f>
         <v>10</v>
       </c>
-      <c r="C19" s="61" t="s">
+      <c r="C19" s="109" t="s">
         <v>317</v>
       </c>
-      <c r="D19" s="37" t="s">
+      <c r="D19" s="110" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="38" t="s">
+      <c r="E19" s="111" t="s">
         <v>76</v>
       </c>
-      <c r="F19" s="37" t="s">
+      <c r="F19" s="110" t="s">
         <v>143</v>
       </c>
-      <c r="G19" s="38" t="s">
+      <c r="G19" s="111" t="s">
         <v>189</v>
       </c>
-      <c r="H19" s="37" t="s">
+      <c r="H19" s="110" t="s">
         <v>233</v>
       </c>
-      <c r="I19" s="37" t="s">
+      <c r="I19" s="110" t="s">
         <v>353</v>
       </c>
-      <c r="J19" s="37" t="s">
+      <c r="J19" s="110" t="s">
         <v>354</v>
       </c>
-      <c r="K19" s="38" t="s">
+      <c r="K19" s="111" t="s">
         <v>270</v>
       </c>
-      <c r="L19" s="37">
+      <c r="L19" s="110">
         <v>1</v>
       </c>
-      <c r="M19" s="41">
+      <c r="M19" s="112">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N19" s="41">
+      <c r="N19" s="112">
         <v>50</v>
       </c>
-      <c r="O19" s="64" t="s">
+      <c r="O19" s="113" t="s">
         <v>344</v>
       </c>
-      <c r="P19" s="41">
+      <c r="P19" s="112">
         <v>5.3E-3</v>
       </c>
-      <c r="Q19" s="41">
+      <c r="Q19" s="112">
         <f t="shared" ref="Q19" si="8">P19*N19</f>
         <v>0.26500000000000001</v>
       </c>
@@ -3576,54 +3535,54 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="60" t="s">
+      <c r="C20" s="105" t="s">
         <v>317</v>
       </c>
-      <c r="D20" s="39" t="s">
+      <c r="D20" s="106" t="s">
         <v>11</v>
       </c>
-      <c r="E20" s="40" t="s">
+      <c r="E20" s="107" t="s">
         <v>77</v>
       </c>
-      <c r="F20" s="39" t="s">
+      <c r="F20" s="106" t="s">
         <v>308</v>
       </c>
-      <c r="G20" s="39" t="s">
+      <c r="G20" s="106" t="s">
         <v>146</v>
       </c>
-      <c r="H20" s="39" t="s">
+      <c r="H20" s="106" t="s">
         <v>234</v>
       </c>
-      <c r="I20" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="J20" s="39" t="s">
+      <c r="I20" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J20" s="106" t="s">
         <v>355</v>
       </c>
-      <c r="K20" s="40" t="s">
+      <c r="K20" s="107" t="s">
         <v>261</v>
       </c>
-      <c r="L20" s="39">
+      <c r="L20" s="106">
         <v>1</v>
       </c>
-      <c r="M20" s="42">
+      <c r="M20" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N20" s="42">
+      <c r="N20" s="96">
         <v>22</v>
       </c>
-      <c r="O20" s="65" t="s">
+      <c r="O20" s="108" t="s">
         <v>344</v>
       </c>
-      <c r="P20" s="42">
+      <c r="P20" s="96">
         <v>0.22189999999999999</v>
       </c>
-      <c r="Q20" s="42">
+      <c r="Q20" s="96">
         <f t="shared" ref="Q20" si="9">N20*P20</f>
         <v>4.8818000000000001</v>
       </c>
-      <c r="R20" s="42"/>
+      <c r="R20" s="96"/>
     </row>
     <row r="21" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
@@ -3631,50 +3590,50 @@
         <f>ROW(B21) - ROW($B$9)</f>
         <v>12</v>
       </c>
-      <c r="C21" s="61" t="s">
+      <c r="C21" s="109" t="s">
         <v>317</v>
       </c>
-      <c r="D21" s="37" t="s">
+      <c r="D21" s="110" t="s">
         <v>12</v>
       </c>
-      <c r="E21" s="38" t="s">
+      <c r="E21" s="111" t="s">
         <v>78</v>
       </c>
-      <c r="F21" s="37" t="s">
+      <c r="F21" s="110" t="s">
         <v>144</v>
       </c>
-      <c r="G21" s="38" t="s">
+      <c r="G21" s="111" t="s">
         <v>190</v>
       </c>
-      <c r="H21" s="37" t="s">
+      <c r="H21" s="110" t="s">
         <v>228</v>
       </c>
-      <c r="I21" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="J21" s="37" t="s">
+      <c r="I21" s="110" t="s">
+        <v>314</v>
+      </c>
+      <c r="J21" s="110" t="s">
         <v>356</v>
       </c>
-      <c r="K21" s="38" t="s">
+      <c r="K21" s="111" t="s">
         <v>271</v>
       </c>
-      <c r="L21" s="37">
+      <c r="L21" s="110">
         <v>2</v>
       </c>
-      <c r="M21" s="41">
+      <c r="M21" s="112">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N21" s="41">
+      <c r="N21" s="112">
         <v>50</v>
       </c>
-      <c r="O21" s="64" t="s">
+      <c r="O21" s="113" t="s">
         <v>344</v>
       </c>
-      <c r="P21" s="41">
+      <c r="P21" s="112">
         <v>7.7000000000000002E-3</v>
       </c>
-      <c r="Q21" s="41">
+      <c r="Q21" s="112">
         <f t="shared" ref="Q21" si="10">P21*N21</f>
         <v>0.38500000000000001</v>
       </c>
@@ -3686,7 +3645,7 @@
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="61" t="s">
+      <c r="C22" s="60" t="s">
         <v>317</v>
       </c>
       <c r="D22" s="37" t="s">
@@ -3723,7 +3682,7 @@
       <c r="N22" s="41">
         <v>40</v>
       </c>
-      <c r="O22" s="64" t="s">
+      <c r="O22" s="63" t="s">
         <v>344</v>
       </c>
       <c r="P22" s="41">
@@ -3741,11 +3700,11 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="60" t="s">
+      <c r="C23" s="59" t="s">
         <v>317</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E23" s="40" t="s">
         <v>80</v>
@@ -3778,7 +3737,7 @@
       <c r="N23" s="42">
         <v>40</v>
       </c>
-      <c r="O23" s="65" t="s">
+      <c r="O23" s="64" t="s">
         <v>344</v>
       </c>
       <c r="P23" s="42">
@@ -3788,7 +3747,7 @@
         <f t="shared" ref="Q23" si="12">N23*P23</f>
         <v>0.7679999999999999</v>
       </c>
-      <c r="R23" s="84"/>
+      <c r="R23" s="77"/>
     </row>
     <row r="24" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
@@ -3796,7 +3755,7 @@
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="61" t="s">
+      <c r="C24" s="60" t="s">
         <v>317</v>
       </c>
       <c r="D24" s="37" t="s">
@@ -3808,7 +3767,7 @@
       <c r="F24" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="G24" s="66">
+      <c r="G24" s="65">
         <v>885012205080</v>
       </c>
       <c r="H24" s="37" t="s">
@@ -3833,7 +3792,7 @@
       <c r="N24" s="41">
         <v>50</v>
       </c>
-      <c r="O24" s="64" t="s">
+      <c r="O24" s="63" t="s">
         <v>344</v>
       </c>
       <c r="P24" s="41">
@@ -3851,7 +3810,7 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="60" t="s">
+      <c r="C25" s="59" t="s">
         <v>317</v>
       </c>
       <c r="D25" s="39" t="s">
@@ -3888,7 +3847,7 @@
       <c r="N25" s="42">
         <v>100</v>
       </c>
-      <c r="O25" s="65" t="s">
+      <c r="O25" s="64" t="s">
         <v>344</v>
       </c>
       <c r="P25" s="42">
@@ -3906,54 +3865,54 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="60" t="s">
+      <c r="C26" s="105" t="s">
         <v>317</v>
       </c>
-      <c r="D26" s="39" t="s">
+      <c r="D26" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="E26" s="86" t="s">
-        <v>433</v>
-      </c>
-      <c r="F26" s="39" t="s">
+      <c r="E26" s="114" t="s">
+        <v>431</v>
+      </c>
+      <c r="F26" s="106" t="s">
         <v>143</v>
       </c>
-      <c r="G26" s="87" t="s">
-        <v>434</v>
-      </c>
-      <c r="H26" s="88" t="s">
-        <v>435</v>
-      </c>
-      <c r="I26" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="J26" s="39" t="s">
-        <v>436</v>
-      </c>
-      <c r="K26" s="102" t="s">
-        <v>455</v>
-      </c>
-      <c r="L26" s="39">
+      <c r="G26" s="114" t="s">
+        <v>459</v>
+      </c>
+      <c r="H26" s="115" t="s">
+        <v>249</v>
+      </c>
+      <c r="I26" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J26" s="106" t="s">
+        <v>432</v>
+      </c>
+      <c r="K26" s="114" t="s">
+        <v>446</v>
+      </c>
+      <c r="L26" s="106">
         <v>1</v>
       </c>
-      <c r="M26" s="42">
+      <c r="M26" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N26" s="42">
+      <c r="N26" s="96">
         <v>100</v>
       </c>
-      <c r="O26" s="65" t="s">
+      <c r="O26" s="108" t="s">
         <v>344</v>
       </c>
-      <c r="P26" s="42">
+      <c r="P26" s="96">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="Q26" s="42">
+      <c r="Q26" s="96">
         <f t="shared" ref="Q26" si="15">N26*P26</f>
         <v>0.33999999999999997</v>
       </c>
-      <c r="R26" s="84"/>
+      <c r="R26" s="76"/>
     </row>
     <row r="27" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
@@ -3961,54 +3920,54 @@
         <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
-      <c r="C27" s="61" t="s">
+      <c r="C27" s="109" t="s">
         <v>317</v>
       </c>
-      <c r="D27" s="37" t="s">
-        <v>454</v>
-      </c>
-      <c r="E27" s="38" t="s">
+      <c r="D27" s="110" t="s">
+        <v>445</v>
+      </c>
+      <c r="E27" s="111" t="s">
         <v>83</v>
       </c>
-      <c r="F27" s="37" t="s">
+      <c r="F27" s="110" t="s">
         <v>147</v>
       </c>
-      <c r="G27" s="38" t="s">
+      <c r="G27" s="111" t="s">
         <v>194</v>
       </c>
-      <c r="H27" s="37" t="s">
+      <c r="H27" s="110" t="s">
         <v>231</v>
       </c>
-      <c r="I27" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="J27" s="37" t="s">
+      <c r="I27" s="110" t="s">
+        <v>314</v>
+      </c>
+      <c r="J27" s="110" t="s">
         <v>363</v>
       </c>
-      <c r="K27" s="38" t="s">
+      <c r="K27" s="111" t="s">
         <v>275</v>
       </c>
-      <c r="L27" s="37">
+      <c r="L27" s="110">
         <v>1</v>
       </c>
-      <c r="M27" s="41">
+      <c r="M27" s="112">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N27" s="41">
+      <c r="N27" s="112">
         <v>30</v>
       </c>
-      <c r="O27" s="64" t="s">
+      <c r="O27" s="113" t="s">
         <v>344</v>
       </c>
-      <c r="P27" s="41">
+      <c r="P27" s="112">
         <v>0.2525</v>
       </c>
-      <c r="Q27" s="41">
+      <c r="Q27" s="112">
         <f t="shared" ref="Q27" si="16">P27*N27</f>
         <v>7.5750000000000002</v>
       </c>
-      <c r="R27" s="85"/>
+      <c r="R27" s="78"/>
     </row>
     <row r="28" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
@@ -4016,7 +3975,7 @@
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="61" t="s">
+      <c r="C28" s="60" t="s">
         <v>317</v>
       </c>
       <c r="D28" s="37" t="s">
@@ -4053,7 +4012,7 @@
       <c r="N28" s="41">
         <v>22</v>
       </c>
-      <c r="O28" s="64" t="s">
+      <c r="O28" s="63" t="s">
         <v>344</v>
       </c>
       <c r="P28" s="41">
@@ -4071,7 +4030,7 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="60" t="s">
+      <c r="C29" s="59" t="s">
         <v>317</v>
       </c>
       <c r="D29" s="39" t="s">
@@ -4108,7 +4067,7 @@
       <c r="N29" s="42">
         <v>21</v>
       </c>
-      <c r="O29" s="65" t="s">
+      <c r="O29" s="64" t="s">
         <v>344</v>
       </c>
       <c r="P29" s="42">
@@ -4126,7 +4085,7 @@
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="61" t="s">
+      <c r="C30" s="60" t="s">
         <v>317</v>
       </c>
       <c r="D30" s="37" t="s">
@@ -4163,7 +4122,7 @@
       <c r="N30" s="41">
         <v>100</v>
       </c>
-      <c r="O30" s="64" t="s">
+      <c r="O30" s="63" t="s">
         <v>344</v>
       </c>
       <c r="P30" s="41">
@@ -4181,50 +4140,50 @@
         <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
-      <c r="C31" s="61" t="s">
+      <c r="C31" s="109" t="s">
         <v>317</v>
       </c>
-      <c r="D31" s="37" t="s">
+      <c r="D31" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="38" t="s">
+      <c r="E31" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="F31" s="37" t="s">
+      <c r="F31" s="110" t="s">
         <v>143</v>
       </c>
-      <c r="G31" s="38" t="s">
+      <c r="G31" s="111" t="s">
         <v>197</v>
       </c>
-      <c r="H31" s="37" t="s">
+      <c r="H31" s="110" t="s">
         <v>228</v>
       </c>
-      <c r="I31" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="J31" s="37" t="s">
+      <c r="I31" s="110" t="s">
+        <v>314</v>
+      </c>
+      <c r="J31" s="110" t="s">
         <v>367</v>
       </c>
-      <c r="K31" s="38" t="s">
+      <c r="K31" s="111" t="s">
         <v>279</v>
       </c>
-      <c r="L31" s="37">
+      <c r="L31" s="110">
         <v>4</v>
       </c>
-      <c r="M31" s="41">
+      <c r="M31" s="112">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N31" s="41">
+      <c r="N31" s="112">
         <v>100</v>
       </c>
-      <c r="O31" s="64" t="s">
+      <c r="O31" s="113" t="s">
         <v>344</v>
       </c>
-      <c r="P31" s="41">
+      <c r="P31" s="112">
         <v>5.4999999999999997E-3</v>
       </c>
-      <c r="Q31" s="41">
+      <c r="Q31" s="112">
         <f t="shared" ref="Q31" si="20">P31*N31</f>
         <v>0.54999999999999993</v>
       </c>
@@ -4236,54 +4195,54 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="60" t="s">
+      <c r="C32" s="105" t="s">
         <v>318</v>
       </c>
-      <c r="D32" s="39" t="s">
+      <c r="D32" s="106" t="s">
         <v>21</v>
       </c>
-      <c r="E32" s="40" t="s">
+      <c r="E32" s="107" t="s">
         <v>88</v>
       </c>
-      <c r="F32" s="39" t="s">
+      <c r="F32" s="106" t="s">
         <v>308</v>
       </c>
-      <c r="G32" s="40" t="s">
+      <c r="G32" s="107" t="s">
         <v>150</v>
       </c>
-      <c r="H32" s="39" t="s">
+      <c r="H32" s="106" t="s">
         <v>237</v>
       </c>
-      <c r="I32" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="J32" s="39" t="s">
+      <c r="I32" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J32" s="106" t="s">
         <v>368</v>
       </c>
-      <c r="K32" s="40" t="s">
-        <v>314</v>
-      </c>
-      <c r="L32" s="39">
+      <c r="K32" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="L32" s="106">
         <v>1</v>
       </c>
-      <c r="M32" s="42">
+      <c r="M32" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N32" s="42">
+      <c r="N32" s="96">
         <v>30</v>
       </c>
-      <c r="O32" s="65" t="s">
+      <c r="O32" s="108" t="s">
         <v>344</v>
       </c>
-      <c r="P32" s="42">
+      <c r="P32" s="96">
         <v>4.87E-2</v>
       </c>
-      <c r="Q32" s="42">
+      <c r="Q32" s="96">
         <f t="shared" ref="Q32" si="21">N32*P32</f>
         <v>1.4610000000000001</v>
       </c>
-      <c r="R32" s="42"/>
+      <c r="R32" s="96"/>
     </row>
     <row r="33" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1"/>
@@ -4291,50 +4250,50 @@
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
-      <c r="C33" s="61" t="s">
+      <c r="C33" s="109" t="s">
         <v>318</v>
       </c>
-      <c r="D33" s="37" t="s">
+      <c r="D33" s="110" t="s">
         <v>22</v>
       </c>
-      <c r="E33" s="38" t="s">
+      <c r="E33" s="111" t="s">
         <v>89</v>
       </c>
-      <c r="F33" s="37" t="s">
+      <c r="F33" s="110" t="s">
         <v>151</v>
       </c>
-      <c r="G33" s="38" t="s">
+      <c r="G33" s="111" t="s">
         <v>280</v>
       </c>
-      <c r="H33" s="37" t="s">
+      <c r="H33" s="110" t="s">
         <v>238</v>
       </c>
-      <c r="I33" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="J33" s="37" t="s">
+      <c r="I33" s="110" t="s">
+        <v>314</v>
+      </c>
+      <c r="J33" s="110" t="s">
         <v>369</v>
       </c>
-      <c r="K33" s="38" t="s">
-        <v>314</v>
-      </c>
-      <c r="L33" s="37">
+      <c r="K33" s="111" t="s">
+        <v>314</v>
+      </c>
+      <c r="L33" s="110">
         <v>1</v>
       </c>
-      <c r="M33" s="41">
+      <c r="M33" s="112">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N33" s="41">
+      <c r="N33" s="112">
         <v>30</v>
       </c>
-      <c r="O33" s="64" t="s">
+      <c r="O33" s="113" t="s">
         <v>344</v>
       </c>
-      <c r="P33" s="41">
+      <c r="P33" s="112">
         <v>7.4300000000000005E-2</v>
       </c>
-      <c r="Q33" s="41">
+      <c r="Q33" s="112">
         <f t="shared" ref="Q33" si="22">P33*N33</f>
         <v>2.2290000000000001</v>
       </c>
@@ -4346,54 +4305,54 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="60" t="s">
+      <c r="C34" s="105" t="s">
         <v>318</v>
       </c>
-      <c r="D34" s="39" t="s">
-        <v>444</v>
-      </c>
-      <c r="E34" s="40" t="s">
+      <c r="D34" s="106" t="s">
+        <v>464</v>
+      </c>
+      <c r="E34" s="107" t="s">
         <v>90</v>
       </c>
-      <c r="F34" s="39" t="s">
+      <c r="F34" s="106" t="s">
         <v>151</v>
       </c>
-      <c r="G34" s="40" t="s">
+      <c r="G34" s="107" t="s">
         <v>281</v>
       </c>
-      <c r="H34" s="39" t="s">
+      <c r="H34" s="106" t="s">
         <v>238</v>
       </c>
-      <c r="I34" s="39" t="s">
+      <c r="I34" s="106" t="s">
         <v>281</v>
       </c>
-      <c r="J34" s="39" t="s">
+      <c r="J34" s="106" t="s">
         <v>370</v>
       </c>
-      <c r="K34" s="40" t="s">
-        <v>314</v>
-      </c>
-      <c r="L34" s="39">
+      <c r="K34" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="L34" s="106">
         <v>2</v>
       </c>
-      <c r="M34" s="42">
+      <c r="M34" s="96">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N34" s="42">
+      <c r="N34" s="96">
         <v>60</v>
       </c>
-      <c r="O34" s="65" t="s">
+      <c r="O34" s="108" t="s">
         <v>344</v>
       </c>
-      <c r="P34" s="42">
+      <c r="P34" s="96">
         <v>2.8899999999999999E-2</v>
       </c>
-      <c r="Q34" s="42">
+      <c r="Q34" s="96">
         <f t="shared" ref="Q34" si="23">N34*P34</f>
         <v>1.734</v>
       </c>
-      <c r="R34" s="89"/>
+      <c r="R34" s="78"/>
     </row>
     <row r="35" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1"/>
@@ -4401,55 +4360,55 @@
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="103" t="s">
+      <c r="C35" s="89" t="s">
         <v>318</v>
       </c>
-      <c r="D35" s="104" t="s">
-        <v>456</v>
-      </c>
-      <c r="E35" s="105" t="s">
+      <c r="D35" s="90" t="s">
+        <v>447</v>
+      </c>
+      <c r="E35" s="91" t="s">
         <v>91</v>
       </c>
-      <c r="F35" s="104" t="s">
+      <c r="F35" s="90" t="s">
         <v>152</v>
       </c>
-      <c r="G35" s="105" t="s">
+      <c r="G35" s="91" t="s">
         <v>198</v>
       </c>
-      <c r="H35" s="104" t="s">
+      <c r="H35" s="90" t="s">
         <v>239</v>
       </c>
-      <c r="I35" s="104" t="s">
+      <c r="I35" s="90" t="s">
         <v>371</v>
       </c>
-      <c r="J35" s="104" t="s">
+      <c r="J35" s="90" t="s">
         <v>372</v>
       </c>
-      <c r="K35" s="105" t="s">
-        <v>314</v>
-      </c>
-      <c r="L35" s="106">
+      <c r="K35" s="91" t="s">
+        <v>314</v>
+      </c>
+      <c r="L35" s="92">
         <v>8</v>
       </c>
-      <c r="M35" s="107">
+      <c r="M35" s="93">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="N35" s="108">
+      <c r="N35" s="94">
         <v>170</v>
       </c>
-      <c r="O35" s="109" t="s">
+      <c r="O35" s="95" t="s">
         <v>344</v>
       </c>
-      <c r="P35" s="107">
+      <c r="P35" s="93">
         <v>0.12590000000000001</v>
       </c>
-      <c r="Q35" s="107">
+      <c r="Q35" s="93">
         <f t="shared" ref="Q35" si="24">P35*N35</f>
         <v>21.403000000000002</v>
       </c>
-      <c r="R35" s="94" t="s">
-        <v>457</v>
+      <c r="R35" s="84" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="36" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4458,54 +4417,54 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="60" t="s">
+      <c r="C36" s="105" t="s">
         <v>320</v>
       </c>
-      <c r="D36" s="39" t="s">
+      <c r="D36" s="106" t="s">
         <v>23</v>
       </c>
-      <c r="E36" s="40" t="s">
+      <c r="E36" s="107" t="s">
         <v>92</v>
       </c>
-      <c r="F36" s="39" t="s">
+      <c r="F36" s="106" t="s">
         <v>308</v>
       </c>
-      <c r="G36" s="40" t="s">
+      <c r="G36" s="107" t="s">
         <v>153</v>
       </c>
-      <c r="H36" s="39" t="s">
+      <c r="H36" s="106" t="s">
         <v>240</v>
       </c>
-      <c r="I36" s="39" t="s">
+      <c r="I36" s="106" t="s">
         <v>373</v>
       </c>
-      <c r="J36" s="39" t="s">
+      <c r="J36" s="106" t="s">
         <v>374</v>
       </c>
-      <c r="K36" s="40" t="s">
-        <v>314</v>
-      </c>
-      <c r="L36" s="39">
+      <c r="K36" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="L36" s="106">
         <v>1</v>
       </c>
-      <c r="M36" s="42">
+      <c r="M36" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N36" s="42">
+      <c r="N36" s="96">
         <v>30</v>
       </c>
-      <c r="O36" s="65" t="s">
+      <c r="O36" s="108" t="s">
         <v>344</v>
       </c>
-      <c r="P36" s="42">
+      <c r="P36" s="96">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="Q36" s="42">
+      <c r="Q36" s="96">
         <f t="shared" ref="Q36" si="25">N36*P36</f>
         <v>1.68</v>
       </c>
-      <c r="R36" s="42"/>
+      <c r="R36" s="96"/>
     </row>
     <row r="37" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1"/>
@@ -4513,50 +4472,50 @@
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
-      <c r="C37" s="61" t="s">
+      <c r="C37" s="109" t="s">
         <v>319</v>
       </c>
-      <c r="D37" s="37" t="s">
+      <c r="D37" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="E37" s="38" t="s">
+      <c r="E37" s="111" t="s">
         <v>93</v>
       </c>
-      <c r="F37" s="37" t="s">
+      <c r="F37" s="110" t="s">
         <v>309</v>
       </c>
-      <c r="G37" s="38" t="s">
+      <c r="G37" s="111" t="s">
         <v>154</v>
       </c>
-      <c r="H37" s="37" t="s">
+      <c r="H37" s="110" t="s">
         <v>233</v>
       </c>
-      <c r="I37" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="J37" s="37" t="s">
+      <c r="I37" s="110" t="s">
+        <v>314</v>
+      </c>
+      <c r="J37" s="110" t="s">
         <v>375</v>
       </c>
-      <c r="K37" s="38" t="s">
-        <v>314</v>
-      </c>
-      <c r="L37" s="37">
+      <c r="K37" s="111" t="s">
+        <v>314</v>
+      </c>
+      <c r="L37" s="110">
         <v>4</v>
       </c>
-      <c r="M37" s="41">
+      <c r="M37" s="112">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N37" s="41">
+      <c r="N37" s="112">
         <v>100</v>
       </c>
-      <c r="O37" s="64" t="s">
+      <c r="O37" s="113" t="s">
         <v>344</v>
       </c>
-      <c r="P37" s="41">
+      <c r="P37" s="112">
         <v>2.9499999999999998E-2</v>
       </c>
-      <c r="Q37" s="41">
+      <c r="Q37" s="112">
         <f t="shared" ref="Q37" si="26">P37*N37</f>
         <v>2.9499999999999997</v>
       </c>
@@ -4568,54 +4527,54 @@
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="60" t="s">
+      <c r="C38" s="105" t="s">
         <v>321</v>
       </c>
-      <c r="D38" s="39" t="s">
+      <c r="D38" s="106" t="s">
         <v>25</v>
       </c>
-      <c r="E38" s="40" t="s">
+      <c r="E38" s="107" t="s">
         <v>94</v>
       </c>
-      <c r="F38" s="39" t="s">
+      <c r="F38" s="106" t="s">
         <v>308</v>
       </c>
-      <c r="G38" s="40" t="s">
+      <c r="G38" s="107" t="s">
         <v>155</v>
       </c>
-      <c r="H38" s="39" t="s">
+      <c r="H38" s="106" t="s">
         <v>241</v>
       </c>
-      <c r="I38" s="39" t="s">
+      <c r="I38" s="106" t="s">
         <v>376</v>
       </c>
-      <c r="J38" s="39" t="s">
+      <c r="J38" s="106" t="s">
         <v>377</v>
       </c>
-      <c r="K38" s="40" t="s">
-        <v>314</v>
-      </c>
-      <c r="L38" s="39">
+      <c r="K38" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="L38" s="106">
         <v>1</v>
       </c>
-      <c r="M38" s="42">
+      <c r="M38" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N38" s="42">
+      <c r="N38" s="96">
         <v>21</v>
       </c>
-      <c r="O38" s="65" t="s">
+      <c r="O38" s="108" t="s">
         <v>344</v>
       </c>
-      <c r="P38" s="42">
+      <c r="P38" s="96">
         <v>0.53559999999999997</v>
       </c>
-      <c r="Q38" s="42">
+      <c r="Q38" s="96">
         <f t="shared" ref="Q38" si="27">N38*P38</f>
         <v>11.247599999999998</v>
       </c>
-      <c r="R38" s="89"/>
+      <c r="R38" s="78"/>
     </row>
     <row r="39" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1"/>
@@ -4623,54 +4582,54 @@
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="61" t="s">
+      <c r="C39" s="109" t="s">
         <v>321</v>
       </c>
-      <c r="D39" s="37" t="s">
+      <c r="D39" s="110" t="s">
         <v>26</v>
       </c>
-      <c r="E39" s="38" t="s">
+      <c r="E39" s="111" t="s">
         <v>95</v>
       </c>
-      <c r="F39" s="37" t="s">
+      <c r="F39" s="110" t="s">
         <v>308</v>
       </c>
-      <c r="G39" s="38" t="s">
+      <c r="G39" s="111" t="s">
         <v>156</v>
       </c>
-      <c r="H39" s="37" t="s">
+      <c r="H39" s="110" t="s">
         <v>242</v>
       </c>
-      <c r="I39" s="37" t="s">
+      <c r="I39" s="110" t="s">
         <v>378</v>
       </c>
-      <c r="J39" s="37" t="s">
+      <c r="J39" s="110" t="s">
         <v>379</v>
       </c>
-      <c r="K39" s="38" t="s">
-        <v>314</v>
-      </c>
-      <c r="L39" s="37">
+      <c r="K39" s="111" t="s">
+        <v>314</v>
+      </c>
+      <c r="L39" s="110">
         <v>2</v>
       </c>
-      <c r="M39" s="41">
+      <c r="M39" s="112">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N39" s="41">
+      <c r="N39" s="112">
         <v>42</v>
       </c>
-      <c r="O39" s="64" t="s">
+      <c r="O39" s="113" t="s">
         <v>344</v>
       </c>
-      <c r="P39" s="41">
+      <c r="P39" s="112">
         <v>0.65639999999999998</v>
       </c>
-      <c r="Q39" s="41">
+      <c r="Q39" s="112">
         <f t="shared" ref="Q39" si="28">P39*N39</f>
         <v>27.5688</v>
       </c>
-      <c r="R39" s="85"/>
+      <c r="R39" s="78"/>
     </row>
     <row r="40" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1"/>
@@ -4678,54 +4637,54 @@
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="60" t="s">
+      <c r="C40" s="105" t="s">
         <v>322</v>
       </c>
-      <c r="D40" s="39" t="s">
+      <c r="D40" s="106" t="s">
         <v>27</v>
       </c>
-      <c r="E40" s="40" t="s">
+      <c r="E40" s="107" t="s">
         <v>96</v>
       </c>
-      <c r="F40" s="39" t="s">
+      <c r="F40" s="106" t="s">
         <v>308</v>
       </c>
-      <c r="G40" s="40" t="s">
+      <c r="G40" s="107" t="s">
         <v>157</v>
       </c>
-      <c r="H40" s="39" t="s">
+      <c r="H40" s="106" t="s">
         <v>243</v>
       </c>
-      <c r="I40" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="J40" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="K40" s="40" t="s">
-        <v>314</v>
-      </c>
-      <c r="L40" s="39">
+      <c r="I40" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J40" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="K40" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="L40" s="106">
         <v>1</v>
       </c>
-      <c r="M40" s="42">
+      <c r="M40" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N40" s="42">
+      <c r="N40" s="96">
         <v>21</v>
       </c>
-      <c r="O40" s="65" t="s">
+      <c r="O40" s="108" t="s">
         <v>380</v>
       </c>
-      <c r="P40" s="42">
+      <c r="P40" s="96">
         <v>1.2</v>
       </c>
-      <c r="Q40" s="42">
+      <c r="Q40" s="96">
         <f t="shared" ref="Q40" si="29">N40*P40</f>
         <v>25.2</v>
       </c>
-      <c r="R40" s="42"/>
+      <c r="R40" s="96"/>
     </row>
     <row r="41" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1"/>
@@ -4733,50 +4692,50 @@
         <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
-      <c r="C41" s="61" t="s">
+      <c r="C41" s="109" t="s">
         <v>322</v>
       </c>
-      <c r="D41" s="37" t="s">
+      <c r="D41" s="110" t="s">
         <v>28</v>
       </c>
-      <c r="E41" s="38" t="s">
+      <c r="E41" s="111" t="s">
         <v>97</v>
       </c>
-      <c r="F41" s="37" t="s">
+      <c r="F41" s="110" t="s">
         <v>308</v>
       </c>
-      <c r="G41" s="38" t="s">
+      <c r="G41" s="111" t="s">
         <v>158</v>
       </c>
-      <c r="H41" s="37" t="s">
+      <c r="H41" s="110" t="s">
         <v>244</v>
       </c>
-      <c r="I41" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="J41" s="37" t="s">
+      <c r="I41" s="110" t="s">
+        <v>314</v>
+      </c>
+      <c r="J41" s="110" t="s">
         <v>381</v>
       </c>
-      <c r="K41" s="38" t="s">
-        <v>314</v>
-      </c>
-      <c r="L41" s="37">
+      <c r="K41" s="111" t="s">
+        <v>314</v>
+      </c>
+      <c r="L41" s="110">
         <v>1</v>
       </c>
-      <c r="M41" s="41">
+      <c r="M41" s="112">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N41" s="41">
+      <c r="N41" s="112">
         <v>25</v>
       </c>
-      <c r="O41" s="64" t="s">
+      <c r="O41" s="113" t="s">
         <v>344</v>
       </c>
-      <c r="P41" s="41">
+      <c r="P41" s="112">
         <v>9.2200000000000004E-2</v>
       </c>
-      <c r="Q41" s="41">
+      <c r="Q41" s="112">
         <f t="shared" ref="Q41" si="30">P41*N41</f>
         <v>2.3050000000000002</v>
       </c>
@@ -4788,54 +4747,54 @@
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="60" t="s">
+      <c r="C42" s="105" t="s">
         <v>319</v>
       </c>
-      <c r="D42" s="39" t="s">
+      <c r="D42" s="106" t="s">
         <v>29</v>
       </c>
-      <c r="E42" s="40" t="s">
+      <c r="E42" s="107" t="s">
         <v>98</v>
       </c>
-      <c r="F42" s="39" t="s">
+      <c r="F42" s="106" t="s">
         <v>308</v>
       </c>
-      <c r="G42" s="40" t="s">
+      <c r="G42" s="107" t="s">
         <v>159</v>
       </c>
-      <c r="H42" s="39" t="s">
+      <c r="H42" s="106" t="s">
         <v>233</v>
       </c>
-      <c r="I42" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="J42" s="39" t="s">
+      <c r="I42" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J42" s="106" t="s">
         <v>382</v>
       </c>
-      <c r="K42" s="40" t="s">
+      <c r="K42" s="107" t="s">
         <v>282</v>
       </c>
-      <c r="L42" s="39">
+      <c r="L42" s="106">
         <v>1</v>
       </c>
-      <c r="M42" s="42">
+      <c r="M42" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N42" s="42">
+      <c r="N42" s="96">
         <v>21</v>
       </c>
-      <c r="O42" s="65" t="s">
+      <c r="O42" s="108" t="s">
         <v>344</v>
       </c>
-      <c r="P42" s="42">
+      <c r="P42" s="96">
         <v>0.45629999999999998</v>
       </c>
-      <c r="Q42" s="42">
+      <c r="Q42" s="96">
         <f t="shared" ref="Q42" si="31">N42*P42</f>
         <v>9.5823</v>
       </c>
-      <c r="R42" s="42"/>
+      <c r="R42" s="96"/>
     </row>
     <row r="43" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
@@ -4843,54 +4802,54 @@
         <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
       </c>
-      <c r="C43" s="61" t="s">
+      <c r="C43" s="109" t="s">
         <v>319</v>
       </c>
-      <c r="D43" s="37" t="s">
+      <c r="D43" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="E43" s="38" t="s">
-        <v>460</v>
-      </c>
-      <c r="F43" s="37" t="s">
+      <c r="E43" s="111" t="s">
+        <v>451</v>
+      </c>
+      <c r="F43" s="110" t="s">
         <v>308</v>
       </c>
-      <c r="G43" s="38" t="s">
-        <v>459</v>
-      </c>
-      <c r="H43" s="37" t="s">
-        <v>442</v>
-      </c>
-      <c r="I43" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="J43" s="37" t="s">
-        <v>443</v>
-      </c>
-      <c r="K43" s="38" t="s">
-        <v>458</v>
-      </c>
-      <c r="L43" s="37">
+      <c r="G43" s="111" t="s">
+        <v>450</v>
+      </c>
+      <c r="H43" s="110" t="s">
+        <v>437</v>
+      </c>
+      <c r="I43" s="110" t="s">
+        <v>314</v>
+      </c>
+      <c r="J43" s="110" t="s">
+        <v>438</v>
+      </c>
+      <c r="K43" s="111" t="s">
+        <v>449</v>
+      </c>
+      <c r="L43" s="110">
         <v>1</v>
       </c>
-      <c r="M43" s="41">
+      <c r="M43" s="112">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N43" s="41">
+      <c r="N43" s="112">
         <v>25</v>
       </c>
-      <c r="O43" s="64" t="s">
+      <c r="O43" s="113" t="s">
         <v>344</v>
       </c>
-      <c r="P43" s="41">
+      <c r="P43" s="112">
         <v>0.1012</v>
       </c>
-      <c r="Q43" s="41">
+      <c r="Q43" s="112">
         <f t="shared" ref="Q43" si="32">P43*N43</f>
         <v>2.5299999999999998</v>
       </c>
-      <c r="R43" s="81"/>
+      <c r="R43" s="77"/>
     </row>
     <row r="44" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
@@ -4898,54 +4857,54 @@
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C44" s="60" t="s">
+      <c r="C44" s="105" t="s">
         <v>323</v>
       </c>
-      <c r="D44" s="39" t="s">
+      <c r="D44" s="106" t="s">
         <v>31</v>
       </c>
-      <c r="E44" s="40" t="s">
+      <c r="E44" s="107" t="s">
         <v>99</v>
       </c>
-      <c r="F44" s="39" t="s">
+      <c r="F44" s="106" t="s">
         <v>308</v>
       </c>
-      <c r="G44" s="40" t="s">
+      <c r="G44" s="107" t="s">
         <v>160</v>
       </c>
-      <c r="H44" s="39" t="s">
+      <c r="H44" s="106" t="s">
         <v>245</v>
       </c>
-      <c r="I44" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="J44" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="K44" s="40" t="s">
-        <v>314</v>
-      </c>
-      <c r="L44" s="39">
+      <c r="I44" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J44" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="K44" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="L44" s="106">
         <v>1</v>
       </c>
-      <c r="M44" s="42">
+      <c r="M44" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N44" s="42">
+      <c r="N44" s="96">
         <v>30</v>
       </c>
-      <c r="O44" s="65" t="s">
+      <c r="O44" s="108" t="s">
         <v>383</v>
       </c>
-      <c r="P44" s="42">
+      <c r="P44" s="96">
         <v>0.156</v>
       </c>
-      <c r="Q44" s="42">
+      <c r="Q44" s="96">
         <f t="shared" ref="Q44" si="33">N44*P44</f>
         <v>4.68</v>
       </c>
-      <c r="R44" s="42"/>
+      <c r="R44" s="96"/>
     </row>
     <row r="45" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
@@ -4953,109 +4912,109 @@
         <f>ROW(B45) - ROW($B$9)</f>
         <v>36</v>
       </c>
-      <c r="C45" s="61" t="s">
+      <c r="C45" s="109" t="s">
         <v>323</v>
       </c>
-      <c r="D45" s="37" t="s">
+      <c r="D45" s="110" t="s">
         <v>32</v>
       </c>
-      <c r="E45" s="38" t="s">
+      <c r="E45" s="111" t="s">
         <v>100</v>
       </c>
-      <c r="F45" s="37" t="s">
+      <c r="F45" s="110" t="s">
         <v>161</v>
       </c>
-      <c r="G45" s="38" t="s">
+      <c r="G45" s="111" t="s">
         <v>199</v>
       </c>
-      <c r="H45" s="37" t="s">
+      <c r="H45" s="110" t="s">
         <v>246</v>
       </c>
-      <c r="I45" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="J45" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="K45" s="38" t="s">
-        <v>314</v>
-      </c>
-      <c r="L45" s="37">
+      <c r="I45" s="110" t="s">
+        <v>314</v>
+      </c>
+      <c r="J45" s="110" t="s">
+        <v>314</v>
+      </c>
+      <c r="K45" s="111" t="s">
+        <v>314</v>
+      </c>
+      <c r="L45" s="110">
         <v>1</v>
       </c>
-      <c r="M45" s="41">
+      <c r="M45" s="112">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N45" s="41">
+      <c r="N45" s="112">
         <v>30</v>
       </c>
-      <c r="O45" s="64" t="s">
+      <c r="O45" s="113" t="s">
         <v>384</v>
       </c>
-      <c r="P45" s="41">
+      <c r="P45" s="112">
         <v>0.08</v>
       </c>
-      <c r="Q45" s="41">
+      <c r="Q45" s="112">
         <f t="shared" ref="Q45" si="34">P45*N45</f>
         <v>2.4</v>
       </c>
-      <c r="R45" s="41"/>
+      <c r="R45" s="112"/>
     </row>
     <row r="46" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1"/>
-      <c r="B46" s="53">
+      <c r="B46" s="116">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C46" s="60" t="s">
+      <c r="C46" s="105" t="s">
         <v>321</v>
       </c>
-      <c r="D46" s="39" t="s">
+      <c r="D46" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="E46" s="40" t="s">
+      <c r="E46" s="107" t="s">
         <v>101</v>
       </c>
-      <c r="F46" s="39" t="s">
+      <c r="F46" s="106" t="s">
         <v>308</v>
       </c>
-      <c r="G46" s="40" t="s">
+      <c r="G46" s="107" t="s">
         <v>162</v>
       </c>
-      <c r="H46" s="39" t="s">
+      <c r="H46" s="106" t="s">
         <v>247</v>
       </c>
-      <c r="I46" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="J46" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="K46" s="40" t="s">
-        <v>314</v>
-      </c>
-      <c r="L46" s="39">
+      <c r="I46" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J46" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="K46" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="L46" s="106">
         <v>2</v>
       </c>
-      <c r="M46" s="42">
+      <c r="M46" s="96">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N46" s="42">
+      <c r="N46" s="96">
         <v>50</v>
       </c>
-      <c r="O46" s="65" t="s">
+      <c r="O46" s="108" t="s">
         <v>380</v>
       </c>
-      <c r="P46" s="42">
+      <c r="P46" s="96">
         <v>1.5</v>
       </c>
-      <c r="Q46" s="42">
+      <c r="Q46" s="96">
         <f t="shared" ref="Q46" si="35">N46*P46</f>
         <v>75</v>
       </c>
-      <c r="R46" s="42"/>
+      <c r="R46" s="96"/>
     </row>
     <row r="47" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
@@ -5063,47 +5022,47 @@
         <f>ROW(B47) - ROW($B$9)</f>
         <v>38</v>
       </c>
-      <c r="C47" s="67" t="s">
+      <c r="C47" s="97" t="s">
         <v>283</v>
       </c>
-      <c r="D47" s="68" t="s">
+      <c r="D47" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="E47" s="69" t="s">
+      <c r="E47" s="99" t="s">
         <v>102</v>
       </c>
-      <c r="F47" s="68" t="s">
+      <c r="F47" s="98" t="s">
         <v>163</v>
       </c>
-      <c r="G47" s="69" t="s">
-        <v>314</v>
-      </c>
-      <c r="H47" s="68" t="s">
-        <v>314</v>
-      </c>
-      <c r="I47" s="68"/>
-      <c r="J47" s="68"/>
-      <c r="K47" s="69" t="s">
-        <v>314</v>
-      </c>
-      <c r="L47" s="68">
+      <c r="G47" s="99" t="s">
+        <v>314</v>
+      </c>
+      <c r="H47" s="98" t="s">
+        <v>314</v>
+      </c>
+      <c r="I47" s="98"/>
+      <c r="J47" s="98"/>
+      <c r="K47" s="99" t="s">
+        <v>314</v>
+      </c>
+      <c r="L47" s="98">
         <v>4</v>
       </c>
-      <c r="M47" s="70">
+      <c r="M47" s="66">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N47" s="70">
+      <c r="N47" s="66">
         <f t="shared" ref="N47" si="36">M47+(M47*0.1)</f>
         <v>88</v>
       </c>
-      <c r="O47" s="70"/>
-      <c r="P47" s="70"/>
-      <c r="Q47" s="70">
+      <c r="O47" s="66"/>
+      <c r="P47" s="66"/>
+      <c r="Q47" s="66">
         <f t="shared" ref="Q47" si="37">P47*N47</f>
         <v>0</v>
       </c>
-      <c r="R47" s="71" t="s">
+      <c r="R47" s="66" t="s">
         <v>385</v>
       </c>
     </row>
@@ -5113,54 +5072,54 @@
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C48" s="60" t="s">
+      <c r="C48" s="105" t="s">
         <v>322</v>
       </c>
-      <c r="D48" s="39" t="s">
+      <c r="D48" s="106" t="s">
         <v>35</v>
       </c>
-      <c r="E48" s="40" t="s">
+      <c r="E48" s="107" t="s">
         <v>103</v>
       </c>
-      <c r="F48" s="39" t="s">
+      <c r="F48" s="106" t="s">
         <v>164</v>
       </c>
-      <c r="G48" s="40">
+      <c r="G48" s="107">
         <v>61300211121</v>
       </c>
-      <c r="H48" s="39" t="s">
+      <c r="H48" s="106" t="s">
         <v>235</v>
       </c>
-      <c r="I48" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="J48" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="K48" s="40" t="s">
-        <v>314</v>
-      </c>
-      <c r="L48" s="39">
+      <c r="I48" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J48" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="K48" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="L48" s="106">
         <v>4</v>
       </c>
-      <c r="M48" s="42">
+      <c r="M48" s="96">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N48" s="42">
+      <c r="N48" s="96">
         <v>90</v>
       </c>
-      <c r="O48" s="65" t="s">
+      <c r="O48" s="108" t="s">
         <v>380</v>
       </c>
-      <c r="P48" s="42">
+      <c r="P48" s="96">
         <v>0.13</v>
       </c>
-      <c r="Q48" s="42">
+      <c r="Q48" s="96">
         <f t="shared" ref="Q48" si="38">N48*P48</f>
         <v>11.700000000000001</v>
       </c>
-      <c r="R48" s="42"/>
+      <c r="R48" s="96"/>
     </row>
     <row r="49" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1"/>
@@ -5168,54 +5127,54 @@
         <f>ROW(B49) - ROW($B$9)</f>
         <v>40</v>
       </c>
-      <c r="C49" s="61" t="s">
+      <c r="C49" s="109" t="s">
         <v>324</v>
       </c>
-      <c r="D49" s="37" t="s">
-        <v>448</v>
-      </c>
-      <c r="E49" s="38" t="s">
+      <c r="D49" s="110" t="s">
+        <v>440</v>
+      </c>
+      <c r="E49" s="111" t="s">
         <v>104</v>
       </c>
-      <c r="F49" s="37" t="s">
+      <c r="F49" s="110" t="s">
         <v>165</v>
       </c>
-      <c r="G49" s="38" t="s">
+      <c r="G49" s="111" t="s">
         <v>200</v>
       </c>
-      <c r="H49" s="37" t="s">
+      <c r="H49" s="110" t="s">
         <v>248</v>
       </c>
-      <c r="I49" s="37" t="s">
+      <c r="I49" s="110" t="s">
         <v>386</v>
       </c>
-      <c r="J49" s="37" t="s">
+      <c r="J49" s="110" t="s">
         <v>387</v>
       </c>
-      <c r="K49" s="38" t="s">
-        <v>314</v>
-      </c>
-      <c r="L49" s="37">
+      <c r="K49" s="111" t="s">
+        <v>314</v>
+      </c>
+      <c r="L49" s="110">
         <v>4</v>
       </c>
-      <c r="M49" s="41">
+      <c r="M49" s="112">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N49" s="41">
+      <c r="N49" s="112">
         <v>85</v>
       </c>
-      <c r="O49" s="64" t="s">
+      <c r="O49" s="113" t="s">
         <v>344</v>
       </c>
-      <c r="P49" s="41">
+      <c r="P49" s="112">
         <v>0.21740000000000001</v>
       </c>
-      <c r="Q49" s="41">
+      <c r="Q49" s="112">
         <f t="shared" ref="Q49" si="39">P49*N49</f>
         <v>18.478999999999999</v>
       </c>
-      <c r="R49" s="41"/>
+      <c r="R49" s="112"/>
     </row>
     <row r="50" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1"/>
@@ -5223,54 +5182,54 @@
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="C50" s="60" t="s">
+      <c r="C50" s="105" t="s">
         <v>325</v>
       </c>
-      <c r="D50" s="39" t="s">
+      <c r="D50" s="106" t="s">
         <v>36</v>
       </c>
-      <c r="E50" s="40" t="s">
+      <c r="E50" s="107" t="s">
         <v>105</v>
       </c>
-      <c r="F50" s="39" t="s">
+      <c r="F50" s="106" t="s">
         <v>166</v>
       </c>
-      <c r="G50" s="40" t="s">
+      <c r="G50" s="107" t="s">
         <v>201</v>
       </c>
-      <c r="H50" s="39" t="s">
+      <c r="H50" s="106" t="s">
         <v>229</v>
       </c>
-      <c r="I50" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="J50" s="39" t="s">
+      <c r="I50" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J50" s="106" t="s">
         <v>388</v>
       </c>
-      <c r="K50" s="40" t="s">
+      <c r="K50" s="107" t="s">
         <v>284</v>
       </c>
-      <c r="L50" s="39">
+      <c r="L50" s="106">
         <v>2</v>
       </c>
-      <c r="M50" s="42">
+      <c r="M50" s="96">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N50" s="42">
+      <c r="N50" s="96">
         <v>100</v>
       </c>
-      <c r="O50" s="65" t="s">
+      <c r="O50" s="108" t="s">
         <v>344</v>
       </c>
-      <c r="P50" s="42">
+      <c r="P50" s="96">
         <v>1E-3</v>
       </c>
-      <c r="Q50" s="42">
+      <c r="Q50" s="96">
         <f t="shared" ref="Q50" si="40">N50*P50</f>
         <v>0.1</v>
       </c>
-      <c r="R50" s="42"/>
+      <c r="R50" s="96"/>
     </row>
     <row r="51" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1"/>
@@ -5278,54 +5237,54 @@
         <f>ROW(B51) - ROW($B$9)</f>
         <v>42</v>
       </c>
-      <c r="C51" s="61" t="s">
+      <c r="C51" s="109" t="s">
         <v>325</v>
       </c>
-      <c r="D51" s="37" t="s">
+      <c r="D51" s="110" t="s">
         <v>37</v>
       </c>
-      <c r="E51" s="38" t="s">
+      <c r="E51" s="111" t="s">
         <v>106</v>
       </c>
-      <c r="F51" s="37" t="s">
+      <c r="F51" s="110" t="s">
         <v>166</v>
       </c>
-      <c r="G51" s="38" t="s">
+      <c r="G51" s="111" t="s">
         <v>202</v>
       </c>
-      <c r="H51" s="37" t="s">
+      <c r="H51" s="110" t="s">
         <v>229</v>
       </c>
-      <c r="I51" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="J51" s="37" t="s">
+      <c r="I51" s="110" t="s">
+        <v>314</v>
+      </c>
+      <c r="J51" s="110" t="s">
         <v>389</v>
       </c>
-      <c r="K51" s="38" t="s">
+      <c r="K51" s="111" t="s">
         <v>285</v>
       </c>
-      <c r="L51" s="37">
+      <c r="L51" s="110">
         <v>1</v>
       </c>
-      <c r="M51" s="41">
+      <c r="M51" s="112">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N51" s="41">
+      <c r="N51" s="112">
         <v>100</v>
       </c>
-      <c r="O51" s="64" t="s">
+      <c r="O51" s="113" t="s">
         <v>344</v>
       </c>
-      <c r="P51" s="41">
+      <c r="P51" s="112">
         <v>1.4E-3</v>
       </c>
-      <c r="Q51" s="41">
+      <c r="Q51" s="112">
         <f t="shared" ref="Q51" si="41">P51*N51</f>
         <v>0.13999999999999999</v>
       </c>
-      <c r="R51" s="41"/>
+      <c r="R51" s="112"/>
     </row>
     <row r="52" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1"/>
@@ -5333,54 +5292,54 @@
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="C52" s="60" t="s">
+      <c r="C52" s="105" t="s">
         <v>325</v>
       </c>
-      <c r="D52" s="39" t="s">
+      <c r="D52" s="106" t="s">
         <v>38</v>
       </c>
-      <c r="E52" s="40" t="s">
+      <c r="E52" s="107" t="s">
         <v>107</v>
       </c>
-      <c r="F52" s="39" t="s">
+      <c r="F52" s="106" t="s">
         <v>166</v>
       </c>
-      <c r="G52" s="40" t="s">
+      <c r="G52" s="107" t="s">
         <v>203</v>
       </c>
-      <c r="H52" s="39" t="s">
+      <c r="H52" s="106" t="s">
         <v>249</v>
       </c>
-      <c r="I52" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="J52" s="39" t="s">
+      <c r="I52" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J52" s="106" t="s">
         <v>390</v>
       </c>
-      <c r="K52" s="40" t="s">
+      <c r="K52" s="107" t="s">
         <v>286</v>
       </c>
-      <c r="L52" s="39">
+      <c r="L52" s="106">
         <v>1</v>
       </c>
-      <c r="M52" s="42">
+      <c r="M52" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N52" s="42">
+      <c r="N52" s="96">
         <v>100</v>
       </c>
-      <c r="O52" s="65" t="s">
+      <c r="O52" s="108" t="s">
         <v>344</v>
       </c>
-      <c r="P52" s="42">
+      <c r="P52" s="96">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="Q52" s="42">
+      <c r="Q52" s="96">
         <f t="shared" ref="Q52" si="42">N52*P52</f>
         <v>0.16</v>
       </c>
-      <c r="R52" s="42"/>
+      <c r="R52" s="96"/>
     </row>
     <row r="53" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1"/>
@@ -5388,54 +5347,54 @@
         <f>ROW(B53) - ROW($B$9)</f>
         <v>44</v>
       </c>
-      <c r="C53" s="61" t="s">
+      <c r="C53" s="109" t="s">
         <v>325</v>
       </c>
-      <c r="D53" s="37" t="s">
+      <c r="D53" s="110" t="s">
         <v>39</v>
       </c>
-      <c r="E53" s="38" t="s">
+      <c r="E53" s="111" t="s">
         <v>108</v>
       </c>
-      <c r="F53" s="37" t="s">
+      <c r="F53" s="110" t="s">
         <v>166</v>
       </c>
-      <c r="G53" s="38" t="s">
+      <c r="G53" s="111" t="s">
         <v>204</v>
       </c>
-      <c r="H53" s="37" t="s">
+      <c r="H53" s="110" t="s">
         <v>229</v>
       </c>
-      <c r="I53" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="J53" s="37" t="s">
+      <c r="I53" s="110" t="s">
+        <v>314</v>
+      </c>
+      <c r="J53" s="110" t="s">
         <v>391</v>
       </c>
-      <c r="K53" s="38" t="s">
+      <c r="K53" s="111" t="s">
         <v>287</v>
       </c>
-      <c r="L53" s="37">
+      <c r="L53" s="110">
         <v>2</v>
       </c>
-      <c r="M53" s="41">
+      <c r="M53" s="112">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N53" s="41">
+      <c r="N53" s="112">
         <v>100</v>
       </c>
-      <c r="O53" s="64" t="s">
+      <c r="O53" s="113" t="s">
         <v>344</v>
       </c>
-      <c r="P53" s="41">
+      <c r="P53" s="112">
         <v>1.4E-3</v>
       </c>
-      <c r="Q53" s="41">
+      <c r="Q53" s="112">
         <f t="shared" ref="Q53" si="43">P53*N53</f>
         <v>0.13999999999999999</v>
       </c>
-      <c r="R53" s="41"/>
+      <c r="R53" s="112"/>
     </row>
     <row r="54" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1"/>
@@ -5443,54 +5402,54 @@
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="C54" s="60" t="s">
+      <c r="C54" s="105" t="s">
         <v>325</v>
       </c>
-      <c r="D54" s="39" t="s">
+      <c r="D54" s="106" t="s">
         <v>40</v>
       </c>
-      <c r="E54" s="40" t="s">
+      <c r="E54" s="107" t="s">
         <v>109</v>
       </c>
-      <c r="F54" s="39" t="s">
+      <c r="F54" s="106" t="s">
         <v>166</v>
       </c>
-      <c r="G54" s="40" t="s">
+      <c r="G54" s="107" t="s">
         <v>205</v>
       </c>
-      <c r="H54" s="39" t="s">
+      <c r="H54" s="106" t="s">
         <v>229</v>
       </c>
-      <c r="I54" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="J54" s="39" t="s">
+      <c r="I54" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J54" s="106" t="s">
         <v>392</v>
       </c>
-      <c r="K54" s="40" t="s">
+      <c r="K54" s="107" t="s">
         <v>288</v>
       </c>
-      <c r="L54" s="39">
+      <c r="L54" s="106">
         <v>4</v>
       </c>
-      <c r="M54" s="42">
+      <c r="M54" s="96">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N54" s="42">
+      <c r="N54" s="96">
         <v>100</v>
       </c>
-      <c r="O54" s="65" t="s">
+      <c r="O54" s="108" t="s">
         <v>344</v>
       </c>
-      <c r="P54" s="42">
+      <c r="P54" s="96">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q54" s="42">
+      <c r="Q54" s="96">
         <f t="shared" ref="Q54" si="44">N54*P54</f>
         <v>0.13</v>
       </c>
-      <c r="R54" s="42"/>
+      <c r="R54" s="96"/>
     </row>
     <row r="55" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1"/>
@@ -5498,54 +5457,54 @@
         <f>ROW(B55) - ROW($B$9)</f>
         <v>46</v>
       </c>
-      <c r="C55" s="61" t="s">
+      <c r="C55" s="109" t="s">
         <v>325</v>
       </c>
-      <c r="D55" s="37" t="s">
+      <c r="D55" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="E55" s="38" t="s">
+      <c r="E55" s="111" t="s">
         <v>110</v>
       </c>
-      <c r="F55" s="37" t="s">
+      <c r="F55" s="110" t="s">
         <v>167</v>
       </c>
-      <c r="G55" s="38" t="s">
+      <c r="G55" s="111" t="s">
         <v>330</v>
       </c>
-      <c r="H55" s="37" t="s">
+      <c r="H55" s="110" t="s">
         <v>250</v>
       </c>
-      <c r="I55" s="37" t="s">
+      <c r="I55" s="110" t="s">
         <v>393</v>
       </c>
-      <c r="J55" s="37" t="s">
+      <c r="J55" s="110" t="s">
         <v>394</v>
       </c>
-      <c r="K55" s="38" t="s">
+      <c r="K55" s="111" t="s">
         <v>289</v>
       </c>
-      <c r="L55" s="37">
+      <c r="L55" s="110">
         <v>4</v>
       </c>
-      <c r="M55" s="41">
+      <c r="M55" s="112">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N55" s="41">
+      <c r="N55" s="112">
         <v>90</v>
       </c>
-      <c r="O55" s="64" t="s">
+      <c r="O55" s="113" t="s">
         <v>344</v>
       </c>
-      <c r="P55" s="41">
+      <c r="P55" s="112">
         <v>6.4500000000000002E-2</v>
       </c>
-      <c r="Q55" s="41">
+      <c r="Q55" s="112">
         <f t="shared" ref="Q55" si="45">P55*N55</f>
         <v>5.8049999999999997</v>
       </c>
-      <c r="R55" s="41"/>
+      <c r="R55" s="112"/>
     </row>
     <row r="56" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
@@ -5553,20 +5512,20 @@
         <f>ROW(B56) - ROW($B$9)</f>
         <v>47</v>
       </c>
-      <c r="C56" s="61" t="s">
+      <c r="C56" s="60" t="s">
         <v>325</v>
       </c>
       <c r="D56" s="37" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E56" s="37" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="F56" s="37" t="s">
         <v>166</v>
       </c>
       <c r="G56" s="37" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H56" s="37" t="s">
         <v>252</v>
@@ -5575,10 +5534,10 @@
         <v>314</v>
       </c>
       <c r="J56" s="37" t="s">
+        <v>427</v>
+      </c>
+      <c r="K56" s="37" t="s">
         <v>428</v>
-      </c>
-      <c r="K56" s="37" t="s">
-        <v>429</v>
       </c>
       <c r="L56" s="37">
         <v>8</v>
@@ -5587,10 +5546,10 @@
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="N56" s="110">
+      <c r="N56" s="96">
         <v>100</v>
       </c>
-      <c r="O56" s="90" t="s">
+      <c r="O56" s="80" t="s">
         <v>344</v>
       </c>
       <c r="P56" s="37">
@@ -5600,7 +5559,7 @@
         <f t="shared" ref="Q56" si="46">N56*P56</f>
         <v>0.11</v>
       </c>
-      <c r="R56" s="81"/>
+      <c r="R56" s="76"/>
     </row>
     <row r="57" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1"/>
@@ -5608,54 +5567,54 @@
         <f>ROW(B57) - ROW($B$9)</f>
         <v>48</v>
       </c>
-      <c r="C57" s="61" t="s">
+      <c r="C57" s="109" t="s">
         <v>325</v>
       </c>
-      <c r="D57" s="37" t="s">
+      <c r="D57" s="110" t="s">
         <v>42</v>
       </c>
-      <c r="E57" s="38" t="s">
+      <c r="E57" s="111" t="s">
         <v>112</v>
       </c>
-      <c r="F57" s="37" t="s">
+      <c r="F57" s="110" t="s">
         <v>166</v>
       </c>
-      <c r="G57" s="38" t="s">
+      <c r="G57" s="111" t="s">
         <v>207</v>
       </c>
-      <c r="H57" s="37" t="s">
+      <c r="H57" s="110" t="s">
         <v>251</v>
       </c>
-      <c r="I57" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="J57" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="K57" s="38" t="s">
+      <c r="I57" s="110" t="s">
+        <v>314</v>
+      </c>
+      <c r="J57" s="110" t="s">
+        <v>314</v>
+      </c>
+      <c r="K57" s="111" t="s">
         <v>291</v>
       </c>
-      <c r="L57" s="37">
+      <c r="L57" s="110">
         <v>1</v>
       </c>
-      <c r="M57" s="41">
+      <c r="M57" s="112">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N57" s="41">
+      <c r="N57" s="112">
         <v>30</v>
       </c>
-      <c r="O57" s="64" t="s">
+      <c r="O57" s="113" t="s">
         <v>383</v>
       </c>
-      <c r="P57" s="41">
+      <c r="P57" s="112">
         <v>1.8589999999999999E-2</v>
       </c>
-      <c r="Q57" s="41">
+      <c r="Q57" s="112">
         <f t="shared" ref="Q57" si="47">P57*N57</f>
         <v>0.55769999999999997</v>
       </c>
-      <c r="R57" s="41"/>
+      <c r="R57" s="112"/>
     </row>
     <row r="58" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1"/>
@@ -5663,54 +5622,54 @@
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="C58" s="60" t="s">
+      <c r="C58" s="105" t="s">
         <v>325</v>
       </c>
-      <c r="D58" s="39" t="s">
+      <c r="D58" s="106" t="s">
         <v>43</v>
       </c>
-      <c r="E58" s="40" t="s">
+      <c r="E58" s="107" t="s">
         <v>113</v>
       </c>
-      <c r="F58" s="39" t="s">
+      <c r="F58" s="106" t="s">
         <v>166</v>
       </c>
-      <c r="G58" s="40" t="s">
+      <c r="G58" s="107" t="s">
         <v>208</v>
       </c>
-      <c r="H58" s="39" t="s">
+      <c r="H58" s="106" t="s">
         <v>229</v>
       </c>
-      <c r="I58" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="J58" s="39" t="s">
+      <c r="I58" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J58" s="106" t="s">
         <v>396</v>
       </c>
-      <c r="K58" s="40" t="s">
+      <c r="K58" s="107" t="s">
         <v>292</v>
       </c>
-      <c r="L58" s="39">
+      <c r="L58" s="106">
         <v>1</v>
       </c>
-      <c r="M58" s="42">
+      <c r="M58" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N58" s="42">
+      <c r="N58" s="96">
         <v>100</v>
       </c>
-      <c r="O58" s="65" t="s">
+      <c r="O58" s="108" t="s">
         <v>344</v>
       </c>
-      <c r="P58" s="42">
+      <c r="P58" s="96">
         <v>1.4E-3</v>
       </c>
-      <c r="Q58" s="42">
+      <c r="Q58" s="96">
         <f t="shared" ref="Q58" si="48">N58*P58</f>
         <v>0.13999999999999999</v>
       </c>
-      <c r="R58" s="42"/>
+      <c r="R58" s="96"/>
     </row>
     <row r="59" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1"/>
@@ -5718,54 +5677,54 @@
         <f>ROW(B59) - ROW($B$9)</f>
         <v>50</v>
       </c>
-      <c r="C59" s="61" t="s">
+      <c r="C59" s="109" t="s">
         <v>325</v>
       </c>
-      <c r="D59" s="37" t="s">
+      <c r="D59" s="110" t="s">
         <v>44</v>
       </c>
-      <c r="E59" s="38" t="s">
+      <c r="E59" s="111" t="s">
         <v>114</v>
       </c>
-      <c r="F59" s="37" t="s">
+      <c r="F59" s="110" t="s">
         <v>166</v>
       </c>
-      <c r="G59" s="38" t="s">
+      <c r="G59" s="111" t="s">
         <v>209</v>
       </c>
-      <c r="H59" s="37" t="s">
+      <c r="H59" s="110" t="s">
         <v>251</v>
       </c>
-      <c r="I59" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="J59" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="K59" s="38" t="s">
+      <c r="I59" s="110" t="s">
+        <v>314</v>
+      </c>
+      <c r="J59" s="110" t="s">
+        <v>314</v>
+      </c>
+      <c r="K59" s="111" t="s">
         <v>293</v>
       </c>
-      <c r="L59" s="37">
+      <c r="L59" s="110">
         <v>1</v>
       </c>
-      <c r="M59" s="41">
+      <c r="M59" s="112">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N59" s="41">
+      <c r="N59" s="112">
         <v>50</v>
       </c>
-      <c r="O59" s="64" t="s">
+      <c r="O59" s="113" t="s">
         <v>383</v>
       </c>
-      <c r="P59" s="41">
+      <c r="P59" s="112">
         <v>4.6699999999999997E-3</v>
       </c>
-      <c r="Q59" s="41">
+      <c r="Q59" s="112">
         <f t="shared" ref="Q59" si="49">P59*N59</f>
         <v>0.23349999999999999</v>
       </c>
-      <c r="R59" s="41"/>
+      <c r="R59" s="112"/>
     </row>
     <row r="60" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1"/>
@@ -5773,54 +5732,54 @@
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="C60" s="60" t="s">
+      <c r="C60" s="105" t="s">
         <v>325</v>
       </c>
-      <c r="D60" s="39" t="s">
+      <c r="D60" s="106" t="s">
         <v>45</v>
       </c>
-      <c r="E60" s="40" t="s">
+      <c r="E60" s="107" t="s">
         <v>115</v>
       </c>
-      <c r="F60" s="39" t="s">
+      <c r="F60" s="106" t="s">
         <v>166</v>
       </c>
-      <c r="G60" s="40" t="s">
+      <c r="G60" s="107" t="s">
         <v>210</v>
       </c>
-      <c r="H60" s="39" t="s">
+      <c r="H60" s="106" t="s">
         <v>229</v>
       </c>
-      <c r="I60" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="J60" s="39" t="s">
+      <c r="I60" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J60" s="106" t="s">
         <v>397</v>
       </c>
-      <c r="K60" s="40" t="s">
+      <c r="K60" s="107" t="s">
         <v>294</v>
       </c>
-      <c r="L60" s="39">
+      <c r="L60" s="106">
         <v>1</v>
       </c>
-      <c r="M60" s="42">
+      <c r="M60" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N60" s="42">
+      <c r="N60" s="96">
         <v>100</v>
       </c>
-      <c r="O60" s="65" t="s">
+      <c r="O60" s="108" t="s">
         <v>344</v>
       </c>
-      <c r="P60" s="42">
+      <c r="P60" s="96">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q60" s="42">
+      <c r="Q60" s="96">
         <f t="shared" ref="Q60" si="50">N60*P60</f>
         <v>0.12</v>
       </c>
-      <c r="R60" s="42"/>
+      <c r="R60" s="96"/>
     </row>
     <row r="61" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1"/>
@@ -5828,54 +5787,54 @@
         <f>ROW(B61) - ROW($B$9)</f>
         <v>52</v>
       </c>
-      <c r="C61" s="61" t="s">
+      <c r="C61" s="109" t="s">
         <v>325</v>
       </c>
-      <c r="D61" s="37" t="s">
+      <c r="D61" s="110" t="s">
         <v>46</v>
       </c>
-      <c r="E61" s="38" t="s">
+      <c r="E61" s="111" t="s">
         <v>116</v>
       </c>
-      <c r="F61" s="37" t="s">
+      <c r="F61" s="110" t="s">
         <v>166</v>
       </c>
-      <c r="G61" s="38" t="s">
+      <c r="G61" s="111" t="s">
         <v>211</v>
       </c>
-      <c r="H61" s="37" t="s">
+      <c r="H61" s="110" t="s">
         <v>251</v>
       </c>
-      <c r="I61" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="J61" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="K61" s="38" t="s">
+      <c r="I61" s="110" t="s">
+        <v>314</v>
+      </c>
+      <c r="J61" s="110" t="s">
+        <v>314</v>
+      </c>
+      <c r="K61" s="111" t="s">
         <v>295</v>
       </c>
-      <c r="L61" s="37">
+      <c r="L61" s="110">
         <v>1</v>
       </c>
-      <c r="M61" s="41">
+      <c r="M61" s="112">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N61" s="41">
+      <c r="N61" s="112">
         <v>50</v>
       </c>
-      <c r="O61" s="64" t="s">
+      <c r="O61" s="113" t="s">
         <v>383</v>
       </c>
-      <c r="P61" s="41">
+      <c r="P61" s="112">
         <v>1.11E-2</v>
       </c>
-      <c r="Q61" s="41">
+      <c r="Q61" s="112">
         <f t="shared" ref="Q61" si="51">P61*N61</f>
         <v>0.55500000000000005</v>
       </c>
-      <c r="R61" s="41"/>
+      <c r="R61" s="112"/>
     </row>
     <row r="62" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1"/>
@@ -5883,54 +5842,54 @@
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="C62" s="60" t="s">
+      <c r="C62" s="105" t="s">
         <v>325</v>
       </c>
-      <c r="D62" s="39" t="s">
+      <c r="D62" s="106" t="s">
         <v>47</v>
       </c>
-      <c r="E62" s="40" t="s">
+      <c r="E62" s="107" t="s">
         <v>117</v>
       </c>
-      <c r="F62" s="39" t="s">
+      <c r="F62" s="106" t="s">
         <v>166</v>
       </c>
-      <c r="G62" s="40" t="s">
+      <c r="G62" s="107" t="s">
         <v>212</v>
       </c>
-      <c r="H62" s="39" t="s">
+      <c r="H62" s="106" t="s">
         <v>229</v>
       </c>
-      <c r="I62" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="J62" s="39" t="s">
+      <c r="I62" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J62" s="106" t="s">
         <v>398</v>
       </c>
-      <c r="K62" s="40" t="s">
+      <c r="K62" s="107" t="s">
         <v>296</v>
       </c>
-      <c r="L62" s="39">
+      <c r="L62" s="106">
         <v>1</v>
       </c>
-      <c r="M62" s="42">
+      <c r="M62" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N62" s="42">
+      <c r="N62" s="96">
         <v>100</v>
       </c>
-      <c r="O62" s="65" t="s">
+      <c r="O62" s="108" t="s">
         <v>344</v>
       </c>
-      <c r="P62" s="42">
+      <c r="P62" s="96">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="Q62" s="42">
+      <c r="Q62" s="96">
         <f t="shared" ref="Q62" si="52">N62*P62</f>
         <v>0.21</v>
       </c>
-      <c r="R62" s="42"/>
+      <c r="R62" s="96"/>
     </row>
     <row r="63" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1"/>
@@ -5938,54 +5897,54 @@
         <f>ROW(B63) - ROW($B$9)</f>
         <v>54</v>
       </c>
-      <c r="C63" s="61" t="s">
+      <c r="C63" s="109" t="s">
         <v>325</v>
       </c>
-      <c r="D63" s="37" t="s">
+      <c r="D63" s="110" t="s">
         <v>48</v>
       </c>
-      <c r="E63" s="38" t="s">
+      <c r="E63" s="111" t="s">
         <v>118</v>
       </c>
-      <c r="F63" s="37" t="s">
+      <c r="F63" s="110" t="s">
         <v>166</v>
       </c>
-      <c r="G63" s="38" t="s">
+      <c r="G63" s="111" t="s">
         <v>213</v>
       </c>
-      <c r="H63" s="37" t="s">
+      <c r="H63" s="110" t="s">
         <v>229</v>
       </c>
-      <c r="I63" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="J63" s="37" t="s">
+      <c r="I63" s="110" t="s">
+        <v>314</v>
+      </c>
+      <c r="J63" s="110" t="s">
         <v>399</v>
       </c>
-      <c r="K63" s="38" t="s">
+      <c r="K63" s="111" t="s">
         <v>297</v>
       </c>
-      <c r="L63" s="37">
+      <c r="L63" s="110">
         <v>1</v>
       </c>
-      <c r="M63" s="41">
+      <c r="M63" s="112">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N63" s="41">
+      <c r="N63" s="112">
         <v>100</v>
       </c>
-      <c r="O63" s="64" t="s">
+      <c r="O63" s="113" t="s">
         <v>344</v>
       </c>
-      <c r="P63" s="41">
+      <c r="P63" s="112">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="Q63" s="41">
+      <c r="Q63" s="112">
         <f t="shared" ref="Q63" si="53">P63*N63</f>
         <v>0.16</v>
       </c>
-      <c r="R63" s="41"/>
+      <c r="R63" s="112"/>
     </row>
     <row r="64" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1"/>
@@ -5993,54 +5952,54 @@
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="C64" s="60" t="s">
+      <c r="C64" s="105" t="s">
         <v>325</v>
       </c>
-      <c r="D64" s="39" t="s">
+      <c r="D64" s="106" t="s">
         <v>49</v>
       </c>
-      <c r="E64" s="40" t="s">
+      <c r="E64" s="107" t="s">
         <v>119</v>
       </c>
-      <c r="F64" s="39" t="s">
+      <c r="F64" s="106" t="s">
         <v>166</v>
       </c>
-      <c r="G64" s="40" t="s">
+      <c r="G64" s="107" t="s">
         <v>214</v>
       </c>
-      <c r="H64" s="39" t="s">
+      <c r="H64" s="106" t="s">
         <v>229</v>
       </c>
-      <c r="I64" s="39" t="s">
+      <c r="I64" s="106" t="s">
         <v>400</v>
       </c>
-      <c r="J64" s="39" t="s">
+      <c r="J64" s="106" t="s">
         <v>401</v>
       </c>
-      <c r="K64" s="40" t="s">
+      <c r="K64" s="107" t="s">
         <v>298</v>
       </c>
-      <c r="L64" s="39">
+      <c r="L64" s="106">
         <v>1</v>
       </c>
-      <c r="M64" s="42">
+      <c r="M64" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N64" s="42">
+      <c r="N64" s="96">
         <v>50</v>
       </c>
-      <c r="O64" s="65" t="s">
+      <c r="O64" s="108" t="s">
         <v>344</v>
       </c>
-      <c r="P64" s="42">
+      <c r="P64" s="96">
         <v>6.8999999999999999E-3</v>
       </c>
-      <c r="Q64" s="42">
+      <c r="Q64" s="96">
         <f t="shared" ref="Q64" si="54">N64*P64</f>
         <v>0.34499999999999997</v>
       </c>
-      <c r="R64" s="42"/>
+      <c r="R64" s="96"/>
     </row>
     <row r="65" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1"/>
@@ -6048,54 +6007,54 @@
         <f>ROW(B65) - ROW($B$9)</f>
         <v>56</v>
       </c>
-      <c r="C65" s="61" t="s">
+      <c r="C65" s="109" t="s">
         <v>325</v>
       </c>
-      <c r="D65" s="37" t="s">
-        <v>403</v>
-      </c>
-      <c r="E65" s="38" t="s">
+      <c r="D65" s="110" t="s">
+        <v>465</v>
+      </c>
+      <c r="E65" s="111" t="s">
         <v>120</v>
       </c>
-      <c r="F65" s="37" t="s">
+      <c r="F65" s="110" t="s">
         <v>166</v>
       </c>
-      <c r="G65" s="38" t="s">
+      <c r="G65" s="111" t="s">
         <v>215</v>
       </c>
-      <c r="H65" s="37" t="s">
+      <c r="H65" s="110" t="s">
         <v>229</v>
       </c>
-      <c r="I65" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="J65" s="37" t="s">
+      <c r="I65" s="110" t="s">
+        <v>314</v>
+      </c>
+      <c r="J65" s="110" t="s">
         <v>402</v>
       </c>
-      <c r="K65" s="38" t="s">
+      <c r="K65" s="111" t="s">
         <v>299</v>
       </c>
-      <c r="L65" s="37">
+      <c r="L65" s="110">
         <v>2</v>
       </c>
-      <c r="M65" s="41">
+      <c r="M65" s="112">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N65" s="41">
+      <c r="N65" s="112">
         <v>100</v>
       </c>
-      <c r="O65" s="64" t="s">
+      <c r="O65" s="113" t="s">
         <v>344</v>
       </c>
-      <c r="P65" s="41">
+      <c r="P65" s="112">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="Q65" s="41">
+      <c r="Q65" s="112">
         <f t="shared" ref="Q65" si="55">P65*N65</f>
         <v>0.11</v>
       </c>
-      <c r="R65" s="41"/>
+      <c r="R65" s="112"/>
     </row>
     <row r="66" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
@@ -6103,7 +6062,7 @@
         <f>ROW(B66) - ROW($B$9)</f>
         <v>57</v>
       </c>
-      <c r="C66" s="61" t="s">
+      <c r="C66" s="60" t="s">
         <v>325</v>
       </c>
       <c r="D66" s="37" t="s">
@@ -6125,7 +6084,7 @@
         <v>314</v>
       </c>
       <c r="J66" s="37" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K66" s="38" t="s">
         <v>300</v>
@@ -6140,7 +6099,7 @@
       <c r="N66" s="41">
         <v>100</v>
       </c>
-      <c r="O66" s="64" t="s">
+      <c r="O66" s="63" t="s">
         <v>344</v>
       </c>
       <c r="P66" s="41">
@@ -6158,11 +6117,11 @@
         <f>ROW(B67) - ROW($B$9)</f>
         <v>58</v>
       </c>
-      <c r="C67" s="60" t="s">
+      <c r="C67" s="59" t="s">
         <v>325</v>
       </c>
-      <c r="D67" s="88" t="s">
-        <v>426</v>
+      <c r="D67" s="87" t="s">
+        <v>425</v>
       </c>
       <c r="E67" s="40" t="s">
         <v>111</v>
@@ -6193,7 +6152,7 @@
       <c r="N67" s="42">
         <v>100</v>
       </c>
-      <c r="O67" s="65" t="s">
+      <c r="O67" s="64" t="s">
         <v>344</v>
       </c>
       <c r="P67" s="42">
@@ -6203,7 +6162,7 @@
         <f>N67*P67</f>
         <v>0.15</v>
       </c>
-      <c r="R67" s="84"/>
+      <c r="R67" s="77"/>
     </row>
     <row r="68" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1"/>
@@ -6211,7 +6170,7 @@
         <f>ROW(B68) - ROW($B$9)</f>
         <v>59</v>
       </c>
-      <c r="C68" s="61" t="s">
+      <c r="C68" s="60" t="s">
         <v>325</v>
       </c>
       <c r="D68" s="37" t="s">
@@ -6233,7 +6192,7 @@
         <v>314</v>
       </c>
       <c r="J68" s="37" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="K68" s="38" t="s">
         <v>301</v>
@@ -6248,7 +6207,7 @@
       <c r="N68" s="41">
         <v>100</v>
       </c>
-      <c r="O68" s="64" t="s">
+      <c r="O68" s="63" t="s">
         <v>344</v>
       </c>
       <c r="P68" s="41">
@@ -6266,7 +6225,7 @@
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="C69" s="60" t="s">
+      <c r="C69" s="59" t="s">
         <v>325</v>
       </c>
       <c r="D69" s="39" t="s">
@@ -6303,8 +6262,8 @@
       <c r="N69" s="42">
         <v>25</v>
       </c>
-      <c r="O69" s="65" t="s">
-        <v>406</v>
+      <c r="O69" s="64" t="s">
+        <v>405</v>
       </c>
       <c r="P69" s="42">
         <v>8.5400000000000004E-2</v>
@@ -6321,20 +6280,20 @@
         <f>ROW(B70) - ROW($B$9)</f>
         <v>61</v>
       </c>
-      <c r="C70" s="61" t="s">
+      <c r="C70" s="60" t="s">
         <v>325</v>
       </c>
       <c r="D70" s="37" t="s">
         <v>53</v>
       </c>
       <c r="E70" s="38" t="s">
-        <v>440</v>
-      </c>
-      <c r="F70" s="96" t="s">
+        <v>435</v>
+      </c>
+      <c r="F70" s="86" t="s">
         <v>166</v>
       </c>
       <c r="G70" s="38" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="H70" s="37" t="s">
         <v>252</v>
@@ -6343,10 +6302,10 @@
         <v>314</v>
       </c>
       <c r="J70" s="37" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="K70" s="38" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="L70" s="37">
         <v>1</v>
@@ -6358,7 +6317,7 @@
       <c r="N70" s="41">
         <v>50</v>
       </c>
-      <c r="O70" s="64" t="s">
+      <c r="O70" s="63" t="s">
         <v>344</v>
       </c>
       <c r="P70" s="41">
@@ -6368,7 +6327,7 @@
         <f t="shared" ref="Q70" si="60">P70*N70</f>
         <v>0.19</v>
       </c>
-      <c r="R70" s="81"/>
+      <c r="R70" s="76"/>
     </row>
     <row r="71" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1"/>
@@ -6376,11 +6335,11 @@
         <f>ROW(B71) - ROW($B$9)</f>
         <v>62</v>
       </c>
-      <c r="C71" s="60" t="s">
+      <c r="C71" s="59" t="s">
         <v>325</v>
       </c>
       <c r="D71" s="39" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="E71" s="40" t="s">
         <v>127</v>
@@ -6398,7 +6357,7 @@
         <v>314</v>
       </c>
       <c r="J71" s="39" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="K71" s="40" t="s">
         <v>306</v>
@@ -6413,7 +6372,7 @@
       <c r="N71" s="42">
         <v>200</v>
       </c>
-      <c r="O71" s="65" t="s">
+      <c r="O71" s="64" t="s">
         <v>344</v>
       </c>
       <c r="P71" s="42">
@@ -6423,7 +6382,7 @@
         <f t="shared" ref="Q71" si="61">N71*P71</f>
         <v>0.24</v>
       </c>
-      <c r="R71" s="84"/>
+      <c r="R71" s="77"/>
     </row>
     <row r="72" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1"/>
@@ -6431,7 +6390,7 @@
         <f>ROW(B72) - ROW($B$9)</f>
         <v>63</v>
       </c>
-      <c r="C72" s="61" t="s">
+      <c r="C72" s="60" t="s">
         <v>325</v>
       </c>
       <c r="D72" s="37" t="s">
@@ -6453,7 +6412,7 @@
         <v>314</v>
       </c>
       <c r="J72" s="37" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="K72" s="38" t="s">
         <v>303</v>
@@ -6468,7 +6427,7 @@
       <c r="N72" s="41">
         <v>100</v>
       </c>
-      <c r="O72" s="64" t="s">
+      <c r="O72" s="63" t="s">
         <v>344</v>
       </c>
       <c r="P72" s="41">
@@ -6486,7 +6445,7 @@
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="C73" s="60" t="s">
+      <c r="C73" s="59" t="s">
         <v>325</v>
       </c>
       <c r="D73" s="39" t="s">
@@ -6508,7 +6467,7 @@
         <v>314</v>
       </c>
       <c r="J73" s="39" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K73" s="40" t="s">
         <v>304</v>
@@ -6523,7 +6482,7 @@
       <c r="N73" s="42">
         <v>50</v>
       </c>
-      <c r="O73" s="65" t="s">
+      <c r="O73" s="64" t="s">
         <v>344</v>
       </c>
       <c r="P73" s="42">
@@ -6541,55 +6500,55 @@
         <f>ROW(B74) - ROW($B$9)</f>
         <v>65</v>
       </c>
-      <c r="C74" s="111" t="s">
+      <c r="C74" s="97" t="s">
         <v>325</v>
       </c>
-      <c r="D74" s="112" t="s">
+      <c r="D74" s="98" t="s">
         <v>56</v>
       </c>
-      <c r="E74" s="113" t="s">
+      <c r="E74" s="99" t="s">
         <v>126</v>
       </c>
-      <c r="F74" s="112" t="s">
+      <c r="F74" s="98" t="s">
         <v>168</v>
       </c>
-      <c r="G74" s="113" t="s">
+      <c r="G74" s="99" t="s">
         <v>219</v>
       </c>
-      <c r="H74" s="112" t="s">
+      <c r="H74" s="98" t="s">
         <v>229</v>
       </c>
-      <c r="I74" s="112" t="s">
-        <v>314</v>
-      </c>
-      <c r="J74" s="112" t="s">
-        <v>409</v>
-      </c>
-      <c r="K74" s="113" t="s">
+      <c r="I74" s="98" t="s">
+        <v>314</v>
+      </c>
+      <c r="J74" s="98" t="s">
+        <v>408</v>
+      </c>
+      <c r="K74" s="99" t="s">
         <v>305</v>
       </c>
-      <c r="L74" s="112">
+      <c r="L74" s="98">
         <v>4</v>
       </c>
-      <c r="M74" s="71">
+      <c r="M74" s="66">
         <f t="shared" si="59"/>
         <v>80</v>
       </c>
-      <c r="N74" s="71">
+      <c r="N74" s="66">
         <v>100</v>
       </c>
-      <c r="O74" s="114" t="s">
+      <c r="O74" s="100" t="s">
         <v>344</v>
       </c>
-      <c r="P74" s="71">
+      <c r="P74" s="66">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q74" s="71">
+      <c r="Q74" s="66">
         <f t="shared" ref="Q74" si="64">P74*N74</f>
         <v>0.12</v>
       </c>
-      <c r="R74" s="71" t="s">
-        <v>464</v>
+      <c r="R74" s="66" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="75" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -6598,51 +6557,51 @@
         <f>ROW(B75) - ROW($B$9)</f>
         <v>66</v>
       </c>
-      <c r="C75" s="111" t="s">
+      <c r="C75" s="97" t="s">
         <v>169</v>
       </c>
-      <c r="D75" s="112" t="s">
-        <v>465</v>
-      </c>
-      <c r="E75" s="113" t="s">
+      <c r="D75" s="98" t="s">
+        <v>456</v>
+      </c>
+      <c r="E75" s="99" t="s">
         <v>128</v>
       </c>
-      <c r="F75" s="112" t="s">
+      <c r="F75" s="98" t="s">
         <v>169</v>
       </c>
-      <c r="G75" s="113" t="s">
-        <v>314</v>
-      </c>
-      <c r="H75" s="112" t="s">
-        <v>314</v>
-      </c>
-      <c r="I75" s="112" t="s">
-        <v>314</v>
-      </c>
-      <c r="J75" s="112" t="s">
-        <v>314</v>
-      </c>
-      <c r="K75" s="113" t="s">
-        <v>314</v>
-      </c>
-      <c r="L75" s="112">
-        <v>11</v>
-      </c>
-      <c r="M75" s="71">
+      <c r="G75" s="99" t="s">
+        <v>314</v>
+      </c>
+      <c r="H75" s="98" t="s">
+        <v>314</v>
+      </c>
+      <c r="I75" s="98" t="s">
+        <v>314</v>
+      </c>
+      <c r="J75" s="98" t="s">
+        <v>314</v>
+      </c>
+      <c r="K75" s="99" t="s">
+        <v>314</v>
+      </c>
+      <c r="L75" s="98">
+        <v>15</v>
+      </c>
+      <c r="M75" s="66">
         <f t="shared" si="59"/>
-        <v>220</v>
-      </c>
-      <c r="N75" s="71">
+        <v>300</v>
+      </c>
+      <c r="N75" s="66">
         <f t="shared" ref="N75:N76" si="65">M75+(M75*0.1)</f>
-        <v>242</v>
-      </c>
-      <c r="O75" s="71"/>
-      <c r="P75" s="71"/>
-      <c r="Q75" s="71">
+        <v>330</v>
+      </c>
+      <c r="O75" s="66"/>
+      <c r="P75" s="66"/>
+      <c r="Q75" s="66">
         <f t="shared" ref="Q75" si="66">P75*N75</f>
         <v>0</v>
       </c>
-      <c r="R75" s="71" t="s">
+      <c r="R75" s="66" t="s">
         <v>385</v>
       </c>
     </row>
@@ -6652,49 +6611,51 @@
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="C76" s="60" t="s">
+      <c r="C76" s="105" t="s">
         <v>327</v>
       </c>
-      <c r="D76" s="39" t="s">
+      <c r="D76" s="106" t="s">
         <v>57</v>
       </c>
-      <c r="E76" s="40" t="s">
+      <c r="E76" s="107" t="s">
         <v>129</v>
       </c>
-      <c r="F76" s="39" t="s">
+      <c r="F76" s="106" t="s">
         <v>170</v>
       </c>
-      <c r="G76" s="40"/>
-      <c r="H76" s="39" t="s">
+      <c r="G76" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="H76" s="106" t="s">
         <v>254</v>
       </c>
-      <c r="I76" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="J76" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="K76" s="40" t="s">
-        <v>314</v>
-      </c>
-      <c r="L76" s="39">
+      <c r="I76" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J76" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="K76" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="L76" s="106">
         <v>1</v>
       </c>
-      <c r="M76" s="42">
+      <c r="M76" s="96">
         <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N76" s="42">
+      <c r="N76" s="96">
         <f t="shared" si="65"/>
         <v>22</v>
       </c>
-      <c r="O76" s="42"/>
-      <c r="P76" s="42"/>
-      <c r="Q76" s="42">
+      <c r="O76" s="96"/>
+      <c r="P76" s="96"/>
+      <c r="Q76" s="96">
         <f t="shared" ref="Q76" si="67">N76*P76</f>
         <v>0</v>
       </c>
-      <c r="R76" s="42"/>
+      <c r="R76" s="96"/>
     </row>
     <row r="77" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1"/>
@@ -6702,54 +6663,54 @@
         <f>ROW(B77) - ROW($B$9)</f>
         <v>68</v>
       </c>
-      <c r="C77" s="61" t="s">
+      <c r="C77" s="109" t="s">
         <v>328</v>
       </c>
-      <c r="D77" s="37" t="s">
+      <c r="D77" s="110" t="s">
         <v>58</v>
       </c>
-      <c r="E77" s="38" t="s">
+      <c r="E77" s="111" t="s">
         <v>130</v>
       </c>
-      <c r="F77" s="37" t="s">
+      <c r="F77" s="110" t="s">
         <v>308</v>
       </c>
-      <c r="G77" s="38">
+      <c r="G77" s="111">
         <v>750314597</v>
       </c>
-      <c r="H77" s="37" t="s">
+      <c r="H77" s="110" t="s">
         <v>255</v>
       </c>
-      <c r="I77" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="J77" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="K77" s="38" t="s">
-        <v>314</v>
-      </c>
-      <c r="L77" s="37">
+      <c r="I77" s="110" t="s">
+        <v>314</v>
+      </c>
+      <c r="J77" s="110" t="s">
+        <v>314</v>
+      </c>
+      <c r="K77" s="111" t="s">
+        <v>314</v>
+      </c>
+      <c r="L77" s="110">
         <v>1</v>
       </c>
-      <c r="M77" s="41">
+      <c r="M77" s="112">
         <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N77" s="41">
+      <c r="N77" s="112">
         <v>21</v>
       </c>
-      <c r="O77" s="64" t="s">
+      <c r="O77" s="113" t="s">
         <v>380</v>
       </c>
-      <c r="P77" s="41">
+      <c r="P77" s="112">
         <v>3.81</v>
       </c>
-      <c r="Q77" s="41">
+      <c r="Q77" s="112">
         <f t="shared" ref="Q77" si="68">P77*N77</f>
         <v>80.010000000000005</v>
       </c>
-      <c r="R77" s="41"/>
+      <c r="R77" s="112"/>
     </row>
     <row r="78" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1"/>
@@ -6757,54 +6718,54 @@
         <f t="shared" si="0"/>
         <v>69</v>
       </c>
-      <c r="C78" s="60" t="s">
+      <c r="C78" s="105" t="s">
         <v>329</v>
       </c>
-      <c r="D78" s="39" t="s">
+      <c r="D78" s="106" t="s">
         <v>59</v>
       </c>
-      <c r="E78" s="40" t="s">
+      <c r="E78" s="107" t="s">
         <v>131</v>
       </c>
-      <c r="F78" s="39" t="s">
+      <c r="F78" s="106" t="s">
         <v>308</v>
       </c>
-      <c r="G78" s="40" t="s">
+      <c r="G78" s="107" t="s">
         <v>171</v>
       </c>
-      <c r="H78" s="39" t="s">
+      <c r="H78" s="106" t="s">
         <v>256</v>
       </c>
-      <c r="I78" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="J78" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="K78" s="40" t="s">
-        <v>314</v>
-      </c>
-      <c r="L78" s="39">
+      <c r="I78" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J78" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="K78" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="L78" s="106">
         <v>1</v>
       </c>
-      <c r="M78" s="42">
+      <c r="M78" s="96">
         <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N78" s="42">
+      <c r="N78" s="96">
         <v>21</v>
       </c>
-      <c r="O78" s="65" t="s">
-        <v>411</v>
-      </c>
-      <c r="P78" s="42">
+      <c r="O78" s="108" t="s">
+        <v>410</v>
+      </c>
+      <c r="P78" s="96">
         <v>2.48</v>
       </c>
-      <c r="Q78" s="42">
+      <c r="Q78" s="96">
         <f t="shared" ref="Q78" si="69">N78*P78</f>
         <v>52.08</v>
       </c>
-      <c r="R78" s="42"/>
+      <c r="R78" s="96"/>
     </row>
     <row r="79" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1"/>
@@ -6812,54 +6773,54 @@
         <f>ROW(B79) - ROW($B$9)</f>
         <v>70</v>
       </c>
-      <c r="C79" s="61" t="s">
+      <c r="C79" s="109" t="s">
         <v>329</v>
       </c>
-      <c r="D79" s="37" t="s">
+      <c r="D79" s="110" t="s">
         <v>60</v>
       </c>
-      <c r="E79" s="38" t="s">
+      <c r="E79" s="111" t="s">
         <v>132</v>
       </c>
-      <c r="F79" s="37" t="s">
+      <c r="F79" s="110" t="s">
         <v>172</v>
       </c>
-      <c r="G79" s="38" t="s">
+      <c r="G79" s="111" t="s">
         <v>221</v>
       </c>
-      <c r="H79" s="37" t="s">
+      <c r="H79" s="110" t="s">
         <v>257</v>
       </c>
-      <c r="I79" s="37" t="s">
+      <c r="I79" s="110" t="s">
+        <v>411</v>
+      </c>
+      <c r="J79" s="110" t="s">
         <v>412</v>
       </c>
-      <c r="J79" s="37" t="s">
-        <v>413</v>
-      </c>
-      <c r="K79" s="38" t="s">
-        <v>314</v>
-      </c>
-      <c r="L79" s="37">
+      <c r="K79" s="111" t="s">
+        <v>314</v>
+      </c>
+      <c r="L79" s="110">
         <v>1</v>
       </c>
-      <c r="M79" s="41">
+      <c r="M79" s="112">
         <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N79" s="41">
+      <c r="N79" s="112">
         <v>21</v>
       </c>
-      <c r="O79" s="64" t="s">
+      <c r="O79" s="113" t="s">
         <v>344</v>
       </c>
-      <c r="P79" s="41">
+      <c r="P79" s="112">
         <v>1.3939999999999999</v>
       </c>
-      <c r="Q79" s="41">
+      <c r="Q79" s="112">
         <f t="shared" ref="Q79" si="70">P79*N79</f>
         <v>29.273999999999997</v>
       </c>
-      <c r="R79" s="85"/>
+      <c r="R79" s="79"/>
     </row>
     <row r="80" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1"/>
@@ -6867,54 +6828,54 @@
         <f t="shared" si="0"/>
         <v>71</v>
       </c>
-      <c r="C80" s="60" t="s">
+      <c r="C80" s="105" t="s">
         <v>329</v>
       </c>
-      <c r="D80" s="39" t="s">
+      <c r="D80" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="E80" s="40" t="s">
+      <c r="E80" s="107" t="s">
         <v>133</v>
       </c>
-      <c r="F80" s="39" t="s">
+      <c r="F80" s="106" t="s">
         <v>173</v>
       </c>
-      <c r="G80" s="40" t="s">
+      <c r="G80" s="107" t="s">
         <v>222</v>
       </c>
-      <c r="H80" s="39" t="s">
+      <c r="H80" s="106" t="s">
         <v>256</v>
       </c>
-      <c r="I80" s="39" t="s">
+      <c r="I80" s="106" t="s">
+        <v>413</v>
+      </c>
+      <c r="J80" s="106" t="s">
         <v>414</v>
       </c>
-      <c r="J80" s="39" t="s">
-        <v>415</v>
-      </c>
-      <c r="K80" s="40" t="s">
-        <v>314</v>
-      </c>
-      <c r="L80" s="39">
+      <c r="K80" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="L80" s="106">
         <v>1</v>
       </c>
-      <c r="M80" s="42">
+      <c r="M80" s="96">
         <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N80" s="42">
+      <c r="N80" s="96">
         <v>21</v>
       </c>
-      <c r="O80" s="65" t="s">
+      <c r="O80" s="108" t="s">
         <v>344</v>
       </c>
-      <c r="P80" s="42">
+      <c r="P80" s="96">
         <v>0.69430000000000003</v>
       </c>
-      <c r="Q80" s="42">
+      <c r="Q80" s="96">
         <f t="shared" ref="Q80" si="71">N80*P80</f>
         <v>14.580300000000001</v>
       </c>
-      <c r="R80" s="89"/>
+      <c r="R80" s="78"/>
     </row>
     <row r="81" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1"/>
@@ -6922,54 +6883,54 @@
         <f>ROW(B81) - ROW($B$9)</f>
         <v>72</v>
       </c>
-      <c r="C81" s="61" t="s">
+      <c r="C81" s="109" t="s">
         <v>329</v>
       </c>
-      <c r="D81" s="37" t="s">
+      <c r="D81" s="110" t="s">
         <v>62</v>
       </c>
-      <c r="E81" s="38" t="s">
+      <c r="E81" s="111" t="s">
         <v>134</v>
       </c>
-      <c r="F81" s="37" t="s">
+      <c r="F81" s="110" t="s">
         <v>310</v>
       </c>
-      <c r="G81" s="38" t="s">
+      <c r="G81" s="111" t="s">
         <v>174</v>
       </c>
-      <c r="H81" s="37" t="s">
+      <c r="H81" s="110" t="s">
         <v>256</v>
       </c>
-      <c r="I81" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="J81" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="K81" s="38" t="s">
-        <v>314</v>
-      </c>
-      <c r="L81" s="37">
+      <c r="I81" s="110" t="s">
+        <v>314</v>
+      </c>
+      <c r="J81" s="110" t="s">
+        <v>314</v>
+      </c>
+      <c r="K81" s="111" t="s">
+        <v>314</v>
+      </c>
+      <c r="L81" s="110">
         <v>1</v>
       </c>
-      <c r="M81" s="41">
+      <c r="M81" s="112">
         <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N81" s="41">
+      <c r="N81" s="112">
         <v>21</v>
       </c>
-      <c r="O81" s="64" t="s">
-        <v>411</v>
-      </c>
-      <c r="P81" s="41">
+      <c r="O81" s="113" t="s">
+        <v>410</v>
+      </c>
+      <c r="P81" s="112">
         <v>3.637</v>
       </c>
-      <c r="Q81" s="41">
+      <c r="Q81" s="112">
         <f t="shared" ref="Q81" si="72">P81*N81</f>
         <v>76.376999999999995</v>
       </c>
-      <c r="R81" s="41"/>
+      <c r="R81" s="112"/>
     </row>
     <row r="82" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1"/>
@@ -6977,54 +6938,54 @@
         <f t="shared" si="0"/>
         <v>73</v>
       </c>
-      <c r="C82" s="60" t="s">
+      <c r="C82" s="105" t="s">
         <v>329</v>
       </c>
-      <c r="D82" s="39" t="s">
+      <c r="D82" s="106" t="s">
         <v>63</v>
       </c>
-      <c r="E82" s="40" t="s">
+      <c r="E82" s="107" t="s">
         <v>135</v>
       </c>
-      <c r="F82" s="39" t="s">
+      <c r="F82" s="106" t="s">
         <v>175</v>
       </c>
-      <c r="G82" s="40" t="s">
+      <c r="G82" s="107" t="s">
         <v>223</v>
       </c>
-      <c r="H82" s="39" t="s">
+      <c r="H82" s="106" t="s">
         <v>256</v>
       </c>
-      <c r="I82" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="J82" s="39" t="s">
-        <v>416</v>
-      </c>
-      <c r="K82" s="40" t="s">
-        <v>314</v>
-      </c>
-      <c r="L82" s="39">
+      <c r="I82" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J82" s="106" t="s">
+        <v>415</v>
+      </c>
+      <c r="K82" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="L82" s="106">
         <v>1</v>
       </c>
-      <c r="M82" s="42">
+      <c r="M82" s="96">
         <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N82" s="42">
+      <c r="N82" s="96">
         <v>21</v>
       </c>
-      <c r="O82" s="65" t="s">
+      <c r="O82" s="108" t="s">
         <v>344</v>
       </c>
-      <c r="P82" s="42">
+      <c r="P82" s="96">
         <v>0.43280000000000002</v>
       </c>
-      <c r="Q82" s="42">
+      <c r="Q82" s="96">
         <f t="shared" ref="Q82" si="73">N82*P82</f>
         <v>9.0888000000000009</v>
       </c>
-      <c r="R82" s="42"/>
+      <c r="R82" s="96"/>
     </row>
     <row r="83" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1"/>
@@ -7032,55 +6993,55 @@
         <f>ROW(B83) - ROW($B$9)</f>
         <v>74</v>
       </c>
-      <c r="C83" s="76" t="s">
+      <c r="C83" s="71" t="s">
         <v>329</v>
       </c>
-      <c r="D83" s="77" t="s">
+      <c r="D83" s="72" t="s">
         <v>64</v>
       </c>
-      <c r="E83" s="78" t="s">
+      <c r="E83" s="73" t="s">
         <v>136</v>
       </c>
-      <c r="F83" s="77" t="s">
+      <c r="F83" s="72" t="s">
         <v>176</v>
       </c>
-      <c r="G83" s="78" t="s">
+      <c r="G83" s="73" t="s">
         <v>224</v>
       </c>
-      <c r="H83" s="77" t="s">
+      <c r="H83" s="72" t="s">
         <v>258</v>
       </c>
-      <c r="I83" s="77" t="s">
-        <v>314</v>
-      </c>
-      <c r="J83" s="77" t="s">
-        <v>417</v>
-      </c>
-      <c r="K83" s="78" t="s">
-        <v>314</v>
-      </c>
-      <c r="L83" s="77">
+      <c r="I83" s="72" t="s">
+        <v>314</v>
+      </c>
+      <c r="J83" s="72" t="s">
+        <v>416</v>
+      </c>
+      <c r="K83" s="73" t="s">
+        <v>314</v>
+      </c>
+      <c r="L83" s="72">
         <v>1</v>
       </c>
-      <c r="M83" s="79">
+      <c r="M83" s="74">
         <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N83" s="79">
+      <c r="N83" s="74">
         <v>21</v>
       </c>
-      <c r="O83" s="80" t="s">
+      <c r="O83" s="75" t="s">
         <v>344</v>
       </c>
-      <c r="P83" s="79">
+      <c r="P83" s="74">
         <v>7.4638</v>
       </c>
-      <c r="Q83" s="79">
+      <c r="Q83" s="74">
         <f t="shared" ref="Q83" si="74">P83*N83</f>
         <v>156.7398</v>
       </c>
-      <c r="R83" s="79" t="s">
-        <v>446</v>
+      <c r="R83" s="74" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="84" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7089,54 +7050,54 @@
         <f t="shared" si="0"/>
         <v>75</v>
       </c>
-      <c r="C84" s="60" t="s">
+      <c r="C84" s="105" t="s">
         <v>329</v>
       </c>
-      <c r="D84" s="39" t="s">
+      <c r="D84" s="106" t="s">
         <v>65</v>
       </c>
-      <c r="E84" s="40" t="s">
+      <c r="E84" s="107" t="s">
         <v>137</v>
       </c>
-      <c r="F84" s="39" t="s">
+      <c r="F84" s="106" t="s">
         <v>177</v>
       </c>
-      <c r="G84" s="40" t="s">
+      <c r="G84" s="107" t="s">
         <v>225</v>
       </c>
-      <c r="H84" s="39" t="s">
+      <c r="H84" s="106" t="s">
         <v>259</v>
       </c>
-      <c r="I84" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="J84" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="K84" s="58" t="s">
+      <c r="I84" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="J84" s="106" t="s">
+        <v>314</v>
+      </c>
+      <c r="K84" s="117" t="s">
         <v>315</v>
       </c>
-      <c r="L84" s="39">
+      <c r="L84" s="106">
         <v>1</v>
       </c>
-      <c r="M84" s="42">
+      <c r="M84" s="96">
         <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N84" s="42">
+      <c r="N84" s="96">
         <v>21</v>
       </c>
-      <c r="O84" s="65" t="s">
-        <v>411</v>
-      </c>
-      <c r="P84" s="42">
+      <c r="O84" s="108" t="s">
+        <v>410</v>
+      </c>
+      <c r="P84" s="96">
         <v>2.6459999999999999</v>
       </c>
-      <c r="Q84" s="42">
+      <c r="Q84" s="96">
         <f t="shared" ref="Q84" si="75">N84*P84</f>
         <v>55.565999999999995</v>
       </c>
-      <c r="R84" s="42"/>
+      <c r="R84" s="96"/>
     </row>
     <row r="85" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="1"/>
@@ -7144,166 +7105,164 @@
         <f>ROW(B85) - ROW($B$9)</f>
         <v>76</v>
       </c>
-      <c r="C85" s="61" t="s">
+      <c r="C85" s="109" t="s">
         <v>329</v>
       </c>
-      <c r="D85" s="37" t="s">
-        <v>466</v>
-      </c>
-      <c r="E85" s="38" t="s">
+      <c r="D85" s="110" t="s">
+        <v>457</v>
+      </c>
+      <c r="E85" s="111" t="s">
         <v>138</v>
       </c>
-      <c r="F85" s="37" t="s">
+      <c r="F85" s="110" t="s">
         <v>311</v>
       </c>
-      <c r="G85" s="38" t="s">
+      <c r="G85" s="111" t="s">
         <v>178</v>
       </c>
-      <c r="H85" s="37" t="s">
+      <c r="H85" s="110" t="s">
         <v>256</v>
       </c>
-      <c r="I85" s="37" t="s">
+      <c r="I85" s="110" t="s">
+        <v>417</v>
+      </c>
+      <c r="J85" s="110" t="s">
         <v>418</v>
       </c>
-      <c r="J85" s="37" t="s">
-        <v>419</v>
-      </c>
-      <c r="K85" s="38" t="s">
-        <v>314</v>
-      </c>
-      <c r="L85" s="96">
+      <c r="K85" s="111" t="s">
+        <v>314</v>
+      </c>
+      <c r="L85" s="118">
         <v>2</v>
       </c>
-      <c r="M85" s="41">
+      <c r="M85" s="112">
         <f t="shared" si="59"/>
         <v>40</v>
       </c>
-      <c r="N85" s="41">
+      <c r="N85" s="112">
         <v>42</v>
       </c>
-      <c r="O85" s="64" t="s">
+      <c r="O85" s="113" t="s">
         <v>344</v>
       </c>
-      <c r="P85" s="41">
+      <c r="P85" s="112">
         <v>2.2974000000000001</v>
       </c>
-      <c r="Q85" s="41">
+      <c r="Q85" s="112">
         <f t="shared" ref="Q85" si="76">P85*N85</f>
         <v>96.490800000000007</v>
       </c>
-      <c r="R85" s="85"/>
-    </row>
-    <row r="86" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="R85" s="79"/>
+    </row>
+    <row r="86" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="1"/>
       <c r="B86" s="53">
-        <f t="shared" si="0"/>
+        <f>ROW(B86) - ROW($B$9)</f>
         <v>77</v>
       </c>
       <c r="C86" s="60" t="s">
         <v>329</v>
       </c>
-      <c r="D86" s="39" t="s">
+      <c r="D86" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="E86" s="40" t="s">
-        <v>139</v>
-      </c>
-      <c r="F86" s="39" t="s">
-        <v>312</v>
-      </c>
-      <c r="G86" s="40" t="s">
-        <v>179</v>
-      </c>
-      <c r="H86" s="39" t="s">
-        <v>259</v>
-      </c>
-      <c r="I86" s="39" t="s">
-        <v>420</v>
-      </c>
-      <c r="J86" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="K86" s="40" t="s">
-        <v>314</v>
-      </c>
-      <c r="L86" s="39">
+      <c r="E86" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="F86" s="37" t="s">
+        <v>313</v>
+      </c>
+      <c r="G86" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="H86" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="I86" s="62" t="s">
+        <v>314</v>
+      </c>
+      <c r="J86" s="62" t="s">
+        <v>421</v>
+      </c>
+      <c r="K86" s="38" t="s">
+        <v>314</v>
+      </c>
+      <c r="L86" s="37">
         <v>1</v>
       </c>
-      <c r="M86" s="42">
-        <f t="shared" si="59"/>
+      <c r="M86" s="41">
+        <f>L86*20</f>
         <v>20</v>
       </c>
-      <c r="N86" s="42">
+      <c r="N86" s="41">
         <v>21</v>
       </c>
-      <c r="O86" s="65" t="s">
-        <v>421</v>
-      </c>
-      <c r="P86" s="42">
-        <v>3.532</v>
-      </c>
-      <c r="Q86" s="42">
-        <f t="shared" ref="Q86" si="77">N86*P86</f>
-        <v>74.171999999999997</v>
-      </c>
-      <c r="R86" s="89" t="s">
-        <v>445</v>
-      </c>
+      <c r="O86" s="63" t="s">
+        <v>344</v>
+      </c>
+      <c r="P86" s="41">
+        <v>0.39140000000000003</v>
+      </c>
+      <c r="Q86" s="41">
+        <f t="shared" ref="Q86" si="77">P86*N86</f>
+        <v>8.2194000000000003</v>
+      </c>
+      <c r="R86" s="41"/>
     </row>
     <row r="87" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="1"/>
       <c r="B87" s="53">
-        <f>ROW(B87) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>78</v>
       </c>
-      <c r="C87" s="61" t="s">
+      <c r="C87" s="59" t="s">
         <v>329</v>
       </c>
-      <c r="D87" s="37" t="s">
-        <v>467</v>
-      </c>
-      <c r="E87" s="38" t="s">
-        <v>140</v>
-      </c>
-      <c r="F87" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="G87" s="38" t="s">
-        <v>180</v>
-      </c>
-      <c r="H87" s="37" t="s">
-        <v>256</v>
-      </c>
-      <c r="I87" s="63" t="s">
-        <v>314</v>
-      </c>
-      <c r="J87" s="63" t="s">
-        <v>422</v>
-      </c>
-      <c r="K87" s="38" t="s">
-        <v>314</v>
-      </c>
-      <c r="L87" s="37">
+      <c r="D87" s="39" t="s">
+        <v>458</v>
+      </c>
+      <c r="E87" s="40" t="s">
+        <v>139</v>
+      </c>
+      <c r="F87" s="39" t="s">
+        <v>312</v>
+      </c>
+      <c r="G87" s="40" t="s">
+        <v>179</v>
+      </c>
+      <c r="H87" s="39" t="s">
+        <v>259</v>
+      </c>
+      <c r="I87" s="39" t="s">
+        <v>419</v>
+      </c>
+      <c r="J87" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="K87" s="40" t="s">
+        <v>314</v>
+      </c>
+      <c r="L87" s="39">
         <v>1</v>
       </c>
-      <c r="M87" s="41">
+      <c r="M87" s="42">
         <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N87" s="41">
+      <c r="N87" s="42">
         <v>21</v>
       </c>
       <c r="O87" s="64" t="s">
-        <v>344</v>
-      </c>
-      <c r="P87" s="41">
-        <v>0.39140000000000003</v>
-      </c>
-      <c r="Q87" s="41">
-        <f t="shared" ref="Q87" si="78">P87*N87</f>
-        <v>8.2194000000000003</v>
-      </c>
-      <c r="R87" s="41"/>
+        <v>420</v>
+      </c>
+      <c r="P87" s="42">
+        <v>3.532</v>
+      </c>
+      <c r="Q87" s="42">
+        <f t="shared" ref="Q87" si="78">N87*P87</f>
+        <v>74.171999999999997</v>
+      </c>
+      <c r="R87" s="79"/>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
@@ -7322,11 +7281,11 @@
       <c r="L88" s="36"/>
       <c r="M88" s="36"/>
       <c r="N88" s="36"/>
-      <c r="O88" s="74" t="s">
-        <v>423</v>
-      </c>
-      <c r="P88" s="72"/>
-      <c r="Q88" s="72">
+      <c r="O88" s="69" t="s">
+        <v>422</v>
+      </c>
+      <c r="P88" s="67"/>
+      <c r="Q88" s="67">
         <f>SUM(Q10:Q87)</f>
         <v>960.72630000000004</v>
       </c>
@@ -7349,11 +7308,11 @@
       <c r="L89" s="9"/>
       <c r="M89" s="9"/>
       <c r="N89" s="9"/>
-      <c r="O89" s="75" t="s">
-        <v>424</v>
-      </c>
-      <c r="P89" s="73"/>
-      <c r="Q89" s="73">
+      <c r="O89" s="70" t="s">
+        <v>423</v>
+      </c>
+      <c r="P89" s="68"/>
+      <c r="Q89" s="68">
         <f>Q88/20</f>
         <v>48.036315000000002</v>
       </c>
@@ -7436,8 +7395,8 @@
     <hyperlink ref="O83" r:id="rId69"/>
     <hyperlink ref="O84" r:id="rId70"/>
     <hyperlink ref="O85" r:id="rId71"/>
-    <hyperlink ref="O86" r:id="rId72"/>
-    <hyperlink ref="O87" r:id="rId73"/>
+    <hyperlink ref="O87" r:id="rId72"/>
+    <hyperlink ref="O86" r:id="rId73"/>
     <hyperlink ref="O56" r:id="rId74"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Deliverables/SM_Top Board/_BOM/eSpark BOM (20 Boards).xlsx
+++ b/Deliverables/SM_Top Board/_BOM/eSpark BOM (20 Boards).xlsx
@@ -2333,6 +2333,51 @@
     <xf numFmtId="0" fontId="25" fillId="6" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2341,51 +2386,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2760,14 +2760,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="101"/>
-      <c r="P1" s="101"/>
-      <c r="Q1" s="101"/>
-      <c r="R1" s="101"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
     </row>
     <row r="2" spans="1:18" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
@@ -2815,7 +2815,7 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="102"/>
+      <c r="R3" s="117"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
@@ -2839,7 +2839,7 @@
       <c r="O4" s="61"/>
       <c r="P4" s="61"/>
       <c r="Q4" s="61"/>
-      <c r="R4" s="103"/>
+      <c r="R4" s="118"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
@@ -2861,7 +2861,7 @@
       <c r="O5" s="61"/>
       <c r="P5" s="61"/>
       <c r="Q5" s="61"/>
-      <c r="R5" s="103"/>
+      <c r="R5" s="118"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
@@ -2881,7 +2881,7 @@
       <c r="O6" s="61"/>
       <c r="P6" s="61"/>
       <c r="Q6" s="61"/>
-      <c r="R6" s="103"/>
+      <c r="R6" s="118"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
@@ -2901,7 +2901,7 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="103"/>
+      <c r="R7" s="118"/>
     </row>
     <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
@@ -2921,7 +2921,7 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="103"/>
+      <c r="R8" s="118"/>
     </row>
     <row r="9" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
@@ -3327,7 +3327,7 @@
       <c r="F16" s="37" t="s">
         <v>143</v>
       </c>
-      <c r="G16" s="104" t="s">
+      <c r="G16" s="101" t="s">
         <v>433</v>
       </c>
       <c r="H16" s="86" t="s">
@@ -3425,34 +3425,34 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="105" t="s">
+      <c r="C18" s="102" t="s">
         <v>317</v>
       </c>
-      <c r="D18" s="106" t="s">
+      <c r="D18" s="103" t="s">
         <v>357</v>
       </c>
-      <c r="E18" s="107" t="s">
+      <c r="E18" s="104" t="s">
         <v>75</v>
       </c>
-      <c r="F18" s="106" t="s">
+      <c r="F18" s="103" t="s">
         <v>145</v>
       </c>
-      <c r="G18" s="107" t="s">
+      <c r="G18" s="104" t="s">
         <v>188</v>
       </c>
-      <c r="H18" s="106" t="s">
+      <c r="H18" s="103" t="s">
         <v>232</v>
       </c>
-      <c r="I18" s="106" t="s">
+      <c r="I18" s="103" t="s">
         <v>352</v>
       </c>
-      <c r="J18" s="106" t="s">
+      <c r="J18" s="103" t="s">
         <v>351</v>
       </c>
-      <c r="K18" s="107" t="s">
+      <c r="K18" s="104" t="s">
         <v>269</v>
       </c>
-      <c r="L18" s="106">
+      <c r="L18" s="103">
         <v>8</v>
       </c>
       <c r="M18" s="96">
@@ -3462,7 +3462,7 @@
       <c r="N18" s="96">
         <v>180</v>
       </c>
-      <c r="O18" s="108" t="s">
+      <c r="O18" s="105" t="s">
         <v>344</v>
       </c>
       <c r="P18" s="96">
@@ -3480,54 +3480,54 @@
         <f>ROW(B19) - ROW($B$9)</f>
         <v>10</v>
       </c>
-      <c r="C19" s="109" t="s">
+      <c r="C19" s="106" t="s">
         <v>317</v>
       </c>
-      <c r="D19" s="110" t="s">
+      <c r="D19" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="111" t="s">
+      <c r="E19" s="108" t="s">
         <v>76</v>
       </c>
-      <c r="F19" s="110" t="s">
+      <c r="F19" s="107" t="s">
         <v>143</v>
       </c>
-      <c r="G19" s="111" t="s">
+      <c r="G19" s="108" t="s">
         <v>189</v>
       </c>
-      <c r="H19" s="110" t="s">
+      <c r="H19" s="107" t="s">
         <v>233</v>
       </c>
-      <c r="I19" s="110" t="s">
+      <c r="I19" s="107" t="s">
         <v>353</v>
       </c>
-      <c r="J19" s="110" t="s">
+      <c r="J19" s="107" t="s">
         <v>354</v>
       </c>
-      <c r="K19" s="111" t="s">
+      <c r="K19" s="108" t="s">
         <v>270</v>
       </c>
-      <c r="L19" s="110">
+      <c r="L19" s="107">
         <v>1</v>
       </c>
-      <c r="M19" s="112">
+      <c r="M19" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N19" s="112">
+      <c r="N19" s="109">
         <v>50</v>
       </c>
-      <c r="O19" s="113" t="s">
+      <c r="O19" s="110" t="s">
         <v>344</v>
       </c>
-      <c r="P19" s="112">
+      <c r="P19" s="109">
         <v>5.3E-3</v>
       </c>
-      <c r="Q19" s="112">
+      <c r="Q19" s="109">
         <f t="shared" ref="Q19" si="8">P19*N19</f>
         <v>0.26500000000000001</v>
       </c>
-      <c r="R19" s="41"/>
+      <c r="R19" s="109"/>
     </row>
     <row r="20" spans="1:18" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1"/>
@@ -3535,34 +3535,34 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="105" t="s">
+      <c r="C20" s="102" t="s">
         <v>317</v>
       </c>
-      <c r="D20" s="106" t="s">
+      <c r="D20" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="E20" s="107" t="s">
+      <c r="E20" s="104" t="s">
         <v>77</v>
       </c>
-      <c r="F20" s="106" t="s">
+      <c r="F20" s="103" t="s">
         <v>308</v>
       </c>
-      <c r="G20" s="106" t="s">
+      <c r="G20" s="103" t="s">
         <v>146</v>
       </c>
-      <c r="H20" s="106" t="s">
+      <c r="H20" s="103" t="s">
         <v>234</v>
       </c>
-      <c r="I20" s="106" t="s">
-        <v>314</v>
-      </c>
-      <c r="J20" s="106" t="s">
+      <c r="I20" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J20" s="103" t="s">
         <v>355</v>
       </c>
-      <c r="K20" s="107" t="s">
+      <c r="K20" s="104" t="s">
         <v>261</v>
       </c>
-      <c r="L20" s="106">
+      <c r="L20" s="103">
         <v>1</v>
       </c>
       <c r="M20" s="96">
@@ -3572,7 +3572,7 @@
       <c r="N20" s="96">
         <v>22</v>
       </c>
-      <c r="O20" s="108" t="s">
+      <c r="O20" s="105" t="s">
         <v>344</v>
       </c>
       <c r="P20" s="96">
@@ -3590,54 +3590,54 @@
         <f>ROW(B21) - ROW($B$9)</f>
         <v>12</v>
       </c>
-      <c r="C21" s="109" t="s">
+      <c r="C21" s="106" t="s">
         <v>317</v>
       </c>
-      <c r="D21" s="110" t="s">
+      <c r="D21" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="E21" s="111" t="s">
+      <c r="E21" s="108" t="s">
         <v>78</v>
       </c>
-      <c r="F21" s="110" t="s">
+      <c r="F21" s="107" t="s">
         <v>144</v>
       </c>
-      <c r="G21" s="111" t="s">
+      <c r="G21" s="108" t="s">
         <v>190</v>
       </c>
-      <c r="H21" s="110" t="s">
+      <c r="H21" s="107" t="s">
         <v>228</v>
       </c>
-      <c r="I21" s="110" t="s">
-        <v>314</v>
-      </c>
-      <c r="J21" s="110" t="s">
+      <c r="I21" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J21" s="107" t="s">
         <v>356</v>
       </c>
-      <c r="K21" s="111" t="s">
+      <c r="K21" s="108" t="s">
         <v>271</v>
       </c>
-      <c r="L21" s="110">
+      <c r="L21" s="107">
         <v>2</v>
       </c>
-      <c r="M21" s="112">
+      <c r="M21" s="109">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N21" s="112">
+      <c r="N21" s="109">
         <v>50</v>
       </c>
-      <c r="O21" s="113" t="s">
+      <c r="O21" s="110" t="s">
         <v>344</v>
       </c>
-      <c r="P21" s="112">
+      <c r="P21" s="109">
         <v>7.7000000000000002E-3</v>
       </c>
-      <c r="Q21" s="112">
+      <c r="Q21" s="109">
         <f t="shared" ref="Q21" si="10">P21*N21</f>
         <v>0.38500000000000001</v>
       </c>
-      <c r="R21" s="41"/>
+      <c r="R21" s="109"/>
     </row>
     <row r="22" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1"/>
@@ -3865,34 +3865,34 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="105" t="s">
+      <c r="C26" s="102" t="s">
         <v>317</v>
       </c>
-      <c r="D26" s="106" t="s">
+      <c r="D26" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="E26" s="114" t="s">
+      <c r="E26" s="111" t="s">
         <v>431</v>
       </c>
-      <c r="F26" s="106" t="s">
+      <c r="F26" s="103" t="s">
         <v>143</v>
       </c>
-      <c r="G26" s="114" t="s">
+      <c r="G26" s="111" t="s">
         <v>459</v>
       </c>
-      <c r="H26" s="115" t="s">
+      <c r="H26" s="112" t="s">
         <v>249</v>
       </c>
-      <c r="I26" s="106" t="s">
-        <v>314</v>
-      </c>
-      <c r="J26" s="106" t="s">
+      <c r="I26" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J26" s="103" t="s">
         <v>432</v>
       </c>
-      <c r="K26" s="114" t="s">
+      <c r="K26" s="111" t="s">
         <v>446</v>
       </c>
-      <c r="L26" s="106">
+      <c r="L26" s="103">
         <v>1</v>
       </c>
       <c r="M26" s="96">
@@ -3902,7 +3902,7 @@
       <c r="N26" s="96">
         <v>100</v>
       </c>
-      <c r="O26" s="108" t="s">
+      <c r="O26" s="105" t="s">
         <v>344</v>
       </c>
       <c r="P26" s="96">
@@ -3920,54 +3920,54 @@
         <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
-      <c r="C27" s="109" t="s">
+      <c r="C27" s="106" t="s">
         <v>317</v>
       </c>
-      <c r="D27" s="110" t="s">
+      <c r="D27" s="107" t="s">
         <v>445</v>
       </c>
-      <c r="E27" s="111" t="s">
+      <c r="E27" s="108" t="s">
         <v>83</v>
       </c>
-      <c r="F27" s="110" t="s">
+      <c r="F27" s="107" t="s">
         <v>147</v>
       </c>
-      <c r="G27" s="111" t="s">
+      <c r="G27" s="108" t="s">
         <v>194</v>
       </c>
-      <c r="H27" s="110" t="s">
+      <c r="H27" s="107" t="s">
         <v>231</v>
       </c>
-      <c r="I27" s="110" t="s">
-        <v>314</v>
-      </c>
-      <c r="J27" s="110" t="s">
+      <c r="I27" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J27" s="107" t="s">
         <v>363</v>
       </c>
-      <c r="K27" s="111" t="s">
+      <c r="K27" s="108" t="s">
         <v>275</v>
       </c>
-      <c r="L27" s="110">
+      <c r="L27" s="107">
         <v>1</v>
       </c>
-      <c r="M27" s="112">
+      <c r="M27" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N27" s="112">
+      <c r="N27" s="109">
         <v>30</v>
       </c>
-      <c r="O27" s="113" t="s">
+      <c r="O27" s="110" t="s">
         <v>344</v>
       </c>
-      <c r="P27" s="112">
+      <c r="P27" s="109">
         <v>0.2525</v>
       </c>
-      <c r="Q27" s="112">
+      <c r="Q27" s="109">
         <f t="shared" ref="Q27" si="16">P27*N27</f>
         <v>7.5750000000000002</v>
       </c>
-      <c r="R27" s="78"/>
+      <c r="R27" s="79"/>
     </row>
     <row r="28" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
@@ -4140,54 +4140,54 @@
         <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
-      <c r="C31" s="109" t="s">
+      <c r="C31" s="106" t="s">
         <v>317</v>
       </c>
-      <c r="D31" s="110" t="s">
+      <c r="D31" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="111" t="s">
+      <c r="E31" s="108" t="s">
         <v>87</v>
       </c>
-      <c r="F31" s="110" t="s">
+      <c r="F31" s="107" t="s">
         <v>143</v>
       </c>
-      <c r="G31" s="111" t="s">
+      <c r="G31" s="108" t="s">
         <v>197</v>
       </c>
-      <c r="H31" s="110" t="s">
+      <c r="H31" s="107" t="s">
         <v>228</v>
       </c>
-      <c r="I31" s="110" t="s">
-        <v>314</v>
-      </c>
-      <c r="J31" s="110" t="s">
+      <c r="I31" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J31" s="107" t="s">
         <v>367</v>
       </c>
-      <c r="K31" s="111" t="s">
+      <c r="K31" s="108" t="s">
         <v>279</v>
       </c>
-      <c r="L31" s="110">
+      <c r="L31" s="107">
         <v>4</v>
       </c>
-      <c r="M31" s="112">
+      <c r="M31" s="109">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N31" s="112">
+      <c r="N31" s="109">
         <v>100</v>
       </c>
-      <c r="O31" s="113" t="s">
+      <c r="O31" s="110" t="s">
         <v>344</v>
       </c>
-      <c r="P31" s="112">
+      <c r="P31" s="109">
         <v>5.4999999999999997E-3</v>
       </c>
-      <c r="Q31" s="112">
+      <c r="Q31" s="109">
         <f t="shared" ref="Q31" si="20">P31*N31</f>
         <v>0.54999999999999993</v>
       </c>
-      <c r="R31" s="41"/>
+      <c r="R31" s="109"/>
     </row>
     <row r="32" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1"/>
@@ -4195,34 +4195,34 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="105" t="s">
+      <c r="C32" s="102" t="s">
         <v>318</v>
       </c>
-      <c r="D32" s="106" t="s">
+      <c r="D32" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="E32" s="107" t="s">
+      <c r="E32" s="104" t="s">
         <v>88</v>
       </c>
-      <c r="F32" s="106" t="s">
+      <c r="F32" s="103" t="s">
         <v>308</v>
       </c>
-      <c r="G32" s="107" t="s">
+      <c r="G32" s="104" t="s">
         <v>150</v>
       </c>
-      <c r="H32" s="106" t="s">
+      <c r="H32" s="103" t="s">
         <v>237</v>
       </c>
-      <c r="I32" s="106" t="s">
-        <v>314</v>
-      </c>
-      <c r="J32" s="106" t="s">
+      <c r="I32" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J32" s="103" t="s">
         <v>368</v>
       </c>
-      <c r="K32" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="L32" s="106">
+      <c r="K32" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L32" s="103">
         <v>1</v>
       </c>
       <c r="M32" s="96">
@@ -4232,7 +4232,7 @@
       <c r="N32" s="96">
         <v>30</v>
       </c>
-      <c r="O32" s="108" t="s">
+      <c r="O32" s="105" t="s">
         <v>344</v>
       </c>
       <c r="P32" s="96">
@@ -4250,54 +4250,54 @@
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
-      <c r="C33" s="109" t="s">
+      <c r="C33" s="106" t="s">
         <v>318</v>
       </c>
-      <c r="D33" s="110" t="s">
+      <c r="D33" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="E33" s="111" t="s">
+      <c r="E33" s="108" t="s">
         <v>89</v>
       </c>
-      <c r="F33" s="110" t="s">
+      <c r="F33" s="107" t="s">
         <v>151</v>
       </c>
-      <c r="G33" s="111" t="s">
+      <c r="G33" s="108" t="s">
         <v>280</v>
       </c>
-      <c r="H33" s="110" t="s">
+      <c r="H33" s="107" t="s">
         <v>238</v>
       </c>
-      <c r="I33" s="110" t="s">
-        <v>314</v>
-      </c>
-      <c r="J33" s="110" t="s">
+      <c r="I33" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J33" s="107" t="s">
         <v>369</v>
       </c>
-      <c r="K33" s="111" t="s">
-        <v>314</v>
-      </c>
-      <c r="L33" s="110">
+      <c r="K33" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L33" s="107">
         <v>1</v>
       </c>
-      <c r="M33" s="112">
+      <c r="M33" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N33" s="112">
+      <c r="N33" s="109">
         <v>30</v>
       </c>
-      <c r="O33" s="113" t="s">
+      <c r="O33" s="110" t="s">
         <v>344</v>
       </c>
-      <c r="P33" s="112">
+      <c r="P33" s="109">
         <v>7.4300000000000005E-2</v>
       </c>
-      <c r="Q33" s="112">
+      <c r="Q33" s="109">
         <f t="shared" ref="Q33" si="22">P33*N33</f>
         <v>2.2290000000000001</v>
       </c>
-      <c r="R33" s="41"/>
+      <c r="R33" s="109"/>
     </row>
     <row r="34" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
@@ -4305,34 +4305,34 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="105" t="s">
+      <c r="C34" s="102" t="s">
         <v>318</v>
       </c>
-      <c r="D34" s="106" t="s">
+      <c r="D34" s="103" t="s">
         <v>464</v>
       </c>
-      <c r="E34" s="107" t="s">
+      <c r="E34" s="104" t="s">
         <v>90</v>
       </c>
-      <c r="F34" s="106" t="s">
+      <c r="F34" s="103" t="s">
         <v>151</v>
       </c>
-      <c r="G34" s="107" t="s">
+      <c r="G34" s="104" t="s">
         <v>281</v>
       </c>
-      <c r="H34" s="106" t="s">
+      <c r="H34" s="103" t="s">
         <v>238</v>
       </c>
-      <c r="I34" s="106" t="s">
+      <c r="I34" s="103" t="s">
         <v>281</v>
       </c>
-      <c r="J34" s="106" t="s">
+      <c r="J34" s="103" t="s">
         <v>370</v>
       </c>
-      <c r="K34" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="L34" s="106">
+      <c r="K34" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L34" s="103">
         <v>2</v>
       </c>
       <c r="M34" s="96">
@@ -4342,7 +4342,7 @@
       <c r="N34" s="96">
         <v>60</v>
       </c>
-      <c r="O34" s="108" t="s">
+      <c r="O34" s="105" t="s">
         <v>344</v>
       </c>
       <c r="P34" s="96">
@@ -4417,34 +4417,34 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="105" t="s">
+      <c r="C36" s="102" t="s">
         <v>320</v>
       </c>
-      <c r="D36" s="106" t="s">
+      <c r="D36" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="E36" s="107" t="s">
+      <c r="E36" s="104" t="s">
         <v>92</v>
       </c>
-      <c r="F36" s="106" t="s">
+      <c r="F36" s="103" t="s">
         <v>308</v>
       </c>
-      <c r="G36" s="107" t="s">
+      <c r="G36" s="104" t="s">
         <v>153</v>
       </c>
-      <c r="H36" s="106" t="s">
+      <c r="H36" s="103" t="s">
         <v>240</v>
       </c>
-      <c r="I36" s="106" t="s">
+      <c r="I36" s="103" t="s">
         <v>373</v>
       </c>
-      <c r="J36" s="106" t="s">
+      <c r="J36" s="103" t="s">
         <v>374</v>
       </c>
-      <c r="K36" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="L36" s="106">
+      <c r="K36" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L36" s="103">
         <v>1</v>
       </c>
       <c r="M36" s="96">
@@ -4454,7 +4454,7 @@
       <c r="N36" s="96">
         <v>30</v>
       </c>
-      <c r="O36" s="108" t="s">
+      <c r="O36" s="105" t="s">
         <v>344</v>
       </c>
       <c r="P36" s="96">
@@ -4472,54 +4472,54 @@
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
-      <c r="C37" s="109" t="s">
+      <c r="C37" s="106" t="s">
         <v>319</v>
       </c>
-      <c r="D37" s="110" t="s">
+      <c r="D37" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="E37" s="111" t="s">
+      <c r="E37" s="108" t="s">
         <v>93</v>
       </c>
-      <c r="F37" s="110" t="s">
+      <c r="F37" s="107" t="s">
         <v>309</v>
       </c>
-      <c r="G37" s="111" t="s">
+      <c r="G37" s="108" t="s">
         <v>154</v>
       </c>
-      <c r="H37" s="110" t="s">
+      <c r="H37" s="107" t="s">
         <v>233</v>
       </c>
-      <c r="I37" s="110" t="s">
-        <v>314</v>
-      </c>
-      <c r="J37" s="110" t="s">
+      <c r="I37" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J37" s="107" t="s">
         <v>375</v>
       </c>
-      <c r="K37" s="111" t="s">
-        <v>314</v>
-      </c>
-      <c r="L37" s="110">
+      <c r="K37" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L37" s="107">
         <v>4</v>
       </c>
-      <c r="M37" s="112">
+      <c r="M37" s="109">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N37" s="112">
+      <c r="N37" s="109">
         <v>100</v>
       </c>
-      <c r="O37" s="113" t="s">
+      <c r="O37" s="110" t="s">
         <v>344</v>
       </c>
-      <c r="P37" s="112">
+      <c r="P37" s="109">
         <v>2.9499999999999998E-2</v>
       </c>
-      <c r="Q37" s="112">
+      <c r="Q37" s="109">
         <f t="shared" ref="Q37" si="26">P37*N37</f>
         <v>2.9499999999999997</v>
       </c>
-      <c r="R37" s="41"/>
+      <c r="R37" s="109"/>
     </row>
     <row r="38" spans="1:18" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1"/>
@@ -4527,34 +4527,34 @@
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="105" t="s">
+      <c r="C38" s="102" t="s">
         <v>321</v>
       </c>
-      <c r="D38" s="106" t="s">
+      <c r="D38" s="103" t="s">
         <v>25</v>
       </c>
-      <c r="E38" s="107" t="s">
+      <c r="E38" s="104" t="s">
         <v>94</v>
       </c>
-      <c r="F38" s="106" t="s">
+      <c r="F38" s="103" t="s">
         <v>308</v>
       </c>
-      <c r="G38" s="107" t="s">
+      <c r="G38" s="104" t="s">
         <v>155</v>
       </c>
-      <c r="H38" s="106" t="s">
+      <c r="H38" s="103" t="s">
         <v>241</v>
       </c>
-      <c r="I38" s="106" t="s">
+      <c r="I38" s="103" t="s">
         <v>376</v>
       </c>
-      <c r="J38" s="106" t="s">
+      <c r="J38" s="103" t="s">
         <v>377</v>
       </c>
-      <c r="K38" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="L38" s="106">
+      <c r="K38" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L38" s="103">
         <v>1</v>
       </c>
       <c r="M38" s="96">
@@ -4564,7 +4564,7 @@
       <c r="N38" s="96">
         <v>21</v>
       </c>
-      <c r="O38" s="108" t="s">
+      <c r="O38" s="105" t="s">
         <v>344</v>
       </c>
       <c r="P38" s="96">
@@ -4582,54 +4582,54 @@
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="109" t="s">
+      <c r="C39" s="106" t="s">
         <v>321</v>
       </c>
-      <c r="D39" s="110" t="s">
+      <c r="D39" s="107" t="s">
         <v>26</v>
       </c>
-      <c r="E39" s="111" t="s">
+      <c r="E39" s="108" t="s">
         <v>95</v>
       </c>
-      <c r="F39" s="110" t="s">
+      <c r="F39" s="107" t="s">
         <v>308</v>
       </c>
-      <c r="G39" s="111" t="s">
+      <c r="G39" s="108" t="s">
         <v>156</v>
       </c>
-      <c r="H39" s="110" t="s">
+      <c r="H39" s="107" t="s">
         <v>242</v>
       </c>
-      <c r="I39" s="110" t="s">
+      <c r="I39" s="107" t="s">
         <v>378</v>
       </c>
-      <c r="J39" s="110" t="s">
+      <c r="J39" s="107" t="s">
         <v>379</v>
       </c>
-      <c r="K39" s="111" t="s">
-        <v>314</v>
-      </c>
-      <c r="L39" s="110">
+      <c r="K39" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L39" s="107">
         <v>2</v>
       </c>
-      <c r="M39" s="112">
+      <c r="M39" s="109">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N39" s="112">
+      <c r="N39" s="109">
         <v>42</v>
       </c>
-      <c r="O39" s="113" t="s">
+      <c r="O39" s="110" t="s">
         <v>344</v>
       </c>
-      <c r="P39" s="112">
+      <c r="P39" s="109">
         <v>0.65639999999999998</v>
       </c>
-      <c r="Q39" s="112">
+      <c r="Q39" s="109">
         <f t="shared" ref="Q39" si="28">P39*N39</f>
         <v>27.5688</v>
       </c>
-      <c r="R39" s="78"/>
+      <c r="R39" s="79"/>
     </row>
     <row r="40" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1"/>
@@ -4637,34 +4637,34 @@
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="105" t="s">
+      <c r="C40" s="102" t="s">
         <v>322</v>
       </c>
-      <c r="D40" s="106" t="s">
+      <c r="D40" s="103" t="s">
         <v>27</v>
       </c>
-      <c r="E40" s="107" t="s">
+      <c r="E40" s="104" t="s">
         <v>96</v>
       </c>
-      <c r="F40" s="106" t="s">
+      <c r="F40" s="103" t="s">
         <v>308</v>
       </c>
-      <c r="G40" s="107" t="s">
+      <c r="G40" s="104" t="s">
         <v>157</v>
       </c>
-      <c r="H40" s="106" t="s">
+      <c r="H40" s="103" t="s">
         <v>243</v>
       </c>
-      <c r="I40" s="106" t="s">
-        <v>314</v>
-      </c>
-      <c r="J40" s="106" t="s">
-        <v>314</v>
-      </c>
-      <c r="K40" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="L40" s="106">
+      <c r="I40" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J40" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="K40" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L40" s="103">
         <v>1</v>
       </c>
       <c r="M40" s="96">
@@ -4674,7 +4674,7 @@
       <c r="N40" s="96">
         <v>21</v>
       </c>
-      <c r="O40" s="108" t="s">
+      <c r="O40" s="105" t="s">
         <v>380</v>
       </c>
       <c r="P40" s="96">
@@ -4692,54 +4692,54 @@
         <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
-      <c r="C41" s="109" t="s">
+      <c r="C41" s="106" t="s">
         <v>322</v>
       </c>
-      <c r="D41" s="110" t="s">
+      <c r="D41" s="107" t="s">
         <v>28</v>
       </c>
-      <c r="E41" s="111" t="s">
+      <c r="E41" s="108" t="s">
         <v>97</v>
       </c>
-      <c r="F41" s="110" t="s">
+      <c r="F41" s="107" t="s">
         <v>308</v>
       </c>
-      <c r="G41" s="111" t="s">
+      <c r="G41" s="108" t="s">
         <v>158</v>
       </c>
-      <c r="H41" s="110" t="s">
+      <c r="H41" s="107" t="s">
         <v>244</v>
       </c>
-      <c r="I41" s="110" t="s">
-        <v>314</v>
-      </c>
-      <c r="J41" s="110" t="s">
+      <c r="I41" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J41" s="107" t="s">
         <v>381</v>
       </c>
-      <c r="K41" s="111" t="s">
-        <v>314</v>
-      </c>
-      <c r="L41" s="110">
+      <c r="K41" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L41" s="107">
         <v>1</v>
       </c>
-      <c r="M41" s="112">
+      <c r="M41" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N41" s="112">
+      <c r="N41" s="109">
         <v>25</v>
       </c>
-      <c r="O41" s="113" t="s">
+      <c r="O41" s="110" t="s">
         <v>344</v>
       </c>
-      <c r="P41" s="112">
+      <c r="P41" s="109">
         <v>9.2200000000000004E-2</v>
       </c>
-      <c r="Q41" s="112">
+      <c r="Q41" s="109">
         <f t="shared" ref="Q41" si="30">P41*N41</f>
         <v>2.3050000000000002</v>
       </c>
-      <c r="R41" s="41"/>
+      <c r="R41" s="109"/>
     </row>
     <row r="42" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1"/>
@@ -4747,34 +4747,34 @@
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="105" t="s">
+      <c r="C42" s="102" t="s">
         <v>319</v>
       </c>
-      <c r="D42" s="106" t="s">
+      <c r="D42" s="103" t="s">
         <v>29</v>
       </c>
-      <c r="E42" s="107" t="s">
+      <c r="E42" s="104" t="s">
         <v>98</v>
       </c>
-      <c r="F42" s="106" t="s">
+      <c r="F42" s="103" t="s">
         <v>308</v>
       </c>
-      <c r="G42" s="107" t="s">
+      <c r="G42" s="104" t="s">
         <v>159</v>
       </c>
-      <c r="H42" s="106" t="s">
+      <c r="H42" s="103" t="s">
         <v>233</v>
       </c>
-      <c r="I42" s="106" t="s">
-        <v>314</v>
-      </c>
-      <c r="J42" s="106" t="s">
+      <c r="I42" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J42" s="103" t="s">
         <v>382</v>
       </c>
-      <c r="K42" s="107" t="s">
+      <c r="K42" s="104" t="s">
         <v>282</v>
       </c>
-      <c r="L42" s="106">
+      <c r="L42" s="103">
         <v>1</v>
       </c>
       <c r="M42" s="96">
@@ -4784,7 +4784,7 @@
       <c r="N42" s="96">
         <v>21</v>
       </c>
-      <c r="O42" s="108" t="s">
+      <c r="O42" s="105" t="s">
         <v>344</v>
       </c>
       <c r="P42" s="96">
@@ -4802,50 +4802,50 @@
         <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
       </c>
-      <c r="C43" s="109" t="s">
+      <c r="C43" s="106" t="s">
         <v>319</v>
       </c>
-      <c r="D43" s="110" t="s">
+      <c r="D43" s="107" t="s">
         <v>30</v>
       </c>
-      <c r="E43" s="111" t="s">
+      <c r="E43" s="108" t="s">
         <v>451</v>
       </c>
-      <c r="F43" s="110" t="s">
+      <c r="F43" s="107" t="s">
         <v>308</v>
       </c>
-      <c r="G43" s="111" t="s">
+      <c r="G43" s="108" t="s">
         <v>450</v>
       </c>
-      <c r="H43" s="110" t="s">
+      <c r="H43" s="107" t="s">
         <v>437</v>
       </c>
-      <c r="I43" s="110" t="s">
-        <v>314</v>
-      </c>
-      <c r="J43" s="110" t="s">
+      <c r="I43" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J43" s="107" t="s">
         <v>438</v>
       </c>
-      <c r="K43" s="111" t="s">
+      <c r="K43" s="108" t="s">
         <v>449</v>
       </c>
-      <c r="L43" s="110">
+      <c r="L43" s="107">
         <v>1</v>
       </c>
-      <c r="M43" s="112">
+      <c r="M43" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N43" s="112">
+      <c r="N43" s="109">
         <v>25</v>
       </c>
-      <c r="O43" s="113" t="s">
+      <c r="O43" s="110" t="s">
         <v>344</v>
       </c>
-      <c r="P43" s="112">
+      <c r="P43" s="109">
         <v>0.1012</v>
       </c>
-      <c r="Q43" s="112">
+      <c r="Q43" s="109">
         <f t="shared" ref="Q43" si="32">P43*N43</f>
         <v>2.5299999999999998</v>
       </c>
@@ -4857,34 +4857,34 @@
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C44" s="105" t="s">
+      <c r="C44" s="102" t="s">
         <v>323</v>
       </c>
-      <c r="D44" s="106" t="s">
+      <c r="D44" s="103" t="s">
         <v>31</v>
       </c>
-      <c r="E44" s="107" t="s">
+      <c r="E44" s="104" t="s">
         <v>99</v>
       </c>
-      <c r="F44" s="106" t="s">
+      <c r="F44" s="103" t="s">
         <v>308</v>
       </c>
-      <c r="G44" s="107" t="s">
+      <c r="G44" s="104" t="s">
         <v>160</v>
       </c>
-      <c r="H44" s="106" t="s">
+      <c r="H44" s="103" t="s">
         <v>245</v>
       </c>
-      <c r="I44" s="106" t="s">
-        <v>314</v>
-      </c>
-      <c r="J44" s="106" t="s">
-        <v>314</v>
-      </c>
-      <c r="K44" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="L44" s="106">
+      <c r="I44" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J44" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="K44" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L44" s="103">
         <v>1</v>
       </c>
       <c r="M44" s="96">
@@ -4894,7 +4894,7 @@
       <c r="N44" s="96">
         <v>30</v>
       </c>
-      <c r="O44" s="108" t="s">
+      <c r="O44" s="105" t="s">
         <v>383</v>
       </c>
       <c r="P44" s="96">
@@ -4912,89 +4912,89 @@
         <f>ROW(B45) - ROW($B$9)</f>
         <v>36</v>
       </c>
-      <c r="C45" s="109" t="s">
+      <c r="C45" s="106" t="s">
         <v>323</v>
       </c>
-      <c r="D45" s="110" t="s">
+      <c r="D45" s="107" t="s">
         <v>32</v>
       </c>
-      <c r="E45" s="111" t="s">
+      <c r="E45" s="108" t="s">
         <v>100</v>
       </c>
-      <c r="F45" s="110" t="s">
+      <c r="F45" s="107" t="s">
         <v>161</v>
       </c>
-      <c r="G45" s="111" t="s">
+      <c r="G45" s="108" t="s">
         <v>199</v>
       </c>
-      <c r="H45" s="110" t="s">
+      <c r="H45" s="107" t="s">
         <v>246</v>
       </c>
-      <c r="I45" s="110" t="s">
-        <v>314</v>
-      </c>
-      <c r="J45" s="110" t="s">
-        <v>314</v>
-      </c>
-      <c r="K45" s="111" t="s">
-        <v>314</v>
-      </c>
-      <c r="L45" s="110">
+      <c r="I45" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J45" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="K45" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L45" s="107">
         <v>1</v>
       </c>
-      <c r="M45" s="112">
+      <c r="M45" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N45" s="112">
+      <c r="N45" s="109">
         <v>30</v>
       </c>
-      <c r="O45" s="113" t="s">
+      <c r="O45" s="110" t="s">
         <v>384</v>
       </c>
-      <c r="P45" s="112">
+      <c r="P45" s="109">
         <v>0.08</v>
       </c>
-      <c r="Q45" s="112">
+      <c r="Q45" s="109">
         <f t="shared" ref="Q45" si="34">P45*N45</f>
         <v>2.4</v>
       </c>
-      <c r="R45" s="112"/>
+      <c r="R45" s="109"/>
     </row>
     <row r="46" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1"/>
-      <c r="B46" s="116">
+      <c r="B46" s="113">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C46" s="105" t="s">
+      <c r="C46" s="102" t="s">
         <v>321</v>
       </c>
-      <c r="D46" s="106" t="s">
+      <c r="D46" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="E46" s="107" t="s">
+      <c r="E46" s="104" t="s">
         <v>101</v>
       </c>
-      <c r="F46" s="106" t="s">
+      <c r="F46" s="103" t="s">
         <v>308</v>
       </c>
-      <c r="G46" s="107" t="s">
+      <c r="G46" s="104" t="s">
         <v>162</v>
       </c>
-      <c r="H46" s="106" t="s">
+      <c r="H46" s="103" t="s">
         <v>247</v>
       </c>
-      <c r="I46" s="106" t="s">
-        <v>314</v>
-      </c>
-      <c r="J46" s="106" t="s">
-        <v>314</v>
-      </c>
-      <c r="K46" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="L46" s="106">
+      <c r="I46" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J46" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="K46" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L46" s="103">
         <v>2</v>
       </c>
       <c r="M46" s="96">
@@ -5004,7 +5004,7 @@
       <c r="N46" s="96">
         <v>50</v>
       </c>
-      <c r="O46" s="108" t="s">
+      <c r="O46" s="105" t="s">
         <v>380</v>
       </c>
       <c r="P46" s="96">
@@ -5072,34 +5072,34 @@
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C48" s="105" t="s">
+      <c r="C48" s="102" t="s">
         <v>322</v>
       </c>
-      <c r="D48" s="106" t="s">
+      <c r="D48" s="103" t="s">
         <v>35</v>
       </c>
-      <c r="E48" s="107" t="s">
+      <c r="E48" s="104" t="s">
         <v>103</v>
       </c>
-      <c r="F48" s="106" t="s">
+      <c r="F48" s="103" t="s">
         <v>164</v>
       </c>
-      <c r="G48" s="107">
+      <c r="G48" s="104">
         <v>61300211121</v>
       </c>
-      <c r="H48" s="106" t="s">
+      <c r="H48" s="103" t="s">
         <v>235</v>
       </c>
-      <c r="I48" s="106" t="s">
-        <v>314</v>
-      </c>
-      <c r="J48" s="106" t="s">
-        <v>314</v>
-      </c>
-      <c r="K48" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="L48" s="106">
+      <c r="I48" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J48" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="K48" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L48" s="103">
         <v>4</v>
       </c>
       <c r="M48" s="96">
@@ -5109,7 +5109,7 @@
       <c r="N48" s="96">
         <v>90</v>
       </c>
-      <c r="O48" s="108" t="s">
+      <c r="O48" s="105" t="s">
         <v>380</v>
       </c>
       <c r="P48" s="96">
@@ -5127,54 +5127,54 @@
         <f>ROW(B49) - ROW($B$9)</f>
         <v>40</v>
       </c>
-      <c r="C49" s="109" t="s">
+      <c r="C49" s="106" t="s">
         <v>324</v>
       </c>
-      <c r="D49" s="110" t="s">
+      <c r="D49" s="107" t="s">
         <v>440</v>
       </c>
-      <c r="E49" s="111" t="s">
+      <c r="E49" s="108" t="s">
         <v>104</v>
       </c>
-      <c r="F49" s="110" t="s">
+      <c r="F49" s="107" t="s">
         <v>165</v>
       </c>
-      <c r="G49" s="111" t="s">
+      <c r="G49" s="108" t="s">
         <v>200</v>
       </c>
-      <c r="H49" s="110" t="s">
+      <c r="H49" s="107" t="s">
         <v>248</v>
       </c>
-      <c r="I49" s="110" t="s">
+      <c r="I49" s="107" t="s">
         <v>386</v>
       </c>
-      <c r="J49" s="110" t="s">
+      <c r="J49" s="107" t="s">
         <v>387</v>
       </c>
-      <c r="K49" s="111" t="s">
-        <v>314</v>
-      </c>
-      <c r="L49" s="110">
+      <c r="K49" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L49" s="107">
         <v>4</v>
       </c>
-      <c r="M49" s="112">
+      <c r="M49" s="109">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N49" s="112">
+      <c r="N49" s="109">
         <v>85</v>
       </c>
-      <c r="O49" s="113" t="s">
+      <c r="O49" s="110" t="s">
         <v>344</v>
       </c>
-      <c r="P49" s="112">
+      <c r="P49" s="109">
         <v>0.21740000000000001</v>
       </c>
-      <c r="Q49" s="112">
+      <c r="Q49" s="109">
         <f t="shared" ref="Q49" si="39">P49*N49</f>
         <v>18.478999999999999</v>
       </c>
-      <c r="R49" s="112"/>
+      <c r="R49" s="109"/>
     </row>
     <row r="50" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1"/>
@@ -5182,34 +5182,34 @@
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="C50" s="105" t="s">
+      <c r="C50" s="102" t="s">
         <v>325</v>
       </c>
-      <c r="D50" s="106" t="s">
+      <c r="D50" s="103" t="s">
         <v>36</v>
       </c>
-      <c r="E50" s="107" t="s">
+      <c r="E50" s="104" t="s">
         <v>105</v>
       </c>
-      <c r="F50" s="106" t="s">
+      <c r="F50" s="103" t="s">
         <v>166</v>
       </c>
-      <c r="G50" s="107" t="s">
+      <c r="G50" s="104" t="s">
         <v>201</v>
       </c>
-      <c r="H50" s="106" t="s">
+      <c r="H50" s="103" t="s">
         <v>229</v>
       </c>
-      <c r="I50" s="106" t="s">
-        <v>314</v>
-      </c>
-      <c r="J50" s="106" t="s">
+      <c r="I50" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J50" s="103" t="s">
         <v>388</v>
       </c>
-      <c r="K50" s="107" t="s">
+      <c r="K50" s="104" t="s">
         <v>284</v>
       </c>
-      <c r="L50" s="106">
+      <c r="L50" s="103">
         <v>2</v>
       </c>
       <c r="M50" s="96">
@@ -5219,7 +5219,7 @@
       <c r="N50" s="96">
         <v>100</v>
       </c>
-      <c r="O50" s="108" t="s">
+      <c r="O50" s="105" t="s">
         <v>344</v>
       </c>
       <c r="P50" s="96">
@@ -5237,54 +5237,54 @@
         <f>ROW(B51) - ROW($B$9)</f>
         <v>42</v>
       </c>
-      <c r="C51" s="109" t="s">
+      <c r="C51" s="106" t="s">
         <v>325</v>
       </c>
-      <c r="D51" s="110" t="s">
+      <c r="D51" s="107" t="s">
         <v>37</v>
       </c>
-      <c r="E51" s="111" t="s">
+      <c r="E51" s="108" t="s">
         <v>106</v>
       </c>
-      <c r="F51" s="110" t="s">
+      <c r="F51" s="107" t="s">
         <v>166</v>
       </c>
-      <c r="G51" s="111" t="s">
+      <c r="G51" s="108" t="s">
         <v>202</v>
       </c>
-      <c r="H51" s="110" t="s">
+      <c r="H51" s="107" t="s">
         <v>229</v>
       </c>
-      <c r="I51" s="110" t="s">
-        <v>314</v>
-      </c>
-      <c r="J51" s="110" t="s">
+      <c r="I51" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J51" s="107" t="s">
         <v>389</v>
       </c>
-      <c r="K51" s="111" t="s">
+      <c r="K51" s="108" t="s">
         <v>285</v>
       </c>
-      <c r="L51" s="110">
+      <c r="L51" s="107">
         <v>1</v>
       </c>
-      <c r="M51" s="112">
+      <c r="M51" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N51" s="112">
+      <c r="N51" s="109">
         <v>100</v>
       </c>
-      <c r="O51" s="113" t="s">
+      <c r="O51" s="110" t="s">
         <v>344</v>
       </c>
-      <c r="P51" s="112">
+      <c r="P51" s="109">
         <v>1.4E-3</v>
       </c>
-      <c r="Q51" s="112">
+      <c r="Q51" s="109">
         <f t="shared" ref="Q51" si="41">P51*N51</f>
         <v>0.13999999999999999</v>
       </c>
-      <c r="R51" s="112"/>
+      <c r="R51" s="109"/>
     </row>
     <row r="52" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1"/>
@@ -5292,34 +5292,34 @@
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="C52" s="105" t="s">
+      <c r="C52" s="102" t="s">
         <v>325</v>
       </c>
-      <c r="D52" s="106" t="s">
+      <c r="D52" s="103" t="s">
         <v>38</v>
       </c>
-      <c r="E52" s="107" t="s">
+      <c r="E52" s="104" t="s">
         <v>107</v>
       </c>
-      <c r="F52" s="106" t="s">
+      <c r="F52" s="103" t="s">
         <v>166</v>
       </c>
-      <c r="G52" s="107" t="s">
+      <c r="G52" s="104" t="s">
         <v>203</v>
       </c>
-      <c r="H52" s="106" t="s">
+      <c r="H52" s="103" t="s">
         <v>249</v>
       </c>
-      <c r="I52" s="106" t="s">
-        <v>314</v>
-      </c>
-      <c r="J52" s="106" t="s">
+      <c r="I52" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J52" s="103" t="s">
         <v>390</v>
       </c>
-      <c r="K52" s="107" t="s">
+      <c r="K52" s="104" t="s">
         <v>286</v>
       </c>
-      <c r="L52" s="106">
+      <c r="L52" s="103">
         <v>1</v>
       </c>
       <c r="M52" s="96">
@@ -5329,7 +5329,7 @@
       <c r="N52" s="96">
         <v>100</v>
       </c>
-      <c r="O52" s="108" t="s">
+      <c r="O52" s="105" t="s">
         <v>344</v>
       </c>
       <c r="P52" s="96">
@@ -5347,54 +5347,54 @@
         <f>ROW(B53) - ROW($B$9)</f>
         <v>44</v>
       </c>
-      <c r="C53" s="109" t="s">
+      <c r="C53" s="106" t="s">
         <v>325</v>
       </c>
-      <c r="D53" s="110" t="s">
+      <c r="D53" s="107" t="s">
         <v>39</v>
       </c>
-      <c r="E53" s="111" t="s">
+      <c r="E53" s="108" t="s">
         <v>108</v>
       </c>
-      <c r="F53" s="110" t="s">
+      <c r="F53" s="107" t="s">
         <v>166</v>
       </c>
-      <c r="G53" s="111" t="s">
+      <c r="G53" s="108" t="s">
         <v>204</v>
       </c>
-      <c r="H53" s="110" t="s">
+      <c r="H53" s="107" t="s">
         <v>229</v>
       </c>
-      <c r="I53" s="110" t="s">
-        <v>314</v>
-      </c>
-      <c r="J53" s="110" t="s">
+      <c r="I53" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J53" s="107" t="s">
         <v>391</v>
       </c>
-      <c r="K53" s="111" t="s">
+      <c r="K53" s="108" t="s">
         <v>287</v>
       </c>
-      <c r="L53" s="110">
+      <c r="L53" s="107">
         <v>2</v>
       </c>
-      <c r="M53" s="112">
+      <c r="M53" s="109">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N53" s="112">
+      <c r="N53" s="109">
         <v>100</v>
       </c>
-      <c r="O53" s="113" t="s">
+      <c r="O53" s="110" t="s">
         <v>344</v>
       </c>
-      <c r="P53" s="112">
+      <c r="P53" s="109">
         <v>1.4E-3</v>
       </c>
-      <c r="Q53" s="112">
+      <c r="Q53" s="109">
         <f t="shared" ref="Q53" si="43">P53*N53</f>
         <v>0.13999999999999999</v>
       </c>
-      <c r="R53" s="112"/>
+      <c r="R53" s="109"/>
     </row>
     <row r="54" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1"/>
@@ -5402,34 +5402,34 @@
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="C54" s="105" t="s">
+      <c r="C54" s="102" t="s">
         <v>325</v>
       </c>
-      <c r="D54" s="106" t="s">
+      <c r="D54" s="103" t="s">
         <v>40</v>
       </c>
-      <c r="E54" s="107" t="s">
+      <c r="E54" s="104" t="s">
         <v>109</v>
       </c>
-      <c r="F54" s="106" t="s">
+      <c r="F54" s="103" t="s">
         <v>166</v>
       </c>
-      <c r="G54" s="107" t="s">
+      <c r="G54" s="104" t="s">
         <v>205</v>
       </c>
-      <c r="H54" s="106" t="s">
+      <c r="H54" s="103" t="s">
         <v>229</v>
       </c>
-      <c r="I54" s="106" t="s">
-        <v>314</v>
-      </c>
-      <c r="J54" s="106" t="s">
+      <c r="I54" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J54" s="103" t="s">
         <v>392</v>
       </c>
-      <c r="K54" s="107" t="s">
+      <c r="K54" s="104" t="s">
         <v>288</v>
       </c>
-      <c r="L54" s="106">
+      <c r="L54" s="103">
         <v>4</v>
       </c>
       <c r="M54" s="96">
@@ -5439,7 +5439,7 @@
       <c r="N54" s="96">
         <v>100</v>
       </c>
-      <c r="O54" s="108" t="s">
+      <c r="O54" s="105" t="s">
         <v>344</v>
       </c>
       <c r="P54" s="96">
@@ -5457,54 +5457,54 @@
         <f>ROW(B55) - ROW($B$9)</f>
         <v>46</v>
       </c>
-      <c r="C55" s="109" t="s">
+      <c r="C55" s="106" t="s">
         <v>325</v>
       </c>
-      <c r="D55" s="110" t="s">
+      <c r="D55" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="E55" s="111" t="s">
+      <c r="E55" s="108" t="s">
         <v>110</v>
       </c>
-      <c r="F55" s="110" t="s">
+      <c r="F55" s="107" t="s">
         <v>167</v>
       </c>
-      <c r="G55" s="111" t="s">
+      <c r="G55" s="108" t="s">
         <v>330</v>
       </c>
-      <c r="H55" s="110" t="s">
+      <c r="H55" s="107" t="s">
         <v>250</v>
       </c>
-      <c r="I55" s="110" t="s">
+      <c r="I55" s="107" t="s">
         <v>393</v>
       </c>
-      <c r="J55" s="110" t="s">
+      <c r="J55" s="107" t="s">
         <v>394</v>
       </c>
-      <c r="K55" s="111" t="s">
+      <c r="K55" s="108" t="s">
         <v>289</v>
       </c>
-      <c r="L55" s="110">
+      <c r="L55" s="107">
         <v>4</v>
       </c>
-      <c r="M55" s="112">
+      <c r="M55" s="109">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N55" s="112">
+      <c r="N55" s="109">
         <v>90</v>
       </c>
-      <c r="O55" s="113" t="s">
+      <c r="O55" s="110" t="s">
         <v>344</v>
       </c>
-      <c r="P55" s="112">
+      <c r="P55" s="109">
         <v>6.4500000000000002E-2</v>
       </c>
-      <c r="Q55" s="112">
+      <c r="Q55" s="109">
         <f t="shared" ref="Q55" si="45">P55*N55</f>
         <v>5.8049999999999997</v>
       </c>
-      <c r="R55" s="112"/>
+      <c r="R55" s="109"/>
     </row>
     <row r="56" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
@@ -5567,54 +5567,54 @@
         <f>ROW(B57) - ROW($B$9)</f>
         <v>48</v>
       </c>
-      <c r="C57" s="109" t="s">
+      <c r="C57" s="106" t="s">
         <v>325</v>
       </c>
-      <c r="D57" s="110" t="s">
+      <c r="D57" s="107" t="s">
         <v>42</v>
       </c>
-      <c r="E57" s="111" t="s">
+      <c r="E57" s="108" t="s">
         <v>112</v>
       </c>
-      <c r="F57" s="110" t="s">
+      <c r="F57" s="107" t="s">
         <v>166</v>
       </c>
-      <c r="G57" s="111" t="s">
+      <c r="G57" s="108" t="s">
         <v>207</v>
       </c>
-      <c r="H57" s="110" t="s">
+      <c r="H57" s="107" t="s">
         <v>251</v>
       </c>
-      <c r="I57" s="110" t="s">
-        <v>314</v>
-      </c>
-      <c r="J57" s="110" t="s">
-        <v>314</v>
-      </c>
-      <c r="K57" s="111" t="s">
+      <c r="I57" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J57" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="K57" s="108" t="s">
         <v>291</v>
       </c>
-      <c r="L57" s="110">
+      <c r="L57" s="107">
         <v>1</v>
       </c>
-      <c r="M57" s="112">
+      <c r="M57" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N57" s="112">
+      <c r="N57" s="109">
         <v>30</v>
       </c>
-      <c r="O57" s="113" t="s">
+      <c r="O57" s="110" t="s">
         <v>383</v>
       </c>
-      <c r="P57" s="112">
+      <c r="P57" s="109">
         <v>1.8589999999999999E-2</v>
       </c>
-      <c r="Q57" s="112">
+      <c r="Q57" s="109">
         <f t="shared" ref="Q57" si="47">P57*N57</f>
         <v>0.55769999999999997</v>
       </c>
-      <c r="R57" s="112"/>
+      <c r="R57" s="109"/>
     </row>
     <row r="58" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1"/>
@@ -5622,34 +5622,34 @@
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="C58" s="105" t="s">
+      <c r="C58" s="102" t="s">
         <v>325</v>
       </c>
-      <c r="D58" s="106" t="s">
+      <c r="D58" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="E58" s="107" t="s">
+      <c r="E58" s="104" t="s">
         <v>113</v>
       </c>
-      <c r="F58" s="106" t="s">
+      <c r="F58" s="103" t="s">
         <v>166</v>
       </c>
-      <c r="G58" s="107" t="s">
+      <c r="G58" s="104" t="s">
         <v>208</v>
       </c>
-      <c r="H58" s="106" t="s">
+      <c r="H58" s="103" t="s">
         <v>229</v>
       </c>
-      <c r="I58" s="106" t="s">
-        <v>314</v>
-      </c>
-      <c r="J58" s="106" t="s">
+      <c r="I58" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J58" s="103" t="s">
         <v>396</v>
       </c>
-      <c r="K58" s="107" t="s">
+      <c r="K58" s="104" t="s">
         <v>292</v>
       </c>
-      <c r="L58" s="106">
+      <c r="L58" s="103">
         <v>1</v>
       </c>
       <c r="M58" s="96">
@@ -5659,7 +5659,7 @@
       <c r="N58" s="96">
         <v>100</v>
       </c>
-      <c r="O58" s="108" t="s">
+      <c r="O58" s="105" t="s">
         <v>344</v>
       </c>
       <c r="P58" s="96">
@@ -5677,54 +5677,54 @@
         <f>ROW(B59) - ROW($B$9)</f>
         <v>50</v>
       </c>
-      <c r="C59" s="109" t="s">
+      <c r="C59" s="106" t="s">
         <v>325</v>
       </c>
-      <c r="D59" s="110" t="s">
+      <c r="D59" s="107" t="s">
         <v>44</v>
       </c>
-      <c r="E59" s="111" t="s">
+      <c r="E59" s="108" t="s">
         <v>114</v>
       </c>
-      <c r="F59" s="110" t="s">
+      <c r="F59" s="107" t="s">
         <v>166</v>
       </c>
-      <c r="G59" s="111" t="s">
+      <c r="G59" s="108" t="s">
         <v>209</v>
       </c>
-      <c r="H59" s="110" t="s">
+      <c r="H59" s="107" t="s">
         <v>251</v>
       </c>
-      <c r="I59" s="110" t="s">
-        <v>314</v>
-      </c>
-      <c r="J59" s="110" t="s">
-        <v>314</v>
-      </c>
-      <c r="K59" s="111" t="s">
+      <c r="I59" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J59" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="K59" s="108" t="s">
         <v>293</v>
       </c>
-      <c r="L59" s="110">
+      <c r="L59" s="107">
         <v>1</v>
       </c>
-      <c r="M59" s="112">
+      <c r="M59" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N59" s="112">
+      <c r="N59" s="109">
         <v>50</v>
       </c>
-      <c r="O59" s="113" t="s">
+      <c r="O59" s="110" t="s">
         <v>383</v>
       </c>
-      <c r="P59" s="112">
+      <c r="P59" s="109">
         <v>4.6699999999999997E-3</v>
       </c>
-      <c r="Q59" s="112">
+      <c r="Q59" s="109">
         <f t="shared" ref="Q59" si="49">P59*N59</f>
         <v>0.23349999999999999</v>
       </c>
-      <c r="R59" s="112"/>
+      <c r="R59" s="109"/>
     </row>
     <row r="60" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1"/>
@@ -5732,34 +5732,34 @@
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="C60" s="105" t="s">
+      <c r="C60" s="102" t="s">
         <v>325</v>
       </c>
-      <c r="D60" s="106" t="s">
+      <c r="D60" s="103" t="s">
         <v>45</v>
       </c>
-      <c r="E60" s="107" t="s">
+      <c r="E60" s="104" t="s">
         <v>115</v>
       </c>
-      <c r="F60" s="106" t="s">
+      <c r="F60" s="103" t="s">
         <v>166</v>
       </c>
-      <c r="G60" s="107" t="s">
+      <c r="G60" s="104" t="s">
         <v>210</v>
       </c>
-      <c r="H60" s="106" t="s">
+      <c r="H60" s="103" t="s">
         <v>229</v>
       </c>
-      <c r="I60" s="106" t="s">
-        <v>314</v>
-      </c>
-      <c r="J60" s="106" t="s">
+      <c r="I60" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J60" s="103" t="s">
         <v>397</v>
       </c>
-      <c r="K60" s="107" t="s">
+      <c r="K60" s="104" t="s">
         <v>294</v>
       </c>
-      <c r="L60" s="106">
+      <c r="L60" s="103">
         <v>1</v>
       </c>
       <c r="M60" s="96">
@@ -5769,7 +5769,7 @@
       <c r="N60" s="96">
         <v>100</v>
       </c>
-      <c r="O60" s="108" t="s">
+      <c r="O60" s="105" t="s">
         <v>344</v>
       </c>
       <c r="P60" s="96">
@@ -5787,54 +5787,54 @@
         <f>ROW(B61) - ROW($B$9)</f>
         <v>52</v>
       </c>
-      <c r="C61" s="109" t="s">
+      <c r="C61" s="106" t="s">
         <v>325</v>
       </c>
-      <c r="D61" s="110" t="s">
+      <c r="D61" s="107" t="s">
         <v>46</v>
       </c>
-      <c r="E61" s="111" t="s">
+      <c r="E61" s="108" t="s">
         <v>116</v>
       </c>
-      <c r="F61" s="110" t="s">
+      <c r="F61" s="107" t="s">
         <v>166</v>
       </c>
-      <c r="G61" s="111" t="s">
+      <c r="G61" s="108" t="s">
         <v>211</v>
       </c>
-      <c r="H61" s="110" t="s">
+      <c r="H61" s="107" t="s">
         <v>251</v>
       </c>
-      <c r="I61" s="110" t="s">
-        <v>314</v>
-      </c>
-      <c r="J61" s="110" t="s">
-        <v>314</v>
-      </c>
-      <c r="K61" s="111" t="s">
+      <c r="I61" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J61" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="K61" s="108" t="s">
         <v>295</v>
       </c>
-      <c r="L61" s="110">
+      <c r="L61" s="107">
         <v>1</v>
       </c>
-      <c r="M61" s="112">
+      <c r="M61" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N61" s="112">
+      <c r="N61" s="109">
         <v>50</v>
       </c>
-      <c r="O61" s="113" t="s">
+      <c r="O61" s="110" t="s">
         <v>383</v>
       </c>
-      <c r="P61" s="112">
+      <c r="P61" s="109">
         <v>1.11E-2</v>
       </c>
-      <c r="Q61" s="112">
+      <c r="Q61" s="109">
         <f t="shared" ref="Q61" si="51">P61*N61</f>
         <v>0.55500000000000005</v>
       </c>
-      <c r="R61" s="112"/>
+      <c r="R61" s="109"/>
     </row>
     <row r="62" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1"/>
@@ -5842,34 +5842,34 @@
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="C62" s="105" t="s">
+      <c r="C62" s="102" t="s">
         <v>325</v>
       </c>
-      <c r="D62" s="106" t="s">
+      <c r="D62" s="103" t="s">
         <v>47</v>
       </c>
-      <c r="E62" s="107" t="s">
+      <c r="E62" s="104" t="s">
         <v>117</v>
       </c>
-      <c r="F62" s="106" t="s">
+      <c r="F62" s="103" t="s">
         <v>166</v>
       </c>
-      <c r="G62" s="107" t="s">
+      <c r="G62" s="104" t="s">
         <v>212</v>
       </c>
-      <c r="H62" s="106" t="s">
+      <c r="H62" s="103" t="s">
         <v>229</v>
       </c>
-      <c r="I62" s="106" t="s">
-        <v>314</v>
-      </c>
-      <c r="J62" s="106" t="s">
+      <c r="I62" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J62" s="103" t="s">
         <v>398</v>
       </c>
-      <c r="K62" s="107" t="s">
+      <c r="K62" s="104" t="s">
         <v>296</v>
       </c>
-      <c r="L62" s="106">
+      <c r="L62" s="103">
         <v>1</v>
       </c>
       <c r="M62" s="96">
@@ -5879,7 +5879,7 @@
       <c r="N62" s="96">
         <v>100</v>
       </c>
-      <c r="O62" s="108" t="s">
+      <c r="O62" s="105" t="s">
         <v>344</v>
       </c>
       <c r="P62" s="96">
@@ -5897,54 +5897,54 @@
         <f>ROW(B63) - ROW($B$9)</f>
         <v>54</v>
       </c>
-      <c r="C63" s="109" t="s">
+      <c r="C63" s="106" t="s">
         <v>325</v>
       </c>
-      <c r="D63" s="110" t="s">
+      <c r="D63" s="107" t="s">
         <v>48</v>
       </c>
-      <c r="E63" s="111" t="s">
+      <c r="E63" s="108" t="s">
         <v>118</v>
       </c>
-      <c r="F63" s="110" t="s">
+      <c r="F63" s="107" t="s">
         <v>166</v>
       </c>
-      <c r="G63" s="111" t="s">
+      <c r="G63" s="108" t="s">
         <v>213</v>
       </c>
-      <c r="H63" s="110" t="s">
+      <c r="H63" s="107" t="s">
         <v>229</v>
       </c>
-      <c r="I63" s="110" t="s">
-        <v>314</v>
-      </c>
-      <c r="J63" s="110" t="s">
+      <c r="I63" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J63" s="107" t="s">
         <v>399</v>
       </c>
-      <c r="K63" s="111" t="s">
+      <c r="K63" s="108" t="s">
         <v>297</v>
       </c>
-      <c r="L63" s="110">
+      <c r="L63" s="107">
         <v>1</v>
       </c>
-      <c r="M63" s="112">
+      <c r="M63" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N63" s="112">
+      <c r="N63" s="109">
         <v>100</v>
       </c>
-      <c r="O63" s="113" t="s">
+      <c r="O63" s="110" t="s">
         <v>344</v>
       </c>
-      <c r="P63" s="112">
+      <c r="P63" s="109">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="Q63" s="112">
+      <c r="Q63" s="109">
         <f t="shared" ref="Q63" si="53">P63*N63</f>
         <v>0.16</v>
       </c>
-      <c r="R63" s="112"/>
+      <c r="R63" s="109"/>
     </row>
     <row r="64" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1"/>
@@ -5952,34 +5952,34 @@
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="C64" s="105" t="s">
+      <c r="C64" s="102" t="s">
         <v>325</v>
       </c>
-      <c r="D64" s="106" t="s">
+      <c r="D64" s="103" t="s">
         <v>49</v>
       </c>
-      <c r="E64" s="107" t="s">
+      <c r="E64" s="104" t="s">
         <v>119</v>
       </c>
-      <c r="F64" s="106" t="s">
+      <c r="F64" s="103" t="s">
         <v>166</v>
       </c>
-      <c r="G64" s="107" t="s">
+      <c r="G64" s="104" t="s">
         <v>214</v>
       </c>
-      <c r="H64" s="106" t="s">
+      <c r="H64" s="103" t="s">
         <v>229</v>
       </c>
-      <c r="I64" s="106" t="s">
+      <c r="I64" s="103" t="s">
         <v>400</v>
       </c>
-      <c r="J64" s="106" t="s">
+      <c r="J64" s="103" t="s">
         <v>401</v>
       </c>
-      <c r="K64" s="107" t="s">
+      <c r="K64" s="104" t="s">
         <v>298</v>
       </c>
-      <c r="L64" s="106">
+      <c r="L64" s="103">
         <v>1</v>
       </c>
       <c r="M64" s="96">
@@ -5989,7 +5989,7 @@
       <c r="N64" s="96">
         <v>50</v>
       </c>
-      <c r="O64" s="108" t="s">
+      <c r="O64" s="105" t="s">
         <v>344</v>
       </c>
       <c r="P64" s="96">
@@ -6007,54 +6007,54 @@
         <f>ROW(B65) - ROW($B$9)</f>
         <v>56</v>
       </c>
-      <c r="C65" s="109" t="s">
+      <c r="C65" s="106" t="s">
         <v>325</v>
       </c>
-      <c r="D65" s="110" t="s">
+      <c r="D65" s="107" t="s">
         <v>465</v>
       </c>
-      <c r="E65" s="111" t="s">
+      <c r="E65" s="108" t="s">
         <v>120</v>
       </c>
-      <c r="F65" s="110" t="s">
+      <c r="F65" s="107" t="s">
         <v>166</v>
       </c>
-      <c r="G65" s="111" t="s">
+      <c r="G65" s="108" t="s">
         <v>215</v>
       </c>
-      <c r="H65" s="110" t="s">
+      <c r="H65" s="107" t="s">
         <v>229</v>
       </c>
-      <c r="I65" s="110" t="s">
-        <v>314</v>
-      </c>
-      <c r="J65" s="110" t="s">
+      <c r="I65" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J65" s="107" t="s">
         <v>402</v>
       </c>
-      <c r="K65" s="111" t="s">
+      <c r="K65" s="108" t="s">
         <v>299</v>
       </c>
-      <c r="L65" s="110">
+      <c r="L65" s="107">
         <v>2</v>
       </c>
-      <c r="M65" s="112">
+      <c r="M65" s="109">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N65" s="112">
+      <c r="N65" s="109">
         <v>100</v>
       </c>
-      <c r="O65" s="113" t="s">
+      <c r="O65" s="110" t="s">
         <v>344</v>
       </c>
-      <c r="P65" s="112">
+      <c r="P65" s="109">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="Q65" s="112">
+      <c r="Q65" s="109">
         <f t="shared" ref="Q65" si="55">P65*N65</f>
         <v>0.11</v>
       </c>
-      <c r="R65" s="112"/>
+      <c r="R65" s="109"/>
     </row>
     <row r="66" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
@@ -6611,34 +6611,34 @@
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="C76" s="105" t="s">
+      <c r="C76" s="102" t="s">
         <v>327</v>
       </c>
-      <c r="D76" s="106" t="s">
+      <c r="D76" s="103" t="s">
         <v>57</v>
       </c>
-      <c r="E76" s="107" t="s">
+      <c r="E76" s="104" t="s">
         <v>129</v>
       </c>
-      <c r="F76" s="106" t="s">
+      <c r="F76" s="103" t="s">
         <v>170</v>
       </c>
-      <c r="G76" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="H76" s="106" t="s">
+      <c r="G76" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="H76" s="103" t="s">
         <v>254</v>
       </c>
-      <c r="I76" s="106" t="s">
-        <v>314</v>
-      </c>
-      <c r="J76" s="106" t="s">
-        <v>314</v>
-      </c>
-      <c r="K76" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="L76" s="106">
+      <c r="I76" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J76" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="K76" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L76" s="103">
         <v>1</v>
       </c>
       <c r="M76" s="96">
@@ -6663,54 +6663,54 @@
         <f>ROW(B77) - ROW($B$9)</f>
         <v>68</v>
       </c>
-      <c r="C77" s="109" t="s">
+      <c r="C77" s="106" t="s">
         <v>328</v>
       </c>
-      <c r="D77" s="110" t="s">
+      <c r="D77" s="107" t="s">
         <v>58</v>
       </c>
-      <c r="E77" s="111" t="s">
+      <c r="E77" s="108" t="s">
         <v>130</v>
       </c>
-      <c r="F77" s="110" t="s">
+      <c r="F77" s="107" t="s">
         <v>308</v>
       </c>
-      <c r="G77" s="111">
+      <c r="G77" s="108">
         <v>750314597</v>
       </c>
-      <c r="H77" s="110" t="s">
+      <c r="H77" s="107" t="s">
         <v>255</v>
       </c>
-      <c r="I77" s="110" t="s">
-        <v>314</v>
-      </c>
-      <c r="J77" s="110" t="s">
-        <v>314</v>
-      </c>
-      <c r="K77" s="111" t="s">
-        <v>314</v>
-      </c>
-      <c r="L77" s="110">
+      <c r="I77" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J77" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="K77" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L77" s="107">
         <v>1</v>
       </c>
-      <c r="M77" s="112">
+      <c r="M77" s="109">
         <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N77" s="112">
+      <c r="N77" s="109">
         <v>21</v>
       </c>
-      <c r="O77" s="113" t="s">
+      <c r="O77" s="110" t="s">
         <v>380</v>
       </c>
-      <c r="P77" s="112">
+      <c r="P77" s="109">
         <v>3.81</v>
       </c>
-      <c r="Q77" s="112">
+      <c r="Q77" s="109">
         <f t="shared" ref="Q77" si="68">P77*N77</f>
         <v>80.010000000000005</v>
       </c>
-      <c r="R77" s="112"/>
+      <c r="R77" s="109"/>
     </row>
     <row r="78" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1"/>
@@ -6718,34 +6718,34 @@
         <f t="shared" si="0"/>
         <v>69</v>
       </c>
-      <c r="C78" s="105" t="s">
+      <c r="C78" s="102" t="s">
         <v>329</v>
       </c>
-      <c r="D78" s="106" t="s">
+      <c r="D78" s="103" t="s">
         <v>59</v>
       </c>
-      <c r="E78" s="107" t="s">
+      <c r="E78" s="104" t="s">
         <v>131</v>
       </c>
-      <c r="F78" s="106" t="s">
+      <c r="F78" s="103" t="s">
         <v>308</v>
       </c>
-      <c r="G78" s="107" t="s">
+      <c r="G78" s="104" t="s">
         <v>171</v>
       </c>
-      <c r="H78" s="106" t="s">
+      <c r="H78" s="103" t="s">
         <v>256</v>
       </c>
-      <c r="I78" s="106" t="s">
-        <v>314</v>
-      </c>
-      <c r="J78" s="106" t="s">
-        <v>314</v>
-      </c>
-      <c r="K78" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="L78" s="106">
+      <c r="I78" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J78" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="K78" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L78" s="103">
         <v>1</v>
       </c>
       <c r="M78" s="96">
@@ -6755,7 +6755,7 @@
       <c r="N78" s="96">
         <v>21</v>
       </c>
-      <c r="O78" s="108" t="s">
+      <c r="O78" s="105" t="s">
         <v>410</v>
       </c>
       <c r="P78" s="96">
@@ -6773,50 +6773,50 @@
         <f>ROW(B79) - ROW($B$9)</f>
         <v>70</v>
       </c>
-      <c r="C79" s="109" t="s">
+      <c r="C79" s="106" t="s">
         <v>329</v>
       </c>
-      <c r="D79" s="110" t="s">
+      <c r="D79" s="107" t="s">
         <v>60</v>
       </c>
-      <c r="E79" s="111" t="s">
+      <c r="E79" s="108" t="s">
         <v>132</v>
       </c>
-      <c r="F79" s="110" t="s">
+      <c r="F79" s="107" t="s">
         <v>172</v>
       </c>
-      <c r="G79" s="111" t="s">
+      <c r="G79" s="108" t="s">
         <v>221</v>
       </c>
-      <c r="H79" s="110" t="s">
+      <c r="H79" s="107" t="s">
         <v>257</v>
       </c>
-      <c r="I79" s="110" t="s">
+      <c r="I79" s="107" t="s">
         <v>411</v>
       </c>
-      <c r="J79" s="110" t="s">
+      <c r="J79" s="107" t="s">
         <v>412</v>
       </c>
-      <c r="K79" s="111" t="s">
-        <v>314</v>
-      </c>
-      <c r="L79" s="110">
+      <c r="K79" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L79" s="107">
         <v>1</v>
       </c>
-      <c r="M79" s="112">
+      <c r="M79" s="109">
         <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N79" s="112">
+      <c r="N79" s="109">
         <v>21</v>
       </c>
-      <c r="O79" s="113" t="s">
+      <c r="O79" s="110" t="s">
         <v>344</v>
       </c>
-      <c r="P79" s="112">
+      <c r="P79" s="109">
         <v>1.3939999999999999</v>
       </c>
-      <c r="Q79" s="112">
+      <c r="Q79" s="109">
         <f t="shared" ref="Q79" si="70">P79*N79</f>
         <v>29.273999999999997</v>
       </c>
@@ -6828,34 +6828,34 @@
         <f t="shared" si="0"/>
         <v>71</v>
       </c>
-      <c r="C80" s="105" t="s">
+      <c r="C80" s="102" t="s">
         <v>329</v>
       </c>
-      <c r="D80" s="106" t="s">
+      <c r="D80" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="E80" s="107" t="s">
+      <c r="E80" s="104" t="s">
         <v>133</v>
       </c>
-      <c r="F80" s="106" t="s">
+      <c r="F80" s="103" t="s">
         <v>173</v>
       </c>
-      <c r="G80" s="107" t="s">
+      <c r="G80" s="104" t="s">
         <v>222</v>
       </c>
-      <c r="H80" s="106" t="s">
+      <c r="H80" s="103" t="s">
         <v>256</v>
       </c>
-      <c r="I80" s="106" t="s">
+      <c r="I80" s="103" t="s">
         <v>413</v>
       </c>
-      <c r="J80" s="106" t="s">
+      <c r="J80" s="103" t="s">
         <v>414</v>
       </c>
-      <c r="K80" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="L80" s="106">
+      <c r="K80" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L80" s="103">
         <v>1</v>
       </c>
       <c r="M80" s="96">
@@ -6865,7 +6865,7 @@
       <c r="N80" s="96">
         <v>21</v>
       </c>
-      <c r="O80" s="108" t="s">
+      <c r="O80" s="105" t="s">
         <v>344</v>
       </c>
       <c r="P80" s="96">
@@ -6883,54 +6883,54 @@
         <f>ROW(B81) - ROW($B$9)</f>
         <v>72</v>
       </c>
-      <c r="C81" s="109" t="s">
+      <c r="C81" s="106" t="s">
         <v>329</v>
       </c>
-      <c r="D81" s="110" t="s">
+      <c r="D81" s="107" t="s">
         <v>62</v>
       </c>
-      <c r="E81" s="111" t="s">
+      <c r="E81" s="108" t="s">
         <v>134</v>
       </c>
-      <c r="F81" s="110" t="s">
+      <c r="F81" s="107" t="s">
         <v>310</v>
       </c>
-      <c r="G81" s="111" t="s">
+      <c r="G81" s="108" t="s">
         <v>174</v>
       </c>
-      <c r="H81" s="110" t="s">
+      <c r="H81" s="107" t="s">
         <v>256</v>
       </c>
-      <c r="I81" s="110" t="s">
-        <v>314</v>
-      </c>
-      <c r="J81" s="110" t="s">
-        <v>314</v>
-      </c>
-      <c r="K81" s="111" t="s">
-        <v>314</v>
-      </c>
-      <c r="L81" s="110">
+      <c r="I81" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="J81" s="107" t="s">
+        <v>314</v>
+      </c>
+      <c r="K81" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L81" s="107">
         <v>1</v>
       </c>
-      <c r="M81" s="112">
+      <c r="M81" s="109">
         <f t="shared" si="59"/>
         <v>20</v>
       </c>
-      <c r="N81" s="112">
+      <c r="N81" s="109">
         <v>21</v>
       </c>
-      <c r="O81" s="113" t="s">
+      <c r="O81" s="110" t="s">
         <v>410</v>
       </c>
-      <c r="P81" s="112">
+      <c r="P81" s="109">
         <v>3.637</v>
       </c>
-      <c r="Q81" s="112">
+      <c r="Q81" s="109">
         <f t="shared" ref="Q81" si="72">P81*N81</f>
         <v>76.376999999999995</v>
       </c>
-      <c r="R81" s="112"/>
+      <c r="R81" s="109"/>
     </row>
     <row r="82" spans="1:18" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1"/>
@@ -6938,34 +6938,34 @@
         <f t="shared" si="0"/>
         <v>73</v>
       </c>
-      <c r="C82" s="105" t="s">
+      <c r="C82" s="102" t="s">
         <v>329</v>
       </c>
-      <c r="D82" s="106" t="s">
+      <c r="D82" s="103" t="s">
         <v>63</v>
       </c>
-      <c r="E82" s="107" t="s">
+      <c r="E82" s="104" t="s">
         <v>135</v>
       </c>
-      <c r="F82" s="106" t="s">
+      <c r="F82" s="103" t="s">
         <v>175</v>
       </c>
-      <c r="G82" s="107" t="s">
+      <c r="G82" s="104" t="s">
         <v>223</v>
       </c>
-      <c r="H82" s="106" t="s">
+      <c r="H82" s="103" t="s">
         <v>256</v>
       </c>
-      <c r="I82" s="106" t="s">
-        <v>314</v>
-      </c>
-      <c r="J82" s="106" t="s">
+      <c r="I82" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J82" s="103" t="s">
         <v>415</v>
       </c>
-      <c r="K82" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="L82" s="106">
+      <c r="K82" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="L82" s="103">
         <v>1</v>
       </c>
       <c r="M82" s="96">
@@ -6975,7 +6975,7 @@
       <c r="N82" s="96">
         <v>21</v>
       </c>
-      <c r="O82" s="108" t="s">
+      <c r="O82" s="105" t="s">
         <v>344</v>
       </c>
       <c r="P82" s="96">
@@ -7050,34 +7050,34 @@
         <f t="shared" si="0"/>
         <v>75</v>
       </c>
-      <c r="C84" s="105" t="s">
+      <c r="C84" s="102" t="s">
         <v>329</v>
       </c>
-      <c r="D84" s="106" t="s">
+      <c r="D84" s="103" t="s">
         <v>65</v>
       </c>
-      <c r="E84" s="107" t="s">
+      <c r="E84" s="104" t="s">
         <v>137</v>
       </c>
-      <c r="F84" s="106" t="s">
+      <c r="F84" s="103" t="s">
         <v>177</v>
       </c>
-      <c r="G84" s="107" t="s">
+      <c r="G84" s="104" t="s">
         <v>225</v>
       </c>
-      <c r="H84" s="106" t="s">
+      <c r="H84" s="103" t="s">
         <v>259</v>
       </c>
-      <c r="I84" s="106" t="s">
-        <v>314</v>
-      </c>
-      <c r="J84" s="106" t="s">
-        <v>314</v>
-      </c>
-      <c r="K84" s="117" t="s">
+      <c r="I84" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="J84" s="103" t="s">
+        <v>314</v>
+      </c>
+      <c r="K84" s="114" t="s">
         <v>315</v>
       </c>
-      <c r="L84" s="106">
+      <c r="L84" s="103">
         <v>1</v>
       </c>
       <c r="M84" s="96">
@@ -7087,7 +7087,7 @@
       <c r="N84" s="96">
         <v>21</v>
       </c>
-      <c r="O84" s="108" t="s">
+      <c r="O84" s="105" t="s">
         <v>410</v>
       </c>
       <c r="P84" s="96">
@@ -7105,50 +7105,50 @@
         <f>ROW(B85) - ROW($B$9)</f>
         <v>76</v>
       </c>
-      <c r="C85" s="109" t="s">
+      <c r="C85" s="106" t="s">
         <v>329</v>
       </c>
-      <c r="D85" s="110" t="s">
+      <c r="D85" s="107" t="s">
         <v>457</v>
       </c>
-      <c r="E85" s="111" t="s">
+      <c r="E85" s="108" t="s">
         <v>138</v>
       </c>
-      <c r="F85" s="110" t="s">
+      <c r="F85" s="107" t="s">
         <v>311</v>
       </c>
-      <c r="G85" s="111" t="s">
+      <c r="G85" s="108" t="s">
         <v>178</v>
       </c>
-      <c r="H85" s="110" t="s">
+      <c r="H85" s="107" t="s">
         <v>256</v>
       </c>
-      <c r="I85" s="110" t="s">
+      <c r="I85" s="107" t="s">
         <v>417</v>
       </c>
-      <c r="J85" s="110" t="s">
+      <c r="J85" s="107" t="s">
         <v>418</v>
       </c>
-      <c r="K85" s="111" t="s">
-        <v>314</v>
-      </c>
-      <c r="L85" s="118">
+      <c r="K85" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="L85" s="115">
         <v>2</v>
       </c>
-      <c r="M85" s="112">
+      <c r="M85" s="109">
         <f t="shared" si="59"/>
         <v>40</v>
       </c>
-      <c r="N85" s="112">
+      <c r="N85" s="109">
         <v>42</v>
       </c>
-      <c r="O85" s="113" t="s">
+      <c r="O85" s="110" t="s">
         <v>344</v>
       </c>
-      <c r="P85" s="112">
+      <c r="P85" s="109">
         <v>2.2974000000000001</v>
       </c>
-      <c r="Q85" s="112">
+      <c r="Q85" s="109">
         <f t="shared" ref="Q85" si="76">P85*N85</f>
         <v>96.490800000000007</v>
       </c>
